--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" activeTab="6"/>
+    <workbookView windowWidth="29868" windowHeight="13451" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="Item" sheetId="1" r:id="rId1"/>
@@ -13,7 +13,10 @@
     <sheet name="BlindBox" sheetId="4" r:id="rId4"/>
     <sheet name="GameDevelopConfig" sheetId="5" r:id="rId5"/>
     <sheet name="PayTable" sheetId="6" r:id="rId6"/>
-    <sheet name="Rarity" sheetId="7" r:id="rId7"/>
+    <sheet name="RarityUI" sheetId="7" r:id="rId7"/>
+    <sheet name="TabGroup" sheetId="8" r:id="rId8"/>
+    <sheet name="DogReaction" sheetId="9" r:id="rId9"/>
+    <sheet name="EquipmentSlotConfig" sheetId="10" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1054" uniqueCount="592">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1343" uniqueCount="717">
   <si>
     <t>##var</t>
   </si>
@@ -47,7 +50,7 @@
     <t>ItemType</t>
   </si>
   <si>
-    <t>Rarity</t>
+    <t>ItemRarity</t>
   </si>
   <si>
     <t>SortOrder</t>
@@ -107,7 +110,7 @@
     <t>内部名称方便记忆</t>
   </si>
   <si>
-    <t>排序权重，数字越大约靠前</t>
+    <t>排序权重，数字越小约靠前</t>
   </si>
   <si>
     <t>盲盒权重</t>
@@ -1326,6 +1329,12 @@
     <t>在全部国家隐藏</t>
   </si>
   <si>
+    <t>Default</t>
+  </si>
+  <si>
+    <t>默认</t>
+  </si>
+  <si>
     <t>小狗头部装饰</t>
   </si>
   <si>
@@ -1341,6 +1350,12 @@
     <t>Saudi Arabia赌博/宗教/酒精/色情/进化论</t>
   </si>
   <si>
+    <t>Serious</t>
+  </si>
+  <si>
+    <t>严肃</t>
+  </si>
+  <si>
     <t>小狗眼部装饰</t>
   </si>
   <si>
@@ -1356,6 +1371,12 @@
     <t>United Arab Emirates赌博/宗教/酒精/色情</t>
   </si>
   <si>
+    <t>Bored</t>
+  </si>
+  <si>
+    <t>无聊</t>
+  </si>
+  <si>
     <t>手臂层的装饰</t>
   </si>
   <si>
@@ -1371,6 +1392,12 @@
     <t>Iran宗教/进化论/赌博/政治/西方文化</t>
   </si>
   <si>
+    <t>Wink</t>
+  </si>
+  <si>
+    <t>媚眼</t>
+  </si>
+  <si>
     <t>玩家手臂衣服</t>
   </si>
   <si>
@@ -1389,6 +1416,12 @@
     <t>Pakistan国家形象/政治</t>
   </si>
   <si>
+    <t>Excited</t>
+  </si>
+  <si>
+    <t>兴奋</t>
+  </si>
+  <si>
     <t>桌布</t>
   </si>
   <si>
@@ -1407,6 +1440,12 @@
     <t>Malaysia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Starstruck</t>
+  </si>
+  <si>
+    <t>崇拜</t>
+  </si>
+  <si>
     <t>背景</t>
   </si>
   <si>
@@ -1419,6 +1458,12 @@
     <t>Indonesia赌博/暴力/LGBTQ/酒精</t>
   </si>
   <si>
+    <t>Silent</t>
+  </si>
+  <si>
+    <t>沉默</t>
+  </si>
+  <si>
     <t>玩家手部装饰</t>
   </si>
   <si>
@@ -1431,6 +1476,12 @@
     <t>Russia赌博/LGBTQ/极端主义</t>
   </si>
   <si>
+    <t>Reject</t>
+  </si>
+  <si>
+    <t>拒绝</t>
+  </si>
+  <si>
     <t>玩家嗜好品</t>
   </si>
   <si>
@@ -1455,6 +1506,9 @@
     <t>North Korea国际制裁/政治</t>
   </si>
   <si>
+    <t>卡面</t>
+  </si>
+  <si>
     <t>SY</t>
   </si>
   <si>
@@ -1488,10 +1542,13 @@
     <t>Head</t>
   </si>
   <si>
-    <t>ClawLucky_Left_Back</t>
-  </si>
-  <si>
-    <t>ClawLucky_Right_Palms</t>
+    <t>Claw_Left_Back</t>
+  </si>
+  <si>
+    <t>Claw_Right_Palms</t>
+  </si>
+  <si>
+    <t>Tongue_Regular</t>
   </si>
   <si>
     <t>Ears_Happy</t>
@@ -1545,6 +1602,9 @@
     <t>狗右爪</t>
   </si>
   <si>
+    <t>舌头</t>
+  </si>
+  <si>
     <t>高兴耳朵</t>
   </si>
   <si>
@@ -1587,10 +1647,13 @@
     <t>Head_Chubby.png</t>
   </si>
   <si>
-    <t>Claw_Lucky_Left.tres</t>
-  </si>
-  <si>
-    <t>Claw_Lucky_Right.tres</t>
+    <t>Claw_Lucky_Left.png</t>
+  </si>
+  <si>
+    <t>Claw_Lucky_Right.png</t>
+  </si>
+  <si>
+    <t>Tongue_Regular.png</t>
   </si>
   <si>
     <t>Ears_Plane.png</t>
@@ -1701,6 +1764,9 @@
     <t>PayoutMultiplier</t>
   </si>
   <si>
+    <t>HandRank</t>
+  </si>
+  <si>
     <t>OriginalName</t>
   </si>
   <si>
@@ -1710,6 +1776,9 @@
     <t>SafeName_CN</t>
   </si>
   <si>
+    <t>EHandRank</t>
+  </si>
+  <si>
     <t>赔率</t>
   </si>
   <si>
@@ -1722,6 +1791,9 @@
     <t>安全中文</t>
   </si>
   <si>
+    <t>JacksOrBetter</t>
+  </si>
+  <si>
     <t>Jacks or Better</t>
   </si>
   <si>
@@ -1731,6 +1803,9 @@
     <t>好犬优选</t>
   </si>
   <si>
+    <t>TwoPair</t>
+  </si>
+  <si>
     <t>Two Pair</t>
   </si>
   <si>
@@ -1740,6 +1815,9 @@
     <t>双犬配对</t>
   </si>
   <si>
+    <t>ThreeOfAKind</t>
+  </si>
+  <si>
     <t>Three of a Kind</t>
   </si>
   <si>
@@ -1767,6 +1845,9 @@
     <t>同色犬舍</t>
   </si>
   <si>
+    <t>FullHouse</t>
+  </si>
+  <si>
     <t>Full House</t>
   </si>
   <si>
@@ -1776,6 +1857,9 @@
     <t>狗狗满堂</t>
   </si>
   <si>
+    <t>FourOfAKind</t>
+  </si>
+  <si>
     <t>Four of a Kind</t>
   </si>
   <si>
@@ -1785,6 +1869,9 @@
     <t>四犬成团</t>
   </si>
   <si>
+    <t>StraightFlush</t>
+  </si>
+  <si>
     <t>Straight Flush</t>
   </si>
   <si>
@@ -1794,6 +1881,9 @@
     <t>纯种犬连击</t>
   </si>
   <si>
+    <t>RoyalFlush</t>
+  </si>
+  <si>
     <t>Royal Flush</t>
   </si>
   <si>
@@ -1809,10 +1899,298 @@
     <t>PlateAssetPath</t>
   </si>
   <si>
+    <t>边框</t>
+  </si>
+  <si>
+    <t>底板</t>
+  </si>
+  <si>
     <t>UI\ItemUI\Frame_Legendary.png</t>
   </si>
   <si>
     <t>UI\ItemUI\Plate_Legendary.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Epic.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Rare.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Common.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special1.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Frame_Special2.png</t>
+  </si>
+  <si>
+    <t>UI\ItemUI\Plate_Special2.png</t>
+  </si>
+  <si>
+    <t>TabName</t>
+  </si>
+  <si>
+    <t>*TabItemTypeList</t>
+  </si>
+  <si>
+    <t>list,EItemType</t>
+  </si>
+  <si>
+    <t>包含类型</t>
+  </si>
+  <si>
+    <t>在标签栏的顺序</t>
+  </si>
+  <si>
+    <t>Hat</t>
+  </si>
+  <si>
+    <t>Eye</t>
+  </si>
+  <si>
+    <t>Player</t>
+  </si>
+  <si>
+    <t>Theme</t>
+  </si>
+  <si>
+    <t>Card</t>
+  </si>
+  <si>
+    <t>DogReactionTrigger</t>
+  </si>
+  <si>
+    <t>AssetRef</t>
+  </si>
+  <si>
+    <t>EarAsset</t>
+  </si>
+  <si>
+    <t>EyeAsset</t>
+  </si>
+  <si>
+    <t>OverrideHeadwear</t>
+  </si>
+  <si>
+    <t>WearGlasses</t>
+  </si>
+  <si>
+    <t>LeftPawAnimation</t>
+  </si>
+  <si>
+    <t>RightPawAnimation</t>
+  </si>
+  <si>
+    <t>TongueAnimation</t>
+  </si>
+  <si>
+    <t>Notes</t>
+  </si>
+  <si>
+    <t>EDogReactionTrigger</t>
+  </si>
+  <si>
+    <t>复用引用枚举所对应的美术资源参数。其自身的值可以Override引用的值</t>
+  </si>
+  <si>
+    <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
+  </si>
+  <si>
+    <t>枚举</t>
+  </si>
+  <si>
+    <t>注释</t>
+  </si>
+  <si>
+    <t>引用枚举</t>
+  </si>
+  <si>
+    <t>耳朵资源</t>
+  </si>
+  <si>
+    <t>眼睛资源</t>
+  </si>
+  <si>
+    <t>头饰变化</t>
+  </si>
+  <si>
+    <t>戴上眼镜</t>
+  </si>
+  <si>
+    <t>左爪子</t>
+  </si>
+  <si>
+    <t>右爪子</t>
+  </si>
+  <si>
+    <t>手背</t>
+  </si>
+  <si>
+    <t>正常</t>
+  </si>
+  <si>
+    <t>手心，摆手</t>
+  </si>
+  <si>
+    <t>WaitingForBet</t>
+  </si>
+  <si>
+    <t>等待下注时</t>
+  </si>
+  <si>
+    <t>默认，该品种狗默认表情</t>
+  </si>
+  <si>
+    <t>Dealt</t>
+  </si>
+  <si>
+    <t>等待玩家选牌</t>
+  </si>
+  <si>
+    <t>WaitingForHint</t>
+  </si>
+  <si>
+    <t>玩家选牌中等待询问时</t>
+  </si>
+  <si>
+    <t>严肃，面无表情，等待玩家询问</t>
+  </si>
+  <si>
+    <t>HintResult</t>
+  </si>
+  <si>
+    <t>展示询问结果</t>
+  </si>
+  <si>
+    <t>Bespoke</t>
+  </si>
+  <si>
+    <t>约定</t>
+  </si>
+  <si>
+    <t>如果玩家进行了询问，再作出相应的预测表情。</t>
+  </si>
+  <si>
+    <t>HintExhausted</t>
+  </si>
+  <si>
+    <t>询问机会用尽</t>
+  </si>
+  <si>
+    <t>如果玩家又更改了选牌，则作出拒绝回答的表情。</t>
+  </si>
+  <si>
+    <t>RefuseHint</t>
+  </si>
+  <si>
+    <t>拒绝询问</t>
+  </si>
+  <si>
+    <t>如果玩家再次询问，则作出拒绝回答的动作。</t>
+  </si>
+  <si>
+    <t>Drawing</t>
+  </si>
+  <si>
+    <t>补牌中</t>
+  </si>
+  <si>
+    <t>严肃，面无表情</t>
+  </si>
+  <si>
+    <t>Settled</t>
+  </si>
+  <si>
+    <t>看到结算结果</t>
+  </si>
+  <si>
+    <t>根据牌型优劣作出相应表情</t>
+  </si>
+  <si>
+    <t>SawNothing</t>
+  </si>
+  <si>
+    <t>看到坏牌</t>
+  </si>
+  <si>
+    <t>SawJacksOrBetter</t>
+  </si>
+  <si>
+    <t>看到高对</t>
+  </si>
+  <si>
+    <t>SawTwoPair</t>
+  </si>
+  <si>
+    <t>看到两对</t>
+  </si>
+  <si>
+    <t>SawThreeOfAKind</t>
+  </si>
+  <si>
+    <t>看到三条</t>
+  </si>
+  <si>
+    <t>SawStraight</t>
+  </si>
+  <si>
+    <t>看到顺子</t>
+  </si>
+  <si>
+    <t>SawFlush</t>
+  </si>
+  <si>
+    <t>看到同花</t>
+  </si>
+  <si>
+    <t>SawFullHouse</t>
+  </si>
+  <si>
+    <t>看到葫芦</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
+  </si>
+  <si>
+    <t>SawFourOfAKind</t>
+  </si>
+  <si>
+    <t>看到四条</t>
+  </si>
+  <si>
+    <t>SawStraightFlush</t>
+  </si>
+  <si>
+    <t>看到同花顺</t>
+  </si>
+  <si>
+    <t>SawRoyalFlush</t>
+  </si>
+  <si>
+    <t>看到皇家同花顺</t>
+  </si>
+  <si>
+    <t>CanUnequip</t>
+  </si>
+  <si>
+    <t>可脱光吗</t>
   </si>
 </sst>
 </file>
@@ -4603,13 +4981,13 @@
         <v>300</v>
       </c>
       <c r="H45">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I45" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L45">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M45" t="s">
         <v>205</v>
@@ -5093,13 +5471,13 @@
         <v>300</v>
       </c>
       <c r="H59">
-        <v>300</v>
+        <v>0</v>
       </c>
       <c r="I59" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L59">
-        <v>1001</v>
+        <v>0</v>
       </c>
       <c r="M59" t="s">
         <v>262</v>
@@ -6558,6 +6936,144 @@
       </c>
       <c r="N98" t="s">
         <v>424</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:C15"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="2"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.0833333333333" customWidth="1"/>
+    <col min="3" max="3" width="11.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:3">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>3</v>
+      </c>
+      <c r="C1" t="s">
+        <v>715</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3">
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3">
+      <c r="B6" t="s">
+        <v>90</v>
+      </c>
+      <c r="C6" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3">
+      <c r="B7" t="s">
+        <v>132</v>
+      </c>
+      <c r="C7" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3">
+      <c r="B8" t="s">
+        <v>153</v>
+      </c>
+      <c r="C8" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:3">
+      <c r="B9" t="s">
+        <v>321</v>
+      </c>
+      <c r="C9" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:3">
+      <c r="B10" t="s">
+        <v>171</v>
+      </c>
+      <c r="C10" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:3">
+      <c r="B11" t="s">
+        <v>204</v>
+      </c>
+      <c r="C11" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:3">
+      <c r="B12" t="s">
+        <v>249</v>
+      </c>
+      <c r="C12" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:3">
+      <c r="B13" t="s">
+        <v>365</v>
+      </c>
+      <c r="C13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3">
+      <c r="B14" t="s">
+        <v>413</v>
+      </c>
+      <c r="C14" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3">
+      <c r="B15" t="s">
+        <v>418</v>
+      </c>
+      <c r="C15" t="b">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6569,311 +7085,335 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="B2:M13"/>
+  <dimension ref="B2:P13"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="11.4166666666667" customWidth="1"/>
-    <col min="11" max="11" width="12.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="12.5833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="2" spans="2:13">
+    <row r="2" spans="2:16">
       <c r="B2" s="4" t="s">
         <v>47</v>
       </c>
       <c r="C2" s="4" t="s">
         <v>425</v>
       </c>
-      <c r="D2" s="4">
+      <c r="E2" s="4" t="s">
+        <v>426</v>
+      </c>
+      <c r="F2" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4" t="s">
+        <v>427</v>
+      </c>
+      <c r="I2" s="4" t="s">
+        <v>154</v>
+      </c>
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="4" t="s">
-        <v>426</v>
-      </c>
-      <c r="H2" s="4" t="s">
-        <v>65</v>
-      </c>
-      <c r="I2" s="4"/>
-      <c r="J2" s="4" t="s">
-        <v>427</v>
-      </c>
       <c r="K2" s="4" t="s">
-        <v>154</v>
-      </c>
-      <c r="L2" s="4">
-        <v>1</v>
-      </c>
-      <c r="M2" s="4" t="s">
         <v>428</v>
       </c>
-    </row>
-    <row r="3" spans="2:13">
+      <c r="O2" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="P2" s="4" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="3" spans="2:16">
       <c r="B3" s="4" t="s">
         <v>90</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>429</v>
-      </c>
-      <c r="D3" s="4">
+        <v>431</v>
+      </c>
+      <c r="E3" s="4" t="s">
+        <v>432</v>
+      </c>
+      <c r="F3" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="G3" s="4"/>
+      <c r="H3" s="4" t="s">
+        <v>433</v>
+      </c>
+      <c r="I3" s="4" t="s">
+        <v>434</v>
+      </c>
+      <c r="J3" s="4">
         <v>2</v>
       </c>
-      <c r="G3" s="4" t="s">
-        <v>430</v>
-      </c>
-      <c r="H3" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="I3" s="4"/>
-      <c r="J3" s="4" t="s">
-        <v>431</v>
-      </c>
       <c r="K3" s="4" t="s">
-        <v>432</v>
-      </c>
-      <c r="L3" s="4">
-        <v>2</v>
-      </c>
-      <c r="M3" s="4" t="s">
-        <v>433</v>
-      </c>
-    </row>
-    <row r="4" spans="2:13">
+        <v>435</v>
+      </c>
+      <c r="O3" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="P3" s="4" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="2:16">
       <c r="B4" s="4" t="s">
         <v>132</v>
       </c>
       <c r="C4" s="4" t="s">
-        <v>434</v>
-      </c>
-      <c r="D4" s="4">
-        <v>3</v>
-      </c>
-      <c r="G4" s="4" t="s">
-        <v>435</v>
-      </c>
+        <v>438</v>
+      </c>
+      <c r="E4" s="4" t="s">
+        <v>439</v>
+      </c>
+      <c r="F4" s="4" t="s">
+        <v>91</v>
+      </c>
+      <c r="G4" s="4"/>
       <c r="H4" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="I4" s="4"/>
-      <c r="J4" s="4" t="s">
-        <v>436</v>
+        <v>440</v>
+      </c>
+      <c r="I4" s="4" t="s">
+        <v>441</v>
+      </c>
+      <c r="J4" s="4">
+        <v>4</v>
       </c>
       <c r="K4" s="4" t="s">
-        <v>437</v>
-      </c>
-      <c r="L4" s="4">
-        <v>4</v>
-      </c>
-      <c r="M4" s="4" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="5" spans="2:13">
+        <v>442</v>
+      </c>
+      <c r="O4" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="P4" s="4" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="5" spans="2:16">
       <c r="B5" s="4" t="s">
         <v>153</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>439</v>
-      </c>
-      <c r="D5" s="4">
-        <v>4</v>
-      </c>
-      <c r="G5" s="4" t="s">
-        <v>440</v>
-      </c>
+        <v>445</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>446</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>366</v>
+      </c>
+      <c r="G5" s="4"/>
       <c r="H5" s="4" t="s">
-        <v>366</v>
-      </c>
-      <c r="I5" s="4"/>
-      <c r="J5" s="4" t="s">
-        <v>441</v>
+        <v>447</v>
+      </c>
+      <c r="I5" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="J5" s="4">
+        <v>8</v>
       </c>
       <c r="K5" s="4" t="s">
-        <v>442</v>
-      </c>
-      <c r="L5" s="4">
-        <v>8</v>
-      </c>
-      <c r="M5" s="4" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="6" spans="2:13">
+        <v>449</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="6" spans="2:16">
       <c r="B6" s="4" t="s">
         <v>171</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>444</v>
-      </c>
-      <c r="D6" s="4">
-        <v>5</v>
-      </c>
-      <c r="G6" s="4" t="s">
-        <v>445</v>
-      </c>
+        <v>452</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>453</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>454</v>
+      </c>
+      <c r="G6" s="4"/>
       <c r="H6" s="4" t="s">
-        <v>446</v>
-      </c>
-      <c r="I6" s="4"/>
-      <c r="J6" s="4" t="s">
-        <v>447</v>
+        <v>455</v>
+      </c>
+      <c r="I6" s="4" t="s">
+        <v>456</v>
+      </c>
+      <c r="J6" s="4">
+        <v>16</v>
       </c>
       <c r="K6" s="4" t="s">
-        <v>448</v>
-      </c>
-      <c r="L6" s="4">
-        <v>16</v>
-      </c>
-      <c r="M6" s="4" t="s">
-        <v>449</v>
-      </c>
-    </row>
-    <row r="7" spans="2:13">
+        <v>457</v>
+      </c>
+      <c r="O6" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="P6" s="4" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="7" spans="2:16">
       <c r="B7" s="4" t="s">
         <v>204</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>450</v>
-      </c>
-      <c r="D7" s="4">
-        <v>6</v>
-      </c>
-      <c r="G7" s="4" t="s">
-        <v>451</v>
-      </c>
+        <v>460</v>
+      </c>
+      <c r="E7" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="G7" s="4"/>
       <c r="H7" s="4" t="s">
-        <v>452</v>
-      </c>
-      <c r="I7" s="4"/>
-      <c r="J7" s="4" t="s">
-        <v>453</v>
+        <v>463</v>
+      </c>
+      <c r="I7" s="4" t="s">
+        <v>464</v>
+      </c>
+      <c r="J7" s="4">
+        <v>32</v>
       </c>
       <c r="K7" s="4" t="s">
-        <v>454</v>
-      </c>
-      <c r="L7" s="4">
-        <v>32</v>
-      </c>
-      <c r="M7" s="4" t="s">
-        <v>455</v>
-      </c>
-    </row>
-    <row r="8" spans="2:13">
+        <v>465</v>
+      </c>
+      <c r="O7" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="P7" s="4" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="8" spans="2:16">
       <c r="B8" s="4" t="s">
         <v>249</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>456</v>
-      </c>
-      <c r="D8" s="4">
-        <v>7</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>457</v>
+        <v>468</v>
+      </c>
+      <c r="H8" s="4" t="s">
+        <v>469</v>
+      </c>
+      <c r="I8" s="4" t="s">
+        <v>470</v>
+      </c>
+      <c r="J8" s="4">
+        <v>64</v>
       </c>
       <c r="K8" s="4" t="s">
-        <v>458</v>
-      </c>
-      <c r="L8" s="4">
-        <v>64</v>
-      </c>
-      <c r="M8" s="4" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="9" spans="2:13">
+        <v>471</v>
+      </c>
+      <c r="O8" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="P8" s="4" t="s">
+        <v>473</v>
+      </c>
+    </row>
+    <row r="9" spans="2:16">
       <c r="B9" s="4" t="s">
         <v>321</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>460</v>
-      </c>
-      <c r="D9" s="4">
-        <v>8</v>
-      </c>
-      <c r="J9" s="4" t="s">
-        <v>461</v>
+        <v>474</v>
+      </c>
+      <c r="H9" s="4" t="s">
+        <v>475</v>
+      </c>
+      <c r="I9" s="4" t="s">
+        <v>476</v>
+      </c>
+      <c r="J9" s="4">
+        <v>128</v>
       </c>
       <c r="K9" s="4" t="s">
-        <v>462</v>
-      </c>
-      <c r="L9" s="4">
-        <v>128</v>
-      </c>
-      <c r="M9" s="4" t="s">
-        <v>463</v>
-      </c>
-    </row>
-    <row r="10" spans="2:13">
+        <v>477</v>
+      </c>
+      <c r="O9" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="P9" s="4" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="10" spans="2:16">
       <c r="B10" s="4" t="s">
         <v>365</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="D10" s="4">
-        <v>9</v>
-      </c>
-      <c r="J10" s="4" t="s">
-        <v>465</v>
+        <v>480</v>
+      </c>
+      <c r="H10" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="I10" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="J10" s="4">
+        <v>256</v>
       </c>
       <c r="K10" s="4" t="s">
-        <v>466</v>
-      </c>
-      <c r="L10" s="4">
-        <v>256</v>
-      </c>
-      <c r="M10" s="4" t="s">
-        <v>467</v>
-      </c>
-    </row>
-    <row r="11" spans="2:13">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="11" spans="2:16">
       <c r="B11" s="4" t="s">
         <v>413</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>468</v>
-      </c>
-      <c r="D11" s="4">
-        <v>10</v>
-      </c>
-      <c r="J11" s="4" t="s">
-        <v>469</v>
+        <v>484</v>
+      </c>
+      <c r="H11" s="4" t="s">
+        <v>485</v>
+      </c>
+      <c r="I11" s="4" t="s">
+        <v>486</v>
+      </c>
+      <c r="J11" s="4">
+        <v>512</v>
       </c>
       <c r="K11" s="4" t="s">
-        <v>470</v>
-      </c>
-      <c r="L11" s="4">
-        <v>512</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="12" spans="2:13">
-      <c r="J12" s="4" t="s">
-        <v>472</v>
+        <v>487</v>
+      </c>
+    </row>
+    <row r="12" spans="2:16">
+      <c r="B12" t="s">
+        <v>418</v>
+      </c>
+      <c r="C12" t="s">
+        <v>488</v>
+      </c>
+      <c r="H12" s="4" t="s">
+        <v>489</v>
+      </c>
+      <c r="I12" s="4" t="s">
+        <v>490</v>
+      </c>
+      <c r="J12" s="4">
+        <v>1024</v>
       </c>
       <c r="K12" s="4" t="s">
-        <v>473</v>
-      </c>
-      <c r="L12" s="4">
-        <v>1024</v>
-      </c>
-      <c r="M12" s="4" t="s">
-        <v>474</v>
-      </c>
-    </row>
-    <row r="13" spans="2:13">
-      <c r="J13" s="4" t="s">
-        <v>475</v>
+        <v>491</v>
+      </c>
+    </row>
+    <row r="13" spans="2:16">
+      <c r="H13" s="4" t="s">
+        <v>492</v>
+      </c>
+      <c r="I13" s="4" t="s">
+        <v>493</v>
+      </c>
+      <c r="J13" s="4">
+        <v>2048</v>
       </c>
       <c r="K13" s="4" t="s">
-        <v>476</v>
-      </c>
-      <c r="L13" s="4">
-        <v>2048</v>
-      </c>
-      <c r="M13" s="4" t="s">
-        <v>477</v>
+        <v>494</v>
       </c>
     </row>
   </sheetData>
@@ -6885,28 +7425,28 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:R16"/>
+  <dimension ref="A1:S16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
     <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="30.1666666666667" customWidth="1"/>
+    <col min="7" max="7" width="15.5" customWidth="1"/>
     <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
     <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="10" width="20.8333333333333" customWidth="1"/>
-    <col min="11" max="11" width="14.5" customWidth="1"/>
-    <col min="12" max="12" width="13.4166666666667" customWidth="1"/>
-    <col min="13" max="13" width="14.3333333333333" customWidth="1"/>
-    <col min="14" max="14" width="13" customWidth="1"/>
-    <col min="15" max="15" width="14.8333333333333" customWidth="1"/>
-    <col min="16" max="16" width="14" customWidth="1"/>
-    <col min="17" max="17" width="15.4166666666667" customWidth="1"/>
-    <col min="18" max="18" width="13.4166666666667" customWidth="1"/>
+    <col min="10" max="11" width="20.8333333333333" customWidth="1"/>
+    <col min="12" max="12" width="14.5" customWidth="1"/>
+    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
+    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="14.8333333333333" customWidth="1"/>
+    <col min="17" max="17" width="14" customWidth="1"/>
+    <col min="18" max="18" width="15.4166666666667" customWidth="1"/>
+    <col min="19" max="19" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18">
+    <row r="1" spans="1:19">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -6915,52 +7455,55 @@
       </c>
       <c r="C1" s="1"/>
       <c r="D1" s="1" t="s">
-        <v>478</v>
+        <v>495</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>479</v>
+        <v>496</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>480</v>
+        <v>497</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>481</v>
+        <v>498</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>482</v>
+        <v>499</v>
       </c>
       <c r="I1" t="s">
-        <v>483</v>
+        <v>500</v>
       </c>
       <c r="J1" t="s">
-        <v>484</v>
+        <v>501</v>
       </c>
       <c r="K1" t="s">
-        <v>485</v>
+        <v>502</v>
       </c>
       <c r="L1" t="s">
-        <v>486</v>
+        <v>503</v>
       </c>
       <c r="M1" t="s">
-        <v>487</v>
+        <v>504</v>
       </c>
       <c r="N1" t="s">
-        <v>488</v>
+        <v>505</v>
       </c>
       <c r="O1" t="s">
-        <v>489</v>
+        <v>506</v>
       </c>
       <c r="P1" t="s">
-        <v>490</v>
+        <v>507</v>
       </c>
       <c r="Q1" t="s">
-        <v>491</v>
+        <v>508</v>
       </c>
       <c r="R1" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18">
+        <v>509</v>
+      </c>
+      <c r="S1" t="s">
+        <v>510</v>
+      </c>
+    </row>
+    <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -7013,8 +7556,11 @@
       <c r="R2" s="1" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:18">
+      <c r="S2" s="1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:19">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
@@ -7022,15 +7568,15 @@
       <c r="C3" s="2"/>
       <c r="D3" s="2"/>
       <c r="E3" s="2" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="F3" s="2" t="s">
-        <v>493</v>
+        <v>511</v>
       </c>
       <c r="G3" s="2"/>
       <c r="H3" s="2"/>
     </row>
-    <row r="4" spans="1:18">
+    <row r="4" spans="1:19">
       <c r="A4" s="2" t="s">
         <v>22</v>
       </c>
@@ -7038,108 +7584,114 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>494</v>
+        <v>512</v>
       </c>
       <c r="D4" t="s">
-        <v>495</v>
+        <v>513</v>
       </c>
       <c r="E4" t="s">
-        <v>496</v>
+        <v>514</v>
       </c>
       <c r="F4" t="s">
-        <v>497</v>
+        <v>515</v>
       </c>
       <c r="G4" t="s">
-        <v>498</v>
+        <v>516</v>
       </c>
       <c r="H4" t="s">
-        <v>499</v>
+        <v>517</v>
       </c>
       <c r="I4" t="s">
-        <v>500</v>
+        <v>518</v>
       </c>
       <c r="J4" t="s">
-        <v>501</v>
+        <v>519</v>
       </c>
       <c r="K4" t="s">
-        <v>502</v>
+        <v>520</v>
       </c>
       <c r="L4" t="s">
-        <v>503</v>
+        <v>521</v>
       </c>
       <c r="M4" t="s">
-        <v>504</v>
+        <v>522</v>
       </c>
       <c r="N4" t="s">
-        <v>505</v>
+        <v>523</v>
       </c>
       <c r="O4" t="s">
-        <v>506</v>
+        <v>524</v>
       </c>
       <c r="P4" t="s">
-        <v>507</v>
+        <v>525</v>
       </c>
       <c r="Q4" t="s">
-        <v>508</v>
+        <v>526</v>
       </c>
       <c r="R4" t="s">
-        <v>509</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18">
+        <v>527</v>
+      </c>
+      <c r="S4" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>510</v>
+        <v>529</v>
       </c>
       <c r="D5" t="s">
-        <v>511</v>
+        <v>530</v>
       </c>
       <c r="E5" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F5" t="s">
-        <v>513</v>
+        <v>532</v>
       </c>
       <c r="G5" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H5" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I5" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J5" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K5" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L5" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M5" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N5" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O5" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P5" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q5" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R5" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19">
       <c r="B6">
         <v>1002</v>
       </c>
@@ -7147,52 +7699,55 @@
         <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>524</v>
+        <v>544</v>
       </c>
       <c r="E6" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F6" t="s">
-        <v>520</v>
+        <v>540</v>
       </c>
       <c r="G6" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="H6" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I6" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J6" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K6" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L6" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M6" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N6" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O6" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P6" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q6" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R6" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S6" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="B7">
         <v>1003</v>
       </c>
@@ -7200,52 +7755,55 @@
         <v>56</v>
       </c>
       <c r="D7" t="s">
-        <v>526</v>
+        <v>546</v>
       </c>
       <c r="E7" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F7" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="G7" t="s">
-        <v>527</v>
+        <v>547</v>
       </c>
       <c r="H7" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I7" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J7" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K7" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L7" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M7" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N7" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O7" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P7" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q7" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R7" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S7" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="8" spans="1:19">
       <c r="B8">
         <v>1004</v>
       </c>
@@ -7253,52 +7811,55 @@
         <v>60</v>
       </c>
       <c r="D8" t="s">
-        <v>528</v>
+        <v>548</v>
       </c>
       <c r="E8" t="s">
-        <v>518</v>
+        <v>538</v>
       </c>
       <c r="F8" t="s">
-        <v>519</v>
+        <v>539</v>
       </c>
       <c r="G8" t="s">
-        <v>529</v>
+        <v>549</v>
       </c>
       <c r="H8" t="s">
-        <v>515</v>
+        <v>534</v>
       </c>
       <c r="I8" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J8" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K8" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L8" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M8" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N8" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O8" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P8" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q8" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R8" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S8" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="9" spans="1:19">
       <c r="B9">
         <v>1005</v>
       </c>
@@ -7306,52 +7867,55 @@
         <v>64</v>
       </c>
       <c r="D9" t="s">
-        <v>530</v>
+        <v>550</v>
       </c>
       <c r="E9" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F9" t="s">
-        <v>521</v>
+        <v>541</v>
       </c>
       <c r="G9" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H9" t="s">
+        <v>551</v>
+      </c>
+      <c r="I9" t="s">
+        <v>535</v>
+      </c>
+      <c r="J9" t="s">
+        <v>536</v>
+      </c>
+      <c r="K9" t="s">
+        <v>537</v>
+      </c>
+      <c r="L9" t="s">
         <v>531</v>
       </c>
-      <c r="I9" t="s">
-        <v>516</v>
-      </c>
-      <c r="J9" t="s">
-        <v>517</v>
-      </c>
-      <c r="K9" t="s">
-        <v>512</v>
-      </c>
-      <c r="L9" t="s">
-        <v>518</v>
-      </c>
       <c r="M9" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N9" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O9" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P9" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q9" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R9" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S9" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="10" spans="1:19">
       <c r="B10">
         <v>1006</v>
       </c>
@@ -7359,52 +7923,55 @@
         <v>68</v>
       </c>
       <c r="D10" t="s">
+        <v>552</v>
+      </c>
+      <c r="E10" t="s">
+        <v>538</v>
+      </c>
+      <c r="F10" t="s">
         <v>532</v>
       </c>
-      <c r="E10" t="s">
-        <v>518</v>
-      </c>
-      <c r="F10" t="s">
-        <v>513</v>
-      </c>
       <c r="G10" t="s">
-        <v>514</v>
+        <v>533</v>
       </c>
       <c r="H10" t="s">
-        <v>533</v>
+        <v>553</v>
       </c>
       <c r="I10" t="s">
-        <v>516</v>
+        <v>535</v>
       </c>
       <c r="J10" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K10" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L10" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M10" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N10" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O10" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P10" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q10" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R10" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S10" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="11" spans="1:19">
       <c r="B11">
         <v>1007</v>
       </c>
@@ -7412,52 +7979,55 @@
         <v>71</v>
       </c>
       <c r="D11" t="s">
-        <v>534</v>
+        <v>554</v>
       </c>
       <c r="E11" t="s">
-        <v>512</v>
+        <v>531</v>
       </c>
       <c r="F11" t="s">
-        <v>523</v>
+        <v>543</v>
       </c>
       <c r="G11" t="s">
-        <v>525</v>
+        <v>545</v>
       </c>
       <c r="H11" t="s">
+        <v>551</v>
+      </c>
+      <c r="I11" t="s">
+        <v>535</v>
+      </c>
+      <c r="J11" t="s">
+        <v>536</v>
+      </c>
+      <c r="K11" t="s">
+        <v>537</v>
+      </c>
+      <c r="L11" t="s">
         <v>531</v>
       </c>
-      <c r="I11" t="s">
-        <v>516</v>
-      </c>
-      <c r="J11" t="s">
-        <v>517</v>
-      </c>
-      <c r="K11" t="s">
-        <v>512</v>
-      </c>
-      <c r="L11" t="s">
-        <v>518</v>
-      </c>
       <c r="M11" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N11" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O11" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P11" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q11" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R11" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S11" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="12" spans="1:19">
       <c r="B12">
         <v>1008</v>
       </c>
@@ -7465,52 +8035,55 @@
         <v>74</v>
       </c>
       <c r="D12" t="s">
+        <v>555</v>
+      </c>
+      <c r="E12" t="s">
+        <v>531</v>
+      </c>
+      <c r="F12" t="s">
+        <v>532</v>
+      </c>
+      <c r="G12" t="s">
+        <v>545</v>
+      </c>
+      <c r="H12" t="s">
+        <v>553</v>
+      </c>
+      <c r="I12" t="s">
         <v>535</v>
       </c>
-      <c r="E12" t="s">
-        <v>512</v>
-      </c>
-      <c r="F12" t="s">
-        <v>513</v>
-      </c>
-      <c r="G12" t="s">
-        <v>525</v>
-      </c>
-      <c r="H12" t="s">
-        <v>533</v>
-      </c>
-      <c r="I12" t="s">
-        <v>516</v>
-      </c>
       <c r="J12" t="s">
-        <v>517</v>
+        <v>536</v>
       </c>
       <c r="K12" t="s">
-        <v>512</v>
+        <v>537</v>
       </c>
       <c r="L12" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M12" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N12" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O12" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P12" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q12" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R12" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="13" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S12" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:19">
       <c r="B13">
         <v>1009</v>
       </c>
@@ -7518,52 +8091,55 @@
         <v>77</v>
       </c>
       <c r="D13" t="s">
+        <v>556</v>
+      </c>
+      <c r="E13" t="s">
+        <v>531</v>
+      </c>
+      <c r="F13" t="s">
+        <v>543</v>
+      </c>
+      <c r="G13" t="s">
+        <v>547</v>
+      </c>
+      <c r="H13" t="s">
+        <v>551</v>
+      </c>
+      <c r="I13" t="s">
+        <v>535</v>
+      </c>
+      <c r="J13" t="s">
         <v>536</v>
       </c>
-      <c r="E13" t="s">
-        <v>512</v>
-      </c>
-      <c r="F13" t="s">
-        <v>523</v>
-      </c>
-      <c r="G13" t="s">
-        <v>527</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="K13" t="s">
+        <v>537</v>
+      </c>
+      <c r="L13" t="s">
         <v>531</v>
       </c>
-      <c r="I13" t="s">
-        <v>516</v>
-      </c>
-      <c r="J13" t="s">
-        <v>517</v>
-      </c>
-      <c r="K13" t="s">
-        <v>512</v>
-      </c>
-      <c r="L13" t="s">
-        <v>518</v>
-      </c>
       <c r="M13" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N13" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O13" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P13" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q13" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R13" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="14" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S13" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="14" spans="1:19">
       <c r="B14">
         <v>1010</v>
       </c>
@@ -7571,52 +8147,55 @@
         <v>80</v>
       </c>
       <c r="D14" t="s">
+        <v>557</v>
+      </c>
+      <c r="E14" t="s">
+        <v>531</v>
+      </c>
+      <c r="F14" t="s">
+        <v>532</v>
+      </c>
+      <c r="G14" t="s">
+        <v>547</v>
+      </c>
+      <c r="H14" t="s">
+        <v>553</v>
+      </c>
+      <c r="I14" t="s">
+        <v>535</v>
+      </c>
+      <c r="J14" t="s">
+        <v>536</v>
+      </c>
+      <c r="K14" t="s">
         <v>537</v>
       </c>
-      <c r="E14" t="s">
-        <v>512</v>
-      </c>
-      <c r="F14" t="s">
-        <v>513</v>
-      </c>
-      <c r="G14" t="s">
-        <v>527</v>
-      </c>
-      <c r="H14" t="s">
-        <v>533</v>
-      </c>
-      <c r="I14" t="s">
-        <v>516</v>
-      </c>
-      <c r="J14" t="s">
-        <v>517</v>
-      </c>
-      <c r="K14" t="s">
-        <v>512</v>
-      </c>
       <c r="L14" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="M14" t="s">
-        <v>519</v>
+        <v>538</v>
       </c>
       <c r="N14" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O14" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P14" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q14" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R14" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S14" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="15" spans="1:19">
       <c r="B15">
         <v>1011</v>
       </c>
@@ -7624,102 +8203,108 @@
         <v>83</v>
       </c>
       <c r="D15" t="s">
+        <v>558</v>
+      </c>
+      <c r="E15" t="s">
+        <v>531</v>
+      </c>
+      <c r="F15" t="s">
+        <v>532</v>
+      </c>
+      <c r="G15" t="s">
+        <v>549</v>
+      </c>
+      <c r="H15" t="s">
+        <v>551</v>
+      </c>
+      <c r="I15" t="s">
+        <v>535</v>
+      </c>
+      <c r="J15" t="s">
+        <v>536</v>
+      </c>
+      <c r="K15" t="s">
+        <v>537</v>
+      </c>
+      <c r="L15" t="s">
+        <v>531</v>
+      </c>
+      <c r="M15" t="s">
         <v>538</v>
       </c>
-      <c r="E15" t="s">
-        <v>512</v>
-      </c>
-      <c r="F15" t="s">
-        <v>513</v>
-      </c>
-      <c r="G15" t="s">
-        <v>529</v>
-      </c>
-      <c r="H15" t="s">
-        <v>531</v>
-      </c>
-      <c r="I15" t="s">
-        <v>516</v>
-      </c>
-      <c r="J15" t="s">
-        <v>517</v>
-      </c>
-      <c r="K15" t="s">
-        <v>512</v>
-      </c>
-      <c r="L15" t="s">
-        <v>518</v>
-      </c>
-      <c r="M15" t="s">
-        <v>519</v>
-      </c>
       <c r="N15" t="s">
-        <v>513</v>
+        <v>539</v>
       </c>
       <c r="O15" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="P15" t="s">
-        <v>521</v>
+        <v>540</v>
       </c>
       <c r="Q15" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R15" t="s">
-        <v>523</v>
-      </c>
-    </row>
-    <row r="16" spans="1:18">
+        <v>542</v>
+      </c>
+      <c r="S15" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="16" spans="1:19">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
+        <v>559</v>
+      </c>
+      <c r="D16" t="s">
+        <v>560</v>
+      </c>
+      <c r="E16" t="s">
+        <v>531</v>
+      </c>
+      <c r="F16" t="s">
+        <v>542</v>
+      </c>
+      <c r="G16" t="s">
+        <v>549</v>
+      </c>
+      <c r="H16" t="s">
+        <v>553</v>
+      </c>
+      <c r="I16" t="s">
+        <v>535</v>
+      </c>
+      <c r="J16" t="s">
+        <v>536</v>
+      </c>
+      <c r="K16" t="s">
+        <v>537</v>
+      </c>
+      <c r="L16" t="s">
+        <v>531</v>
+      </c>
+      <c r="M16" t="s">
+        <v>538</v>
+      </c>
+      <c r="N16" t="s">
         <v>539</v>
       </c>
-      <c r="D16" t="s">
+      <c r="O16" t="s">
+        <v>532</v>
+      </c>
+      <c r="P16" t="s">
         <v>540</v>
       </c>
-      <c r="E16" t="s">
-        <v>512</v>
-      </c>
-      <c r="F16" t="s">
-        <v>522</v>
-      </c>
-      <c r="G16" t="s">
-        <v>529</v>
-      </c>
-      <c r="H16" t="s">
-        <v>533</v>
-      </c>
-      <c r="I16" t="s">
-        <v>516</v>
-      </c>
-      <c r="J16" t="s">
-        <v>517</v>
-      </c>
-      <c r="K16" t="s">
-        <v>512</v>
-      </c>
-      <c r="L16" t="s">
-        <v>518</v>
-      </c>
-      <c r="M16" t="s">
-        <v>519</v>
-      </c>
-      <c r="N16" t="s">
-        <v>513</v>
-      </c>
-      <c r="O16" t="s">
-        <v>520</v>
-      </c>
-      <c r="P16" t="s">
-        <v>521</v>
-      </c>
       <c r="Q16" t="s">
-        <v>522</v>
+        <v>541</v>
       </c>
       <c r="R16" t="s">
-        <v>523</v>
+        <v>542</v>
+      </c>
+      <c r="S16" t="s">
+        <v>543</v>
       </c>
     </row>
   </sheetData>
@@ -7747,10 +8332,10 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>541</v>
+        <v>561</v>
       </c>
       <c r="D1" t="s">
-        <v>542</v>
+        <v>562</v>
       </c>
       <c r="E1" t="s">
         <v>12</v>
@@ -7764,7 +8349,7 @@
         <v>15</v>
       </c>
       <c r="C2" t="s">
-        <v>543</v>
+        <v>563</v>
       </c>
       <c r="D2" t="s">
         <v>15</v>
@@ -7781,10 +8366,10 @@
         <v>32</v>
       </c>
       <c r="C3" t="s">
-        <v>544</v>
+        <v>564</v>
       </c>
       <c r="D3" t="s">
-        <v>545</v>
+        <v>565</v>
       </c>
       <c r="E3" s="3" t="s">
         <v>42</v>
@@ -7884,7 +8469,7 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>546</v>
+        <v>566</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>22</v>
@@ -7900,22 +8485,22 @@
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>547</v>
+        <v>567</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>548</v>
+        <v>568</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>549</v>
+        <v>569</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="1" t="s">
-        <v>550</v>
+        <v>570</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>551</v>
+        <v>571</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>19</v>
@@ -7924,7 +8509,7 @@
         <v>0</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>552</v>
+        <v>572</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -7995,16 +8580,17 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <dimension ref="A1:G13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
   <cols>
     <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="13.75" customWidth="1"/>
-    <col min="5" max="5" width="14" customWidth="1"/>
-    <col min="6" max="6" width="12.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.75" customWidth="1"/>
+    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -8012,19 +8598,22 @@
         <v>1</v>
       </c>
       <c r="C1" t="s">
-        <v>553</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>554</v>
-      </c>
-      <c r="E1" t="s">
-        <v>555</v>
+        <v>573</v>
+      </c>
+      <c r="D1" t="s">
+        <v>574</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>575</v>
       </c>
       <c r="F1" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
+        <v>576</v>
+      </c>
+      <c r="G1" t="s">
+        <v>577</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7">
       <c r="A2" s="1" t="s">
         <v>14</v>
       </c>
@@ -8034,24 +8623,27 @@
       <c r="C2" t="s">
         <v>15</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="E2" t="s">
+      <c r="D2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E2" s="1" t="s">
         <v>16</v>
       </c>
       <c r="F2" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="3" spans="1:6">
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7">
       <c r="A3" s="2" t="s">
         <v>22</v>
       </c>
       <c r="B3" s="2"/>
-      <c r="D3" s="2"/>
-    </row>
-    <row r="4" spans="1:6">
+      <c r="E3" s="2"/>
+    </row>
+    <row r="4" spans="1:7">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -8059,169 +8651,196 @@
         <v>32</v>
       </c>
       <c r="C4" t="s">
-        <v>557</v>
-      </c>
-      <c r="D4" t="s">
-        <v>558</v>
+        <v>579</v>
       </c>
       <c r="E4" t="s">
-        <v>559</v>
+        <v>580</v>
       </c>
       <c r="F4" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
+        <v>581</v>
+      </c>
+      <c r="G4" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
         <v>50</v>
       </c>
-      <c r="D5" t="s">
-        <v>561</v>
+      <c r="D5" s="4" t="s">
+        <v>583</v>
       </c>
       <c r="E5" t="s">
-        <v>562</v>
+        <v>584</v>
       </c>
       <c r="F5" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
+        <v>585</v>
+      </c>
+      <c r="G5" t="s">
+        <v>586</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
         <v>100</v>
       </c>
-      <c r="D6" t="s">
-        <v>564</v>
+      <c r="D6" s="4" t="s">
+        <v>587</v>
       </c>
       <c r="E6" t="s">
-        <v>565</v>
+        <v>588</v>
       </c>
       <c r="F6" t="s">
-        <v>566</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
+        <v>589</v>
+      </c>
+      <c r="G6" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
         <v>150</v>
       </c>
-      <c r="D7" t="s">
-        <v>567</v>
+      <c r="D7" s="4" t="s">
+        <v>591</v>
       </c>
       <c r="E7" t="s">
-        <v>568</v>
+        <v>592</v>
       </c>
       <c r="F7" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
+        <v>593</v>
+      </c>
+      <c r="G7" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
         <v>200</v>
       </c>
-      <c r="D8" t="s">
-        <v>570</v>
+      <c r="D8" s="4" t="s">
+        <v>595</v>
       </c>
       <c r="E8" t="s">
-        <v>571</v>
+        <v>595</v>
       </c>
       <c r="F8" t="s">
-        <v>572</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
+        <v>596</v>
+      </c>
+      <c r="G8" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
         <v>300</v>
       </c>
-      <c r="D9" t="s">
-        <v>573</v>
+      <c r="D9" s="4" t="s">
+        <v>598</v>
       </c>
       <c r="E9" t="s">
-        <v>574</v>
+        <v>598</v>
       </c>
       <c r="F9" t="s">
-        <v>575</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
+        <v>599</v>
+      </c>
+      <c r="G9" t="s">
+        <v>600</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
         <v>450</v>
       </c>
-      <c r="D10" t="s">
-        <v>576</v>
+      <c r="D10" s="4" t="s">
+        <v>601</v>
       </c>
       <c r="E10" t="s">
-        <v>577</v>
+        <v>602</v>
       </c>
       <c r="F10" t="s">
-        <v>578</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
+        <v>603</v>
+      </c>
+      <c r="G10" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
         <v>1000</v>
       </c>
-      <c r="D11" t="s">
-        <v>579</v>
+      <c r="D11" s="4" t="s">
+        <v>605</v>
       </c>
       <c r="E11" t="s">
-        <v>580</v>
+        <v>606</v>
       </c>
       <c r="F11" t="s">
-        <v>581</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
+        <v>607</v>
+      </c>
+      <c r="G11" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
         <v>2500</v>
       </c>
-      <c r="D12" t="s">
-        <v>582</v>
+      <c r="D12" s="4" t="s">
+        <v>609</v>
       </c>
       <c r="E12" t="s">
-        <v>583</v>
+        <v>610</v>
       </c>
       <c r="F12" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
+        <v>611</v>
+      </c>
+      <c r="G12" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
         <v>12500</v>
       </c>
-      <c r="D13" t="s">
-        <v>585</v>
+      <c r="D13" s="4" t="s">
+        <v>613</v>
       </c>
       <c r="E13" t="s">
-        <v>586</v>
+        <v>614</v>
       </c>
       <c r="F13" t="s">
-        <v>587</v>
+        <v>615</v>
+      </c>
+      <c r="G13" t="s">
+        <v>616</v>
       </c>
     </row>
   </sheetData>
@@ -8256,10 +8875,10 @@
         <v>4</v>
       </c>
       <c r="E1" t="s">
-        <v>588</v>
+        <v>617</v>
       </c>
       <c r="F1" t="s">
-        <v>589</v>
+        <v>618</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8303,6 +8922,12 @@
       <c r="D4" t="s">
         <v>36</v>
       </c>
+      <c r="E4" t="s">
+        <v>619</v>
+      </c>
+      <c r="F4" t="s">
+        <v>620</v>
+      </c>
     </row>
     <row r="5" spans="1:6">
       <c r="B5">
@@ -8315,10 +8940,10 @@
         <v>65</v>
       </c>
       <c r="E5" t="s">
-        <v>590</v>
+        <v>621</v>
       </c>
       <c r="F5" t="s">
-        <v>591</v>
+        <v>622</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8326,10 +8951,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>48</v>
+      </c>
+      <c r="E6" t="s">
+        <v>623</v>
+      </c>
+      <c r="F6" t="s">
+        <v>624</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8337,10 +8968,16 @@
         <v>1003</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>91</v>
+      </c>
+      <c r="E7" t="s">
+        <v>625</v>
+      </c>
+      <c r="F7" t="s">
+        <v>626</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8348,10 +8985,16 @@
         <v>1004</v>
       </c>
       <c r="C8" s="4" t="s">
-        <v>440</v>
+        <v>446</v>
       </c>
       <c r="D8" s="4" t="s">
         <v>366</v>
+      </c>
+      <c r="E8" t="s">
+        <v>627</v>
+      </c>
+      <c r="F8" t="s">
+        <v>628</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8359,10 +9002,16 @@
         <v>1005</v>
       </c>
       <c r="C9" s="4" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>446</v>
+        <v>454</v>
+      </c>
+      <c r="E9" t="s">
+        <v>629</v>
+      </c>
+      <c r="F9" t="s">
+        <v>630</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -8370,10 +9019,962 @@
         <v>1006</v>
       </c>
       <c r="C10" s="4" t="s">
+        <v>461</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="E10" t="s">
+        <v>631</v>
+      </c>
+      <c r="F10" t="s">
+        <v>632</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:E32"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <cols>
+    <col min="3" max="3" width="13.5" customWidth="1"/>
+    <col min="4" max="4" width="21.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="13.25" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:5">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>633</v>
+      </c>
+      <c r="D1" t="s">
+        <v>634</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:5">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" t="s">
+        <v>16</v>
+      </c>
+      <c r="D2" t="s">
+        <v>635</v>
+      </c>
+      <c r="E2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="C3" t="s">
+        <v>33</v>
+      </c>
+      <c r="D3" t="s">
+        <v>636</v>
+      </c>
+      <c r="E3" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="B4">
+        <v>1001</v>
+      </c>
+      <c r="C4" t="s">
+        <v>47</v>
+      </c>
+      <c r="D4" t="s">
+        <v>47</v>
+      </c>
+      <c r="E4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="B5">
+        <v>1002</v>
+      </c>
+      <c r="C5" t="s">
+        <v>638</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="B6">
+        <v>1003</v>
+      </c>
+      <c r="C6" t="s">
+        <v>639</v>
+      </c>
+      <c r="D6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E6">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="B7">
+        <v>1004</v>
+      </c>
+      <c r="C7" t="s">
+        <v>640</v>
+      </c>
+      <c r="D7" t="s">
+        <v>153</v>
+      </c>
+      <c r="E7">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="D8" t="s">
+        <v>321</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="D9" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>641</v>
+      </c>
+      <c r="D10" t="s">
+        <v>204</v>
+      </c>
+      <c r="E10">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="D11" t="s">
+        <v>249</v>
+      </c>
+    </row>
+    <row r="12" spans="1:5">
+      <c r="D12" t="s">
+        <v>365</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="B13">
+        <v>1006</v>
+      </c>
+      <c r="C13" t="s">
+        <v>642</v>
+      </c>
+      <c r="D13" t="s">
+        <v>413</v>
+      </c>
+      <c r="E13">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="14" spans="1:5">
+      <c r="D14" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="23" spans="3:4">
+      <c r="C23" s="4"/>
+      <c r="D23" s="4"/>
+    </row>
+    <row r="24" spans="3:4">
+      <c r="C24" s="4"/>
+      <c r="D24" s="4"/>
+    </row>
+    <row r="25" spans="3:4">
+      <c r="C25" s="4"/>
+      <c r="D25" s="4"/>
+    </row>
+    <row r="26" spans="3:4">
+      <c r="C26" s="4"/>
+      <c r="D26" s="4"/>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="4"/>
+      <c r="D27" s="4"/>
+    </row>
+    <row r="28" spans="3:4">
+      <c r="C28" s="4"/>
+      <c r="D28" s="4"/>
+    </row>
+    <row r="29" spans="3:4">
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+    </row>
+    <row r="30" spans="3:4">
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+    </row>
+    <row r="31" spans="3:4">
+      <c r="C31" s="4"/>
+      <c r="D31" s="4"/>
+    </row>
+    <row r="32" spans="3:4">
+      <c r="C32" s="4"/>
+      <c r="D32" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:N30"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="3" max="3" width="19" customWidth="1"/>
+    <col min="4" max="4" width="18.75" customWidth="1"/>
+    <col min="5" max="5" width="18.1666666666667" customWidth="1"/>
+    <col min="6" max="6" width="4.58333333333333" customWidth="1"/>
+    <col min="7" max="7" width="10.6666666666667" customWidth="1"/>
+    <col min="8" max="10" width="11.5" customWidth="1"/>
+    <col min="11" max="13" width="9.58333333333333" customWidth="1"/>
+    <col min="20" max="20" width="12.9166666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:14">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>643</v>
+      </c>
+      <c r="E1" t="s">
+        <v>644</v>
+      </c>
+      <c r="G1" t="s">
+        <v>645</v>
+      </c>
+      <c r="H1" t="s">
+        <v>646</v>
+      </c>
+      <c r="I1" t="s">
+        <v>647</v>
+      </c>
+      <c r="J1" t="s">
+        <v>648</v>
+      </c>
+      <c r="K1" t="s">
+        <v>649</v>
+      </c>
+      <c r="L1" t="s">
+        <v>650</v>
+      </c>
+      <c r="M1" t="s">
+        <v>651</v>
+      </c>
+      <c r="N1" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
+      <c r="A2" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="E2" t="s">
+        <v>653</v>
+      </c>
+      <c r="G2" t="s">
+        <v>16</v>
+      </c>
+      <c r="H2" t="s">
+        <v>16</v>
+      </c>
+      <c r="I2" t="s">
+        <v>16</v>
+      </c>
+      <c r="J2" t="s">
+        <v>19</v>
+      </c>
+      <c r="K2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M2" t="s">
+        <v>16</v>
+      </c>
+      <c r="N2" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" ht="104.4" spans="1:14">
+      <c r="A3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="2"/>
+      <c r="E3" s="3" t="s">
+        <v>654</v>
+      </c>
+      <c r="I3" s="3" t="s">
+        <v>655</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
+      <c r="A4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B4" t="s">
+        <v>32</v>
+      </c>
+      <c r="C4" t="s">
+        <v>656</v>
+      </c>
+      <c r="D4" t="s">
+        <v>657</v>
+      </c>
+      <c r="E4" t="s">
+        <v>658</v>
+      </c>
+      <c r="F4" t="s">
+        <v>657</v>
+      </c>
+      <c r="G4" t="s">
+        <v>659</v>
+      </c>
+      <c r="H4" t="s">
+        <v>660</v>
+      </c>
+      <c r="I4" t="s">
+        <v>661</v>
+      </c>
+      <c r="J4" t="s">
+        <v>662</v>
+      </c>
+      <c r="K4" t="s">
+        <v>663</v>
+      </c>
+      <c r="L4" t="s">
+        <v>664</v>
+      </c>
+      <c r="M4" t="s">
+        <v>520</v>
+      </c>
+      <c r="N4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="D5" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="G5" t="s">
+        <v>430</v>
+      </c>
+      <c r="H5" t="s">
+        <v>430</v>
+      </c>
+      <c r="J5" t="b">
+        <v>0</v>
+      </c>
+      <c r="K5" t="s">
+        <v>665</v>
+      </c>
+      <c r="L5" t="s">
+        <v>665</v>
+      </c>
+      <c r="M5" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>437</v>
+      </c>
+      <c r="G6" t="s">
+        <v>503</v>
+      </c>
+      <c r="H6" t="s">
+        <v>506</v>
+      </c>
+      <c r="J6" t="b">
+        <v>0</v>
+      </c>
+      <c r="K6" t="s">
+        <v>665</v>
+      </c>
+      <c r="L6" t="s">
+        <v>665</v>
+      </c>
+      <c r="M6" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>444</v>
+      </c>
+      <c r="G7" t="s">
+        <v>504</v>
+      </c>
+      <c r="H7" t="s">
+        <v>505</v>
+      </c>
+      <c r="J7" t="b">
+        <v>0</v>
+      </c>
+      <c r="K7" t="s">
+        <v>665</v>
+      </c>
+      <c r="L7" t="s">
+        <v>665</v>
+      </c>
+      <c r="M7" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" s="4" t="s">
         <v>451</v>
       </c>
+      <c r="G8" t="s">
+        <v>503</v>
+      </c>
+      <c r="H8" t="s">
+        <v>510</v>
+      </c>
+      <c r="J8" t="b">
+        <v>0</v>
+      </c>
+      <c r="K8" t="s">
+        <v>665</v>
+      </c>
+      <c r="L8" t="s">
+        <v>665</v>
+      </c>
+      <c r="M8" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>459</v>
+      </c>
+      <c r="G9" t="s">
+        <v>503</v>
+      </c>
+      <c r="H9" t="s">
+        <v>507</v>
+      </c>
+      <c r="J9" t="b">
+        <v>0</v>
+      </c>
+      <c r="K9" t="s">
+        <v>665</v>
+      </c>
+      <c r="L9" t="s">
+        <v>665</v>
+      </c>
+      <c r="M9" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>466</v>
+      </c>
       <c r="D10" s="4" t="s">
-        <v>452</v>
+        <v>467</v>
+      </c>
+      <c r="G10" t="s">
+        <v>503</v>
+      </c>
+      <c r="H10" t="s">
+        <v>508</v>
+      </c>
+      <c r="J10" t="b">
+        <v>0</v>
+      </c>
+      <c r="K10" t="s">
+        <v>665</v>
+      </c>
+      <c r="L10" t="s">
+        <v>665</v>
+      </c>
+      <c r="M10" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="D11" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="G11" t="s">
+        <v>504</v>
+      </c>
+      <c r="H11" t="s">
+        <v>505</v>
+      </c>
+      <c r="J11" t="b">
+        <v>1</v>
+      </c>
+      <c r="K11" t="s">
+        <v>665</v>
+      </c>
+      <c r="L11" t="s">
+        <v>665</v>
+      </c>
+      <c r="M11" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="G12" t="s">
+        <v>504</v>
+      </c>
+      <c r="H12" t="s">
+        <v>509</v>
+      </c>
+      <c r="J12" t="b">
+        <v>1</v>
+      </c>
+      <c r="K12" t="s">
+        <v>667</v>
+      </c>
+      <c r="L12" t="s">
+        <v>667</v>
+      </c>
+      <c r="M12" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
+      <c r="B13">
+        <v>2001</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>668</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>669</v>
+      </c>
+      <c r="E13" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="F13" t="s">
+        <v>430</v>
+      </c>
+      <c r="N13" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
+      <c r="B14">
+        <v>2002</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>671</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>672</v>
+      </c>
+      <c r="E14" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="F14" t="s">
+        <v>430</v>
+      </c>
+      <c r="N14" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
+      <c r="B15">
+        <v>2003</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>673</v>
+      </c>
+      <c r="D15" s="4" t="s">
+        <v>674</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="F15" t="s">
+        <v>437</v>
+      </c>
+      <c r="N15" t="s">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
+      <c r="B16">
+        <v>2004</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>676</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>677</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>678</v>
+      </c>
+      <c r="F16" t="s">
+        <v>679</v>
+      </c>
+      <c r="N16" t="s">
+        <v>680</v>
+      </c>
+    </row>
+    <row r="17" spans="2:14">
+      <c r="B17">
+        <v>2005</v>
+      </c>
+      <c r="C17" s="4" t="s">
+        <v>681</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>682</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>472</v>
+      </c>
+      <c r="F17" s="4" t="s">
+        <v>473</v>
+      </c>
+      <c r="N17" t="s">
+        <v>683</v>
+      </c>
+    </row>
+    <row r="18" spans="2:14">
+      <c r="B18">
+        <v>2006</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>684</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>685</v>
+      </c>
+      <c r="E18" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F18" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="N18" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="19" spans="2:14">
+      <c r="B19">
+        <v>2007</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>687</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>688</v>
+      </c>
+      <c r="E19" s="4" t="s">
+        <v>436</v>
+      </c>
+      <c r="F19" t="s">
+        <v>437</v>
+      </c>
+      <c r="N19" t="s">
+        <v>689</v>
+      </c>
+    </row>
+    <row r="20" spans="2:14">
+      <c r="B20">
+        <v>2008</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>690</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>691</v>
+      </c>
+      <c r="E20" t="s">
+        <v>678</v>
+      </c>
+      <c r="F20" t="s">
+        <v>679</v>
+      </c>
+      <c r="N20" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="21" spans="2:14">
+      <c r="B21">
+        <v>3001</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>693</v>
+      </c>
+      <c r="D21" s="4" t="s">
+        <v>694</v>
+      </c>
+      <c r="E21" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F21" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="22" spans="2:14">
+      <c r="B22">
+        <v>3002</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>695</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>696</v>
+      </c>
+      <c r="E22" s="4" t="s">
+        <v>443</v>
+      </c>
+      <c r="F22" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="23" spans="2:14">
+      <c r="B23">
+        <v>3003</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>697</v>
+      </c>
+      <c r="D23" s="4" t="s">
+        <v>698</v>
+      </c>
+      <c r="E23" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F23" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="24" spans="2:14">
+      <c r="B24">
+        <v>3004</v>
+      </c>
+      <c r="C24" s="4" t="s">
+        <v>699</v>
+      </c>
+      <c r="D24" s="4" t="s">
+        <v>700</v>
+      </c>
+      <c r="E24" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F24" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="25" spans="2:14">
+      <c r="B25">
+        <v>3005</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>701</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>702</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="F25" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="26" spans="2:14">
+      <c r="B26">
+        <v>3006</v>
+      </c>
+      <c r="C26" s="4" t="s">
+        <v>703</v>
+      </c>
+      <c r="D26" s="4" t="s">
+        <v>704</v>
+      </c>
+      <c r="E26" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="F26" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="27" spans="2:14">
+      <c r="B27">
+        <v>3007</v>
+      </c>
+      <c r="C27" s="4" t="s">
+        <v>705</v>
+      </c>
+      <c r="D27" s="4" t="s">
+        <v>706</v>
+      </c>
+      <c r="E27" s="4" t="s">
+        <v>458</v>
+      </c>
+      <c r="F27" t="s">
+        <v>459</v>
+      </c>
+      <c r="M27" t="s">
+        <v>707</v>
+      </c>
+      <c r="N27" t="s">
+        <v>708</v>
+      </c>
+    </row>
+    <row r="28" spans="2:14">
+      <c r="B28">
+        <v>3008</v>
+      </c>
+      <c r="C28" s="4" t="s">
+        <v>709</v>
+      </c>
+      <c r="D28" s="4" t="s">
+        <v>710</v>
+      </c>
+      <c r="E28" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="F28" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="29" spans="2:14">
+      <c r="B29">
+        <v>3009</v>
+      </c>
+      <c r="C29" s="4" t="s">
+        <v>711</v>
+      </c>
+      <c r="D29" s="4" t="s">
+        <v>712</v>
+      </c>
+      <c r="E29" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="F29" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="30" spans="2:14">
+      <c r="B30">
+        <v>3010</v>
+      </c>
+      <c r="C30" s="4" t="s">
+        <v>713</v>
+      </c>
+      <c r="D30" s="4" t="s">
+        <v>714</v>
+      </c>
+      <c r="E30" s="4" t="s">
+        <v>466</v>
+      </c>
+      <c r="F30" t="s">
+        <v>467</v>
+      </c>
+      <c r="M30" t="s">
+        <v>707</v>
+      </c>
+      <c r="N30" t="s">
+        <v>708</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13008" tabRatio="717" activeTab="4"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="7"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -14,6 +14,7 @@
     <sheet name="RarityUI" sheetId="7" r:id="rId5"/>
     <sheet name="DogReaction" sheetId="9" r:id="rId6"/>
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId7"/>
+    <sheet name="BGMList" sheetId="12" r:id="rId8"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -33,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="720" uniqueCount="368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="394">
   <si>
     <t>Dog</t>
   </si>
@@ -341,6 +342,9 @@
     <t>HandRank</t>
   </si>
   <si>
+    <t>LuckyWeight</t>
+  </si>
+  <si>
     <t>OriginalName</t>
   </si>
   <si>
@@ -365,12 +369,18 @@
     <t>##</t>
   </si>
   <si>
+    <t>奖励筹码具体数值</t>
+  </si>
+  <si>
     <t>id</t>
   </si>
   <si>
     <t>赔率</t>
   </si>
   <si>
+    <t>幸运发牌权重</t>
+  </si>
+  <si>
     <t>原始名称</t>
   </si>
   <si>
@@ -524,6 +534,9 @@
     <t>DefaultEyes</t>
   </si>
   <si>
+    <t>DefaultTongue</t>
+  </si>
+  <si>
     <t>FolderPath</t>
   </si>
   <si>
@@ -869,6 +882,9 @@
     <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
   </si>
   <si>
+    <t>左指画面左侧，而非狗自己的左</t>
+  </si>
+  <si>
     <t>枚举</t>
   </si>
   <si>
@@ -908,6 +924,21 @@
     <t>手心，摆手</t>
   </si>
   <si>
+    <t>Hello</t>
+  </si>
+  <si>
+    <t>哈喽</t>
+  </si>
+  <si>
+    <t>手心，摆手两次</t>
+  </si>
+  <si>
+    <t>哈气</t>
+  </si>
+  <si>
+    <t>舌头上下略微移动</t>
+  </si>
+  <si>
     <t>WaitingForBet</t>
   </si>
   <si>
@@ -944,7 +975,7 @@
     <t>约定</t>
   </si>
   <si>
-    <t>如果玩家进行了询问，再作出相应的预测表情。</t>
+    <t>如果玩家进行了询问，再作出相应的预测表情。（未真实现具体内容只做表内意图表达）</t>
   </si>
   <si>
     <t>HintExhausted</t>
@@ -980,7 +1011,13 @@
     <t>看到结算结果</t>
   </si>
   <si>
-    <t>根据牌型优劣作出相应表情</t>
+    <t>根据牌型优劣作出相应表情（未真实现具体内容只做表内意图表达）</t>
+  </si>
+  <si>
+    <t>InteractionHint</t>
+  </si>
+  <si>
+    <t>提示玩家可以询问</t>
   </si>
   <si>
     <t>SawNothing</t>
@@ -1025,12 +1062,6 @@
     <t>看到葫芦</t>
   </si>
   <si>
-    <t>哈气</t>
-  </si>
-  <si>
-    <t>舌头上下略微移动</t>
-  </si>
-  <si>
     <t>SawFourOfAKind</t>
   </si>
   <si>
@@ -1137,6 +1168,54 @@
   </si>
   <si>
     <t>HighEnergy</t>
+  </si>
+  <si>
+    <t>VolumeDb</t>
+  </si>
+  <si>
+    <t>Enabled</t>
+  </si>
+  <si>
+    <t>AudioPath</t>
+  </si>
+  <si>
+    <t>单曲音量补偿，默认 0；过响可填 -3、-6</t>
+  </si>
+  <si>
+    <t>用于新版本预留</t>
+  </si>
+  <si>
+    <t>用于显示的名称</t>
+  </si>
+  <si>
+    <t>音量微调</t>
+  </si>
+  <si>
+    <t>是否可被随机播放到</t>
+  </si>
+  <si>
+    <t>Rise and Shine</t>
+  </si>
+  <si>
+    <t>Audio/BGM/01.Rise and Shine.mp3</t>
+  </si>
+  <si>
+    <t>On a Roll</t>
+  </si>
+  <si>
+    <t>Audio/BGM/02.On a Roll.mp3</t>
+  </si>
+  <si>
+    <t>Little Wins</t>
+  </si>
+  <si>
+    <t>Audio/BGM/03.Little Wins.mp3</t>
+  </si>
+  <si>
+    <t>Call It a Day</t>
+  </si>
+  <si>
+    <t>Audio/BGM/04.Call It a Day.mp3</t>
   </si>
 </sst>
 </file>
@@ -2690,17 +2769,18 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:G13"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="6"/>
+  <dimension ref="A1:I13"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
-    <col min="3" max="3" width="14.8333333333333" customWidth="1"/>
-    <col min="4" max="4" width="12.5833333333333" customWidth="1"/>
-    <col min="5" max="5" width="13.75" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
-    <col min="7" max="7" width="12.9166666666667" customWidth="1"/>
+    <col min="3" max="4" width="14.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="12.5833333333333" customWidth="1"/>
+    <col min="6" max="6" width="15.0833333333333" customWidth="1"/>
+    <col min="7" max="7" width="13.75" customWidth="1"/>
+    <col min="8" max="8" width="14" customWidth="1"/>
+    <col min="9" max="9" width="12.9166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:9">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -2710,247 +2790,314 @@
       <c r="C1" t="s">
         <v>100</v>
       </c>
-      <c r="D1" t="s">
+      <c r="E1" t="s">
         <v>101</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="F1" t="s">
         <v>102</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
         <v>104</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
+      <c r="I1" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" t="s">
         <v>107</v>
       </c>
-      <c r="E2" s="2" t="s">
+      <c r="E2" t="s">
         <v>108</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
-      </c>
-      <c r="G2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7">
+        <v>107</v>
+      </c>
+      <c r="G2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:7">
+      <c r="C3"/>
+      <c r="D3" t="s">
+        <v>111</v>
+      </c>
+      <c r="G3" s="3"/>
+    </row>
+    <row r="4" spans="1:9">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
-      </c>
-      <c r="E4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="F4" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="G4" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
+        <v>115</v>
+      </c>
+      <c r="H4" t="s">
+        <v>116</v>
+      </c>
+      <c r="I4" t="s">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5">
+        <v>1</v>
+      </c>
+      <c r="D5">
         <v>50</v>
       </c>
-      <c r="D5" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="E5" t="s">
-        <v>116</v>
-      </c>
-      <c r="F5" t="s">
-        <v>117</v>
+      <c r="E5" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="F5" s="4">
+        <v>0</v>
       </c>
       <c r="G5" t="s">
-        <v>118</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
+        <v>119</v>
+      </c>
+      <c r="H5" t="s">
+        <v>120</v>
+      </c>
+      <c r="I5" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6">
+        <v>2</v>
+      </c>
+      <c r="D6">
         <v>100</v>
       </c>
-      <c r="D6" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="E6" t="s">
-        <v>120</v>
-      </c>
-      <c r="F6" t="s">
-        <v>121</v>
+      <c r="E6" s="4" t="s">
+        <v>122</v>
+      </c>
+      <c r="F6" s="4">
+        <v>80</v>
       </c>
       <c r="G6" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
+        <v>123</v>
+      </c>
+      <c r="H6" t="s">
+        <v>124</v>
+      </c>
+      <c r="I6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7">
+        <v>3</v>
+      </c>
+      <c r="D7">
         <v>150</v>
       </c>
-      <c r="D7" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="E7" t="s">
-        <v>124</v>
-      </c>
-      <c r="F7" t="s">
-        <v>125</v>
+      <c r="E7" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F7" s="4">
+        <v>65</v>
       </c>
       <c r="G7" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
+        <v>127</v>
+      </c>
+      <c r="H7" t="s">
+        <v>128</v>
+      </c>
+      <c r="I7" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8">
+        <v>4</v>
+      </c>
+      <c r="D8">
         <v>200</v>
       </c>
-      <c r="D8" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" t="s">
-        <v>127</v>
-      </c>
-      <c r="F8" t="s">
-        <v>128</v>
+      <c r="E8" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="F8" s="4">
+        <v>65</v>
       </c>
       <c r="G8" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
+        <v>130</v>
+      </c>
+      <c r="H8" t="s">
+        <v>131</v>
+      </c>
+      <c r="I8" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9">
+        <v>6</v>
+      </c>
+      <c r="D9">
         <v>300</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="E9" t="s">
-        <v>130</v>
-      </c>
-      <c r="F9" t="s">
-        <v>131</v>
+      <c r="E9" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="F9" s="4">
+        <v>36</v>
       </c>
       <c r="G9" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
+        <v>133</v>
+      </c>
+      <c r="H9" t="s">
+        <v>134</v>
+      </c>
+      <c r="I9" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10">
+        <v>9</v>
+      </c>
+      <c r="D10">
         <v>450</v>
       </c>
-      <c r="D10" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="E10" t="s">
-        <v>134</v>
-      </c>
-      <c r="F10" t="s">
-        <v>135</v>
+      <c r="E10" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="F10" s="4">
+        <v>28</v>
       </c>
       <c r="G10" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7">
+        <v>137</v>
+      </c>
+      <c r="H10" t="s">
+        <v>138</v>
+      </c>
+      <c r="I10" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11">
+        <v>20</v>
+      </c>
+      <c r="D11">
         <v>1000</v>
       </c>
-      <c r="D11" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="E11" t="s">
-        <v>138</v>
-      </c>
-      <c r="F11" t="s">
-        <v>139</v>
+      <c r="E11" s="4" t="s">
+        <v>140</v>
+      </c>
+      <c r="F11" s="4">
+        <v>14</v>
       </c>
       <c r="G11" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7">
+        <v>141</v>
+      </c>
+      <c r="H11" t="s">
+        <v>142</v>
+      </c>
+      <c r="I11" t="s">
+        <v>143</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12">
+        <v>50</v>
+      </c>
+      <c r="D12">
         <v>2500</v>
       </c>
-      <c r="D12" s="4" t="s">
-        <v>141</v>
-      </c>
-      <c r="E12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F12" t="s">
-        <v>143</v>
+      <c r="E12" s="4" t="s">
+        <v>144</v>
+      </c>
+      <c r="F12" s="4">
+        <v>9</v>
       </c>
       <c r="G12" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7">
+        <v>145</v>
+      </c>
+      <c r="H12" t="s">
+        <v>146</v>
+      </c>
+      <c r="I12" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13">
+        <v>250</v>
+      </c>
+      <c r="D13">
         <v>12500</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>145</v>
-      </c>
-      <c r="E13" t="s">
-        <v>146</v>
-      </c>
-      <c r="F13" t="s">
-        <v>147</v>
+      <c r="E13" s="4" t="s">
+        <v>148</v>
+      </c>
+      <c r="F13" s="4">
+        <v>3</v>
       </c>
       <c r="G13" t="s">
-        <v>148</v>
+        <v>149</v>
+      </c>
+      <c r="H13" t="s">
+        <v>150</v>
+      </c>
+      <c r="I13" t="s">
+        <v>151</v>
       </c>
     </row>
   </sheetData>
@@ -2972,64 +3119,64 @@
   <sheetData>
     <row r="1" spans="1:5">
       <c r="A1" s="5" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="D1" s="4"/>
       <c r="E1" s="4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
       <c r="A2" s="5"/>
       <c r="B2" s="4" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="C2" s="4"/>
       <c r="D2" s="4" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3" s="2" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="B3" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="C3" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="D3" s="2">
         <v>1</v>
       </c>
       <c r="E3" s="4" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4" s="2" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="B4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C4" t="s">
         <v>158</v>
-      </c>
-      <c r="C4" t="s">
-        <v>155</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
       </c>
       <c r="E4" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -3079,28 +3226,28 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:S16"/>
+  <dimension ref="A1:T16"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
-    <col min="4" max="6" width="21.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="15.5" customWidth="1"/>
-    <col min="8" max="8" width="16.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="18.5" customWidth="1"/>
-    <col min="10" max="11" width="20.8333333333333" customWidth="1"/>
-    <col min="12" max="12" width="14.5" customWidth="1"/>
-    <col min="13" max="13" width="13.4166666666667" customWidth="1"/>
-    <col min="14" max="14" width="14.3333333333333" customWidth="1"/>
-    <col min="15" max="15" width="13" customWidth="1"/>
-    <col min="16" max="16" width="14.8333333333333" customWidth="1"/>
-    <col min="17" max="17" width="14" customWidth="1"/>
-    <col min="18" max="18" width="15.4166666666667" customWidth="1"/>
-    <col min="19" max="19" width="13.4166666666667" customWidth="1"/>
+    <col min="4" max="7" width="21.9166666666667" customWidth="1"/>
+    <col min="8" max="8" width="15.5" customWidth="1"/>
+    <col min="9" max="9" width="16.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="18.5" customWidth="1"/>
+    <col min="11" max="12" width="20.8333333333333" customWidth="1"/>
+    <col min="13" max="13" width="14.5" customWidth="1"/>
+    <col min="14" max="14" width="13.4166666666667" customWidth="1"/>
+    <col min="15" max="15" width="14.3333333333333" customWidth="1"/>
+    <col min="16" max="16" width="13" customWidth="1"/>
+    <col min="17" max="17" width="14.8333333333333" customWidth="1"/>
+    <col min="18" max="18" width="14" customWidth="1"/>
+    <col min="19" max="19" width="15.4166666666667" customWidth="1"/>
+    <col min="20" max="20" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19">
+    <row r="1" spans="1:20">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -3109,856 +3256,899 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>164</v>
-      </c>
-      <c r="I1" t="s">
-        <v>165</v>
+        <v>167</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>168</v>
       </c>
       <c r="J1" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="K1" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="L1" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="M1" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="N1" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="O1" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="P1" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="Q1" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="R1" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="S1" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19">
+        <v>178</v>
+      </c>
+      <c r="T1" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="2" spans="1:20">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2"/>
       <c r="D2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="G2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="O2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="P2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="Q2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="R2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="S2" s="2" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:19">
+        <v>109</v>
+      </c>
+      <c r="T2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:20">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
-    </row>
-    <row r="4" spans="1:19">
+      <c r="I3" s="3"/>
+    </row>
+    <row r="4" spans="1:20">
       <c r="A4" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="D4" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="E4" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="F4" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H4" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="I4" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J4" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="K4" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="L4" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="M4" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="N4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="O4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="P4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="Q4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="R4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="S4" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="5" spans="1:19">
+        <v>196</v>
+      </c>
+      <c r="T4" t="s">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20">
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="D5" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E5" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F5" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G5" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="H5" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="I5" t="s">
+        <v>203</v>
+      </c>
+      <c r="J5" t="s">
+        <v>204</v>
+      </c>
+      <c r="K5" t="s">
+        <v>205</v>
+      </c>
+      <c r="L5" t="s">
+        <v>206</v>
+      </c>
+      <c r="M5" t="s">
         <v>200</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>207</v>
+      </c>
+      <c r="O5" t="s">
+        <v>208</v>
+      </c>
+      <c r="P5" t="s">
         <v>201</v>
       </c>
-      <c r="K5" t="s">
-        <v>202</v>
-      </c>
-      <c r="L5" t="s">
-        <v>196</v>
-      </c>
-      <c r="M5" t="s">
-        <v>203</v>
-      </c>
-      <c r="N5" t="s">
-        <v>204</v>
-      </c>
-      <c r="O5" t="s">
-        <v>197</v>
-      </c>
-      <c r="P5" t="s">
-        <v>205</v>
-      </c>
       <c r="Q5" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S5" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="6" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T5" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20">
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>213</v>
+      </c>
+      <c r="D6" t="s">
+        <v>214</v>
+      </c>
+      <c r="E6" t="s">
+        <v>200</v>
+      </c>
+      <c r="F6" t="s">
         <v>209</v>
       </c>
-      <c r="D6" t="s">
+      <c r="G6" t="s">
+        <v>171</v>
+      </c>
+      <c r="H6" t="s">
+        <v>215</v>
+      </c>
+      <c r="I6" t="s">
+        <v>203</v>
+      </c>
+      <c r="J6" t="s">
+        <v>204</v>
+      </c>
+      <c r="K6" t="s">
+        <v>205</v>
+      </c>
+      <c r="L6" t="s">
+        <v>206</v>
+      </c>
+      <c r="M6" t="s">
+        <v>200</v>
+      </c>
+      <c r="N6" t="s">
+        <v>207</v>
+      </c>
+      <c r="O6" t="s">
+        <v>208</v>
+      </c>
+      <c r="P6" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>209</v>
+      </c>
+      <c r="R6" t="s">
         <v>210</v>
       </c>
-      <c r="E6" t="s">
-        <v>196</v>
-      </c>
-      <c r="F6" t="s">
-        <v>205</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="S6" t="s">
         <v>211</v>
       </c>
-      <c r="H6" t="s">
-        <v>199</v>
-      </c>
-      <c r="I6" t="s">
-        <v>200</v>
-      </c>
-      <c r="J6" t="s">
-        <v>201</v>
-      </c>
-      <c r="K6" t="s">
-        <v>202</v>
-      </c>
-      <c r="L6" t="s">
-        <v>196</v>
-      </c>
-      <c r="M6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N6" t="s">
-        <v>204</v>
-      </c>
-      <c r="O6" t="s">
-        <v>197</v>
-      </c>
-      <c r="P6" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>206</v>
-      </c>
-      <c r="R6" t="s">
-        <v>207</v>
-      </c>
-      <c r="S6" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="7" spans="1:19">
+      <c r="T6" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20">
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>216</v>
+      </c>
+      <c r="D7" t="s">
+        <v>217</v>
+      </c>
+      <c r="E7" t="s">
+        <v>200</v>
+      </c>
+      <c r="F7" t="s">
+        <v>210</v>
+      </c>
+      <c r="G7" t="s">
+        <v>171</v>
+      </c>
+      <c r="H7" t="s">
+        <v>218</v>
+      </c>
+      <c r="I7" t="s">
+        <v>203</v>
+      </c>
+      <c r="J7" t="s">
+        <v>204</v>
+      </c>
+      <c r="K7" t="s">
+        <v>205</v>
+      </c>
+      <c r="L7" t="s">
+        <v>206</v>
+      </c>
+      <c r="M7" t="s">
+        <v>200</v>
+      </c>
+      <c r="N7" t="s">
+        <v>207</v>
+      </c>
+      <c r="O7" t="s">
+        <v>208</v>
+      </c>
+      <c r="P7" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>209</v>
+      </c>
+      <c r="R7" t="s">
+        <v>210</v>
+      </c>
+      <c r="S7" t="s">
+        <v>211</v>
+      </c>
+      <c r="T7" t="s">
         <v>212</v>
       </c>
-      <c r="D7" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" t="s">
-        <v>196</v>
-      </c>
-      <c r="F7" t="s">
-        <v>206</v>
-      </c>
-      <c r="G7" t="s">
-        <v>214</v>
-      </c>
-      <c r="H7" t="s">
-        <v>199</v>
-      </c>
-      <c r="I7" t="s">
-        <v>200</v>
-      </c>
-      <c r="J7" t="s">
-        <v>201</v>
-      </c>
-      <c r="K7" t="s">
-        <v>202</v>
-      </c>
-      <c r="L7" t="s">
-        <v>196</v>
-      </c>
-      <c r="M7" t="s">
-        <v>203</v>
-      </c>
-      <c r="N7" t="s">
-        <v>204</v>
-      </c>
-      <c r="O7" t="s">
-        <v>197</v>
-      </c>
-      <c r="P7" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>206</v>
-      </c>
-      <c r="R7" t="s">
-        <v>207</v>
-      </c>
-      <c r="S7" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="8" spans="1:19">
+    </row>
+    <row r="8" spans="1:20">
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="D8" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="E8" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" t="s">
+        <v>171</v>
+      </c>
+      <c r="H8" t="s">
+        <v>221</v>
+      </c>
+      <c r="I8" t="s">
         <v>203</v>
       </c>
-      <c r="F8" t="s">
+      <c r="J8" t="s">
         <v>204</v>
       </c>
-      <c r="G8" t="s">
-        <v>217</v>
-      </c>
-      <c r="H8" t="s">
-        <v>199</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="K8" t="s">
+        <v>205</v>
+      </c>
+      <c r="L8" t="s">
+        <v>206</v>
+      </c>
+      <c r="M8" t="s">
         <v>200</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>207</v>
+      </c>
+      <c r="O8" t="s">
+        <v>208</v>
+      </c>
+      <c r="P8" t="s">
         <v>201</v>
       </c>
-      <c r="K8" t="s">
-        <v>202</v>
-      </c>
-      <c r="L8" t="s">
-        <v>196</v>
-      </c>
-      <c r="M8" t="s">
-        <v>203</v>
-      </c>
-      <c r="N8" t="s">
-        <v>204</v>
-      </c>
-      <c r="O8" t="s">
-        <v>197</v>
-      </c>
-      <c r="P8" t="s">
-        <v>205</v>
-      </c>
       <c r="Q8" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R8" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S8" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="9" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T8" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20">
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="D9" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="E9" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F9" t="s">
+        <v>210</v>
+      </c>
+      <c r="G9" t="s">
+        <v>171</v>
+      </c>
+      <c r="H9" t="s">
+        <v>202</v>
+      </c>
+      <c r="I9" t="s">
+        <v>224</v>
+      </c>
+      <c r="J9" t="s">
+        <v>204</v>
+      </c>
+      <c r="K9" t="s">
+        <v>205</v>
+      </c>
+      <c r="L9" t="s">
         <v>206</v>
       </c>
-      <c r="G9" t="s">
-        <v>198</v>
-      </c>
-      <c r="H9" t="s">
-        <v>220</v>
-      </c>
-      <c r="I9" t="s">
+      <c r="M9" t="s">
         <v>200</v>
       </c>
-      <c r="J9" t="s">
+      <c r="N9" t="s">
+        <v>207</v>
+      </c>
+      <c r="O9" t="s">
+        <v>208</v>
+      </c>
+      <c r="P9" t="s">
         <v>201</v>
       </c>
-      <c r="K9" t="s">
-        <v>202</v>
-      </c>
-      <c r="L9" t="s">
-        <v>196</v>
-      </c>
-      <c r="M9" t="s">
-        <v>203</v>
-      </c>
-      <c r="N9" t="s">
-        <v>204</v>
-      </c>
-      <c r="O9" t="s">
-        <v>197</v>
-      </c>
-      <c r="P9" t="s">
-        <v>205</v>
-      </c>
       <c r="Q9" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R9" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S9" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="10" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T9" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20">
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="D10" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="E10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="F10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G10" t="s">
-        <v>198</v>
+        <v>171</v>
       </c>
       <c r="H10" t="s">
-        <v>223</v>
+        <v>202</v>
       </c>
       <c r="I10" t="s">
+        <v>227</v>
+      </c>
+      <c r="J10" t="s">
+        <v>204</v>
+      </c>
+      <c r="K10" t="s">
+        <v>205</v>
+      </c>
+      <c r="L10" t="s">
+        <v>206</v>
+      </c>
+      <c r="M10" t="s">
         <v>200</v>
       </c>
-      <c r="J10" t="s">
+      <c r="N10" t="s">
+        <v>207</v>
+      </c>
+      <c r="O10" t="s">
+        <v>208</v>
+      </c>
+      <c r="P10" t="s">
         <v>201</v>
       </c>
-      <c r="K10" t="s">
-        <v>202</v>
-      </c>
-      <c r="L10" t="s">
-        <v>196</v>
-      </c>
-      <c r="M10" t="s">
-        <v>203</v>
-      </c>
-      <c r="N10" t="s">
-        <v>204</v>
-      </c>
-      <c r="O10" t="s">
-        <v>197</v>
-      </c>
-      <c r="P10" t="s">
-        <v>205</v>
-      </c>
       <c r="Q10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S10" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="11" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T10" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20">
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
+        <v>228</v>
+      </c>
+      <c r="D11" t="s">
+        <v>229</v>
+      </c>
+      <c r="E11" t="s">
+        <v>200</v>
+      </c>
+      <c r="F11" t="s">
+        <v>212</v>
+      </c>
+      <c r="G11" t="s">
+        <v>171</v>
+      </c>
+      <c r="H11" t="s">
+        <v>215</v>
+      </c>
+      <c r="I11" t="s">
         <v>224</v>
       </c>
-      <c r="D11" t="s">
-        <v>225</v>
-      </c>
-      <c r="E11" t="s">
-        <v>196</v>
-      </c>
-      <c r="F11" t="s">
+      <c r="J11" t="s">
+        <v>204</v>
+      </c>
+      <c r="K11" t="s">
+        <v>205</v>
+      </c>
+      <c r="L11" t="s">
+        <v>206</v>
+      </c>
+      <c r="M11" t="s">
+        <v>200</v>
+      </c>
+      <c r="N11" t="s">
+        <v>207</v>
+      </c>
+      <c r="O11" t="s">
         <v>208</v>
       </c>
-      <c r="G11" t="s">
+      <c r="P11" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>209</v>
+      </c>
+      <c r="R11" t="s">
+        <v>210</v>
+      </c>
+      <c r="S11" t="s">
         <v>211</v>
       </c>
-      <c r="H11" t="s">
-        <v>220</v>
-      </c>
-      <c r="I11" t="s">
-        <v>200</v>
-      </c>
-      <c r="J11" t="s">
-        <v>201</v>
-      </c>
-      <c r="K11" t="s">
-        <v>202</v>
-      </c>
-      <c r="L11" t="s">
-        <v>196</v>
-      </c>
-      <c r="M11" t="s">
-        <v>203</v>
-      </c>
-      <c r="N11" t="s">
-        <v>204</v>
-      </c>
-      <c r="O11" t="s">
-        <v>197</v>
-      </c>
-      <c r="P11" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>206</v>
-      </c>
-      <c r="R11" t="s">
-        <v>207</v>
-      </c>
-      <c r="S11" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="12" spans="1:19">
+      <c r="T11" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20">
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="D12" t="s">
+        <v>231</v>
+      </c>
+      <c r="E12" t="s">
+        <v>200</v>
+      </c>
+      <c r="F12" t="s">
+        <v>201</v>
+      </c>
+      <c r="G12" t="s">
+        <v>171</v>
+      </c>
+      <c r="H12" t="s">
+        <v>215</v>
+      </c>
+      <c r="I12" t="s">
         <v>227</v>
       </c>
-      <c r="E12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F12" t="s">
-        <v>197</v>
-      </c>
-      <c r="G12" t="s">
+      <c r="J12" t="s">
+        <v>204</v>
+      </c>
+      <c r="K12" t="s">
+        <v>205</v>
+      </c>
+      <c r="L12" t="s">
+        <v>206</v>
+      </c>
+      <c r="M12" t="s">
+        <v>200</v>
+      </c>
+      <c r="N12" t="s">
+        <v>207</v>
+      </c>
+      <c r="O12" t="s">
+        <v>208</v>
+      </c>
+      <c r="P12" t="s">
+        <v>201</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>209</v>
+      </c>
+      <c r="R12" t="s">
+        <v>210</v>
+      </c>
+      <c r="S12" t="s">
         <v>211</v>
       </c>
-      <c r="H12" t="s">
-        <v>223</v>
-      </c>
-      <c r="I12" t="s">
-        <v>200</v>
-      </c>
-      <c r="J12" t="s">
-        <v>201</v>
-      </c>
-      <c r="K12" t="s">
-        <v>202</v>
-      </c>
-      <c r="L12" t="s">
-        <v>196</v>
-      </c>
-      <c r="M12" t="s">
-        <v>203</v>
-      </c>
-      <c r="N12" t="s">
-        <v>204</v>
-      </c>
-      <c r="O12" t="s">
-        <v>197</v>
-      </c>
-      <c r="P12" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>206</v>
-      </c>
-      <c r="R12" t="s">
-        <v>207</v>
-      </c>
-      <c r="S12" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="13" spans="1:19">
+      <c r="T12" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20">
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="E13" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F13" t="s">
+        <v>212</v>
+      </c>
+      <c r="G13" t="s">
+        <v>171</v>
+      </c>
+      <c r="H13" t="s">
+        <v>218</v>
+      </c>
+      <c r="I13" t="s">
+        <v>224</v>
+      </c>
+      <c r="J13" t="s">
+        <v>204</v>
+      </c>
+      <c r="K13" t="s">
+        <v>205</v>
+      </c>
+      <c r="L13" t="s">
+        <v>206</v>
+      </c>
+      <c r="M13" t="s">
+        <v>200</v>
+      </c>
+      <c r="N13" t="s">
+        <v>207</v>
+      </c>
+      <c r="O13" t="s">
         <v>208</v>
       </c>
-      <c r="G13" t="s">
-        <v>214</v>
-      </c>
-      <c r="H13" t="s">
-        <v>220</v>
-      </c>
-      <c r="I13" t="s">
-        <v>200</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="P13" t="s">
         <v>201</v>
       </c>
-      <c r="K13" t="s">
-        <v>202</v>
-      </c>
-      <c r="L13" t="s">
-        <v>196</v>
-      </c>
-      <c r="M13" t="s">
-        <v>203</v>
-      </c>
-      <c r="N13" t="s">
-        <v>204</v>
-      </c>
-      <c r="O13" t="s">
-        <v>197</v>
-      </c>
-      <c r="P13" t="s">
-        <v>205</v>
-      </c>
       <c r="Q13" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R13" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S13" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="14" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T13" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20">
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="D14" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="E14" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F14" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G14" t="s">
-        <v>214</v>
+        <v>171</v>
       </c>
       <c r="H14" t="s">
-        <v>223</v>
+        <v>218</v>
       </c>
       <c r="I14" t="s">
+        <v>227</v>
+      </c>
+      <c r="J14" t="s">
+        <v>204</v>
+      </c>
+      <c r="K14" t="s">
+        <v>205</v>
+      </c>
+      <c r="L14" t="s">
+        <v>206</v>
+      </c>
+      <c r="M14" t="s">
         <v>200</v>
       </c>
-      <c r="J14" t="s">
+      <c r="N14" t="s">
+        <v>207</v>
+      </c>
+      <c r="O14" t="s">
+        <v>208</v>
+      </c>
+      <c r="P14" t="s">
         <v>201</v>
       </c>
-      <c r="K14" t="s">
-        <v>202</v>
-      </c>
-      <c r="L14" t="s">
-        <v>196</v>
-      </c>
-      <c r="M14" t="s">
-        <v>203</v>
-      </c>
-      <c r="N14" t="s">
-        <v>204</v>
-      </c>
-      <c r="O14" t="s">
-        <v>197</v>
-      </c>
-      <c r="P14" t="s">
-        <v>205</v>
-      </c>
       <c r="Q14" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R14" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S14" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="15" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T14" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20">
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="D15" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="E15" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F15" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="G15" t="s">
-        <v>217</v>
+        <v>171</v>
       </c>
       <c r="H15" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="I15" t="s">
+        <v>224</v>
+      </c>
+      <c r="J15" t="s">
+        <v>204</v>
+      </c>
+      <c r="K15" t="s">
+        <v>205</v>
+      </c>
+      <c r="L15" t="s">
+        <v>206</v>
+      </c>
+      <c r="M15" t="s">
         <v>200</v>
       </c>
-      <c r="J15" t="s">
+      <c r="N15" t="s">
+        <v>207</v>
+      </c>
+      <c r="O15" t="s">
+        <v>208</v>
+      </c>
+      <c r="P15" t="s">
         <v>201</v>
       </c>
-      <c r="K15" t="s">
-        <v>202</v>
-      </c>
-      <c r="L15" t="s">
-        <v>196</v>
-      </c>
-      <c r="M15" t="s">
-        <v>203</v>
-      </c>
-      <c r="N15" t="s">
-        <v>204</v>
-      </c>
-      <c r="O15" t="s">
-        <v>197</v>
-      </c>
-      <c r="P15" t="s">
-        <v>205</v>
-      </c>
       <c r="Q15" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R15" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S15" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="16" spans="1:19">
+        <v>211</v>
+      </c>
+      <c r="T15" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20">
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="D16" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="E16" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="F16" t="s">
+        <v>211</v>
+      </c>
+      <c r="G16" t="s">
+        <v>171</v>
+      </c>
+      <c r="H16" t="s">
+        <v>221</v>
+      </c>
+      <c r="I16" t="s">
+        <v>227</v>
+      </c>
+      <c r="J16" t="s">
+        <v>204</v>
+      </c>
+      <c r="K16" t="s">
+        <v>205</v>
+      </c>
+      <c r="L16" t="s">
+        <v>206</v>
+      </c>
+      <c r="M16" t="s">
+        <v>200</v>
+      </c>
+      <c r="N16" t="s">
         <v>207</v>
       </c>
-      <c r="G16" t="s">
-        <v>217</v>
-      </c>
-      <c r="H16" t="s">
-        <v>223</v>
-      </c>
-      <c r="I16" t="s">
-        <v>200</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="O16" t="s">
+        <v>208</v>
+      </c>
+      <c r="P16" t="s">
         <v>201</v>
       </c>
-      <c r="K16" t="s">
-        <v>202</v>
-      </c>
-      <c r="L16" t="s">
-        <v>196</v>
-      </c>
-      <c r="M16" t="s">
-        <v>203</v>
-      </c>
-      <c r="N16" t="s">
-        <v>204</v>
-      </c>
-      <c r="O16" t="s">
-        <v>197</v>
-      </c>
-      <c r="P16" t="s">
-        <v>205</v>
-      </c>
       <c r="Q16" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="R16" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="S16" t="s">
-        <v>208</v>
+        <v>211</v>
+      </c>
+      <c r="T16" t="s">
+        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -3987,41 +4177,41 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="D1" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="E1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F1" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="E2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
@@ -4029,22 +4219,22 @@
     </row>
     <row r="4" spans="1:6">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="D4" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="E4" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="F4" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4058,10 +4248,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="F5" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4069,16 +4259,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="F6" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4092,10 +4282,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="F7" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4109,10 +4299,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="F8" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4126,10 +4316,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="F9" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4137,16 +4327,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="D10" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="E10" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="F10" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4160,10 +4350,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F11" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4177,10 +4367,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="F12" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
     </row>
   </sheetData>
@@ -4192,7 +4382,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N30"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -4213,129 +4403,132 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="E1" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="G1" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="H1" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="I1" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="J1" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="K1" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="L1" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="M1" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="N1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="G2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="I2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="K2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="L2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="M2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="104.4" spans="1:14">
       <c r="A3" s="3" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>277</v>
+        <v>281</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="4" spans="1:14">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>278</v>
+        <v>283</v>
       </c>
       <c r="D4" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="E4" t="s">
-        <v>280</v>
+        <v>285</v>
       </c>
       <c r="F4" t="s">
-        <v>279</v>
+        <v>284</v>
       </c>
       <c r="G4" t="s">
-        <v>281</v>
+        <v>286</v>
       </c>
       <c r="H4" t="s">
-        <v>282</v>
+        <v>287</v>
       </c>
       <c r="I4" t="s">
-        <v>283</v>
+        <v>288</v>
       </c>
       <c r="J4" t="s">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="K4" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="L4" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="M4" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="N4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4358,13 +4551,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L5" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M5" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -4378,22 +4571,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H6" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L6" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M6" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4407,22 +4600,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H7" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L7" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M7" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4436,22 +4629,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H8" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L8" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M8" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4465,22 +4658,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H9" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L9" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M9" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4494,22 +4687,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L10" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M10" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4523,22 +4716,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H11" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="L11" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="M11" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4552,53 +4745,65 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="H12" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="L12" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="M12" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
     </row>
     <row r="13" spans="1:14">
       <c r="B13">
-        <v>2001</v>
+        <v>1009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>291</v>
+        <v>296</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>292</v>
-      </c>
-      <c r="E13" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="F13" t="s">
-        <v>8</v>
+        <v>297</v>
+      </c>
+      <c r="G13" t="s">
+        <v>172</v>
+      </c>
+      <c r="H13" t="s">
+        <v>175</v>
+      </c>
+      <c r="J13" t="b">
+        <v>0</v>
+      </c>
+      <c r="K13" t="s">
+        <v>293</v>
+      </c>
+      <c r="L13" t="s">
+        <v>298</v>
+      </c>
+      <c r="M13" t="s">
+        <v>299</v>
       </c>
       <c r="N13" t="s">
-        <v>293</v>
+        <v>300</v>
       </c>
     </row>
     <row r="14" spans="1:14">
       <c r="B14">
-        <v>2002</v>
+        <v>2001</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>294</v>
+        <v>301</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>295</v>
+        <v>302</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4607,240 +4812,243 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>293</v>
+        <v>303</v>
       </c>
     </row>
     <row r="15" spans="1:14">
       <c r="B15">
-        <v>2003</v>
+        <v>2002</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="E15" s="4" t="s">
-        <v>16</v>
+        <v>7</v>
       </c>
       <c r="F15" t="s">
-        <v>17</v>
+        <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>298</v>
+        <v>303</v>
       </c>
     </row>
     <row r="16" spans="1:14">
       <c r="B16">
-        <v>2004</v>
+        <v>2003</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>299</v>
+        <v>306</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>300</v>
+        <v>307</v>
       </c>
       <c r="E16" s="4" t="s">
-        <v>301</v>
+        <v>16</v>
       </c>
       <c r="F16" t="s">
-        <v>302</v>
+        <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>303</v>
+        <v>308</v>
       </c>
     </row>
     <row r="17" spans="2:14">
       <c r="B17">
-        <v>2005</v>
+        <v>2004</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>304</v>
+        <v>309</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>305</v>
+        <v>310</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>59</v>
-      </c>
-      <c r="F17" s="4" t="s">
-        <v>60</v>
+        <v>311</v>
+      </c>
+      <c r="F17" t="s">
+        <v>312</v>
       </c>
       <c r="N17" t="s">
-        <v>306</v>
+        <v>313</v>
       </c>
     </row>
     <row r="18" spans="2:14">
       <c r="B18">
-        <v>2006</v>
+        <v>2005</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>307</v>
+        <v>314</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>308</v>
+        <v>315</v>
       </c>
       <c r="E18" s="4" t="s">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="F18" s="4" t="s">
-        <v>67</v>
+        <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>309</v>
+        <v>316</v>
       </c>
     </row>
     <row r="19" spans="2:14">
       <c r="B19">
-        <v>2007</v>
+        <v>2006</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>310</v>
+        <v>317</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>311</v>
+        <v>318</v>
       </c>
       <c r="E19" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F19" t="s">
-        <v>17</v>
+        <v>66</v>
+      </c>
+      <c r="F19" s="4" t="s">
+        <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>312</v>
+        <v>319</v>
       </c>
     </row>
     <row r="20" spans="2:14">
       <c r="B20">
-        <v>2008</v>
+        <v>2007</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>313</v>
+        <v>320</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>314</v>
-      </c>
-      <c r="E20" t="s">
-        <v>301</v>
+        <v>321</v>
+      </c>
+      <c r="E20" s="4" t="s">
+        <v>16</v>
       </c>
       <c r="F20" t="s">
-        <v>302</v>
+        <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>315</v>
+        <v>322</v>
       </c>
     </row>
     <row r="21" spans="2:14">
       <c r="B21">
-        <v>3001</v>
+        <v>2008</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>316</v>
+        <v>323</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>317</v>
-      </c>
-      <c r="E21" s="4" t="s">
-        <v>25</v>
+        <v>324</v>
+      </c>
+      <c r="E21" t="s">
+        <v>311</v>
       </c>
       <c r="F21" t="s">
-        <v>26</v>
+        <v>312</v>
+      </c>
+      <c r="N21" t="s">
+        <v>325</v>
       </c>
     </row>
     <row r="22" spans="2:14">
       <c r="B22">
-        <v>3002</v>
+        <v>2009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>25</v>
-      </c>
-      <c r="F22" t="s">
-        <v>26</v>
+        <v>296</v>
+      </c>
+      <c r="F22" s="4" t="s">
+        <v>297</v>
       </c>
     </row>
     <row r="23" spans="2:14">
       <c r="B23">
-        <v>3003</v>
+        <v>3001</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="E23" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F23" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="24" spans="2:14">
       <c r="B24">
-        <v>3004</v>
+        <v>3002</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="E24" s="4" t="s">
-        <v>34</v>
+        <v>25</v>
       </c>
       <c r="F24" t="s">
-        <v>35</v>
+        <v>26</v>
       </c>
     </row>
     <row r="25" spans="2:14">
       <c r="B25">
-        <v>3005</v>
+        <v>3003</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F25" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="26" spans="2:14">
       <c r="B26">
-        <v>3006</v>
+        <v>3004</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="E26" s="4" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F26" t="s">
-        <v>44</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="2:14">
       <c r="B27">
-        <v>3007</v>
+        <v>3005</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -4848,56 +5056,56 @@
       <c r="F27" t="s">
         <v>44</v>
       </c>
-      <c r="M27" t="s">
-        <v>330</v>
-      </c>
-      <c r="N27" t="s">
-        <v>331</v>
-      </c>
     </row>
     <row r="28" spans="2:14">
       <c r="B28">
-        <v>3008</v>
+        <v>3006</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="E28" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F28" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="29" spans="2:14">
       <c r="B29">
-        <v>3009</v>
+        <v>3007</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="F29" t="s">
-        <v>53</v>
+        <v>44</v>
+      </c>
+      <c r="M29" t="s">
+        <v>299</v>
+      </c>
+      <c r="N29" t="s">
+        <v>300</v>
       </c>
     </row>
     <row r="30" spans="2:14">
       <c r="B30">
-        <v>3010</v>
+        <v>3008</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -4905,11 +5113,45 @@
       <c r="F30" t="s">
         <v>53</v>
       </c>
-      <c r="M30" t="s">
-        <v>330</v>
-      </c>
-      <c r="N30" t="s">
-        <v>331</v>
+    </row>
+    <row r="31" spans="2:14">
+      <c r="B31">
+        <v>3009</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>344</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>345</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F31" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="32" spans="2:14">
+      <c r="B32">
+        <v>3010</v>
+      </c>
+      <c r="C32" s="4" t="s">
+        <v>346</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>347</v>
+      </c>
+      <c r="E32" s="4" t="s">
+        <v>52</v>
+      </c>
+      <c r="F32" t="s">
+        <v>53</v>
+      </c>
+      <c r="M32" t="s">
+        <v>299</v>
+      </c>
+      <c r="N32" t="s">
+        <v>300</v>
       </c>
     </row>
   </sheetData>
@@ -4945,136 +5187,136 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>338</v>
+        <v>348</v>
       </c>
       <c r="D1" t="s">
-        <v>339</v>
+        <v>349</v>
       </c>
       <c r="E1" t="s">
-        <v>340</v>
+        <v>350</v>
       </c>
       <c r="F1" t="s">
-        <v>341</v>
+        <v>351</v>
       </c>
       <c r="G1" t="s">
-        <v>342</v>
+        <v>352</v>
       </c>
       <c r="H1" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="I1" t="s">
-        <v>343</v>
+        <v>353</v>
       </c>
       <c r="J1" t="s">
-        <v>344</v>
+        <v>354</v>
       </c>
       <c r="K1" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
     </row>
     <row r="2" spans="1:11">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="E2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="F2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G2" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="I2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="J2" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="K2" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="3" ht="87" spans="1:11">
       <c r="A3" s="1" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>345</v>
+        <v>355</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>346</v>
+        <v>356</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>347</v>
+        <v>357</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>348</v>
+        <v>358</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>349</v>
+        <v>359</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>350</v>
+        <v>360</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>351</v>
+        <v>361</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>352</v>
+        <v>362</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>353</v>
+        <v>363</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>354</v>
+        <v>364</v>
       </c>
       <c r="D4" t="s">
-        <v>355</v>
+        <v>365</v>
       </c>
       <c r="E4" t="s">
-        <v>356</v>
+        <v>366</v>
       </c>
       <c r="F4" t="s">
-        <v>357</v>
+        <v>367</v>
       </c>
       <c r="G4" t="s">
-        <v>358</v>
+        <v>368</v>
       </c>
       <c r="H4" t="s">
-        <v>359</v>
+        <v>369</v>
       </c>
       <c r="I4" t="s">
-        <v>360</v>
+        <v>370</v>
       </c>
       <c r="J4" t="s">
-        <v>361</v>
+        <v>371</v>
       </c>
       <c r="K4" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5082,7 +5324,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>362</v>
+        <v>372</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5106,7 +5348,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>363</v>
+        <v>373</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5114,7 +5356,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>364</v>
+        <v>374</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5138,7 +5380,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5146,7 +5388,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>366</v>
+        <v>376</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -5170,7 +5412,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>365</v>
+        <v>375</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5178,7 +5420,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>367</v>
+        <v>377</v>
       </c>
       <c r="D8">
         <v>181</v>
@@ -5202,8 +5444,169 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>365</v>
-      </c>
+        <v>375</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:F9"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.25" customWidth="1"/>
+    <col min="3" max="3" width="19.5833333333333" customWidth="1"/>
+    <col min="4" max="4" width="12.75" customWidth="1"/>
+    <col min="5" max="5" width="16.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="30.8333333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>99</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E1" t="s">
+        <v>379</v>
+      </c>
+      <c r="F1" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>158</v>
+      </c>
+      <c r="E2" t="s">
+        <v>279</v>
+      </c>
+      <c r="F2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="52.2" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="3"/>
+      <c r="C3" s="3"/>
+      <c r="D3" s="1" t="s">
+        <v>381</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C4" t="s">
+        <v>383</v>
+      </c>
+      <c r="D4" t="s">
+        <v>384</v>
+      </c>
+      <c r="E4" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>386</v>
+      </c>
+      <c r="D5">
+        <v>0</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
+      </c>
+      <c r="F5" s="4" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6">
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>388</v>
+      </c>
+      <c r="D6">
+        <v>0</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
+      </c>
+      <c r="F6" s="4" t="s">
+        <v>389</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6">
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>390</v>
+      </c>
+      <c r="D7">
+        <v>0</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
+      </c>
+      <c r="F7" s="4" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>392</v>
+      </c>
+      <c r="D8">
+        <v>0</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
+      </c>
+      <c r="F8" s="4" t="s">
+        <v>393</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6">
+      <c r="F9" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="7"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -15,6 +15,8 @@
     <sheet name="DogReaction" sheetId="9" r:id="rId6"/>
     <sheet name="DesktopActivityState" sheetId="11" r:id="rId7"/>
     <sheet name="BGMList" sheetId="12" r:id="rId8"/>
+    <sheet name="Achievement" sheetId="13" r:id="rId9"/>
+    <sheet name="PlayerStatistic" sheetId="14" r:id="rId10"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -34,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="779" uniqueCount="394">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="700">
   <si>
     <t>Dog</t>
   </si>
@@ -390,10 +392,10 @@
     <t>安全中文</t>
   </si>
   <si>
-    <t>JacksOrBetter</t>
-  </si>
-  <si>
-    <t>Jacks or Better</t>
+    <t>OnePair</t>
+  </si>
+  <si>
+    <t>One Pair</t>
   </si>
   <si>
     <t>Top Dogs</t>
@@ -498,13 +500,13 @@
     <t>名称</t>
   </si>
   <si>
-    <t>value</t>
+    <t>value备注</t>
   </si>
   <si>
     <t>描述</t>
   </si>
   <si>
-    <t>BlindBoxTimeScale</t>
+    <t>BlindBoxWaitDurationMultiplier</t>
   </si>
   <si>
     <t>等待盲盒时间倍率</t>
@@ -525,6 +527,33 @@
     <t>盲盒消耗筹码倍率</t>
   </si>
   <si>
+    <t>PlayerStatisticScale</t>
+  </si>
+  <si>
+    <t>统计倍率</t>
+  </si>
+  <si>
+    <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
+  </si>
+  <si>
+    <t>BlindBoxBacklogClaimDelaySeconds</t>
+  </si>
+  <si>
+    <t>积压盲盒展示时短间隔时间</t>
+  </si>
+  <si>
+    <t>秒，实际使用时需要受到BlindBoxTimeScale影响，为了不让玩家对于盲盒间隔的心里预期剧烈变化因此设计了该值</t>
+  </si>
+  <si>
+    <t>BlindBoxPostNewbieDelaySeconds</t>
+  </si>
+  <si>
+    <t>新手与正式盲盒的间隔时间</t>
+  </si>
+  <si>
+    <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -1026,10 +1055,10 @@
     <t>看到坏牌</t>
   </si>
   <si>
-    <t>SawJacksOrBetter</t>
-  </si>
-  <si>
-    <t>看到高对</t>
+    <t>SawOnePair</t>
+  </si>
+  <si>
+    <t>看到一对</t>
   </si>
   <si>
     <t>SawTwoPair</t>
@@ -1216,6 +1245,897 @@
   </si>
   <si>
     <t>Audio/BGM/04.Call It a Day.mp3</t>
+  </si>
+  <si>
+    <t>AchievementId</t>
+  </si>
+  <si>
+    <t>ApiName</t>
+  </si>
+  <si>
+    <t>RuleType</t>
+  </si>
+  <si>
+    <t>TargetKey</t>
+  </si>
+  <si>
+    <t>TargetValue</t>
+  </si>
+  <si>
+    <t>IsHidden</t>
+  </si>
+  <si>
+    <t>EAchievementRuleType</t>
+  </si>
+  <si>
+    <t>long</t>
+  </si>
+  <si>
+    <t>成就唯一 ID；发布后不可复用</t>
+  </si>
+  <si>
+    <t>平台和存档使用的稳定机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType=首次非初始获得部位；FirstExternalItemRarity=首次非初始获得指定品质；FirstEvent=首次发生事件；StatisticAtLeast=统计达到数值</t>
+  </si>
+  <si>
+    <t>由 RuleType 决定含义：部位/品质/事件/PlayerStatistic 的 StatisticKey</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast 的数值门槛；首次类规则填 1</t>
+  </si>
+  <si>
+    <t>是否在平台/游戏内解锁前隐藏</t>
+  </si>
+  <si>
+    <t>填写策划说明或设计约束</t>
+  </si>
+  <si>
+    <t>成就 id</t>
+  </si>
+  <si>
+    <t>API 名</t>
+  </si>
+  <si>
+    <t>解锁规则</t>
+  </si>
+  <si>
+    <t>目标</t>
+  </si>
+  <si>
+    <t>目标数值</t>
+  </si>
+  <si>
+    <t>隐藏成就</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_DOG</t>
+  </si>
+  <si>
+    <t>FirstExternalItemType</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得一只狗；默认红柴不计入</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_HEADWEAR</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得头部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_EYEWEAR</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得眼部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ARM</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得玩家手臂</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CLOTHES</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得衣服</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_TABLE</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得桌布</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_BACKGROUND</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得背景</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ACCESSORY</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得手部装饰</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_REFRESHMENT</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得饮品/消耗品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CARD_BACK</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得卡背</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_CARD_FACE</t>
+  </si>
+  <si>
+    <t>首次从非初始来源获得卡面</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_THREE_OF_A_KIND</t>
+  </si>
+  <si>
+    <t>StatisticAtLeast</t>
+  </si>
+  <si>
+    <t>PokerHandRankThreeOfAKindCount</t>
+  </si>
+  <si>
+    <t>首次达成三条</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_STRAIGHT</t>
+  </si>
+  <si>
+    <t>PokerHandRankStraightCount</t>
+  </si>
+  <si>
+    <t>首次达成顺子</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成同花</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FULL_HOUSE</t>
+  </si>
+  <si>
+    <t>PokerHandRankFullHouseCount</t>
+  </si>
+  <si>
+    <t>首次达成葫芦</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_FOUR_OF_A_KIND</t>
+  </si>
+  <si>
+    <t>PokerHandRankFourOfAKindCount</t>
+  </si>
+  <si>
+    <t>首次达成四条</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_STRAIGHT_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankStraightFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成同花顺</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_ROYAL_FLUSH</t>
+  </si>
+  <si>
+    <t>PokerHandRankRoyalFlushCount</t>
+  </si>
+  <si>
+    <t>首次达成皇家同花顺</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_HINT</t>
+  </si>
+  <si>
+    <t>FirstEvent</t>
+  </si>
+  <si>
+    <t>DogHintAsked</t>
+  </si>
+  <si>
+    <t>首次询问狗狗牌运</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_REFUSAL</t>
+  </si>
+  <si>
+    <t>DogHintRefused</t>
+  </si>
+  <si>
+    <t>首次被狗狗拒绝回答</t>
+  </si>
+  <si>
+    <t>ACH_DOG_FIRST_STARSTRUCK</t>
+  </si>
+  <si>
+    <t>DesktopStarstruckEntered</t>
+  </si>
+  <si>
+    <t>首次打字使狗狗进入崇拜状态；仅状态切换时计一次</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_RARE_ITEM</t>
+  </si>
+  <si>
+    <t>FirstExternalItemRarity</t>
+  </si>
+  <si>
+    <t>首次获得稀有物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_EPIC_ITEM</t>
+  </si>
+  <si>
+    <t>首次获得史诗物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_LEGENDARY_ITEM</t>
+  </si>
+  <si>
+    <t>首次获得传说物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_MYTHIC_ITEM</t>
+  </si>
+  <si>
+    <t>首次获得神话物品</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_BODY_DECORATION</t>
+  </si>
+  <si>
+    <t>BodyDecoration</t>
+  </si>
+  <si>
+    <t>首次获得玩家体表装饰（体毛、纹身、美甲等）</t>
+  </si>
+  <si>
+    <t>StatisticId</t>
+  </si>
+  <si>
+    <t>StatisticKey</t>
+  </si>
+  <si>
+    <t>DisplayName</t>
+  </si>
+  <si>
+    <t>Unit</t>
+  </si>
+  <si>
+    <t>StatisticType</t>
+  </si>
+  <si>
+    <t>PlatformApiName</t>
+  </si>
+  <si>
+    <t>SyncToPlatform</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticUnit</t>
+  </si>
+  <si>
+    <t>EPlayerStatisticType</t>
+  </si>
+  <si>
+    <t>表内稳定数字 ID；发布后不可复用</t>
+  </si>
+  <si>
+    <t>游戏内部、Achievement.TargetKey 和数据导出共用的稳定机器名</t>
+  </si>
+  <si>
+    <t>CSV 数据字典用的中文名称</t>
+  </si>
+  <si>
+    <t>数值单位</t>
+  </si>
+  <si>
+    <t>Counter=只增累计；Maximum=仅保留最高值</t>
+  </si>
+  <si>
+    <t>未来 Steam/其他平台使用的机器名；发布后不要改名</t>
+  </si>
+  <si>
+    <t>未来是否同步到平台统计</t>
+  </si>
+  <si>
+    <t>最重要的统计口径；Debug 行为不应改变任何正式统计</t>
+  </si>
+  <si>
+    <t>统计 id</t>
+  </si>
+  <si>
+    <t>统计键</t>
+  </si>
+  <si>
+    <t>单位</t>
+  </si>
+  <si>
+    <t>统计类型</t>
+  </si>
+  <si>
+    <t>平台 API 名</t>
+  </si>
+  <si>
+    <t>同步平台</t>
+  </si>
+  <si>
+    <t>GameRuntimeSeconds</t>
+  </si>
+  <si>
+    <t>累计游戏运行时间</t>
+  </si>
+  <si>
+    <t>Seconds</t>
+  </si>
+  <si>
+    <t>Counter</t>
+  </si>
+  <si>
+    <t>STAT_GAME_RUNTIME_SECONDS</t>
+  </si>
+  <si>
+    <t>游戏启动至退出的累计运行秒数；对应现有 TotalPlaySeconds</t>
+  </si>
+  <si>
+    <t>AppLaunchCount</t>
+  </si>
+  <si>
+    <t>游戏启动次数</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>STAT_APP_LAUNCH_COUNT</t>
+  </si>
+  <si>
+    <t>累计正常初始化游戏数据的次数</t>
+  </si>
+  <si>
+    <t>DesktopModeSeconds</t>
+  </si>
+  <si>
+    <t>桌宠模式时长</t>
+  </si>
+  <si>
+    <t>STAT_DESKTOP_MODE_SECONDS</t>
+  </si>
+  <si>
+    <t>桌宠模式实际处于可见状态的累计秒数</t>
+  </si>
+  <si>
+    <t>PokerModeSeconds</t>
+  </si>
+  <si>
+    <t>扑克模式时长</t>
+  </si>
+  <si>
+    <t>STAT_POKER_MODE_SECONDS</t>
+  </si>
+  <si>
+    <t>扑克游玩模式处于激活状态的累计秒数</t>
+  </si>
+  <si>
+    <t>GlobalInputCount</t>
+  </si>
+  <si>
+    <t>累计全局输入次数（键鼠）</t>
+  </si>
+  <si>
+    <t>STAT_GLOBAL_INPUT_COUNT</t>
+  </si>
+  <si>
+    <t>真实全局输入次数；不受未来筹码产出倍率影响，目前是打字和筹码1比1，但有频率上限锁（打字包括鼠标点击）</t>
+  </si>
+  <si>
+    <t>GlobalInputChipsEarned</t>
+  </si>
+  <si>
+    <t>累计全局输入获得筹码</t>
+  </si>
+  <si>
+    <t>Chips</t>
+  </si>
+  <si>
+    <t>STAT_GLOBAL_INPUT_CHIPS_EARNED</t>
+  </si>
+  <si>
+    <t>仅累计 GlobalInputTracker 的真实打字奖励筹码（包括鼠标点击）</t>
+  </si>
+  <si>
+    <t>PokerHandsPlayed</t>
+  </si>
+  <si>
+    <t>累计扑克局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_PLAYED</t>
+  </si>
+  <si>
+    <t>成功下注并开始发牌的扑克局数</t>
+  </si>
+  <si>
+    <t>PokerHandsWon</t>
+  </si>
+  <si>
+    <t>累计扑克获胜局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_WON</t>
+  </si>
+  <si>
+    <t>最终结算有正向扑克奖励的局数</t>
+  </si>
+  <si>
+    <t>PokerHandsLost</t>
+  </si>
+  <si>
+    <t>累计扑克未获奖局数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_HANDS_LOST</t>
+  </si>
+  <si>
+    <t>最终结算没有扑克奖励的局数</t>
+  </si>
+  <si>
+    <t>PokerChipsWon</t>
+  </si>
+  <si>
+    <t>累计扑克赢取筹码</t>
+  </si>
+  <si>
+    <t>STAT_POKER_CHIPS_WON</t>
+  </si>
+  <si>
+    <t>仅累计玩家实际收取的扑克奖励；不含打字、盲盒和 Debug 发放</t>
+  </si>
+  <si>
+    <t>PokerChipsWagered</t>
+  </si>
+  <si>
+    <t>累计扑克下注筹码</t>
+  </si>
+  <si>
+    <t>STAT_POKER_CHIPS_WAGERED</t>
+  </si>
+  <si>
+    <t>累计实际下注的扑克筹码</t>
+  </si>
+  <si>
+    <t>PokerHandRankNothingCount</t>
+  </si>
+  <si>
+    <t>坏牌次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_NOTHING_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为坏牌的次数</t>
+  </si>
+  <si>
+    <t>PokerHandRankOnePairCount</t>
+  </si>
+  <si>
+    <t>一对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_ONE_PAIR_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为一对的次数</t>
+  </si>
+  <si>
+    <t>PokerHandRankTwoPairCount</t>
+  </si>
+  <si>
+    <t>两对次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_TWO_PAIR_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为两对的次数</t>
+  </si>
+  <si>
+    <t>三条次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_THREE_OF_A_KIND_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为三条的次数</t>
+  </si>
+  <si>
+    <t>顺子次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_STRAIGHT_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为顺子的次数</t>
+  </si>
+  <si>
+    <t>同花次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为同花的次数</t>
+  </si>
+  <si>
+    <t>葫芦次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FULL_HOUSE_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为葫芦的次数</t>
+  </si>
+  <si>
+    <t>四条次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_FOUR_OF_A_KIND_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为四条的次数</t>
+  </si>
+  <si>
+    <t>同花顺次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_STRAIGHT_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为同花顺的次数</t>
+  </si>
+  <si>
+    <t>皇家同花顺次数</t>
+  </si>
+  <si>
+    <t>STAT_POKER_ROYAL_FLUSH_COUNT</t>
+  </si>
+  <si>
+    <t>最终结算为皇家同花顺的次数</t>
+  </si>
+  <si>
+    <t>BlindBoxOpenedCount</t>
+  </si>
+  <si>
+    <t>打开盲盒次数</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_OPENED_COUNT</t>
+  </si>
+  <si>
+    <t>成功打开盲盒的次数</t>
+  </si>
+  <si>
+    <t>BlindBoxChipsSpent</t>
+  </si>
+  <si>
+    <t>开启盲盒花费筹码</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_CHIPS_SPENT</t>
+  </si>
+  <si>
+    <t>累计实际成功开启盲盒时扣除的筹码；不记录因筹码不足而失败的尝试</t>
+  </si>
+  <si>
+    <t>BlindBoxRewardClaimedCount</t>
+  </si>
+  <si>
+    <t>领取盲盒奖励次数</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_REWARD_CLAIMED_COUNT</t>
+  </si>
+  <si>
+    <t>成功领取盲盒奖励的次数</t>
+  </si>
+  <si>
+    <t>ExternalItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>非初始道具获得数量</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得的道具数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>BlindBoxItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>盲盒获得道具数量</t>
+  </si>
+  <si>
+    <t>STAT_BLIND_BOX_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从盲盒领取到的道具数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>DogHintAskedCount</t>
+  </si>
+  <si>
+    <t>询问狗狗牌运次数</t>
+  </si>
+  <si>
+    <t>STAT_DOG_HINT_ASKED_COUNT</t>
+  </si>
+  <si>
+    <t>玩家询问狗狗牌运的次数</t>
+  </si>
+  <si>
+    <t>DogHintAskedWinningHandCount</t>
+  </si>
+  <si>
+    <t>询问狗狗后获奖局数</t>
+  </si>
+  <si>
+    <t>STAT_DOG_HINT_ASKED_WIN_COUNT</t>
+  </si>
+  <si>
+    <t>该局曾询问狗狗牌运，且最终结算有奖励的次数；不要求玩家完全按建议保留牌</t>
+  </si>
+  <si>
+    <t>ExternalCommonItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得普通物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_COMMON_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得普通品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalUncommonItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得优秀物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_UNCOMMON_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得优秀品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalRareItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得稀有物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_RARE_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得稀有品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalEpicItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得史诗物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_EPIC_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得史诗品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalLegendaryItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得传说物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_LEGENDARY_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得传说品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalMythicItemAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得神话物品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_MYTHIC_ITEM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得神话品质物品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalDogAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得狗狗数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_DOG_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得狗狗的数量；重复狗狗按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalHeadwearAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得帽子数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_HEADWEAR_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得头部装饰的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalEyewearAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得眼镜数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_EYEWEAR_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得眼部装饰的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalArmAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得手臂数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ARM_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得 Arm 部位道具的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalClothesAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得衣服数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_CLOTHES_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得衣服的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalTableAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得桌布数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_TABLE_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得桌布的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalBackgroundAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得背景数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_BACKGROUND_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得背景的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalAccessoryAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得手部装饰数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_ACCESSORY_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得手部装饰的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalRefreshmentAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得饮品数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_REFRESHMENT_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得饮品/消耗品的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalCardBackAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得卡背数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_CARD_BACK_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得卡背的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalCardFaceAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得卡面数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_CARD_FACE_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得卡面的数量；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>ExternalBodyDecorationAcquiredCount</t>
+  </si>
+  <si>
+    <t>获得体表装饰数</t>
+  </si>
+  <si>
+    <t>STAT_EXTERNAL_BODY_DECORATION_ACQUIRED_COUNT</t>
+  </si>
+  <si>
+    <t>从非初始来源获得体表装饰的数量，例如体毛、纹身、美甲；重复道具按实际数量累计</t>
+  </si>
+  <si>
+    <t>PeakHalfHourInputChipsEarned</t>
+  </si>
+  <si>
+    <t>半小时周期打字筹码峰值</t>
+  </si>
+  <si>
+    <t>Maximum</t>
+  </si>
+  <si>
+    <t>STAT_PEAK_HALF_HOUR_INPUT_CHIPS_EARNED</t>
+  </si>
+  <si>
+    <t>游戏运行期间，按系统本地时间的自然半小时分段累计键鼠获得的筹码；首尾分段可能不足 30 分钟。</t>
   </si>
 </sst>
 </file>
@@ -2766,6 +3686,1502 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I51"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="11.5833333333333" customWidth="1"/>
+    <col min="3" max="3" width="30.9166666666667" customWidth="1"/>
+    <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
+    <col min="5" max="5" width="14.9166666666667" customWidth="1"/>
+    <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
+    <col min="7" max="7" width="51" customWidth="1"/>
+    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
+    <col min="9" max="9" width="53.0833333333333" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>491</v>
+      </c>
+      <c r="C1" t="s">
+        <v>492</v>
+      </c>
+      <c r="D1" t="s">
+        <v>493</v>
+      </c>
+      <c r="E1" t="s">
+        <v>494</v>
+      </c>
+      <c r="F1" t="s">
+        <v>495</v>
+      </c>
+      <c r="G1" t="s">
+        <v>496</v>
+      </c>
+      <c r="H1" t="s">
+        <v>497</v>
+      </c>
+      <c r="I1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>109</v>
+      </c>
+      <c r="E2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F2" t="s">
+        <v>499</v>
+      </c>
+      <c r="G2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>288</v>
+      </c>
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="89" customHeight="1" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>503</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>504</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>505</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>506</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>508</v>
+      </c>
+      <c r="C4" t="s">
+        <v>509</v>
+      </c>
+      <c r="D4" t="s">
+        <v>254</v>
+      </c>
+      <c r="E4" t="s">
+        <v>510</v>
+      </c>
+      <c r="F4" t="s">
+        <v>511</v>
+      </c>
+      <c r="G4" t="s">
+        <v>512</v>
+      </c>
+      <c r="H4" t="s">
+        <v>513</v>
+      </c>
+      <c r="I4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5">
+        <v>1001</v>
+      </c>
+      <c r="C5" t="s">
+        <v>514</v>
+      </c>
+      <c r="D5" t="s">
+        <v>515</v>
+      </c>
+      <c r="E5" t="s">
+        <v>516</v>
+      </c>
+      <c r="F5" t="s">
+        <v>517</v>
+      </c>
+      <c r="G5" t="s">
+        <v>518</v>
+      </c>
+      <c r="H5" t="b">
+        <v>1</v>
+      </c>
+      <c r="I5" t="s">
+        <v>519</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B6">
+        <v>1002</v>
+      </c>
+      <c r="C6" t="s">
+        <v>520</v>
+      </c>
+      <c r="D6" t="s">
+        <v>521</v>
+      </c>
+      <c r="E6" t="s">
+        <v>522</v>
+      </c>
+      <c r="F6" t="s">
+        <v>517</v>
+      </c>
+      <c r="G6" t="s">
+        <v>523</v>
+      </c>
+      <c r="H6" t="b">
+        <v>1</v>
+      </c>
+      <c r="I6" t="s">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B7">
+        <v>1003</v>
+      </c>
+      <c r="C7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D7" t="s">
+        <v>526</v>
+      </c>
+      <c r="E7" t="s">
+        <v>516</v>
+      </c>
+      <c r="F7" t="s">
+        <v>517</v>
+      </c>
+      <c r="G7" t="s">
+        <v>527</v>
+      </c>
+      <c r="H7" t="b">
+        <v>1</v>
+      </c>
+      <c r="I7" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8">
+        <v>1004</v>
+      </c>
+      <c r="C8" t="s">
+        <v>529</v>
+      </c>
+      <c r="D8" t="s">
+        <v>530</v>
+      </c>
+      <c r="E8" t="s">
+        <v>516</v>
+      </c>
+      <c r="F8" t="s">
+        <v>517</v>
+      </c>
+      <c r="G8" t="s">
+        <v>531</v>
+      </c>
+      <c r="H8" t="b">
+        <v>1</v>
+      </c>
+      <c r="I8" t="s">
+        <v>532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B9">
+        <v>1005</v>
+      </c>
+      <c r="C9" t="s">
+        <v>533</v>
+      </c>
+      <c r="D9" t="s">
+        <v>534</v>
+      </c>
+      <c r="E9" t="s">
+        <v>522</v>
+      </c>
+      <c r="F9" t="s">
+        <v>517</v>
+      </c>
+      <c r="G9" t="s">
+        <v>535</v>
+      </c>
+      <c r="H9" t="b">
+        <v>1</v>
+      </c>
+      <c r="I9" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B10">
+        <v>1006</v>
+      </c>
+      <c r="C10" t="s">
+        <v>537</v>
+      </c>
+      <c r="D10" t="s">
+        <v>538</v>
+      </c>
+      <c r="E10" t="s">
+        <v>539</v>
+      </c>
+      <c r="F10" t="s">
+        <v>517</v>
+      </c>
+      <c r="G10" t="s">
+        <v>540</v>
+      </c>
+      <c r="H10" t="b">
+        <v>1</v>
+      </c>
+      <c r="I10" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11">
+        <v>1007</v>
+      </c>
+      <c r="C11" t="s">
+        <v>542</v>
+      </c>
+      <c r="D11" t="s">
+        <v>543</v>
+      </c>
+      <c r="E11" t="s">
+        <v>522</v>
+      </c>
+      <c r="F11" t="s">
+        <v>517</v>
+      </c>
+      <c r="G11" t="s">
+        <v>544</v>
+      </c>
+      <c r="H11" t="b">
+        <v>1</v>
+      </c>
+      <c r="I11" t="s">
+        <v>545</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B12">
+        <v>1008</v>
+      </c>
+      <c r="C12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D12" t="s">
+        <v>547</v>
+      </c>
+      <c r="E12" t="s">
+        <v>522</v>
+      </c>
+      <c r="F12" t="s">
+        <v>517</v>
+      </c>
+      <c r="G12" t="s">
+        <v>548</v>
+      </c>
+      <c r="H12" t="b">
+        <v>1</v>
+      </c>
+      <c r="I12" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9">
+      <c r="A13" t="s">
+        <v>384</v>
+      </c>
+      <c r="B13">
+        <v>1009</v>
+      </c>
+      <c r="C13" t="s">
+        <v>550</v>
+      </c>
+      <c r="D13" t="s">
+        <v>551</v>
+      </c>
+      <c r="E13" t="s">
+        <v>522</v>
+      </c>
+      <c r="F13" t="s">
+        <v>517</v>
+      </c>
+      <c r="G13" t="s">
+        <v>552</v>
+      </c>
+      <c r="H13" t="b">
+        <v>1</v>
+      </c>
+      <c r="I13" t="s">
+        <v>553</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9">
+      <c r="A14" t="s">
+        <v>384</v>
+      </c>
+      <c r="B14">
+        <v>1010</v>
+      </c>
+      <c r="C14" t="s">
+        <v>554</v>
+      </c>
+      <c r="D14" t="s">
+        <v>555</v>
+      </c>
+      <c r="E14" t="s">
+        <v>539</v>
+      </c>
+      <c r="F14" t="s">
+        <v>517</v>
+      </c>
+      <c r="G14" t="s">
+        <v>556</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
+      </c>
+      <c r="I14" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9">
+      <c r="A15" t="s">
+        <v>384</v>
+      </c>
+      <c r="B15">
+        <v>1011</v>
+      </c>
+      <c r="C15" t="s">
+        <v>558</v>
+      </c>
+      <c r="D15" t="s">
+        <v>559</v>
+      </c>
+      <c r="E15" t="s">
+        <v>539</v>
+      </c>
+      <c r="F15" t="s">
+        <v>517</v>
+      </c>
+      <c r="G15" t="s">
+        <v>560</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
+      </c>
+      <c r="I15" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9">
+      <c r="A16" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16">
+        <v>1012</v>
+      </c>
+      <c r="C16" t="s">
+        <v>562</v>
+      </c>
+      <c r="D16" t="s">
+        <v>563</v>
+      </c>
+      <c r="E16" t="s">
+        <v>522</v>
+      </c>
+      <c r="F16" t="s">
+        <v>517</v>
+      </c>
+      <c r="G16" t="s">
+        <v>564</v>
+      </c>
+      <c r="H16" t="b">
+        <v>1</v>
+      </c>
+      <c r="I16" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9">
+      <c r="A17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17">
+        <v>1013</v>
+      </c>
+      <c r="C17" t="s">
+        <v>566</v>
+      </c>
+      <c r="D17" t="s">
+        <v>567</v>
+      </c>
+      <c r="E17" t="s">
+        <v>522</v>
+      </c>
+      <c r="F17" t="s">
+        <v>517</v>
+      </c>
+      <c r="G17" t="s">
+        <v>568</v>
+      </c>
+      <c r="H17" t="b">
+        <v>1</v>
+      </c>
+      <c r="I17" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9">
+      <c r="A18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B18">
+        <v>1014</v>
+      </c>
+      <c r="C18" t="s">
+        <v>570</v>
+      </c>
+      <c r="D18" t="s">
+        <v>571</v>
+      </c>
+      <c r="E18" t="s">
+        <v>522</v>
+      </c>
+      <c r="F18" t="s">
+        <v>517</v>
+      </c>
+      <c r="G18" t="s">
+        <v>572</v>
+      </c>
+      <c r="H18" t="b">
+        <v>1</v>
+      </c>
+      <c r="I18" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9">
+      <c r="A19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19">
+        <v>1015</v>
+      </c>
+      <c r="C19" t="s">
+        <v>449</v>
+      </c>
+      <c r="D19" t="s">
+        <v>574</v>
+      </c>
+      <c r="E19" t="s">
+        <v>522</v>
+      </c>
+      <c r="F19" t="s">
+        <v>517</v>
+      </c>
+      <c r="G19" t="s">
+        <v>575</v>
+      </c>
+      <c r="H19" t="b">
+        <v>1</v>
+      </c>
+      <c r="I19" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9">
+      <c r="A20" t="s">
+        <v>384</v>
+      </c>
+      <c r="B20">
+        <v>1016</v>
+      </c>
+      <c r="C20" t="s">
+        <v>452</v>
+      </c>
+      <c r="D20" t="s">
+        <v>577</v>
+      </c>
+      <c r="E20" t="s">
+        <v>522</v>
+      </c>
+      <c r="F20" t="s">
+        <v>517</v>
+      </c>
+      <c r="G20" t="s">
+        <v>578</v>
+      </c>
+      <c r="H20" t="b">
+        <v>1</v>
+      </c>
+      <c r="I20" t="s">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9">
+      <c r="A21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B21">
+        <v>1017</v>
+      </c>
+      <c r="C21" t="s">
+        <v>455</v>
+      </c>
+      <c r="D21" t="s">
+        <v>580</v>
+      </c>
+      <c r="E21" t="s">
+        <v>522</v>
+      </c>
+      <c r="F21" t="s">
+        <v>517</v>
+      </c>
+      <c r="G21" t="s">
+        <v>581</v>
+      </c>
+      <c r="H21" t="b">
+        <v>1</v>
+      </c>
+      <c r="I21" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9">
+      <c r="A22" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22">
+        <v>1018</v>
+      </c>
+      <c r="C22" t="s">
+        <v>458</v>
+      </c>
+      <c r="D22" t="s">
+        <v>583</v>
+      </c>
+      <c r="E22" t="s">
+        <v>522</v>
+      </c>
+      <c r="F22" t="s">
+        <v>517</v>
+      </c>
+      <c r="G22" t="s">
+        <v>584</v>
+      </c>
+      <c r="H22" t="b">
+        <v>1</v>
+      </c>
+      <c r="I22" t="s">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9">
+      <c r="A23" t="s">
+        <v>384</v>
+      </c>
+      <c r="B23">
+        <v>1019</v>
+      </c>
+      <c r="C23" t="s">
+        <v>461</v>
+      </c>
+      <c r="D23" t="s">
+        <v>586</v>
+      </c>
+      <c r="E23" t="s">
+        <v>522</v>
+      </c>
+      <c r="F23" t="s">
+        <v>517</v>
+      </c>
+      <c r="G23" t="s">
+        <v>587</v>
+      </c>
+      <c r="H23" t="b">
+        <v>1</v>
+      </c>
+      <c r="I23" t="s">
+        <v>588</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9">
+      <c r="A24" t="s">
+        <v>384</v>
+      </c>
+      <c r="B24">
+        <v>1020</v>
+      </c>
+      <c r="C24" t="s">
+        <v>464</v>
+      </c>
+      <c r="D24" t="s">
+        <v>589</v>
+      </c>
+      <c r="E24" t="s">
+        <v>522</v>
+      </c>
+      <c r="F24" t="s">
+        <v>517</v>
+      </c>
+      <c r="G24" t="s">
+        <v>590</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
+      </c>
+      <c r="I24" t="s">
+        <v>591</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9">
+      <c r="A25" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25">
+        <v>1021</v>
+      </c>
+      <c r="C25" t="s">
+        <v>467</v>
+      </c>
+      <c r="D25" t="s">
+        <v>592</v>
+      </c>
+      <c r="E25" t="s">
+        <v>522</v>
+      </c>
+      <c r="F25" t="s">
+        <v>517</v>
+      </c>
+      <c r="G25" t="s">
+        <v>593</v>
+      </c>
+      <c r="H25" t="b">
+        <v>1</v>
+      </c>
+      <c r="I25" t="s">
+        <v>594</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9">
+      <c r="A26" t="s">
+        <v>384</v>
+      </c>
+      <c r="B26">
+        <v>1022</v>
+      </c>
+      <c r="C26" t="s">
+        <v>595</v>
+      </c>
+      <c r="D26" t="s">
+        <v>596</v>
+      </c>
+      <c r="E26" t="s">
+        <v>522</v>
+      </c>
+      <c r="F26" t="s">
+        <v>517</v>
+      </c>
+      <c r="G26" t="s">
+        <v>597</v>
+      </c>
+      <c r="H26" t="b">
+        <v>1</v>
+      </c>
+      <c r="I26" t="s">
+        <v>598</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9">
+      <c r="A27" t="s">
+        <v>384</v>
+      </c>
+      <c r="B27">
+        <v>1030</v>
+      </c>
+      <c r="C27" t="s">
+        <v>599</v>
+      </c>
+      <c r="D27" t="s">
+        <v>600</v>
+      </c>
+      <c r="E27" t="s">
+        <v>539</v>
+      </c>
+      <c r="F27" t="s">
+        <v>517</v>
+      </c>
+      <c r="G27" t="s">
+        <v>601</v>
+      </c>
+      <c r="H27" t="b">
+        <v>1</v>
+      </c>
+      <c r="I27" t="s">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9">
+      <c r="A28" t="s">
+        <v>384</v>
+      </c>
+      <c r="B28">
+        <v>1023</v>
+      </c>
+      <c r="C28" t="s">
+        <v>603</v>
+      </c>
+      <c r="D28" t="s">
+        <v>604</v>
+      </c>
+      <c r="E28" t="s">
+        <v>522</v>
+      </c>
+      <c r="F28" t="s">
+        <v>517</v>
+      </c>
+      <c r="G28" t="s">
+        <v>605</v>
+      </c>
+      <c r="H28" t="b">
+        <v>1</v>
+      </c>
+      <c r="I28" t="s">
+        <v>606</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9">
+      <c r="A29" t="s">
+        <v>384</v>
+      </c>
+      <c r="B29">
+        <v>1024</v>
+      </c>
+      <c r="C29" t="s">
+        <v>607</v>
+      </c>
+      <c r="D29" t="s">
+        <v>608</v>
+      </c>
+      <c r="E29" t="s">
+        <v>522</v>
+      </c>
+      <c r="F29" t="s">
+        <v>517</v>
+      </c>
+      <c r="G29" t="s">
+        <v>609</v>
+      </c>
+      <c r="H29" t="b">
+        <v>1</v>
+      </c>
+      <c r="I29" t="s">
+        <v>610</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9">
+      <c r="A30" t="s">
+        <v>384</v>
+      </c>
+      <c r="B30">
+        <v>1025</v>
+      </c>
+      <c r="C30" t="s">
+        <v>611</v>
+      </c>
+      <c r="D30" t="s">
+        <v>612</v>
+      </c>
+      <c r="E30" t="s">
+        <v>522</v>
+      </c>
+      <c r="F30" t="s">
+        <v>517</v>
+      </c>
+      <c r="G30" t="s">
+        <v>613</v>
+      </c>
+      <c r="H30" t="b">
+        <v>1</v>
+      </c>
+      <c r="I30" t="s">
+        <v>614</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9">
+      <c r="A31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B31">
+        <v>1026</v>
+      </c>
+      <c r="C31" t="s">
+        <v>615</v>
+      </c>
+      <c r="D31" t="s">
+        <v>616</v>
+      </c>
+      <c r="E31" t="s">
+        <v>522</v>
+      </c>
+      <c r="F31" t="s">
+        <v>517</v>
+      </c>
+      <c r="G31" t="s">
+        <v>617</v>
+      </c>
+      <c r="H31" t="b">
+        <v>1</v>
+      </c>
+      <c r="I31" t="s">
+        <v>618</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9">
+      <c r="A32" t="s">
+        <v>384</v>
+      </c>
+      <c r="B32">
+        <v>1031</v>
+      </c>
+      <c r="C32" t="s">
+        <v>619</v>
+      </c>
+      <c r="D32" t="s">
+        <v>620</v>
+      </c>
+      <c r="E32" t="s">
+        <v>522</v>
+      </c>
+      <c r="F32" t="s">
+        <v>517</v>
+      </c>
+      <c r="G32" t="s">
+        <v>621</v>
+      </c>
+      <c r="H32" t="b">
+        <v>1</v>
+      </c>
+      <c r="I32" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" t="s">
+        <v>384</v>
+      </c>
+      <c r="B33">
+        <v>1032</v>
+      </c>
+      <c r="C33" t="s">
+        <v>623</v>
+      </c>
+      <c r="D33" t="s">
+        <v>624</v>
+      </c>
+      <c r="E33" t="s">
+        <v>522</v>
+      </c>
+      <c r="F33" t="s">
+        <v>517</v>
+      </c>
+      <c r="G33" t="s">
+        <v>625</v>
+      </c>
+      <c r="H33" t="b">
+        <v>1</v>
+      </c>
+      <c r="I33" t="s">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" t="s">
+        <v>384</v>
+      </c>
+      <c r="B34">
+        <v>1033</v>
+      </c>
+      <c r="C34" t="s">
+        <v>627</v>
+      </c>
+      <c r="D34" t="s">
+        <v>628</v>
+      </c>
+      <c r="E34" t="s">
+        <v>522</v>
+      </c>
+      <c r="F34" t="s">
+        <v>517</v>
+      </c>
+      <c r="G34" t="s">
+        <v>629</v>
+      </c>
+      <c r="H34" t="b">
+        <v>1</v>
+      </c>
+      <c r="I34" t="s">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" t="s">
+        <v>384</v>
+      </c>
+      <c r="B35">
+        <v>1034</v>
+      </c>
+      <c r="C35" t="s">
+        <v>631</v>
+      </c>
+      <c r="D35" t="s">
+        <v>632</v>
+      </c>
+      <c r="E35" t="s">
+        <v>522</v>
+      </c>
+      <c r="F35" t="s">
+        <v>517</v>
+      </c>
+      <c r="G35" t="s">
+        <v>633</v>
+      </c>
+      <c r="H35" t="b">
+        <v>1</v>
+      </c>
+      <c r="I35" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="A36" t="s">
+        <v>384</v>
+      </c>
+      <c r="B36">
+        <v>1035</v>
+      </c>
+      <c r="C36" t="s">
+        <v>635</v>
+      </c>
+      <c r="D36" t="s">
+        <v>636</v>
+      </c>
+      <c r="E36" t="s">
+        <v>522</v>
+      </c>
+      <c r="F36" t="s">
+        <v>517</v>
+      </c>
+      <c r="G36" t="s">
+        <v>637</v>
+      </c>
+      <c r="H36" t="b">
+        <v>1</v>
+      </c>
+      <c r="I36" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" t="s">
+        <v>384</v>
+      </c>
+      <c r="B37">
+        <v>1036</v>
+      </c>
+      <c r="C37" t="s">
+        <v>639</v>
+      </c>
+      <c r="D37" t="s">
+        <v>640</v>
+      </c>
+      <c r="E37" t="s">
+        <v>522</v>
+      </c>
+      <c r="F37" t="s">
+        <v>517</v>
+      </c>
+      <c r="G37" t="s">
+        <v>641</v>
+      </c>
+      <c r="H37" t="b">
+        <v>1</v>
+      </c>
+      <c r="I37" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9">
+      <c r="A38" t="s">
+        <v>384</v>
+      </c>
+      <c r="B38">
+        <v>1037</v>
+      </c>
+      <c r="C38" t="s">
+        <v>643</v>
+      </c>
+      <c r="D38" t="s">
+        <v>644</v>
+      </c>
+      <c r="E38" t="s">
+        <v>522</v>
+      </c>
+      <c r="F38" t="s">
+        <v>517</v>
+      </c>
+      <c r="G38" t="s">
+        <v>645</v>
+      </c>
+      <c r="H38" t="b">
+        <v>1</v>
+      </c>
+      <c r="I38" t="s">
+        <v>646</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9">
+      <c r="A39" t="s">
+        <v>384</v>
+      </c>
+      <c r="B39">
+        <v>1038</v>
+      </c>
+      <c r="C39" t="s">
+        <v>647</v>
+      </c>
+      <c r="D39" t="s">
+        <v>648</v>
+      </c>
+      <c r="E39" t="s">
+        <v>522</v>
+      </c>
+      <c r="F39" t="s">
+        <v>517</v>
+      </c>
+      <c r="G39" t="s">
+        <v>649</v>
+      </c>
+      <c r="H39" t="b">
+        <v>1</v>
+      </c>
+      <c r="I39" t="s">
+        <v>650</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9">
+      <c r="A40" t="s">
+        <v>384</v>
+      </c>
+      <c r="B40">
+        <v>1039</v>
+      </c>
+      <c r="C40" t="s">
+        <v>651</v>
+      </c>
+      <c r="D40" t="s">
+        <v>652</v>
+      </c>
+      <c r="E40" t="s">
+        <v>522</v>
+      </c>
+      <c r="F40" t="s">
+        <v>517</v>
+      </c>
+      <c r="G40" t="s">
+        <v>653</v>
+      </c>
+      <c r="H40" t="b">
+        <v>1</v>
+      </c>
+      <c r="I40" t="s">
+        <v>654</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" t="s">
+        <v>384</v>
+      </c>
+      <c r="B41">
+        <v>1040</v>
+      </c>
+      <c r="C41" t="s">
+        <v>655</v>
+      </c>
+      <c r="D41" t="s">
+        <v>656</v>
+      </c>
+      <c r="E41" t="s">
+        <v>522</v>
+      </c>
+      <c r="F41" t="s">
+        <v>517</v>
+      </c>
+      <c r="G41" t="s">
+        <v>657</v>
+      </c>
+      <c r="H41" t="b">
+        <v>1</v>
+      </c>
+      <c r="I41" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" t="s">
+        <v>384</v>
+      </c>
+      <c r="B42">
+        <v>1041</v>
+      </c>
+      <c r="C42" t="s">
+        <v>659</v>
+      </c>
+      <c r="D42" t="s">
+        <v>660</v>
+      </c>
+      <c r="E42" t="s">
+        <v>522</v>
+      </c>
+      <c r="F42" t="s">
+        <v>517</v>
+      </c>
+      <c r="G42" t="s">
+        <v>661</v>
+      </c>
+      <c r="H42" t="b">
+        <v>1</v>
+      </c>
+      <c r="I42" t="s">
+        <v>662</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9">
+      <c r="A43" t="s">
+        <v>384</v>
+      </c>
+      <c r="B43">
+        <v>1042</v>
+      </c>
+      <c r="C43" t="s">
+        <v>663</v>
+      </c>
+      <c r="D43" t="s">
+        <v>664</v>
+      </c>
+      <c r="E43" t="s">
+        <v>522</v>
+      </c>
+      <c r="F43" t="s">
+        <v>517</v>
+      </c>
+      <c r="G43" t="s">
+        <v>665</v>
+      </c>
+      <c r="H43" t="b">
+        <v>1</v>
+      </c>
+      <c r="I43" t="s">
+        <v>666</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9">
+      <c r="A44" t="s">
+        <v>384</v>
+      </c>
+      <c r="B44">
+        <v>1043</v>
+      </c>
+      <c r="C44" t="s">
+        <v>667</v>
+      </c>
+      <c r="D44" t="s">
+        <v>668</v>
+      </c>
+      <c r="E44" t="s">
+        <v>522</v>
+      </c>
+      <c r="F44" t="s">
+        <v>517</v>
+      </c>
+      <c r="G44" t="s">
+        <v>669</v>
+      </c>
+      <c r="H44" t="b">
+        <v>1</v>
+      </c>
+      <c r="I44" t="s">
+        <v>670</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="A45" t="s">
+        <v>384</v>
+      </c>
+      <c r="B45">
+        <v>1044</v>
+      </c>
+      <c r="C45" t="s">
+        <v>671</v>
+      </c>
+      <c r="D45" t="s">
+        <v>672</v>
+      </c>
+      <c r="E45" t="s">
+        <v>522</v>
+      </c>
+      <c r="F45" t="s">
+        <v>517</v>
+      </c>
+      <c r="G45" t="s">
+        <v>673</v>
+      </c>
+      <c r="H45" t="b">
+        <v>1</v>
+      </c>
+      <c r="I45" t="s">
+        <v>674</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="A46" t="s">
+        <v>384</v>
+      </c>
+      <c r="B46">
+        <v>1045</v>
+      </c>
+      <c r="C46" t="s">
+        <v>675</v>
+      </c>
+      <c r="D46" t="s">
+        <v>676</v>
+      </c>
+      <c r="E46" t="s">
+        <v>522</v>
+      </c>
+      <c r="F46" t="s">
+        <v>517</v>
+      </c>
+      <c r="G46" t="s">
+        <v>677</v>
+      </c>
+      <c r="H46" t="b">
+        <v>1</v>
+      </c>
+      <c r="I46" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="A47" t="s">
+        <v>384</v>
+      </c>
+      <c r="B47">
+        <v>1046</v>
+      </c>
+      <c r="C47" t="s">
+        <v>679</v>
+      </c>
+      <c r="D47" t="s">
+        <v>680</v>
+      </c>
+      <c r="E47" t="s">
+        <v>522</v>
+      </c>
+      <c r="F47" t="s">
+        <v>517</v>
+      </c>
+      <c r="G47" t="s">
+        <v>681</v>
+      </c>
+      <c r="H47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I47" t="s">
+        <v>682</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="A48" t="s">
+        <v>384</v>
+      </c>
+      <c r="B48">
+        <v>1047</v>
+      </c>
+      <c r="C48" t="s">
+        <v>683</v>
+      </c>
+      <c r="D48" t="s">
+        <v>684</v>
+      </c>
+      <c r="E48" t="s">
+        <v>522</v>
+      </c>
+      <c r="F48" t="s">
+        <v>517</v>
+      </c>
+      <c r="G48" t="s">
+        <v>685</v>
+      </c>
+      <c r="H48" t="b">
+        <v>1</v>
+      </c>
+      <c r="I48" t="s">
+        <v>686</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9">
+      <c r="A49" t="s">
+        <v>384</v>
+      </c>
+      <c r="B49">
+        <v>1048</v>
+      </c>
+      <c r="C49" t="s">
+        <v>687</v>
+      </c>
+      <c r="D49" t="s">
+        <v>688</v>
+      </c>
+      <c r="E49" t="s">
+        <v>522</v>
+      </c>
+      <c r="F49" t="s">
+        <v>517</v>
+      </c>
+      <c r="G49" t="s">
+        <v>689</v>
+      </c>
+      <c r="H49" t="b">
+        <v>1</v>
+      </c>
+      <c r="I49" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9">
+      <c r="B50">
+        <v>1049</v>
+      </c>
+      <c r="C50" t="s">
+        <v>691</v>
+      </c>
+      <c r="D50" t="s">
+        <v>692</v>
+      </c>
+      <c r="E50" t="s">
+        <v>522</v>
+      </c>
+      <c r="F50" t="s">
+        <v>517</v>
+      </c>
+      <c r="G50" t="s">
+        <v>693</v>
+      </c>
+      <c r="H50" t="b">
+        <v>1</v>
+      </c>
+      <c r="I50" t="s">
+        <v>694</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9">
+      <c r="B51">
+        <v>1050</v>
+      </c>
+      <c r="C51" t="s">
+        <v>695</v>
+      </c>
+      <c r="D51" t="s">
+        <v>696</v>
+      </c>
+      <c r="E51" t="s">
+        <v>539</v>
+      </c>
+      <c r="F51" t="s">
+        <v>697</v>
+      </c>
+      <c r="G51" t="s">
+        <v>698</v>
+      </c>
+      <c r="H51" t="b">
+        <v>1</v>
+      </c>
+      <c r="I51" t="s">
+        <v>699</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
@@ -2837,7 +5253,6 @@
         <v>110</v>
       </c>
       <c r="B3" s="3"/>
-      <c r="C3"/>
       <c r="D3" t="s">
         <v>111</v>
       </c>
@@ -3112,9 +5527,9 @@
   <dimension ref="A1:E10"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
   <cols>
-    <col min="1" max="1" width="21.9166666666667" customWidth="1"/>
-    <col min="2" max="2" width="15.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="70.1666666666667" customWidth="1"/>
+    <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
+    <col min="2" max="2" width="22.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="84.5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
@@ -3180,23 +5595,55 @@
       </c>
     </row>
     <row r="5" spans="1:5">
-      <c r="A5" s="2"/>
-      <c r="B5" s="2"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="2"/>
+      <c r="A5" s="2" t="s">
+        <v>163</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C5" t="s">
+        <v>158</v>
+      </c>
+      <c r="D5" s="2">
+        <v>10</v>
+      </c>
+      <c r="E5" t="s">
+        <v>165</v>
+      </c>
     </row>
     <row r="6" spans="1:5">
-      <c r="A6" s="2"/>
-      <c r="B6" s="2"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
+      <c r="A6" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="C6" t="s">
+        <v>158</v>
+      </c>
+      <c r="D6" s="2">
+        <v>30</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>168</v>
+      </c>
     </row>
     <row r="7" spans="1:5">
-      <c r="A7" s="2"/>
-      <c r="B7" s="2"/>
-      <c r="C7" s="4"/>
-      <c r="D7" s="2"/>
-      <c r="E7" s="2"/>
+      <c r="A7" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="C7" t="s">
+        <v>158</v>
+      </c>
+      <c r="D7" s="2">
+        <v>60</v>
+      </c>
+      <c r="E7" t="s">
+        <v>171</v>
+      </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8" s="2"/>
@@ -3256,55 +5703,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>163</v>
+        <v>172</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>164</v>
+        <v>173</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>165</v>
+        <v>174</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>166</v>
+        <v>175</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>167</v>
+        <v>176</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>168</v>
+        <v>177</v>
       </c>
       <c r="J1" t="s">
-        <v>169</v>
+        <v>178</v>
       </c>
       <c r="K1" t="s">
-        <v>170</v>
+        <v>179</v>
       </c>
       <c r="L1" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="M1" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="N1" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="O1" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="P1" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="Q1" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="R1" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="S1" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="T1" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -3375,10 +5822,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -3392,55 +5839,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="D4" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="E4" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="F4" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H4" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="I4" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J4" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="K4" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="L4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="M4" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="N4" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="O4" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="P4" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="Q4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="R4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="S4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="T4" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -3448,58 +5895,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="D5" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="E5" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F5" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G5" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H5" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="I5" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="J5" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K5" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="L5" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M5" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N5" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O5" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P5" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="Q5" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R5" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S5" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T5" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -3507,58 +5954,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>222</v>
+      </c>
+      <c r="D6" t="s">
+        <v>223</v>
+      </c>
+      <c r="E6" t="s">
+        <v>209</v>
+      </c>
+      <c r="F6" t="s">
+        <v>218</v>
+      </c>
+      <c r="G6" t="s">
+        <v>180</v>
+      </c>
+      <c r="H6" t="s">
+        <v>224</v>
+      </c>
+      <c r="I6" t="s">
+        <v>212</v>
+      </c>
+      <c r="J6" t="s">
         <v>213</v>
       </c>
-      <c r="D6" t="s">
+      <c r="K6" t="s">
         <v>214</v>
       </c>
-      <c r="E6" t="s">
-        <v>200</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="L6" t="s">
+        <v>215</v>
+      </c>
+      <c r="M6" t="s">
         <v>209</v>
       </c>
-      <c r="G6" t="s">
-        <v>171</v>
-      </c>
-      <c r="H6" t="s">
-        <v>215</v>
-      </c>
-      <c r="I6" t="s">
-        <v>203</v>
-      </c>
-      <c r="J6" t="s">
-        <v>204</v>
-      </c>
-      <c r="K6" t="s">
-        <v>205</v>
-      </c>
-      <c r="L6" t="s">
-        <v>206</v>
-      </c>
-      <c r="M6" t="s">
-        <v>200</v>
-      </c>
       <c r="N6" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O6" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P6" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="Q6" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R6" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S6" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T6" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -3566,58 +6013,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>225</v>
+      </c>
+      <c r="D7" t="s">
+        <v>226</v>
+      </c>
+      <c r="E7" t="s">
+        <v>209</v>
+      </c>
+      <c r="F7" t="s">
+        <v>219</v>
+      </c>
+      <c r="G7" t="s">
+        <v>180</v>
+      </c>
+      <c r="H7" t="s">
+        <v>227</v>
+      </c>
+      <c r="I7" t="s">
+        <v>212</v>
+      </c>
+      <c r="J7" t="s">
+        <v>213</v>
+      </c>
+      <c r="K7" t="s">
+        <v>214</v>
+      </c>
+      <c r="L7" t="s">
+        <v>215</v>
+      </c>
+      <c r="M7" t="s">
+        <v>209</v>
+      </c>
+      <c r="N7" t="s">
         <v>216</v>
       </c>
-      <c r="D7" t="s">
+      <c r="O7" t="s">
         <v>217</v>
       </c>
-      <c r="E7" t="s">
-        <v>200</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="P7" t="s">
         <v>210</v>
       </c>
-      <c r="G7" t="s">
-        <v>171</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="Q7" t="s">
         <v>218</v>
       </c>
-      <c r="I7" t="s">
-        <v>203</v>
-      </c>
-      <c r="J7" t="s">
-        <v>204</v>
-      </c>
-      <c r="K7" t="s">
-        <v>205</v>
-      </c>
-      <c r="L7" t="s">
-        <v>206</v>
-      </c>
-      <c r="M7" t="s">
-        <v>200</v>
-      </c>
-      <c r="N7" t="s">
-        <v>207</v>
-      </c>
-      <c r="O7" t="s">
-        <v>208</v>
-      </c>
-      <c r="P7" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>209</v>
-      </c>
       <c r="R7" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S7" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T7" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -3625,58 +6072,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
+        <v>228</v>
+      </c>
+      <c r="D8" t="s">
+        <v>229</v>
+      </c>
+      <c r="E8" t="s">
+        <v>216</v>
+      </c>
+      <c r="F8" t="s">
+        <v>217</v>
+      </c>
+      <c r="G8" t="s">
+        <v>180</v>
+      </c>
+      <c r="H8" t="s">
+        <v>230</v>
+      </c>
+      <c r="I8" t="s">
+        <v>212</v>
+      </c>
+      <c r="J8" t="s">
+        <v>213</v>
+      </c>
+      <c r="K8" t="s">
+        <v>214</v>
+      </c>
+      <c r="L8" t="s">
+        <v>215</v>
+      </c>
+      <c r="M8" t="s">
+        <v>209</v>
+      </c>
+      <c r="N8" t="s">
+        <v>216</v>
+      </c>
+      <c r="O8" t="s">
+        <v>217</v>
+      </c>
+      <c r="P8" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>218</v>
+      </c>
+      <c r="R8" t="s">
         <v>219</v>
       </c>
-      <c r="D8" t="s">
+      <c r="S8" t="s">
         <v>220</v>
       </c>
-      <c r="E8" t="s">
-        <v>207</v>
-      </c>
-      <c r="F8" t="s">
-        <v>208</v>
-      </c>
-      <c r="G8" t="s">
-        <v>171</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="T8" t="s">
         <v>221</v>
-      </c>
-      <c r="I8" t="s">
-        <v>203</v>
-      </c>
-      <c r="J8" t="s">
-        <v>204</v>
-      </c>
-      <c r="K8" t="s">
-        <v>205</v>
-      </c>
-      <c r="L8" t="s">
-        <v>206</v>
-      </c>
-      <c r="M8" t="s">
-        <v>200</v>
-      </c>
-      <c r="N8" t="s">
-        <v>207</v>
-      </c>
-      <c r="O8" t="s">
-        <v>208</v>
-      </c>
-      <c r="P8" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>209</v>
-      </c>
-      <c r="R8" t="s">
-        <v>210</v>
-      </c>
-      <c r="S8" t="s">
-        <v>211</v>
-      </c>
-      <c r="T8" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -3684,58 +6131,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="D9" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="E9" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F9" t="s">
+        <v>219</v>
+      </c>
+      <c r="G9" t="s">
+        <v>180</v>
+      </c>
+      <c r="H9" t="s">
+        <v>211</v>
+      </c>
+      <c r="I9" t="s">
+        <v>233</v>
+      </c>
+      <c r="J9" t="s">
+        <v>213</v>
+      </c>
+      <c r="K9" t="s">
+        <v>214</v>
+      </c>
+      <c r="L9" t="s">
+        <v>215</v>
+      </c>
+      <c r="M9" t="s">
+        <v>209</v>
+      </c>
+      <c r="N9" t="s">
+        <v>216</v>
+      </c>
+      <c r="O9" t="s">
+        <v>217</v>
+      </c>
+      <c r="P9" t="s">
         <v>210</v>
       </c>
-      <c r="G9" t="s">
-        <v>171</v>
-      </c>
-      <c r="H9" t="s">
-        <v>202</v>
-      </c>
-      <c r="I9" t="s">
-        <v>224</v>
-      </c>
-      <c r="J9" t="s">
-        <v>204</v>
-      </c>
-      <c r="K9" t="s">
-        <v>205</v>
-      </c>
-      <c r="L9" t="s">
-        <v>206</v>
-      </c>
-      <c r="M9" t="s">
-        <v>200</v>
-      </c>
-      <c r="N9" t="s">
-        <v>207</v>
-      </c>
-      <c r="O9" t="s">
-        <v>208</v>
-      </c>
-      <c r="P9" t="s">
-        <v>201</v>
-      </c>
       <c r="Q9" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R9" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S9" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T9" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -3743,58 +6190,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>225</v>
+        <v>234</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>235</v>
       </c>
       <c r="E10" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="F10" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G10" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H10" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="I10" t="s">
-        <v>227</v>
+        <v>236</v>
       </c>
       <c r="J10" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="K10" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="L10" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="M10" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N10" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O10" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P10" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="Q10" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R10" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S10" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T10" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -3802,58 +6249,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>228</v>
+        <v>237</v>
       </c>
       <c r="D11" t="s">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="E11" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="G11" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H11" t="s">
+        <v>224</v>
+      </c>
+      <c r="I11" t="s">
+        <v>233</v>
+      </c>
+      <c r="J11" t="s">
+        <v>213</v>
+      </c>
+      <c r="K11" t="s">
+        <v>214</v>
+      </c>
+      <c r="L11" t="s">
         <v>215</v>
       </c>
-      <c r="I11" t="s">
-        <v>224</v>
-      </c>
-      <c r="J11" t="s">
-        <v>204</v>
-      </c>
-      <c r="K11" t="s">
-        <v>205</v>
-      </c>
-      <c r="L11" t="s">
-        <v>206</v>
-      </c>
       <c r="M11" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N11" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O11" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P11" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="Q11" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R11" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S11" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -3861,58 +6308,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>230</v>
+        <v>239</v>
       </c>
       <c r="D12" t="s">
-        <v>231</v>
+        <v>240</v>
       </c>
       <c r="E12" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F12" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G12" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H12" t="s">
+        <v>224</v>
+      </c>
+      <c r="I12" t="s">
+        <v>236</v>
+      </c>
+      <c r="J12" t="s">
+        <v>213</v>
+      </c>
+      <c r="K12" t="s">
+        <v>214</v>
+      </c>
+      <c r="L12" t="s">
         <v>215</v>
       </c>
-      <c r="I12" t="s">
-        <v>227</v>
-      </c>
-      <c r="J12" t="s">
-        <v>204</v>
-      </c>
-      <c r="K12" t="s">
-        <v>205</v>
-      </c>
-      <c r="L12" t="s">
-        <v>206</v>
-      </c>
       <c r="M12" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="N12" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="O12" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="P12" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="Q12" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
       <c r="R12" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S12" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T12" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -3920,58 +6367,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>232</v>
+        <v>241</v>
       </c>
       <c r="D13" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" t="s">
+        <v>209</v>
+      </c>
+      <c r="F13" t="s">
+        <v>221</v>
+      </c>
+      <c r="G13" t="s">
+        <v>180</v>
+      </c>
+      <c r="H13" t="s">
+        <v>227</v>
+      </c>
+      <c r="I13" t="s">
         <v>233</v>
       </c>
-      <c r="E13" t="s">
-        <v>200</v>
-      </c>
-      <c r="F13" t="s">
-        <v>212</v>
-      </c>
-      <c r="G13" t="s">
-        <v>171</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
+        <v>213</v>
+      </c>
+      <c r="K13" t="s">
+        <v>214</v>
+      </c>
+      <c r="L13" t="s">
+        <v>215</v>
+      </c>
+      <c r="M13" t="s">
+        <v>209</v>
+      </c>
+      <c r="N13" t="s">
+        <v>216</v>
+      </c>
+      <c r="O13" t="s">
+        <v>217</v>
+      </c>
+      <c r="P13" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q13" t="s">
         <v>218</v>
       </c>
-      <c r="I13" t="s">
-        <v>224</v>
-      </c>
-      <c r="J13" t="s">
-        <v>204</v>
-      </c>
-      <c r="K13" t="s">
-        <v>205</v>
-      </c>
-      <c r="L13" t="s">
-        <v>206</v>
-      </c>
-      <c r="M13" t="s">
-        <v>200</v>
-      </c>
-      <c r="N13" t="s">
-        <v>207</v>
-      </c>
-      <c r="O13" t="s">
-        <v>208</v>
-      </c>
-      <c r="P13" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>209</v>
-      </c>
       <c r="R13" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S13" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T13" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -3979,58 +6426,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D14" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E14" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F14" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G14" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H14" t="s">
+        <v>227</v>
+      </c>
+      <c r="I14" t="s">
+        <v>236</v>
+      </c>
+      <c r="J14" t="s">
+        <v>213</v>
+      </c>
+      <c r="K14" t="s">
+        <v>214</v>
+      </c>
+      <c r="L14" t="s">
+        <v>215</v>
+      </c>
+      <c r="M14" t="s">
+        <v>209</v>
+      </c>
+      <c r="N14" t="s">
+        <v>216</v>
+      </c>
+      <c r="O14" t="s">
+        <v>217</v>
+      </c>
+      <c r="P14" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q14" t="s">
         <v>218</v>
       </c>
-      <c r="I14" t="s">
-        <v>227</v>
-      </c>
-      <c r="J14" t="s">
-        <v>204</v>
-      </c>
-      <c r="K14" t="s">
-        <v>205</v>
-      </c>
-      <c r="L14" t="s">
-        <v>206</v>
-      </c>
-      <c r="M14" t="s">
-        <v>200</v>
-      </c>
-      <c r="N14" t="s">
-        <v>207</v>
-      </c>
-      <c r="O14" t="s">
-        <v>208</v>
-      </c>
-      <c r="P14" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>209</v>
-      </c>
       <c r="R14" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="S14" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="T14" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -4038,58 +6485,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>236</v>
+        <v>245</v>
       </c>
       <c r="D15" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="E15" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F15" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="G15" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H15" t="s">
+        <v>230</v>
+      </c>
+      <c r="I15" t="s">
+        <v>233</v>
+      </c>
+      <c r="J15" t="s">
+        <v>213</v>
+      </c>
+      <c r="K15" t="s">
+        <v>214</v>
+      </c>
+      <c r="L15" t="s">
+        <v>215</v>
+      </c>
+      <c r="M15" t="s">
+        <v>209</v>
+      </c>
+      <c r="N15" t="s">
+        <v>216</v>
+      </c>
+      <c r="O15" t="s">
+        <v>217</v>
+      </c>
+      <c r="P15" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>218</v>
+      </c>
+      <c r="R15" t="s">
+        <v>219</v>
+      </c>
+      <c r="S15" t="s">
+        <v>220</v>
+      </c>
+      <c r="T15" t="s">
         <v>221</v>
-      </c>
-      <c r="I15" t="s">
-        <v>224</v>
-      </c>
-      <c r="J15" t="s">
-        <v>204</v>
-      </c>
-      <c r="K15" t="s">
-        <v>205</v>
-      </c>
-      <c r="L15" t="s">
-        <v>206</v>
-      </c>
-      <c r="M15" t="s">
-        <v>200</v>
-      </c>
-      <c r="N15" t="s">
-        <v>207</v>
-      </c>
-      <c r="O15" t="s">
-        <v>208</v>
-      </c>
-      <c r="P15" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>209</v>
-      </c>
-      <c r="R15" t="s">
-        <v>210</v>
-      </c>
-      <c r="S15" t="s">
-        <v>211</v>
-      </c>
-      <c r="T15" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -4097,58 +6544,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="D16" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="E16" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="F16" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="G16" t="s">
-        <v>171</v>
+        <v>180</v>
       </c>
       <c r="H16" t="s">
+        <v>230</v>
+      </c>
+      <c r="I16" t="s">
+        <v>236</v>
+      </c>
+      <c r="J16" t="s">
+        <v>213</v>
+      </c>
+      <c r="K16" t="s">
+        <v>214</v>
+      </c>
+      <c r="L16" t="s">
+        <v>215</v>
+      </c>
+      <c r="M16" t="s">
+        <v>209</v>
+      </c>
+      <c r="N16" t="s">
+        <v>216</v>
+      </c>
+      <c r="O16" t="s">
+        <v>217</v>
+      </c>
+      <c r="P16" t="s">
+        <v>210</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>218</v>
+      </c>
+      <c r="R16" t="s">
+        <v>219</v>
+      </c>
+      <c r="S16" t="s">
+        <v>220</v>
+      </c>
+      <c r="T16" t="s">
         <v>221</v>
-      </c>
-      <c r="I16" t="s">
-        <v>227</v>
-      </c>
-      <c r="J16" t="s">
-        <v>204</v>
-      </c>
-      <c r="K16" t="s">
-        <v>205</v>
-      </c>
-      <c r="L16" t="s">
-        <v>206</v>
-      </c>
-      <c r="M16" t="s">
-        <v>200</v>
-      </c>
-      <c r="N16" t="s">
-        <v>207</v>
-      </c>
-      <c r="O16" t="s">
-        <v>208</v>
-      </c>
-      <c r="P16" t="s">
-        <v>201</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>209</v>
-      </c>
-      <c r="R16" t="s">
-        <v>210</v>
-      </c>
-      <c r="S16" t="s">
-        <v>211</v>
-      </c>
-      <c r="T16" t="s">
-        <v>212</v>
       </c>
     </row>
   </sheetData>
@@ -4177,16 +6624,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D1" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E1" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="F1" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -4200,7 +6647,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -4225,16 +6672,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="D4" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="E4" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="F4" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -4248,10 +6695,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="F5" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -4259,16 +6706,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="D6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="F6" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -4282,10 +6729,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F7" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4299,10 +6746,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="F8" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -4316,10 +6763,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="F9" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -4327,16 +6774,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
       <c r="D10" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="E10" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
       <c r="F10" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4350,10 +6797,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F11" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -4367,10 +6814,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F12" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
   </sheetData>
@@ -4403,34 +6850,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="E1" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
       <c r="G1" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="H1" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
       <c r="I1" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="J1" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="K1" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="L1" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="M1" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="N1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -4441,10 +6888,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="E2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -4456,7 +6903,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -4478,13 +6925,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -4495,40 +6942,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="D4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="E4" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="F4" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="G4" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="H4" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="I4" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="J4" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="K4" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="L4" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="M4" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="N4" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -4551,13 +6998,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L5" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M5" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -4571,22 +7018,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H6" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L6" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M6" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -4600,22 +7047,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H7" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L7" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M7" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -4629,22 +7076,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L8" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M8" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -4658,22 +7105,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H9" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L9" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M9" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -4687,22 +7134,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H10" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L10" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M10" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -4716,22 +7163,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H11" t="s">
-        <v>174</v>
+        <v>183</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L11" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="M11" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -4745,22 +7192,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>173</v>
+        <v>182</v>
       </c>
       <c r="H12" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="L12" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="M12" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -4768,31 +7215,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="G13" t="s">
-        <v>172</v>
+        <v>181</v>
       </c>
       <c r="H13" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="L13" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="M13" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="N13" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -4800,10 +7247,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="4" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="E14" s="4" t="s">
         <v>7</v>
@@ -4812,7 +7259,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -4820,10 +7267,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="4" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="E15" s="4" t="s">
         <v>7</v>
@@ -4832,7 +7279,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -4840,10 +7287,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="4" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="E16" s="4" t="s">
         <v>16</v>
@@ -4852,7 +7299,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -4860,19 +7307,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="4" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F17" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N17" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -4880,10 +7327,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="4" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="E18" s="4" t="s">
         <v>59</v>
@@ -4892,7 +7339,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -4900,10 +7347,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="D19" s="4" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="E19" s="4" t="s">
         <v>66</v>
@@ -4912,7 +7359,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -4920,10 +7367,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="4" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="E20" s="4" t="s">
         <v>16</v>
@@ -4932,7 +7379,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -4940,19 +7387,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="E21" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="F21" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
       <c r="N21" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -4960,16 +7407,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E22" s="4" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="F22" s="4" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -4977,10 +7424,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="4" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
       <c r="D23" s="4" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="E23" s="4" t="s">
         <v>25</v>
@@ -4994,10 +7441,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="4" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="D24" s="4" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
       <c r="E24" s="4" t="s">
         <v>25</v>
@@ -5011,10 +7458,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="4" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="E25" s="4" t="s">
         <v>34</v>
@@ -5028,10 +7475,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="4" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="E26" s="4" t="s">
         <v>34</v>
@@ -5045,10 +7492,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
       <c r="E27" s="4" t="s">
         <v>43</v>
@@ -5062,10 +7509,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="4" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E28" s="4" t="s">
         <v>43</v>
@@ -5079,10 +7526,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="4" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E29" s="4" t="s">
         <v>43</v>
@@ -5091,10 +7538,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="N29" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -5102,10 +7549,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="E30" s="4" t="s">
         <v>52</v>
@@ -5119,10 +7566,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="E31" s="4" t="s">
         <v>52</v>
@@ -5136,10 +7583,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D32" s="4" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="E32" s="4" t="s">
         <v>52</v>
@@ -5148,10 +7595,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="N32" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
     </row>
   </sheetData>
@@ -5187,31 +7634,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D1" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E1" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="F1" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="G1" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="H1" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="I1" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="J1" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="K1" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -5237,10 +7684,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="I2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -5254,34 +7701,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>360</v>
+        <v>369</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>361</v>
+        <v>370</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>362</v>
+        <v>371</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>363</v>
+        <v>372</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -5292,31 +7739,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>364</v>
+        <v>373</v>
       </c>
       <c r="D4" t="s">
-        <v>365</v>
+        <v>374</v>
       </c>
       <c r="E4" t="s">
-        <v>366</v>
+        <v>375</v>
       </c>
       <c r="F4" t="s">
-        <v>367</v>
+        <v>376</v>
       </c>
       <c r="G4" t="s">
-        <v>368</v>
+        <v>377</v>
       </c>
       <c r="H4" t="s">
-        <v>369</v>
+        <v>378</v>
       </c>
       <c r="I4" t="s">
-        <v>370</v>
+        <v>379</v>
       </c>
       <c r="J4" t="s">
-        <v>371</v>
+        <v>380</v>
       </c>
       <c r="K4" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -5324,7 +7771,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>372</v>
+        <v>381</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5336,7 +7783,7 @@
         <v>10</v>
       </c>
       <c r="G5">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="H5" t="s">
         <v>25</v>
@@ -5348,7 +7795,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>373</v>
+        <v>382</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -5356,7 +7803,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>374</v>
+        <v>383</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -5365,7 +7812,7 @@
         <v>80</v>
       </c>
       <c r="F6">
-        <v>1</v>
+        <v>0.3</v>
       </c>
       <c r="G6">
         <v>3</v>
@@ -5380,7 +7827,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -5388,13 +7835,13 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>376</v>
+        <v>385</v>
       </c>
       <c r="D7">
         <v>81</v>
       </c>
       <c r="E7">
-        <v>180</v>
+        <v>300</v>
       </c>
       <c r="F7">
         <v>5</v>
@@ -5412,7 +7859,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -5420,16 +7867,16 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>377</v>
+        <v>386</v>
       </c>
       <c r="D8">
-        <v>181</v>
+        <v>301</v>
       </c>
       <c r="E8">
         <v>0</v>
       </c>
       <c r="F8">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G8">
         <v>3</v>
@@ -5444,7 +7891,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>375</v>
+        <v>384</v>
       </c>
     </row>
   </sheetData>
@@ -5475,16 +7922,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D1" t="s">
-        <v>378</v>
+        <v>387</v>
       </c>
       <c r="E1" t="s">
-        <v>379</v>
+        <v>388</v>
       </c>
       <c r="F1" t="s">
-        <v>380</v>
+        <v>389</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -5501,7 +7948,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -5514,10 +7961,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>381</v>
+        <v>390</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>382</v>
+        <v>391</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -5528,13 +7975,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>383</v>
+        <v>392</v>
       </c>
       <c r="D4" t="s">
-        <v>384</v>
+        <v>393</v>
       </c>
       <c r="E4" t="s">
-        <v>385</v>
+        <v>394</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -5542,7 +7989,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>386</v>
+        <v>395</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -5551,7 +7998,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>387</v>
+        <v>396</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -5559,7 +8006,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>388</v>
+        <v>397</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -5568,7 +8015,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="4" t="s">
-        <v>389</v>
+        <v>398</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -5576,7 +8023,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>390</v>
+        <v>399</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -5585,7 +8032,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="4" t="s">
-        <v>391</v>
+        <v>400</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -5593,7 +8040,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>401</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -5602,11 +8049,810 @@
         <v>1</v>
       </c>
       <c r="F8" s="4" t="s">
-        <v>393</v>
+        <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:6">
       <c r="F9" s="4"/>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:H30"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="13.4166666666667" customWidth="1"/>
+    <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
+    <col min="4" max="4" width="19.0833333333333" customWidth="1"/>
+    <col min="5" max="5" width="29.4166666666667" customWidth="1"/>
+    <col min="6" max="6" width="22.25" customWidth="1"/>
+    <col min="7" max="7" width="25" customWidth="1"/>
+    <col min="8" max="8" width="42.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:8">
+      <c r="A1" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>403</v>
+      </c>
+      <c r="C1" t="s">
+        <v>404</v>
+      </c>
+      <c r="D1" t="s">
+        <v>405</v>
+      </c>
+      <c r="E1" t="s">
+        <v>406</v>
+      </c>
+      <c r="F1" t="s">
+        <v>407</v>
+      </c>
+      <c r="G1" t="s">
+        <v>408</v>
+      </c>
+      <c r="H1" t="s">
+        <v>286</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="A2" s="2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E2" t="s">
+        <v>109</v>
+      </c>
+      <c r="F2" t="s">
+        <v>410</v>
+      </c>
+      <c r="G2" t="s">
+        <v>288</v>
+      </c>
+      <c r="H2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="81" customHeight="1" spans="1:8">
+      <c r="A3" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="3" t="s">
+        <v>411</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>413</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>417</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>418</v>
+      </c>
+      <c r="C4" t="s">
+        <v>419</v>
+      </c>
+      <c r="D4" t="s">
+        <v>420</v>
+      </c>
+      <c r="E4" t="s">
+        <v>421</v>
+      </c>
+      <c r="F4" t="s">
+        <v>422</v>
+      </c>
+      <c r="G4" t="s">
+        <v>423</v>
+      </c>
+      <c r="H4" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="A5" t="s">
+        <v>384</v>
+      </c>
+      <c r="B5">
+        <v>1000</v>
+      </c>
+      <c r="C5" t="s">
+        <v>424</v>
+      </c>
+      <c r="D5" t="s">
+        <v>425</v>
+      </c>
+      <c r="E5" t="s">
+        <v>0</v>
+      </c>
+      <c r="F5">
+        <v>1</v>
+      </c>
+      <c r="G5" t="b">
+        <v>0</v>
+      </c>
+      <c r="H5" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="A6" t="s">
+        <v>384</v>
+      </c>
+      <c r="B6">
+        <v>1001</v>
+      </c>
+      <c r="C6" t="s">
+        <v>427</v>
+      </c>
+      <c r="D6" t="s">
+        <v>425</v>
+      </c>
+      <c r="E6" t="s">
+        <v>9</v>
+      </c>
+      <c r="F6">
+        <v>1</v>
+      </c>
+      <c r="G6" t="b">
+        <v>0</v>
+      </c>
+      <c r="H6" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8">
+      <c r="A7" t="s">
+        <v>384</v>
+      </c>
+      <c r="B7">
+        <v>1002</v>
+      </c>
+      <c r="C7" t="s">
+        <v>429</v>
+      </c>
+      <c r="D7" t="s">
+        <v>425</v>
+      </c>
+      <c r="E7" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7">
+        <v>1</v>
+      </c>
+      <c r="G7" t="b">
+        <v>0</v>
+      </c>
+      <c r="H7" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" t="s">
+        <v>384</v>
+      </c>
+      <c r="B8">
+        <v>1003</v>
+      </c>
+      <c r="C8" t="s">
+        <v>431</v>
+      </c>
+      <c r="D8" t="s">
+        <v>425</v>
+      </c>
+      <c r="E8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" t="s">
+        <v>432</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="A9" t="s">
+        <v>384</v>
+      </c>
+      <c r="B9">
+        <v>1004</v>
+      </c>
+      <c r="C9" t="s">
+        <v>433</v>
+      </c>
+      <c r="D9" t="s">
+        <v>425</v>
+      </c>
+      <c r="E9" t="s">
+        <v>36</v>
+      </c>
+      <c r="F9">
+        <v>1</v>
+      </c>
+      <c r="G9" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" t="s">
+        <v>434</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="A10" t="s">
+        <v>384</v>
+      </c>
+      <c r="B10">
+        <v>1005</v>
+      </c>
+      <c r="C10" t="s">
+        <v>435</v>
+      </c>
+      <c r="D10" t="s">
+        <v>425</v>
+      </c>
+      <c r="E10" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10">
+        <v>1</v>
+      </c>
+      <c r="G10" t="b">
+        <v>0</v>
+      </c>
+      <c r="H10" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="A11" t="s">
+        <v>384</v>
+      </c>
+      <c r="B11">
+        <v>1006</v>
+      </c>
+      <c r="C11" t="s">
+        <v>437</v>
+      </c>
+      <c r="D11" t="s">
+        <v>425</v>
+      </c>
+      <c r="E11" t="s">
+        <v>54</v>
+      </c>
+      <c r="F11">
+        <v>1</v>
+      </c>
+      <c r="G11" t="b">
+        <v>0</v>
+      </c>
+      <c r="H11" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8">
+      <c r="A12" t="s">
+        <v>384</v>
+      </c>
+      <c r="B12">
+        <v>1007</v>
+      </c>
+      <c r="C12" t="s">
+        <v>439</v>
+      </c>
+      <c r="D12" t="s">
+        <v>425</v>
+      </c>
+      <c r="E12" t="s">
+        <v>61</v>
+      </c>
+      <c r="F12">
+        <v>1</v>
+      </c>
+      <c r="G12" t="b">
+        <v>0</v>
+      </c>
+      <c r="H12" t="s">
+        <v>440</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" t="s">
+        <v>384</v>
+      </c>
+      <c r="B13">
+        <v>1008</v>
+      </c>
+      <c r="C13" t="s">
+        <v>441</v>
+      </c>
+      <c r="D13" t="s">
+        <v>425</v>
+      </c>
+      <c r="E13" t="s">
+        <v>68</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="A14" t="s">
+        <v>384</v>
+      </c>
+      <c r="B14">
+        <v>1009</v>
+      </c>
+      <c r="C14" t="s">
+        <v>443</v>
+      </c>
+      <c r="D14" t="s">
+        <v>425</v>
+      </c>
+      <c r="E14" t="s">
+        <v>73</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="s">
+        <v>444</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8">
+      <c r="A15" t="s">
+        <v>384</v>
+      </c>
+      <c r="B15">
+        <v>1010</v>
+      </c>
+      <c r="C15" t="s">
+        <v>445</v>
+      </c>
+      <c r="D15" t="s">
+        <v>425</v>
+      </c>
+      <c r="E15" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>1</v>
+      </c>
+      <c r="H15" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="A16" t="s">
+        <v>384</v>
+      </c>
+      <c r="B16">
+        <v>1101</v>
+      </c>
+      <c r="C16" t="s">
+        <v>447</v>
+      </c>
+      <c r="D16" t="s">
+        <v>448</v>
+      </c>
+      <c r="E16" t="s">
+        <v>449</v>
+      </c>
+      <c r="F16">
+        <v>1</v>
+      </c>
+      <c r="G16" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" t="s">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8">
+      <c r="A17" t="s">
+        <v>384</v>
+      </c>
+      <c r="B17">
+        <v>1102</v>
+      </c>
+      <c r="C17" t="s">
+        <v>451</v>
+      </c>
+      <c r="D17" t="s">
+        <v>448</v>
+      </c>
+      <c r="E17" t="s">
+        <v>452</v>
+      </c>
+      <c r="F17">
+        <v>1</v>
+      </c>
+      <c r="G17" t="b">
+        <v>0</v>
+      </c>
+      <c r="H17" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8">
+      <c r="A18" t="s">
+        <v>384</v>
+      </c>
+      <c r="B18">
+        <v>1103</v>
+      </c>
+      <c r="C18" t="s">
+        <v>454</v>
+      </c>
+      <c r="D18" t="s">
+        <v>448</v>
+      </c>
+      <c r="E18" t="s">
+        <v>455</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+      <c r="G18" t="b">
+        <v>0</v>
+      </c>
+      <c r="H18" t="s">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8">
+      <c r="A19" t="s">
+        <v>384</v>
+      </c>
+      <c r="B19">
+        <v>1104</v>
+      </c>
+      <c r="C19" t="s">
+        <v>457</v>
+      </c>
+      <c r="D19" t="s">
+        <v>448</v>
+      </c>
+      <c r="E19" t="s">
+        <v>458</v>
+      </c>
+      <c r="F19">
+        <v>1</v>
+      </c>
+      <c r="G19" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" t="s">
+        <v>459</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8">
+      <c r="A20" t="s">
+        <v>384</v>
+      </c>
+      <c r="B20">
+        <v>1105</v>
+      </c>
+      <c r="C20" t="s">
+        <v>460</v>
+      </c>
+      <c r="D20" t="s">
+        <v>448</v>
+      </c>
+      <c r="E20" t="s">
+        <v>461</v>
+      </c>
+      <c r="F20">
+        <v>1</v>
+      </c>
+      <c r="G20" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" t="s">
+        <v>462</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8">
+      <c r="A21" t="s">
+        <v>384</v>
+      </c>
+      <c r="B21">
+        <v>1106</v>
+      </c>
+      <c r="C21" t="s">
+        <v>463</v>
+      </c>
+      <c r="D21" t="s">
+        <v>448</v>
+      </c>
+      <c r="E21" t="s">
+        <v>464</v>
+      </c>
+      <c r="F21">
+        <v>1</v>
+      </c>
+      <c r="G21" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8">
+      <c r="A22" t="s">
+        <v>384</v>
+      </c>
+      <c r="B22">
+        <v>1107</v>
+      </c>
+      <c r="C22" t="s">
+        <v>466</v>
+      </c>
+      <c r="D22" t="s">
+        <v>448</v>
+      </c>
+      <c r="E22" t="s">
+        <v>467</v>
+      </c>
+      <c r="F22">
+        <v>1</v>
+      </c>
+      <c r="G22" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" t="s">
+        <v>468</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8">
+      <c r="A23" t="s">
+        <v>384</v>
+      </c>
+      <c r="B23">
+        <v>1201</v>
+      </c>
+      <c r="C23" t="s">
+        <v>469</v>
+      </c>
+      <c r="D23" t="s">
+        <v>470</v>
+      </c>
+      <c r="E23" t="s">
+        <v>471</v>
+      </c>
+      <c r="F23">
+        <v>1</v>
+      </c>
+      <c r="G23" t="b">
+        <v>0</v>
+      </c>
+      <c r="H23" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8">
+      <c r="A24" t="s">
+        <v>384</v>
+      </c>
+      <c r="B24">
+        <v>1202</v>
+      </c>
+      <c r="C24" t="s">
+        <v>473</v>
+      </c>
+      <c r="D24" t="s">
+        <v>470</v>
+      </c>
+      <c r="E24" t="s">
+        <v>474</v>
+      </c>
+      <c r="F24">
+        <v>1</v>
+      </c>
+      <c r="G24" t="b">
+        <v>1</v>
+      </c>
+      <c r="H24" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8">
+      <c r="A25" t="s">
+        <v>384</v>
+      </c>
+      <c r="B25">
+        <v>1203</v>
+      </c>
+      <c r="C25" t="s">
+        <v>476</v>
+      </c>
+      <c r="D25" t="s">
+        <v>470</v>
+      </c>
+      <c r="E25" t="s">
+        <v>477</v>
+      </c>
+      <c r="F25">
+        <v>1</v>
+      </c>
+      <c r="G25" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8">
+      <c r="A26" t="s">
+        <v>384</v>
+      </c>
+      <c r="B26">
+        <v>1301</v>
+      </c>
+      <c r="C26" t="s">
+        <v>479</v>
+      </c>
+      <c r="D26" t="s">
+        <v>480</v>
+      </c>
+      <c r="E26" t="s">
+        <v>20</v>
+      </c>
+      <c r="F26">
+        <v>1</v>
+      </c>
+      <c r="G26" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8">
+      <c r="A27" t="s">
+        <v>384</v>
+      </c>
+      <c r="B27">
+        <v>1302</v>
+      </c>
+      <c r="C27" t="s">
+        <v>482</v>
+      </c>
+      <c r="D27" t="s">
+        <v>480</v>
+      </c>
+      <c r="E27" t="s">
+        <v>11</v>
+      </c>
+      <c r="F27">
+        <v>1</v>
+      </c>
+      <c r="G27" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" t="s">
+        <v>483</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8">
+      <c r="A28" t="s">
+        <v>384</v>
+      </c>
+      <c r="B28">
+        <v>1303</v>
+      </c>
+      <c r="C28" t="s">
+        <v>484</v>
+      </c>
+      <c r="D28" t="s">
+        <v>480</v>
+      </c>
+      <c r="E28" t="s">
+        <v>2</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+      <c r="G28" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8">
+      <c r="A29" t="s">
+        <v>384</v>
+      </c>
+      <c r="B29">
+        <v>1304</v>
+      </c>
+      <c r="C29" t="s">
+        <v>486</v>
+      </c>
+      <c r="D29" t="s">
+        <v>480</v>
+      </c>
+      <c r="E29" t="s">
+        <v>269</v>
+      </c>
+      <c r="F29">
+        <v>1</v>
+      </c>
+      <c r="G29" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8">
+      <c r="B30">
+        <v>1011</v>
+      </c>
+      <c r="C30" t="s">
+        <v>488</v>
+      </c>
+      <c r="D30" t="s">
+        <v>425</v>
+      </c>
+      <c r="E30" t="s">
+        <v>489</v>
+      </c>
+      <c r="F30">
+        <v>1</v>
+      </c>
+      <c r="G30" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" t="s">
+        <v>490</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1315" uniqueCount="700">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="859">
   <si>
     <t>Dog</t>
   </si>
@@ -1265,6 +1265,21 @@
     <t>IsHidden</t>
   </si>
   <si>
+    <t>SteamNameEn</t>
+  </si>
+  <si>
+    <t>SteamDescriptionEn</t>
+  </si>
+  <si>
+    <t>SteamNameZhHans</t>
+  </si>
+  <si>
+    <t>SteamDescriptionZhHans</t>
+  </si>
+  <si>
+    <t>SteamTitleBriefZhHans</t>
+  </si>
+  <si>
     <t>EAchievementRuleType</t>
   </si>
   <si>
@@ -1292,6 +1307,21 @@
     <t>填写策划说明或设计约束</t>
   </si>
   <si>
+    <t>Steam 默认英文名称；为空时生成器报错</t>
+  </si>
+  <si>
+    <t>Steam 默认英文描述；为空时生成器报错</t>
+  </si>
+  <si>
+    <t>Steam 简体中文名称；为空时生成器报错</t>
+  </si>
+  <si>
+    <t>Steam 简体中文描述；为空时生成器报错</t>
+  </si>
+  <si>
+    <t>供其他语言本地化理解标题含义、语气和梗；不在 Steam 直接显示。</t>
+  </si>
+  <si>
     <t>成就 id</t>
   </si>
   <si>
@@ -1310,6 +1340,21 @@
     <t>隐藏成就</t>
   </si>
   <si>
+    <t>英文名称</t>
+  </si>
+  <si>
+    <t>英文描述</t>
+  </si>
+  <si>
+    <t>简中名称</t>
+  </si>
+  <si>
+    <t>简中描述</t>
+  </si>
+  <si>
+    <t>标题释义（供翻译）</t>
+  </si>
+  <si>
     <t>ACH_FIRST_DOG</t>
   </si>
   <si>
@@ -1319,22 +1364,82 @@
     <t>首次从非初始来源获得一只狗；默认红柴不计入</t>
   </si>
   <si>
+    <t>A New Friend</t>
+  </si>
+  <si>
+    <t>Obtain a dog from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>初识新友</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得一只狗。</t>
+  </si>
+  <si>
+    <t>首次获得一只默认以外的小狗；强调结识一位新朋友，但颜色并不一定是哪种。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_HEADWEAR</t>
   </si>
   <si>
     <t>首次从非初始来源获得头部装饰</t>
   </si>
   <si>
+    <t>Hats Off!</t>
+  </si>
+  <si>
+    <t>Obtain headwear from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>一帽惊人</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得头部装饰。</t>
+  </si>
+  <si>
+    <t>首次获得头部装饰；强调第一次收集到帽子或头饰的惊喜，正常情况下会自动戴在小狗的之前光秃秃的头上。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_EYEWEAR</t>
   </si>
   <si>
     <t>首次从非初始来源获得眼部装饰</t>
   </si>
   <si>
+    <t>A New Look</t>
+  </si>
+  <si>
+    <t>Obtain eyewear from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>另眼相看</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得眼部装饰。</t>
+  </si>
+  <si>
+    <t>首次获得眼部装饰；强调换上眼镜后的全新造型，正常情况下会自动戴在小狗的脸上。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_ARM</t>
   </si>
   <si>
-    <t>首次从非初始来源获得玩家手臂</t>
+    <t>首次从非初始来源获得玩家手臂，一般是机械手臂、麒麟臂等非人手臂</t>
+  </si>
+  <si>
+    <t>Not Your Average Arm</t>
+  </si>
+  <si>
+    <t>Obtain a player arm from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>非同凡手</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得玩家手臂。</t>
+  </si>
+  <si>
+    <t>首次获得非人类的玩家手臂外观，如机械臂或麒麟臂；强调玩家从普通人形迈向科技或神怪化的自我改造，拥有一只不凡的手。</t>
   </si>
   <si>
     <t>ACH_FIRST_CLOTHES</t>
@@ -1343,42 +1448,147 @@
     <t>首次从非初始来源获得衣服</t>
   </si>
   <si>
+    <t>Dressed to Impress</t>
+  </si>
+  <si>
+    <t>Obtain clothing from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>盛装登场</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得衣服。</t>
+  </si>
+  <si>
+    <t>首次获得衣服；强调玩家也有了新衣服，正常情况下玩家的手臂会自动穿上衣服</t>
+  </si>
+  <si>
     <t>ACH_FIRST_TABLE</t>
   </si>
   <si>
     <t>首次从非初始来源获得桌布</t>
   </si>
   <si>
+    <t>Set the Table</t>
+  </si>
+  <si>
+    <t>Obtain a tablecloth from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>桌上生花</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得桌布。</t>
+  </si>
+  <si>
+    <t>首次获得桌布；强调更换桌子后的手感</t>
+  </si>
+  <si>
     <t>ACH_FIRST_BACKGROUND</t>
   </si>
   <si>
     <t>首次从非初始来源获得背景</t>
   </si>
   <si>
+    <t>Change of Scenery</t>
+  </si>
+  <si>
+    <t>Obtain a background from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>别有天地</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得背景。</t>
+  </si>
+  <si>
+    <t>首次获得背景；强调更换场景、换个新环境。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_ACCESSORY</t>
   </si>
   <si>
     <t>首次从非初始来源获得手部装饰</t>
   </si>
   <si>
+    <t>Handy Accessory</t>
+  </si>
+  <si>
+    <t>Obtain an accessory from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>腕间风采</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得手部装饰。</t>
+  </si>
+  <si>
+    <t>首次获得手部装饰；强调玩家手腕部装饰的饰品，但因为范围比较大且不知道玩家的性别，因此有可能会给男玩家自动装一个女款手镯也说不定。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_REFRESHMENT</t>
   </si>
   <si>
     <t>首次从非初始来源获得饮品/消耗品</t>
   </si>
   <si>
+    <t>Cheers!</t>
+  </si>
+  <si>
+    <t>Obtain a refreshment from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>举杯同庆</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得饮品或消耗品。</t>
+  </si>
+  <si>
+    <t>首次获得饮品或消耗品；用轻松的干杯语气庆祝。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_CARD_BACK</t>
   </si>
   <si>
     <t>首次从非初始来源获得卡背</t>
   </si>
   <si>
+    <t>Hidden Hand</t>
+  </si>
+  <si>
+    <t>Obtain a card back from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>暗藏玄机</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得卡背。</t>
+  </si>
+  <si>
+    <t>首次获得卡背；强调卡牌背面也有可收集的隐藏外观。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_CARD_FACE</t>
   </si>
   <si>
     <t>首次从非初始来源获得卡面</t>
   </si>
   <si>
+    <t>Face Value</t>
+  </si>
+  <si>
+    <t>Obtain card faces from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>牌面十足</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得卡面。</t>
+  </si>
+  <si>
+    <t>首次获得卡面；卡面不会从盲盒中开出，通常是其他途径获得。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_THREE_OF_A_KIND</t>
   </si>
   <si>
@@ -1391,6 +1601,21 @@
     <t>首次达成三条</t>
   </si>
   <si>
+    <t>Three of a Kind!</t>
+  </si>
+  <si>
+    <t>Make a three of a kind for the first time.</t>
+  </si>
+  <si>
+    <t>三条！</t>
+  </si>
+  <si>
+    <t>首次组成三条。</t>
+  </si>
+  <si>
+    <t>首次组成三条；使用标准扑克牌型名称，带首次达成的喜悦。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_STRAIGHT</t>
   </si>
   <si>
@@ -1400,6 +1625,21 @@
     <t>首次达成顺子</t>
   </si>
   <si>
+    <t>Straight!</t>
+  </si>
+  <si>
+    <t>Make a straight for the first time.</t>
+  </si>
+  <si>
+    <t>顺子！</t>
+  </si>
+  <si>
+    <t>首次组成顺子。</t>
+  </si>
+  <si>
+    <t>首次组成顺子；使用标准扑克牌型名称，简短有力。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_FLUSH</t>
   </si>
   <si>
@@ -1409,6 +1649,21 @@
     <t>首次达成同花</t>
   </si>
   <si>
+    <t>Flush!</t>
+  </si>
+  <si>
+    <t>Make a flush for the first time.</t>
+  </si>
+  <si>
+    <t>同花！</t>
+  </si>
+  <si>
+    <t>首次组成同花。</t>
+  </si>
+  <si>
+    <t>首次组成同花；使用标准扑克牌型名称，简短有力。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_FULL_HOUSE</t>
   </si>
   <si>
@@ -1418,6 +1673,21 @@
     <t>首次达成葫芦</t>
   </si>
   <si>
+    <t>Full House!</t>
+  </si>
+  <si>
+    <t>Make a full house for the first time.</t>
+  </si>
+  <si>
+    <t>葫芦！</t>
+  </si>
+  <si>
+    <t>首次组成葫芦。</t>
+  </si>
+  <si>
+    <t>首次组成葫芦；使用标准扑克牌型名称，简短有力。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_FOUR_OF_A_KIND</t>
   </si>
   <si>
@@ -1427,6 +1697,21 @@
     <t>首次达成四条</t>
   </si>
   <si>
+    <t>Four of a Kind!</t>
+  </si>
+  <si>
+    <t>Make a four of a kind for the first time.</t>
+  </si>
+  <si>
+    <t>四条！</t>
+  </si>
+  <si>
+    <t>首次组成四条。</t>
+  </si>
+  <si>
+    <t>首次组成四条；使用标准扑克牌型名称，简短有力。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_STRAIGHT_FLUSH</t>
   </si>
   <si>
@@ -1436,6 +1721,21 @@
     <t>首次达成同花顺</t>
   </si>
   <si>
+    <t>Straight Flush!</t>
+  </si>
+  <si>
+    <t>Make a straight flush for the first time.</t>
+  </si>
+  <si>
+    <t>同花顺！</t>
+  </si>
+  <si>
+    <t>首次组成同花顺。</t>
+  </si>
+  <si>
+    <t>首次组成同花顺；使用标准扑克牌型名称，简短有力。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_ROYAL_FLUSH</t>
   </si>
   <si>
@@ -1445,6 +1745,21 @@
     <t>首次达成皇家同花顺</t>
   </si>
   <si>
+    <t>Royal Flush!</t>
+  </si>
+  <si>
+    <t>Make a royal flush for the first time.</t>
+  </si>
+  <si>
+    <t>皇家同花顺！</t>
+  </si>
+  <si>
+    <t>首次组成皇家同花顺。</t>
+  </si>
+  <si>
+    <t>首次组成皇家同花顺；最高级的扑克牌型，强调难得和荣耀感。</t>
+  </si>
+  <si>
     <t>ACH_DOG_FIRST_HINT</t>
   </si>
   <si>
@@ -1457,6 +1772,21 @@
     <t>首次询问狗狗牌运</t>
   </si>
   <si>
+    <t>Ask the Dog</t>
+  </si>
+  <si>
+    <t>Ask the dog for a poker hint for the first time.</t>
+  </si>
+  <si>
+    <t>问问小狗</t>
+  </si>
+  <si>
+    <t>首次向小狗询问扑克提示。</t>
+  </si>
+  <si>
+    <t>首次向小狗询问扑克提示；像向熟悉扑克的狗狗请教。</t>
+  </si>
+  <si>
     <t>ACH_DOG_FIRST_REFUSAL</t>
   </si>
   <si>
@@ -1466,6 +1796,21 @@
     <t>首次被狗狗拒绝回答</t>
   </si>
   <si>
+    <t>Talk to the Paw</t>
+  </si>
+  <si>
+    <t>Have the dog refuse to give you a poker hint for the first time.</t>
+  </si>
+  <si>
+    <t>汪力不支</t>
+  </si>
+  <si>
+    <t>首次被小狗拒绝提供扑克提示。</t>
+  </si>
+  <si>
+    <t>小狗首次拒绝提供扑克提示；强调小狗可能有些累了或者灵力耗尽。（就像中国神话中，济公他每天只能用3次法术）</t>
+  </si>
+  <si>
     <t>ACH_DOG_FIRST_STARSTRUCK</t>
   </si>
   <si>
@@ -1475,33 +1820,150 @@
     <t>首次打字使狗狗进入崇拜状态；仅状态切换时计一次</t>
   </si>
   <si>
+    <t>Make the dog enter its starstruck state by typing for the first time.</t>
+  </si>
+  <si>
+    <t>肃然起敬</t>
+  </si>
+  <si>
+    <t>首次通过打字让小狗进入崇拜状态。</t>
+  </si>
+  <si>
+    <t>首次通过打字让小狗进入崇拜状态；强调主人努力工作的样子令人崇拜</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_COMMON_ITEM</t>
+  </si>
+  <si>
+    <t>FirstExternalItemRarity</t>
+  </si>
+  <si>
+    <t>首次获得普通物品</t>
+  </si>
+  <si>
+    <t>Unearthed Gift</t>
+  </si>
+  <si>
+    <t>Obtain a common item for the first time.</t>
+  </si>
+  <si>
+    <t>泥土馈赠</t>
+  </si>
+  <si>
+    <t>首次获得普通物品。小狗从泥土里刨出一份礼物。</t>
+  </si>
+  <si>
+    <t>首次获得普通物品；棕色盲盒象征泥土，小狗从土里刨出一份好东西，郑重地献给主人。</t>
+  </si>
+  <si>
+    <t>ACH_FIRST_UNCOMMON_ITEM</t>
+  </si>
+  <si>
+    <t>Uncommon</t>
+  </si>
+  <si>
+    <t>首次获得优秀物品</t>
+  </si>
+  <si>
+    <t>Gift from the Grove</t>
+  </si>
+  <si>
+    <t>Obtain an uncommon item for the first time.</t>
+  </si>
+  <si>
+    <t>林间馈赠</t>
+  </si>
+  <si>
+    <t>首次获得优秀物品。小狗从林间带回一份礼物。</t>
+  </si>
+  <si>
+    <t>首次获得优秀物品；绿色盲盒象征树林，小狗从树上或林间带回一份更好的礼物给主人。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_RARE_ITEM</t>
   </si>
   <si>
-    <t>FirstExternalItemRarity</t>
-  </si>
-  <si>
     <t>首次获得稀有物品</t>
   </si>
   <si>
+    <t>Rare Find</t>
+  </si>
+  <si>
+    <t>Obtain a rare item for the first time.</t>
+  </si>
+  <si>
+    <t>天降好礼</t>
+  </si>
+  <si>
+    <t>首次获得稀有物品。小狗从云间捎来一份礼物。</t>
+  </si>
+  <si>
+    <t>首次获得稀有物品；蓝色盲盒象征天空，像小狗从高处或云间带回一份更难得的礼物。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_EPIC_ITEM</t>
   </si>
   <si>
     <t>首次获得史诗物品</t>
   </si>
   <si>
+    <t>Epic Find</t>
+  </si>
+  <si>
+    <t>Obtain an epic item for the first time.</t>
+  </si>
+  <si>
+    <t>星河赠礼</t>
+  </si>
+  <si>
+    <t>首次获得史诗物品。小狗从星空中寻得一份礼物。</t>
+  </si>
+  <si>
+    <t>首次获得史诗物品；紫色盲盒象征星空，像小狗在繁星间寻得并送回的珍贵礼物。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_LEGENDARY_ITEM</t>
   </si>
   <si>
     <t>首次获得传说物品</t>
   </si>
   <si>
+    <t>Legendary Find</t>
+  </si>
+  <si>
+    <t>Obtain a legendary item for the first time.</t>
+  </si>
+  <si>
+    <t>天赐珍宝</t>
+  </si>
+  <si>
+    <t>首次获得传说物品。小狗从天堂带回一份礼物。</t>
+  </si>
+  <si>
+    <t>首次获得传说物品；金色盲盒象征天堂，像一份从天上降下、由小狗郑重献给主人罕见礼物。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_MYTHIC_ITEM</t>
   </si>
   <si>
     <t>首次获得神话物品</t>
   </si>
   <si>
+    <t>Mythic Find</t>
+  </si>
+  <si>
+    <t>Obtain a mythic item for the first time.</t>
+  </si>
+  <si>
+    <t>神域赐福</t>
+  </si>
+  <si>
+    <t>首次获得神话物品。小狗自神域带回一份礼物。</t>
+  </si>
+  <si>
+    <t>首次获得神话物品；红色盲盒象征神域，像小狗跨入神域后带回、近乎神赐的至高礼物。</t>
+  </si>
+  <si>
     <t>ACH_FIRST_BODY_DECORATION</t>
   </si>
   <si>
@@ -1509,6 +1971,21 @@
   </si>
   <si>
     <t>首次获得玩家体表装饰（体毛、纹身、美甲等）</t>
+  </si>
+  <si>
+    <t>Body Beautiful</t>
+  </si>
+  <si>
+    <t>Obtain body decoration from a non-default source for the first time.</t>
+  </si>
+  <si>
+    <t>锦上添花</t>
+  </si>
+  <si>
+    <t>首次从默认来源以外的途径获得体表装饰。</t>
+  </si>
+  <si>
+    <t>首次获得玩家体表装饰，如体毛、纹身或美甲；强调身体外观的自定义。</t>
   </si>
   <si>
     <t>StatisticId</t>
@@ -2756,7 +3233,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -2768,6 +3245,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -3309,374 +3789,374 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:16">
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="F2" s="4" t="s">
+      <c r="F2" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="G2" s="4"/>
-      <c r="H2" s="4" t="s">
+      <c r="G2" s="5"/>
+      <c r="H2" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="I2" s="4" t="s">
+      <c r="I2" s="5" t="s">
         <v>5</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="5">
         <v>1</v>
       </c>
-      <c r="K2" s="4" t="s">
+      <c r="K2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="O2" s="4" t="s">
+      <c r="O2" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="P2" s="4" t="s">
+      <c r="P2" s="5" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" spans="2:16">
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="5" t="s">
         <v>9</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="5" t="s">
         <v>10</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="F3" s="4" t="s">
+      <c r="F3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="G3" s="4"/>
-      <c r="H3" s="4" t="s">
+      <c r="G3" s="5"/>
+      <c r="H3" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="4" t="s">
+      <c r="I3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="5">
         <v>2</v>
       </c>
-      <c r="K3" s="4" t="s">
+      <c r="K3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="O3" s="4" t="s">
+      <c r="O3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="P3" s="4" t="s">
+      <c r="P3" s="5" t="s">
         <v>17</v>
       </c>
     </row>
     <row r="4" spans="2:16">
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="5" t="s">
         <v>19</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="F4" s="4" t="s">
+      <c r="F4" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="G4" s="4"/>
-      <c r="H4" s="4" t="s">
+      <c r="G4" s="5"/>
+      <c r="H4" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="I4" s="4" t="s">
+      <c r="I4" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="5">
         <v>4</v>
       </c>
-      <c r="K4" s="4" t="s">
+      <c r="K4" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="O4" s="4" t="s">
+      <c r="O4" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="P4" s="4" t="s">
+      <c r="P4" s="5" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="5" spans="2:16">
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="5" t="s">
         <v>27</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="G5" s="4"/>
-      <c r="H5" s="4" t="s">
+      <c r="G5" s="5"/>
+      <c r="H5" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="I5" s="4" t="s">
+      <c r="I5" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="5">
         <v>8</v>
       </c>
-      <c r="K5" s="4" t="s">
+      <c r="K5" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="O5" s="4" t="s">
+      <c r="O5" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="P5" s="4" t="s">
+      <c r="P5" s="5" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="6" spans="2:16">
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>39</v>
       </c>
-      <c r="G6" s="4"/>
-      <c r="H6" s="4" t="s">
+      <c r="G6" s="5"/>
+      <c r="H6" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I6" s="4" t="s">
+      <c r="I6" s="5" t="s">
         <v>41</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="5">
         <v>16</v>
       </c>
-      <c r="K6" s="4" t="s">
+      <c r="K6" s="5" t="s">
         <v>42</v>
       </c>
-      <c r="O6" s="4" t="s">
+      <c r="O6" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="P6" s="4" t="s">
+      <c r="P6" s="5" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="7" spans="2:16">
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="G7" s="4"/>
-      <c r="H7" s="4" t="s">
+      <c r="G7" s="5"/>
+      <c r="H7" s="5" t="s">
         <v>49</v>
       </c>
-      <c r="I7" s="4" t="s">
+      <c r="I7" s="5" t="s">
         <v>50</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="5">
         <v>32</v>
       </c>
-      <c r="K7" s="4" t="s">
+      <c r="K7" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="O7" s="4" t="s">
+      <c r="O7" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="P7" s="4" t="s">
+      <c r="P7" s="5" t="s">
         <v>53</v>
       </c>
     </row>
     <row r="8" spans="2:16">
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="H8" s="4" t="s">
+      <c r="H8" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="I8" s="4" t="s">
+      <c r="I8" s="5" t="s">
         <v>57</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="5">
         <v>64</v>
       </c>
-      <c r="K8" s="4" t="s">
+      <c r="K8" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="O8" s="4" t="s">
+      <c r="O8" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="P8" s="4" t="s">
+      <c r="P8" s="5" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="9" spans="2:16">
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="5" t="s">
         <v>61</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="H9" s="4" t="s">
+      <c r="H9" s="5" t="s">
         <v>63</v>
       </c>
-      <c r="I9" s="4" t="s">
+      <c r="I9" s="5" t="s">
         <v>64</v>
       </c>
-      <c r="J9" s="4">
+      <c r="J9" s="5">
         <v>128</v>
       </c>
-      <c r="K9" s="4" t="s">
+      <c r="K9" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="O9" s="4" t="s">
+      <c r="O9" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="P9" s="4" t="s">
+      <c r="P9" s="5" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="10" spans="2:16">
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="5" t="s">
         <v>68</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="H10" s="4" t="s">
+      <c r="H10" s="5" t="s">
         <v>70</v>
       </c>
-      <c r="I10" s="4" t="s">
+      <c r="I10" s="5" t="s">
         <v>71</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="5">
         <v>256</v>
       </c>
-      <c r="K10" s="4" t="s">
+      <c r="K10" s="5" t="s">
         <v>72</v>
       </c>
     </row>
     <row r="11" spans="2:16">
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="5" t="s">
         <v>73</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="H11" s="4" t="s">
+      <c r="H11" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="4" t="s">
+      <c r="I11" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="5">
         <v>512</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="K11" s="5" t="s">
         <v>77</v>
       </c>
     </row>
     <row r="12" spans="2:16">
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="H12" s="4" t="s">
+      <c r="H12" s="5" t="s">
         <v>80</v>
       </c>
-      <c r="I12" s="4" t="s">
+      <c r="I12" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="5">
         <v>1024</v>
       </c>
-      <c r="K12" s="4" t="s">
+      <c r="K12" s="5" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="13" spans="2:16">
-      <c r="H13" s="4" t="s">
+      <c r="H13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="4" t="s">
+      <c r="I13" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="5">
         <v>2048</v>
       </c>
-      <c r="K13" s="4" t="s">
+      <c r="K13" s="5" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="18" spans="2:3">
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="19" spans="2:3">
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="20" spans="2:3">
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="21" spans="2:3">
-      <c r="B21" s="4" t="s">
+      <c r="B21" s="5" t="s">
         <v>92</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="22" spans="2:3">
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="23" spans="2:3">
-      <c r="B23" s="4" t="s">
+      <c r="B23" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>97</v>
       </c>
     </row>
@@ -3708,25 +4188,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>491</v>
+        <v>650</v>
       </c>
       <c r="C1" t="s">
-        <v>492</v>
+        <v>651</v>
       </c>
       <c r="D1" t="s">
-        <v>493</v>
+        <v>652</v>
       </c>
       <c r="E1" t="s">
-        <v>494</v>
+        <v>653</v>
       </c>
       <c r="F1" t="s">
-        <v>495</v>
+        <v>654</v>
       </c>
       <c r="G1" t="s">
-        <v>496</v>
+        <v>655</v>
       </c>
       <c r="H1" t="s">
-        <v>497</v>
+        <v>656</v>
       </c>
       <c r="I1" t="s">
         <v>286</v>
@@ -3746,10 +4226,10 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>498</v>
+        <v>657</v>
       </c>
       <c r="F2" t="s">
-        <v>499</v>
+        <v>658</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -3766,28 +4246,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>500</v>
+        <v>659</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>501</v>
+        <v>660</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>502</v>
+        <v>661</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>503</v>
+        <v>662</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>504</v>
+        <v>663</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>505</v>
+        <v>664</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>506</v>
+        <v>665</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>507</v>
+        <v>666</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -3795,25 +4275,25 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>508</v>
+        <v>667</v>
       </c>
       <c r="C4" t="s">
-        <v>509</v>
+        <v>668</v>
       </c>
       <c r="D4" t="s">
         <v>254</v>
       </c>
       <c r="E4" t="s">
-        <v>510</v>
+        <v>669</v>
       </c>
       <c r="F4" t="s">
-        <v>511</v>
+        <v>670</v>
       </c>
       <c r="G4" t="s">
-        <v>512</v>
+        <v>671</v>
       </c>
       <c r="H4" t="s">
-        <v>513</v>
+        <v>672</v>
       </c>
       <c r="I4" t="s">
         <v>301</v>
@@ -3827,25 +4307,25 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>514</v>
+        <v>673</v>
       </c>
       <c r="D5" t="s">
-        <v>515</v>
+        <v>674</v>
       </c>
       <c r="E5" t="s">
-        <v>516</v>
+        <v>675</v>
       </c>
       <c r="F5" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G5" t="s">
-        <v>518</v>
+        <v>677</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>519</v>
+        <v>678</v>
       </c>
     </row>
     <row r="6" spans="1:9">
@@ -3856,25 +4336,25 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>520</v>
+        <v>679</v>
       </c>
       <c r="D6" t="s">
-        <v>521</v>
+        <v>680</v>
       </c>
       <c r="E6" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F6" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G6" t="s">
-        <v>523</v>
+        <v>682</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>524</v>
+        <v>683</v>
       </c>
     </row>
     <row r="7" spans="1:9">
@@ -3885,25 +4365,25 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>525</v>
+        <v>684</v>
       </c>
       <c r="D7" t="s">
-        <v>526</v>
+        <v>685</v>
       </c>
       <c r="E7" t="s">
-        <v>516</v>
+        <v>675</v>
       </c>
       <c r="F7" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G7" t="s">
-        <v>527</v>
+        <v>686</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>528</v>
+        <v>687</v>
       </c>
     </row>
     <row r="8" spans="1:9">
@@ -3914,25 +4394,25 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>529</v>
+        <v>688</v>
       </c>
       <c r="D8" t="s">
-        <v>530</v>
+        <v>689</v>
       </c>
       <c r="E8" t="s">
-        <v>516</v>
+        <v>675</v>
       </c>
       <c r="F8" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G8" t="s">
-        <v>531</v>
+        <v>690</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>532</v>
+        <v>691</v>
       </c>
     </row>
     <row r="9" spans="1:9">
@@ -3943,25 +4423,25 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>533</v>
+        <v>692</v>
       </c>
       <c r="D9" t="s">
-        <v>534</v>
+        <v>693</v>
       </c>
       <c r="E9" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F9" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G9" t="s">
-        <v>535</v>
+        <v>694</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>536</v>
+        <v>695</v>
       </c>
     </row>
     <row r="10" spans="1:9">
@@ -3972,25 +4452,25 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>537</v>
+        <v>696</v>
       </c>
       <c r="D10" t="s">
-        <v>538</v>
+        <v>697</v>
       </c>
       <c r="E10" t="s">
-        <v>539</v>
+        <v>698</v>
       </c>
       <c r="F10" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G10" t="s">
-        <v>540</v>
+        <v>699</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>541</v>
+        <v>700</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -4001,25 +4481,25 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>542</v>
+        <v>701</v>
       </c>
       <c r="D11" t="s">
-        <v>543</v>
+        <v>702</v>
       </c>
       <c r="E11" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F11" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G11" t="s">
-        <v>544</v>
+        <v>703</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>545</v>
+        <v>704</v>
       </c>
     </row>
     <row r="12" spans="1:9">
@@ -4030,25 +4510,25 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>546</v>
+        <v>705</v>
       </c>
       <c r="D12" t="s">
-        <v>547</v>
+        <v>706</v>
       </c>
       <c r="E12" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F12" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G12" t="s">
-        <v>548</v>
+        <v>707</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>549</v>
+        <v>708</v>
       </c>
     </row>
     <row r="13" spans="1:9">
@@ -4059,25 +4539,25 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>550</v>
+        <v>709</v>
       </c>
       <c r="D13" t="s">
-        <v>551</v>
+        <v>710</v>
       </c>
       <c r="E13" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F13" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G13" t="s">
-        <v>552</v>
+        <v>711</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>553</v>
+        <v>712</v>
       </c>
     </row>
     <row r="14" spans="1:9">
@@ -4088,25 +4568,25 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>554</v>
+        <v>713</v>
       </c>
       <c r="D14" t="s">
-        <v>555</v>
+        <v>714</v>
       </c>
       <c r="E14" t="s">
-        <v>539</v>
+        <v>698</v>
       </c>
       <c r="F14" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G14" t="s">
-        <v>556</v>
+        <v>715</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>557</v>
+        <v>716</v>
       </c>
     </row>
     <row r="15" spans="1:9">
@@ -4117,25 +4597,25 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>558</v>
+        <v>717</v>
       </c>
       <c r="D15" t="s">
-        <v>559</v>
+        <v>718</v>
       </c>
       <c r="E15" t="s">
-        <v>539</v>
+        <v>698</v>
       </c>
       <c r="F15" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G15" t="s">
-        <v>560</v>
+        <v>719</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>561</v>
+        <v>720</v>
       </c>
     </row>
     <row r="16" spans="1:9">
@@ -4146,25 +4626,25 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>562</v>
+        <v>721</v>
       </c>
       <c r="D16" t="s">
-        <v>563</v>
+        <v>722</v>
       </c>
       <c r="E16" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F16" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G16" t="s">
-        <v>564</v>
+        <v>723</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>565</v>
+        <v>724</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -4175,25 +4655,25 @@
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>566</v>
+        <v>725</v>
       </c>
       <c r="D17" t="s">
-        <v>567</v>
+        <v>726</v>
       </c>
       <c r="E17" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F17" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G17" t="s">
-        <v>568</v>
+        <v>727</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>569</v>
+        <v>728</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -4204,25 +4684,25 @@
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>570</v>
+        <v>729</v>
       </c>
       <c r="D18" t="s">
-        <v>571</v>
+        <v>730</v>
       </c>
       <c r="E18" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F18" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G18" t="s">
-        <v>572</v>
+        <v>731</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>573</v>
+        <v>732</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -4233,25 +4713,25 @@
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="D19" t="s">
-        <v>574</v>
+        <v>733</v>
       </c>
       <c r="E19" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F19" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G19" t="s">
-        <v>575</v>
+        <v>734</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>576</v>
+        <v>735</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -4262,25 +4742,25 @@
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>452</v>
+        <v>527</v>
       </c>
       <c r="D20" t="s">
-        <v>577</v>
+        <v>736</v>
       </c>
       <c r="E20" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F20" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G20" t="s">
-        <v>578</v>
+        <v>737</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>579</v>
+        <v>738</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -4291,25 +4771,25 @@
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="D21" t="s">
-        <v>580</v>
+        <v>739</v>
       </c>
       <c r="E21" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F21" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G21" t="s">
-        <v>581</v>
+        <v>740</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>582</v>
+        <v>741</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -4320,25 +4800,25 @@
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>458</v>
+        <v>543</v>
       </c>
       <c r="D22" t="s">
-        <v>583</v>
+        <v>742</v>
       </c>
       <c r="E22" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F22" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G22" t="s">
-        <v>584</v>
+        <v>743</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>585</v>
+        <v>744</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -4349,25 +4829,25 @@
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>461</v>
+        <v>551</v>
       </c>
       <c r="D23" t="s">
-        <v>586</v>
+        <v>745</v>
       </c>
       <c r="E23" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F23" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G23" t="s">
-        <v>587</v>
+        <v>746</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>588</v>
+        <v>747</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -4378,25 +4858,25 @@
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>464</v>
+        <v>559</v>
       </c>
       <c r="D24" t="s">
-        <v>589</v>
+        <v>748</v>
       </c>
       <c r="E24" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F24" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G24" t="s">
-        <v>590</v>
+        <v>749</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>591</v>
+        <v>750</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -4407,25 +4887,25 @@
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>467</v>
+        <v>567</v>
       </c>
       <c r="D25" t="s">
-        <v>592</v>
+        <v>751</v>
       </c>
       <c r="E25" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F25" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G25" t="s">
-        <v>593</v>
+        <v>752</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>594</v>
+        <v>753</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -4436,25 +4916,25 @@
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>595</v>
+        <v>754</v>
       </c>
       <c r="D26" t="s">
-        <v>596</v>
+        <v>755</v>
       </c>
       <c r="E26" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F26" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G26" t="s">
-        <v>597</v>
+        <v>756</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>598</v>
+        <v>757</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -4465,25 +4945,25 @@
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>599</v>
+        <v>758</v>
       </c>
       <c r="D27" t="s">
-        <v>600</v>
+        <v>759</v>
       </c>
       <c r="E27" t="s">
-        <v>539</v>
+        <v>698</v>
       </c>
       <c r="F27" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G27" t="s">
-        <v>601</v>
+        <v>760</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>602</v>
+        <v>761</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -4494,25 +4974,25 @@
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>603</v>
+        <v>762</v>
       </c>
       <c r="D28" t="s">
-        <v>604</v>
+        <v>763</v>
       </c>
       <c r="E28" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F28" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G28" t="s">
-        <v>605</v>
+        <v>764</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>606</v>
+        <v>765</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -4523,25 +5003,25 @@
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>607</v>
+        <v>766</v>
       </c>
       <c r="D29" t="s">
-        <v>608</v>
+        <v>767</v>
       </c>
       <c r="E29" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F29" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G29" t="s">
-        <v>609</v>
+        <v>768</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>610</v>
+        <v>769</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -4552,25 +5032,25 @@
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>611</v>
+        <v>770</v>
       </c>
       <c r="D30" t="s">
-        <v>612</v>
+        <v>771</v>
       </c>
       <c r="E30" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F30" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G30" t="s">
-        <v>613</v>
+        <v>772</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>614</v>
+        <v>773</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -4581,25 +5061,25 @@
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>615</v>
+        <v>774</v>
       </c>
       <c r="D31" t="s">
-        <v>616</v>
+        <v>775</v>
       </c>
       <c r="E31" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F31" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G31" t="s">
-        <v>617</v>
+        <v>776</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>618</v>
+        <v>777</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4610,25 +5090,25 @@
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>619</v>
+        <v>778</v>
       </c>
       <c r="D32" t="s">
-        <v>620</v>
+        <v>779</v>
       </c>
       <c r="E32" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F32" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G32" t="s">
-        <v>621</v>
+        <v>780</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>622</v>
+        <v>781</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4639,25 +5119,25 @@
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>623</v>
+        <v>782</v>
       </c>
       <c r="D33" t="s">
-        <v>624</v>
+        <v>783</v>
       </c>
       <c r="E33" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F33" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G33" t="s">
-        <v>625</v>
+        <v>784</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>626</v>
+        <v>785</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4668,25 +5148,25 @@
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>627</v>
+        <v>786</v>
       </c>
       <c r="D34" t="s">
-        <v>628</v>
+        <v>787</v>
       </c>
       <c r="E34" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F34" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G34" t="s">
-        <v>629</v>
+        <v>788</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>630</v>
+        <v>789</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4697,25 +5177,25 @@
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>631</v>
+        <v>790</v>
       </c>
       <c r="D35" t="s">
-        <v>632</v>
+        <v>791</v>
       </c>
       <c r="E35" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F35" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G35" t="s">
-        <v>633</v>
+        <v>792</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>634</v>
+        <v>793</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4726,25 +5206,25 @@
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>635</v>
+        <v>794</v>
       </c>
       <c r="D36" t="s">
-        <v>636</v>
+        <v>795</v>
       </c>
       <c r="E36" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F36" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G36" t="s">
-        <v>637</v>
+        <v>796</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>638</v>
+        <v>797</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4755,25 +5235,25 @@
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>639</v>
+        <v>798</v>
       </c>
       <c r="D37" t="s">
-        <v>640</v>
+        <v>799</v>
       </c>
       <c r="E37" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F37" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G37" t="s">
-        <v>641</v>
+        <v>800</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>642</v>
+        <v>801</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4784,25 +5264,25 @@
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>643</v>
+        <v>802</v>
       </c>
       <c r="D38" t="s">
-        <v>644</v>
+        <v>803</v>
       </c>
       <c r="E38" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F38" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G38" t="s">
-        <v>645</v>
+        <v>804</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>646</v>
+        <v>805</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4813,25 +5293,25 @@
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>647</v>
+        <v>806</v>
       </c>
       <c r="D39" t="s">
-        <v>648</v>
+        <v>807</v>
       </c>
       <c r="E39" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F39" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G39" t="s">
-        <v>649</v>
+        <v>808</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>650</v>
+        <v>809</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4842,25 +5322,25 @@
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>651</v>
+        <v>810</v>
       </c>
       <c r="D40" t="s">
-        <v>652</v>
+        <v>811</v>
       </c>
       <c r="E40" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F40" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G40" t="s">
-        <v>653</v>
+        <v>812</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>654</v>
+        <v>813</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4871,25 +5351,25 @@
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>655</v>
+        <v>814</v>
       </c>
       <c r="D41" t="s">
-        <v>656</v>
+        <v>815</v>
       </c>
       <c r="E41" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F41" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G41" t="s">
-        <v>657</v>
+        <v>816</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>658</v>
+        <v>817</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4900,25 +5380,25 @@
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>659</v>
+        <v>818</v>
       </c>
       <c r="D42" t="s">
-        <v>660</v>
+        <v>819</v>
       </c>
       <c r="E42" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F42" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G42" t="s">
-        <v>661</v>
+        <v>820</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>662</v>
+        <v>821</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4929,25 +5409,25 @@
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>663</v>
+        <v>822</v>
       </c>
       <c r="D43" t="s">
-        <v>664</v>
+        <v>823</v>
       </c>
       <c r="E43" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F43" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G43" t="s">
-        <v>665</v>
+        <v>824</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>666</v>
+        <v>825</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4958,25 +5438,25 @@
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>667</v>
+        <v>826</v>
       </c>
       <c r="D44" t="s">
-        <v>668</v>
+        <v>827</v>
       </c>
       <c r="E44" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F44" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G44" t="s">
-        <v>669</v>
+        <v>828</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>670</v>
+        <v>829</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4987,25 +5467,25 @@
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>671</v>
+        <v>830</v>
       </c>
       <c r="D45" t="s">
-        <v>672</v>
+        <v>831</v>
       </c>
       <c r="E45" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F45" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G45" t="s">
-        <v>673</v>
+        <v>832</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>674</v>
+        <v>833</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -5016,25 +5496,25 @@
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>675</v>
+        <v>834</v>
       </c>
       <c r="D46" t="s">
+        <v>835</v>
+      </c>
+      <c r="E46" t="s">
+        <v>681</v>
+      </c>
+      <c r="F46" t="s">
         <v>676</v>
       </c>
-      <c r="E46" t="s">
-        <v>522</v>
-      </c>
-      <c r="F46" t="s">
-        <v>517</v>
-      </c>
       <c r="G46" t="s">
-        <v>677</v>
+        <v>836</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>678</v>
+        <v>837</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -5045,25 +5525,25 @@
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>679</v>
+        <v>838</v>
       </c>
       <c r="D47" t="s">
-        <v>680</v>
+        <v>839</v>
       </c>
       <c r="E47" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F47" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G47" t="s">
-        <v>681</v>
+        <v>840</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>682</v>
+        <v>841</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -5074,25 +5554,25 @@
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>683</v>
+        <v>842</v>
       </c>
       <c r="D48" t="s">
-        <v>684</v>
+        <v>843</v>
       </c>
       <c r="E48" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F48" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G48" t="s">
-        <v>685</v>
+        <v>844</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>686</v>
+        <v>845</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -5103,25 +5583,25 @@
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>687</v>
+        <v>846</v>
       </c>
       <c r="D49" t="s">
-        <v>688</v>
+        <v>847</v>
       </c>
       <c r="E49" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F49" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G49" t="s">
-        <v>689</v>
+        <v>848</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>690</v>
+        <v>849</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5129,25 +5609,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>691</v>
+        <v>850</v>
       </c>
       <c r="D50" t="s">
-        <v>692</v>
+        <v>851</v>
       </c>
       <c r="E50" t="s">
-        <v>522</v>
+        <v>681</v>
       </c>
       <c r="F50" t="s">
-        <v>517</v>
+        <v>676</v>
       </c>
       <c r="G50" t="s">
-        <v>693</v>
+        <v>852</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>694</v>
+        <v>853</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5155,25 +5635,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>695</v>
+        <v>854</v>
       </c>
       <c r="D51" t="s">
-        <v>696</v>
+        <v>855</v>
       </c>
       <c r="E51" t="s">
-        <v>539</v>
+        <v>698</v>
       </c>
       <c r="F51" t="s">
-        <v>697</v>
+        <v>856</v>
       </c>
       <c r="G51" t="s">
-        <v>698</v>
+        <v>857</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>699</v>
+        <v>858</v>
       </c>
     </row>
   </sheetData>
@@ -5291,10 +5771,10 @@
       <c r="D5">
         <v>50</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="5" t="s">
         <v>118</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="5">
         <v>0</v>
       </c>
       <c r="G5" t="s">
@@ -5317,10 +5797,10 @@
       <c r="D6">
         <v>100</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="5">
         <v>80</v>
       </c>
       <c r="G6" t="s">
@@ -5343,10 +5823,10 @@
       <c r="D7">
         <v>150</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="5">
         <v>65</v>
       </c>
       <c r="G7" t="s">
@@ -5369,10 +5849,10 @@
       <c r="D8">
         <v>200</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="5">
         <v>65</v>
       </c>
       <c r="G8" t="s">
@@ -5395,10 +5875,10 @@
       <c r="D9">
         <v>300</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="5" t="s">
         <v>133</v>
       </c>
-      <c r="F9" s="4">
+      <c r="F9" s="5">
         <v>36</v>
       </c>
       <c r="G9" t="s">
@@ -5421,10 +5901,10 @@
       <c r="D10">
         <v>450</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="5" t="s">
         <v>136</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="5">
         <v>28</v>
       </c>
       <c r="G10" t="s">
@@ -5447,10 +5927,10 @@
       <c r="D11">
         <v>1000</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="5" t="s">
         <v>140</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="5">
         <v>14</v>
       </c>
       <c r="G11" t="s">
@@ -5473,10 +5953,10 @@
       <c r="D12">
         <v>2500</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="5" t="s">
         <v>144</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="5">
         <v>9</v>
       </c>
       <c r="G12" t="s">
@@ -5499,10 +5979,10 @@
       <c r="D13">
         <v>12500</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="5" t="s">
         <v>148</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="5">
         <v>3</v>
       </c>
       <c r="G13" t="s">
@@ -5533,30 +6013,30 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5">
-      <c r="A1" s="5" t="s">
+      <c r="A1" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>110</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4" t="s">
+      <c r="D1" s="5"/>
+      <c r="E1" s="5" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="5"/>
-      <c r="B2" s="4" t="s">
+      <c r="A2" s="6"/>
+      <c r="B2" s="5" t="s">
         <v>153</v>
       </c>
-      <c r="C2" s="4"/>
-      <c r="D2" s="4" t="s">
+      <c r="C2" s="5"/>
+      <c r="D2" s="5" t="s">
         <v>154</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="5" t="s">
         <v>155</v>
       </c>
     </row>
@@ -5573,7 +6053,7 @@
       <c r="D3" s="2">
         <v>1</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="5" t="s">
         <v>159</v>
       </c>
     </row>
@@ -5653,14 +6133,14 @@
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
       <c r="B9" s="2"/>
-      <c r="C9" s="4"/>
+      <c r="C9" s="5"/>
       <c r="D9" s="2"/>
       <c r="E9" s="2"/>
     </row>
     <row r="10" spans="1:5">
       <c r="A10" s="2"/>
       <c r="B10" s="2"/>
-      <c r="C10" s="4"/>
+      <c r="C10" s="5"/>
       <c r="D10" s="2"/>
       <c r="E10" s="2"/>
     </row>
@@ -6688,10 +7168,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E5" t="s">
@@ -6705,10 +7185,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>260</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
@@ -6722,10 +7202,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>21</v>
       </c>
       <c r="E7" t="s">
@@ -6739,10 +7219,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>12</v>
       </c>
       <c r="E8" t="s">
@@ -6756,10 +7236,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>3</v>
       </c>
       <c r="E9" t="s">
@@ -6790,10 +7270,10 @@
       <c r="B11">
         <v>2001</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>39</v>
       </c>
       <c r="E11" t="s">
@@ -6807,10 +7287,10 @@
       <c r="B12">
         <v>2002</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>47</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>48</v>
       </c>
       <c r="E12" t="s">
@@ -6982,10 +7462,10 @@
       <c r="B5">
         <v>1001</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="5" t="s">
         <v>7</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="5" t="s">
         <v>8</v>
       </c>
       <c r="G5" t="s">
@@ -7011,10 +7491,10 @@
       <c r="B6">
         <v>1002</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="5" t="s">
         <v>17</v>
       </c>
       <c r="G6" t="s">
@@ -7040,10 +7520,10 @@
       <c r="B7">
         <v>1003</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="5" t="s">
         <v>26</v>
       </c>
       <c r="G7" t="s">
@@ -7069,10 +7549,10 @@
       <c r="B8">
         <v>1004</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="5" t="s">
         <v>35</v>
       </c>
       <c r="G8" t="s">
@@ -7098,10 +7578,10 @@
       <c r="B9">
         <v>1005</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="5" t="s">
         <v>44</v>
       </c>
       <c r="G9" t="s">
@@ -7127,10 +7607,10 @@
       <c r="B10">
         <v>1006</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="5" t="s">
         <v>52</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="5" t="s">
         <v>53</v>
       </c>
       <c r="G10" t="s">
@@ -7156,10 +7636,10 @@
       <c r="B11">
         <v>1007</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="5" t="s">
         <v>60</v>
       </c>
       <c r="G11" t="s">
@@ -7185,10 +7665,10 @@
       <c r="B12">
         <v>1008</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="5" t="s">
         <v>67</v>
       </c>
       <c r="G12" t="s">
@@ -7214,10 +7694,10 @@
       <c r="B13">
         <v>1009</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>306</v>
       </c>
       <c r="G13" t="s">
@@ -7246,13 +7726,13 @@
       <c r="B14">
         <v>2001</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="5" t="s">
         <v>310</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="5" t="s">
         <v>311</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F14" t="s">
@@ -7266,13 +7746,13 @@
       <c r="B15">
         <v>2002</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="5" t="s">
         <v>313</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="5" t="s">
         <v>314</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="5" t="s">
         <v>7</v>
       </c>
       <c r="F15" t="s">
@@ -7286,13 +7766,13 @@
       <c r="B16">
         <v>2003</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="5" t="s">
         <v>315</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="5" t="s">
         <v>316</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F16" t="s">
@@ -7306,13 +7786,13 @@
       <c r="B17">
         <v>2004</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="5" t="s">
         <v>318</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="5" t="s">
         <v>319</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="5" t="s">
         <v>320</v>
       </c>
       <c r="F17" t="s">
@@ -7326,16 +7806,16 @@
       <c r="B18">
         <v>2005</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="5" t="s">
         <v>323</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="5" t="s">
         <v>324</v>
       </c>
-      <c r="E18" s="4" t="s">
+      <c r="E18" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="F18" s="4" t="s">
+      <c r="F18" s="5" t="s">
         <v>60</v>
       </c>
       <c r="N18" t="s">
@@ -7346,16 +7826,16 @@
       <c r="B19">
         <v>2006</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="5" t="s">
         <v>327</v>
       </c>
-      <c r="E19" s="4" t="s">
+      <c r="E19" s="5" t="s">
         <v>66</v>
       </c>
-      <c r="F19" s="4" t="s">
+      <c r="F19" s="5" t="s">
         <v>67</v>
       </c>
       <c r="N19" t="s">
@@ -7366,13 +7846,13 @@
       <c r="B20">
         <v>2007</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="5" t="s">
         <v>329</v>
       </c>
-      <c r="D20" s="4" t="s">
+      <c r="D20" s="5" t="s">
         <v>330</v>
       </c>
-      <c r="E20" s="4" t="s">
+      <c r="E20" s="5" t="s">
         <v>16</v>
       </c>
       <c r="F20" t="s">
@@ -7386,10 +7866,10 @@
       <c r="B21">
         <v>2008</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="5" t="s">
         <v>332</v>
       </c>
-      <c r="D21" s="4" t="s">
+      <c r="D21" s="5" t="s">
         <v>333</v>
       </c>
       <c r="E21" t="s">
@@ -7406,16 +7886,16 @@
       <c r="B22">
         <v>2009</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="5" t="s">
         <v>335</v>
       </c>
-      <c r="D22" s="4" t="s">
+      <c r="D22" s="5" t="s">
         <v>336</v>
       </c>
-      <c r="E22" s="4" t="s">
+      <c r="E22" s="5" t="s">
         <v>305</v>
       </c>
-      <c r="F22" s="4" t="s">
+      <c r="F22" s="5" t="s">
         <v>306</v>
       </c>
     </row>
@@ -7423,13 +7903,13 @@
       <c r="B23">
         <v>3001</v>
       </c>
-      <c r="C23" s="4" t="s">
+      <c r="C23" s="5" t="s">
         <v>337</v>
       </c>
-      <c r="D23" s="4" t="s">
+      <c r="D23" s="5" t="s">
         <v>338</v>
       </c>
-      <c r="E23" s="4" t="s">
+      <c r="E23" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F23" t="s">
@@ -7440,13 +7920,13 @@
       <c r="B24">
         <v>3002</v>
       </c>
-      <c r="C24" s="4" t="s">
+      <c r="C24" s="5" t="s">
         <v>339</v>
       </c>
-      <c r="D24" s="4" t="s">
+      <c r="D24" s="5" t="s">
         <v>340</v>
       </c>
-      <c r="E24" s="4" t="s">
+      <c r="E24" s="5" t="s">
         <v>25</v>
       </c>
       <c r="F24" t="s">
@@ -7457,13 +7937,13 @@
       <c r="B25">
         <v>3003</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="C25" s="5" t="s">
         <v>341</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="5" t="s">
         <v>342</v>
       </c>
-      <c r="E25" s="4" t="s">
+      <c r="E25" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F25" t="s">
@@ -7474,13 +7954,13 @@
       <c r="B26">
         <v>3004</v>
       </c>
-      <c r="C26" s="4" t="s">
+      <c r="C26" s="5" t="s">
         <v>343</v>
       </c>
-      <c r="D26" s="4" t="s">
+      <c r="D26" s="5" t="s">
         <v>344</v>
       </c>
-      <c r="E26" s="4" t="s">
+      <c r="E26" s="5" t="s">
         <v>34</v>
       </c>
       <c r="F26" t="s">
@@ -7491,13 +7971,13 @@
       <c r="B27">
         <v>3005</v>
       </c>
-      <c r="C27" s="4" t="s">
+      <c r="C27" s="5" t="s">
         <v>345</v>
       </c>
-      <c r="D27" s="4" t="s">
+      <c r="D27" s="5" t="s">
         <v>346</v>
       </c>
-      <c r="E27" s="4" t="s">
+      <c r="E27" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F27" t="s">
@@ -7508,13 +7988,13 @@
       <c r="B28">
         <v>3006</v>
       </c>
-      <c r="C28" s="4" t="s">
+      <c r="C28" s="5" t="s">
         <v>347</v>
       </c>
-      <c r="D28" s="4" t="s">
+      <c r="D28" s="5" t="s">
         <v>348</v>
       </c>
-      <c r="E28" s="4" t="s">
+      <c r="E28" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F28" t="s">
@@ -7525,13 +8005,13 @@
       <c r="B29">
         <v>3007</v>
       </c>
-      <c r="C29" s="4" t="s">
+      <c r="C29" s="5" t="s">
         <v>349</v>
       </c>
-      <c r="D29" s="4" t="s">
+      <c r="D29" s="5" t="s">
         <v>350</v>
       </c>
-      <c r="E29" s="4" t="s">
+      <c r="E29" s="5" t="s">
         <v>43</v>
       </c>
       <c r="F29" t="s">
@@ -7548,13 +8028,13 @@
       <c r="B30">
         <v>3008</v>
       </c>
-      <c r="C30" s="4" t="s">
+      <c r="C30" s="5" t="s">
         <v>351</v>
       </c>
-      <c r="D30" s="4" t="s">
+      <c r="D30" s="5" t="s">
         <v>352</v>
       </c>
-      <c r="E30" s="4" t="s">
+      <c r="E30" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F30" t="s">
@@ -7565,13 +8045,13 @@
       <c r="B31">
         <v>3009</v>
       </c>
-      <c r="C31" s="4" t="s">
+      <c r="C31" s="5" t="s">
         <v>353</v>
       </c>
-      <c r="D31" s="4" t="s">
+      <c r="D31" s="5" t="s">
         <v>354</v>
       </c>
-      <c r="E31" s="4" t="s">
+      <c r="E31" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F31" t="s">
@@ -7582,13 +8062,13 @@
       <c r="B32">
         <v>3010</v>
       </c>
-      <c r="C32" s="4" t="s">
+      <c r="C32" s="5" t="s">
         <v>355</v>
       </c>
-      <c r="D32" s="4" t="s">
+      <c r="D32" s="5" t="s">
         <v>356</v>
       </c>
-      <c r="E32" s="4" t="s">
+      <c r="E32" s="5" t="s">
         <v>52</v>
       </c>
       <c r="F32" t="s">
@@ -7997,7 +8477,7 @@
       <c r="E5" t="b">
         <v>1</v>
       </c>
-      <c r="F5" s="4" t="s">
+      <c r="F5" s="5" t="s">
         <v>396</v>
       </c>
     </row>
@@ -8014,7 +8494,7 @@
       <c r="E6" t="b">
         <v>1</v>
       </c>
-      <c r="F6" s="4" t="s">
+      <c r="F6" s="5" t="s">
         <v>398</v>
       </c>
     </row>
@@ -8031,7 +8511,7 @@
       <c r="E7" t="b">
         <v>1</v>
       </c>
-      <c r="F7" s="4" t="s">
+      <c r="F7" s="5" t="s">
         <v>400</v>
       </c>
     </row>
@@ -8048,12 +8528,12 @@
       <c r="E8" t="b">
         <v>1</v>
       </c>
-      <c r="F8" s="4" t="s">
+      <c r="F8" s="5" t="s">
         <v>402</v>
       </c>
     </row>
     <row r="9" spans="1:6">
-      <c r="F9" s="4"/>
+      <c r="F9" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8064,8 +8544,8 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H30"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
+  <dimension ref="A1:M32"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="13.4166666666667" customWidth="1"/>
@@ -8075,9 +8555,14 @@
     <col min="6" max="6" width="22.25" customWidth="1"/>
     <col min="7" max="7" width="25" customWidth="1"/>
     <col min="8" max="8" width="42.5" customWidth="1"/>
+    <col min="9" max="9" width="33.9166666666667" customWidth="1"/>
+    <col min="10" max="10" width="59.9166666666667" customWidth="1"/>
+    <col min="11" max="11" width="33.9166666666667" customWidth="1"/>
+    <col min="12" max="12" width="38.8333333333333" customWidth="1"/>
+    <col min="13" max="13" width="85.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8">
+    <row r="1" spans="1:13">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
@@ -8102,8 +8587,23 @@
       <c r="H1" t="s">
         <v>286</v>
       </c>
-    </row>
-    <row r="2" spans="1:8">
+      <c r="I1" t="s">
+        <v>409</v>
+      </c>
+      <c r="J1" t="s">
+        <v>410</v>
+      </c>
+      <c r="K1" t="s">
+        <v>411</v>
+      </c>
+      <c r="L1" t="s">
+        <v>412</v>
+      </c>
+      <c r="M1" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -8114,13 +8614,13 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>409</v>
+        <v>414</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>410</v>
+        <v>415</v>
       </c>
       <c r="G2" t="s">
         <v>288</v>
@@ -8128,60 +8628,105 @@
       <c r="H2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" ht="81" customHeight="1" spans="1:8">
+      <c r="I2" t="s">
+        <v>109</v>
+      </c>
+      <c r="J2" t="s">
+        <v>109</v>
+      </c>
+      <c r="K2" t="s">
+        <v>109</v>
+      </c>
+      <c r="L2" t="s">
+        <v>109</v>
+      </c>
+      <c r="M2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1" spans="1:13">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>411</v>
+        <v>416</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>412</v>
+        <v>417</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>413</v>
+        <v>418</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>414</v>
+        <v>419</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>415</v>
+        <v>420</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>416</v>
+        <v>421</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>417</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8">
+        <v>422</v>
+      </c>
+      <c r="I3" t="s">
+        <v>423</v>
+      </c>
+      <c r="J3" t="s">
+        <v>424</v>
+      </c>
+      <c r="K3" t="s">
+        <v>425</v>
+      </c>
+      <c r="L3" t="s">
+        <v>426</v>
+      </c>
+      <c r="M3" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13">
       <c r="A4" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>418</v>
+        <v>428</v>
       </c>
       <c r="C4" t="s">
-        <v>419</v>
+        <v>429</v>
       </c>
       <c r="D4" t="s">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="E4" t="s">
-        <v>421</v>
+        <v>431</v>
       </c>
       <c r="F4" t="s">
-        <v>422</v>
+        <v>432</v>
       </c>
       <c r="G4" t="s">
-        <v>423</v>
+        <v>433</v>
       </c>
       <c r="H4" t="s">
         <v>301</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
+      <c r="I4" t="s">
+        <v>434</v>
+      </c>
+      <c r="J4" t="s">
+        <v>435</v>
+      </c>
+      <c r="K4" t="s">
+        <v>436</v>
+      </c>
+      <c r="L4" t="s">
+        <v>437</v>
+      </c>
+      <c r="M4" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13">
       <c r="A5" t="s">
         <v>384</v>
       </c>
@@ -8189,10 +8734,10 @@
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>424</v>
+        <v>439</v>
       </c>
       <c r="D5" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8204,10 +8749,25 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
+        <v>441</v>
+      </c>
+      <c r="I5" t="s">
+        <v>442</v>
+      </c>
+      <c r="J5" t="s">
+        <v>443</v>
+      </c>
+      <c r="K5" t="s">
+        <v>444</v>
+      </c>
+      <c r="L5" t="s">
+        <v>445</v>
+      </c>
+      <c r="M5" t="s">
+        <v>446</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13">
       <c r="A6" t="s">
         <v>384</v>
       </c>
@@ -8215,10 +8775,10 @@
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>427</v>
+        <v>447</v>
       </c>
       <c r="D6" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8230,10 +8790,25 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
+        <v>448</v>
+      </c>
+      <c r="I6" t="s">
+        <v>449</v>
+      </c>
+      <c r="J6" t="s">
+        <v>450</v>
+      </c>
+      <c r="K6" t="s">
+        <v>451</v>
+      </c>
+      <c r="L6" t="s">
+        <v>452</v>
+      </c>
+      <c r="M6" t="s">
+        <v>453</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13">
       <c r="A7" t="s">
         <v>384</v>
       </c>
@@ -8241,10 +8816,10 @@
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>429</v>
+        <v>454</v>
       </c>
       <c r="D7" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8256,10 +8831,25 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>430</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
+        <v>455</v>
+      </c>
+      <c r="I7" t="s">
+        <v>456</v>
+      </c>
+      <c r="J7" t="s">
+        <v>457</v>
+      </c>
+      <c r="K7" t="s">
+        <v>458</v>
+      </c>
+      <c r="L7" t="s">
+        <v>459</v>
+      </c>
+      <c r="M7" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13">
       <c r="A8" t="s">
         <v>384</v>
       </c>
@@ -8267,10 +8857,10 @@
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>431</v>
+        <v>461</v>
       </c>
       <c r="D8" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8281,11 +8871,26 @@
       <c r="G8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" t="s">
-        <v>432</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
+      <c r="H8" s="4" t="s">
+        <v>462</v>
+      </c>
+      <c r="I8" t="s">
+        <v>463</v>
+      </c>
+      <c r="J8" t="s">
+        <v>464</v>
+      </c>
+      <c r="K8" t="s">
+        <v>465</v>
+      </c>
+      <c r="L8" t="s">
+        <v>466</v>
+      </c>
+      <c r="M8" t="s">
+        <v>467</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13">
       <c r="A9" t="s">
         <v>384</v>
       </c>
@@ -8293,10 +8898,10 @@
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>433</v>
+        <v>468</v>
       </c>
       <c r="D9" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8308,10 +8913,25 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>434</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
+        <v>469</v>
+      </c>
+      <c r="I9" t="s">
+        <v>470</v>
+      </c>
+      <c r="J9" t="s">
+        <v>471</v>
+      </c>
+      <c r="K9" t="s">
+        <v>472</v>
+      </c>
+      <c r="L9" t="s">
+        <v>473</v>
+      </c>
+      <c r="M9" t="s">
+        <v>474</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13">
       <c r="A10" t="s">
         <v>384</v>
       </c>
@@ -8319,10 +8939,10 @@
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>435</v>
+        <v>475</v>
       </c>
       <c r="D10" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8334,10 +8954,25 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>436</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
+        <v>476</v>
+      </c>
+      <c r="I10" t="s">
+        <v>477</v>
+      </c>
+      <c r="J10" t="s">
+        <v>478</v>
+      </c>
+      <c r="K10" t="s">
+        <v>479</v>
+      </c>
+      <c r="L10" t="s">
+        <v>480</v>
+      </c>
+      <c r="M10" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13">
       <c r="A11" t="s">
         <v>384</v>
       </c>
@@ -8345,10 +8980,10 @@
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="D11" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8360,10 +8995,25 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>438</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8">
+        <v>483</v>
+      </c>
+      <c r="I11" t="s">
+        <v>484</v>
+      </c>
+      <c r="J11" t="s">
+        <v>485</v>
+      </c>
+      <c r="K11" t="s">
+        <v>486</v>
+      </c>
+      <c r="L11" t="s">
+        <v>487</v>
+      </c>
+      <c r="M11" t="s">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13">
       <c r="A12" t="s">
         <v>384</v>
       </c>
@@ -8371,10 +9021,10 @@
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>439</v>
+        <v>489</v>
       </c>
       <c r="D12" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -8386,10 +9036,25 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>440</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
+        <v>490</v>
+      </c>
+      <c r="I12" t="s">
+        <v>491</v>
+      </c>
+      <c r="J12" t="s">
+        <v>492</v>
+      </c>
+      <c r="K12" t="s">
+        <v>493</v>
+      </c>
+      <c r="L12" t="s">
+        <v>494</v>
+      </c>
+      <c r="M12" t="s">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13">
       <c r="A13" t="s">
         <v>384</v>
       </c>
@@ -8397,10 +9062,10 @@
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>441</v>
+        <v>496</v>
       </c>
       <c r="D13" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -8412,10 +9077,25 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>442</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
+        <v>497</v>
+      </c>
+      <c r="I13" t="s">
+        <v>498</v>
+      </c>
+      <c r="J13" t="s">
+        <v>499</v>
+      </c>
+      <c r="K13" t="s">
+        <v>500</v>
+      </c>
+      <c r="L13" t="s">
+        <v>501</v>
+      </c>
+      <c r="M13" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13">
       <c r="A14" t="s">
         <v>384</v>
       </c>
@@ -8423,10 +9103,10 @@
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>443</v>
+        <v>503</v>
       </c>
       <c r="D14" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -8438,10 +9118,25 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8">
+        <v>504</v>
+      </c>
+      <c r="I14" t="s">
+        <v>505</v>
+      </c>
+      <c r="J14" t="s">
+        <v>506</v>
+      </c>
+      <c r="K14" t="s">
+        <v>507</v>
+      </c>
+      <c r="L14" t="s">
+        <v>508</v>
+      </c>
+      <c r="M14" t="s">
+        <v>509</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13">
       <c r="A15" t="s">
         <v>384</v>
       </c>
@@ -8449,10 +9144,10 @@
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>445</v>
+        <v>510</v>
       </c>
       <c r="D15" t="s">
-        <v>425</v>
+        <v>440</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -8464,10 +9159,25 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>446</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8">
+        <v>511</v>
+      </c>
+      <c r="I15" t="s">
+        <v>512</v>
+      </c>
+      <c r="J15" t="s">
+        <v>513</v>
+      </c>
+      <c r="K15" t="s">
+        <v>514</v>
+      </c>
+      <c r="L15" t="s">
+        <v>515</v>
+      </c>
+      <c r="M15" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13">
       <c r="A16" t="s">
         <v>384</v>
       </c>
@@ -8475,13 +9185,13 @@
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>447</v>
+        <v>517</v>
       </c>
       <c r="D16" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E16" t="s">
-        <v>449</v>
+        <v>519</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -8490,10 +9200,25 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8">
+        <v>520</v>
+      </c>
+      <c r="I16" t="s">
+        <v>521</v>
+      </c>
+      <c r="J16" t="s">
+        <v>522</v>
+      </c>
+      <c r="K16" t="s">
+        <v>523</v>
+      </c>
+      <c r="L16" t="s">
+        <v>524</v>
+      </c>
+      <c r="M16" t="s">
+        <v>525</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13">
       <c r="A17" t="s">
         <v>384</v>
       </c>
@@ -8501,13 +9226,13 @@
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>451</v>
+        <v>526</v>
       </c>
       <c r="D17" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E17" t="s">
-        <v>452</v>
+        <v>527</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -8516,10 +9241,25 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>453</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8">
+        <v>528</v>
+      </c>
+      <c r="I17" t="s">
+        <v>529</v>
+      </c>
+      <c r="J17" t="s">
+        <v>530</v>
+      </c>
+      <c r="K17" t="s">
+        <v>531</v>
+      </c>
+      <c r="L17" t="s">
+        <v>532</v>
+      </c>
+      <c r="M17" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="18" spans="1:13">
       <c r="A18" t="s">
         <v>384</v>
       </c>
@@ -8527,13 +9267,13 @@
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>454</v>
+        <v>534</v>
       </c>
       <c r="D18" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E18" t="s">
-        <v>455</v>
+        <v>535</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -8542,10 +9282,25 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8">
+        <v>536</v>
+      </c>
+      <c r="I18" t="s">
+        <v>537</v>
+      </c>
+      <c r="J18" t="s">
+        <v>538</v>
+      </c>
+      <c r="K18" t="s">
+        <v>539</v>
+      </c>
+      <c r="L18" t="s">
+        <v>540</v>
+      </c>
+      <c r="M18" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="19" spans="1:13">
       <c r="A19" t="s">
         <v>384</v>
       </c>
@@ -8553,13 +9308,13 @@
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>457</v>
+        <v>542</v>
       </c>
       <c r="D19" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E19" t="s">
-        <v>458</v>
+        <v>543</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -8568,10 +9323,25 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8">
+        <v>544</v>
+      </c>
+      <c r="I19" t="s">
+        <v>545</v>
+      </c>
+      <c r="J19" t="s">
+        <v>546</v>
+      </c>
+      <c r="K19" t="s">
+        <v>547</v>
+      </c>
+      <c r="L19" t="s">
+        <v>548</v>
+      </c>
+      <c r="M19" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13">
       <c r="A20" t="s">
         <v>384</v>
       </c>
@@ -8579,13 +9349,13 @@
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>460</v>
+        <v>550</v>
       </c>
       <c r="D20" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E20" t="s">
-        <v>461</v>
+        <v>551</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -8594,10 +9364,25 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>462</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8">
+        <v>552</v>
+      </c>
+      <c r="I20" t="s">
+        <v>553</v>
+      </c>
+      <c r="J20" t="s">
+        <v>554</v>
+      </c>
+      <c r="K20" t="s">
+        <v>555</v>
+      </c>
+      <c r="L20" t="s">
+        <v>556</v>
+      </c>
+      <c r="M20" t="s">
+        <v>557</v>
+      </c>
+    </row>
+    <row r="21" spans="1:13">
       <c r="A21" t="s">
         <v>384</v>
       </c>
@@ -8605,13 +9390,13 @@
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>463</v>
+        <v>558</v>
       </c>
       <c r="D21" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E21" t="s">
-        <v>464</v>
+        <v>559</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -8620,10 +9405,25 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>465</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8">
+        <v>560</v>
+      </c>
+      <c r="I21" t="s">
+        <v>561</v>
+      </c>
+      <c r="J21" t="s">
+        <v>562</v>
+      </c>
+      <c r="K21" t="s">
+        <v>563</v>
+      </c>
+      <c r="L21" t="s">
+        <v>564</v>
+      </c>
+      <c r="M21" t="s">
+        <v>565</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13">
       <c r="A22" t="s">
         <v>384</v>
       </c>
@@ -8631,13 +9431,13 @@
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>466</v>
+        <v>566</v>
       </c>
       <c r="D22" t="s">
-        <v>448</v>
+        <v>518</v>
       </c>
       <c r="E22" t="s">
-        <v>467</v>
+        <v>567</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -8646,10 +9446,25 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>468</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8">
+        <v>568</v>
+      </c>
+      <c r="I22" t="s">
+        <v>569</v>
+      </c>
+      <c r="J22" t="s">
+        <v>570</v>
+      </c>
+      <c r="K22" t="s">
+        <v>571</v>
+      </c>
+      <c r="L22" t="s">
+        <v>572</v>
+      </c>
+      <c r="M22" t="s">
+        <v>573</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13">
       <c r="A23" t="s">
         <v>384</v>
       </c>
@@ -8657,13 +9472,13 @@
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>469</v>
+        <v>574</v>
       </c>
       <c r="D23" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="E23" t="s">
-        <v>471</v>
+        <v>576</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -8672,10 +9487,25 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>472</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8">
+        <v>577</v>
+      </c>
+      <c r="I23" t="s">
+        <v>578</v>
+      </c>
+      <c r="J23" t="s">
+        <v>579</v>
+      </c>
+      <c r="K23" t="s">
+        <v>580</v>
+      </c>
+      <c r="L23" t="s">
+        <v>581</v>
+      </c>
+      <c r="M23" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13">
       <c r="A24" t="s">
         <v>384</v>
       </c>
@@ -8683,13 +9513,13 @@
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>473</v>
+        <v>583</v>
       </c>
       <c r="D24" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="E24" t="s">
-        <v>474</v>
+        <v>584</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -8698,10 +9528,25 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>475</v>
-      </c>
-    </row>
-    <row r="25" spans="1:8">
+        <v>585</v>
+      </c>
+      <c r="I24" t="s">
+        <v>586</v>
+      </c>
+      <c r="J24" t="s">
+        <v>587</v>
+      </c>
+      <c r="K24" t="s">
+        <v>588</v>
+      </c>
+      <c r="L24" t="s">
+        <v>589</v>
+      </c>
+      <c r="M24" t="s">
+        <v>590</v>
+      </c>
+    </row>
+    <row r="25" spans="1:13">
       <c r="A25" t="s">
         <v>384</v>
       </c>
@@ -8709,13 +9554,13 @@
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>476</v>
+        <v>591</v>
       </c>
       <c r="D25" t="s">
-        <v>470</v>
+        <v>575</v>
       </c>
       <c r="E25" t="s">
-        <v>477</v>
+        <v>592</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -8724,24 +9569,36 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8">
-      <c r="A26" t="s">
-        <v>384</v>
-      </c>
+        <v>593</v>
+      </c>
+      <c r="I25" t="s">
+        <v>52</v>
+      </c>
+      <c r="J25" t="s">
+        <v>594</v>
+      </c>
+      <c r="K25" t="s">
+        <v>595</v>
+      </c>
+      <c r="L25" t="s">
+        <v>596</v>
+      </c>
+      <c r="M25" t="s">
+        <v>597</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13">
       <c r="B26">
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>479</v>
+        <v>598</v>
       </c>
       <c r="D26" t="s">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="E26" t="s">
-        <v>20</v>
+        <v>29</v>
       </c>
       <c r="F26">
         <v>1</v>
@@ -8750,24 +9607,36 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>481</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8">
-      <c r="A27" t="s">
-        <v>384</v>
-      </c>
+        <v>600</v>
+      </c>
+      <c r="I26" t="s">
+        <v>601</v>
+      </c>
+      <c r="J26" t="s">
+        <v>602</v>
+      </c>
+      <c r="K26" t="s">
+        <v>603</v>
+      </c>
+      <c r="L26" t="s">
+        <v>604</v>
+      </c>
+      <c r="M26" t="s">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13">
       <c r="B27">
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>482</v>
+        <v>606</v>
       </c>
       <c r="D27" t="s">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="E27" t="s">
-        <v>11</v>
+        <v>607</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -8776,10 +9645,25 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>483</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8">
+        <v>608</v>
+      </c>
+      <c r="I27" t="s">
+        <v>609</v>
+      </c>
+      <c r="J27" t="s">
+        <v>610</v>
+      </c>
+      <c r="K27" t="s">
+        <v>611</v>
+      </c>
+      <c r="L27" t="s">
+        <v>612</v>
+      </c>
+      <c r="M27" t="s">
+        <v>613</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13">
       <c r="A28" t="s">
         <v>384</v>
       </c>
@@ -8787,13 +9671,13 @@
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>484</v>
+        <v>614</v>
       </c>
       <c r="D28" t="s">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="E28" t="s">
-        <v>2</v>
+        <v>20</v>
       </c>
       <c r="F28">
         <v>1</v>
@@ -8802,10 +9686,25 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8">
+        <v>615</v>
+      </c>
+      <c r="I28" t="s">
+        <v>616</v>
+      </c>
+      <c r="J28" t="s">
+        <v>617</v>
+      </c>
+      <c r="K28" t="s">
+        <v>618</v>
+      </c>
+      <c r="L28" t="s">
+        <v>619</v>
+      </c>
+      <c r="M28" t="s">
+        <v>620</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13">
       <c r="A29" t="s">
         <v>384</v>
       </c>
@@ -8813,13 +9712,13 @@
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>486</v>
+        <v>621</v>
       </c>
       <c r="D29" t="s">
-        <v>480</v>
+        <v>599</v>
       </c>
       <c r="E29" t="s">
-        <v>269</v>
+        <v>11</v>
       </c>
       <c r="F29">
         <v>1</v>
@@ -8828,21 +9727,39 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>487</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8">
+        <v>622</v>
+      </c>
+      <c r="I29" t="s">
+        <v>623</v>
+      </c>
+      <c r="J29" t="s">
+        <v>624</v>
+      </c>
+      <c r="K29" t="s">
+        <v>625</v>
+      </c>
+      <c r="L29" t="s">
+        <v>626</v>
+      </c>
+      <c r="M29" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13">
+      <c r="A30" t="s">
+        <v>384</v>
+      </c>
       <c r="B30">
-        <v>1011</v>
+        <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>488</v>
+        <v>628</v>
       </c>
       <c r="D30" t="s">
-        <v>425</v>
+        <v>599</v>
       </c>
       <c r="E30" t="s">
-        <v>489</v>
+        <v>2</v>
       </c>
       <c r="F30">
         <v>1</v>
@@ -8851,7 +9768,101 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>490</v>
+        <v>629</v>
+      </c>
+      <c r="I30" t="s">
+        <v>630</v>
+      </c>
+      <c r="J30" t="s">
+        <v>631</v>
+      </c>
+      <c r="K30" t="s">
+        <v>632</v>
+      </c>
+      <c r="L30" t="s">
+        <v>633</v>
+      </c>
+      <c r="M30" t="s">
+        <v>634</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13">
+      <c r="A31" t="s">
+        <v>384</v>
+      </c>
+      <c r="B31">
+        <v>1306</v>
+      </c>
+      <c r="C31" t="s">
+        <v>635</v>
+      </c>
+      <c r="D31" t="s">
+        <v>599</v>
+      </c>
+      <c r="E31" t="s">
+        <v>269</v>
+      </c>
+      <c r="F31">
+        <v>1</v>
+      </c>
+      <c r="G31" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" t="s">
+        <v>636</v>
+      </c>
+      <c r="I31" t="s">
+        <v>637</v>
+      </c>
+      <c r="J31" t="s">
+        <v>638</v>
+      </c>
+      <c r="K31" t="s">
+        <v>639</v>
+      </c>
+      <c r="L31" t="s">
+        <v>640</v>
+      </c>
+      <c r="M31" t="s">
+        <v>641</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13">
+      <c r="B32">
+        <v>1011</v>
+      </c>
+      <c r="C32" t="s">
+        <v>642</v>
+      </c>
+      <c r="D32" t="s">
+        <v>440</v>
+      </c>
+      <c r="E32" t="s">
+        <v>643</v>
+      </c>
+      <c r="F32">
+        <v>1</v>
+      </c>
+      <c r="G32" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" t="s">
+        <v>644</v>
+      </c>
+      <c r="I32" t="s">
+        <v>645</v>
+      </c>
+      <c r="J32" t="s">
+        <v>646</v>
+      </c>
+      <c r="K32" t="s">
+        <v>647</v>
+      </c>
+      <c r="L32" t="s">
+        <v>648</v>
+      </c>
+      <c r="M32" t="s">
+        <v>649</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1483" uniqueCount="859">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
   <si>
     <t>Dog</t>
   </si>
@@ -552,6 +552,15 @@
   </si>
   <si>
     <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+  </si>
+  <si>
+    <t>LinkTreeVisibleBannerCount</t>
+  </si>
+  <si>
+    <t>LinkTree最佳显示条目数量</t>
+  </si>
+  <si>
+    <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4188,28 +4197,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>650</v>
+        <v>653</v>
       </c>
       <c r="C1" t="s">
-        <v>651</v>
+        <v>654</v>
       </c>
       <c r="D1" t="s">
-        <v>652</v>
+        <v>655</v>
       </c>
       <c r="E1" t="s">
-        <v>653</v>
+        <v>656</v>
       </c>
       <c r="F1" t="s">
-        <v>654</v>
+        <v>657</v>
       </c>
       <c r="G1" t="s">
-        <v>655</v>
+        <v>658</v>
       </c>
       <c r="H1" t="s">
-        <v>656</v>
+        <v>659</v>
       </c>
       <c r="I1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4226,16 +4235,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>657</v>
+        <v>660</v>
       </c>
       <c r="F2" t="s">
-        <v>658</v>
+        <v>661</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4246,28 +4255,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>659</v>
+        <v>662</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>660</v>
+        <v>663</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>661</v>
+        <v>664</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>662</v>
+        <v>665</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>663</v>
+        <v>666</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>664</v>
+        <v>667</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>665</v>
+        <v>668</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>666</v>
+        <v>669</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4275,1333 +4284,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>667</v>
+        <v>670</v>
       </c>
       <c r="C4" t="s">
-        <v>668</v>
+        <v>671</v>
       </c>
       <c r="D4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>669</v>
+        <v>672</v>
       </c>
       <c r="F4" t="s">
-        <v>670</v>
+        <v>673</v>
       </c>
       <c r="G4" t="s">
-        <v>671</v>
+        <v>674</v>
       </c>
       <c r="H4" t="s">
-        <v>672</v>
+        <v>675</v>
       </c>
       <c r="I4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>673</v>
+        <v>676</v>
       </c>
       <c r="D5" t="s">
-        <v>674</v>
+        <v>677</v>
       </c>
       <c r="E5" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F5" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G5" t="s">
-        <v>677</v>
+        <v>680</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>678</v>
+        <v>681</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>682</v>
+      </c>
+      <c r="D6" t="s">
+        <v>683</v>
+      </c>
+      <c r="E6" t="s">
+        <v>684</v>
+      </c>
+      <c r="F6" t="s">
         <v>679</v>
       </c>
-      <c r="D6" t="s">
-        <v>680</v>
-      </c>
-      <c r="E6" t="s">
-        <v>681</v>
-      </c>
-      <c r="F6" t="s">
-        <v>676</v>
-      </c>
       <c r="G6" t="s">
-        <v>682</v>
+        <v>685</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>683</v>
+        <v>686</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="D7" t="s">
-        <v>685</v>
+        <v>688</v>
       </c>
       <c r="E7" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F7" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G7" t="s">
-        <v>686</v>
+        <v>689</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>687</v>
+        <v>690</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>688</v>
+        <v>691</v>
       </c>
       <c r="D8" t="s">
-        <v>689</v>
+        <v>692</v>
       </c>
       <c r="E8" t="s">
-        <v>675</v>
+        <v>678</v>
       </c>
       <c r="F8" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G8" t="s">
-        <v>690</v>
+        <v>693</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>691</v>
+        <v>694</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>692</v>
+        <v>695</v>
       </c>
       <c r="D9" t="s">
-        <v>693</v>
+        <v>696</v>
       </c>
       <c r="E9" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F9" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G9" t="s">
-        <v>694</v>
+        <v>697</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>695</v>
+        <v>698</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>696</v>
+        <v>699</v>
       </c>
       <c r="D10" t="s">
-        <v>697</v>
+        <v>700</v>
       </c>
       <c r="E10" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F10" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G10" t="s">
-        <v>699</v>
+        <v>702</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>700</v>
+        <v>703</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="D11" t="s">
-        <v>702</v>
+        <v>705</v>
       </c>
       <c r="E11" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F11" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G11" t="s">
-        <v>703</v>
+        <v>706</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>704</v>
+        <v>707</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>705</v>
+        <v>708</v>
       </c>
       <c r="D12" t="s">
-        <v>706</v>
+        <v>709</v>
       </c>
       <c r="E12" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F12" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G12" t="s">
-        <v>707</v>
+        <v>710</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>708</v>
+        <v>711</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="D13" t="s">
-        <v>710</v>
+        <v>713</v>
       </c>
       <c r="E13" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F13" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G13" t="s">
-        <v>711</v>
+        <v>714</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>712</v>
+        <v>715</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="D14" t="s">
-        <v>714</v>
+        <v>717</v>
       </c>
       <c r="E14" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F14" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G14" t="s">
-        <v>715</v>
+        <v>718</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>716</v>
+        <v>719</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>717</v>
+        <v>720</v>
       </c>
       <c r="D15" t="s">
-        <v>718</v>
+        <v>721</v>
       </c>
       <c r="E15" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F15" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G15" t="s">
-        <v>719</v>
+        <v>722</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>720</v>
+        <v>723</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>721</v>
+        <v>724</v>
       </c>
       <c r="D16" t="s">
-        <v>722</v>
+        <v>725</v>
       </c>
       <c r="E16" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F16" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G16" t="s">
-        <v>723</v>
+        <v>726</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>724</v>
+        <v>727</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>725</v>
+        <v>728</v>
       </c>
       <c r="D17" t="s">
-        <v>726</v>
+        <v>729</v>
       </c>
       <c r="E17" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F17" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G17" t="s">
-        <v>727</v>
+        <v>730</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>728</v>
+        <v>731</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>729</v>
+        <v>732</v>
       </c>
       <c r="D18" t="s">
-        <v>730</v>
+        <v>733</v>
       </c>
       <c r="E18" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F18" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G18" t="s">
-        <v>731</v>
+        <v>734</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>732</v>
+        <v>735</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="D19" t="s">
-        <v>733</v>
+        <v>736</v>
       </c>
       <c r="E19" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F19" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G19" t="s">
-        <v>734</v>
+        <v>737</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>735</v>
+        <v>738</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="D20" t="s">
-        <v>736</v>
+        <v>739</v>
       </c>
       <c r="E20" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F20" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G20" t="s">
-        <v>737</v>
+        <v>740</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>738</v>
+        <v>741</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="D21" t="s">
-        <v>739</v>
+        <v>742</v>
       </c>
       <c r="E21" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F21" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G21" t="s">
-        <v>740</v>
+        <v>743</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>741</v>
+        <v>744</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="D22" t="s">
-        <v>742</v>
+        <v>745</v>
       </c>
       <c r="E22" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F22" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G22" t="s">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>744</v>
+        <v>747</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="D23" t="s">
-        <v>745</v>
+        <v>748</v>
       </c>
       <c r="E23" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F23" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G23" t="s">
-        <v>746</v>
+        <v>749</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>747</v>
+        <v>750</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="D24" t="s">
-        <v>748</v>
+        <v>751</v>
       </c>
       <c r="E24" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F24" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G24" t="s">
-        <v>749</v>
+        <v>752</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>750</v>
+        <v>753</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="D25" t="s">
-        <v>751</v>
+        <v>754</v>
       </c>
       <c r="E25" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F25" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G25" t="s">
-        <v>752</v>
+        <v>755</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>753</v>
+        <v>756</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>754</v>
+        <v>757</v>
       </c>
       <c r="D26" t="s">
-        <v>755</v>
+        <v>758</v>
       </c>
       <c r="E26" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F26" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G26" t="s">
-        <v>756</v>
+        <v>759</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>757</v>
+        <v>760</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>758</v>
+        <v>761</v>
       </c>
       <c r="D27" t="s">
-        <v>759</v>
+        <v>762</v>
       </c>
       <c r="E27" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F27" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G27" t="s">
-        <v>760</v>
+        <v>763</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>761</v>
+        <v>764</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>762</v>
+        <v>765</v>
       </c>
       <c r="D28" t="s">
-        <v>763</v>
+        <v>766</v>
       </c>
       <c r="E28" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F28" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G28" t="s">
-        <v>764</v>
+        <v>767</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>765</v>
+        <v>768</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>766</v>
+        <v>769</v>
       </c>
       <c r="D29" t="s">
-        <v>767</v>
+        <v>770</v>
       </c>
       <c r="E29" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F29" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G29" t="s">
-        <v>768</v>
+        <v>771</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>769</v>
+        <v>772</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>770</v>
+        <v>773</v>
       </c>
       <c r="D30" t="s">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="E30" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F30" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G30" t="s">
-        <v>772</v>
+        <v>775</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>773</v>
+        <v>776</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>774</v>
+        <v>777</v>
       </c>
       <c r="D31" t="s">
-        <v>775</v>
+        <v>778</v>
       </c>
       <c r="E31" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F31" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G31" t="s">
-        <v>776</v>
+        <v>779</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>777</v>
+        <v>780</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>778</v>
+        <v>781</v>
       </c>
       <c r="D32" t="s">
-        <v>779</v>
+        <v>782</v>
       </c>
       <c r="E32" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F32" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G32" t="s">
-        <v>780</v>
+        <v>783</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>781</v>
+        <v>784</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>782</v>
+        <v>785</v>
       </c>
       <c r="D33" t="s">
-        <v>783</v>
+        <v>786</v>
       </c>
       <c r="E33" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F33" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G33" t="s">
-        <v>784</v>
+        <v>787</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>785</v>
+        <v>788</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>786</v>
+        <v>789</v>
       </c>
       <c r="D34" t="s">
-        <v>787</v>
+        <v>790</v>
       </c>
       <c r="E34" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F34" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G34" t="s">
-        <v>788</v>
+        <v>791</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>789</v>
+        <v>792</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>790</v>
+        <v>793</v>
       </c>
       <c r="D35" t="s">
-        <v>791</v>
+        <v>794</v>
       </c>
       <c r="E35" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F35" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G35" t="s">
-        <v>792</v>
+        <v>795</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>793</v>
+        <v>796</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>794</v>
+        <v>797</v>
       </c>
       <c r="D36" t="s">
-        <v>795</v>
+        <v>798</v>
       </c>
       <c r="E36" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F36" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G36" t="s">
-        <v>796</v>
+        <v>799</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>797</v>
+        <v>800</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>798</v>
+        <v>801</v>
       </c>
       <c r="D37" t="s">
-        <v>799</v>
+        <v>802</v>
       </c>
       <c r="E37" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F37" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G37" t="s">
-        <v>800</v>
+        <v>803</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>801</v>
+        <v>804</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>802</v>
+        <v>805</v>
       </c>
       <c r="D38" t="s">
-        <v>803</v>
+        <v>806</v>
       </c>
       <c r="E38" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F38" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G38" t="s">
-        <v>804</v>
+        <v>807</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>805</v>
+        <v>808</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>806</v>
+        <v>809</v>
       </c>
       <c r="D39" t="s">
-        <v>807</v>
+        <v>810</v>
       </c>
       <c r="E39" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F39" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G39" t="s">
-        <v>808</v>
+        <v>811</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>809</v>
+        <v>812</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>810</v>
+        <v>813</v>
       </c>
       <c r="D40" t="s">
-        <v>811</v>
+        <v>814</v>
       </c>
       <c r="E40" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F40" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G40" t="s">
-        <v>812</v>
+        <v>815</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>813</v>
+        <v>816</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>814</v>
+        <v>817</v>
       </c>
       <c r="D41" t="s">
-        <v>815</v>
+        <v>818</v>
       </c>
       <c r="E41" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F41" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G41" t="s">
-        <v>816</v>
+        <v>819</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>817</v>
+        <v>820</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>818</v>
+        <v>821</v>
       </c>
       <c r="D42" t="s">
-        <v>819</v>
+        <v>822</v>
       </c>
       <c r="E42" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F42" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G42" t="s">
-        <v>820</v>
+        <v>823</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>821</v>
+        <v>824</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>822</v>
+        <v>825</v>
       </c>
       <c r="D43" t="s">
-        <v>823</v>
+        <v>826</v>
       </c>
       <c r="E43" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F43" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G43" t="s">
-        <v>824</v>
+        <v>827</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>825</v>
+        <v>828</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>826</v>
+        <v>829</v>
       </c>
       <c r="D44" t="s">
-        <v>827</v>
+        <v>830</v>
       </c>
       <c r="E44" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F44" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G44" t="s">
-        <v>828</v>
+        <v>831</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>829</v>
+        <v>832</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>830</v>
+        <v>833</v>
       </c>
       <c r="D45" t="s">
-        <v>831</v>
+        <v>834</v>
       </c>
       <c r="E45" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F45" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G45" t="s">
-        <v>832</v>
+        <v>835</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>833</v>
+        <v>836</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>834</v>
+        <v>837</v>
       </c>
       <c r="D46" t="s">
-        <v>835</v>
+        <v>838</v>
       </c>
       <c r="E46" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F46" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G46" t="s">
-        <v>836</v>
+        <v>839</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>837</v>
+        <v>840</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>838</v>
+        <v>841</v>
       </c>
       <c r="D47" t="s">
-        <v>839</v>
+        <v>842</v>
       </c>
       <c r="E47" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F47" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G47" t="s">
-        <v>840</v>
+        <v>843</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>841</v>
+        <v>844</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>842</v>
+        <v>845</v>
       </c>
       <c r="D48" t="s">
-        <v>843</v>
+        <v>846</v>
       </c>
       <c r="E48" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F48" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G48" t="s">
-        <v>844</v>
+        <v>847</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>845</v>
+        <v>848</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>846</v>
+        <v>849</v>
       </c>
       <c r="D49" t="s">
-        <v>847</v>
+        <v>850</v>
       </c>
       <c r="E49" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F49" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G49" t="s">
-        <v>848</v>
+        <v>851</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>849</v>
+        <v>852</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5609,25 +5618,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>850</v>
+        <v>853</v>
       </c>
       <c r="D50" t="s">
-        <v>851</v>
+        <v>854</v>
       </c>
       <c r="E50" t="s">
-        <v>681</v>
+        <v>684</v>
       </c>
       <c r="F50" t="s">
-        <v>676</v>
+        <v>679</v>
       </c>
       <c r="G50" t="s">
-        <v>852</v>
+        <v>855</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>853</v>
+        <v>856</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5635,25 +5644,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>854</v>
+        <v>857</v>
       </c>
       <c r="D51" t="s">
-        <v>855</v>
+        <v>858</v>
       </c>
       <c r="E51" t="s">
-        <v>698</v>
+        <v>701</v>
       </c>
       <c r="F51" t="s">
-        <v>856</v>
+        <v>859</v>
       </c>
       <c r="G51" t="s">
-        <v>857</v>
+        <v>860</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>858</v>
+        <v>861</v>
       </c>
     </row>
   </sheetData>
@@ -6126,9 +6135,21 @@
       </c>
     </row>
     <row r="8" spans="1:5">
-      <c r="A8" s="2"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
+      <c r="A8" s="2" t="s">
+        <v>172</v>
+      </c>
+      <c r="B8" t="s">
+        <v>173</v>
+      </c>
+      <c r="C8" t="s">
+        <v>107</v>
+      </c>
+      <c r="D8" s="2">
+        <v>5</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>174</v>
+      </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9" s="2"/>
@@ -6183,55 +6204,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="J1" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="K1" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="L1" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="M1" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="N1" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="O1" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="P1" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="Q1" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="R1" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="S1" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="T1" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6302,10 +6323,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6319,55 +6340,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="D4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="E4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="H4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="I4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="J4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="K4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="L4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="M4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="N4" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="O4" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="P4" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="Q4" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="R4" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="S4" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="T4" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6375,58 +6396,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="D5" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="E5" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F5" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G5" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H5" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="I5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" t="s">
+        <v>216</v>
+      </c>
+      <c r="K5" t="s">
+        <v>217</v>
+      </c>
+      <c r="L5" t="s">
+        <v>218</v>
+      </c>
+      <c r="M5" t="s">
         <v>212</v>
       </c>
-      <c r="J5" t="s">
+      <c r="N5" t="s">
+        <v>219</v>
+      </c>
+      <c r="O5" t="s">
+        <v>220</v>
+      </c>
+      <c r="P5" t="s">
         <v>213</v>
       </c>
-      <c r="K5" t="s">
-        <v>214</v>
-      </c>
-      <c r="L5" t="s">
-        <v>215</v>
-      </c>
-      <c r="M5" t="s">
-        <v>209</v>
-      </c>
-      <c r="N5" t="s">
-        <v>216</v>
-      </c>
-      <c r="O5" t="s">
-        <v>217</v>
-      </c>
-      <c r="P5" t="s">
-        <v>210</v>
-      </c>
       <c r="Q5" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R5" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S5" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T5" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6434,58 +6455,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D6" t="s">
+        <v>226</v>
+      </c>
+      <c r="E6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" t="s">
+        <v>218</v>
+      </c>
+      <c r="M6" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P6" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>221</v>
+      </c>
+      <c r="R6" t="s">
         <v>222</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" t="s">
         <v>223</v>
       </c>
-      <c r="E6" t="s">
-        <v>209</v>
-      </c>
-      <c r="F6" t="s">
-        <v>218</v>
-      </c>
-      <c r="G6" t="s">
-        <v>180</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="T6" t="s">
         <v>224</v>
-      </c>
-      <c r="I6" t="s">
-        <v>212</v>
-      </c>
-      <c r="J6" t="s">
-        <v>213</v>
-      </c>
-      <c r="K6" t="s">
-        <v>214</v>
-      </c>
-      <c r="L6" t="s">
-        <v>215</v>
-      </c>
-      <c r="M6" t="s">
-        <v>209</v>
-      </c>
-      <c r="N6" t="s">
-        <v>216</v>
-      </c>
-      <c r="O6" t="s">
-        <v>217</v>
-      </c>
-      <c r="P6" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>218</v>
-      </c>
-      <c r="R6" t="s">
-        <v>219</v>
-      </c>
-      <c r="S6" t="s">
-        <v>220</v>
-      </c>
-      <c r="T6" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6493,58 +6514,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="D7" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" t="s">
+        <v>218</v>
+      </c>
+      <c r="M7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" t="s">
         <v>219</v>
       </c>
-      <c r="G7" t="s">
-        <v>180</v>
-      </c>
-      <c r="H7" t="s">
-        <v>227</v>
-      </c>
-      <c r="I7" t="s">
-        <v>212</v>
-      </c>
-      <c r="J7" t="s">
+      <c r="O7" t="s">
+        <v>220</v>
+      </c>
+      <c r="P7" t="s">
         <v>213</v>
       </c>
-      <c r="K7" t="s">
-        <v>214</v>
-      </c>
-      <c r="L7" t="s">
-        <v>215</v>
-      </c>
-      <c r="M7" t="s">
-        <v>209</v>
-      </c>
-      <c r="N7" t="s">
-        <v>216</v>
-      </c>
-      <c r="O7" t="s">
-        <v>217</v>
-      </c>
-      <c r="P7" t="s">
-        <v>210</v>
-      </c>
       <c r="Q7" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R7" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S7" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T7" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6552,58 +6573,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>229</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
+        <v>219</v>
+      </c>
+      <c r="F8" t="s">
+        <v>220</v>
+      </c>
+      <c r="G8" t="s">
+        <v>183</v>
+      </c>
+      <c r="H8" t="s">
+        <v>233</v>
+      </c>
+      <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" t="s">
         <v>216</v>
       </c>
-      <c r="F8" t="s">
+      <c r="K8" t="s">
         <v>217</v>
       </c>
-      <c r="G8" t="s">
-        <v>180</v>
-      </c>
-      <c r="H8" t="s">
-        <v>230</v>
-      </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
+        <v>218</v>
+      </c>
+      <c r="M8" t="s">
         <v>212</v>
       </c>
-      <c r="J8" t="s">
+      <c r="N8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P8" t="s">
         <v>213</v>
       </c>
-      <c r="K8" t="s">
-        <v>214</v>
-      </c>
-      <c r="L8" t="s">
-        <v>215</v>
-      </c>
-      <c r="M8" t="s">
-        <v>209</v>
-      </c>
-      <c r="N8" t="s">
-        <v>216</v>
-      </c>
-      <c r="O8" t="s">
-        <v>217</v>
-      </c>
-      <c r="P8" t="s">
-        <v>210</v>
-      </c>
       <c r="Q8" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R8" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S8" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T8" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6611,58 +6632,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" t="s">
+        <v>217</v>
+      </c>
+      <c r="L9" t="s">
+        <v>218</v>
+      </c>
+      <c r="M9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" t="s">
         <v>219</v>
       </c>
-      <c r="G9" t="s">
-        <v>180</v>
-      </c>
-      <c r="H9" t="s">
-        <v>211</v>
-      </c>
-      <c r="I9" t="s">
-        <v>233</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="O9" t="s">
+        <v>220</v>
+      </c>
+      <c r="P9" t="s">
         <v>213</v>
       </c>
-      <c r="K9" t="s">
-        <v>214</v>
-      </c>
-      <c r="L9" t="s">
-        <v>215</v>
-      </c>
-      <c r="M9" t="s">
-        <v>209</v>
-      </c>
-      <c r="N9" t="s">
-        <v>216</v>
-      </c>
-      <c r="O9" t="s">
-        <v>217</v>
-      </c>
-      <c r="P9" t="s">
-        <v>210</v>
-      </c>
       <c r="Q9" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R9" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S9" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T9" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6670,58 +6691,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
+        <v>219</v>
+      </c>
+      <c r="F10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" t="s">
         <v>216</v>
       </c>
-      <c r="F10" t="s">
-        <v>210</v>
-      </c>
-      <c r="G10" t="s">
-        <v>180</v>
-      </c>
-      <c r="H10" t="s">
-        <v>211</v>
-      </c>
-      <c r="I10" t="s">
-        <v>236</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="K10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L10" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10" t="s">
+        <v>212</v>
+      </c>
+      <c r="N10" t="s">
+        <v>219</v>
+      </c>
+      <c r="O10" t="s">
+        <v>220</v>
+      </c>
+      <c r="P10" t="s">
         <v>213</v>
       </c>
-      <c r="K10" t="s">
-        <v>214</v>
-      </c>
-      <c r="L10" t="s">
-        <v>215</v>
-      </c>
-      <c r="M10" t="s">
-        <v>209</v>
-      </c>
-      <c r="N10" t="s">
-        <v>216</v>
-      </c>
-      <c r="O10" t="s">
-        <v>217</v>
-      </c>
-      <c r="P10" t="s">
-        <v>210</v>
-      </c>
       <c r="Q10" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R10" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S10" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T10" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6729,58 +6750,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" t="s">
+        <v>218</v>
+      </c>
+      <c r="M11" t="s">
+        <v>212</v>
+      </c>
+      <c r="N11" t="s">
+        <v>219</v>
+      </c>
+      <c r="O11" t="s">
+        <v>220</v>
+      </c>
+      <c r="P11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" t="s">
         <v>221</v>
       </c>
-      <c r="G11" t="s">
-        <v>180</v>
-      </c>
-      <c r="H11" t="s">
+      <c r="R11" t="s">
+        <v>222</v>
+      </c>
+      <c r="S11" t="s">
+        <v>223</v>
+      </c>
+      <c r="T11" t="s">
         <v>224</v>
-      </c>
-      <c r="I11" t="s">
-        <v>233</v>
-      </c>
-      <c r="J11" t="s">
-        <v>213</v>
-      </c>
-      <c r="K11" t="s">
-        <v>214</v>
-      </c>
-      <c r="L11" t="s">
-        <v>215</v>
-      </c>
-      <c r="M11" t="s">
-        <v>209</v>
-      </c>
-      <c r="N11" t="s">
-        <v>216</v>
-      </c>
-      <c r="O11" t="s">
-        <v>217</v>
-      </c>
-      <c r="P11" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>218</v>
-      </c>
-      <c r="R11" t="s">
-        <v>219</v>
-      </c>
-      <c r="S11" t="s">
-        <v>220</v>
-      </c>
-      <c r="T11" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6788,58 +6809,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
+        <v>242</v>
+      </c>
+      <c r="D12" t="s">
+        <v>243</v>
+      </c>
+      <c r="E12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I12" t="s">
         <v>239</v>
       </c>
-      <c r="D12" t="s">
-        <v>240</v>
-      </c>
-      <c r="E12" t="s">
-        <v>209</v>
-      </c>
-      <c r="F12" t="s">
-        <v>210</v>
-      </c>
-      <c r="G12" t="s">
-        <v>180</v>
-      </c>
-      <c r="H12" t="s">
+      <c r="J12" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" t="s">
+        <v>218</v>
+      </c>
+      <c r="M12" t="s">
+        <v>212</v>
+      </c>
+      <c r="N12" t="s">
+        <v>219</v>
+      </c>
+      <c r="O12" t="s">
+        <v>220</v>
+      </c>
+      <c r="P12" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>221</v>
+      </c>
+      <c r="R12" t="s">
+        <v>222</v>
+      </c>
+      <c r="S12" t="s">
+        <v>223</v>
+      </c>
+      <c r="T12" t="s">
         <v>224</v>
-      </c>
-      <c r="I12" t="s">
-        <v>236</v>
-      </c>
-      <c r="J12" t="s">
-        <v>213</v>
-      </c>
-      <c r="K12" t="s">
-        <v>214</v>
-      </c>
-      <c r="L12" t="s">
-        <v>215</v>
-      </c>
-      <c r="M12" t="s">
-        <v>209</v>
-      </c>
-      <c r="N12" t="s">
-        <v>216</v>
-      </c>
-      <c r="O12" t="s">
-        <v>217</v>
-      </c>
-      <c r="P12" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>218</v>
-      </c>
-      <c r="R12" t="s">
-        <v>219</v>
-      </c>
-      <c r="S12" t="s">
-        <v>220</v>
-      </c>
-      <c r="T12" t="s">
-        <v>221</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6847,58 +6868,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I13" t="s">
+        <v>236</v>
+      </c>
+      <c r="J13" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" t="s">
+        <v>218</v>
+      </c>
+      <c r="M13" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" t="s">
+        <v>219</v>
+      </c>
+      <c r="O13" t="s">
+        <v>220</v>
+      </c>
+      <c r="P13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" t="s">
         <v>221</v>
       </c>
-      <c r="G13" t="s">
-        <v>180</v>
-      </c>
-      <c r="H13" t="s">
-        <v>227</v>
-      </c>
-      <c r="I13" t="s">
-        <v>233</v>
-      </c>
-      <c r="J13" t="s">
-        <v>213</v>
-      </c>
-      <c r="K13" t="s">
-        <v>214</v>
-      </c>
-      <c r="L13" t="s">
-        <v>215</v>
-      </c>
-      <c r="M13" t="s">
-        <v>209</v>
-      </c>
-      <c r="N13" t="s">
-        <v>216</v>
-      </c>
-      <c r="O13" t="s">
-        <v>217</v>
-      </c>
-      <c r="P13" t="s">
-        <v>210</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>218</v>
-      </c>
       <c r="R13" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S13" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T13" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6906,58 +6927,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F14" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G14" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H14" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="I14" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="J14" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" t="s">
+        <v>218</v>
+      </c>
+      <c r="M14" t="s">
+        <v>212</v>
+      </c>
+      <c r="N14" t="s">
+        <v>219</v>
+      </c>
+      <c r="O14" t="s">
+        <v>220</v>
+      </c>
+      <c r="P14" t="s">
         <v>213</v>
       </c>
-      <c r="K14" t="s">
-        <v>214</v>
-      </c>
-      <c r="L14" t="s">
-        <v>215</v>
-      </c>
-      <c r="M14" t="s">
-        <v>209</v>
-      </c>
-      <c r="N14" t="s">
-        <v>216</v>
-      </c>
-      <c r="O14" t="s">
-        <v>217</v>
-      </c>
-      <c r="P14" t="s">
-        <v>210</v>
-      </c>
       <c r="Q14" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R14" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S14" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T14" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6965,58 +6986,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>245</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>246</v>
+        <v>249</v>
       </c>
       <c r="E15" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F15" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="G15" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="H15" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="I15" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="J15" t="s">
+        <v>216</v>
+      </c>
+      <c r="K15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" t="s">
+        <v>218</v>
+      </c>
+      <c r="M15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N15" t="s">
+        <v>219</v>
+      </c>
+      <c r="O15" t="s">
+        <v>220</v>
+      </c>
+      <c r="P15" t="s">
         <v>213</v>
       </c>
-      <c r="K15" t="s">
-        <v>214</v>
-      </c>
-      <c r="L15" t="s">
-        <v>215</v>
-      </c>
-      <c r="M15" t="s">
-        <v>209</v>
-      </c>
-      <c r="N15" t="s">
-        <v>216</v>
-      </c>
-      <c r="O15" t="s">
-        <v>217</v>
-      </c>
-      <c r="P15" t="s">
-        <v>210</v>
-      </c>
       <c r="Q15" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R15" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S15" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T15" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7024,58 +7045,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F16" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I16" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" t="s">
+        <v>218</v>
+      </c>
+      <c r="M16" t="s">
+        <v>212</v>
+      </c>
+      <c r="N16" t="s">
+        <v>219</v>
+      </c>
+      <c r="O16" t="s">
         <v>220</v>
       </c>
-      <c r="G16" t="s">
-        <v>180</v>
-      </c>
-      <c r="H16" t="s">
-        <v>230</v>
-      </c>
-      <c r="I16" t="s">
-        <v>236</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="P16" t="s">
         <v>213</v>
       </c>
-      <c r="K16" t="s">
-        <v>214</v>
-      </c>
-      <c r="L16" t="s">
-        <v>215</v>
-      </c>
-      <c r="M16" t="s">
-        <v>209</v>
-      </c>
-      <c r="N16" t="s">
-        <v>216</v>
-      </c>
-      <c r="O16" t="s">
-        <v>217</v>
-      </c>
-      <c r="P16" t="s">
-        <v>210</v>
-      </c>
       <c r="Q16" t="s">
-        <v>218</v>
+        <v>221</v>
       </c>
       <c r="R16" t="s">
-        <v>219</v>
+        <v>222</v>
       </c>
       <c r="S16" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
       <c r="T16" t="s">
-        <v>221</v>
+        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -7104,16 +7125,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="E1" t="s">
-        <v>251</v>
+        <v>254</v>
       </c>
       <c r="F1" t="s">
-        <v>252</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7127,7 +7148,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7152,16 +7173,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>255</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>256</v>
+        <v>259</v>
       </c>
       <c r="F4" t="s">
-        <v>257</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7175,10 +7196,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>258</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>259</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7186,16 +7207,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>261</v>
+        <v>264</v>
       </c>
       <c r="F6" t="s">
-        <v>262</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7209,10 +7230,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>263</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>264</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7226,10 +7247,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>265</v>
+        <v>268</v>
       </c>
       <c r="F8" t="s">
-        <v>266</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7243,10 +7264,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>267</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>268</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7254,16 +7275,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>273</v>
       </c>
       <c r="E10" t="s">
-        <v>271</v>
+        <v>274</v>
       </c>
       <c r="F10" t="s">
-        <v>272</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7277,10 +7298,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>273</v>
+        <v>276</v>
       </c>
       <c r="F11" t="s">
-        <v>274</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7294,10 +7315,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>275</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -7330,34 +7351,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="E1" t="s">
-        <v>278</v>
+        <v>281</v>
       </c>
       <c r="G1" t="s">
-        <v>279</v>
+        <v>282</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>283</v>
       </c>
       <c r="I1" t="s">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="J1" t="s">
-        <v>282</v>
+        <v>285</v>
       </c>
       <c r="K1" t="s">
-        <v>283</v>
+        <v>286</v>
       </c>
       <c r="L1" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="M1" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="N1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7368,10 +7389,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7383,7 +7404,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7405,13 +7426,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7422,40 +7443,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="D4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="E4" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="F4" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="G4" t="s">
-        <v>295</v>
+        <v>298</v>
       </c>
       <c r="H4" t="s">
-        <v>296</v>
+        <v>299</v>
       </c>
       <c r="I4" t="s">
-        <v>297</v>
+        <v>300</v>
       </c>
       <c r="J4" t="s">
-        <v>298</v>
+        <v>301</v>
       </c>
       <c r="K4" t="s">
-        <v>299</v>
+        <v>302</v>
       </c>
       <c r="L4" t="s">
-        <v>300</v>
+        <v>303</v>
       </c>
       <c r="M4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="N4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7478,13 +7499,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L5" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M5" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7498,22 +7519,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L6" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M6" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7527,22 +7548,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L7" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M7" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7556,22 +7577,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L8" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M8" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7585,22 +7606,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M9" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7614,22 +7635,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L10" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M10" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7643,22 +7664,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L11" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="M11" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7672,22 +7693,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>304</v>
+        <v>307</v>
       </c>
       <c r="M12" t="s">
-        <v>303</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7695,31 +7716,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="G13" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H13" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>302</v>
+        <v>305</v>
       </c>
       <c r="L13" t="s">
-        <v>307</v>
+        <v>310</v>
       </c>
       <c r="M13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N13" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7727,10 +7748,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7739,7 +7760,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7747,10 +7768,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7759,7 +7780,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7767,10 +7788,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7779,7 +7800,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7787,19 +7808,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F17" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N17" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7807,10 +7828,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7819,7 +7840,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7827,10 +7848,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7839,7 +7860,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7847,10 +7868,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7859,7 +7880,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7867,19 +7888,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
       <c r="E21" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="F21" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="N21" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7887,16 +7908,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>305</v>
+        <v>308</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>306</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7904,10 +7925,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>337</v>
+        <v>340</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>338</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7921,10 +7942,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>339</v>
+        <v>342</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>340</v>
+        <v>343</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7938,10 +7959,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>341</v>
+        <v>344</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>342</v>
+        <v>345</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7955,10 +7976,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>343</v>
+        <v>346</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -7972,10 +7993,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>345</v>
+        <v>348</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>346</v>
+        <v>349</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -7989,10 +8010,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>347</v>
+        <v>350</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>348</v>
+        <v>351</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8006,10 +8027,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>349</v>
+        <v>352</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>350</v>
+        <v>353</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8018,10 +8039,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8029,10 +8050,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>351</v>
+        <v>354</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8046,10 +8067,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>353</v>
+        <v>356</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8063,10 +8084,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>355</v>
+        <v>358</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>356</v>
+        <v>359</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8075,10 +8096,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
   </sheetData>
@@ -8114,31 +8135,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>357</v>
+        <v>360</v>
       </c>
       <c r="D1" t="s">
-        <v>358</v>
+        <v>361</v>
       </c>
       <c r="E1" t="s">
-        <v>359</v>
+        <v>362</v>
       </c>
       <c r="F1" t="s">
-        <v>360</v>
+        <v>363</v>
       </c>
       <c r="G1" t="s">
-        <v>361</v>
+        <v>364</v>
       </c>
       <c r="H1" t="s">
-        <v>277</v>
+        <v>280</v>
       </c>
       <c r="I1" t="s">
-        <v>362</v>
+        <v>365</v>
       </c>
       <c r="J1" t="s">
-        <v>363</v>
+        <v>366</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8164,10 +8185,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="I2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8181,34 +8202,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>364</v>
+        <v>367</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>365</v>
+        <v>368</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>366</v>
+        <v>369</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>367</v>
+        <v>370</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>368</v>
+        <v>371</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>369</v>
+        <v>372</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>370</v>
+        <v>373</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>371</v>
+        <v>374</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>372</v>
+        <v>375</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8219,31 +8240,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>373</v>
+        <v>376</v>
       </c>
       <c r="D4" t="s">
-        <v>374</v>
+        <v>377</v>
       </c>
       <c r="E4" t="s">
-        <v>375</v>
+        <v>378</v>
       </c>
       <c r="F4" t="s">
-        <v>376</v>
+        <v>379</v>
       </c>
       <c r="G4" t="s">
-        <v>377</v>
+        <v>380</v>
       </c>
       <c r="H4" t="s">
-        <v>378</v>
+        <v>381</v>
       </c>
       <c r="I4" t="s">
-        <v>379</v>
+        <v>382</v>
       </c>
       <c r="J4" t="s">
-        <v>380</v>
+        <v>383</v>
       </c>
       <c r="K4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8251,7 +8272,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>381</v>
+        <v>384</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8275,7 +8296,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>382</v>
+        <v>385</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8283,7 +8304,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>383</v>
+        <v>386</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8307,7 +8328,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8315,7 +8336,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>385</v>
+        <v>388</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8339,7 +8360,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8347,7 +8368,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>386</v>
+        <v>389</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8371,7 +8392,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
     </row>
   </sheetData>
@@ -8402,16 +8423,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>387</v>
+        <v>390</v>
       </c>
       <c r="E1" t="s">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="F1" t="s">
-        <v>389</v>
+        <v>392</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8428,7 +8449,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8441,10 +8462,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>391</v>
+        <v>394</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8455,13 +8476,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>392</v>
+        <v>395</v>
       </c>
       <c r="D4" t="s">
-        <v>393</v>
+        <v>396</v>
       </c>
       <c r="E4" t="s">
-        <v>394</v>
+        <v>397</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8469,7 +8490,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>395</v>
+        <v>398</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8478,7 +8499,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>396</v>
+        <v>399</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8486,7 +8507,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8495,7 +8516,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>398</v>
+        <v>401</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8503,7 +8524,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>399</v>
+        <v>402</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8512,7 +8533,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>400</v>
+        <v>403</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8520,7 +8541,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>404</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8529,7 +8550,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>402</v>
+        <v>405</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8567,40 +8588,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>403</v>
+        <v>406</v>
       </c>
       <c r="C1" t="s">
-        <v>404</v>
+        <v>407</v>
       </c>
       <c r="D1" t="s">
-        <v>405</v>
+        <v>408</v>
       </c>
       <c r="E1" t="s">
-        <v>406</v>
+        <v>409</v>
       </c>
       <c r="F1" t="s">
-        <v>407</v>
+        <v>410</v>
       </c>
       <c r="G1" t="s">
-        <v>408</v>
+        <v>411</v>
       </c>
       <c r="H1" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
-        <v>409</v>
+        <v>412</v>
       </c>
       <c r="J1" t="s">
-        <v>410</v>
+        <v>413</v>
       </c>
       <c r="K1" t="s">
-        <v>411</v>
+        <v>414</v>
       </c>
       <c r="L1" t="s">
-        <v>412</v>
+        <v>415</v>
       </c>
       <c r="M1" t="s">
-        <v>413</v>
+        <v>416</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8614,16 +8635,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>414</v>
+        <v>417</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>415</v>
+        <v>418</v>
       </c>
       <c r="G2" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8649,40 +8670,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>416</v>
+        <v>419</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>417</v>
+        <v>420</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>418</v>
+        <v>421</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>419</v>
+        <v>422</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>420</v>
+        <v>423</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>421</v>
+        <v>424</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>422</v>
+        <v>425</v>
       </c>
       <c r="I3" t="s">
-        <v>423</v>
+        <v>426</v>
       </c>
       <c r="J3" t="s">
-        <v>424</v>
+        <v>427</v>
       </c>
       <c r="K3" t="s">
-        <v>425</v>
+        <v>428</v>
       </c>
       <c r="L3" t="s">
-        <v>426</v>
+        <v>429</v>
       </c>
       <c r="M3" t="s">
-        <v>427</v>
+        <v>430</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8690,54 +8711,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>428</v>
+        <v>431</v>
       </c>
       <c r="C4" t="s">
-        <v>429</v>
+        <v>432</v>
       </c>
       <c r="D4" t="s">
-        <v>430</v>
+        <v>433</v>
       </c>
       <c r="E4" t="s">
-        <v>431</v>
+        <v>434</v>
       </c>
       <c r="F4" t="s">
-        <v>432</v>
+        <v>435</v>
       </c>
       <c r="G4" t="s">
-        <v>433</v>
+        <v>436</v>
       </c>
       <c r="H4" t="s">
-        <v>301</v>
+        <v>304</v>
       </c>
       <c r="I4" t="s">
-        <v>434</v>
+        <v>437</v>
       </c>
       <c r="J4" t="s">
-        <v>435</v>
+        <v>438</v>
       </c>
       <c r="K4" t="s">
-        <v>436</v>
+        <v>439</v>
       </c>
       <c r="L4" t="s">
-        <v>437</v>
+        <v>440</v>
       </c>
       <c r="M4" t="s">
-        <v>438</v>
+        <v>441</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="D5" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8749,36 +8770,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="I5" t="s">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="J5" t="s">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="K5" t="s">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="L5" t="s">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="M5" t="s">
-        <v>446</v>
+        <v>449</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="D6" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8790,36 +8811,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="I6" t="s">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="J6" t="s">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="K6" t="s">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L6" t="s">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M6" t="s">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="D7" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8831,36 +8852,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="I7" t="s">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="J7" t="s">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="K7" t="s">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="L7" t="s">
-        <v>459</v>
+        <v>462</v>
       </c>
       <c r="M7" t="s">
-        <v>460</v>
+        <v>463</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>461</v>
+        <v>464</v>
       </c>
       <c r="D8" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8872,36 +8893,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="I8" t="s">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="J8" t="s">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="K8" t="s">
-        <v>465</v>
+        <v>468</v>
       </c>
       <c r="L8" t="s">
-        <v>466</v>
+        <v>469</v>
       </c>
       <c r="M8" t="s">
-        <v>467</v>
+        <v>470</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="D9" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8913,36 +8934,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="I9" t="s">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="J9" t="s">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="K9" t="s">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="L9" t="s">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="M9" t="s">
-        <v>474</v>
+        <v>477</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="D10" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8954,36 +8975,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="I10" t="s">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="J10" t="s">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="K10" t="s">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="L10" t="s">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="M10" t="s">
-        <v>481</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="D11" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -8995,36 +9016,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="I11" t="s">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="J11" t="s">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="K11" t="s">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="L11" t="s">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="M11" t="s">
-        <v>488</v>
+        <v>491</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>489</v>
+        <v>492</v>
       </c>
       <c r="D12" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9036,36 +9057,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>490</v>
+        <v>493</v>
       </c>
       <c r="I12" t="s">
-        <v>491</v>
+        <v>494</v>
       </c>
       <c r="J12" t="s">
-        <v>492</v>
+        <v>495</v>
       </c>
       <c r="K12" t="s">
-        <v>493</v>
+        <v>496</v>
       </c>
       <c r="L12" t="s">
-        <v>494</v>
+        <v>497</v>
       </c>
       <c r="M12" t="s">
-        <v>495</v>
+        <v>498</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>496</v>
+        <v>499</v>
       </c>
       <c r="D13" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9077,36 +9098,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>497</v>
+        <v>500</v>
       </c>
       <c r="I13" t="s">
-        <v>498</v>
+        <v>501</v>
       </c>
       <c r="J13" t="s">
-        <v>499</v>
+        <v>502</v>
       </c>
       <c r="K13" t="s">
-        <v>500</v>
+        <v>503</v>
       </c>
       <c r="L13" t="s">
-        <v>501</v>
+        <v>504</v>
       </c>
       <c r="M13" t="s">
-        <v>502</v>
+        <v>505</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>503</v>
+        <v>506</v>
       </c>
       <c r="D14" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9118,36 +9139,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>504</v>
+        <v>507</v>
       </c>
       <c r="I14" t="s">
-        <v>505</v>
+        <v>508</v>
       </c>
       <c r="J14" t="s">
-        <v>506</v>
+        <v>509</v>
       </c>
       <c r="K14" t="s">
-        <v>507</v>
+        <v>510</v>
       </c>
       <c r="L14" t="s">
-        <v>508</v>
+        <v>511</v>
       </c>
       <c r="M14" t="s">
-        <v>509</v>
+        <v>512</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>510</v>
+        <v>513</v>
       </c>
       <c r="D15" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9159,39 +9180,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>511</v>
+        <v>514</v>
       </c>
       <c r="I15" t="s">
-        <v>512</v>
+        <v>515</v>
       </c>
       <c r="J15" t="s">
-        <v>513</v>
+        <v>516</v>
       </c>
       <c r="K15" t="s">
-        <v>514</v>
+        <v>517</v>
       </c>
       <c r="L15" t="s">
-        <v>515</v>
+        <v>518</v>
       </c>
       <c r="M15" t="s">
-        <v>516</v>
+        <v>519</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>517</v>
+        <v>520</v>
       </c>
       <c r="D16" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E16" t="s">
-        <v>519</v>
+        <v>522</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9200,39 +9221,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>520</v>
+        <v>523</v>
       </c>
       <c r="I16" t="s">
-        <v>521</v>
+        <v>524</v>
       </c>
       <c r="J16" t="s">
-        <v>522</v>
+        <v>525</v>
       </c>
       <c r="K16" t="s">
-        <v>523</v>
+        <v>526</v>
       </c>
       <c r="L16" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="M16" t="s">
-        <v>525</v>
+        <v>528</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>526</v>
+        <v>529</v>
       </c>
       <c r="D17" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E17" t="s">
-        <v>527</v>
+        <v>530</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9241,39 +9262,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>528</v>
+        <v>531</v>
       </c>
       <c r="I17" t="s">
-        <v>529</v>
+        <v>532</v>
       </c>
       <c r="J17" t="s">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="K17" t="s">
-        <v>531</v>
+        <v>534</v>
       </c>
       <c r="L17" t="s">
-        <v>532</v>
+        <v>535</v>
       </c>
       <c r="M17" t="s">
-        <v>533</v>
+        <v>536</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>534</v>
+        <v>537</v>
       </c>
       <c r="D18" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E18" t="s">
-        <v>535</v>
+        <v>538</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9282,39 +9303,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>536</v>
+        <v>539</v>
       </c>
       <c r="I18" t="s">
-        <v>537</v>
+        <v>540</v>
       </c>
       <c r="J18" t="s">
-        <v>538</v>
+        <v>541</v>
       </c>
       <c r="K18" t="s">
-        <v>539</v>
+        <v>542</v>
       </c>
       <c r="L18" t="s">
-        <v>540</v>
+        <v>543</v>
       </c>
       <c r="M18" t="s">
-        <v>541</v>
+        <v>544</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>542</v>
+        <v>545</v>
       </c>
       <c r="D19" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E19" t="s">
-        <v>543</v>
+        <v>546</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9323,39 +9344,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>544</v>
+        <v>547</v>
       </c>
       <c r="I19" t="s">
-        <v>545</v>
+        <v>548</v>
       </c>
       <c r="J19" t="s">
-        <v>546</v>
+        <v>549</v>
       </c>
       <c r="K19" t="s">
-        <v>547</v>
+        <v>550</v>
       </c>
       <c r="L19" t="s">
-        <v>548</v>
+        <v>551</v>
       </c>
       <c r="M19" t="s">
-        <v>549</v>
+        <v>552</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>550</v>
+        <v>553</v>
       </c>
       <c r="D20" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E20" t="s">
-        <v>551</v>
+        <v>554</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9364,39 +9385,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>552</v>
+        <v>555</v>
       </c>
       <c r="I20" t="s">
-        <v>553</v>
+        <v>556</v>
       </c>
       <c r="J20" t="s">
-        <v>554</v>
+        <v>557</v>
       </c>
       <c r="K20" t="s">
-        <v>555</v>
+        <v>558</v>
       </c>
       <c r="L20" t="s">
-        <v>556</v>
+        <v>559</v>
       </c>
       <c r="M20" t="s">
-        <v>557</v>
+        <v>560</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>558</v>
+        <v>561</v>
       </c>
       <c r="D21" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E21" t="s">
-        <v>559</v>
+        <v>562</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9405,39 +9426,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>560</v>
+        <v>563</v>
       </c>
       <c r="I21" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="J21" t="s">
-        <v>562</v>
+        <v>565</v>
       </c>
       <c r="K21" t="s">
-        <v>563</v>
+        <v>566</v>
       </c>
       <c r="L21" t="s">
-        <v>564</v>
+        <v>567</v>
       </c>
       <c r="M21" t="s">
-        <v>565</v>
+        <v>568</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>566</v>
+        <v>569</v>
       </c>
       <c r="D22" t="s">
-        <v>518</v>
+        <v>521</v>
       </c>
       <c r="E22" t="s">
-        <v>567</v>
+        <v>570</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9446,39 +9467,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>568</v>
+        <v>571</v>
       </c>
       <c r="I22" t="s">
-        <v>569</v>
+        <v>572</v>
       </c>
       <c r="J22" t="s">
-        <v>570</v>
+        <v>573</v>
       </c>
       <c r="K22" t="s">
-        <v>571</v>
+        <v>574</v>
       </c>
       <c r="L22" t="s">
-        <v>572</v>
+        <v>575</v>
       </c>
       <c r="M22" t="s">
-        <v>573</v>
+        <v>576</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>574</v>
+        <v>577</v>
       </c>
       <c r="D23" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E23" t="s">
-        <v>576</v>
+        <v>579</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9487,39 +9508,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>577</v>
+        <v>580</v>
       </c>
       <c r="I23" t="s">
-        <v>578</v>
+        <v>581</v>
       </c>
       <c r="J23" t="s">
-        <v>579</v>
+        <v>582</v>
       </c>
       <c r="K23" t="s">
-        <v>580</v>
+        <v>583</v>
       </c>
       <c r="L23" t="s">
-        <v>581</v>
+        <v>584</v>
       </c>
       <c r="M23" t="s">
-        <v>582</v>
+        <v>585</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>583</v>
+        <v>586</v>
       </c>
       <c r="D24" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E24" t="s">
-        <v>584</v>
+        <v>587</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9528,39 +9549,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>585</v>
+        <v>588</v>
       </c>
       <c r="I24" t="s">
-        <v>586</v>
+        <v>589</v>
       </c>
       <c r="J24" t="s">
-        <v>587</v>
+        <v>590</v>
       </c>
       <c r="K24" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="L24" t="s">
-        <v>589</v>
+        <v>592</v>
       </c>
       <c r="M24" t="s">
-        <v>590</v>
+        <v>593</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>591</v>
+        <v>594</v>
       </c>
       <c r="D25" t="s">
-        <v>575</v>
+        <v>578</v>
       </c>
       <c r="E25" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9569,22 +9590,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="K25" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="L25" t="s">
-        <v>596</v>
+        <v>599</v>
       </c>
       <c r="M25" t="s">
-        <v>597</v>
+        <v>600</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9592,10 +9613,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>598</v>
+        <v>601</v>
       </c>
       <c r="D26" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9607,22 +9628,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>600</v>
+        <v>603</v>
       </c>
       <c r="I26" t="s">
-        <v>601</v>
+        <v>604</v>
       </c>
       <c r="J26" t="s">
-        <v>602</v>
+        <v>605</v>
       </c>
       <c r="K26" t="s">
-        <v>603</v>
+        <v>606</v>
       </c>
       <c r="L26" t="s">
-        <v>604</v>
+        <v>607</v>
       </c>
       <c r="M26" t="s">
-        <v>605</v>
+        <v>608</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9630,13 +9651,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>606</v>
+        <v>609</v>
       </c>
       <c r="D27" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E27" t="s">
-        <v>607</v>
+        <v>610</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9645,36 +9666,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>608</v>
+        <v>611</v>
       </c>
       <c r="I27" t="s">
-        <v>609</v>
+        <v>612</v>
       </c>
       <c r="J27" t="s">
-        <v>610</v>
+        <v>613</v>
       </c>
       <c r="K27" t="s">
-        <v>611</v>
+        <v>614</v>
       </c>
       <c r="L27" t="s">
-        <v>612</v>
+        <v>615</v>
       </c>
       <c r="M27" t="s">
-        <v>613</v>
+        <v>616</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>614</v>
+        <v>617</v>
       </c>
       <c r="D28" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9686,36 +9707,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>615</v>
+        <v>618</v>
       </c>
       <c r="I28" t="s">
-        <v>616</v>
+        <v>619</v>
       </c>
       <c r="J28" t="s">
-        <v>617</v>
+        <v>620</v>
       </c>
       <c r="K28" t="s">
-        <v>618</v>
+        <v>621</v>
       </c>
       <c r="L28" t="s">
-        <v>619</v>
+        <v>622</v>
       </c>
       <c r="M28" t="s">
-        <v>620</v>
+        <v>623</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>621</v>
+        <v>624</v>
       </c>
       <c r="D29" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9727,36 +9748,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>622</v>
+        <v>625</v>
       </c>
       <c r="I29" t="s">
-        <v>623</v>
+        <v>626</v>
       </c>
       <c r="J29" t="s">
-        <v>624</v>
+        <v>627</v>
       </c>
       <c r="K29" t="s">
-        <v>625</v>
+        <v>628</v>
       </c>
       <c r="L29" t="s">
-        <v>626</v>
+        <v>629</v>
       </c>
       <c r="M29" t="s">
-        <v>627</v>
+        <v>630</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>628</v>
+        <v>631</v>
       </c>
       <c r="D30" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9768,39 +9789,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>629</v>
+        <v>632</v>
       </c>
       <c r="I30" t="s">
-        <v>630</v>
+        <v>633</v>
       </c>
       <c r="J30" t="s">
-        <v>631</v>
+        <v>634</v>
       </c>
       <c r="K30" t="s">
-        <v>632</v>
+        <v>635</v>
       </c>
       <c r="L30" t="s">
-        <v>633</v>
+        <v>636</v>
       </c>
       <c r="M30" t="s">
-        <v>634</v>
+        <v>637</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>384</v>
+        <v>387</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>635</v>
+        <v>638</v>
       </c>
       <c r="D31" t="s">
-        <v>599</v>
+        <v>602</v>
       </c>
       <c r="E31" t="s">
-        <v>269</v>
+        <v>272</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9809,22 +9830,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>636</v>
+        <v>639</v>
       </c>
       <c r="I31" t="s">
-        <v>637</v>
+        <v>640</v>
       </c>
       <c r="J31" t="s">
-        <v>638</v>
+        <v>641</v>
       </c>
       <c r="K31" t="s">
-        <v>639</v>
+        <v>642</v>
       </c>
       <c r="L31" t="s">
-        <v>640</v>
+        <v>643</v>
       </c>
       <c r="M31" t="s">
-        <v>641</v>
+        <v>644</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9832,13 +9853,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>642</v>
+        <v>645</v>
       </c>
       <c r="D32" t="s">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="E32" t="s">
-        <v>643</v>
+        <v>646</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9847,22 +9868,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>644</v>
+        <v>647</v>
       </c>
       <c r="I32" t="s">
-        <v>645</v>
+        <v>648</v>
       </c>
       <c r="J32" t="s">
-        <v>646</v>
+        <v>649</v>
       </c>
       <c r="K32" t="s">
-        <v>647</v>
+        <v>650</v>
       </c>
       <c r="L32" t="s">
-        <v>648</v>
+        <v>651</v>
       </c>
       <c r="M32" t="s">
-        <v>649</v>
+        <v>652</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="8"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -536,22 +536,13 @@
     <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
   </si>
   <si>
-    <t>BlindBoxBacklogClaimDelaySeconds</t>
-  </si>
-  <si>
-    <t>积压盲盒展示时短间隔时间</t>
-  </si>
-  <si>
-    <t>秒，实际使用时需要受到BlindBoxTimeScale影响，为了不让玩家对于盲盒间隔的心里预期剧烈变化因此设计了该值</t>
-  </si>
-  <si>
-    <t>BlindBoxPostNewbieDelaySeconds</t>
-  </si>
-  <si>
-    <t>新手与正式盲盒的间隔时间</t>
-  </si>
-  <si>
-    <t>秒，新手阶段结束后与第一个正式盲盒的间隔时间</t>
+    <t>BlindBoxLoopIntervalSeconds</t>
+  </si>
+  <si>
+    <t>正常阶段盲盒展示间隔</t>
+  </si>
+  <si>
+    <t>秒；第 12 个新手奖励入账后，按此基础间隔产生展示点并触发循环 Steam 掉落检查；实际时长受 BlindBoxWaitDurationMultiplier 影响</t>
   </si>
   <si>
     <t>LinkTreeVisibleBannerCount</t>
@@ -560,7 +551,16 @@
     <t>LinkTree最佳显示条目数量</t>
   </si>
   <si>
-    <t>未领取奖励的条目和固定条目数量之和不足该值只，以已领取奖励的条目填充占位</t>
+    <t>未领取奖励的条目和固定条目数量之和不足该值时，以已领取奖励的条目填充占位</t>
+  </si>
+  <si>
+    <t>SteamPlaytimeDropLeadSeconds</t>
+  </si>
+  <si>
+    <t>Steam提前准备盲盒的秒数</t>
+  </si>
+  <si>
+    <t>仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
   </si>
   <si>
     <t>IconName</t>
@@ -6060,7 +6060,7 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="E3" s="5" t="s">
         <v>159</v>
@@ -6111,7 +6111,7 @@
         <v>158</v>
       </c>
       <c r="D6" s="2">
-        <v>30</v>
+        <v>90</v>
       </c>
       <c r="E6" s="2" t="s">
         <v>168</v>
@@ -6125,10 +6125,10 @@
         <v>170</v>
       </c>
       <c r="C7" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="D7" s="2">
-        <v>60</v>
+        <v>5</v>
       </c>
       <c r="E7" t="s">
         <v>171</v>
@@ -6145,7 +6145,7 @@
         <v>107</v>
       </c>
       <c r="D8" s="2">
-        <v>5</v>
+        <v>60</v>
       </c>
       <c r="E8" s="2" t="s">
         <v>174</v>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1487" uniqueCount="862">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="874">
   <si>
     <t>Dog</t>
   </si>
@@ -560,7 +560,34 @@
     <t>Steam提前准备盲盒的秒数</t>
   </si>
   <si>
-    <t>仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
+    <t>秒；仅供转换器使用，仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
+  </si>
+  <si>
+    <t>SteamPlaytimeRequestLeadSeconds</t>
+  </si>
+  <si>
+    <t>Steam掉落请求提前秒数</t>
+  </si>
+  <si>
+    <t>仅供客户端使用。在本地展示前多久开始调用 TriggerItemDrop。</t>
+  </si>
+  <si>
+    <t>BlindBoxLoopSteamVoucherInventoryLimit</t>
+  </si>
+  <si>
+    <t>循环Steam盲盒券库存上限</t>
+  </si>
+  <si>
+    <t>正常循环阶段允许玩家在 Steam 库存中累计的盲盒成本券数量上限。客户端统计对应 ItemDef 的所有实例及堆叠数量；达到上限时暂停调用循环 PlaytimeGenerator，消耗后低于上限时恢复请求。填 0 表示不限制。</t>
+  </si>
+  <si>
+    <t>ProactiveInteractionHintIdleSeconds</t>
+  </si>
+  <si>
+    <t>新手操作提示等待时间</t>
+  </si>
+  <si>
+    <t>秒；当玩家在规定时间内无正确操作时，需要操作的目标会作出相应的提示动作</t>
   </si>
   <si>
     <t>IconName</t>
@@ -1116,6 +1143,15 @@
   </si>
   <si>
     <t>看到皇家同花顺</t>
+  </si>
+  <si>
+    <t>RefuseRefreshment</t>
+  </si>
+  <si>
+    <t>劝玩家别喝了</t>
+  </si>
+  <si>
+    <t>当有Buff持续中时，玩家又在背包中点击了Refreshment，则狗狗作出该表情动作</t>
   </si>
   <si>
     <t>StateName</t>
@@ -2634,7 +2670,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="21">
+  <fonts count="22">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -2644,6 +2680,13 @@
     <font>
       <sz val="12"/>
       <color rgb="FF1C1E21"/>
+      <name val="微软雅黑"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
@@ -3112,16 +3155,13 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -3130,119 +3170,122 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="9">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -3263,6 +3306,12 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -4197,28 +4246,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>653</v>
+        <v>665</v>
       </c>
       <c r="C1" t="s">
-        <v>654</v>
+        <v>666</v>
       </c>
       <c r="D1" t="s">
-        <v>655</v>
+        <v>667</v>
       </c>
       <c r="E1" t="s">
-        <v>656</v>
+        <v>668</v>
       </c>
       <c r="F1" t="s">
-        <v>657</v>
+        <v>669</v>
       </c>
       <c r="G1" t="s">
-        <v>658</v>
+        <v>670</v>
       </c>
       <c r="H1" t="s">
-        <v>659</v>
+        <v>671</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4235,16 +4284,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>660</v>
+        <v>672</v>
       </c>
       <c r="F2" t="s">
-        <v>661</v>
+        <v>673</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4255,28 +4304,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>662</v>
+        <v>674</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>663</v>
+        <v>675</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>664</v>
+        <v>676</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>665</v>
+        <v>677</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>666</v>
+        <v>678</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>667</v>
+        <v>679</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>668</v>
+        <v>680</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>669</v>
+        <v>681</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4284,1333 +4333,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>670</v>
+        <v>682</v>
       </c>
       <c r="C4" t="s">
-        <v>671</v>
+        <v>683</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="E4" t="s">
-        <v>672</v>
+        <v>684</v>
       </c>
       <c r="F4" t="s">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="G4" t="s">
-        <v>674</v>
+        <v>686</v>
       </c>
       <c r="H4" t="s">
-        <v>675</v>
+        <v>687</v>
       </c>
       <c r="I4" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>676</v>
+        <v>688</v>
       </c>
       <c r="D5" t="s">
-        <v>677</v>
+        <v>689</v>
       </c>
       <c r="E5" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="F5" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G5" t="s">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>681</v>
+        <v>693</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>682</v>
+        <v>694</v>
       </c>
       <c r="D6" t="s">
-        <v>683</v>
+        <v>695</v>
       </c>
       <c r="E6" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F6" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G6" t="s">
-        <v>685</v>
+        <v>697</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>686</v>
+        <v>698</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>687</v>
+        <v>699</v>
       </c>
       <c r="D7" t="s">
-        <v>688</v>
+        <v>700</v>
       </c>
       <c r="E7" t="s">
-        <v>678</v>
+        <v>690</v>
       </c>
       <c r="F7" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G7" t="s">
-        <v>689</v>
+        <v>701</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>690</v>
+        <v>702</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
+        <v>703</v>
+      </c>
+      <c r="D8" t="s">
+        <v>704</v>
+      </c>
+      <c r="E8" t="s">
+        <v>690</v>
+      </c>
+      <c r="F8" t="s">
         <v>691</v>
       </c>
-      <c r="D8" t="s">
-        <v>692</v>
-      </c>
-      <c r="E8" t="s">
-        <v>678</v>
-      </c>
-      <c r="F8" t="s">
-        <v>679</v>
-      </c>
       <c r="G8" t="s">
-        <v>693</v>
+        <v>705</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>694</v>
+        <v>706</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>695</v>
+        <v>707</v>
       </c>
       <c r="D9" t="s">
+        <v>708</v>
+      </c>
+      <c r="E9" t="s">
         <v>696</v>
       </c>
-      <c r="E9" t="s">
-        <v>684</v>
-      </c>
       <c r="F9" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G9" t="s">
-        <v>697</v>
+        <v>709</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>698</v>
+        <v>710</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>699</v>
+        <v>711</v>
       </c>
       <c r="D10" t="s">
-        <v>700</v>
+        <v>712</v>
       </c>
       <c r="E10" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F10" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G10" t="s">
-        <v>702</v>
+        <v>714</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>703</v>
+        <v>715</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>704</v>
+        <v>716</v>
       </c>
       <c r="D11" t="s">
-        <v>705</v>
+        <v>717</v>
       </c>
       <c r="E11" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F11" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G11" t="s">
-        <v>706</v>
+        <v>718</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>707</v>
+        <v>719</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>708</v>
+        <v>720</v>
       </c>
       <c r="D12" t="s">
-        <v>709</v>
+        <v>721</v>
       </c>
       <c r="E12" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F12" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G12" t="s">
-        <v>710</v>
+        <v>722</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>711</v>
+        <v>723</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>712</v>
+        <v>724</v>
       </c>
       <c r="D13" t="s">
-        <v>713</v>
+        <v>725</v>
       </c>
       <c r="E13" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F13" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G13" t="s">
-        <v>714</v>
+        <v>726</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>715</v>
+        <v>727</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>716</v>
+        <v>728</v>
       </c>
       <c r="D14" t="s">
-        <v>717</v>
+        <v>729</v>
       </c>
       <c r="E14" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F14" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G14" t="s">
-        <v>718</v>
+        <v>730</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>719</v>
+        <v>731</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>720</v>
+        <v>732</v>
       </c>
       <c r="D15" t="s">
-        <v>721</v>
+        <v>733</v>
       </c>
       <c r="E15" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F15" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G15" t="s">
-        <v>722</v>
+        <v>734</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>723</v>
+        <v>735</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>724</v>
+        <v>736</v>
       </c>
       <c r="D16" t="s">
-        <v>725</v>
+        <v>737</v>
       </c>
       <c r="E16" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F16" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G16" t="s">
-        <v>726</v>
+        <v>738</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>727</v>
+        <v>739</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>728</v>
+        <v>740</v>
       </c>
       <c r="D17" t="s">
-        <v>729</v>
+        <v>741</v>
       </c>
       <c r="E17" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F17" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G17" t="s">
-        <v>730</v>
+        <v>742</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>731</v>
+        <v>743</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>732</v>
+        <v>744</v>
       </c>
       <c r="D18" t="s">
-        <v>733</v>
+        <v>745</v>
       </c>
       <c r="E18" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F18" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G18" t="s">
-        <v>734</v>
+        <v>746</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>735</v>
+        <v>747</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="D19" t="s">
-        <v>736</v>
+        <v>748</v>
       </c>
       <c r="E19" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F19" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G19" t="s">
-        <v>737</v>
+        <v>749</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>738</v>
+        <v>750</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="D20" t="s">
-        <v>739</v>
+        <v>751</v>
       </c>
       <c r="E20" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F20" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G20" t="s">
-        <v>740</v>
+        <v>752</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>741</v>
+        <v>753</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="D21" t="s">
-        <v>742</v>
+        <v>754</v>
       </c>
       <c r="E21" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F21" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G21" t="s">
-        <v>743</v>
+        <v>755</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>744</v>
+        <v>756</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="D22" t="s">
-        <v>745</v>
+        <v>757</v>
       </c>
       <c r="E22" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F22" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G22" t="s">
-        <v>746</v>
+        <v>758</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>747</v>
+        <v>759</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="D23" t="s">
-        <v>748</v>
+        <v>760</v>
       </c>
       <c r="E23" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F23" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G23" t="s">
-        <v>749</v>
+        <v>761</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>750</v>
+        <v>762</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="D24" t="s">
-        <v>751</v>
+        <v>763</v>
       </c>
       <c r="E24" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F24" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G24" t="s">
-        <v>752</v>
+        <v>764</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>753</v>
+        <v>765</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="D25" t="s">
-        <v>754</v>
+        <v>766</v>
       </c>
       <c r="E25" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F25" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G25" t="s">
-        <v>755</v>
+        <v>767</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>756</v>
+        <v>768</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>757</v>
+        <v>769</v>
       </c>
       <c r="D26" t="s">
-        <v>758</v>
+        <v>770</v>
       </c>
       <c r="E26" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F26" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G26" t="s">
-        <v>759</v>
+        <v>771</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>760</v>
+        <v>772</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>761</v>
+        <v>773</v>
       </c>
       <c r="D27" t="s">
-        <v>762</v>
+        <v>774</v>
       </c>
       <c r="E27" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F27" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G27" t="s">
-        <v>763</v>
+        <v>775</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>764</v>
+        <v>776</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>765</v>
+        <v>777</v>
       </c>
       <c r="D28" t="s">
-        <v>766</v>
+        <v>778</v>
       </c>
       <c r="E28" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F28" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G28" t="s">
-        <v>767</v>
+        <v>779</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>768</v>
+        <v>780</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>769</v>
+        <v>781</v>
       </c>
       <c r="D29" t="s">
-        <v>770</v>
+        <v>782</v>
       </c>
       <c r="E29" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F29" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G29" t="s">
-        <v>771</v>
+        <v>783</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>772</v>
+        <v>784</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>773</v>
+        <v>785</v>
       </c>
       <c r="D30" t="s">
-        <v>774</v>
+        <v>786</v>
       </c>
       <c r="E30" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F30" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G30" t="s">
-        <v>775</v>
+        <v>787</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>776</v>
+        <v>788</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>777</v>
+        <v>789</v>
       </c>
       <c r="D31" t="s">
-        <v>778</v>
+        <v>790</v>
       </c>
       <c r="E31" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F31" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G31" t="s">
-        <v>779</v>
+        <v>791</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>780</v>
+        <v>792</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>781</v>
+        <v>793</v>
       </c>
       <c r="D32" t="s">
-        <v>782</v>
+        <v>794</v>
       </c>
       <c r="E32" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F32" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G32" t="s">
-        <v>783</v>
+        <v>795</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>784</v>
+        <v>796</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>785</v>
+        <v>797</v>
       </c>
       <c r="D33" t="s">
-        <v>786</v>
+        <v>798</v>
       </c>
       <c r="E33" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F33" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G33" t="s">
-        <v>787</v>
+        <v>799</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>788</v>
+        <v>800</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>789</v>
+        <v>801</v>
       </c>
       <c r="D34" t="s">
-        <v>790</v>
+        <v>802</v>
       </c>
       <c r="E34" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F34" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G34" t="s">
-        <v>791</v>
+        <v>803</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>792</v>
+        <v>804</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>793</v>
+        <v>805</v>
       </c>
       <c r="D35" t="s">
-        <v>794</v>
+        <v>806</v>
       </c>
       <c r="E35" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F35" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G35" t="s">
-        <v>795</v>
+        <v>807</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>796</v>
+        <v>808</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>797</v>
+        <v>809</v>
       </c>
       <c r="D36" t="s">
-        <v>798</v>
+        <v>810</v>
       </c>
       <c r="E36" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F36" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G36" t="s">
-        <v>799</v>
+        <v>811</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>800</v>
+        <v>812</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>801</v>
+        <v>813</v>
       </c>
       <c r="D37" t="s">
-        <v>802</v>
+        <v>814</v>
       </c>
       <c r="E37" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F37" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G37" t="s">
-        <v>803</v>
+        <v>815</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>804</v>
+        <v>816</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>805</v>
+        <v>817</v>
       </c>
       <c r="D38" t="s">
-        <v>806</v>
+        <v>818</v>
       </c>
       <c r="E38" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F38" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G38" t="s">
-        <v>807</v>
+        <v>819</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>808</v>
+        <v>820</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>809</v>
+        <v>821</v>
       </c>
       <c r="D39" t="s">
-        <v>810</v>
+        <v>822</v>
       </c>
       <c r="E39" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F39" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G39" t="s">
-        <v>811</v>
+        <v>823</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>812</v>
+        <v>824</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>813</v>
+        <v>825</v>
       </c>
       <c r="D40" t="s">
-        <v>814</v>
+        <v>826</v>
       </c>
       <c r="E40" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F40" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G40" t="s">
-        <v>815</v>
+        <v>827</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>816</v>
+        <v>828</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>817</v>
+        <v>829</v>
       </c>
       <c r="D41" t="s">
-        <v>818</v>
+        <v>830</v>
       </c>
       <c r="E41" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F41" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G41" t="s">
-        <v>819</v>
+        <v>831</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>820</v>
+        <v>832</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>821</v>
+        <v>833</v>
       </c>
       <c r="D42" t="s">
-        <v>822</v>
+        <v>834</v>
       </c>
       <c r="E42" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F42" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G42" t="s">
-        <v>823</v>
+        <v>835</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>824</v>
+        <v>836</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>825</v>
+        <v>837</v>
       </c>
       <c r="D43" t="s">
-        <v>826</v>
+        <v>838</v>
       </c>
       <c r="E43" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F43" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G43" t="s">
-        <v>827</v>
+        <v>839</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>828</v>
+        <v>840</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>829</v>
+        <v>841</v>
       </c>
       <c r="D44" t="s">
-        <v>830</v>
+        <v>842</v>
       </c>
       <c r="E44" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F44" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G44" t="s">
-        <v>831</v>
+        <v>843</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>832</v>
+        <v>844</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>833</v>
+        <v>845</v>
       </c>
       <c r="D45" t="s">
-        <v>834</v>
+        <v>846</v>
       </c>
       <c r="E45" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F45" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G45" t="s">
-        <v>835</v>
+        <v>847</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>836</v>
+        <v>848</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>837</v>
+        <v>849</v>
       </c>
       <c r="D46" t="s">
-        <v>838</v>
+        <v>850</v>
       </c>
       <c r="E46" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F46" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G46" t="s">
-        <v>839</v>
+        <v>851</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>840</v>
+        <v>852</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>841</v>
+        <v>853</v>
       </c>
       <c r="D47" t="s">
-        <v>842</v>
+        <v>854</v>
       </c>
       <c r="E47" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F47" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G47" t="s">
-        <v>843</v>
+        <v>855</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>844</v>
+        <v>856</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>845</v>
+        <v>857</v>
       </c>
       <c r="D48" t="s">
-        <v>846</v>
+        <v>858</v>
       </c>
       <c r="E48" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F48" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G48" t="s">
-        <v>847</v>
+        <v>859</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>848</v>
+        <v>860</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>849</v>
+        <v>861</v>
       </c>
       <c r="D49" t="s">
-        <v>850</v>
+        <v>862</v>
       </c>
       <c r="E49" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F49" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G49" t="s">
-        <v>851</v>
+        <v>863</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>852</v>
+        <v>864</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5618,25 +5667,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>853</v>
+        <v>865</v>
       </c>
       <c r="D50" t="s">
-        <v>854</v>
+        <v>866</v>
       </c>
       <c r="E50" t="s">
-        <v>684</v>
+        <v>696</v>
       </c>
       <c r="F50" t="s">
-        <v>679</v>
+        <v>691</v>
       </c>
       <c r="G50" t="s">
-        <v>855</v>
+        <v>867</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>856</v>
+        <v>868</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5644,25 +5693,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>857</v>
+        <v>869</v>
       </c>
       <c r="D51" t="s">
-        <v>858</v>
+        <v>870</v>
       </c>
       <c r="E51" t="s">
-        <v>701</v>
+        <v>713</v>
       </c>
       <c r="F51" t="s">
-        <v>859</v>
+        <v>871</v>
       </c>
       <c r="G51" t="s">
-        <v>860</v>
+        <v>872</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>861</v>
+        <v>873</v>
       </c>
     </row>
   </sheetData>
@@ -6013,8 +6062,8 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="4"/>
+  <dimension ref="A1:H19"/>
+  <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
     <col min="2" max="2" width="22.4166666666667" customWidth="1"/>
@@ -6152,18 +6201,73 @@
       </c>
     </row>
     <row r="9" spans="1:5">
-      <c r="A9" s="2"/>
-      <c r="B9" s="2"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="2"/>
-      <c r="E9" s="2"/>
+      <c r="A9" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="C9" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="2">
+        <v>90</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>177</v>
+      </c>
     </row>
     <row r="10" spans="1:5">
-      <c r="A10" s="2"/>
-      <c r="B10" s="2"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
+      <c r="A10" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="D10" s="2">
+        <v>9</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" t="s">
+        <v>181</v>
+      </c>
+      <c r="B11" t="s">
+        <v>182</v>
+      </c>
+      <c r="C11" t="s">
+        <v>107</v>
+      </c>
+      <c r="D11">
+        <v>6</v>
+      </c>
+      <c r="E11" t="s">
+        <v>183</v>
+      </c>
+    </row>
+    <row r="17" spans="5:8">
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="7"/>
+    </row>
+    <row r="18" spans="5:8">
+      <c r="E18" s="1"/>
+      <c r="F18" s="1"/>
+      <c r="G18" s="1"/>
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="5:8">
+      <c r="E19" s="1"/>
+      <c r="F19" s="1"/>
+      <c r="G19" s="1"/>
+      <c r="H19" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6204,55 +6308,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
-        <v>175</v>
+        <v>184</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>176</v>
+        <v>185</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>177</v>
+        <v>186</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>179</v>
+        <v>188</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>180</v>
+        <v>189</v>
       </c>
       <c r="J1" t="s">
-        <v>181</v>
+        <v>190</v>
       </c>
       <c r="K1" t="s">
-        <v>182</v>
+        <v>191</v>
       </c>
       <c r="L1" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="M1" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="N1" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="O1" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="P1" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="Q1" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="R1" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="S1" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="T1" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6323,10 +6427,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>192</v>
+        <v>201</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6340,55 +6444,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>193</v>
+        <v>202</v>
       </c>
       <c r="D4" t="s">
-        <v>194</v>
+        <v>203</v>
       </c>
       <c r="E4" t="s">
-        <v>195</v>
+        <v>204</v>
       </c>
       <c r="F4" t="s">
-        <v>196</v>
+        <v>205</v>
       </c>
       <c r="H4" t="s">
-        <v>197</v>
+        <v>206</v>
       </c>
       <c r="I4" t="s">
-        <v>198</v>
+        <v>207</v>
       </c>
       <c r="J4" t="s">
-        <v>199</v>
+        <v>208</v>
       </c>
       <c r="K4" t="s">
-        <v>200</v>
+        <v>209</v>
       </c>
       <c r="L4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="M4" t="s">
-        <v>202</v>
+        <v>211</v>
       </c>
       <c r="N4" t="s">
-        <v>203</v>
+        <v>212</v>
       </c>
       <c r="O4" t="s">
-        <v>204</v>
+        <v>213</v>
       </c>
       <c r="P4" t="s">
-        <v>205</v>
+        <v>214</v>
       </c>
       <c r="Q4" t="s">
-        <v>206</v>
+        <v>215</v>
       </c>
       <c r="R4" t="s">
-        <v>207</v>
+        <v>216</v>
       </c>
       <c r="S4" t="s">
-        <v>208</v>
+        <v>217</v>
       </c>
       <c r="T4" t="s">
-        <v>209</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6396,58 +6500,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>210</v>
+        <v>219</v>
       </c>
       <c r="D5" t="s">
-        <v>211</v>
+        <v>220</v>
       </c>
       <c r="E5" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F5" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G5" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H5" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I5" t="s">
-        <v>215</v>
+        <v>224</v>
       </c>
       <c r="J5" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="K5" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="L5" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="M5" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="N5" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="O5" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="P5" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Q5" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="R5" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S5" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T5" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6455,58 +6559,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>234</v>
+      </c>
+      <c r="D6" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" t="s">
+        <v>221</v>
+      </c>
+      <c r="F6" t="s">
+        <v>230</v>
+      </c>
+      <c r="G6" t="s">
+        <v>192</v>
+      </c>
+      <c r="H6" t="s">
+        <v>236</v>
+      </c>
+      <c r="I6" t="s">
+        <v>224</v>
+      </c>
+      <c r="J6" t="s">
         <v>225</v>
       </c>
-      <c r="D6" t="s">
+      <c r="K6" t="s">
         <v>226</v>
       </c>
-      <c r="E6" t="s">
-        <v>212</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="L6" t="s">
+        <v>227</v>
+      </c>
+      <c r="M6" t="s">
         <v>221</v>
       </c>
-      <c r="G6" t="s">
-        <v>183</v>
-      </c>
-      <c r="H6" t="s">
-        <v>227</v>
-      </c>
-      <c r="I6" t="s">
-        <v>215</v>
-      </c>
-      <c r="J6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" t="s">
-        <v>217</v>
-      </c>
-      <c r="L6" t="s">
-        <v>218</v>
-      </c>
-      <c r="M6" t="s">
-        <v>212</v>
-      </c>
       <c r="N6" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="O6" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="P6" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Q6" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="R6" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S6" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T6" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6514,58 +6618,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
+        <v>237</v>
+      </c>
+      <c r="D7" t="s">
+        <v>238</v>
+      </c>
+      <c r="E7" t="s">
+        <v>221</v>
+      </c>
+      <c r="F7" t="s">
+        <v>231</v>
+      </c>
+      <c r="G7" t="s">
+        <v>192</v>
+      </c>
+      <c r="H7" t="s">
+        <v>239</v>
+      </c>
+      <c r="I7" t="s">
+        <v>224</v>
+      </c>
+      <c r="J7" t="s">
+        <v>225</v>
+      </c>
+      <c r="K7" t="s">
+        <v>226</v>
+      </c>
+      <c r="L7" t="s">
+        <v>227</v>
+      </c>
+      <c r="M7" t="s">
+        <v>221</v>
+      </c>
+      <c r="N7" t="s">
         <v>228</v>
       </c>
-      <c r="D7" t="s">
+      <c r="O7" t="s">
         <v>229</v>
       </c>
-      <c r="E7" t="s">
-        <v>212</v>
-      </c>
-      <c r="F7" t="s">
+      <c r="P7" t="s">
         <v>222</v>
       </c>
-      <c r="G7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" t="s">
+      <c r="Q7" t="s">
         <v>230</v>
       </c>
-      <c r="I7" t="s">
-        <v>215</v>
-      </c>
-      <c r="J7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K7" t="s">
-        <v>217</v>
-      </c>
-      <c r="L7" t="s">
-        <v>218</v>
-      </c>
-      <c r="M7" t="s">
-        <v>212</v>
-      </c>
-      <c r="N7" t="s">
-        <v>219</v>
-      </c>
-      <c r="O7" t="s">
-        <v>220</v>
-      </c>
-      <c r="P7" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>221</v>
-      </c>
       <c r="R7" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S7" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T7" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6573,58 +6677,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
+        <v>240</v>
+      </c>
+      <c r="D8" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" t="s">
+        <v>228</v>
+      </c>
+      <c r="F8" t="s">
+        <v>229</v>
+      </c>
+      <c r="G8" t="s">
+        <v>192</v>
+      </c>
+      <c r="H8" t="s">
+        <v>242</v>
+      </c>
+      <c r="I8" t="s">
+        <v>224</v>
+      </c>
+      <c r="J8" t="s">
+        <v>225</v>
+      </c>
+      <c r="K8" t="s">
+        <v>226</v>
+      </c>
+      <c r="L8" t="s">
+        <v>227</v>
+      </c>
+      <c r="M8" t="s">
+        <v>221</v>
+      </c>
+      <c r="N8" t="s">
+        <v>228</v>
+      </c>
+      <c r="O8" t="s">
+        <v>229</v>
+      </c>
+      <c r="P8" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>230</v>
+      </c>
+      <c r="R8" t="s">
         <v>231</v>
       </c>
-      <c r="D8" t="s">
+      <c r="S8" t="s">
         <v>232</v>
       </c>
-      <c r="E8" t="s">
-        <v>219</v>
-      </c>
-      <c r="F8" t="s">
-        <v>220</v>
-      </c>
-      <c r="G8" t="s">
-        <v>183</v>
-      </c>
-      <c r="H8" t="s">
+      <c r="T8" t="s">
         <v>233</v>
-      </c>
-      <c r="I8" t="s">
-        <v>215</v>
-      </c>
-      <c r="J8" t="s">
-        <v>216</v>
-      </c>
-      <c r="K8" t="s">
-        <v>217</v>
-      </c>
-      <c r="L8" t="s">
-        <v>218</v>
-      </c>
-      <c r="M8" t="s">
-        <v>212</v>
-      </c>
-      <c r="N8" t="s">
-        <v>219</v>
-      </c>
-      <c r="O8" t="s">
-        <v>220</v>
-      </c>
-      <c r="P8" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>221</v>
-      </c>
-      <c r="R8" t="s">
-        <v>222</v>
-      </c>
-      <c r="S8" t="s">
-        <v>223</v>
-      </c>
-      <c r="T8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6632,58 +6736,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>243</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>244</v>
       </c>
       <c r="E9" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F9" t="s">
+        <v>231</v>
+      </c>
+      <c r="G9" t="s">
+        <v>192</v>
+      </c>
+      <c r="H9" t="s">
+        <v>223</v>
+      </c>
+      <c r="I9" t="s">
+        <v>245</v>
+      </c>
+      <c r="J9" t="s">
+        <v>225</v>
+      </c>
+      <c r="K9" t="s">
+        <v>226</v>
+      </c>
+      <c r="L9" t="s">
+        <v>227</v>
+      </c>
+      <c r="M9" t="s">
+        <v>221</v>
+      </c>
+      <c r="N9" t="s">
+        <v>228</v>
+      </c>
+      <c r="O9" t="s">
+        <v>229</v>
+      </c>
+      <c r="P9" t="s">
         <v>222</v>
       </c>
-      <c r="G9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" t="s">
-        <v>214</v>
-      </c>
-      <c r="I9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" t="s">
-        <v>216</v>
-      </c>
-      <c r="K9" t="s">
-        <v>217</v>
-      </c>
-      <c r="L9" t="s">
-        <v>218</v>
-      </c>
-      <c r="M9" t="s">
-        <v>212</v>
-      </c>
-      <c r="N9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O9" t="s">
-        <v>220</v>
-      </c>
-      <c r="P9" t="s">
-        <v>213</v>
-      </c>
       <c r="Q9" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="R9" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S9" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T9" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6691,58 +6795,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>246</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>247</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="F10" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G10" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H10" t="s">
-        <v>214</v>
+        <v>223</v>
       </c>
       <c r="I10" t="s">
-        <v>239</v>
+        <v>248</v>
       </c>
       <c r="J10" t="s">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="K10" t="s">
-        <v>217</v>
+        <v>226</v>
       </c>
       <c r="L10" t="s">
-        <v>218</v>
+        <v>227</v>
       </c>
       <c r="M10" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="N10" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="O10" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="P10" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Q10" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="R10" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S10" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T10" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6750,58 +6854,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>249</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>250</v>
       </c>
       <c r="E11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F11" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
       <c r="G11" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H11" t="s">
+        <v>236</v>
+      </c>
+      <c r="I11" t="s">
+        <v>245</v>
+      </c>
+      <c r="J11" t="s">
+        <v>225</v>
+      </c>
+      <c r="K11" t="s">
+        <v>226</v>
+      </c>
+      <c r="L11" t="s">
         <v>227</v>
       </c>
-      <c r="I11" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" t="s">
-        <v>216</v>
-      </c>
-      <c r="K11" t="s">
-        <v>217</v>
-      </c>
-      <c r="L11" t="s">
-        <v>218</v>
-      </c>
       <c r="M11" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="N11" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="O11" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="P11" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Q11" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="R11" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S11" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T11" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6809,58 +6913,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="D12" t="s">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="E12" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F12" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G12" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H12" t="s">
+        <v>236</v>
+      </c>
+      <c r="I12" t="s">
+        <v>248</v>
+      </c>
+      <c r="J12" t="s">
+        <v>225</v>
+      </c>
+      <c r="K12" t="s">
+        <v>226</v>
+      </c>
+      <c r="L12" t="s">
         <v>227</v>
       </c>
-      <c r="I12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" t="s">
-        <v>217</v>
-      </c>
-      <c r="L12" t="s">
-        <v>218</v>
-      </c>
       <c r="M12" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="N12" t="s">
-        <v>219</v>
+        <v>228</v>
       </c>
       <c r="O12" t="s">
-        <v>220</v>
+        <v>229</v>
       </c>
       <c r="P12" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="Q12" t="s">
-        <v>221</v>
+        <v>230</v>
       </c>
       <c r="R12" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S12" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T12" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6868,58 +6972,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>253</v>
       </c>
       <c r="D13" t="s">
+        <v>254</v>
+      </c>
+      <c r="E13" t="s">
+        <v>221</v>
+      </c>
+      <c r="F13" t="s">
+        <v>233</v>
+      </c>
+      <c r="G13" t="s">
+        <v>192</v>
+      </c>
+      <c r="H13" t="s">
+        <v>239</v>
+      </c>
+      <c r="I13" t="s">
         <v>245</v>
       </c>
-      <c r="E13" t="s">
-        <v>212</v>
-      </c>
-      <c r="F13" t="s">
-        <v>224</v>
-      </c>
-      <c r="G13" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" t="s">
+      <c r="J13" t="s">
+        <v>225</v>
+      </c>
+      <c r="K13" t="s">
+        <v>226</v>
+      </c>
+      <c r="L13" t="s">
+        <v>227</v>
+      </c>
+      <c r="M13" t="s">
+        <v>221</v>
+      </c>
+      <c r="N13" t="s">
+        <v>228</v>
+      </c>
+      <c r="O13" t="s">
+        <v>229</v>
+      </c>
+      <c r="P13" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q13" t="s">
         <v>230</v>
       </c>
-      <c r="I13" t="s">
-        <v>236</v>
-      </c>
-      <c r="J13" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13" t="s">
-        <v>217</v>
-      </c>
-      <c r="L13" t="s">
-        <v>218</v>
-      </c>
-      <c r="M13" t="s">
-        <v>212</v>
-      </c>
-      <c r="N13" t="s">
-        <v>219</v>
-      </c>
-      <c r="O13" t="s">
-        <v>220</v>
-      </c>
-      <c r="P13" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>221</v>
-      </c>
       <c r="R13" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S13" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T13" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -6927,58 +7031,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="E14" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F14" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G14" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H14" t="s">
+        <v>239</v>
+      </c>
+      <c r="I14" t="s">
+        <v>248</v>
+      </c>
+      <c r="J14" t="s">
+        <v>225</v>
+      </c>
+      <c r="K14" t="s">
+        <v>226</v>
+      </c>
+      <c r="L14" t="s">
+        <v>227</v>
+      </c>
+      <c r="M14" t="s">
+        <v>221</v>
+      </c>
+      <c r="N14" t="s">
+        <v>228</v>
+      </c>
+      <c r="O14" t="s">
+        <v>229</v>
+      </c>
+      <c r="P14" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q14" t="s">
         <v>230</v>
       </c>
-      <c r="I14" t="s">
-        <v>239</v>
-      </c>
-      <c r="J14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K14" t="s">
-        <v>217</v>
-      </c>
-      <c r="L14" t="s">
-        <v>218</v>
-      </c>
-      <c r="M14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N14" t="s">
-        <v>219</v>
-      </c>
-      <c r="O14" t="s">
-        <v>220</v>
-      </c>
-      <c r="P14" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>221</v>
-      </c>
       <c r="R14" t="s">
-        <v>222</v>
+        <v>231</v>
       </c>
       <c r="S14" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="T14" t="s">
-        <v>224</v>
+        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -6986,58 +7090,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>257</v>
       </c>
       <c r="D15" t="s">
-        <v>249</v>
+        <v>258</v>
       </c>
       <c r="E15" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F15" t="s">
-        <v>213</v>
+        <v>222</v>
       </c>
       <c r="G15" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H15" t="s">
+        <v>242</v>
+      </c>
+      <c r="I15" t="s">
+        <v>245</v>
+      </c>
+      <c r="J15" t="s">
+        <v>225</v>
+      </c>
+      <c r="K15" t="s">
+        <v>226</v>
+      </c>
+      <c r="L15" t="s">
+        <v>227</v>
+      </c>
+      <c r="M15" t="s">
+        <v>221</v>
+      </c>
+      <c r="N15" t="s">
+        <v>228</v>
+      </c>
+      <c r="O15" t="s">
+        <v>229</v>
+      </c>
+      <c r="P15" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>230</v>
+      </c>
+      <c r="R15" t="s">
+        <v>231</v>
+      </c>
+      <c r="S15" t="s">
+        <v>232</v>
+      </c>
+      <c r="T15" t="s">
         <v>233</v>
-      </c>
-      <c r="I15" t="s">
-        <v>236</v>
-      </c>
-      <c r="J15" t="s">
-        <v>216</v>
-      </c>
-      <c r="K15" t="s">
-        <v>217</v>
-      </c>
-      <c r="L15" t="s">
-        <v>218</v>
-      </c>
-      <c r="M15" t="s">
-        <v>212</v>
-      </c>
-      <c r="N15" t="s">
-        <v>219</v>
-      </c>
-      <c r="O15" t="s">
-        <v>220</v>
-      </c>
-      <c r="P15" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>221</v>
-      </c>
-      <c r="R15" t="s">
-        <v>222</v>
-      </c>
-      <c r="S15" t="s">
-        <v>223</v>
-      </c>
-      <c r="T15" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7045,58 +7149,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>259</v>
       </c>
       <c r="D16" t="s">
-        <v>251</v>
+        <v>260</v>
       </c>
       <c r="E16" t="s">
-        <v>212</v>
+        <v>221</v>
       </c>
       <c r="F16" t="s">
-        <v>223</v>
+        <v>232</v>
       </c>
       <c r="G16" t="s">
-        <v>183</v>
+        <v>192</v>
       </c>
       <c r="H16" t="s">
+        <v>242</v>
+      </c>
+      <c r="I16" t="s">
+        <v>248</v>
+      </c>
+      <c r="J16" t="s">
+        <v>225</v>
+      </c>
+      <c r="K16" t="s">
+        <v>226</v>
+      </c>
+      <c r="L16" t="s">
+        <v>227</v>
+      </c>
+      <c r="M16" t="s">
+        <v>221</v>
+      </c>
+      <c r="N16" t="s">
+        <v>228</v>
+      </c>
+      <c r="O16" t="s">
+        <v>229</v>
+      </c>
+      <c r="P16" t="s">
+        <v>222</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>230</v>
+      </c>
+      <c r="R16" t="s">
+        <v>231</v>
+      </c>
+      <c r="S16" t="s">
+        <v>232</v>
+      </c>
+      <c r="T16" t="s">
         <v>233</v>
-      </c>
-      <c r="I16" t="s">
-        <v>239</v>
-      </c>
-      <c r="J16" t="s">
-        <v>216</v>
-      </c>
-      <c r="K16" t="s">
-        <v>217</v>
-      </c>
-      <c r="L16" t="s">
-        <v>218</v>
-      </c>
-      <c r="M16" t="s">
-        <v>212</v>
-      </c>
-      <c r="N16" t="s">
-        <v>219</v>
-      </c>
-      <c r="O16" t="s">
-        <v>220</v>
-      </c>
-      <c r="P16" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>221</v>
-      </c>
-      <c r="R16" t="s">
-        <v>222</v>
-      </c>
-      <c r="S16" t="s">
-        <v>223</v>
-      </c>
-      <c r="T16" t="s">
-        <v>224</v>
       </c>
     </row>
   </sheetData>
@@ -7125,16 +7229,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>262</v>
       </c>
       <c r="E1" t="s">
-        <v>254</v>
+        <v>263</v>
       </c>
       <c r="F1" t="s">
-        <v>255</v>
+        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7148,7 +7252,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>265</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7173,16 +7277,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>266</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>267</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>268</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7196,10 +7300,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>261</v>
+        <v>270</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>271</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7207,16 +7311,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>263</v>
+        <v>272</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>273</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
+        <v>274</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7230,10 +7334,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>275</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>276</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7247,10 +7351,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>268</v>
+        <v>277</v>
       </c>
       <c r="F8" t="s">
-        <v>269</v>
+        <v>278</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7264,10 +7368,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>279</v>
       </c>
       <c r="F9" t="s">
-        <v>271</v>
+        <v>280</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7275,16 +7379,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="F10" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7298,10 +7402,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7315,10 +7419,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
     </row>
   </sheetData>
@@ -7330,7 +7434,7 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:N32"/>
+  <dimension ref="A1:N33"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="3" max="3" width="19" customWidth="1"/>
@@ -7351,34 +7455,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="E1" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="G1" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="H1" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="I1" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="J1" t="s">
-        <v>285</v>
+        <v>294</v>
       </c>
       <c r="K1" t="s">
-        <v>286</v>
+        <v>295</v>
       </c>
       <c r="L1" t="s">
-        <v>287</v>
+        <v>296</v>
       </c>
       <c r="M1" t="s">
-        <v>288</v>
+        <v>297</v>
       </c>
       <c r="N1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7389,10 +7493,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7404,7 +7508,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7426,13 +7530,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>292</v>
+        <v>301</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>293</v>
+        <v>302</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>294</v>
+        <v>303</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7443,40 +7547,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>295</v>
+        <v>304</v>
       </c>
       <c r="D4" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="E4" t="s">
-        <v>297</v>
+        <v>306</v>
       </c>
       <c r="F4" t="s">
-        <v>296</v>
+        <v>305</v>
       </c>
       <c r="G4" t="s">
-        <v>298</v>
+        <v>307</v>
       </c>
       <c r="H4" t="s">
-        <v>299</v>
+        <v>308</v>
       </c>
       <c r="I4" t="s">
-        <v>300</v>
+        <v>309</v>
       </c>
       <c r="J4" t="s">
-        <v>301</v>
+        <v>310</v>
       </c>
       <c r="K4" t="s">
-        <v>302</v>
+        <v>311</v>
       </c>
       <c r="L4" t="s">
-        <v>303</v>
+        <v>312</v>
       </c>
       <c r="M4" t="s">
-        <v>201</v>
+        <v>210</v>
       </c>
       <c r="N4" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7499,13 +7603,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L5" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M5" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7519,22 +7623,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L6" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M6" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7548,22 +7652,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L7" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M7" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7577,22 +7681,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>200</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L8" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M8" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7606,22 +7710,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>197</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L9" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M9" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7635,22 +7739,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>198</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L10" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M10" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7664,22 +7768,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>195</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L11" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="M11" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7693,22 +7797,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>199</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="L12" t="s">
-        <v>307</v>
+        <v>316</v>
       </c>
       <c r="M12" t="s">
-        <v>306</v>
+        <v>315</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7716,31 +7820,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>193</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>196</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>305</v>
+        <v>314</v>
       </c>
       <c r="L13" t="s">
-        <v>310</v>
+        <v>319</v>
       </c>
       <c r="M13" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="N13" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7748,10 +7852,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>313</v>
+        <v>322</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>314</v>
+        <v>323</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7760,7 +7864,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7768,10 +7872,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>316</v>
+        <v>325</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>317</v>
+        <v>326</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7780,7 +7884,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>315</v>
+        <v>324</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7788,10 +7892,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>318</v>
+        <v>327</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>319</v>
+        <v>328</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7800,7 +7904,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>329</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7808,19 +7912,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>321</v>
+        <v>330</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>322</v>
+        <v>331</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="F17" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="N17" t="s">
-        <v>325</v>
+        <v>334</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7828,10 +7932,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>326</v>
+        <v>335</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>327</v>
+        <v>336</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7840,7 +7944,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>328</v>
+        <v>337</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7848,10 +7952,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>329</v>
+        <v>338</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>330</v>
+        <v>339</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7860,7 +7964,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>331</v>
+        <v>340</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7868,10 +7972,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>332</v>
+        <v>341</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>333</v>
+        <v>342</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7880,7 +7984,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>334</v>
+        <v>343</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7888,19 +7992,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>335</v>
+        <v>344</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>336</v>
+        <v>345</v>
       </c>
       <c r="E21" t="s">
-        <v>323</v>
+        <v>332</v>
       </c>
       <c r="F21" t="s">
-        <v>324</v>
+        <v>333</v>
       </c>
       <c r="N21" t="s">
-        <v>337</v>
+        <v>346</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -7908,16 +8012,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>338</v>
+        <v>347</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>339</v>
+        <v>348</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>308</v>
+        <v>317</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>309</v>
+        <v>318</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -7925,10 +8029,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>340</v>
+        <v>349</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>341</v>
+        <v>350</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -7942,10 +8046,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>342</v>
+        <v>351</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>343</v>
+        <v>352</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -7959,10 +8063,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>344</v>
+        <v>353</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>345</v>
+        <v>354</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -7976,10 +8080,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>346</v>
+        <v>355</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>347</v>
+        <v>356</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -7993,10 +8097,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>348</v>
+        <v>357</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>349</v>
+        <v>358</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8010,10 +8114,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>359</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>351</v>
+        <v>360</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8027,10 +8131,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>352</v>
+        <v>361</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>353</v>
+        <v>362</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8039,10 +8143,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="N29" t="s">
-        <v>312</v>
+        <v>321</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8050,10 +8154,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>354</v>
+        <v>363</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>355</v>
+        <v>364</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8067,10 +8171,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>356</v>
+        <v>365</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>357</v>
+        <v>366</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8084,10 +8188,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>358</v>
+        <v>367</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>359</v>
+        <v>368</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8096,10 +8200,30 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>311</v>
+        <v>320</v>
       </c>
       <c r="N32" t="s">
-        <v>312</v>
+        <v>321</v>
+      </c>
+    </row>
+    <row r="33" customFormat="1" spans="2:14">
+      <c r="B33">
+        <v>4001</v>
+      </c>
+      <c r="C33" s="5" t="s">
+        <v>369</v>
+      </c>
+      <c r="D33" s="5" t="s">
+        <v>370</v>
+      </c>
+      <c r="E33" s="5" t="s">
+        <v>66</v>
+      </c>
+      <c r="F33" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="N33" t="s">
+        <v>371</v>
       </c>
     </row>
   </sheetData>
@@ -8135,31 +8259,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>360</v>
+        <v>372</v>
       </c>
       <c r="D1" t="s">
-        <v>361</v>
+        <v>373</v>
       </c>
       <c r="E1" t="s">
-        <v>362</v>
+        <v>374</v>
       </c>
       <c r="F1" t="s">
-        <v>363</v>
+        <v>375</v>
       </c>
       <c r="G1" t="s">
-        <v>364</v>
+        <v>376</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="I1" t="s">
-        <v>365</v>
+        <v>377</v>
       </c>
       <c r="J1" t="s">
-        <v>366</v>
+        <v>378</v>
       </c>
       <c r="K1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8185,10 +8309,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>290</v>
+        <v>299</v>
       </c>
       <c r="I2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8202,34 +8326,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>367</v>
+        <v>379</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>368</v>
+        <v>380</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>369</v>
+        <v>381</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>370</v>
+        <v>382</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>371</v>
+        <v>383</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>372</v>
+        <v>384</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>373</v>
+        <v>385</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>374</v>
+        <v>386</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>375</v>
+        <v>387</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8240,31 +8364,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>376</v>
+        <v>388</v>
       </c>
       <c r="D4" t="s">
-        <v>377</v>
+        <v>389</v>
       </c>
       <c r="E4" t="s">
-        <v>378</v>
+        <v>390</v>
       </c>
       <c r="F4" t="s">
-        <v>379</v>
+        <v>391</v>
       </c>
       <c r="G4" t="s">
-        <v>380</v>
+        <v>392</v>
       </c>
       <c r="H4" t="s">
-        <v>381</v>
+        <v>393</v>
       </c>
       <c r="I4" t="s">
-        <v>382</v>
+        <v>394</v>
       </c>
       <c r="J4" t="s">
-        <v>383</v>
+        <v>395</v>
       </c>
       <c r="K4" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8272,7 +8396,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>384</v>
+        <v>396</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8296,7 +8420,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>385</v>
+        <v>397</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8304,7 +8428,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>386</v>
+        <v>398</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8328,7 +8452,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8336,7 +8460,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>388</v>
+        <v>400</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8360,7 +8484,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8368,7 +8492,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>389</v>
+        <v>401</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8392,7 +8516,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
     </row>
   </sheetData>
@@ -8423,16 +8547,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>261</v>
       </c>
       <c r="D1" t="s">
-        <v>390</v>
+        <v>402</v>
       </c>
       <c r="E1" t="s">
-        <v>391</v>
+        <v>403</v>
       </c>
       <c r="F1" t="s">
-        <v>392</v>
+        <v>404</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8449,7 +8573,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8462,10 +8586,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>393</v>
+        <v>405</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>394</v>
+        <v>406</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8476,13 +8600,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>395</v>
+        <v>407</v>
       </c>
       <c r="D4" t="s">
-        <v>396</v>
+        <v>408</v>
       </c>
       <c r="E4" t="s">
-        <v>397</v>
+        <v>409</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8490,7 +8614,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8499,7 +8623,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>399</v>
+        <v>411</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8507,7 +8631,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>400</v>
+        <v>412</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8516,7 +8640,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>401</v>
+        <v>413</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8524,7 +8648,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8533,7 +8657,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>403</v>
+        <v>415</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8541,7 +8665,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>404</v>
+        <v>416</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8550,7 +8674,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>405</v>
+        <v>417</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8588,40 +8712,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>406</v>
+        <v>418</v>
       </c>
       <c r="C1" t="s">
-        <v>407</v>
+        <v>419</v>
       </c>
       <c r="D1" t="s">
-        <v>408</v>
+        <v>420</v>
       </c>
       <c r="E1" t="s">
-        <v>409</v>
+        <v>421</v>
       </c>
       <c r="F1" t="s">
-        <v>410</v>
+        <v>422</v>
       </c>
       <c r="G1" t="s">
-        <v>411</v>
+        <v>423</v>
       </c>
       <c r="H1" t="s">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="I1" t="s">
-        <v>412</v>
+        <v>424</v>
       </c>
       <c r="J1" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="K1" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="L1" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="M1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8635,16 +8759,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="G2" t="s">
-        <v>291</v>
+        <v>300</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8670,40 +8794,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>419</v>
+        <v>431</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>420</v>
+        <v>432</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>424</v>
+        <v>436</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>425</v>
+        <v>437</v>
       </c>
       <c r="I3" t="s">
-        <v>426</v>
+        <v>438</v>
       </c>
       <c r="J3" t="s">
-        <v>427</v>
+        <v>439</v>
       </c>
       <c r="K3" t="s">
-        <v>428</v>
+        <v>440</v>
       </c>
       <c r="L3" t="s">
-        <v>429</v>
+        <v>441</v>
       </c>
       <c r="M3" t="s">
-        <v>430</v>
+        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8711,54 +8835,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>431</v>
+        <v>443</v>
       </c>
       <c r="C4" t="s">
-        <v>432</v>
+        <v>444</v>
       </c>
       <c r="D4" t="s">
-        <v>433</v>
+        <v>445</v>
       </c>
       <c r="E4" t="s">
-        <v>434</v>
+        <v>446</v>
       </c>
       <c r="F4" t="s">
-        <v>435</v>
+        <v>447</v>
       </c>
       <c r="G4" t="s">
-        <v>436</v>
+        <v>448</v>
       </c>
       <c r="H4" t="s">
-        <v>304</v>
+        <v>313</v>
       </c>
       <c r="I4" t="s">
-        <v>437</v>
+        <v>449</v>
       </c>
       <c r="J4" t="s">
-        <v>438</v>
+        <v>450</v>
       </c>
       <c r="K4" t="s">
-        <v>439</v>
+        <v>451</v>
       </c>
       <c r="L4" t="s">
-        <v>440</v>
+        <v>452</v>
       </c>
       <c r="M4" t="s">
-        <v>441</v>
+        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>442</v>
+        <v>454</v>
       </c>
       <c r="D5" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8770,36 +8894,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>444</v>
+        <v>456</v>
       </c>
       <c r="I5" t="s">
-        <v>445</v>
+        <v>457</v>
       </c>
       <c r="J5" t="s">
-        <v>446</v>
+        <v>458</v>
       </c>
       <c r="K5" t="s">
-        <v>447</v>
+        <v>459</v>
       </c>
       <c r="L5" t="s">
-        <v>448</v>
+        <v>460</v>
       </c>
       <c r="M5" t="s">
-        <v>449</v>
+        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>450</v>
+        <v>462</v>
       </c>
       <c r="D6" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8811,36 +8935,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>451</v>
+        <v>463</v>
       </c>
       <c r="I6" t="s">
-        <v>452</v>
+        <v>464</v>
       </c>
       <c r="J6" t="s">
-        <v>453</v>
+        <v>465</v>
       </c>
       <c r="K6" t="s">
-        <v>454</v>
+        <v>466</v>
       </c>
       <c r="L6" t="s">
-        <v>455</v>
+        <v>467</v>
       </c>
       <c r="M6" t="s">
-        <v>456</v>
+        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>457</v>
+        <v>469</v>
       </c>
       <c r="D7" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8852,36 +8976,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>458</v>
+        <v>470</v>
       </c>
       <c r="I7" t="s">
-        <v>459</v>
+        <v>471</v>
       </c>
       <c r="J7" t="s">
-        <v>460</v>
+        <v>472</v>
       </c>
       <c r="K7" t="s">
-        <v>461</v>
+        <v>473</v>
       </c>
       <c r="L7" t="s">
-        <v>462</v>
+        <v>474</v>
       </c>
       <c r="M7" t="s">
-        <v>463</v>
+        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>464</v>
+        <v>476</v>
       </c>
       <c r="D8" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -8893,36 +9017,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>465</v>
+        <v>477</v>
       </c>
       <c r="I8" t="s">
-        <v>466</v>
+        <v>478</v>
       </c>
       <c r="J8" t="s">
-        <v>467</v>
+        <v>479</v>
       </c>
       <c r="K8" t="s">
-        <v>468</v>
+        <v>480</v>
       </c>
       <c r="L8" t="s">
-        <v>469</v>
+        <v>481</v>
       </c>
       <c r="M8" t="s">
-        <v>470</v>
+        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>471</v>
+        <v>483</v>
       </c>
       <c r="D9" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -8934,36 +9058,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>472</v>
+        <v>484</v>
       </c>
       <c r="I9" t="s">
-        <v>473</v>
+        <v>485</v>
       </c>
       <c r="J9" t="s">
-        <v>474</v>
+        <v>486</v>
       </c>
       <c r="K9" t="s">
-        <v>475</v>
+        <v>487</v>
       </c>
       <c r="L9" t="s">
-        <v>476</v>
+        <v>488</v>
       </c>
       <c r="M9" t="s">
-        <v>477</v>
+        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>478</v>
+        <v>490</v>
       </c>
       <c r="D10" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -8975,36 +9099,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>479</v>
+        <v>491</v>
       </c>
       <c r="I10" t="s">
-        <v>480</v>
+        <v>492</v>
       </c>
       <c r="J10" t="s">
-        <v>481</v>
+        <v>493</v>
       </c>
       <c r="K10" t="s">
-        <v>482</v>
+        <v>494</v>
       </c>
       <c r="L10" t="s">
-        <v>483</v>
+        <v>495</v>
       </c>
       <c r="M10" t="s">
-        <v>484</v>
+        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>485</v>
+        <v>497</v>
       </c>
       <c r="D11" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9016,36 +9140,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>486</v>
+        <v>498</v>
       </c>
       <c r="I11" t="s">
-        <v>487</v>
+        <v>499</v>
       </c>
       <c r="J11" t="s">
-        <v>488</v>
+        <v>500</v>
       </c>
       <c r="K11" t="s">
-        <v>489</v>
+        <v>501</v>
       </c>
       <c r="L11" t="s">
-        <v>490</v>
+        <v>502</v>
       </c>
       <c r="M11" t="s">
-        <v>491</v>
+        <v>503</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>492</v>
+        <v>504</v>
       </c>
       <c r="D12" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9057,36 +9181,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>493</v>
+        <v>505</v>
       </c>
       <c r="I12" t="s">
-        <v>494</v>
+        <v>506</v>
       </c>
       <c r="J12" t="s">
-        <v>495</v>
+        <v>507</v>
       </c>
       <c r="K12" t="s">
-        <v>496</v>
+        <v>508</v>
       </c>
       <c r="L12" t="s">
-        <v>497</v>
+        <v>509</v>
       </c>
       <c r="M12" t="s">
-        <v>498</v>
+        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>499</v>
+        <v>511</v>
       </c>
       <c r="D13" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9098,36 +9222,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>500</v>
+        <v>512</v>
       </c>
       <c r="I13" t="s">
-        <v>501</v>
+        <v>513</v>
       </c>
       <c r="J13" t="s">
-        <v>502</v>
+        <v>514</v>
       </c>
       <c r="K13" t="s">
-        <v>503</v>
+        <v>515</v>
       </c>
       <c r="L13" t="s">
-        <v>504</v>
+        <v>516</v>
       </c>
       <c r="M13" t="s">
-        <v>505</v>
+        <v>517</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>506</v>
+        <v>518</v>
       </c>
       <c r="D14" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9139,36 +9263,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>507</v>
+        <v>519</v>
       </c>
       <c r="I14" t="s">
-        <v>508</v>
+        <v>520</v>
       </c>
       <c r="J14" t="s">
-        <v>509</v>
+        <v>521</v>
       </c>
       <c r="K14" t="s">
-        <v>510</v>
+        <v>522</v>
       </c>
       <c r="L14" t="s">
-        <v>511</v>
+        <v>523</v>
       </c>
       <c r="M14" t="s">
-        <v>512</v>
+        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>513</v>
+        <v>525</v>
       </c>
       <c r="D15" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9180,39 +9304,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>514</v>
+        <v>526</v>
       </c>
       <c r="I15" t="s">
-        <v>515</v>
+        <v>527</v>
       </c>
       <c r="J15" t="s">
-        <v>516</v>
+        <v>528</v>
       </c>
       <c r="K15" t="s">
-        <v>517</v>
+        <v>529</v>
       </c>
       <c r="L15" t="s">
-        <v>518</v>
+        <v>530</v>
       </c>
       <c r="M15" t="s">
-        <v>519</v>
+        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>520</v>
+        <v>532</v>
       </c>
       <c r="D16" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E16" t="s">
-        <v>522</v>
+        <v>534</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9221,39 +9345,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>523</v>
+        <v>535</v>
       </c>
       <c r="I16" t="s">
-        <v>524</v>
+        <v>536</v>
       </c>
       <c r="J16" t="s">
-        <v>525</v>
+        <v>537</v>
       </c>
       <c r="K16" t="s">
-        <v>526</v>
+        <v>538</v>
       </c>
       <c r="L16" t="s">
-        <v>527</v>
+        <v>539</v>
       </c>
       <c r="M16" t="s">
-        <v>528</v>
+        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>529</v>
+        <v>541</v>
       </c>
       <c r="D17" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E17" t="s">
-        <v>530</v>
+        <v>542</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9262,39 +9386,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>531</v>
+        <v>543</v>
       </c>
       <c r="I17" t="s">
-        <v>532</v>
+        <v>544</v>
       </c>
       <c r="J17" t="s">
-        <v>533</v>
+        <v>545</v>
       </c>
       <c r="K17" t="s">
-        <v>534</v>
+        <v>546</v>
       </c>
       <c r="L17" t="s">
-        <v>535</v>
+        <v>547</v>
       </c>
       <c r="M17" t="s">
-        <v>536</v>
+        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>537</v>
+        <v>549</v>
       </c>
       <c r="D18" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E18" t="s">
-        <v>538</v>
+        <v>550</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9303,39 +9427,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>539</v>
+        <v>551</v>
       </c>
       <c r="I18" t="s">
-        <v>540</v>
+        <v>552</v>
       </c>
       <c r="J18" t="s">
-        <v>541</v>
+        <v>553</v>
       </c>
       <c r="K18" t="s">
-        <v>542</v>
+        <v>554</v>
       </c>
       <c r="L18" t="s">
-        <v>543</v>
+        <v>555</v>
       </c>
       <c r="M18" t="s">
-        <v>544</v>
+        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>545</v>
+        <v>557</v>
       </c>
       <c r="D19" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E19" t="s">
-        <v>546</v>
+        <v>558</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9344,39 +9468,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>547</v>
+        <v>559</v>
       </c>
       <c r="I19" t="s">
-        <v>548</v>
+        <v>560</v>
       </c>
       <c r="J19" t="s">
-        <v>549</v>
+        <v>561</v>
       </c>
       <c r="K19" t="s">
-        <v>550</v>
+        <v>562</v>
       </c>
       <c r="L19" t="s">
-        <v>551</v>
+        <v>563</v>
       </c>
       <c r="M19" t="s">
-        <v>552</v>
+        <v>564</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>553</v>
+        <v>565</v>
       </c>
       <c r="D20" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E20" t="s">
-        <v>554</v>
+        <v>566</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9385,39 +9509,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>555</v>
+        <v>567</v>
       </c>
       <c r="I20" t="s">
-        <v>556</v>
+        <v>568</v>
       </c>
       <c r="J20" t="s">
-        <v>557</v>
+        <v>569</v>
       </c>
       <c r="K20" t="s">
-        <v>558</v>
+        <v>570</v>
       </c>
       <c r="L20" t="s">
-        <v>559</v>
+        <v>571</v>
       </c>
       <c r="M20" t="s">
-        <v>560</v>
+        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>561</v>
+        <v>573</v>
       </c>
       <c r="D21" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E21" t="s">
-        <v>562</v>
+        <v>574</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9426,39 +9550,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>563</v>
+        <v>575</v>
       </c>
       <c r="I21" t="s">
-        <v>564</v>
+        <v>576</v>
       </c>
       <c r="J21" t="s">
-        <v>565</v>
+        <v>577</v>
       </c>
       <c r="K21" t="s">
-        <v>566</v>
+        <v>578</v>
       </c>
       <c r="L21" t="s">
-        <v>567</v>
+        <v>579</v>
       </c>
       <c r="M21" t="s">
-        <v>568</v>
+        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>569</v>
+        <v>581</v>
       </c>
       <c r="D22" t="s">
-        <v>521</v>
+        <v>533</v>
       </c>
       <c r="E22" t="s">
-        <v>570</v>
+        <v>582</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9467,39 +9591,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>571</v>
+        <v>583</v>
       </c>
       <c r="I22" t="s">
-        <v>572</v>
+        <v>584</v>
       </c>
       <c r="J22" t="s">
-        <v>573</v>
+        <v>585</v>
       </c>
       <c r="K22" t="s">
-        <v>574</v>
+        <v>586</v>
       </c>
       <c r="L22" t="s">
-        <v>575</v>
+        <v>587</v>
       </c>
       <c r="M22" t="s">
-        <v>576</v>
+        <v>588</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>577</v>
+        <v>589</v>
       </c>
       <c r="D23" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="E23" t="s">
-        <v>579</v>
+        <v>591</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9508,39 +9632,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>580</v>
+        <v>592</v>
       </c>
       <c r="I23" t="s">
-        <v>581</v>
+        <v>593</v>
       </c>
       <c r="J23" t="s">
-        <v>582</v>
+        <v>594</v>
       </c>
       <c r="K23" t="s">
-        <v>583</v>
+        <v>595</v>
       </c>
       <c r="L23" t="s">
-        <v>584</v>
+        <v>596</v>
       </c>
       <c r="M23" t="s">
-        <v>585</v>
+        <v>597</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>586</v>
+        <v>598</v>
       </c>
       <c r="D24" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="E24" t="s">
-        <v>587</v>
+        <v>599</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9549,39 +9673,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>588</v>
+        <v>600</v>
       </c>
       <c r="I24" t="s">
-        <v>589</v>
+        <v>601</v>
       </c>
       <c r="J24" t="s">
-        <v>590</v>
+        <v>602</v>
       </c>
       <c r="K24" t="s">
-        <v>591</v>
+        <v>603</v>
       </c>
       <c r="L24" t="s">
-        <v>592</v>
+        <v>604</v>
       </c>
       <c r="M24" t="s">
-        <v>593</v>
+        <v>605</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>594</v>
+        <v>606</v>
       </c>
       <c r="D25" t="s">
-        <v>578</v>
+        <v>590</v>
       </c>
       <c r="E25" t="s">
-        <v>595</v>
+        <v>607</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9590,22 +9714,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>596</v>
+        <v>608</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>597</v>
+        <v>609</v>
       </c>
       <c r="K25" t="s">
-        <v>598</v>
+        <v>610</v>
       </c>
       <c r="L25" t="s">
-        <v>599</v>
+        <v>611</v>
       </c>
       <c r="M25" t="s">
-        <v>600</v>
+        <v>612</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9613,10 +9737,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>601</v>
+        <v>613</v>
       </c>
       <c r="D26" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9628,22 +9752,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>603</v>
+        <v>615</v>
       </c>
       <c r="I26" t="s">
-        <v>604</v>
+        <v>616</v>
       </c>
       <c r="J26" t="s">
-        <v>605</v>
+        <v>617</v>
       </c>
       <c r="K26" t="s">
-        <v>606</v>
+        <v>618</v>
       </c>
       <c r="L26" t="s">
-        <v>607</v>
+        <v>619</v>
       </c>
       <c r="M26" t="s">
-        <v>608</v>
+        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9651,13 +9775,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>609</v>
+        <v>621</v>
       </c>
       <c r="D27" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E27" t="s">
-        <v>610</v>
+        <v>622</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9666,36 +9790,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>611</v>
+        <v>623</v>
       </c>
       <c r="I27" t="s">
-        <v>612</v>
+        <v>624</v>
       </c>
       <c r="J27" t="s">
-        <v>613</v>
+        <v>625</v>
       </c>
       <c r="K27" t="s">
-        <v>614</v>
+        <v>626</v>
       </c>
       <c r="L27" t="s">
-        <v>615</v>
+        <v>627</v>
       </c>
       <c r="M27" t="s">
-        <v>616</v>
+        <v>628</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>617</v>
+        <v>629</v>
       </c>
       <c r="D28" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9707,36 +9831,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>618</v>
+        <v>630</v>
       </c>
       <c r="I28" t="s">
-        <v>619</v>
+        <v>631</v>
       </c>
       <c r="J28" t="s">
-        <v>620</v>
+        <v>632</v>
       </c>
       <c r="K28" t="s">
-        <v>621</v>
+        <v>633</v>
       </c>
       <c r="L28" t="s">
-        <v>622</v>
+        <v>634</v>
       </c>
       <c r="M28" t="s">
-        <v>623</v>
+        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>624</v>
+        <v>636</v>
       </c>
       <c r="D29" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9748,36 +9872,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>625</v>
+        <v>637</v>
       </c>
       <c r="I29" t="s">
-        <v>626</v>
+        <v>638</v>
       </c>
       <c r="J29" t="s">
-        <v>627</v>
+        <v>639</v>
       </c>
       <c r="K29" t="s">
-        <v>628</v>
+        <v>640</v>
       </c>
       <c r="L29" t="s">
-        <v>629</v>
+        <v>641</v>
       </c>
       <c r="M29" t="s">
-        <v>630</v>
+        <v>642</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>631</v>
+        <v>643</v>
       </c>
       <c r="D30" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9789,39 +9913,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>632</v>
+        <v>644</v>
       </c>
       <c r="I30" t="s">
-        <v>633</v>
+        <v>645</v>
       </c>
       <c r="J30" t="s">
-        <v>634</v>
+        <v>646</v>
       </c>
       <c r="K30" t="s">
-        <v>635</v>
+        <v>647</v>
       </c>
       <c r="L30" t="s">
-        <v>636</v>
+        <v>648</v>
       </c>
       <c r="M30" t="s">
-        <v>637</v>
+        <v>649</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>387</v>
+        <v>399</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>638</v>
+        <v>650</v>
       </c>
       <c r="D31" t="s">
-        <v>602</v>
+        <v>614</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>281</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9830,22 +9954,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>639</v>
+        <v>651</v>
       </c>
       <c r="I31" t="s">
-        <v>640</v>
+        <v>652</v>
       </c>
       <c r="J31" t="s">
-        <v>641</v>
+        <v>653</v>
       </c>
       <c r="K31" t="s">
-        <v>642</v>
+        <v>654</v>
       </c>
       <c r="L31" t="s">
-        <v>643</v>
+        <v>655</v>
       </c>
       <c r="M31" t="s">
-        <v>644</v>
+        <v>656</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9853,13 +9977,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>645</v>
+        <v>657</v>
       </c>
       <c r="D32" t="s">
-        <v>443</v>
+        <v>455</v>
       </c>
       <c r="E32" t="s">
-        <v>646</v>
+        <v>658</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9868,22 +9992,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>647</v>
+        <v>659</v>
       </c>
       <c r="I32" t="s">
-        <v>648</v>
+        <v>660</v>
       </c>
       <c r="J32" t="s">
-        <v>649</v>
+        <v>661</v>
       </c>
       <c r="K32" t="s">
-        <v>650</v>
+        <v>662</v>
       </c>
       <c r="L32" t="s">
-        <v>651</v>
+        <v>663</v>
       </c>
       <c r="M32" t="s">
-        <v>652</v>
+        <v>664</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="10"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -17,6 +17,7 @@
     <sheet name="BGMList" sheetId="12" r:id="rId8"/>
     <sheet name="Achievement" sheetId="13" r:id="rId9"/>
     <sheet name="PlayerStatistic" sheetId="14" r:id="rId10"/>
+    <sheet name="InteractionHintConfig" sheetId="15" r:id="rId11"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1504" uniqueCount="874">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="914">
   <si>
     <t>Dog</t>
   </si>
@@ -581,15 +582,6 @@
     <t>正常循环阶段允许玩家在 Steam 库存中累计的盲盒成本券数量上限。客户端统计对应 ItemDef 的所有实例及堆叠数量；达到上限时暂停调用循环 PlaytimeGenerator，消耗后低于上限时恢复请求。填 0 表示不限制。</t>
   </si>
   <si>
-    <t>ProactiveInteractionHintIdleSeconds</t>
-  </si>
-  <si>
-    <t>新手操作提示等待时间</t>
-  </si>
-  <si>
-    <t>秒；当玩家在规定时间内无正确操作时，需要操作的目标会作出相应的提示动作</t>
-  </si>
-  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -2658,6 +2650,135 @@
   </si>
   <si>
     <t>游戏运行期间，按系统本地时间的自然半小时分段累计键鼠获得的筹码；首尾分段可能不足 30 分钟。</t>
+  </si>
+  <si>
+    <t>Key</t>
+  </si>
+  <si>
+    <t>Description</t>
+  </si>
+  <si>
+    <t>ProactiveEnabled</t>
+  </si>
+  <si>
+    <t>ProactiveIdleSeconds</t>
+  </si>
+  <si>
+    <t>ProactiveRepeatSeconds</t>
+  </si>
+  <si>
+    <t>PassiveCooldownSeconds</t>
+  </si>
+  <si>
+    <t>唯一配置键</t>
+  </si>
+  <si>
+    <t>中文说明</t>
+  </si>
+  <si>
+    <t>是否启用主动提示</t>
+  </si>
+  <si>
+    <t>首次主动提示前的无操作等待秒数</t>
+  </si>
+  <si>
+    <t>提示播放完后再次提示前的等待秒数，0表示不重复</t>
+  </si>
+  <si>
+    <t>动画本身的时间算是基础间隔，需要加上这个字段用于额外间隔</t>
+  </si>
+  <si>
+    <t>多个提示同时可用时数值越高越优先</t>
+  </si>
+  <si>
+    <t>策划备注</t>
+  </si>
+  <si>
+    <t>配置键</t>
+  </si>
+  <si>
+    <t>启用主动提示</t>
+  </si>
+  <si>
+    <t>首次等待秒数</t>
+  </si>
+  <si>
+    <t>重复等待秒数</t>
+  </si>
+  <si>
+    <t>被动提示额外间隔秒数</t>
+  </si>
+  <si>
+    <t>Poker.WaitingForBet.Refreshment</t>
+  </si>
+  <si>
+    <t>准备下注：提示点击桌面消耗品</t>
+  </si>
+  <si>
+    <t>仅 ReadyToUse 时有效；优先于下注筹码</t>
+  </si>
+  <si>
+    <t>Poker.WaitingForBet.BetStack</t>
+  </si>
+  <si>
+    <t>准备下注：提示点击下注筹码</t>
+  </si>
+  <si>
+    <t>没有可提示的桌面消耗品时生效</t>
+  </si>
+  <si>
+    <t>Poker.Refreshment.UseConfirm</t>
+  </si>
+  <si>
+    <t>消耗品气球已打开：提示点击对号或酒杯</t>
+  </si>
+  <si>
+    <t>气球状态独占优先级；触发后解锁酒杯作为备用确认入口</t>
+  </si>
+  <si>
+    <t>Poker.Dealt.CardSelection</t>
+  </si>
+  <si>
+    <t>发牌后：提示选择需要替换的牌</t>
+  </si>
+  <si>
+    <t>默认全保留且尚未询问小狗时使用</t>
+  </si>
+  <si>
+    <t>Poker.Dealt.DogAdvice</t>
+  </si>
+  <si>
+    <t>发牌后：提示点击小狗询问建议</t>
+  </si>
+  <si>
+    <t>当前阶段可询问小狗时使用</t>
+  </si>
+  <si>
+    <t>Poker.Dealt.HandConfirm</t>
+  </si>
+  <si>
+    <t>发牌后：提示敲桌确认</t>
+  </si>
+  <si>
+    <t>当前手牌已形成可计分组合时使用</t>
+  </si>
+  <si>
+    <t>Poker.Holding.HandConfirm</t>
+  </si>
+  <si>
+    <t>调整保留牌后：提示敲桌确认</t>
+  </si>
+  <si>
+    <t>玩家已调整保留牌或已获得小狗建议后使用</t>
+  </si>
+  <si>
+    <t>Poker.Settled.RewardStack</t>
+  </si>
+  <si>
+    <t>结算后：提示领取奖励筹码</t>
+  </si>
+  <si>
+    <t>存在可领取奖励筹码时使用</t>
   </si>
 </sst>
 </file>
@@ -4246,28 +4367,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>662</v>
+      </c>
+      <c r="C1" t="s">
+        <v>663</v>
+      </c>
+      <c r="D1" t="s">
+        <v>664</v>
+      </c>
+      <c r="E1" t="s">
         <v>665</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>666</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>667</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
         <v>668</v>
       </c>
-      <c r="F1" t="s">
-        <v>669</v>
-      </c>
-      <c r="G1" t="s">
-        <v>670</v>
-      </c>
-      <c r="H1" t="s">
-        <v>671</v>
-      </c>
       <c r="I1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4284,16 +4405,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>672</v>
+        <v>669</v>
       </c>
       <c r="F2" t="s">
-        <v>673</v>
+        <v>670</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4304,28 +4425,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>671</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>672</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>673</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>674</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>675</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>676</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>677</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>679</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>680</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>681</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4333,1333 +4454,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>679</v>
+      </c>
+      <c r="C4" t="s">
+        <v>680</v>
+      </c>
+      <c r="D4" t="s">
+        <v>263</v>
+      </c>
+      <c r="E4" t="s">
+        <v>681</v>
+      </c>
+      <c r="F4" t="s">
         <v>682</v>
       </c>
-      <c r="C4" t="s">
+      <c r="G4" t="s">
         <v>683</v>
       </c>
-      <c r="D4" t="s">
-        <v>266</v>
-      </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>684</v>
       </c>
-      <c r="F4" t="s">
-        <v>685</v>
-      </c>
-      <c r="G4" t="s">
-        <v>686</v>
-      </c>
-      <c r="H4" t="s">
-        <v>687</v>
-      </c>
       <c r="I4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>685</v>
+      </c>
+      <c r="D5" t="s">
+        <v>686</v>
+      </c>
+      <c r="E5" t="s">
+        <v>687</v>
+      </c>
+      <c r="F5" t="s">
         <v>688</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
         <v>689</v>
-      </c>
-      <c r="E5" t="s">
-        <v>690</v>
-      </c>
-      <c r="F5" t="s">
-        <v>691</v>
-      </c>
-      <c r="G5" t="s">
-        <v>692</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>693</v>
+        <v>690</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
+        <v>691</v>
+      </c>
+      <c r="D6" t="s">
+        <v>692</v>
+      </c>
+      <c r="E6" t="s">
+        <v>693</v>
+      </c>
+      <c r="F6" t="s">
+        <v>688</v>
+      </c>
+      <c r="G6" t="s">
         <v>694</v>
-      </c>
-      <c r="D6" t="s">
-        <v>695</v>
-      </c>
-      <c r="E6" t="s">
-        <v>696</v>
-      </c>
-      <c r="F6" t="s">
-        <v>691</v>
-      </c>
-      <c r="G6" t="s">
-        <v>697</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>698</v>
+        <v>695</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>699</v>
+        <v>696</v>
       </c>
       <c r="D7" t="s">
-        <v>700</v>
+        <v>697</v>
       </c>
       <c r="E7" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F7" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G7" t="s">
-        <v>701</v>
+        <v>698</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>702</v>
+        <v>699</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>703</v>
+        <v>700</v>
       </c>
       <c r="D8" t="s">
-        <v>704</v>
+        <v>701</v>
       </c>
       <c r="E8" t="s">
-        <v>690</v>
+        <v>687</v>
       </c>
       <c r="F8" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G8" t="s">
-        <v>705</v>
+        <v>702</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>706</v>
+        <v>703</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>707</v>
+        <v>704</v>
       </c>
       <c r="D9" t="s">
-        <v>708</v>
+        <v>705</v>
       </c>
       <c r="E9" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F9" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G9" t="s">
-        <v>709</v>
+        <v>706</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>710</v>
+        <v>707</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>708</v>
+      </c>
+      <c r="D10" t="s">
+        <v>709</v>
+      </c>
+      <c r="E10" t="s">
+        <v>710</v>
+      </c>
+      <c r="F10" t="s">
+        <v>688</v>
+      </c>
+      <c r="G10" t="s">
         <v>711</v>
-      </c>
-      <c r="D10" t="s">
-        <v>712</v>
-      </c>
-      <c r="E10" t="s">
-        <v>713</v>
-      </c>
-      <c r="F10" t="s">
-        <v>691</v>
-      </c>
-      <c r="G10" t="s">
-        <v>714</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>715</v>
+        <v>712</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>716</v>
+        <v>713</v>
       </c>
       <c r="D11" t="s">
-        <v>717</v>
+        <v>714</v>
       </c>
       <c r="E11" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F11" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G11" t="s">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>719</v>
+        <v>716</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>720</v>
+        <v>717</v>
       </c>
       <c r="D12" t="s">
-        <v>721</v>
+        <v>718</v>
       </c>
       <c r="E12" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F12" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G12" t="s">
-        <v>722</v>
+        <v>719</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>723</v>
+        <v>720</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>724</v>
+        <v>721</v>
       </c>
       <c r="D13" t="s">
-        <v>725</v>
+        <v>722</v>
       </c>
       <c r="E13" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F13" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G13" t="s">
-        <v>726</v>
+        <v>723</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>727</v>
+        <v>724</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>728</v>
+        <v>725</v>
       </c>
       <c r="D14" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="E14" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F14" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G14" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>732</v>
+        <v>729</v>
       </c>
       <c r="D15" t="s">
-        <v>733</v>
+        <v>730</v>
       </c>
       <c r="E15" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F15" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G15" t="s">
-        <v>734</v>
+        <v>731</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>735</v>
+        <v>732</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>736</v>
+        <v>733</v>
       </c>
       <c r="D16" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="E16" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F16" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G16" t="s">
-        <v>738</v>
+        <v>735</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>739</v>
+        <v>736</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>740</v>
+        <v>737</v>
       </c>
       <c r="D17" t="s">
-        <v>741</v>
+        <v>738</v>
       </c>
       <c r="E17" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F17" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G17" t="s">
-        <v>742</v>
+        <v>739</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>743</v>
+        <v>740</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>744</v>
+        <v>741</v>
       </c>
       <c r="D18" t="s">
-        <v>745</v>
+        <v>742</v>
       </c>
       <c r="E18" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F18" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G18" t="s">
-        <v>746</v>
+        <v>743</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="D19" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E19" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F19" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G19" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>750</v>
+        <v>747</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="D20" t="s">
-        <v>751</v>
+        <v>748</v>
       </c>
       <c r="E20" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F20" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G20" t="s">
-        <v>752</v>
+        <v>749</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>753</v>
+        <v>750</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="D21" t="s">
-        <v>754</v>
+        <v>751</v>
       </c>
       <c r="E21" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F21" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G21" t="s">
-        <v>755</v>
+        <v>752</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>756</v>
+        <v>753</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="D22" t="s">
-        <v>757</v>
+        <v>754</v>
       </c>
       <c r="E22" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F22" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G22" t="s">
-        <v>758</v>
+        <v>755</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>759</v>
+        <v>756</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="D23" t="s">
-        <v>760</v>
+        <v>757</v>
       </c>
       <c r="E23" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F23" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G23" t="s">
-        <v>761</v>
+        <v>758</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>762</v>
+        <v>759</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="D24" t="s">
-        <v>763</v>
+        <v>760</v>
       </c>
       <c r="E24" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F24" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G24" t="s">
-        <v>764</v>
+        <v>761</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>765</v>
+        <v>762</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="D25" t="s">
-        <v>766</v>
+        <v>763</v>
       </c>
       <c r="E25" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F25" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G25" t="s">
-        <v>767</v>
+        <v>764</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>768</v>
+        <v>765</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>769</v>
+        <v>766</v>
       </c>
       <c r="D26" t="s">
-        <v>770</v>
+        <v>767</v>
       </c>
       <c r="E26" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F26" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G26" t="s">
-        <v>771</v>
+        <v>768</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>772</v>
+        <v>769</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>773</v>
+        <v>770</v>
       </c>
       <c r="D27" t="s">
-        <v>774</v>
+        <v>771</v>
       </c>
       <c r="E27" t="s">
-        <v>713</v>
+        <v>710</v>
       </c>
       <c r="F27" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G27" t="s">
-        <v>775</v>
+        <v>772</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>776</v>
+        <v>773</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>777</v>
+        <v>774</v>
       </c>
       <c r="D28" t="s">
-        <v>778</v>
+        <v>775</v>
       </c>
       <c r="E28" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F28" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G28" t="s">
-        <v>779</v>
+        <v>776</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>780</v>
+        <v>777</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>781</v>
+        <v>778</v>
       </c>
       <c r="D29" t="s">
-        <v>782</v>
+        <v>779</v>
       </c>
       <c r="E29" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F29" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G29" t="s">
-        <v>783</v>
+        <v>780</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>784</v>
+        <v>781</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>785</v>
+        <v>782</v>
       </c>
       <c r="D30" t="s">
-        <v>786</v>
+        <v>783</v>
       </c>
       <c r="E30" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F30" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G30" t="s">
-        <v>787</v>
+        <v>784</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>788</v>
+        <v>785</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>789</v>
+        <v>786</v>
       </c>
       <c r="D31" t="s">
-        <v>790</v>
+        <v>787</v>
       </c>
       <c r="E31" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F31" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G31" t="s">
-        <v>791</v>
+        <v>788</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>792</v>
+        <v>789</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>793</v>
+        <v>790</v>
       </c>
       <c r="D32" t="s">
-        <v>794</v>
+        <v>791</v>
       </c>
       <c r="E32" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F32" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G32" t="s">
-        <v>795</v>
+        <v>792</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>796</v>
+        <v>793</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>797</v>
+        <v>794</v>
       </c>
       <c r="D33" t="s">
-        <v>798</v>
+        <v>795</v>
       </c>
       <c r="E33" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F33" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G33" t="s">
-        <v>799</v>
+        <v>796</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>800</v>
+        <v>797</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>801</v>
+        <v>798</v>
       </c>
       <c r="D34" t="s">
-        <v>802</v>
+        <v>799</v>
       </c>
       <c r="E34" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F34" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G34" t="s">
-        <v>803</v>
+        <v>800</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>804</v>
+        <v>801</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>805</v>
+        <v>802</v>
       </c>
       <c r="D35" t="s">
-        <v>806</v>
+        <v>803</v>
       </c>
       <c r="E35" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F35" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G35" t="s">
-        <v>807</v>
+        <v>804</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>808</v>
+        <v>805</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>809</v>
+        <v>806</v>
       </c>
       <c r="D36" t="s">
-        <v>810</v>
+        <v>807</v>
       </c>
       <c r="E36" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F36" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G36" t="s">
-        <v>811</v>
+        <v>808</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>812</v>
+        <v>809</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>813</v>
+        <v>810</v>
       </c>
       <c r="D37" t="s">
-        <v>814</v>
+        <v>811</v>
       </c>
       <c r="E37" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F37" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G37" t="s">
-        <v>815</v>
+        <v>812</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>816</v>
+        <v>813</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>817</v>
+        <v>814</v>
       </c>
       <c r="D38" t="s">
-        <v>818</v>
+        <v>815</v>
       </c>
       <c r="E38" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F38" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G38" t="s">
-        <v>819</v>
+        <v>816</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>820</v>
+        <v>817</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>821</v>
+        <v>818</v>
       </c>
       <c r="D39" t="s">
-        <v>822</v>
+        <v>819</v>
       </c>
       <c r="E39" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F39" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G39" t="s">
-        <v>823</v>
+        <v>820</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>824</v>
+        <v>821</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>825</v>
+        <v>822</v>
       </c>
       <c r="D40" t="s">
-        <v>826</v>
+        <v>823</v>
       </c>
       <c r="E40" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F40" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G40" t="s">
-        <v>827</v>
+        <v>824</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>828</v>
+        <v>825</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>829</v>
+        <v>826</v>
       </c>
       <c r="D41" t="s">
-        <v>830</v>
+        <v>827</v>
       </c>
       <c r="E41" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F41" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G41" t="s">
-        <v>831</v>
+        <v>828</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>832</v>
+        <v>829</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>833</v>
+        <v>830</v>
       </c>
       <c r="D42" t="s">
-        <v>834</v>
+        <v>831</v>
       </c>
       <c r="E42" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F42" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G42" t="s">
-        <v>835</v>
+        <v>832</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>836</v>
+        <v>833</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>837</v>
+        <v>834</v>
       </c>
       <c r="D43" t="s">
-        <v>838</v>
+        <v>835</v>
       </c>
       <c r="E43" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F43" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G43" t="s">
-        <v>839</v>
+        <v>836</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>840</v>
+        <v>837</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>841</v>
+        <v>838</v>
       </c>
       <c r="D44" t="s">
-        <v>842</v>
+        <v>839</v>
       </c>
       <c r="E44" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F44" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G44" t="s">
-        <v>843</v>
+        <v>840</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>844</v>
+        <v>841</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>845</v>
+        <v>842</v>
       </c>
       <c r="D45" t="s">
-        <v>846</v>
+        <v>843</v>
       </c>
       <c r="E45" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F45" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G45" t="s">
-        <v>847</v>
+        <v>844</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>848</v>
+        <v>845</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>849</v>
+        <v>846</v>
       </c>
       <c r="D46" t="s">
-        <v>850</v>
+        <v>847</v>
       </c>
       <c r="E46" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F46" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G46" t="s">
-        <v>851</v>
+        <v>848</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>852</v>
+        <v>849</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>853</v>
+        <v>850</v>
       </c>
       <c r="D47" t="s">
-        <v>854</v>
+        <v>851</v>
       </c>
       <c r="E47" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F47" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G47" t="s">
-        <v>855</v>
+        <v>852</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>856</v>
+        <v>853</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>857</v>
+        <v>854</v>
       </c>
       <c r="D48" t="s">
-        <v>858</v>
+        <v>855</v>
       </c>
       <c r="E48" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F48" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G48" t="s">
-        <v>859</v>
+        <v>856</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>860</v>
+        <v>857</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>861</v>
+        <v>858</v>
       </c>
       <c r="D49" t="s">
-        <v>862</v>
+        <v>859</v>
       </c>
       <c r="E49" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F49" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G49" t="s">
-        <v>863</v>
+        <v>860</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>864</v>
+        <v>861</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5667,25 +5788,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>865</v>
+        <v>862</v>
       </c>
       <c r="D50" t="s">
-        <v>866</v>
+        <v>863</v>
       </c>
       <c r="E50" t="s">
-        <v>696</v>
+        <v>693</v>
       </c>
       <c r="F50" t="s">
-        <v>691</v>
+        <v>688</v>
       </c>
       <c r="G50" t="s">
-        <v>867</v>
+        <v>864</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>868</v>
+        <v>865</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5693,25 +5814,389 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
+        <v>866</v>
+      </c>
+      <c r="D51" t="s">
+        <v>867</v>
+      </c>
+      <c r="E51" t="s">
+        <v>710</v>
+      </c>
+      <c r="F51" t="s">
+        <v>868</v>
+      </c>
+      <c r="G51" t="s">
         <v>869</v>
-      </c>
-      <c r="D51" t="s">
-        <v>870</v>
-      </c>
-      <c r="E51" t="s">
-        <v>713</v>
-      </c>
-      <c r="F51" t="s">
-        <v>871</v>
-      </c>
-      <c r="G51" t="s">
-        <v>872</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
+        <v>870</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:I12"/>
+  <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
+  <cols>
+    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
+    <col min="2" max="2" width="29.75" customWidth="1"/>
+    <col min="3" max="3" width="33.3333333333333" customWidth="1"/>
+    <col min="4" max="4" width="15.4166666666667" customWidth="1"/>
+    <col min="5" max="5" width="27.8333333333333" customWidth="1"/>
+    <col min="6" max="7" width="41.75" customWidth="1"/>
+    <col min="8" max="8" width="29.6666666666667" customWidth="1"/>
+    <col min="9" max="9" width="46.1666666666667" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9">
+      <c r="A1" t="s">
+        <v>98</v>
+      </c>
+      <c r="B1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C1" t="s">
+        <v>872</v>
+      </c>
+      <c r="D1" t="s">
         <v>873</v>
+      </c>
+      <c r="E1" t="s">
+        <v>874</v>
+      </c>
+      <c r="F1" t="s">
+        <v>875</v>
+      </c>
+      <c r="G1" t="s">
+        <v>876</v>
+      </c>
+      <c r="H1" t="s">
+        <v>375</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9">
+      <c r="A2" t="s">
+        <v>106</v>
+      </c>
+      <c r="B2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D2" t="s">
+        <v>297</v>
+      </c>
+      <c r="E2" t="s">
+        <v>158</v>
+      </c>
+      <c r="F2" t="s">
+        <v>158</v>
+      </c>
+      <c r="G2" t="s">
+        <v>158</v>
+      </c>
+      <c r="H2" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="3" s="1" customFormat="1" ht="34.8" spans="1:9">
+      <c r="A3" s="1" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>882</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>883</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>884</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9">
+      <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="B4" t="s">
+        <v>885</v>
+      </c>
+      <c r="C4" t="s">
+        <v>878</v>
+      </c>
+      <c r="D4" t="s">
+        <v>886</v>
+      </c>
+      <c r="E4" t="s">
+        <v>887</v>
+      </c>
+      <c r="F4" t="s">
+        <v>888</v>
+      </c>
+      <c r="G4" t="s">
+        <v>889</v>
+      </c>
+      <c r="H4" t="s">
+        <v>392</v>
+      </c>
+      <c r="I4" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9">
+      <c r="A5" t="s">
+        <v>396</v>
+      </c>
+      <c r="B5" t="s">
+        <v>890</v>
+      </c>
+      <c r="C5" t="s">
+        <v>891</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
+      </c>
+      <c r="E5">
+        <v>5</v>
+      </c>
+      <c r="F5">
+        <v>0.8</v>
+      </c>
+      <c r="G5">
+        <v>0.5</v>
+      </c>
+      <c r="H5">
+        <v>200</v>
+      </c>
+      <c r="I5" t="s">
+        <v>892</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9">
+      <c r="A6" t="s">
+        <v>396</v>
+      </c>
+      <c r="B6" t="s">
+        <v>893</v>
+      </c>
+      <c r="C6" t="s">
+        <v>894</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
+      </c>
+      <c r="E6">
+        <v>5</v>
+      </c>
+      <c r="F6">
+        <v>0.8</v>
+      </c>
+      <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>100</v>
+      </c>
+      <c r="I6" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9">
+      <c r="A7" t="s">
+        <v>396</v>
+      </c>
+      <c r="B7" t="s">
+        <v>896</v>
+      </c>
+      <c r="C7" t="s">
+        <v>897</v>
+      </c>
+      <c r="D7" t="b">
+        <v>1</v>
+      </c>
+      <c r="E7">
+        <v>3</v>
+      </c>
+      <c r="F7">
+        <v>0.8</v>
+      </c>
+      <c r="G7">
+        <v>0</v>
+      </c>
+      <c r="H7">
+        <v>300</v>
+      </c>
+      <c r="I7" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9">
+      <c r="A8" t="s">
+        <v>396</v>
+      </c>
+      <c r="B8" t="s">
+        <v>899</v>
+      </c>
+      <c r="C8" t="s">
+        <v>900</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>6</v>
+      </c>
+      <c r="F8">
+        <v>0.8</v>
+      </c>
+      <c r="G8">
+        <v>0.5</v>
+      </c>
+      <c r="H8">
+        <v>100</v>
+      </c>
+      <c r="I8" t="s">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9">
+      <c r="A9" t="s">
+        <v>396</v>
+      </c>
+      <c r="B9" t="s">
+        <v>902</v>
+      </c>
+      <c r="C9" t="s">
+        <v>903</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
+      </c>
+      <c r="E9">
+        <v>5</v>
+      </c>
+      <c r="F9">
+        <v>0.8</v>
+      </c>
+      <c r="G9">
+        <v>0</v>
+      </c>
+      <c r="H9">
+        <v>100</v>
+      </c>
+      <c r="I9" t="s">
+        <v>904</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9">
+      <c r="A10" t="s">
+        <v>396</v>
+      </c>
+      <c r="B10" t="s">
+        <v>905</v>
+      </c>
+      <c r="C10" t="s">
+        <v>906</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
+      </c>
+      <c r="E10">
+        <v>12</v>
+      </c>
+      <c r="F10">
+        <v>1.2</v>
+      </c>
+      <c r="G10">
+        <v>1.2</v>
+      </c>
+      <c r="H10">
+        <v>100</v>
+      </c>
+      <c r="I10" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9">
+      <c r="A11" t="s">
+        <v>396</v>
+      </c>
+      <c r="B11" t="s">
+        <v>908</v>
+      </c>
+      <c r="C11" t="s">
+        <v>909</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
+      </c>
+      <c r="E11">
+        <v>9</v>
+      </c>
+      <c r="F11">
+        <v>1.2</v>
+      </c>
+      <c r="G11">
+        <v>1.2</v>
+      </c>
+      <c r="H11">
+        <v>100</v>
+      </c>
+      <c r="I11" t="s">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9">
+      <c r="A12" t="s">
+        <v>396</v>
+      </c>
+      <c r="B12" t="s">
+        <v>911</v>
+      </c>
+      <c r="C12" t="s">
+        <v>912</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
+      </c>
+      <c r="E12">
+        <v>5</v>
+      </c>
+      <c r="F12">
+        <v>0.8</v>
+      </c>
+      <c r="G12">
+        <v>0</v>
+      </c>
+      <c r="H12">
+        <v>100</v>
+      </c>
+      <c r="I12" t="s">
+        <v>913</v>
       </c>
     </row>
   </sheetData>
@@ -6232,23 +6717,6 @@
       </c>
       <c r="E10" s="2" t="s">
         <v>180</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" t="s">
-        <v>181</v>
-      </c>
-      <c r="B11" t="s">
-        <v>182</v>
-      </c>
-      <c r="C11" t="s">
-        <v>107</v>
-      </c>
-      <c r="D11">
-        <v>6</v>
-      </c>
-      <c r="E11" t="s">
-        <v>183</v>
       </c>
     </row>
     <row r="17" spans="5:8">
@@ -6308,55 +6776,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>182</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>183</v>
+      </c>
+      <c r="G1" s="2" t="s">
         <v>184</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="H1" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="I1" s="2" t="s">
         <v>186</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="J1" t="s">
         <v>187</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="K1" t="s">
         <v>188</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="L1" t="s">
         <v>189</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>190</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>191</v>
       </c>
-      <c r="L1" t="s">
+      <c r="O1" t="s">
         <v>192</v>
       </c>
-      <c r="M1" t="s">
+      <c r="P1" t="s">
         <v>193</v>
       </c>
-      <c r="N1" t="s">
+      <c r="Q1" t="s">
         <v>194</v>
       </c>
-      <c r="O1" t="s">
+      <c r="R1" t="s">
         <v>195</v>
       </c>
-      <c r="P1" t="s">
+      <c r="S1" t="s">
         <v>196</v>
       </c>
-      <c r="Q1" t="s">
+      <c r="T1" t="s">
         <v>197</v>
-      </c>
-      <c r="R1" t="s">
-        <v>198</v>
-      </c>
-      <c r="S1" t="s">
-        <v>199</v>
-      </c>
-      <c r="T1" t="s">
-        <v>200</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6427,10 +6895,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6444,55 +6912,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
+        <v>199</v>
+      </c>
+      <c r="D4" t="s">
+        <v>200</v>
+      </c>
+      <c r="E4" t="s">
+        <v>201</v>
+      </c>
+      <c r="F4" t="s">
         <v>202</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>203</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>204</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>205</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>206</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>207</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>208</v>
       </c>
-      <c r="K4" t="s">
+      <c r="N4" t="s">
         <v>209</v>
       </c>
-      <c r="L4" t="s">
+      <c r="O4" t="s">
         <v>210</v>
       </c>
-      <c r="M4" t="s">
+      <c r="P4" t="s">
         <v>211</v>
       </c>
-      <c r="N4" t="s">
+      <c r="Q4" t="s">
         <v>212</v>
       </c>
-      <c r="O4" t="s">
+      <c r="R4" t="s">
         <v>213</v>
       </c>
-      <c r="P4" t="s">
+      <c r="S4" t="s">
         <v>214</v>
       </c>
-      <c r="Q4" t="s">
+      <c r="T4" t="s">
         <v>215</v>
-      </c>
-      <c r="R4" t="s">
-        <v>216</v>
-      </c>
-      <c r="S4" t="s">
-        <v>217</v>
-      </c>
-      <c r="T4" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6500,58 +6968,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>216</v>
+      </c>
+      <c r="D5" t="s">
+        <v>217</v>
+      </c>
+      <c r="E5" t="s">
+        <v>218</v>
+      </c>
+      <c r="F5" t="s">
         <v>219</v>
       </c>
-      <c r="D5" t="s">
+      <c r="G5" t="s">
+        <v>189</v>
+      </c>
+      <c r="H5" t="s">
         <v>220</v>
       </c>
-      <c r="E5" t="s">
+      <c r="I5" t="s">
         <v>221</v>
       </c>
-      <c r="F5" t="s">
+      <c r="J5" t="s">
         <v>222</v>
       </c>
-      <c r="G5" t="s">
-        <v>192</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="K5" t="s">
         <v>223</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>224</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
+        <v>218</v>
+      </c>
+      <c r="N5" t="s">
         <v>225</v>
       </c>
-      <c r="K5" t="s">
+      <c r="O5" t="s">
         <v>226</v>
       </c>
-      <c r="L5" t="s">
+      <c r="P5" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q5" t="s">
         <v>227</v>
       </c>
-      <c r="M5" t="s">
-        <v>221</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="R5" t="s">
         <v>228</v>
       </c>
-      <c r="O5" t="s">
+      <c r="S5" t="s">
         <v>229</v>
       </c>
-      <c r="P5" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>230</v>
-      </c>
-      <c r="R5" t="s">
-        <v>231</v>
-      </c>
-      <c r="S5" t="s">
-        <v>232</v>
-      </c>
-      <c r="T5" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6559,58 +7027,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="D6" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="E6" t="s">
+        <v>218</v>
+      </c>
+      <c r="F6" t="s">
+        <v>227</v>
+      </c>
+      <c r="G6" t="s">
+        <v>189</v>
+      </c>
+      <c r="H6" t="s">
+        <v>233</v>
+      </c>
+      <c r="I6" t="s">
         <v>221</v>
       </c>
-      <c r="F6" t="s">
+      <c r="J6" t="s">
+        <v>222</v>
+      </c>
+      <c r="K6" t="s">
+        <v>223</v>
+      </c>
+      <c r="L6" t="s">
+        <v>224</v>
+      </c>
+      <c r="M6" t="s">
+        <v>218</v>
+      </c>
+      <c r="N6" t="s">
+        <v>225</v>
+      </c>
+      <c r="O6" t="s">
+        <v>226</v>
+      </c>
+      <c r="P6" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>227</v>
+      </c>
+      <c r="R6" t="s">
+        <v>228</v>
+      </c>
+      <c r="S6" t="s">
+        <v>229</v>
+      </c>
+      <c r="T6" t="s">
         <v>230</v>
-      </c>
-      <c r="G6" t="s">
-        <v>192</v>
-      </c>
-      <c r="H6" t="s">
-        <v>236</v>
-      </c>
-      <c r="I6" t="s">
-        <v>224</v>
-      </c>
-      <c r="J6" t="s">
-        <v>225</v>
-      </c>
-      <c r="K6" t="s">
-        <v>226</v>
-      </c>
-      <c r="L6" t="s">
-        <v>227</v>
-      </c>
-      <c r="M6" t="s">
-        <v>221</v>
-      </c>
-      <c r="N6" t="s">
-        <v>228</v>
-      </c>
-      <c r="O6" t="s">
-        <v>229</v>
-      </c>
-      <c r="P6" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>230</v>
-      </c>
-      <c r="R6" t="s">
-        <v>231</v>
-      </c>
-      <c r="S6" t="s">
-        <v>232</v>
-      </c>
-      <c r="T6" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -6618,58 +7086,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="D7" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="E7" t="s">
+        <v>218</v>
+      </c>
+      <c r="F7" t="s">
+        <v>228</v>
+      </c>
+      <c r="G7" t="s">
+        <v>189</v>
+      </c>
+      <c r="H7" t="s">
+        <v>236</v>
+      </c>
+      <c r="I7" t="s">
         <v>221</v>
       </c>
-      <c r="F7" t="s">
-        <v>231</v>
-      </c>
-      <c r="G7" t="s">
-        <v>192</v>
-      </c>
-      <c r="H7" t="s">
-        <v>239</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="J7" t="s">
+        <v>222</v>
+      </c>
+      <c r="K7" t="s">
+        <v>223</v>
+      </c>
+      <c r="L7" t="s">
         <v>224</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
+        <v>218</v>
+      </c>
+      <c r="N7" t="s">
         <v>225</v>
       </c>
-      <c r="K7" t="s">
+      <c r="O7" t="s">
         <v>226</v>
       </c>
-      <c r="L7" t="s">
+      <c r="P7" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q7" t="s">
         <v>227</v>
       </c>
-      <c r="M7" t="s">
-        <v>221</v>
-      </c>
-      <c r="N7" t="s">
+      <c r="R7" t="s">
         <v>228</v>
       </c>
-      <c r="O7" t="s">
+      <c r="S7" t="s">
         <v>229</v>
       </c>
-      <c r="P7" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q7" t="s">
+      <c r="T7" t="s">
         <v>230</v>
-      </c>
-      <c r="R7" t="s">
-        <v>231</v>
-      </c>
-      <c r="S7" t="s">
-        <v>232</v>
-      </c>
-      <c r="T7" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -6677,58 +7145,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="D8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="E8" t="s">
+        <v>225</v>
+      </c>
+      <c r="F8" t="s">
+        <v>226</v>
+      </c>
+      <c r="G8" t="s">
+        <v>189</v>
+      </c>
+      <c r="H8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I8" t="s">
+        <v>221</v>
+      </c>
+      <c r="J8" t="s">
+        <v>222</v>
+      </c>
+      <c r="K8" t="s">
+        <v>223</v>
+      </c>
+      <c r="L8" t="s">
+        <v>224</v>
+      </c>
+      <c r="M8" t="s">
+        <v>218</v>
+      </c>
+      <c r="N8" t="s">
+        <v>225</v>
+      </c>
+      <c r="O8" t="s">
+        <v>226</v>
+      </c>
+      <c r="P8" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>227</v>
+      </c>
+      <c r="R8" t="s">
         <v>228</v>
       </c>
-      <c r="F8" t="s">
+      <c r="S8" t="s">
         <v>229</v>
       </c>
-      <c r="G8" t="s">
-        <v>192</v>
-      </c>
-      <c r="H8" t="s">
-        <v>242</v>
-      </c>
-      <c r="I8" t="s">
-        <v>224</v>
-      </c>
-      <c r="J8" t="s">
-        <v>225</v>
-      </c>
-      <c r="K8" t="s">
-        <v>226</v>
-      </c>
-      <c r="L8" t="s">
-        <v>227</v>
-      </c>
-      <c r="M8" t="s">
-        <v>221</v>
-      </c>
-      <c r="N8" t="s">
-        <v>228</v>
-      </c>
-      <c r="O8" t="s">
-        <v>229</v>
-      </c>
-      <c r="P8" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q8" t="s">
+      <c r="T8" t="s">
         <v>230</v>
-      </c>
-      <c r="R8" t="s">
-        <v>231</v>
-      </c>
-      <c r="S8" t="s">
-        <v>232</v>
-      </c>
-      <c r="T8" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -6736,58 +7204,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="D9" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="E9" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F9" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="G9" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H9" t="s">
+        <v>220</v>
+      </c>
+      <c r="I9" t="s">
+        <v>242</v>
+      </c>
+      <c r="J9" t="s">
+        <v>222</v>
+      </c>
+      <c r="K9" t="s">
         <v>223</v>
       </c>
-      <c r="I9" t="s">
-        <v>245</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="L9" t="s">
+        <v>224</v>
+      </c>
+      <c r="M9" t="s">
+        <v>218</v>
+      </c>
+      <c r="N9" t="s">
         <v>225</v>
       </c>
-      <c r="K9" t="s">
+      <c r="O9" t="s">
         <v>226</v>
       </c>
-      <c r="L9" t="s">
+      <c r="P9" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q9" t="s">
         <v>227</v>
       </c>
-      <c r="M9" t="s">
-        <v>221</v>
-      </c>
-      <c r="N9" t="s">
+      <c r="R9" t="s">
         <v>228</v>
       </c>
-      <c r="O9" t="s">
+      <c r="S9" t="s">
         <v>229</v>
       </c>
-      <c r="P9" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q9" t="s">
+      <c r="T9" t="s">
         <v>230</v>
-      </c>
-      <c r="R9" t="s">
-        <v>231</v>
-      </c>
-      <c r="S9" t="s">
-        <v>232</v>
-      </c>
-      <c r="T9" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -6795,58 +7263,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="D10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="E10" t="s">
+        <v>225</v>
+      </c>
+      <c r="F10" t="s">
+        <v>219</v>
+      </c>
+      <c r="G10" t="s">
+        <v>189</v>
+      </c>
+      <c r="H10" t="s">
+        <v>220</v>
+      </c>
+      <c r="I10" t="s">
+        <v>245</v>
+      </c>
+      <c r="J10" t="s">
+        <v>222</v>
+      </c>
+      <c r="K10" t="s">
+        <v>223</v>
+      </c>
+      <c r="L10" t="s">
+        <v>224</v>
+      </c>
+      <c r="M10" t="s">
+        <v>218</v>
+      </c>
+      <c r="N10" t="s">
+        <v>225</v>
+      </c>
+      <c r="O10" t="s">
+        <v>226</v>
+      </c>
+      <c r="P10" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>227</v>
+      </c>
+      <c r="R10" t="s">
         <v>228</v>
       </c>
-      <c r="F10" t="s">
-        <v>222</v>
-      </c>
-      <c r="G10" t="s">
-        <v>192</v>
-      </c>
-      <c r="H10" t="s">
-        <v>223</v>
-      </c>
-      <c r="I10" t="s">
-        <v>248</v>
-      </c>
-      <c r="J10" t="s">
-        <v>225</v>
-      </c>
-      <c r="K10" t="s">
-        <v>226</v>
-      </c>
-      <c r="L10" t="s">
-        <v>227</v>
-      </c>
-      <c r="M10" t="s">
-        <v>221</v>
-      </c>
-      <c r="N10" t="s">
-        <v>228</v>
-      </c>
-      <c r="O10" t="s">
+      <c r="S10" t="s">
         <v>229</v>
       </c>
-      <c r="P10" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q10" t="s">
+      <c r="T10" t="s">
         <v>230</v>
-      </c>
-      <c r="R10" t="s">
-        <v>231</v>
-      </c>
-      <c r="S10" t="s">
-        <v>232</v>
-      </c>
-      <c r="T10" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -6854,58 +7322,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="D11" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="E11" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F11" t="s">
+        <v>230</v>
+      </c>
+      <c r="G11" t="s">
+        <v>189</v>
+      </c>
+      <c r="H11" t="s">
         <v>233</v>
       </c>
-      <c r="G11" t="s">
-        <v>192</v>
-      </c>
-      <c r="H11" t="s">
-        <v>236</v>
-      </c>
       <c r="I11" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J11" t="s">
+        <v>222</v>
+      </c>
+      <c r="K11" t="s">
+        <v>223</v>
+      </c>
+      <c r="L11" t="s">
+        <v>224</v>
+      </c>
+      <c r="M11" t="s">
+        <v>218</v>
+      </c>
+      <c r="N11" t="s">
         <v>225</v>
       </c>
-      <c r="K11" t="s">
+      <c r="O11" t="s">
         <v>226</v>
       </c>
-      <c r="L11" t="s">
+      <c r="P11" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q11" t="s">
         <v>227</v>
       </c>
-      <c r="M11" t="s">
-        <v>221</v>
-      </c>
-      <c r="N11" t="s">
+      <c r="R11" t="s">
         <v>228</v>
       </c>
-      <c r="O11" t="s">
+      <c r="S11" t="s">
         <v>229</v>
       </c>
-      <c r="P11" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q11" t="s">
+      <c r="T11" t="s">
         <v>230</v>
-      </c>
-      <c r="R11" t="s">
-        <v>231</v>
-      </c>
-      <c r="S11" t="s">
-        <v>232</v>
-      </c>
-      <c r="T11" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -6913,58 +7381,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="D12" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="E12" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F12" t="s">
+        <v>219</v>
+      </c>
+      <c r="G12" t="s">
+        <v>189</v>
+      </c>
+      <c r="H12" t="s">
+        <v>233</v>
+      </c>
+      <c r="I12" t="s">
+        <v>245</v>
+      </c>
+      <c r="J12" t="s">
         <v>222</v>
       </c>
-      <c r="G12" t="s">
-        <v>192</v>
-      </c>
-      <c r="H12" t="s">
-        <v>236</v>
-      </c>
-      <c r="I12" t="s">
-        <v>248</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="K12" t="s">
+        <v>223</v>
+      </c>
+      <c r="L12" t="s">
+        <v>224</v>
+      </c>
+      <c r="M12" t="s">
+        <v>218</v>
+      </c>
+      <c r="N12" t="s">
         <v>225</v>
       </c>
-      <c r="K12" t="s">
+      <c r="O12" t="s">
         <v>226</v>
       </c>
-      <c r="L12" t="s">
+      <c r="P12" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q12" t="s">
         <v>227</v>
       </c>
-      <c r="M12" t="s">
-        <v>221</v>
-      </c>
-      <c r="N12" t="s">
+      <c r="R12" t="s">
         <v>228</v>
       </c>
-      <c r="O12" t="s">
+      <c r="S12" t="s">
         <v>229</v>
       </c>
-      <c r="P12" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q12" t="s">
+      <c r="T12" t="s">
         <v>230</v>
-      </c>
-      <c r="R12" t="s">
-        <v>231</v>
-      </c>
-      <c r="S12" t="s">
-        <v>232</v>
-      </c>
-      <c r="T12" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -6972,58 +7440,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="D13" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="E13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="G13" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H13" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I13" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="J13" t="s">
+        <v>222</v>
+      </c>
+      <c r="K13" t="s">
+        <v>223</v>
+      </c>
+      <c r="L13" t="s">
+        <v>224</v>
+      </c>
+      <c r="M13" t="s">
+        <v>218</v>
+      </c>
+      <c r="N13" t="s">
         <v>225</v>
       </c>
-      <c r="K13" t="s">
+      <c r="O13" t="s">
         <v>226</v>
       </c>
-      <c r="L13" t="s">
+      <c r="P13" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q13" t="s">
         <v>227</v>
       </c>
-      <c r="M13" t="s">
-        <v>221</v>
-      </c>
-      <c r="N13" t="s">
+      <c r="R13" t="s">
         <v>228</v>
       </c>
-      <c r="O13" t="s">
+      <c r="S13" t="s">
         <v>229</v>
       </c>
-      <c r="P13" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q13" t="s">
+      <c r="T13" t="s">
         <v>230</v>
-      </c>
-      <c r="R13" t="s">
-        <v>231</v>
-      </c>
-      <c r="S13" t="s">
-        <v>232</v>
-      </c>
-      <c r="T13" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -7031,58 +7499,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="D14" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="E14" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F14" t="s">
+        <v>219</v>
+      </c>
+      <c r="G14" t="s">
+        <v>189</v>
+      </c>
+      <c r="H14" t="s">
+        <v>236</v>
+      </c>
+      <c r="I14" t="s">
+        <v>245</v>
+      </c>
+      <c r="J14" t="s">
         <v>222</v>
       </c>
-      <c r="G14" t="s">
-        <v>192</v>
-      </c>
-      <c r="H14" t="s">
-        <v>239</v>
-      </c>
-      <c r="I14" t="s">
-        <v>248</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="K14" t="s">
+        <v>223</v>
+      </c>
+      <c r="L14" t="s">
+        <v>224</v>
+      </c>
+      <c r="M14" t="s">
+        <v>218</v>
+      </c>
+      <c r="N14" t="s">
         <v>225</v>
       </c>
-      <c r="K14" t="s">
+      <c r="O14" t="s">
         <v>226</v>
       </c>
-      <c r="L14" t="s">
+      <c r="P14" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q14" t="s">
         <v>227</v>
       </c>
-      <c r="M14" t="s">
-        <v>221</v>
-      </c>
-      <c r="N14" t="s">
+      <c r="R14" t="s">
         <v>228</v>
       </c>
-      <c r="O14" t="s">
+      <c r="S14" t="s">
         <v>229</v>
       </c>
-      <c r="P14" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q14" t="s">
+      <c r="T14" t="s">
         <v>230</v>
-      </c>
-      <c r="R14" t="s">
-        <v>231</v>
-      </c>
-      <c r="S14" t="s">
-        <v>232</v>
-      </c>
-      <c r="T14" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -7090,58 +7558,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="D15" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="E15" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F15" t="s">
+        <v>219</v>
+      </c>
+      <c r="G15" t="s">
+        <v>189</v>
+      </c>
+      <c r="H15" t="s">
+        <v>239</v>
+      </c>
+      <c r="I15" t="s">
+        <v>242</v>
+      </c>
+      <c r="J15" t="s">
         <v>222</v>
       </c>
-      <c r="G15" t="s">
-        <v>192</v>
-      </c>
-      <c r="H15" t="s">
-        <v>242</v>
-      </c>
-      <c r="I15" t="s">
-        <v>245</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="K15" t="s">
+        <v>223</v>
+      </c>
+      <c r="L15" t="s">
+        <v>224</v>
+      </c>
+      <c r="M15" t="s">
+        <v>218</v>
+      </c>
+      <c r="N15" t="s">
         <v>225</v>
       </c>
-      <c r="K15" t="s">
+      <c r="O15" t="s">
         <v>226</v>
       </c>
-      <c r="L15" t="s">
+      <c r="P15" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q15" t="s">
         <v>227</v>
       </c>
-      <c r="M15" t="s">
-        <v>221</v>
-      </c>
-      <c r="N15" t="s">
+      <c r="R15" t="s">
         <v>228</v>
       </c>
-      <c r="O15" t="s">
+      <c r="S15" t="s">
         <v>229</v>
       </c>
-      <c r="P15" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q15" t="s">
+      <c r="T15" t="s">
         <v>230</v>
-      </c>
-      <c r="R15" t="s">
-        <v>231</v>
-      </c>
-      <c r="S15" t="s">
-        <v>232</v>
-      </c>
-      <c r="T15" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7149,58 +7617,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="D16" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="E16" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F16" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="G16" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H16" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I16" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="J16" t="s">
+        <v>222</v>
+      </c>
+      <c r="K16" t="s">
+        <v>223</v>
+      </c>
+      <c r="L16" t="s">
+        <v>224</v>
+      </c>
+      <c r="M16" t="s">
+        <v>218</v>
+      </c>
+      <c r="N16" t="s">
         <v>225</v>
       </c>
-      <c r="K16" t="s">
+      <c r="O16" t="s">
         <v>226</v>
       </c>
-      <c r="L16" t="s">
+      <c r="P16" t="s">
+        <v>219</v>
+      </c>
+      <c r="Q16" t="s">
         <v>227</v>
       </c>
-      <c r="M16" t="s">
-        <v>221</v>
-      </c>
-      <c r="N16" t="s">
+      <c r="R16" t="s">
         <v>228</v>
       </c>
-      <c r="O16" t="s">
+      <c r="S16" t="s">
         <v>229</v>
       </c>
-      <c r="P16" t="s">
-        <v>222</v>
-      </c>
-      <c r="Q16" t="s">
+      <c r="T16" t="s">
         <v>230</v>
-      </c>
-      <c r="R16" t="s">
-        <v>231</v>
-      </c>
-      <c r="S16" t="s">
-        <v>232</v>
-      </c>
-      <c r="T16" t="s">
-        <v>233</v>
       </c>
     </row>
   </sheetData>
@@ -7229,16 +7697,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="D1" t="s">
+        <v>259</v>
+      </c>
+      <c r="E1" t="s">
+        <v>260</v>
+      </c>
+      <c r="F1" t="s">
         <v>261</v>
-      </c>
-      <c r="D1" t="s">
-        <v>262</v>
-      </c>
-      <c r="E1" t="s">
-        <v>263</v>
-      </c>
-      <c r="F1" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7252,7 +7720,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7277,16 +7745,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>263</v>
+      </c>
+      <c r="D4" t="s">
+        <v>264</v>
+      </c>
+      <c r="E4" t="s">
+        <v>265</v>
+      </c>
+      <c r="F4" t="s">
         <v>266</v>
-      </c>
-      <c r="D4" t="s">
-        <v>267</v>
-      </c>
-      <c r="E4" t="s">
-        <v>268</v>
-      </c>
-      <c r="F4" t="s">
-        <v>269</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7300,10 +7768,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="F5" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7311,16 +7779,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="F6" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7334,10 +7802,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="F7" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7351,10 +7819,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="F8" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7368,10 +7836,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="F9" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7379,16 +7847,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
+        <v>278</v>
+      </c>
+      <c r="D10" t="s">
+        <v>279</v>
+      </c>
+      <c r="E10" t="s">
+        <v>280</v>
+      </c>
+      <c r="F10" t="s">
         <v>281</v>
-      </c>
-      <c r="D10" t="s">
-        <v>282</v>
-      </c>
-      <c r="E10" t="s">
-        <v>283</v>
-      </c>
-      <c r="F10" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7402,10 +7870,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F11" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7419,10 +7887,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F12" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
     </row>
   </sheetData>
@@ -7455,34 +7923,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>286</v>
+      </c>
+      <c r="E1" t="s">
+        <v>287</v>
+      </c>
+      <c r="G1" t="s">
+        <v>288</v>
+      </c>
+      <c r="H1" t="s">
         <v>289</v>
       </c>
-      <c r="E1" t="s">
+      <c r="I1" t="s">
         <v>290</v>
       </c>
-      <c r="G1" t="s">
+      <c r="J1" t="s">
         <v>291</v>
       </c>
-      <c r="H1" t="s">
+      <c r="K1" t="s">
         <v>292</v>
       </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>293</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>294</v>
       </c>
-      <c r="K1" t="s">
+      <c r="N1" t="s">
         <v>295</v>
-      </c>
-      <c r="L1" t="s">
-        <v>296</v>
-      </c>
-      <c r="M1" t="s">
-        <v>297</v>
-      </c>
-      <c r="N1" t="s">
-        <v>298</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7493,10 +7961,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="E2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7508,7 +7976,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7530,13 +7998,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>303</v>
+        <v>300</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7547,40 +8015,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>301</v>
+      </c>
+      <c r="D4" t="s">
+        <v>302</v>
+      </c>
+      <c r="E4" t="s">
+        <v>303</v>
+      </c>
+      <c r="F4" t="s">
+        <v>302</v>
+      </c>
+      <c r="G4" t="s">
         <v>304</v>
       </c>
-      <c r="D4" t="s">
+      <c r="H4" t="s">
         <v>305</v>
       </c>
-      <c r="E4" t="s">
+      <c r="I4" t="s">
         <v>306</v>
       </c>
-      <c r="F4" t="s">
-        <v>305</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>307</v>
       </c>
-      <c r="H4" t="s">
+      <c r="K4" t="s">
         <v>308</v>
       </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>309</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
+        <v>207</v>
+      </c>
+      <c r="N4" t="s">
         <v>310</v>
-      </c>
-      <c r="K4" t="s">
-        <v>311</v>
-      </c>
-      <c r="L4" t="s">
-        <v>312</v>
-      </c>
-      <c r="M4" t="s">
-        <v>210</v>
-      </c>
-      <c r="N4" t="s">
-        <v>313</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7603,13 +8071,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L5" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M5" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7623,22 +8091,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
+        <v>190</v>
+      </c>
+      <c r="H6" t="s">
         <v>193</v>
-      </c>
-      <c r="H6" t="s">
-        <v>196</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L6" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M6" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7652,22 +8120,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H7" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L7" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M7" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -7681,22 +8149,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H8" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L8" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M8" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -7710,22 +8178,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H9" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L9" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M9" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -7739,22 +8207,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L10" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M10" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -7768,22 +8236,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H11" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L11" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="M11" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -7797,22 +8265,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="L12" t="s">
-        <v>316</v>
+        <v>313</v>
       </c>
       <c r="M12" t="s">
-        <v>315</v>
+        <v>312</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -7820,31 +8288,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
       <c r="G13" t="s">
+        <v>190</v>
+      </c>
+      <c r="H13" t="s">
         <v>193</v>
-      </c>
-      <c r="H13" t="s">
-        <v>196</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>314</v>
+        <v>311</v>
       </c>
       <c r="L13" t="s">
-        <v>319</v>
+        <v>316</v>
       </c>
       <c r="M13" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N13" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -7852,10 +8320,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>322</v>
+        <v>319</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>323</v>
+        <v>320</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -7864,7 +8332,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -7872,10 +8340,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>325</v>
+        <v>322</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>326</v>
+        <v>323</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -7884,7 +8352,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>324</v>
+        <v>321</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -7892,10 +8360,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>327</v>
+        <v>324</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>328</v>
+        <v>325</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -7904,7 +8372,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>329</v>
+        <v>326</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -7912,19 +8380,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
+        <v>327</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>328</v>
+      </c>
+      <c r="E17" s="5" t="s">
+        <v>329</v>
+      </c>
+      <c r="F17" t="s">
         <v>330</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="N17" t="s">
         <v>331</v>
-      </c>
-      <c r="E17" s="5" t="s">
-        <v>332</v>
-      </c>
-      <c r="F17" t="s">
-        <v>333</v>
-      </c>
-      <c r="N17" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -7932,10 +8400,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>335</v>
+        <v>332</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>336</v>
+        <v>333</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -7944,7 +8412,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>337</v>
+        <v>334</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -7952,10 +8420,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>338</v>
+        <v>335</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>339</v>
+        <v>336</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -7964,7 +8432,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>340</v>
+        <v>337</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -7972,10 +8440,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>341</v>
+        <v>338</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>342</v>
+        <v>339</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -7984,7 +8452,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>343</v>
+        <v>340</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -7992,19 +8460,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>344</v>
+        <v>341</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>345</v>
+        <v>342</v>
       </c>
       <c r="E21" t="s">
-        <v>332</v>
+        <v>329</v>
       </c>
       <c r="F21" t="s">
-        <v>333</v>
+        <v>330</v>
       </c>
       <c r="N21" t="s">
-        <v>346</v>
+        <v>343</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -8012,16 +8480,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>347</v>
+        <v>344</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>317</v>
+        <v>314</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>318</v>
+        <v>315</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -8029,10 +8497,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -8046,10 +8514,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -8063,10 +8531,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -8080,10 +8548,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -8097,10 +8565,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8114,10 +8582,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8131,10 +8599,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8143,10 +8611,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N29" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8154,10 +8622,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8171,10 +8639,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8188,10 +8656,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8200,10 +8668,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>320</v>
+        <v>317</v>
       </c>
       <c r="N32" t="s">
-        <v>321</v>
+        <v>318</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -8211,10 +8679,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -8223,7 +8691,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
     </row>
   </sheetData>
@@ -8259,31 +8727,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>369</v>
+      </c>
+      <c r="D1" t="s">
+        <v>370</v>
+      </c>
+      <c r="E1" t="s">
+        <v>371</v>
+      </c>
+      <c r="F1" t="s">
         <v>372</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>373</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>286</v>
+      </c>
+      <c r="I1" t="s">
         <v>374</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>375</v>
       </c>
-      <c r="G1" t="s">
-        <v>376</v>
-      </c>
-      <c r="H1" t="s">
-        <v>289</v>
-      </c>
-      <c r="I1" t="s">
-        <v>377</v>
-      </c>
-      <c r="J1" t="s">
-        <v>378</v>
-      </c>
       <c r="K1" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8309,10 +8777,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="I2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8326,34 +8794,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>376</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>377</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>378</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>379</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>380</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>381</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>382</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>384</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>385</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>386</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>387</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8364,31 +8832,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>385</v>
+      </c>
+      <c r="D4" t="s">
+        <v>386</v>
+      </c>
+      <c r="E4" t="s">
+        <v>387</v>
+      </c>
+      <c r="F4" t="s">
         <v>388</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>389</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
         <v>390</v>
       </c>
-      <c r="F4" t="s">
+      <c r="I4" t="s">
         <v>391</v>
       </c>
-      <c r="G4" t="s">
+      <c r="J4" t="s">
         <v>392</v>
       </c>
-      <c r="H4" t="s">
-        <v>393</v>
-      </c>
-      <c r="I4" t="s">
-        <v>394</v>
-      </c>
-      <c r="J4" t="s">
-        <v>395</v>
-      </c>
       <c r="K4" t="s">
-        <v>313</v>
+        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8396,7 +8864,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8420,7 +8888,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8428,7 +8896,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8452,7 +8920,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8460,7 +8928,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8484,7 +8952,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8492,7 +8960,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8516,7 +8984,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
     </row>
   </sheetData>
@@ -8547,16 +9015,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="D1" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="E1" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="F1" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8573,7 +9041,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8586,10 +9054,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8600,13 +9068,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
       <c r="D4" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="E4" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8614,7 +9082,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8623,7 +9091,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8631,7 +9099,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8640,7 +9108,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8648,7 +9116,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -8657,7 +9125,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -8665,7 +9133,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -8674,7 +9142,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -8712,40 +9180,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>415</v>
+      </c>
+      <c r="C1" t="s">
+        <v>416</v>
+      </c>
+      <c r="D1" t="s">
+        <v>417</v>
+      </c>
+      <c r="E1" t="s">
         <v>418</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>419</v>
       </c>
-      <c r="D1" t="s">
+      <c r="G1" t="s">
         <v>420</v>
       </c>
-      <c r="E1" t="s">
+      <c r="H1" t="s">
+        <v>295</v>
+      </c>
+      <c r="I1" t="s">
         <v>421</v>
       </c>
-      <c r="F1" t="s">
+      <c r="J1" t="s">
         <v>422</v>
       </c>
-      <c r="G1" t="s">
+      <c r="K1" t="s">
         <v>423</v>
       </c>
-      <c r="H1" t="s">
-        <v>298</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="L1" t="s">
         <v>424</v>
       </c>
-      <c r="J1" t="s">
+      <c r="M1" t="s">
         <v>425</v>
-      </c>
-      <c r="K1" t="s">
-        <v>426</v>
-      </c>
-      <c r="L1" t="s">
-        <v>427</v>
-      </c>
-      <c r="M1" t="s">
-        <v>428</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -8759,16 +9227,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="G2" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -8794,40 +9262,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>428</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>429</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="E3" s="1" t="s">
         <v>431</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="F3" s="1" t="s">
         <v>432</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="G3" s="1" t="s">
         <v>433</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="H3" s="1" t="s">
         <v>434</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="I3" t="s">
         <v>435</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="J3" t="s">
         <v>436</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="K3" t="s">
         <v>437</v>
       </c>
-      <c r="I3" t="s">
+      <c r="L3" t="s">
         <v>438</v>
       </c>
-      <c r="J3" t="s">
+      <c r="M3" t="s">
         <v>439</v>
-      </c>
-      <c r="K3" t="s">
-        <v>440</v>
-      </c>
-      <c r="L3" t="s">
-        <v>441</v>
-      </c>
-      <c r="M3" t="s">
-        <v>442</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -8835,54 +9303,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>440</v>
+      </c>
+      <c r="C4" t="s">
+        <v>441</v>
+      </c>
+      <c r="D4" t="s">
+        <v>442</v>
+      </c>
+      <c r="E4" t="s">
         <v>443</v>
       </c>
-      <c r="C4" t="s">
+      <c r="F4" t="s">
         <v>444</v>
       </c>
-      <c r="D4" t="s">
+      <c r="G4" t="s">
         <v>445</v>
       </c>
-      <c r="E4" t="s">
+      <c r="H4" t="s">
+        <v>310</v>
+      </c>
+      <c r="I4" t="s">
         <v>446</v>
       </c>
-      <c r="F4" t="s">
+      <c r="J4" t="s">
         <v>447</v>
       </c>
-      <c r="G4" t="s">
+      <c r="K4" t="s">
         <v>448</v>
       </c>
-      <c r="H4" t="s">
-        <v>313</v>
-      </c>
-      <c r="I4" t="s">
+      <c r="L4" t="s">
         <v>449</v>
       </c>
-      <c r="J4" t="s">
+      <c r="M4" t="s">
         <v>450</v>
-      </c>
-      <c r="K4" t="s">
-        <v>451</v>
-      </c>
-      <c r="L4" t="s">
-        <v>452</v>
-      </c>
-      <c r="M4" t="s">
-        <v>453</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>454</v>
+        <v>451</v>
       </c>
       <c r="D5" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -8894,36 +9362,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
+        <v>453</v>
+      </c>
+      <c r="I5" t="s">
+        <v>454</v>
+      </c>
+      <c r="J5" t="s">
+        <v>455</v>
+      </c>
+      <c r="K5" t="s">
         <v>456</v>
       </c>
-      <c r="I5" t="s">
+      <c r="L5" t="s">
         <v>457</v>
       </c>
-      <c r="J5" t="s">
+      <c r="M5" t="s">
         <v>458</v>
-      </c>
-      <c r="K5" t="s">
-        <v>459</v>
-      </c>
-      <c r="L5" t="s">
-        <v>460</v>
-      </c>
-      <c r="M5" t="s">
-        <v>461</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>462</v>
+        <v>459</v>
       </c>
       <c r="D6" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -8935,36 +9403,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
+        <v>460</v>
+      </c>
+      <c r="I6" t="s">
+        <v>461</v>
+      </c>
+      <c r="J6" t="s">
+        <v>462</v>
+      </c>
+      <c r="K6" t="s">
         <v>463</v>
       </c>
-      <c r="I6" t="s">
+      <c r="L6" t="s">
         <v>464</v>
       </c>
-      <c r="J6" t="s">
+      <c r="M6" t="s">
         <v>465</v>
-      </c>
-      <c r="K6" t="s">
-        <v>466</v>
-      </c>
-      <c r="L6" t="s">
-        <v>467</v>
-      </c>
-      <c r="M6" t="s">
-        <v>468</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>469</v>
+        <v>466</v>
       </c>
       <c r="D7" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -8976,36 +9444,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
+        <v>467</v>
+      </c>
+      <c r="I7" t="s">
+        <v>468</v>
+      </c>
+      <c r="J7" t="s">
+        <v>469</v>
+      </c>
+      <c r="K7" t="s">
         <v>470</v>
       </c>
-      <c r="I7" t="s">
+      <c r="L7" t="s">
         <v>471</v>
       </c>
-      <c r="J7" t="s">
+      <c r="M7" t="s">
         <v>472</v>
-      </c>
-      <c r="K7" t="s">
-        <v>473</v>
-      </c>
-      <c r="L7" t="s">
-        <v>474</v>
-      </c>
-      <c r="M7" t="s">
-        <v>475</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>476</v>
+        <v>473</v>
       </c>
       <c r="D8" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -9017,36 +9485,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
+        <v>474</v>
+      </c>
+      <c r="I8" t="s">
+        <v>475</v>
+      </c>
+      <c r="J8" t="s">
+        <v>476</v>
+      </c>
+      <c r="K8" t="s">
         <v>477</v>
       </c>
-      <c r="I8" t="s">
+      <c r="L8" t="s">
         <v>478</v>
       </c>
-      <c r="J8" t="s">
+      <c r="M8" t="s">
         <v>479</v>
-      </c>
-      <c r="K8" t="s">
-        <v>480</v>
-      </c>
-      <c r="L8" t="s">
-        <v>481</v>
-      </c>
-      <c r="M8" t="s">
-        <v>482</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>483</v>
+        <v>480</v>
       </c>
       <c r="D9" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -9058,36 +9526,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
+        <v>481</v>
+      </c>
+      <c r="I9" t="s">
+        <v>482</v>
+      </c>
+      <c r="J9" t="s">
+        <v>483</v>
+      </c>
+      <c r="K9" t="s">
         <v>484</v>
       </c>
-      <c r="I9" t="s">
+      <c r="L9" t="s">
         <v>485</v>
       </c>
-      <c r="J9" t="s">
+      <c r="M9" t="s">
         <v>486</v>
-      </c>
-      <c r="K9" t="s">
-        <v>487</v>
-      </c>
-      <c r="L9" t="s">
-        <v>488</v>
-      </c>
-      <c r="M9" t="s">
-        <v>489</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>490</v>
+        <v>487</v>
       </c>
       <c r="D10" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -9099,36 +9567,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
+        <v>488</v>
+      </c>
+      <c r="I10" t="s">
+        <v>489</v>
+      </c>
+      <c r="J10" t="s">
+        <v>490</v>
+      </c>
+      <c r="K10" t="s">
         <v>491</v>
       </c>
-      <c r="I10" t="s">
+      <c r="L10" t="s">
         <v>492</v>
       </c>
-      <c r="J10" t="s">
+      <c r="M10" t="s">
         <v>493</v>
-      </c>
-      <c r="K10" t="s">
-        <v>494</v>
-      </c>
-      <c r="L10" t="s">
-        <v>495</v>
-      </c>
-      <c r="M10" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>497</v>
+        <v>494</v>
       </c>
       <c r="D11" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9140,36 +9608,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
+        <v>495</v>
+      </c>
+      <c r="I11" t="s">
+        <v>496</v>
+      </c>
+      <c r="J11" t="s">
+        <v>497</v>
+      </c>
+      <c r="K11" t="s">
         <v>498</v>
       </c>
-      <c r="I11" t="s">
+      <c r="L11" t="s">
         <v>499</v>
       </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
         <v>500</v>
-      </c>
-      <c r="K11" t="s">
-        <v>501</v>
-      </c>
-      <c r="L11" t="s">
-        <v>502</v>
-      </c>
-      <c r="M11" t="s">
-        <v>503</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>504</v>
+        <v>501</v>
       </c>
       <c r="D12" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9181,36 +9649,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
+        <v>502</v>
+      </c>
+      <c r="I12" t="s">
+        <v>503</v>
+      </c>
+      <c r="J12" t="s">
+        <v>504</v>
+      </c>
+      <c r="K12" t="s">
         <v>505</v>
       </c>
-      <c r="I12" t="s">
+      <c r="L12" t="s">
         <v>506</v>
       </c>
-      <c r="J12" t="s">
+      <c r="M12" t="s">
         <v>507</v>
-      </c>
-      <c r="K12" t="s">
-        <v>508</v>
-      </c>
-      <c r="L12" t="s">
-        <v>509</v>
-      </c>
-      <c r="M12" t="s">
-        <v>510</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>511</v>
+        <v>508</v>
       </c>
       <c r="D13" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9222,36 +9690,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
+        <v>509</v>
+      </c>
+      <c r="I13" t="s">
+        <v>510</v>
+      </c>
+      <c r="J13" t="s">
+        <v>511</v>
+      </c>
+      <c r="K13" t="s">
         <v>512</v>
       </c>
-      <c r="I13" t="s">
+      <c r="L13" t="s">
         <v>513</v>
       </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
         <v>514</v>
-      </c>
-      <c r="K13" t="s">
-        <v>515</v>
-      </c>
-      <c r="L13" t="s">
-        <v>516</v>
-      </c>
-      <c r="M13" t="s">
-        <v>517</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>518</v>
+        <v>515</v>
       </c>
       <c r="D14" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9263,36 +9731,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
+        <v>516</v>
+      </c>
+      <c r="I14" t="s">
+        <v>517</v>
+      </c>
+      <c r="J14" t="s">
+        <v>518</v>
+      </c>
+      <c r="K14" t="s">
         <v>519</v>
       </c>
-      <c r="I14" t="s">
+      <c r="L14" t="s">
         <v>520</v>
       </c>
-      <c r="J14" t="s">
+      <c r="M14" t="s">
         <v>521</v>
-      </c>
-      <c r="K14" t="s">
-        <v>522</v>
-      </c>
-      <c r="L14" t="s">
-        <v>523</v>
-      </c>
-      <c r="M14" t="s">
-        <v>524</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>525</v>
+        <v>522</v>
       </c>
       <c r="D15" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9304,39 +9772,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
+        <v>523</v>
+      </c>
+      <c r="I15" t="s">
+        <v>524</v>
+      </c>
+      <c r="J15" t="s">
+        <v>525</v>
+      </c>
+      <c r="K15" t="s">
         <v>526</v>
       </c>
-      <c r="I15" t="s">
+      <c r="L15" t="s">
         <v>527</v>
       </c>
-      <c r="J15" t="s">
+      <c r="M15" t="s">
         <v>528</v>
-      </c>
-      <c r="K15" t="s">
-        <v>529</v>
-      </c>
-      <c r="L15" t="s">
-        <v>530</v>
-      </c>
-      <c r="M15" t="s">
-        <v>531</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>532</v>
+        <v>529</v>
       </c>
       <c r="D16" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E16" t="s">
-        <v>534</v>
+        <v>531</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9345,39 +9813,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
+        <v>532</v>
+      </c>
+      <c r="I16" t="s">
+        <v>533</v>
+      </c>
+      <c r="J16" t="s">
+        <v>534</v>
+      </c>
+      <c r="K16" t="s">
         <v>535</v>
       </c>
-      <c r="I16" t="s">
+      <c r="L16" t="s">
         <v>536</v>
       </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
         <v>537</v>
-      </c>
-      <c r="K16" t="s">
-        <v>538</v>
-      </c>
-      <c r="L16" t="s">
-        <v>539</v>
-      </c>
-      <c r="M16" t="s">
-        <v>540</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>541</v>
+        <v>538</v>
       </c>
       <c r="D17" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E17" t="s">
-        <v>542</v>
+        <v>539</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9386,39 +9854,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
+        <v>540</v>
+      </c>
+      <c r="I17" t="s">
+        <v>541</v>
+      </c>
+      <c r="J17" t="s">
+        <v>542</v>
+      </c>
+      <c r="K17" t="s">
         <v>543</v>
       </c>
-      <c r="I17" t="s">
+      <c r="L17" t="s">
         <v>544</v>
       </c>
-      <c r="J17" t="s">
+      <c r="M17" t="s">
         <v>545</v>
-      </c>
-      <c r="K17" t="s">
-        <v>546</v>
-      </c>
-      <c r="L17" t="s">
-        <v>547</v>
-      </c>
-      <c r="M17" t="s">
-        <v>548</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>549</v>
+        <v>546</v>
       </c>
       <c r="D18" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E18" t="s">
-        <v>550</v>
+        <v>547</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9427,39 +9895,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
+        <v>548</v>
+      </c>
+      <c r="I18" t="s">
+        <v>549</v>
+      </c>
+      <c r="J18" t="s">
+        <v>550</v>
+      </c>
+      <c r="K18" t="s">
         <v>551</v>
       </c>
-      <c r="I18" t="s">
+      <c r="L18" t="s">
         <v>552</v>
       </c>
-      <c r="J18" t="s">
+      <c r="M18" t="s">
         <v>553</v>
-      </c>
-      <c r="K18" t="s">
-        <v>554</v>
-      </c>
-      <c r="L18" t="s">
-        <v>555</v>
-      </c>
-      <c r="M18" t="s">
-        <v>556</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>557</v>
+        <v>554</v>
       </c>
       <c r="D19" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E19" t="s">
-        <v>558</v>
+        <v>555</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9468,39 +9936,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
+        <v>556</v>
+      </c>
+      <c r="I19" t="s">
+        <v>557</v>
+      </c>
+      <c r="J19" t="s">
+        <v>558</v>
+      </c>
+      <c r="K19" t="s">
         <v>559</v>
       </c>
-      <c r="I19" t="s">
+      <c r="L19" t="s">
         <v>560</v>
       </c>
-      <c r="J19" t="s">
+      <c r="M19" t="s">
         <v>561</v>
-      </c>
-      <c r="K19" t="s">
-        <v>562</v>
-      </c>
-      <c r="L19" t="s">
-        <v>563</v>
-      </c>
-      <c r="M19" t="s">
-        <v>564</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>565</v>
+        <v>562</v>
       </c>
       <c r="D20" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E20" t="s">
-        <v>566</v>
+        <v>563</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9509,39 +9977,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
+        <v>564</v>
+      </c>
+      <c r="I20" t="s">
+        <v>565</v>
+      </c>
+      <c r="J20" t="s">
+        <v>566</v>
+      </c>
+      <c r="K20" t="s">
         <v>567</v>
       </c>
-      <c r="I20" t="s">
+      <c r="L20" t="s">
         <v>568</v>
       </c>
-      <c r="J20" t="s">
+      <c r="M20" t="s">
         <v>569</v>
-      </c>
-      <c r="K20" t="s">
-        <v>570</v>
-      </c>
-      <c r="L20" t="s">
-        <v>571</v>
-      </c>
-      <c r="M20" t="s">
-        <v>572</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>573</v>
+        <v>570</v>
       </c>
       <c r="D21" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E21" t="s">
-        <v>574</v>
+        <v>571</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9550,39 +10018,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
+        <v>572</v>
+      </c>
+      <c r="I21" t="s">
+        <v>573</v>
+      </c>
+      <c r="J21" t="s">
+        <v>574</v>
+      </c>
+      <c r="K21" t="s">
         <v>575</v>
       </c>
-      <c r="I21" t="s">
+      <c r="L21" t="s">
         <v>576</v>
       </c>
-      <c r="J21" t="s">
+      <c r="M21" t="s">
         <v>577</v>
-      </c>
-      <c r="K21" t="s">
-        <v>578</v>
-      </c>
-      <c r="L21" t="s">
-        <v>579</v>
-      </c>
-      <c r="M21" t="s">
-        <v>580</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>581</v>
+        <v>578</v>
       </c>
       <c r="D22" t="s">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="E22" t="s">
-        <v>582</v>
+        <v>579</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -9591,39 +10059,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
+        <v>580</v>
+      </c>
+      <c r="I22" t="s">
+        <v>581</v>
+      </c>
+      <c r="J22" t="s">
+        <v>582</v>
+      </c>
+      <c r="K22" t="s">
         <v>583</v>
       </c>
-      <c r="I22" t="s">
+      <c r="L22" t="s">
         <v>584</v>
       </c>
-      <c r="J22" t="s">
+      <c r="M22" t="s">
         <v>585</v>
-      </c>
-      <c r="K22" t="s">
-        <v>586</v>
-      </c>
-      <c r="L22" t="s">
-        <v>587</v>
-      </c>
-      <c r="M22" t="s">
-        <v>588</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>589</v>
+        <v>586</v>
       </c>
       <c r="D23" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E23" t="s">
-        <v>591</v>
+        <v>588</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -9632,39 +10100,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
+        <v>589</v>
+      </c>
+      <c r="I23" t="s">
+        <v>590</v>
+      </c>
+      <c r="J23" t="s">
+        <v>591</v>
+      </c>
+      <c r="K23" t="s">
         <v>592</v>
       </c>
-      <c r="I23" t="s">
+      <c r="L23" t="s">
         <v>593</v>
       </c>
-      <c r="J23" t="s">
+      <c r="M23" t="s">
         <v>594</v>
-      </c>
-      <c r="K23" t="s">
-        <v>595</v>
-      </c>
-      <c r="L23" t="s">
-        <v>596</v>
-      </c>
-      <c r="M23" t="s">
-        <v>597</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>598</v>
+        <v>595</v>
       </c>
       <c r="D24" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E24" t="s">
-        <v>599</v>
+        <v>596</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -9673,39 +10141,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
+        <v>597</v>
+      </c>
+      <c r="I24" t="s">
+        <v>598</v>
+      </c>
+      <c r="J24" t="s">
+        <v>599</v>
+      </c>
+      <c r="K24" t="s">
         <v>600</v>
       </c>
-      <c r="I24" t="s">
+      <c r="L24" t="s">
         <v>601</v>
       </c>
-      <c r="J24" t="s">
+      <c r="M24" t="s">
         <v>602</v>
-      </c>
-      <c r="K24" t="s">
-        <v>603</v>
-      </c>
-      <c r="L24" t="s">
-        <v>604</v>
-      </c>
-      <c r="M24" t="s">
-        <v>605</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>606</v>
+        <v>603</v>
       </c>
       <c r="D25" t="s">
-        <v>590</v>
+        <v>587</v>
       </c>
       <c r="E25" t="s">
-        <v>607</v>
+        <v>604</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -9714,22 +10182,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
+        <v>606</v>
+      </c>
+      <c r="K25" t="s">
+        <v>607</v>
+      </c>
+      <c r="L25" t="s">
+        <v>608</v>
+      </c>
+      <c r="M25" t="s">
         <v>609</v>
-      </c>
-      <c r="K25" t="s">
-        <v>610</v>
-      </c>
-      <c r="L25" t="s">
-        <v>611</v>
-      </c>
-      <c r="M25" t="s">
-        <v>612</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -9737,10 +10205,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>613</v>
+        <v>610</v>
       </c>
       <c r="D26" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -9752,22 +10220,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
+        <v>612</v>
+      </c>
+      <c r="I26" t="s">
+        <v>613</v>
+      </c>
+      <c r="J26" t="s">
+        <v>614</v>
+      </c>
+      <c r="K26" t="s">
         <v>615</v>
       </c>
-      <c r="I26" t="s">
+      <c r="L26" t="s">
         <v>616</v>
       </c>
-      <c r="J26" t="s">
+      <c r="M26" t="s">
         <v>617</v>
-      </c>
-      <c r="K26" t="s">
-        <v>618</v>
-      </c>
-      <c r="L26" t="s">
-        <v>619</v>
-      </c>
-      <c r="M26" t="s">
-        <v>620</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -9775,13 +10243,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>621</v>
+        <v>618</v>
       </c>
       <c r="D27" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E27" t="s">
-        <v>622</v>
+        <v>619</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -9790,36 +10258,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
+        <v>620</v>
+      </c>
+      <c r="I27" t="s">
+        <v>621</v>
+      </c>
+      <c r="J27" t="s">
+        <v>622</v>
+      </c>
+      <c r="K27" t="s">
         <v>623</v>
       </c>
-      <c r="I27" t="s">
+      <c r="L27" t="s">
         <v>624</v>
       </c>
-      <c r="J27" t="s">
+      <c r="M27" t="s">
         <v>625</v>
-      </c>
-      <c r="K27" t="s">
-        <v>626</v>
-      </c>
-      <c r="L27" t="s">
-        <v>627</v>
-      </c>
-      <c r="M27" t="s">
-        <v>628</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>629</v>
+        <v>626</v>
       </c>
       <c r="D28" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -9831,36 +10299,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
+        <v>627</v>
+      </c>
+      <c r="I28" t="s">
+        <v>628</v>
+      </c>
+      <c r="J28" t="s">
+        <v>629</v>
+      </c>
+      <c r="K28" t="s">
         <v>630</v>
       </c>
-      <c r="I28" t="s">
+      <c r="L28" t="s">
         <v>631</v>
       </c>
-      <c r="J28" t="s">
+      <c r="M28" t="s">
         <v>632</v>
-      </c>
-      <c r="K28" t="s">
-        <v>633</v>
-      </c>
-      <c r="L28" t="s">
-        <v>634</v>
-      </c>
-      <c r="M28" t="s">
-        <v>635</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>636</v>
+        <v>633</v>
       </c>
       <c r="D29" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -9872,36 +10340,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
+        <v>634</v>
+      </c>
+      <c r="I29" t="s">
+        <v>635</v>
+      </c>
+      <c r="J29" t="s">
+        <v>636</v>
+      </c>
+      <c r="K29" t="s">
         <v>637</v>
       </c>
-      <c r="I29" t="s">
+      <c r="L29" t="s">
         <v>638</v>
       </c>
-      <c r="J29" t="s">
+      <c r="M29" t="s">
         <v>639</v>
-      </c>
-      <c r="K29" t="s">
-        <v>640</v>
-      </c>
-      <c r="L29" t="s">
-        <v>641</v>
-      </c>
-      <c r="M29" t="s">
-        <v>642</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>643</v>
+        <v>640</v>
       </c>
       <c r="D30" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -9913,39 +10381,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
+        <v>641</v>
+      </c>
+      <c r="I30" t="s">
+        <v>642</v>
+      </c>
+      <c r="J30" t="s">
+        <v>643</v>
+      </c>
+      <c r="K30" t="s">
         <v>644</v>
       </c>
-      <c r="I30" t="s">
+      <c r="L30" t="s">
         <v>645</v>
       </c>
-      <c r="J30" t="s">
+      <c r="M30" t="s">
         <v>646</v>
-      </c>
-      <c r="K30" t="s">
-        <v>647</v>
-      </c>
-      <c r="L30" t="s">
-        <v>648</v>
-      </c>
-      <c r="M30" t="s">
-        <v>649</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>650</v>
+        <v>647</v>
       </c>
       <c r="D31" t="s">
-        <v>614</v>
+        <v>611</v>
       </c>
       <c r="E31" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -9954,22 +10422,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
+        <v>648</v>
+      </c>
+      <c r="I31" t="s">
+        <v>649</v>
+      </c>
+      <c r="J31" t="s">
+        <v>650</v>
+      </c>
+      <c r="K31" t="s">
         <v>651</v>
       </c>
-      <c r="I31" t="s">
+      <c r="L31" t="s">
         <v>652</v>
       </c>
-      <c r="J31" t="s">
+      <c r="M31" t="s">
         <v>653</v>
-      </c>
-      <c r="K31" t="s">
-        <v>654</v>
-      </c>
-      <c r="L31" t="s">
-        <v>655</v>
-      </c>
-      <c r="M31" t="s">
-        <v>656</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -9977,13 +10445,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>657</v>
+        <v>654</v>
       </c>
       <c r="D32" t="s">
-        <v>455</v>
+        <v>452</v>
       </c>
       <c r="E32" t="s">
-        <v>658</v>
+        <v>655</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -9992,22 +10460,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
+        <v>656</v>
+      </c>
+      <c r="I32" t="s">
+        <v>657</v>
+      </c>
+      <c r="J32" t="s">
+        <v>658</v>
+      </c>
+      <c r="K32" t="s">
         <v>659</v>
       </c>
-      <c r="I32" t="s">
+      <c r="L32" t="s">
         <v>660</v>
       </c>
-      <c r="J32" t="s">
+      <c r="M32" t="s">
         <v>661</v>
-      </c>
-      <c r="K32" t="s">
-        <v>662</v>
-      </c>
-      <c r="L32" t="s">
-        <v>663</v>
-      </c>
-      <c r="M32" t="s">
-        <v>664</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="10"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="914">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="908">
   <si>
     <t>Dog</t>
   </si>
@@ -555,31 +555,13 @@
     <t>未领取奖励的条目和固定条目数量之和不足该值时，以已领取奖励的条目填充占位</t>
   </si>
   <si>
-    <t>SteamPlaytimeDropLeadSeconds</t>
-  </si>
-  <si>
-    <t>Steam提前准备盲盒的秒数</t>
-  </si>
-  <si>
-    <t>秒；仅供转换器使用，仅用于前 12 个一次性游玩投放；相对本地盲盒展示时间提前请求，用于避开 Steam 分钟计时边界</t>
-  </si>
-  <si>
-    <t>SteamPlaytimeRequestLeadSeconds</t>
-  </si>
-  <si>
-    <t>Steam掉落请求提前秒数</t>
-  </si>
-  <si>
-    <t>仅供客户端使用。在本地展示前多久开始调用 TriggerItemDrop。</t>
-  </si>
-  <si>
-    <t>BlindBoxLoopSteamVoucherInventoryLimit</t>
-  </si>
-  <si>
-    <t>循环Steam盲盒券库存上限</t>
-  </si>
-  <si>
-    <t>正常循环阶段允许玩家在 Steam 库存中累计的盲盒成本券数量上限。客户端统计对应 ItemDef 的所有实例及堆叠数量；达到上限时暂停调用循环 PlaytimeGenerator，消耗后低于上限时恢复请求。填 0 表示不限制。</t>
+    <t>SteamPlaytimeEligibilityLeadSeconds</t>
+  </si>
+  <si>
+    <t>Steam资格提前秒数</t>
+  </si>
+  <si>
+    <t>秒；前 12 个一次性 Steam 投放相对本地展示时间提前取得服务器资格。转换器与客户端必须使用相同的分钟级取整结果；循环阶段不使用本字段。</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4367,28 +4349,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>656</v>
+      </c>
+      <c r="C1" t="s">
+        <v>657</v>
+      </c>
+      <c r="D1" t="s">
+        <v>658</v>
+      </c>
+      <c r="E1" t="s">
+        <v>659</v>
+      </c>
+      <c r="F1" t="s">
+        <v>660</v>
+      </c>
+      <c r="G1" t="s">
+        <v>661</v>
+      </c>
+      <c r="H1" t="s">
         <v>662</v>
       </c>
-      <c r="C1" t="s">
-        <v>663</v>
-      </c>
-      <c r="D1" t="s">
-        <v>664</v>
-      </c>
-      <c r="E1" t="s">
-        <v>665</v>
-      </c>
-      <c r="F1" t="s">
-        <v>666</v>
-      </c>
-      <c r="G1" t="s">
-        <v>667</v>
-      </c>
-      <c r="H1" t="s">
-        <v>668</v>
-      </c>
       <c r="I1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4405,16 +4387,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>669</v>
+        <v>663</v>
       </c>
       <c r="F2" t="s">
-        <v>670</v>
+        <v>664</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4425,28 +4407,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>665</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>666</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>667</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>668</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>669</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>670</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>671</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>672</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>673</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>674</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>675</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>676</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>677</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>678</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4454,1333 +4436,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>679</v>
+        <v>673</v>
       </c>
       <c r="C4" t="s">
-        <v>680</v>
+        <v>674</v>
       </c>
       <c r="D4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="E4" t="s">
-        <v>681</v>
+        <v>675</v>
       </c>
       <c r="F4" t="s">
-        <v>682</v>
+        <v>676</v>
       </c>
       <c r="G4" t="s">
-        <v>683</v>
+        <v>677</v>
       </c>
       <c r="H4" t="s">
-        <v>684</v>
+        <v>678</v>
       </c>
       <c r="I4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>685</v>
+        <v>679</v>
       </c>
       <c r="D5" t="s">
-        <v>686</v>
+        <v>680</v>
       </c>
       <c r="E5" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="F5" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G5" t="s">
-        <v>689</v>
+        <v>683</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>690</v>
+        <v>684</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>691</v>
+        <v>685</v>
       </c>
       <c r="D6" t="s">
-        <v>692</v>
+        <v>686</v>
       </c>
       <c r="E6" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F6" t="s">
+        <v>682</v>
+      </c>
+      <c r="G6" t="s">
         <v>688</v>
-      </c>
-      <c r="G6" t="s">
-        <v>694</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>695</v>
+        <v>689</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>696</v>
+        <v>690</v>
       </c>
       <c r="D7" t="s">
-        <v>697</v>
+        <v>691</v>
       </c>
       <c r="E7" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="F7" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G7" t="s">
-        <v>698</v>
+        <v>692</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>699</v>
+        <v>693</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>700</v>
+        <v>694</v>
       </c>
       <c r="D8" t="s">
-        <v>701</v>
+        <v>695</v>
       </c>
       <c r="E8" t="s">
-        <v>687</v>
+        <v>681</v>
       </c>
       <c r="F8" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G8" t="s">
-        <v>702</v>
+        <v>696</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>703</v>
+        <v>697</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>704</v>
+        <v>698</v>
       </c>
       <c r="D9" t="s">
-        <v>705</v>
+        <v>699</v>
       </c>
       <c r="E9" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F9" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G9" t="s">
-        <v>706</v>
+        <v>700</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>707</v>
+        <v>701</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>708</v>
+        <v>702</v>
       </c>
       <c r="D10" t="s">
-        <v>709</v>
+        <v>703</v>
       </c>
       <c r="E10" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F10" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G10" t="s">
-        <v>711</v>
+        <v>705</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>712</v>
+        <v>706</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>713</v>
+        <v>707</v>
       </c>
       <c r="D11" t="s">
-        <v>714</v>
+        <v>708</v>
       </c>
       <c r="E11" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F11" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G11" t="s">
-        <v>715</v>
+        <v>709</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>716</v>
+        <v>710</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>717</v>
+        <v>711</v>
       </c>
       <c r="D12" t="s">
-        <v>718</v>
+        <v>712</v>
       </c>
       <c r="E12" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F12" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G12" t="s">
-        <v>719</v>
+        <v>713</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>720</v>
+        <v>714</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>721</v>
+        <v>715</v>
       </c>
       <c r="D13" t="s">
-        <v>722</v>
+        <v>716</v>
       </c>
       <c r="E13" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F13" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G13" t="s">
-        <v>723</v>
+        <v>717</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>724</v>
+        <v>718</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>725</v>
+        <v>719</v>
       </c>
       <c r="D14" t="s">
-        <v>726</v>
+        <v>720</v>
       </c>
       <c r="E14" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F14" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G14" t="s">
-        <v>727</v>
+        <v>721</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>728</v>
+        <v>722</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>729</v>
+        <v>723</v>
       </c>
       <c r="D15" t="s">
-        <v>730</v>
+        <v>724</v>
       </c>
       <c r="E15" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F15" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G15" t="s">
-        <v>731</v>
+        <v>725</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>732</v>
+        <v>726</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>733</v>
+        <v>727</v>
       </c>
       <c r="D16" t="s">
-        <v>734</v>
+        <v>728</v>
       </c>
       <c r="E16" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F16" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G16" t="s">
-        <v>735</v>
+        <v>729</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>736</v>
+        <v>730</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>737</v>
+        <v>731</v>
       </c>
       <c r="D17" t="s">
-        <v>738</v>
+        <v>732</v>
       </c>
       <c r="E17" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F17" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G17" t="s">
-        <v>739</v>
+        <v>733</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>740</v>
+        <v>734</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>741</v>
+        <v>735</v>
       </c>
       <c r="D18" t="s">
-        <v>742</v>
+        <v>736</v>
       </c>
       <c r="E18" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F18" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G18" t="s">
-        <v>743</v>
+        <v>737</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>744</v>
+        <v>738</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="D19" t="s">
-        <v>745</v>
+        <v>739</v>
       </c>
       <c r="E19" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F19" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G19" t="s">
-        <v>746</v>
+        <v>740</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>747</v>
+        <v>741</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="D20" t="s">
-        <v>748</v>
+        <v>742</v>
       </c>
       <c r="E20" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F20" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G20" t="s">
-        <v>749</v>
+        <v>743</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>750</v>
+        <v>744</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="D21" t="s">
-        <v>751</v>
+        <v>745</v>
       </c>
       <c r="E21" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F21" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G21" t="s">
-        <v>752</v>
+        <v>746</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>753</v>
+        <v>747</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="D22" t="s">
-        <v>754</v>
+        <v>748</v>
       </c>
       <c r="E22" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F22" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G22" t="s">
-        <v>755</v>
+        <v>749</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>756</v>
+        <v>750</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="D23" t="s">
-        <v>757</v>
+        <v>751</v>
       </c>
       <c r="E23" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F23" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G23" t="s">
-        <v>758</v>
+        <v>752</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>759</v>
+        <v>753</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="D24" t="s">
-        <v>760</v>
+        <v>754</v>
       </c>
       <c r="E24" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F24" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G24" t="s">
-        <v>761</v>
+        <v>755</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>762</v>
+        <v>756</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="D25" t="s">
-        <v>763</v>
+        <v>757</v>
       </c>
       <c r="E25" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F25" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G25" t="s">
-        <v>764</v>
+        <v>758</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>765</v>
+        <v>759</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>766</v>
+        <v>760</v>
       </c>
       <c r="D26" t="s">
-        <v>767</v>
+        <v>761</v>
       </c>
       <c r="E26" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F26" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G26" t="s">
-        <v>768</v>
+        <v>762</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>769</v>
+        <v>763</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>770</v>
+        <v>764</v>
       </c>
       <c r="D27" t="s">
-        <v>771</v>
+        <v>765</v>
       </c>
       <c r="E27" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F27" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G27" t="s">
-        <v>772</v>
+        <v>766</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>773</v>
+        <v>767</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>774</v>
+        <v>768</v>
       </c>
       <c r="D28" t="s">
-        <v>775</v>
+        <v>769</v>
       </c>
       <c r="E28" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F28" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G28" t="s">
-        <v>776</v>
+        <v>770</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>777</v>
+        <v>771</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>778</v>
+        <v>772</v>
       </c>
       <c r="D29" t="s">
-        <v>779</v>
+        <v>773</v>
       </c>
       <c r="E29" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F29" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G29" t="s">
-        <v>780</v>
+        <v>774</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>781</v>
+        <v>775</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>782</v>
+        <v>776</v>
       </c>
       <c r="D30" t="s">
-        <v>783</v>
+        <v>777</v>
       </c>
       <c r="E30" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F30" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G30" t="s">
-        <v>784</v>
+        <v>778</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>785</v>
+        <v>779</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>786</v>
+        <v>780</v>
       </c>
       <c r="D31" t="s">
-        <v>787</v>
+        <v>781</v>
       </c>
       <c r="E31" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F31" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G31" t="s">
-        <v>788</v>
+        <v>782</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>789</v>
+        <v>783</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>790</v>
+        <v>784</v>
       </c>
       <c r="D32" t="s">
-        <v>791</v>
+        <v>785</v>
       </c>
       <c r="E32" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F32" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G32" t="s">
-        <v>792</v>
+        <v>786</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>793</v>
+        <v>787</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>794</v>
+        <v>788</v>
       </c>
       <c r="D33" t="s">
-        <v>795</v>
+        <v>789</v>
       </c>
       <c r="E33" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F33" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G33" t="s">
-        <v>796</v>
+        <v>790</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>797</v>
+        <v>791</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>798</v>
+        <v>792</v>
       </c>
       <c r="D34" t="s">
-        <v>799</v>
+        <v>793</v>
       </c>
       <c r="E34" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F34" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G34" t="s">
-        <v>800</v>
+        <v>794</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>801</v>
+        <v>795</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>802</v>
+        <v>796</v>
       </c>
       <c r="D35" t="s">
-        <v>803</v>
+        <v>797</v>
       </c>
       <c r="E35" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F35" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G35" t="s">
-        <v>804</v>
+        <v>798</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>805</v>
+        <v>799</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>806</v>
+        <v>800</v>
       </c>
       <c r="D36" t="s">
-        <v>807</v>
+        <v>801</v>
       </c>
       <c r="E36" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F36" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G36" t="s">
-        <v>808</v>
+        <v>802</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>809</v>
+        <v>803</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>810</v>
+        <v>804</v>
       </c>
       <c r="D37" t="s">
-        <v>811</v>
+        <v>805</v>
       </c>
       <c r="E37" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F37" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G37" t="s">
-        <v>812</v>
+        <v>806</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>813</v>
+        <v>807</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>814</v>
+        <v>808</v>
       </c>
       <c r="D38" t="s">
-        <v>815</v>
+        <v>809</v>
       </c>
       <c r="E38" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F38" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G38" t="s">
-        <v>816</v>
+        <v>810</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>817</v>
+        <v>811</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>818</v>
+        <v>812</v>
       </c>
       <c r="D39" t="s">
-        <v>819</v>
+        <v>813</v>
       </c>
       <c r="E39" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F39" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G39" t="s">
-        <v>820</v>
+        <v>814</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>821</v>
+        <v>815</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="D40" t="s">
-        <v>823</v>
+        <v>817</v>
       </c>
       <c r="E40" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F40" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G40" t="s">
-        <v>824</v>
+        <v>818</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>825</v>
+        <v>819</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>826</v>
+        <v>820</v>
       </c>
       <c r="D41" t="s">
-        <v>827</v>
+        <v>821</v>
       </c>
       <c r="E41" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F41" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G41" t="s">
-        <v>828</v>
+        <v>822</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>829</v>
+        <v>823</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>830</v>
+        <v>824</v>
       </c>
       <c r="D42" t="s">
-        <v>831</v>
+        <v>825</v>
       </c>
       <c r="E42" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F42" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G42" t="s">
-        <v>832</v>
+        <v>826</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>833</v>
+        <v>827</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>834</v>
+        <v>828</v>
       </c>
       <c r="D43" t="s">
-        <v>835</v>
+        <v>829</v>
       </c>
       <c r="E43" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F43" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G43" t="s">
-        <v>836</v>
+        <v>830</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>837</v>
+        <v>831</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>838</v>
+        <v>832</v>
       </c>
       <c r="D44" t="s">
-        <v>839</v>
+        <v>833</v>
       </c>
       <c r="E44" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F44" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G44" t="s">
-        <v>840</v>
+        <v>834</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>841</v>
+        <v>835</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>842</v>
+        <v>836</v>
       </c>
       <c r="D45" t="s">
-        <v>843</v>
+        <v>837</v>
       </c>
       <c r="E45" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F45" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G45" t="s">
-        <v>844</v>
+        <v>838</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>845</v>
+        <v>839</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>846</v>
+        <v>840</v>
       </c>
       <c r="D46" t="s">
-        <v>847</v>
+        <v>841</v>
       </c>
       <c r="E46" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F46" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G46" t="s">
-        <v>848</v>
+        <v>842</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>849</v>
+        <v>843</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>850</v>
+        <v>844</v>
       </c>
       <c r="D47" t="s">
-        <v>851</v>
+        <v>845</v>
       </c>
       <c r="E47" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F47" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G47" t="s">
-        <v>852</v>
+        <v>846</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>853</v>
+        <v>847</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>854</v>
+        <v>848</v>
       </c>
       <c r="D48" t="s">
-        <v>855</v>
+        <v>849</v>
       </c>
       <c r="E48" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F48" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G48" t="s">
-        <v>856</v>
+        <v>850</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>857</v>
+        <v>851</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>858</v>
+        <v>852</v>
       </c>
       <c r="D49" t="s">
-        <v>859</v>
+        <v>853</v>
       </c>
       <c r="E49" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F49" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G49" t="s">
-        <v>860</v>
+        <v>854</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>861</v>
+        <v>855</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5788,25 +5770,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>862</v>
+        <v>856</v>
       </c>
       <c r="D50" t="s">
-        <v>863</v>
+        <v>857</v>
       </c>
       <c r="E50" t="s">
-        <v>693</v>
+        <v>687</v>
       </c>
       <c r="F50" t="s">
-        <v>688</v>
+        <v>682</v>
       </c>
       <c r="G50" t="s">
-        <v>864</v>
+        <v>858</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>865</v>
+        <v>859</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5814,25 +5796,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>866</v>
+        <v>860</v>
       </c>
       <c r="D51" t="s">
-        <v>867</v>
+        <v>861</v>
       </c>
       <c r="E51" t="s">
-        <v>710</v>
+        <v>704</v>
       </c>
       <c r="F51" t="s">
-        <v>868</v>
+        <v>862</v>
       </c>
       <c r="G51" t="s">
-        <v>869</v>
+        <v>863</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>870</v>
+        <v>864</v>
       </c>
     </row>
   </sheetData>
@@ -5862,25 +5844,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>871</v>
+        <v>865</v>
       </c>
       <c r="C1" t="s">
-        <v>872</v>
+        <v>866</v>
       </c>
       <c r="D1" t="s">
-        <v>873</v>
+        <v>867</v>
       </c>
       <c r="E1" t="s">
-        <v>874</v>
+        <v>868</v>
       </c>
       <c r="F1" t="s">
-        <v>875</v>
+        <v>869</v>
       </c>
       <c r="G1" t="s">
-        <v>876</v>
+        <v>870</v>
       </c>
       <c r="H1" t="s">
-        <v>375</v>
+        <v>369</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5894,7 +5876,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -5914,28 +5896,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>871</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>872</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>875</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>876</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>877</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>878</v>
-      </c>
-      <c r="D3" s="1" t="s">
-        <v>879</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>880</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>881</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>882</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>883</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>884</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -5943,39 +5925,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>885</v>
+        <v>879</v>
       </c>
       <c r="C4" t="s">
-        <v>878</v>
+        <v>872</v>
       </c>
       <c r="D4" t="s">
-        <v>886</v>
+        <v>880</v>
       </c>
       <c r="E4" t="s">
-        <v>887</v>
+        <v>881</v>
       </c>
       <c r="F4" t="s">
-        <v>888</v>
+        <v>882</v>
       </c>
       <c r="G4" t="s">
-        <v>889</v>
+        <v>883</v>
       </c>
       <c r="H4" t="s">
-        <v>392</v>
+        <v>386</v>
       </c>
       <c r="I4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B5" t="s">
-        <v>890</v>
+        <v>884</v>
       </c>
       <c r="C5" t="s">
-        <v>891</v>
+        <v>885</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -5993,18 +5975,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>892</v>
+        <v>886</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B6" t="s">
-        <v>893</v>
+        <v>887</v>
       </c>
       <c r="C6" t="s">
-        <v>894</v>
+        <v>888</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6022,18 +6004,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>895</v>
+        <v>889</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B7" t="s">
-        <v>896</v>
+        <v>890</v>
       </c>
       <c r="C7" t="s">
-        <v>897</v>
+        <v>891</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6051,18 +6033,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>898</v>
+        <v>892</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B8" t="s">
-        <v>899</v>
+        <v>893</v>
       </c>
       <c r="C8" t="s">
-        <v>900</v>
+        <v>894</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6080,18 +6062,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>901</v>
+        <v>895</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B9" t="s">
-        <v>902</v>
+        <v>896</v>
       </c>
       <c r="C9" t="s">
-        <v>903</v>
+        <v>897</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6109,18 +6091,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>904</v>
+        <v>898</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B10" t="s">
-        <v>905</v>
+        <v>899</v>
       </c>
       <c r="C10" t="s">
-        <v>906</v>
+        <v>900</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6138,18 +6120,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>907</v>
+        <v>901</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B11" t="s">
-        <v>908</v>
+        <v>902</v>
       </c>
       <c r="C11" t="s">
-        <v>909</v>
+        <v>903</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6167,18 +6149,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>910</v>
+        <v>904</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B12" t="s">
-        <v>911</v>
+        <v>905</v>
       </c>
       <c r="C12" t="s">
-        <v>912</v>
+        <v>906</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6196,7 +6178,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>913</v>
+        <v>907</v>
       </c>
     </row>
   </sheetData>
@@ -6547,7 +6529,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H19"/>
+  <dimension ref="A1:H17"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
@@ -6555,7 +6537,7 @@
     <col min="5" max="5" width="84.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5">
+    <row r="1" spans="1:8">
       <c r="A1" s="6" t="s">
         <v>152</v>
       </c>
@@ -6570,7 +6552,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="2" spans="1:5">
+    <row r="2" spans="1:8">
       <c r="A2" s="6"/>
       <c r="B2" s="5" t="s">
         <v>153</v>
@@ -6583,7 +6565,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:8">
       <c r="A3" s="2" t="s">
         <v>156</v>
       </c>
@@ -6600,7 +6582,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:8">
       <c r="A4" s="2" t="s">
         <v>160</v>
       </c>
@@ -6617,7 +6599,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:8">
       <c r="A5" s="2" t="s">
         <v>163</v>
       </c>
@@ -6634,7 +6616,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:8">
       <c r="A6" s="2" t="s">
         <v>166</v>
       </c>
@@ -6651,7 +6633,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:8">
       <c r="A7" s="2" t="s">
         <v>169</v>
       </c>
@@ -6668,7 +6650,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:8">
       <c r="A8" s="2" t="s">
         <v>172</v>
       </c>
@@ -6685,57 +6667,23 @@
         <v>174</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="B9" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="2">
-        <v>90</v>
-      </c>
-      <c r="E9" s="2" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="B10" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>107</v>
-      </c>
-      <c r="D10" s="2">
-        <v>9</v>
-      </c>
-      <c r="E10" s="2" t="s">
-        <v>180</v>
-      </c>
+    <row r="15" spans="1:8">
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="7"/>
+    </row>
+    <row r="16" spans="1:8">
+      <c r="E16" s="1"/>
+      <c r="F16" s="1"/>
+      <c r="G16" s="1"/>
+      <c r="H16" s="8"/>
     </row>
     <row r="17" spans="5:8">
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="7"/>
-    </row>
-    <row r="18" spans="5:8">
-      <c r="E18" s="1"/>
-      <c r="F18" s="1"/>
-      <c r="G18" s="1"/>
-      <c r="H18" s="8"/>
-    </row>
-    <row r="19" spans="5:8">
-      <c r="E19" s="1"/>
-      <c r="F19" s="1"/>
-      <c r="G19" s="1"/>
-      <c r="H19" s="8"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
+      <c r="H17" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6776,55 +6724,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
+        <v>175</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>178</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>179</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="J1" t="s">
         <v>181</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="K1" t="s">
         <v>182</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="L1" t="s">
         <v>183</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="M1" t="s">
         <v>184</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="N1" t="s">
         <v>185</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="O1" t="s">
         <v>186</v>
       </c>
-      <c r="J1" t="s">
+      <c r="P1" t="s">
         <v>187</v>
       </c>
-      <c r="K1" t="s">
+      <c r="Q1" t="s">
         <v>188</v>
       </c>
-      <c r="L1" t="s">
+      <c r="R1" t="s">
         <v>189</v>
       </c>
-      <c r="M1" t="s">
+      <c r="S1" t="s">
         <v>190</v>
       </c>
-      <c r="N1" t="s">
+      <c r="T1" t="s">
         <v>191</v>
-      </c>
-      <c r="O1" t="s">
-        <v>192</v>
-      </c>
-      <c r="P1" t="s">
-        <v>193</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>194</v>
-      </c>
-      <c r="R1" t="s">
-        <v>195</v>
-      </c>
-      <c r="S1" t="s">
-        <v>196</v>
-      </c>
-      <c r="T1" t="s">
-        <v>197</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6895,10 +6843,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6912,55 +6860,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
+        <v>193</v>
+      </c>
+      <c r="D4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E4" t="s">
+        <v>195</v>
+      </c>
+      <c r="F4" t="s">
+        <v>196</v>
+      </c>
+      <c r="H4" t="s">
+        <v>197</v>
+      </c>
+      <c r="I4" t="s">
+        <v>198</v>
+      </c>
+      <c r="J4" t="s">
         <v>199</v>
       </c>
-      <c r="D4" t="s">
+      <c r="K4" t="s">
         <v>200</v>
       </c>
-      <c r="E4" t="s">
+      <c r="L4" t="s">
         <v>201</v>
       </c>
-      <c r="F4" t="s">
+      <c r="M4" t="s">
         <v>202</v>
       </c>
-      <c r="H4" t="s">
+      <c r="N4" t="s">
         <v>203</v>
       </c>
-      <c r="I4" t="s">
+      <c r="O4" t="s">
         <v>204</v>
       </c>
-      <c r="J4" t="s">
+      <c r="P4" t="s">
         <v>205</v>
       </c>
-      <c r="K4" t="s">
+      <c r="Q4" t="s">
         <v>206</v>
       </c>
-      <c r="L4" t="s">
+      <c r="R4" t="s">
         <v>207</v>
       </c>
-      <c r="M4" t="s">
+      <c r="S4" t="s">
         <v>208</v>
       </c>
-      <c r="N4" t="s">
+      <c r="T4" t="s">
         <v>209</v>
-      </c>
-      <c r="O4" t="s">
-        <v>210</v>
-      </c>
-      <c r="P4" t="s">
-        <v>211</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>212</v>
-      </c>
-      <c r="R4" t="s">
-        <v>213</v>
-      </c>
-      <c r="S4" t="s">
-        <v>214</v>
-      </c>
-      <c r="T4" t="s">
-        <v>215</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6968,58 +6916,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" t="s">
+        <v>211</v>
+      </c>
+      <c r="E5" t="s">
+        <v>212</v>
+      </c>
+      <c r="F5" t="s">
+        <v>213</v>
+      </c>
+      <c r="G5" t="s">
+        <v>183</v>
+      </c>
+      <c r="H5" t="s">
+        <v>214</v>
+      </c>
+      <c r="I5" t="s">
+        <v>215</v>
+      </c>
+      <c r="J5" t="s">
         <v>216</v>
       </c>
-      <c r="D5" t="s">
+      <c r="K5" t="s">
         <v>217</v>
       </c>
-      <c r="E5" t="s">
+      <c r="L5" t="s">
         <v>218</v>
       </c>
-      <c r="F5" t="s">
+      <c r="M5" t="s">
+        <v>212</v>
+      </c>
+      <c r="N5" t="s">
         <v>219</v>
       </c>
-      <c r="G5" t="s">
-        <v>189</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="O5" t="s">
         <v>220</v>
       </c>
-      <c r="I5" t="s">
+      <c r="P5" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q5" t="s">
         <v>221</v>
       </c>
-      <c r="J5" t="s">
+      <c r="R5" t="s">
         <v>222</v>
       </c>
-      <c r="K5" t="s">
+      <c r="S5" t="s">
         <v>223</v>
       </c>
-      <c r="L5" t="s">
+      <c r="T5" t="s">
         <v>224</v>
-      </c>
-      <c r="M5" t="s">
-        <v>218</v>
-      </c>
-      <c r="N5" t="s">
-        <v>225</v>
-      </c>
-      <c r="O5" t="s">
-        <v>226</v>
-      </c>
-      <c r="P5" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>227</v>
-      </c>
-      <c r="R5" t="s">
-        <v>228</v>
-      </c>
-      <c r="S5" t="s">
-        <v>229</v>
-      </c>
-      <c r="T5" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -7027,58 +6975,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>231</v>
+        <v>225</v>
       </c>
       <c r="D6" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="E6" t="s">
+        <v>212</v>
+      </c>
+      <c r="F6" t="s">
+        <v>221</v>
+      </c>
+      <c r="G6" t="s">
+        <v>183</v>
+      </c>
+      <c r="H6" t="s">
+        <v>227</v>
+      </c>
+      <c r="I6" t="s">
+        <v>215</v>
+      </c>
+      <c r="J6" t="s">
+        <v>216</v>
+      </c>
+      <c r="K6" t="s">
+        <v>217</v>
+      </c>
+      <c r="L6" t="s">
         <v>218</v>
       </c>
-      <c r="F6" t="s">
-        <v>227</v>
-      </c>
-      <c r="G6" t="s">
-        <v>189</v>
-      </c>
-      <c r="H6" t="s">
-        <v>233</v>
-      </c>
-      <c r="I6" t="s">
+      <c r="M6" t="s">
+        <v>212</v>
+      </c>
+      <c r="N6" t="s">
+        <v>219</v>
+      </c>
+      <c r="O6" t="s">
+        <v>220</v>
+      </c>
+      <c r="P6" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q6" t="s">
         <v>221</v>
       </c>
-      <c r="J6" t="s">
+      <c r="R6" t="s">
         <v>222</v>
       </c>
-      <c r="K6" t="s">
+      <c r="S6" t="s">
         <v>223</v>
       </c>
-      <c r="L6" t="s">
+      <c r="T6" t="s">
         <v>224</v>
-      </c>
-      <c r="M6" t="s">
-        <v>218</v>
-      </c>
-      <c r="N6" t="s">
-        <v>225</v>
-      </c>
-      <c r="O6" t="s">
-        <v>226</v>
-      </c>
-      <c r="P6" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>227</v>
-      </c>
-      <c r="R6" t="s">
-        <v>228</v>
-      </c>
-      <c r="S6" t="s">
-        <v>229</v>
-      </c>
-      <c r="T6" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -7086,58 +7034,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>234</v>
+        <v>228</v>
       </c>
       <c r="D7" t="s">
-        <v>235</v>
+        <v>229</v>
       </c>
       <c r="E7" t="s">
+        <v>212</v>
+      </c>
+      <c r="F7" t="s">
+        <v>222</v>
+      </c>
+      <c r="G7" t="s">
+        <v>183</v>
+      </c>
+      <c r="H7" t="s">
+        <v>230</v>
+      </c>
+      <c r="I7" t="s">
+        <v>215</v>
+      </c>
+      <c r="J7" t="s">
+        <v>216</v>
+      </c>
+      <c r="K7" t="s">
+        <v>217</v>
+      </c>
+      <c r="L7" t="s">
         <v>218</v>
       </c>
-      <c r="F7" t="s">
-        <v>228</v>
-      </c>
-      <c r="G7" t="s">
-        <v>189</v>
-      </c>
-      <c r="H7" t="s">
-        <v>236</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="M7" t="s">
+        <v>212</v>
+      </c>
+      <c r="N7" t="s">
+        <v>219</v>
+      </c>
+      <c r="O7" t="s">
+        <v>220</v>
+      </c>
+      <c r="P7" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q7" t="s">
         <v>221</v>
       </c>
-      <c r="J7" t="s">
+      <c r="R7" t="s">
         <v>222</v>
       </c>
-      <c r="K7" t="s">
+      <c r="S7" t="s">
         <v>223</v>
       </c>
-      <c r="L7" t="s">
+      <c r="T7" t="s">
         <v>224</v>
-      </c>
-      <c r="M7" t="s">
-        <v>218</v>
-      </c>
-      <c r="N7" t="s">
-        <v>225</v>
-      </c>
-      <c r="O7" t="s">
-        <v>226</v>
-      </c>
-      <c r="P7" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>227</v>
-      </c>
-      <c r="R7" t="s">
-        <v>228</v>
-      </c>
-      <c r="S7" t="s">
-        <v>229</v>
-      </c>
-      <c r="T7" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -7145,58 +7093,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>237</v>
+        <v>231</v>
       </c>
       <c r="D8" t="s">
-        <v>238</v>
+        <v>232</v>
       </c>
       <c r="E8" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F8" t="s">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="G8" t="s">
-        <v>189</v>
+        <v>183</v>
       </c>
       <c r="H8" t="s">
-        <v>239</v>
+        <v>233</v>
       </c>
       <c r="I8" t="s">
+        <v>215</v>
+      </c>
+      <c r="J8" t="s">
+        <v>216</v>
+      </c>
+      <c r="K8" t="s">
+        <v>217</v>
+      </c>
+      <c r="L8" t="s">
+        <v>218</v>
+      </c>
+      <c r="M8" t="s">
+        <v>212</v>
+      </c>
+      <c r="N8" t="s">
+        <v>219</v>
+      </c>
+      <c r="O8" t="s">
+        <v>220</v>
+      </c>
+      <c r="P8" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q8" t="s">
         <v>221</v>
       </c>
-      <c r="J8" t="s">
+      <c r="R8" t="s">
         <v>222</v>
       </c>
-      <c r="K8" t="s">
+      <c r="S8" t="s">
         <v>223</v>
       </c>
-      <c r="L8" t="s">
+      <c r="T8" t="s">
         <v>224</v>
-      </c>
-      <c r="M8" t="s">
-        <v>218</v>
-      </c>
-      <c r="N8" t="s">
-        <v>225</v>
-      </c>
-      <c r="O8" t="s">
-        <v>226</v>
-      </c>
-      <c r="P8" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>227</v>
-      </c>
-      <c r="R8" t="s">
-        <v>228</v>
-      </c>
-      <c r="S8" t="s">
-        <v>229</v>
-      </c>
-      <c r="T8" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -7204,58 +7152,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="D9" t="s">
-        <v>241</v>
+        <v>235</v>
       </c>
       <c r="E9" t="s">
+        <v>212</v>
+      </c>
+      <c r="F9" t="s">
+        <v>222</v>
+      </c>
+      <c r="G9" t="s">
+        <v>183</v>
+      </c>
+      <c r="H9" t="s">
+        <v>214</v>
+      </c>
+      <c r="I9" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" t="s">
+        <v>216</v>
+      </c>
+      <c r="K9" t="s">
+        <v>217</v>
+      </c>
+      <c r="L9" t="s">
         <v>218</v>
       </c>
-      <c r="F9" t="s">
-        <v>228</v>
-      </c>
-      <c r="G9" t="s">
-        <v>189</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="M9" t="s">
+        <v>212</v>
+      </c>
+      <c r="N9" t="s">
+        <v>219</v>
+      </c>
+      <c r="O9" t="s">
         <v>220</v>
       </c>
-      <c r="I9" t="s">
-        <v>242</v>
-      </c>
-      <c r="J9" t="s">
+      <c r="P9" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>221</v>
+      </c>
+      <c r="R9" t="s">
         <v>222</v>
       </c>
-      <c r="K9" t="s">
+      <c r="S9" t="s">
         <v>223</v>
       </c>
-      <c r="L9" t="s">
+      <c r="T9" t="s">
         <v>224</v>
-      </c>
-      <c r="M9" t="s">
-        <v>218</v>
-      </c>
-      <c r="N9" t="s">
-        <v>225</v>
-      </c>
-      <c r="O9" t="s">
-        <v>226</v>
-      </c>
-      <c r="P9" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>227</v>
-      </c>
-      <c r="R9" t="s">
-        <v>228</v>
-      </c>
-      <c r="S9" t="s">
-        <v>229</v>
-      </c>
-      <c r="T9" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -7263,58 +7211,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>243</v>
+        <v>237</v>
       </c>
       <c r="D10" t="s">
-        <v>244</v>
+        <v>238</v>
       </c>
       <c r="E10" t="s">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="F10" t="s">
+        <v>213</v>
+      </c>
+      <c r="G10" t="s">
+        <v>183</v>
+      </c>
+      <c r="H10" t="s">
+        <v>214</v>
+      </c>
+      <c r="I10" t="s">
+        <v>239</v>
+      </c>
+      <c r="J10" t="s">
+        <v>216</v>
+      </c>
+      <c r="K10" t="s">
+        <v>217</v>
+      </c>
+      <c r="L10" t="s">
+        <v>218</v>
+      </c>
+      <c r="M10" t="s">
+        <v>212</v>
+      </c>
+      <c r="N10" t="s">
         <v>219</v>
       </c>
-      <c r="G10" t="s">
-        <v>189</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="O10" t="s">
         <v>220</v>
       </c>
-      <c r="I10" t="s">
-        <v>245</v>
-      </c>
-      <c r="J10" t="s">
+      <c r="P10" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>221</v>
+      </c>
+      <c r="R10" t="s">
         <v>222</v>
       </c>
-      <c r="K10" t="s">
+      <c r="S10" t="s">
         <v>223</v>
       </c>
-      <c r="L10" t="s">
+      <c r="T10" t="s">
         <v>224</v>
-      </c>
-      <c r="M10" t="s">
-        <v>218</v>
-      </c>
-      <c r="N10" t="s">
-        <v>225</v>
-      </c>
-      <c r="O10" t="s">
-        <v>226</v>
-      </c>
-      <c r="P10" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>227</v>
-      </c>
-      <c r="R10" t="s">
-        <v>228</v>
-      </c>
-      <c r="S10" t="s">
-        <v>229</v>
-      </c>
-      <c r="T10" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -7322,58 +7270,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>246</v>
+        <v>240</v>
       </c>
       <c r="D11" t="s">
-        <v>247</v>
+        <v>241</v>
       </c>
       <c r="E11" t="s">
+        <v>212</v>
+      </c>
+      <c r="F11" t="s">
+        <v>224</v>
+      </c>
+      <c r="G11" t="s">
+        <v>183</v>
+      </c>
+      <c r="H11" t="s">
+        <v>227</v>
+      </c>
+      <c r="I11" t="s">
+        <v>236</v>
+      </c>
+      <c r="J11" t="s">
+        <v>216</v>
+      </c>
+      <c r="K11" t="s">
+        <v>217</v>
+      </c>
+      <c r="L11" t="s">
         <v>218</v>
       </c>
-      <c r="F11" t="s">
-        <v>230</v>
-      </c>
-      <c r="G11" t="s">
-        <v>189</v>
-      </c>
-      <c r="H11" t="s">
-        <v>233</v>
-      </c>
-      <c r="I11" t="s">
-        <v>242</v>
-      </c>
-      <c r="J11" t="s">
+      <c r="M11" t="s">
+        <v>212</v>
+      </c>
+      <c r="N11" t="s">
+        <v>219</v>
+      </c>
+      <c r="O11" t="s">
+        <v>220</v>
+      </c>
+      <c r="P11" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>221</v>
+      </c>
+      <c r="R11" t="s">
         <v>222</v>
       </c>
-      <c r="K11" t="s">
+      <c r="S11" t="s">
         <v>223</v>
       </c>
-      <c r="L11" t="s">
+      <c r="T11" t="s">
         <v>224</v>
-      </c>
-      <c r="M11" t="s">
-        <v>218</v>
-      </c>
-      <c r="N11" t="s">
-        <v>225</v>
-      </c>
-      <c r="O11" t="s">
-        <v>226</v>
-      </c>
-      <c r="P11" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>227</v>
-      </c>
-      <c r="R11" t="s">
-        <v>228</v>
-      </c>
-      <c r="S11" t="s">
-        <v>229</v>
-      </c>
-      <c r="T11" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -7381,58 +7329,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>248</v>
+        <v>242</v>
       </c>
       <c r="D12" t="s">
-        <v>249</v>
+        <v>243</v>
       </c>
       <c r="E12" t="s">
+        <v>212</v>
+      </c>
+      <c r="F12" t="s">
+        <v>213</v>
+      </c>
+      <c r="G12" t="s">
+        <v>183</v>
+      </c>
+      <c r="H12" t="s">
+        <v>227</v>
+      </c>
+      <c r="I12" t="s">
+        <v>239</v>
+      </c>
+      <c r="J12" t="s">
+        <v>216</v>
+      </c>
+      <c r="K12" t="s">
+        <v>217</v>
+      </c>
+      <c r="L12" t="s">
         <v>218</v>
       </c>
-      <c r="F12" t="s">
+      <c r="M12" t="s">
+        <v>212</v>
+      </c>
+      <c r="N12" t="s">
         <v>219</v>
       </c>
-      <c r="G12" t="s">
-        <v>189</v>
-      </c>
-      <c r="H12" t="s">
-        <v>233</v>
-      </c>
-      <c r="I12" t="s">
-        <v>245</v>
-      </c>
-      <c r="J12" t="s">
+      <c r="O12" t="s">
+        <v>220</v>
+      </c>
+      <c r="P12" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>221</v>
+      </c>
+      <c r="R12" t="s">
         <v>222</v>
       </c>
-      <c r="K12" t="s">
+      <c r="S12" t="s">
         <v>223</v>
       </c>
-      <c r="L12" t="s">
+      <c r="T12" t="s">
         <v>224</v>
-      </c>
-      <c r="M12" t="s">
-        <v>218</v>
-      </c>
-      <c r="N12" t="s">
-        <v>225</v>
-      </c>
-      <c r="O12" t="s">
-        <v>226</v>
-      </c>
-      <c r="P12" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>227</v>
-      </c>
-      <c r="R12" t="s">
-        <v>228</v>
-      </c>
-      <c r="S12" t="s">
-        <v>229</v>
-      </c>
-      <c r="T12" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -7440,58 +7388,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>250</v>
+        <v>244</v>
       </c>
       <c r="D13" t="s">
-        <v>251</v>
+        <v>245</v>
       </c>
       <c r="E13" t="s">
+        <v>212</v>
+      </c>
+      <c r="F13" t="s">
+        <v>224</v>
+      </c>
+      <c r="G13" t="s">
+        <v>183</v>
+      </c>
+      <c r="H13" t="s">
+        <v>230</v>
+      </c>
+      <c r="I13" t="s">
+        <v>236</v>
+      </c>
+      <c r="J13" t="s">
+        <v>216</v>
+      </c>
+      <c r="K13" t="s">
+        <v>217</v>
+      </c>
+      <c r="L13" t="s">
         <v>218</v>
       </c>
-      <c r="F13" t="s">
-        <v>230</v>
-      </c>
-      <c r="G13" t="s">
-        <v>189</v>
-      </c>
-      <c r="H13" t="s">
-        <v>236</v>
-      </c>
-      <c r="I13" t="s">
-        <v>242</v>
-      </c>
-      <c r="J13" t="s">
+      <c r="M13" t="s">
+        <v>212</v>
+      </c>
+      <c r="N13" t="s">
+        <v>219</v>
+      </c>
+      <c r="O13" t="s">
+        <v>220</v>
+      </c>
+      <c r="P13" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>221</v>
+      </c>
+      <c r="R13" t="s">
         <v>222</v>
       </c>
-      <c r="K13" t="s">
+      <c r="S13" t="s">
         <v>223</v>
       </c>
-      <c r="L13" t="s">
+      <c r="T13" t="s">
         <v>224</v>
-      </c>
-      <c r="M13" t="s">
-        <v>218</v>
-      </c>
-      <c r="N13" t="s">
-        <v>225</v>
-      </c>
-      <c r="O13" t="s">
-        <v>226</v>
-      </c>
-      <c r="P13" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>227</v>
-      </c>
-      <c r="R13" t="s">
-        <v>228</v>
-      </c>
-      <c r="S13" t="s">
-        <v>229</v>
-      </c>
-      <c r="T13" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -7499,58 +7447,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>252</v>
+        <v>246</v>
       </c>
       <c r="D14" t="s">
-        <v>253</v>
+        <v>247</v>
       </c>
       <c r="E14" t="s">
+        <v>212</v>
+      </c>
+      <c r="F14" t="s">
+        <v>213</v>
+      </c>
+      <c r="G14" t="s">
+        <v>183</v>
+      </c>
+      <c r="H14" t="s">
+        <v>230</v>
+      </c>
+      <c r="I14" t="s">
+        <v>239</v>
+      </c>
+      <c r="J14" t="s">
+        <v>216</v>
+      </c>
+      <c r="K14" t="s">
+        <v>217</v>
+      </c>
+      <c r="L14" t="s">
         <v>218</v>
       </c>
-      <c r="F14" t="s">
+      <c r="M14" t="s">
+        <v>212</v>
+      </c>
+      <c r="N14" t="s">
         <v>219</v>
       </c>
-      <c r="G14" t="s">
-        <v>189</v>
-      </c>
-      <c r="H14" t="s">
-        <v>236</v>
-      </c>
-      <c r="I14" t="s">
-        <v>245</v>
-      </c>
-      <c r="J14" t="s">
+      <c r="O14" t="s">
+        <v>220</v>
+      </c>
+      <c r="P14" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>221</v>
+      </c>
+      <c r="R14" t="s">
         <v>222</v>
       </c>
-      <c r="K14" t="s">
+      <c r="S14" t="s">
         <v>223</v>
       </c>
-      <c r="L14" t="s">
+      <c r="T14" t="s">
         <v>224</v>
-      </c>
-      <c r="M14" t="s">
-        <v>218</v>
-      </c>
-      <c r="N14" t="s">
-        <v>225</v>
-      </c>
-      <c r="O14" t="s">
-        <v>226</v>
-      </c>
-      <c r="P14" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>227</v>
-      </c>
-      <c r="R14" t="s">
-        <v>228</v>
-      </c>
-      <c r="S14" t="s">
-        <v>229</v>
-      </c>
-      <c r="T14" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -7558,58 +7506,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>254</v>
+        <v>248</v>
       </c>
       <c r="D15" t="s">
-        <v>255</v>
+        <v>249</v>
       </c>
       <c r="E15" t="s">
+        <v>212</v>
+      </c>
+      <c r="F15" t="s">
+        <v>213</v>
+      </c>
+      <c r="G15" t="s">
+        <v>183</v>
+      </c>
+      <c r="H15" t="s">
+        <v>233</v>
+      </c>
+      <c r="I15" t="s">
+        <v>236</v>
+      </c>
+      <c r="J15" t="s">
+        <v>216</v>
+      </c>
+      <c r="K15" t="s">
+        <v>217</v>
+      </c>
+      <c r="L15" t="s">
         <v>218</v>
       </c>
-      <c r="F15" t="s">
+      <c r="M15" t="s">
+        <v>212</v>
+      </c>
+      <c r="N15" t="s">
         <v>219</v>
       </c>
-      <c r="G15" t="s">
-        <v>189</v>
-      </c>
-      <c r="H15" t="s">
-        <v>239</v>
-      </c>
-      <c r="I15" t="s">
-        <v>242</v>
-      </c>
-      <c r="J15" t="s">
+      <c r="O15" t="s">
+        <v>220</v>
+      </c>
+      <c r="P15" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>221</v>
+      </c>
+      <c r="R15" t="s">
         <v>222</v>
       </c>
-      <c r="K15" t="s">
+      <c r="S15" t="s">
         <v>223</v>
       </c>
-      <c r="L15" t="s">
+      <c r="T15" t="s">
         <v>224</v>
-      </c>
-      <c r="M15" t="s">
-        <v>218</v>
-      </c>
-      <c r="N15" t="s">
-        <v>225</v>
-      </c>
-      <c r="O15" t="s">
-        <v>226</v>
-      </c>
-      <c r="P15" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>227</v>
-      </c>
-      <c r="R15" t="s">
-        <v>228</v>
-      </c>
-      <c r="S15" t="s">
-        <v>229</v>
-      </c>
-      <c r="T15" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7617,58 +7565,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="D16" t="s">
-        <v>257</v>
+        <v>251</v>
       </c>
       <c r="E16" t="s">
+        <v>212</v>
+      </c>
+      <c r="F16" t="s">
+        <v>223</v>
+      </c>
+      <c r="G16" t="s">
+        <v>183</v>
+      </c>
+      <c r="H16" t="s">
+        <v>233</v>
+      </c>
+      <c r="I16" t="s">
+        <v>239</v>
+      </c>
+      <c r="J16" t="s">
+        <v>216</v>
+      </c>
+      <c r="K16" t="s">
+        <v>217</v>
+      </c>
+      <c r="L16" t="s">
         <v>218</v>
       </c>
-      <c r="F16" t="s">
-        <v>229</v>
-      </c>
-      <c r="G16" t="s">
-        <v>189</v>
-      </c>
-      <c r="H16" t="s">
-        <v>239</v>
-      </c>
-      <c r="I16" t="s">
-        <v>245</v>
-      </c>
-      <c r="J16" t="s">
+      <c r="M16" t="s">
+        <v>212</v>
+      </c>
+      <c r="N16" t="s">
+        <v>219</v>
+      </c>
+      <c r="O16" t="s">
+        <v>220</v>
+      </c>
+      <c r="P16" t="s">
+        <v>213</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>221</v>
+      </c>
+      <c r="R16" t="s">
         <v>222</v>
       </c>
-      <c r="K16" t="s">
+      <c r="S16" t="s">
         <v>223</v>
       </c>
-      <c r="L16" t="s">
+      <c r="T16" t="s">
         <v>224</v>
-      </c>
-      <c r="M16" t="s">
-        <v>218</v>
-      </c>
-      <c r="N16" t="s">
-        <v>225</v>
-      </c>
-      <c r="O16" t="s">
-        <v>226</v>
-      </c>
-      <c r="P16" t="s">
-        <v>219</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>227</v>
-      </c>
-      <c r="R16" t="s">
-        <v>228</v>
-      </c>
-      <c r="S16" t="s">
-        <v>229</v>
-      </c>
-      <c r="T16" t="s">
-        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -7697,16 +7645,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>259</v>
+        <v>253</v>
       </c>
       <c r="E1" t="s">
-        <v>260</v>
+        <v>254</v>
       </c>
       <c r="F1" t="s">
-        <v>261</v>
+        <v>255</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7720,7 +7668,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>262</v>
+        <v>256</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7745,16 +7693,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="D4" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="F4" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7768,10 +7716,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="F5" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7779,16 +7727,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="F6" t="s">
-        <v>271</v>
+        <v>265</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7802,10 +7750,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>272</v>
+        <v>266</v>
       </c>
       <c r="F7" t="s">
-        <v>273</v>
+        <v>267</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7819,10 +7767,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>274</v>
+        <v>268</v>
       </c>
       <c r="F8" t="s">
-        <v>275</v>
+        <v>269</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7836,10 +7784,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>276</v>
+        <v>270</v>
       </c>
       <c r="F9" t="s">
-        <v>277</v>
+        <v>271</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7847,16 +7795,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="D10" t="s">
-        <v>279</v>
+        <v>273</v>
       </c>
       <c r="E10" t="s">
-        <v>280</v>
+        <v>274</v>
       </c>
       <c r="F10" t="s">
-        <v>281</v>
+        <v>275</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7870,10 +7818,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>282</v>
+        <v>276</v>
       </c>
       <c r="F11" t="s">
-        <v>283</v>
+        <v>277</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7887,10 +7835,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>284</v>
+        <v>278</v>
       </c>
       <c r="F12" t="s">
-        <v>285</v>
+        <v>279</v>
       </c>
     </row>
   </sheetData>
@@ -7923,34 +7871,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="E1" t="s">
+        <v>281</v>
+      </c>
+      <c r="G1" t="s">
+        <v>282</v>
+      </c>
+      <c r="H1" t="s">
+        <v>283</v>
+      </c>
+      <c r="I1" t="s">
+        <v>284</v>
+      </c>
+      <c r="J1" t="s">
+        <v>285</v>
+      </c>
+      <c r="K1" t="s">
         <v>286</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>287</v>
       </c>
-      <c r="G1" t="s">
+      <c r="M1" t="s">
         <v>288</v>
       </c>
-      <c r="H1" t="s">
+      <c r="N1" t="s">
         <v>289</v>
-      </c>
-      <c r="I1" t="s">
-        <v>290</v>
-      </c>
-      <c r="J1" t="s">
-        <v>291</v>
-      </c>
-      <c r="K1" t="s">
-        <v>292</v>
-      </c>
-      <c r="L1" t="s">
-        <v>293</v>
-      </c>
-      <c r="M1" t="s">
-        <v>294</v>
-      </c>
-      <c r="N1" t="s">
-        <v>295</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7961,10 +7909,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="E2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7976,7 +7924,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7998,13 +7946,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>298</v>
+        <v>292</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>299</v>
+        <v>293</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>300</v>
+        <v>294</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -8015,40 +7963,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>295</v>
+      </c>
+      <c r="D4" t="s">
+        <v>296</v>
+      </c>
+      <c r="E4" t="s">
+        <v>297</v>
+      </c>
+      <c r="F4" t="s">
+        <v>296</v>
+      </c>
+      <c r="G4" t="s">
+        <v>298</v>
+      </c>
+      <c r="H4" t="s">
+        <v>299</v>
+      </c>
+      <c r="I4" t="s">
+        <v>300</v>
+      </c>
+      <c r="J4" t="s">
         <v>301</v>
       </c>
-      <c r="D4" t="s">
+      <c r="K4" t="s">
         <v>302</v>
       </c>
-      <c r="E4" t="s">
+      <c r="L4" t="s">
         <v>303</v>
       </c>
-      <c r="F4" t="s">
-        <v>302</v>
-      </c>
-      <c r="G4" t="s">
+      <c r="M4" t="s">
+        <v>201</v>
+      </c>
+      <c r="N4" t="s">
         <v>304</v>
-      </c>
-      <c r="H4" t="s">
-        <v>305</v>
-      </c>
-      <c r="I4" t="s">
-        <v>306</v>
-      </c>
-      <c r="J4" t="s">
-        <v>307</v>
-      </c>
-      <c r="K4" t="s">
-        <v>308</v>
-      </c>
-      <c r="L4" t="s">
-        <v>309</v>
-      </c>
-      <c r="M4" t="s">
-        <v>207</v>
-      </c>
-      <c r="N4" t="s">
-        <v>310</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -8071,13 +8019,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L5" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M5" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8091,22 +8039,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H6" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L6" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M6" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8120,22 +8068,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H7" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L7" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M7" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8149,22 +8097,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H8" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L8" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M8" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8178,22 +8126,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H9" t="s">
-        <v>194</v>
+        <v>188</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L9" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M9" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8207,22 +8155,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H10" t="s">
-        <v>195</v>
+        <v>189</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L10" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M10" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8236,22 +8184,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H11" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="L11" t="s">
-        <v>311</v>
+        <v>305</v>
       </c>
       <c r="M11" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8265,22 +8213,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="H12" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="L12" t="s">
-        <v>313</v>
+        <v>307</v>
       </c>
       <c r="M12" t="s">
-        <v>312</v>
+        <v>306</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8288,31 +8236,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
       <c r="G13" t="s">
-        <v>190</v>
+        <v>184</v>
       </c>
       <c r="H13" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
+        <v>305</v>
+      </c>
+      <c r="L13" t="s">
+        <v>310</v>
+      </c>
+      <c r="M13" t="s">
         <v>311</v>
       </c>
-      <c r="L13" t="s">
-        <v>316</v>
-      </c>
-      <c r="M13" t="s">
-        <v>317</v>
-      </c>
       <c r="N13" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8320,10 +8268,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>319</v>
+        <v>313</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>320</v>
+        <v>314</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -8332,7 +8280,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8340,10 +8288,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>322</v>
+        <v>316</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>323</v>
+        <v>317</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -8352,7 +8300,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>321</v>
+        <v>315</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8360,10 +8308,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>324</v>
+        <v>318</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>325</v>
+        <v>319</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -8372,7 +8320,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>326</v>
+        <v>320</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -8380,19 +8328,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>327</v>
+        <v>321</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>328</v>
+        <v>322</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F17" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="N17" t="s">
-        <v>331</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -8400,10 +8348,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>332</v>
+        <v>326</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>333</v>
+        <v>327</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -8412,7 +8360,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>334</v>
+        <v>328</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -8420,10 +8368,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>335</v>
+        <v>329</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>336</v>
+        <v>330</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -8432,7 +8380,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>337</v>
+        <v>331</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -8440,10 +8388,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>338</v>
+        <v>332</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>339</v>
+        <v>333</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -8452,7 +8400,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>340</v>
+        <v>334</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -8460,19 +8408,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>341</v>
+        <v>335</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>342</v>
+        <v>336</v>
       </c>
       <c r="E21" t="s">
-        <v>329</v>
+        <v>323</v>
       </c>
       <c r="F21" t="s">
-        <v>330</v>
+        <v>324</v>
       </c>
       <c r="N21" t="s">
-        <v>343</v>
+        <v>337</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -8480,16 +8428,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>344</v>
+        <v>338</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>345</v>
+        <v>339</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>314</v>
+        <v>308</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>315</v>
+        <v>309</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -8497,10 +8445,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>346</v>
+        <v>340</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>347</v>
+        <v>341</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -8514,10 +8462,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>348</v>
+        <v>342</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>349</v>
+        <v>343</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -8531,10 +8479,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>350</v>
+        <v>344</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>351</v>
+        <v>345</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -8548,10 +8496,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>352</v>
+        <v>346</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>353</v>
+        <v>347</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -8565,10 +8513,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>354</v>
+        <v>348</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>355</v>
+        <v>349</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8582,10 +8530,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>356</v>
+        <v>350</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>357</v>
+        <v>351</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8599,10 +8547,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>358</v>
+        <v>352</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>359</v>
+        <v>353</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8611,10 +8559,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N29" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8622,10 +8570,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>360</v>
+        <v>354</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>361</v>
+        <v>355</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8639,10 +8587,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>362</v>
+        <v>356</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>363</v>
+        <v>357</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8656,10 +8604,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>364</v>
+        <v>358</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>365</v>
+        <v>359</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8668,10 +8616,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>317</v>
+        <v>311</v>
       </c>
       <c r="N32" t="s">
-        <v>318</v>
+        <v>312</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -8679,10 +8627,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>366</v>
+        <v>360</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>367</v>
+        <v>361</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -8691,7 +8639,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>368</v>
+        <v>362</v>
       </c>
     </row>
   </sheetData>
@@ -8727,31 +8675,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
+        <v>363</v>
+      </c>
+      <c r="D1" t="s">
+        <v>364</v>
+      </c>
+      <c r="E1" t="s">
+        <v>365</v>
+      </c>
+      <c r="F1" t="s">
+        <v>366</v>
+      </c>
+      <c r="G1" t="s">
+        <v>367</v>
+      </c>
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
+        <v>368</v>
+      </c>
+      <c r="J1" t="s">
         <v>369</v>
       </c>
-      <c r="D1" t="s">
-        <v>370</v>
-      </c>
-      <c r="E1" t="s">
-        <v>371</v>
-      </c>
-      <c r="F1" t="s">
-        <v>372</v>
-      </c>
-      <c r="G1" t="s">
-        <v>373</v>
-      </c>
-      <c r="H1" t="s">
-        <v>286</v>
-      </c>
-      <c r="I1" t="s">
-        <v>374</v>
-      </c>
-      <c r="J1" t="s">
-        <v>375</v>
-      </c>
       <c r="K1" t="s">
-        <v>295</v>
+        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8777,10 +8725,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>296</v>
+        <v>290</v>
       </c>
       <c r="I2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8794,34 +8742,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
+        <v>370</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>371</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>372</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>373</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>374</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>375</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>376</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" s="1" t="s">
         <v>377</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" s="1" t="s">
         <v>378</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>379</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>380</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>381</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>382</v>
-      </c>
-      <c r="I3" s="1" t="s">
-        <v>383</v>
-      </c>
-      <c r="J3" s="1" t="s">
-        <v>384</v>
-      </c>
       <c r="K3" s="1" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8832,31 +8780,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>379</v>
+      </c>
+      <c r="D4" t="s">
+        <v>380</v>
+      </c>
+      <c r="E4" t="s">
+        <v>381</v>
+      </c>
+      <c r="F4" t="s">
+        <v>382</v>
+      </c>
+      <c r="G4" t="s">
+        <v>383</v>
+      </c>
+      <c r="H4" t="s">
+        <v>384</v>
+      </c>
+      <c r="I4" t="s">
         <v>385</v>
       </c>
-      <c r="D4" t="s">
+      <c r="J4" t="s">
         <v>386</v>
       </c>
-      <c r="E4" t="s">
-        <v>387</v>
-      </c>
-      <c r="F4" t="s">
-        <v>388</v>
-      </c>
-      <c r="G4" t="s">
-        <v>389</v>
-      </c>
-      <c r="H4" t="s">
-        <v>390</v>
-      </c>
-      <c r="I4" t="s">
-        <v>391</v>
-      </c>
-      <c r="J4" t="s">
-        <v>392</v>
-      </c>
       <c r="K4" t="s">
-        <v>310</v>
+        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8864,7 +8812,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>393</v>
+        <v>387</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8888,7 +8836,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>394</v>
+        <v>388</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8896,7 +8844,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>395</v>
+        <v>389</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8920,7 +8868,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8928,7 +8876,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>397</v>
+        <v>391</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8952,7 +8900,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8960,7 +8908,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>398</v>
+        <v>392</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8984,7 +8932,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
     </row>
   </sheetData>
@@ -9015,16 +8963,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>258</v>
+        <v>252</v>
       </c>
       <c r="D1" t="s">
-        <v>399</v>
+        <v>393</v>
       </c>
       <c r="E1" t="s">
-        <v>400</v>
+        <v>394</v>
       </c>
       <c r="F1" t="s">
-        <v>401</v>
+        <v>395</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -9041,7 +8989,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -9054,10 +9002,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>402</v>
+        <v>396</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>403</v>
+        <v>397</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9068,13 +9016,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>404</v>
+        <v>398</v>
       </c>
       <c r="D4" t="s">
-        <v>405</v>
+        <v>399</v>
       </c>
       <c r="E4" t="s">
-        <v>406</v>
+        <v>400</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9082,7 +9030,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>407</v>
+        <v>401</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -9091,7 +9039,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>408</v>
+        <v>402</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9099,7 +9047,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>409</v>
+        <v>403</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -9108,7 +9056,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>410</v>
+        <v>404</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9116,7 +9064,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>411</v>
+        <v>405</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -9125,7 +9073,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>412</v>
+        <v>406</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9133,7 +9081,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>413</v>
+        <v>407</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -9142,7 +9090,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>414</v>
+        <v>408</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9180,40 +9128,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>409</v>
+      </c>
+      <c r="C1" t="s">
+        <v>410</v>
+      </c>
+      <c r="D1" t="s">
+        <v>411</v>
+      </c>
+      <c r="E1" t="s">
+        <v>412</v>
+      </c>
+      <c r="F1" t="s">
+        <v>413</v>
+      </c>
+      <c r="G1" t="s">
+        <v>414</v>
+      </c>
+      <c r="H1" t="s">
+        <v>289</v>
+      </c>
+      <c r="I1" t="s">
         <v>415</v>
       </c>
-      <c r="C1" t="s">
+      <c r="J1" t="s">
         <v>416</v>
       </c>
-      <c r="D1" t="s">
+      <c r="K1" t="s">
         <v>417</v>
       </c>
-      <c r="E1" t="s">
+      <c r="L1" t="s">
         <v>418</v>
       </c>
-      <c r="F1" t="s">
+      <c r="M1" t="s">
         <v>419</v>
-      </c>
-      <c r="G1" t="s">
-        <v>420</v>
-      </c>
-      <c r="H1" t="s">
-        <v>295</v>
-      </c>
-      <c r="I1" t="s">
-        <v>421</v>
-      </c>
-      <c r="J1" t="s">
-        <v>422</v>
-      </c>
-      <c r="K1" t="s">
-        <v>423</v>
-      </c>
-      <c r="L1" t="s">
-        <v>424</v>
-      </c>
-      <c r="M1" t="s">
-        <v>425</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -9227,16 +9175,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>426</v>
+        <v>420</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>427</v>
+        <v>421</v>
       </c>
       <c r="G2" t="s">
-        <v>297</v>
+        <v>291</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -9262,40 +9210,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>422</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>423</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>424</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>425</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>426</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>427</v>
+      </c>
+      <c r="H3" s="1" t="s">
         <v>428</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="I3" t="s">
         <v>429</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="J3" t="s">
         <v>430</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="K3" t="s">
         <v>431</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="L3" t="s">
         <v>432</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="M3" t="s">
         <v>433</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>434</v>
-      </c>
-      <c r="I3" t="s">
-        <v>435</v>
-      </c>
-      <c r="J3" t="s">
-        <v>436</v>
-      </c>
-      <c r="K3" t="s">
-        <v>437</v>
-      </c>
-      <c r="L3" t="s">
-        <v>438</v>
-      </c>
-      <c r="M3" t="s">
-        <v>439</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9303,54 +9251,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>434</v>
+      </c>
+      <c r="C4" t="s">
+        <v>435</v>
+      </c>
+      <c r="D4" t="s">
+        <v>436</v>
+      </c>
+      <c r="E4" t="s">
+        <v>437</v>
+      </c>
+      <c r="F4" t="s">
+        <v>438</v>
+      </c>
+      <c r="G4" t="s">
+        <v>439</v>
+      </c>
+      <c r="H4" t="s">
+        <v>304</v>
+      </c>
+      <c r="I4" t="s">
         <v>440</v>
       </c>
-      <c r="C4" t="s">
+      <c r="J4" t="s">
         <v>441</v>
       </c>
-      <c r="D4" t="s">
+      <c r="K4" t="s">
         <v>442</v>
       </c>
-      <c r="E4" t="s">
+      <c r="L4" t="s">
         <v>443</v>
       </c>
-      <c r="F4" t="s">
+      <c r="M4" t="s">
         <v>444</v>
-      </c>
-      <c r="G4" t="s">
-        <v>445</v>
-      </c>
-      <c r="H4" t="s">
-        <v>310</v>
-      </c>
-      <c r="I4" t="s">
-        <v>446</v>
-      </c>
-      <c r="J4" t="s">
-        <v>447</v>
-      </c>
-      <c r="K4" t="s">
-        <v>448</v>
-      </c>
-      <c r="L4" t="s">
-        <v>449</v>
-      </c>
-      <c r="M4" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>451</v>
+        <v>445</v>
       </c>
       <c r="D5" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -9362,36 +9310,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>453</v>
+        <v>447</v>
       </c>
       <c r="I5" t="s">
-        <v>454</v>
+        <v>448</v>
       </c>
       <c r="J5" t="s">
-        <v>455</v>
+        <v>449</v>
       </c>
       <c r="K5" t="s">
-        <v>456</v>
+        <v>450</v>
       </c>
       <c r="L5" t="s">
-        <v>457</v>
+        <v>451</v>
       </c>
       <c r="M5" t="s">
-        <v>458</v>
+        <v>452</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>459</v>
+        <v>453</v>
       </c>
       <c r="D6" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -9403,36 +9351,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>460</v>
+        <v>454</v>
       </c>
       <c r="I6" t="s">
-        <v>461</v>
+        <v>455</v>
       </c>
       <c r="J6" t="s">
-        <v>462</v>
+        <v>456</v>
       </c>
       <c r="K6" t="s">
-        <v>463</v>
+        <v>457</v>
       </c>
       <c r="L6" t="s">
-        <v>464</v>
+        <v>458</v>
       </c>
       <c r="M6" t="s">
-        <v>465</v>
+        <v>459</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>466</v>
+        <v>460</v>
       </c>
       <c r="D7" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -9444,36 +9392,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>467</v>
+        <v>461</v>
       </c>
       <c r="I7" t="s">
-        <v>468</v>
+        <v>462</v>
       </c>
       <c r="J7" t="s">
-        <v>469</v>
+        <v>463</v>
       </c>
       <c r="K7" t="s">
-        <v>470</v>
+        <v>464</v>
       </c>
       <c r="L7" t="s">
-        <v>471</v>
+        <v>465</v>
       </c>
       <c r="M7" t="s">
-        <v>472</v>
+        <v>466</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>473</v>
+        <v>467</v>
       </c>
       <c r="D8" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -9485,36 +9433,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>474</v>
+        <v>468</v>
       </c>
       <c r="I8" t="s">
-        <v>475</v>
+        <v>469</v>
       </c>
       <c r="J8" t="s">
-        <v>476</v>
+        <v>470</v>
       </c>
       <c r="K8" t="s">
-        <v>477</v>
+        <v>471</v>
       </c>
       <c r="L8" t="s">
-        <v>478</v>
+        <v>472</v>
       </c>
       <c r="M8" t="s">
-        <v>479</v>
+        <v>473</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>480</v>
+        <v>474</v>
       </c>
       <c r="D9" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -9526,36 +9474,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>481</v>
+        <v>475</v>
       </c>
       <c r="I9" t="s">
-        <v>482</v>
+        <v>476</v>
       </c>
       <c r="J9" t="s">
-        <v>483</v>
+        <v>477</v>
       </c>
       <c r="K9" t="s">
-        <v>484</v>
+        <v>478</v>
       </c>
       <c r="L9" t="s">
-        <v>485</v>
+        <v>479</v>
       </c>
       <c r="M9" t="s">
-        <v>486</v>
+        <v>480</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>487</v>
+        <v>481</v>
       </c>
       <c r="D10" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -9567,36 +9515,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>488</v>
+        <v>482</v>
       </c>
       <c r="I10" t="s">
-        <v>489</v>
+        <v>483</v>
       </c>
       <c r="J10" t="s">
-        <v>490</v>
+        <v>484</v>
       </c>
       <c r="K10" t="s">
-        <v>491</v>
+        <v>485</v>
       </c>
       <c r="L10" t="s">
-        <v>492</v>
+        <v>486</v>
       </c>
       <c r="M10" t="s">
-        <v>493</v>
+        <v>487</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>494</v>
+        <v>488</v>
       </c>
       <c r="D11" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9608,36 +9556,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="I11" t="s">
-        <v>496</v>
+        <v>490</v>
       </c>
       <c r="J11" t="s">
-        <v>497</v>
+        <v>491</v>
       </c>
       <c r="K11" t="s">
-        <v>498</v>
+        <v>492</v>
       </c>
       <c r="L11" t="s">
-        <v>499</v>
+        <v>493</v>
       </c>
       <c r="M11" t="s">
-        <v>500</v>
+        <v>494</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>501</v>
+        <v>495</v>
       </c>
       <c r="D12" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9649,36 +9597,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>502</v>
+        <v>496</v>
       </c>
       <c r="I12" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="J12" t="s">
-        <v>504</v>
+        <v>498</v>
       </c>
       <c r="K12" t="s">
-        <v>505</v>
+        <v>499</v>
       </c>
       <c r="L12" t="s">
-        <v>506</v>
+        <v>500</v>
       </c>
       <c r="M12" t="s">
-        <v>507</v>
+        <v>501</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>508</v>
+        <v>502</v>
       </c>
       <c r="D13" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9690,36 +9638,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>509</v>
+        <v>503</v>
       </c>
       <c r="I13" t="s">
-        <v>510</v>
+        <v>504</v>
       </c>
       <c r="J13" t="s">
-        <v>511</v>
+        <v>505</v>
       </c>
       <c r="K13" t="s">
-        <v>512</v>
+        <v>506</v>
       </c>
       <c r="L13" t="s">
-        <v>513</v>
+        <v>507</v>
       </c>
       <c r="M13" t="s">
-        <v>514</v>
+        <v>508</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>515</v>
+        <v>509</v>
       </c>
       <c r="D14" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9731,36 +9679,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>516</v>
+        <v>510</v>
       </c>
       <c r="I14" t="s">
-        <v>517</v>
+        <v>511</v>
       </c>
       <c r="J14" t="s">
-        <v>518</v>
+        <v>512</v>
       </c>
       <c r="K14" t="s">
-        <v>519</v>
+        <v>513</v>
       </c>
       <c r="L14" t="s">
-        <v>520</v>
+        <v>514</v>
       </c>
       <c r="M14" t="s">
-        <v>521</v>
+        <v>515</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>522</v>
+        <v>516</v>
       </c>
       <c r="D15" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9772,39 +9720,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>523</v>
+        <v>517</v>
       </c>
       <c r="I15" t="s">
-        <v>524</v>
+        <v>518</v>
       </c>
       <c r="J15" t="s">
-        <v>525</v>
+        <v>519</v>
       </c>
       <c r="K15" t="s">
-        <v>526</v>
+        <v>520</v>
       </c>
       <c r="L15" t="s">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="M15" t="s">
-        <v>528</v>
+        <v>522</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="D16" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E16" t="s">
-        <v>531</v>
+        <v>525</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9813,39 +9761,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>532</v>
+        <v>526</v>
       </c>
       <c r="I16" t="s">
-        <v>533</v>
+        <v>527</v>
       </c>
       <c r="J16" t="s">
-        <v>534</v>
+        <v>528</v>
       </c>
       <c r="K16" t="s">
-        <v>535</v>
+        <v>529</v>
       </c>
       <c r="L16" t="s">
-        <v>536</v>
+        <v>530</v>
       </c>
       <c r="M16" t="s">
-        <v>537</v>
+        <v>531</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>538</v>
+        <v>532</v>
       </c>
       <c r="D17" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E17" t="s">
-        <v>539</v>
+        <v>533</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9854,39 +9802,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>540</v>
+        <v>534</v>
       </c>
       <c r="I17" t="s">
-        <v>541</v>
+        <v>535</v>
       </c>
       <c r="J17" t="s">
-        <v>542</v>
+        <v>536</v>
       </c>
       <c r="K17" t="s">
-        <v>543</v>
+        <v>537</v>
       </c>
       <c r="L17" t="s">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="M17" t="s">
-        <v>545</v>
+        <v>539</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>546</v>
+        <v>540</v>
       </c>
       <c r="D18" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E18" t="s">
-        <v>547</v>
+        <v>541</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9895,39 +9843,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>548</v>
+        <v>542</v>
       </c>
       <c r="I18" t="s">
-        <v>549</v>
+        <v>543</v>
       </c>
       <c r="J18" t="s">
-        <v>550</v>
+        <v>544</v>
       </c>
       <c r="K18" t="s">
-        <v>551</v>
+        <v>545</v>
       </c>
       <c r="L18" t="s">
-        <v>552</v>
+        <v>546</v>
       </c>
       <c r="M18" t="s">
-        <v>553</v>
+        <v>547</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>554</v>
+        <v>548</v>
       </c>
       <c r="D19" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E19" t="s">
-        <v>555</v>
+        <v>549</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9936,39 +9884,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>556</v>
+        <v>550</v>
       </c>
       <c r="I19" t="s">
-        <v>557</v>
+        <v>551</v>
       </c>
       <c r="J19" t="s">
-        <v>558</v>
+        <v>552</v>
       </c>
       <c r="K19" t="s">
-        <v>559</v>
+        <v>553</v>
       </c>
       <c r="L19" t="s">
-        <v>560</v>
+        <v>554</v>
       </c>
       <c r="M19" t="s">
-        <v>561</v>
+        <v>555</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>562</v>
+        <v>556</v>
       </c>
       <c r="D20" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E20" t="s">
-        <v>563</v>
+        <v>557</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9977,39 +9925,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>564</v>
+        <v>558</v>
       </c>
       <c r="I20" t="s">
-        <v>565</v>
+        <v>559</v>
       </c>
       <c r="J20" t="s">
-        <v>566</v>
+        <v>560</v>
       </c>
       <c r="K20" t="s">
-        <v>567</v>
+        <v>561</v>
       </c>
       <c r="L20" t="s">
-        <v>568</v>
+        <v>562</v>
       </c>
       <c r="M20" t="s">
-        <v>569</v>
+        <v>563</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>570</v>
+        <v>564</v>
       </c>
       <c r="D21" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E21" t="s">
-        <v>571</v>
+        <v>565</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -10018,39 +9966,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>572</v>
+        <v>566</v>
       </c>
       <c r="I21" t="s">
-        <v>573</v>
+        <v>567</v>
       </c>
       <c r="J21" t="s">
-        <v>574</v>
+        <v>568</v>
       </c>
       <c r="K21" t="s">
-        <v>575</v>
+        <v>569</v>
       </c>
       <c r="L21" t="s">
-        <v>576</v>
+        <v>570</v>
       </c>
       <c r="M21" t="s">
-        <v>577</v>
+        <v>571</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>578</v>
+        <v>572</v>
       </c>
       <c r="D22" t="s">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="E22" t="s">
-        <v>579</v>
+        <v>573</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -10059,39 +10007,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="I22" t="s">
-        <v>581</v>
+        <v>575</v>
       </c>
       <c r="J22" t="s">
-        <v>582</v>
+        <v>576</v>
       </c>
       <c r="K22" t="s">
-        <v>583</v>
+        <v>577</v>
       </c>
       <c r="L22" t="s">
-        <v>584</v>
+        <v>578</v>
       </c>
       <c r="M22" t="s">
-        <v>585</v>
+        <v>579</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>586</v>
+        <v>580</v>
       </c>
       <c r="D23" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E23" t="s">
-        <v>588</v>
+        <v>582</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -10100,39 +10048,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>589</v>
+        <v>583</v>
       </c>
       <c r="I23" t="s">
-        <v>590</v>
+        <v>584</v>
       </c>
       <c r="J23" t="s">
-        <v>591</v>
+        <v>585</v>
       </c>
       <c r="K23" t="s">
-        <v>592</v>
+        <v>586</v>
       </c>
       <c r="L23" t="s">
-        <v>593</v>
+        <v>587</v>
       </c>
       <c r="M23" t="s">
-        <v>594</v>
+        <v>588</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>595</v>
+        <v>589</v>
       </c>
       <c r="D24" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E24" t="s">
-        <v>596</v>
+        <v>590</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -10141,39 +10089,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>597</v>
+        <v>591</v>
       </c>
       <c r="I24" t="s">
-        <v>598</v>
+        <v>592</v>
       </c>
       <c r="J24" t="s">
-        <v>599</v>
+        <v>593</v>
       </c>
       <c r="K24" t="s">
-        <v>600</v>
+        <v>594</v>
       </c>
       <c r="L24" t="s">
-        <v>601</v>
+        <v>595</v>
       </c>
       <c r="M24" t="s">
-        <v>602</v>
+        <v>596</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>603</v>
+        <v>597</v>
       </c>
       <c r="D25" t="s">
-        <v>587</v>
+        <v>581</v>
       </c>
       <c r="E25" t="s">
-        <v>604</v>
+        <v>598</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -10182,22 +10130,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>605</v>
+        <v>599</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>606</v>
+        <v>600</v>
       </c>
       <c r="K25" t="s">
-        <v>607</v>
+        <v>601</v>
       </c>
       <c r="L25" t="s">
-        <v>608</v>
+        <v>602</v>
       </c>
       <c r="M25" t="s">
-        <v>609</v>
+        <v>603</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -10205,10 +10153,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>610</v>
+        <v>604</v>
       </c>
       <c r="D26" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -10220,22 +10168,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>612</v>
+        <v>606</v>
       </c>
       <c r="I26" t="s">
-        <v>613</v>
+        <v>607</v>
       </c>
       <c r="J26" t="s">
-        <v>614</v>
+        <v>608</v>
       </c>
       <c r="K26" t="s">
-        <v>615</v>
+        <v>609</v>
       </c>
       <c r="L26" t="s">
-        <v>616</v>
+        <v>610</v>
       </c>
       <c r="M26" t="s">
-        <v>617</v>
+        <v>611</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -10243,13 +10191,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>618</v>
+        <v>612</v>
       </c>
       <c r="D27" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E27" t="s">
-        <v>619</v>
+        <v>613</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -10258,36 +10206,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>620</v>
+        <v>614</v>
       </c>
       <c r="I27" t="s">
-        <v>621</v>
+        <v>615</v>
       </c>
       <c r="J27" t="s">
-        <v>622</v>
+        <v>616</v>
       </c>
       <c r="K27" t="s">
-        <v>623</v>
+        <v>617</v>
       </c>
       <c r="L27" t="s">
-        <v>624</v>
+        <v>618</v>
       </c>
       <c r="M27" t="s">
-        <v>625</v>
+        <v>619</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>626</v>
+        <v>620</v>
       </c>
       <c r="D28" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -10299,36 +10247,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>627</v>
+        <v>621</v>
       </c>
       <c r="I28" t="s">
-        <v>628</v>
+        <v>622</v>
       </c>
       <c r="J28" t="s">
-        <v>629</v>
+        <v>623</v>
       </c>
       <c r="K28" t="s">
-        <v>630</v>
+        <v>624</v>
       </c>
       <c r="L28" t="s">
-        <v>631</v>
+        <v>625</v>
       </c>
       <c r="M28" t="s">
-        <v>632</v>
+        <v>626</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>633</v>
+        <v>627</v>
       </c>
       <c r="D29" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -10340,36 +10288,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>634</v>
+        <v>628</v>
       </c>
       <c r="I29" t="s">
-        <v>635</v>
+        <v>629</v>
       </c>
       <c r="J29" t="s">
-        <v>636</v>
+        <v>630</v>
       </c>
       <c r="K29" t="s">
-        <v>637</v>
+        <v>631</v>
       </c>
       <c r="L29" t="s">
-        <v>638</v>
+        <v>632</v>
       </c>
       <c r="M29" t="s">
-        <v>639</v>
+        <v>633</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>640</v>
+        <v>634</v>
       </c>
       <c r="D30" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -10381,39 +10329,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>641</v>
+        <v>635</v>
       </c>
       <c r="I30" t="s">
-        <v>642</v>
+        <v>636</v>
       </c>
       <c r="J30" t="s">
-        <v>643</v>
+        <v>637</v>
       </c>
       <c r="K30" t="s">
-        <v>644</v>
+        <v>638</v>
       </c>
       <c r="L30" t="s">
-        <v>645</v>
+        <v>639</v>
       </c>
       <c r="M30" t="s">
-        <v>646</v>
+        <v>640</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>396</v>
+        <v>390</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>647</v>
+        <v>641</v>
       </c>
       <c r="D31" t="s">
-        <v>611</v>
+        <v>605</v>
       </c>
       <c r="E31" t="s">
-        <v>278</v>
+        <v>272</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -10422,22 +10370,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>648</v>
+        <v>642</v>
       </c>
       <c r="I31" t="s">
-        <v>649</v>
+        <v>643</v>
       </c>
       <c r="J31" t="s">
-        <v>650</v>
+        <v>644</v>
       </c>
       <c r="K31" t="s">
-        <v>651</v>
+        <v>645</v>
       </c>
       <c r="L31" t="s">
-        <v>652</v>
+        <v>646</v>
       </c>
       <c r="M31" t="s">
-        <v>653</v>
+        <v>647</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -10445,13 +10393,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>654</v>
+        <v>648</v>
       </c>
       <c r="D32" t="s">
-        <v>452</v>
+        <v>446</v>
       </c>
       <c r="E32" t="s">
-        <v>655</v>
+        <v>649</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -10460,22 +10408,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>656</v>
+        <v>650</v>
       </c>
       <c r="I32" t="s">
-        <v>657</v>
+        <v>651</v>
       </c>
       <c r="J32" t="s">
-        <v>658</v>
+        <v>652</v>
       </c>
       <c r="K32" t="s">
-        <v>659</v>
+        <v>653</v>
       </c>
       <c r="L32" t="s">
-        <v>660</v>
+        <v>654</v>
       </c>
       <c r="M32" t="s">
-        <v>661</v>
+        <v>655</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1558" uniqueCount="908">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="899">
   <si>
     <t>Dog</t>
   </si>
@@ -507,24 +507,15 @@
     <t>描述</t>
   </si>
   <si>
-    <t>BlindBoxWaitDurationMultiplier</t>
-  </si>
-  <si>
-    <t>等待盲盒时间倍率</t>
+    <t>BlindBoxCostScale</t>
+  </si>
+  <si>
+    <t>盲盒消耗倍率</t>
   </si>
   <si>
     <t>float</t>
   </si>
   <si>
-    <t>等待盲盒到达时间的倍率，开发时填1,playtest时填5,正式上线填10，数字越大等待时间越久</t>
-  </si>
-  <si>
-    <t>BlindBoxCostScale</t>
-  </si>
-  <si>
-    <t>盲盒消耗倍率</t>
-  </si>
-  <si>
     <t>盲盒消耗筹码倍率</t>
   </si>
   <si>
@@ -537,15 +528,6 @@
     <t>统计时，玩家实际行为乘以倍率作为统计值记录，例如玩家获得1个筹码，倍率是10的话，记为10个筹码</t>
   </si>
   <si>
-    <t>BlindBoxLoopIntervalSeconds</t>
-  </si>
-  <si>
-    <t>正常阶段盲盒展示间隔</t>
-  </si>
-  <si>
-    <t>秒；第 12 个新手奖励入账后，按此基础间隔产生展示点并触发循环 Steam 掉落检查；实际时长受 BlindBoxWaitDurationMultiplier 影响</t>
-  </si>
-  <si>
     <t>LinkTreeVisibleBannerCount</t>
   </si>
   <si>
@@ -553,15 +535,6 @@
   </si>
   <si>
     <t>未领取奖励的条目和固定条目数量之和不足该值时，以已领取奖励的条目填充占位</t>
-  </si>
-  <si>
-    <t>SteamPlaytimeEligibilityLeadSeconds</t>
-  </si>
-  <si>
-    <t>Steam资格提前秒数</t>
-  </si>
-  <si>
-    <t>秒；前 12 个一次性 Steam 投放相对本地展示时间提前取得服务器资格。转换器与客户端必须使用相同的分钟级取整结果；循环阶段不使用本字段。</t>
   </si>
   <si>
     <t>IconName</t>
@@ -4349,28 +4322,28 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>656</v>
+        <v>647</v>
       </c>
       <c r="C1" t="s">
-        <v>657</v>
+        <v>648</v>
       </c>
       <c r="D1" t="s">
-        <v>658</v>
+        <v>649</v>
       </c>
       <c r="E1" t="s">
-        <v>659</v>
+        <v>650</v>
       </c>
       <c r="F1" t="s">
-        <v>660</v>
+        <v>651</v>
       </c>
       <c r="G1" t="s">
-        <v>661</v>
+        <v>652</v>
       </c>
       <c r="H1" t="s">
-        <v>662</v>
+        <v>653</v>
       </c>
       <c r="I1" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -4387,16 +4360,16 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>663</v>
+        <v>654</v>
       </c>
       <c r="F2" t="s">
-        <v>664</v>
+        <v>655</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
       </c>
       <c r="H2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -4407,28 +4380,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>666</v>
+        <v>657</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>668</v>
+        <v>659</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>669</v>
+        <v>660</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>671</v>
+        <v>662</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>672</v>
+        <v>663</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -4436,1333 +4409,1333 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>673</v>
+        <v>664</v>
       </c>
       <c r="C4" t="s">
-        <v>674</v>
+        <v>665</v>
       </c>
       <c r="D4" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="E4" t="s">
-        <v>675</v>
+        <v>666</v>
       </c>
       <c r="F4" t="s">
-        <v>676</v>
+        <v>667</v>
       </c>
       <c r="G4" t="s">
-        <v>677</v>
+        <v>668</v>
       </c>
       <c r="H4" t="s">
-        <v>678</v>
+        <v>669</v>
       </c>
       <c r="I4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>679</v>
+        <v>670</v>
       </c>
       <c r="D5" t="s">
-        <v>680</v>
+        <v>671</v>
       </c>
       <c r="E5" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F5" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G5" t="s">
-        <v>683</v>
+        <v>674</v>
       </c>
       <c r="H5" t="b">
         <v>1</v>
       </c>
       <c r="I5" t="s">
-        <v>684</v>
+        <v>675</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>685</v>
+        <v>676</v>
       </c>
       <c r="D6" t="s">
-        <v>686</v>
+        <v>677</v>
       </c>
       <c r="E6" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F6" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G6" t="s">
-        <v>688</v>
+        <v>679</v>
       </c>
       <c r="H6" t="b">
         <v>1</v>
       </c>
       <c r="I6" t="s">
-        <v>689</v>
+        <v>680</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>690</v>
+        <v>681</v>
       </c>
       <c r="D7" t="s">
-        <v>691</v>
+        <v>682</v>
       </c>
       <c r="E7" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F7" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G7" t="s">
-        <v>692</v>
+        <v>683</v>
       </c>
       <c r="H7" t="b">
         <v>1</v>
       </c>
       <c r="I7" t="s">
-        <v>693</v>
+        <v>684</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>694</v>
+        <v>685</v>
       </c>
       <c r="D8" t="s">
-        <v>695</v>
+        <v>686</v>
       </c>
       <c r="E8" t="s">
-        <v>681</v>
+        <v>672</v>
       </c>
       <c r="F8" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G8" t="s">
-        <v>696</v>
+        <v>687</v>
       </c>
       <c r="H8" t="b">
         <v>1</v>
       </c>
       <c r="I8" t="s">
-        <v>697</v>
+        <v>688</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>698</v>
+        <v>689</v>
       </c>
       <c r="D9" t="s">
-        <v>699</v>
+        <v>690</v>
       </c>
       <c r="E9" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F9" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G9" t="s">
-        <v>700</v>
+        <v>691</v>
       </c>
       <c r="H9" t="b">
         <v>1</v>
       </c>
       <c r="I9" t="s">
-        <v>701</v>
+        <v>692</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>702</v>
+        <v>693</v>
       </c>
       <c r="D10" t="s">
-        <v>703</v>
+        <v>694</v>
       </c>
       <c r="E10" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="F10" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G10" t="s">
-        <v>705</v>
+        <v>696</v>
       </c>
       <c r="H10" t="b">
         <v>1</v>
       </c>
       <c r="I10" t="s">
-        <v>706</v>
+        <v>697</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>707</v>
+        <v>698</v>
       </c>
       <c r="D11" t="s">
-        <v>708</v>
+        <v>699</v>
       </c>
       <c r="E11" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F11" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G11" t="s">
-        <v>709</v>
+        <v>700</v>
       </c>
       <c r="H11" t="b">
         <v>1</v>
       </c>
       <c r="I11" t="s">
-        <v>710</v>
+        <v>701</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>711</v>
+        <v>702</v>
       </c>
       <c r="D12" t="s">
-        <v>712</v>
+        <v>703</v>
       </c>
       <c r="E12" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F12" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G12" t="s">
-        <v>713</v>
+        <v>704</v>
       </c>
       <c r="H12" t="b">
         <v>1</v>
       </c>
       <c r="I12" t="s">
-        <v>714</v>
+        <v>705</v>
       </c>
     </row>
     <row r="13" spans="1:9">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>715</v>
+        <v>706</v>
       </c>
       <c r="D13" t="s">
-        <v>716</v>
+        <v>707</v>
       </c>
       <c r="E13" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F13" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G13" t="s">
-        <v>717</v>
+        <v>708</v>
       </c>
       <c r="H13" t="b">
         <v>1</v>
       </c>
       <c r="I13" t="s">
-        <v>718</v>
+        <v>709</v>
       </c>
     </row>
     <row r="14" spans="1:9">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>719</v>
+        <v>710</v>
       </c>
       <c r="D14" t="s">
-        <v>720</v>
+        <v>711</v>
       </c>
       <c r="E14" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="F14" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G14" t="s">
-        <v>721</v>
+        <v>712</v>
       </c>
       <c r="H14" t="b">
         <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>722</v>
+        <v>713</v>
       </c>
     </row>
     <row r="15" spans="1:9">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>723</v>
+        <v>714</v>
       </c>
       <c r="D15" t="s">
-        <v>724</v>
+        <v>715</v>
       </c>
       <c r="E15" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="F15" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G15" t="s">
-        <v>725</v>
+        <v>716</v>
       </c>
       <c r="H15" t="b">
         <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>726</v>
+        <v>717</v>
       </c>
     </row>
     <row r="16" spans="1:9">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>727</v>
+        <v>718</v>
       </c>
       <c r="D16" t="s">
-        <v>728</v>
+        <v>719</v>
       </c>
       <c r="E16" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F16" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G16" t="s">
-        <v>729</v>
+        <v>720</v>
       </c>
       <c r="H16" t="b">
         <v>1</v>
       </c>
       <c r="I16" t="s">
-        <v>730</v>
+        <v>721</v>
       </c>
     </row>
     <row r="17" spans="1:9">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>731</v>
+        <v>722</v>
       </c>
       <c r="D17" t="s">
-        <v>732</v>
+        <v>723</v>
       </c>
       <c r="E17" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F17" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G17" t="s">
-        <v>733</v>
+        <v>724</v>
       </c>
       <c r="H17" t="b">
         <v>1</v>
       </c>
       <c r="I17" t="s">
-        <v>734</v>
+        <v>725</v>
       </c>
     </row>
     <row r="18" spans="1:9">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>735</v>
+        <v>726</v>
       </c>
       <c r="D18" t="s">
-        <v>736</v>
+        <v>727</v>
       </c>
       <c r="E18" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F18" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G18" t="s">
-        <v>737</v>
+        <v>728</v>
       </c>
       <c r="H18" t="b">
         <v>1</v>
       </c>
       <c r="I18" t="s">
-        <v>738</v>
+        <v>729</v>
       </c>
     </row>
     <row r="19" spans="1:9">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="D19" t="s">
-        <v>739</v>
+        <v>730</v>
       </c>
       <c r="E19" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F19" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G19" t="s">
-        <v>740</v>
+        <v>731</v>
       </c>
       <c r="H19" t="b">
         <v>1</v>
       </c>
       <c r="I19" t="s">
-        <v>741</v>
+        <v>732</v>
       </c>
     </row>
     <row r="20" spans="1:9">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="D20" t="s">
-        <v>742</v>
+        <v>733</v>
       </c>
       <c r="E20" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F20" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G20" t="s">
-        <v>743</v>
+        <v>734</v>
       </c>
       <c r="H20" t="b">
         <v>1</v>
       </c>
       <c r="I20" t="s">
-        <v>744</v>
+        <v>735</v>
       </c>
     </row>
     <row r="21" spans="1:9">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="D21" t="s">
-        <v>745</v>
+        <v>736</v>
       </c>
       <c r="E21" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F21" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G21" t="s">
-        <v>746</v>
+        <v>737</v>
       </c>
       <c r="H21" t="b">
         <v>1</v>
       </c>
       <c r="I21" t="s">
-        <v>747</v>
+        <v>738</v>
       </c>
     </row>
     <row r="22" spans="1:9">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="D22" t="s">
-        <v>748</v>
+        <v>739</v>
       </c>
       <c r="E22" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F22" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G22" t="s">
-        <v>749</v>
+        <v>740</v>
       </c>
       <c r="H22" t="b">
         <v>1</v>
       </c>
       <c r="I22" t="s">
-        <v>750</v>
+        <v>741</v>
       </c>
     </row>
     <row r="23" spans="1:9">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="D23" t="s">
-        <v>751</v>
+        <v>742</v>
       </c>
       <c r="E23" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F23" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G23" t="s">
-        <v>752</v>
+        <v>743</v>
       </c>
       <c r="H23" t="b">
         <v>1</v>
       </c>
       <c r="I23" t="s">
-        <v>753</v>
+        <v>744</v>
       </c>
     </row>
     <row r="24" spans="1:9">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="D24" t="s">
-        <v>754</v>
+        <v>745</v>
       </c>
       <c r="E24" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F24" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G24" t="s">
-        <v>755</v>
+        <v>746</v>
       </c>
       <c r="H24" t="b">
         <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>756</v>
+        <v>747</v>
       </c>
     </row>
     <row r="25" spans="1:9">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="D25" t="s">
-        <v>757</v>
+        <v>748</v>
       </c>
       <c r="E25" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F25" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G25" t="s">
-        <v>758</v>
+        <v>749</v>
       </c>
       <c r="H25" t="b">
         <v>1</v>
       </c>
       <c r="I25" t="s">
-        <v>759</v>
+        <v>750</v>
       </c>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>760</v>
+        <v>751</v>
       </c>
       <c r="D26" t="s">
-        <v>761</v>
+        <v>752</v>
       </c>
       <c r="E26" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F26" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G26" t="s">
-        <v>762</v>
+        <v>753</v>
       </c>
       <c r="H26" t="b">
         <v>1</v>
       </c>
       <c r="I26" t="s">
-        <v>763</v>
+        <v>754</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>764</v>
+        <v>755</v>
       </c>
       <c r="D27" t="s">
-        <v>765</v>
+        <v>756</v>
       </c>
       <c r="E27" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="F27" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G27" t="s">
-        <v>766</v>
+        <v>757</v>
       </c>
       <c r="H27" t="b">
         <v>1</v>
       </c>
       <c r="I27" t="s">
-        <v>767</v>
+        <v>758</v>
       </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>768</v>
+        <v>759</v>
       </c>
       <c r="D28" t="s">
-        <v>769</v>
+        <v>760</v>
       </c>
       <c r="E28" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F28" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G28" t="s">
-        <v>770</v>
+        <v>761</v>
       </c>
       <c r="H28" t="b">
         <v>1</v>
       </c>
       <c r="I28" t="s">
-        <v>771</v>
+        <v>762</v>
       </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>772</v>
+        <v>763</v>
       </c>
       <c r="D29" t="s">
-        <v>773</v>
+        <v>764</v>
       </c>
       <c r="E29" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F29" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G29" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="H29" t="b">
         <v>1</v>
       </c>
       <c r="I29" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="D30" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="E30" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F30" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G30" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
       <c r="H30" t="b">
         <v>1</v>
       </c>
       <c r="I30" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
       <c r="D31" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
       <c r="E31" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F31" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G31" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
       <c r="H31" t="b">
         <v>1</v>
       </c>
       <c r="I31" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
       <c r="D32" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
       <c r="E32" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F32" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G32" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
       <c r="H32" t="b">
         <v>1</v>
       </c>
       <c r="I32" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
     </row>
     <row r="33" spans="1:9">
       <c r="A33" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
       <c r="D33" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
       <c r="E33" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F33" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G33" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
       <c r="H33" t="b">
         <v>1</v>
       </c>
       <c r="I33" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="34" spans="1:9">
       <c r="A34" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
       <c r="D34" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
       <c r="E34" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F34" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G34" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
       <c r="H34" t="b">
         <v>1</v>
       </c>
       <c r="I34" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
     </row>
     <row r="35" spans="1:9">
       <c r="A35" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
       <c r="D35" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
       <c r="E35" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F35" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G35" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
       <c r="H35" t="b">
         <v>1</v>
       </c>
       <c r="I35" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="36" spans="1:9">
       <c r="A36" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
       <c r="D36" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
       <c r="E36" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F36" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G36" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
       <c r="H36" t="b">
         <v>1</v>
       </c>
       <c r="I36" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="37" spans="1:9">
       <c r="A37" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
       <c r="D37" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
       <c r="E37" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F37" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G37" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
       <c r="H37" t="b">
         <v>1</v>
       </c>
       <c r="I37" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="38" spans="1:9">
       <c r="A38" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
       <c r="D38" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
       <c r="E38" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F38" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G38" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
       <c r="H38" t="b">
         <v>1</v>
       </c>
       <c r="I38" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="39" spans="1:9">
       <c r="A39" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
       <c r="D39" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
       <c r="E39" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F39" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G39" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
       <c r="H39" t="b">
         <v>1</v>
       </c>
       <c r="I39" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
     </row>
     <row r="40" spans="1:9">
       <c r="A40" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
       <c r="D40" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
       <c r="E40" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F40" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G40" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
       <c r="H40" t="b">
         <v>1</v>
       </c>
       <c r="I40" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="41" spans="1:9">
       <c r="A41" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
       <c r="D41" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
       <c r="E41" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F41" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G41" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
       <c r="H41" t="b">
         <v>1</v>
       </c>
       <c r="I41" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
     </row>
     <row r="42" spans="1:9">
       <c r="A42" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
       <c r="D42" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
       <c r="E42" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F42" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G42" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
       <c r="H42" t="b">
         <v>1</v>
       </c>
       <c r="I42" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="43" spans="1:9">
       <c r="A43" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
       <c r="D43" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
       <c r="E43" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F43" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G43" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
       <c r="H43" t="b">
         <v>1</v>
       </c>
       <c r="I43" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="44" spans="1:9">
       <c r="A44" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
       <c r="D44" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
       <c r="E44" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F44" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G44" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
       <c r="H44" t="b">
         <v>1</v>
       </c>
       <c r="I44" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
       <c r="D45" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
       <c r="E45" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F45" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G45" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
       <c r="H45" t="b">
         <v>1</v>
       </c>
       <c r="I45" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="46" spans="1:9">
       <c r="A46" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
       <c r="D46" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
       <c r="E46" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F46" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G46" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
       <c r="H46" t="b">
         <v>1</v>
       </c>
       <c r="I46" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="47" spans="1:9">
       <c r="A47" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
       <c r="D47" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
       <c r="E47" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F47" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G47" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
       <c r="H47" t="b">
         <v>1</v>
       </c>
       <c r="I47" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
     </row>
     <row r="48" spans="1:9">
       <c r="A48" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="D48" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="E48" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F48" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G48" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="H48" t="b">
         <v>1</v>
       </c>
       <c r="I48" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
     </row>
     <row r="49" spans="1:9">
       <c r="A49" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="D49" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="E49" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F49" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G49" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="H49" t="b">
         <v>1</v>
       </c>
       <c r="I49" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -5770,25 +5743,25 @@
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="D50" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="E50" t="s">
-        <v>687</v>
+        <v>678</v>
       </c>
       <c r="F50" t="s">
-        <v>682</v>
+        <v>673</v>
       </c>
       <c r="G50" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="H50" t="b">
         <v>1</v>
       </c>
       <c r="I50" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -5796,25 +5769,25 @@
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="D51" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="E51" t="s">
-        <v>704</v>
+        <v>695</v>
       </c>
       <c r="F51" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="G51" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="H51" t="b">
         <v>1</v>
       </c>
       <c r="I51" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
     </row>
   </sheetData>
@@ -5844,25 +5817,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="C1" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="D1" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="E1" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="F1" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="G1" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="H1" t="s">
-        <v>369</v>
+        <v>360</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5876,7 +5849,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -5896,28 +5869,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -5925,39 +5898,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="C4" t="s">
+        <v>863</v>
+      </c>
+      <c r="D4" t="s">
+        <v>871</v>
+      </c>
+      <c r="E4" t="s">
         <v>872</v>
       </c>
-      <c r="D4" t="s">
-        <v>880</v>
-      </c>
-      <c r="E4" t="s">
-        <v>881</v>
-      </c>
       <c r="F4" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="G4" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="H4" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="I4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B5" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="C5" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -5975,18 +5948,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B6" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="C6" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -6004,18 +5977,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B7" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="C7" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6033,18 +6006,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B8" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="C8" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6062,18 +6035,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B9" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="C9" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6091,18 +6064,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B10" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="C10" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6120,18 +6093,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B11" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="C11" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6149,18 +6122,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B12" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="C12" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6178,7 +6151,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
     </row>
   </sheetData>
@@ -6529,7 +6502,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H17"/>
+  <dimension ref="A1:H15"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4" outlineLevelCol="7"/>
   <cols>
     <col min="1" max="1" width="36.6666666666667" customWidth="1"/>
@@ -6576,9 +6549,9 @@
         <v>158</v>
       </c>
       <c r="D3" s="2">
-        <v>4</v>
-      </c>
-      <c r="E3" s="5" t="s">
+        <v>1</v>
+      </c>
+      <c r="E3" t="s">
         <v>159</v>
       </c>
     </row>
@@ -6586,14 +6559,14 @@
       <c r="A4" s="2" t="s">
         <v>160</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="2" t="s">
         <v>161</v>
       </c>
       <c r="C4" t="s">
         <v>158</v>
       </c>
       <c r="D4" s="2">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="E4" t="s">
         <v>162</v>
@@ -6607,83 +6580,39 @@
         <v>164</v>
       </c>
       <c r="C5" t="s">
-        <v>158</v>
+        <v>107</v>
       </c>
       <c r="D5" s="2">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="E5" t="s">
         <v>165</v>
       </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="A6" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="B6" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C6" t="s">
-        <v>158</v>
-      </c>
-      <c r="D6" s="2">
-        <v>90</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8">
-      <c r="A7" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="B7" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="C7" t="s">
-        <v>107</v>
-      </c>
-      <c r="D7" s="2">
-        <v>5</v>
-      </c>
-      <c r="E7" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="B8" t="s">
-        <v>173</v>
-      </c>
-      <c r="C8" t="s">
-        <v>107</v>
-      </c>
-      <c r="D8" s="2">
-        <v>60</v>
-      </c>
-      <c r="E8" s="2" t="s">
-        <v>174</v>
-      </c>
+      <c r="A6" s="2"/>
+      <c r="B6"/>
+      <c r="C6"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="2"/>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="7"/>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="E14" s="1"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="8"/>
     </row>
     <row r="15" spans="1:8">
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="7"/>
-    </row>
-    <row r="16" spans="1:8">
-      <c r="E16" s="1"/>
-      <c r="F16" s="1"/>
-      <c r="G16" s="1"/>
-      <c r="H16" s="8"/>
-    </row>
-    <row r="17" spans="5:8">
-      <c r="E17" s="1"/>
-      <c r="F17" s="1"/>
-      <c r="G17" s="1"/>
-      <c r="H17" s="8"/>
+      <c r="E15" s="1"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="8"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -6724,55 +6653,55 @@
       </c>
       <c r="C1" s="2"/>
       <c r="D1" s="2" t="s">
+        <v>166</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>171</v>
+      </c>
+      <c r="J1" t="s">
+        <v>172</v>
+      </c>
+      <c r="K1" t="s">
+        <v>173</v>
+      </c>
+      <c r="L1" t="s">
+        <v>174</v>
+      </c>
+      <c r="M1" t="s">
         <v>175</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="N1" t="s">
         <v>176</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="O1" t="s">
         <v>177</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="P1" t="s">
         <v>178</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="Q1" t="s">
         <v>179</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="R1" t="s">
         <v>180</v>
       </c>
-      <c r="J1" t="s">
+      <c r="S1" t="s">
         <v>181</v>
       </c>
-      <c r="K1" t="s">
+      <c r="T1" t="s">
         <v>182</v>
-      </c>
-      <c r="L1" t="s">
-        <v>183</v>
-      </c>
-      <c r="M1" t="s">
-        <v>184</v>
-      </c>
-      <c r="N1" t="s">
-        <v>185</v>
-      </c>
-      <c r="O1" t="s">
-        <v>186</v>
-      </c>
-      <c r="P1" t="s">
-        <v>187</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>188</v>
-      </c>
-      <c r="R1" t="s">
-        <v>189</v>
-      </c>
-      <c r="S1" t="s">
-        <v>190</v>
-      </c>
-      <c r="T1" t="s">
-        <v>191</v>
       </c>
     </row>
     <row r="2" spans="1:20">
@@ -6843,10 +6772,10 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -6860,55 +6789,55 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D4" t="s">
+        <v>185</v>
+      </c>
+      <c r="E4" t="s">
+        <v>186</v>
+      </c>
+      <c r="F4" t="s">
+        <v>187</v>
+      </c>
+      <c r="H4" t="s">
+        <v>188</v>
+      </c>
+      <c r="I4" t="s">
+        <v>189</v>
+      </c>
+      <c r="J4" t="s">
+        <v>190</v>
+      </c>
+      <c r="K4" t="s">
+        <v>191</v>
+      </c>
+      <c r="L4" t="s">
+        <v>192</v>
+      </c>
+      <c r="M4" t="s">
         <v>193</v>
       </c>
-      <c r="D4" t="s">
+      <c r="N4" t="s">
         <v>194</v>
       </c>
-      <c r="E4" t="s">
+      <c r="O4" t="s">
         <v>195</v>
       </c>
-      <c r="F4" t="s">
+      <c r="P4" t="s">
         <v>196</v>
       </c>
-      <c r="H4" t="s">
+      <c r="Q4" t="s">
         <v>197</v>
       </c>
-      <c r="I4" t="s">
+      <c r="R4" t="s">
         <v>198</v>
       </c>
-      <c r="J4" t="s">
+      <c r="S4" t="s">
         <v>199</v>
       </c>
-      <c r="K4" t="s">
+      <c r="T4" t="s">
         <v>200</v>
-      </c>
-      <c r="L4" t="s">
-        <v>201</v>
-      </c>
-      <c r="M4" t="s">
-        <v>202</v>
-      </c>
-      <c r="N4" t="s">
-        <v>203</v>
-      </c>
-      <c r="O4" t="s">
-        <v>204</v>
-      </c>
-      <c r="P4" t="s">
-        <v>205</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>206</v>
-      </c>
-      <c r="R4" t="s">
-        <v>207</v>
-      </c>
-      <c r="S4" t="s">
-        <v>208</v>
-      </c>
-      <c r="T4" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="5" spans="1:20">
@@ -6916,58 +6845,58 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
+        <v>201</v>
+      </c>
+      <c r="D5" t="s">
+        <v>202</v>
+      </c>
+      <c r="E5" t="s">
+        <v>203</v>
+      </c>
+      <c r="F5" t="s">
+        <v>204</v>
+      </c>
+      <c r="G5" t="s">
+        <v>174</v>
+      </c>
+      <c r="H5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I5" t="s">
+        <v>206</v>
+      </c>
+      <c r="J5" t="s">
+        <v>207</v>
+      </c>
+      <c r="K5" t="s">
+        <v>208</v>
+      </c>
+      <c r="L5" t="s">
+        <v>209</v>
+      </c>
+      <c r="M5" t="s">
+        <v>203</v>
+      </c>
+      <c r="N5" t="s">
         <v>210</v>
       </c>
-      <c r="D5" t="s">
+      <c r="O5" t="s">
         <v>211</v>
       </c>
-      <c r="E5" t="s">
+      <c r="P5" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q5" t="s">
         <v>212</v>
       </c>
-      <c r="F5" t="s">
+      <c r="R5" t="s">
         <v>213</v>
       </c>
-      <c r="G5" t="s">
-        <v>183</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="S5" t="s">
         <v>214</v>
       </c>
-      <c r="I5" t="s">
+      <c r="T5" t="s">
         <v>215</v>
-      </c>
-      <c r="J5" t="s">
-        <v>216</v>
-      </c>
-      <c r="K5" t="s">
-        <v>217</v>
-      </c>
-      <c r="L5" t="s">
-        <v>218</v>
-      </c>
-      <c r="M5" t="s">
-        <v>212</v>
-      </c>
-      <c r="N5" t="s">
-        <v>219</v>
-      </c>
-      <c r="O5" t="s">
-        <v>220</v>
-      </c>
-      <c r="P5" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>221</v>
-      </c>
-      <c r="R5" t="s">
-        <v>222</v>
-      </c>
-      <c r="S5" t="s">
-        <v>223</v>
-      </c>
-      <c r="T5" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="6" spans="1:20">
@@ -6975,58 +6904,58 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="D6" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="E6" t="s">
+        <v>203</v>
+      </c>
+      <c r="F6" t="s">
         <v>212</v>
       </c>
-      <c r="F6" t="s">
-        <v>221</v>
-      </c>
       <c r="G6" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H6" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="I6" t="s">
+        <v>206</v>
+      </c>
+      <c r="J6" t="s">
+        <v>207</v>
+      </c>
+      <c r="K6" t="s">
+        <v>208</v>
+      </c>
+      <c r="L6" t="s">
+        <v>209</v>
+      </c>
+      <c r="M6" t="s">
+        <v>203</v>
+      </c>
+      <c r="N6" t="s">
+        <v>210</v>
+      </c>
+      <c r="O6" t="s">
+        <v>211</v>
+      </c>
+      <c r="P6" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>212</v>
+      </c>
+      <c r="R6" t="s">
+        <v>213</v>
+      </c>
+      <c r="S6" t="s">
+        <v>214</v>
+      </c>
+      <c r="T6" t="s">
         <v>215</v>
-      </c>
-      <c r="J6" t="s">
-        <v>216</v>
-      </c>
-      <c r="K6" t="s">
-        <v>217</v>
-      </c>
-      <c r="L6" t="s">
-        <v>218</v>
-      </c>
-      <c r="M6" t="s">
-        <v>212</v>
-      </c>
-      <c r="N6" t="s">
-        <v>219</v>
-      </c>
-      <c r="O6" t="s">
-        <v>220</v>
-      </c>
-      <c r="P6" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>221</v>
-      </c>
-      <c r="R6" t="s">
-        <v>222</v>
-      </c>
-      <c r="S6" t="s">
-        <v>223</v>
-      </c>
-      <c r="T6" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="7" spans="1:20">
@@ -7034,58 +6963,58 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="D7" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="E7" t="s">
+        <v>203</v>
+      </c>
+      <c r="F7" t="s">
+        <v>213</v>
+      </c>
+      <c r="G7" t="s">
+        <v>174</v>
+      </c>
+      <c r="H7" t="s">
+        <v>221</v>
+      </c>
+      <c r="I7" t="s">
+        <v>206</v>
+      </c>
+      <c r="J7" t="s">
+        <v>207</v>
+      </c>
+      <c r="K7" t="s">
+        <v>208</v>
+      </c>
+      <c r="L7" t="s">
+        <v>209</v>
+      </c>
+      <c r="M7" t="s">
+        <v>203</v>
+      </c>
+      <c r="N7" t="s">
+        <v>210</v>
+      </c>
+      <c r="O7" t="s">
+        <v>211</v>
+      </c>
+      <c r="P7" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q7" t="s">
         <v>212</v>
       </c>
-      <c r="F7" t="s">
-        <v>222</v>
-      </c>
-      <c r="G7" t="s">
-        <v>183</v>
-      </c>
-      <c r="H7" t="s">
-        <v>230</v>
-      </c>
-      <c r="I7" t="s">
+      <c r="R7" t="s">
+        <v>213</v>
+      </c>
+      <c r="S7" t="s">
+        <v>214</v>
+      </c>
+      <c r="T7" t="s">
         <v>215</v>
-      </c>
-      <c r="J7" t="s">
-        <v>216</v>
-      </c>
-      <c r="K7" t="s">
-        <v>217</v>
-      </c>
-      <c r="L7" t="s">
-        <v>218</v>
-      </c>
-      <c r="M7" t="s">
-        <v>212</v>
-      </c>
-      <c r="N7" t="s">
-        <v>219</v>
-      </c>
-      <c r="O7" t="s">
-        <v>220</v>
-      </c>
-      <c r="P7" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>221</v>
-      </c>
-      <c r="R7" t="s">
-        <v>222</v>
-      </c>
-      <c r="S7" t="s">
-        <v>223</v>
-      </c>
-      <c r="T7" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="8" spans="1:20">
@@ -7093,58 +7022,58 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="D8" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="E8" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F8" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="G8" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="H8" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="I8" t="s">
+        <v>206</v>
+      </c>
+      <c r="J8" t="s">
+        <v>207</v>
+      </c>
+      <c r="K8" t="s">
+        <v>208</v>
+      </c>
+      <c r="L8" t="s">
+        <v>209</v>
+      </c>
+      <c r="M8" t="s">
+        <v>203</v>
+      </c>
+      <c r="N8" t="s">
+        <v>210</v>
+      </c>
+      <c r="O8" t="s">
+        <v>211</v>
+      </c>
+      <c r="P8" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>212</v>
+      </c>
+      <c r="R8" t="s">
+        <v>213</v>
+      </c>
+      <c r="S8" t="s">
+        <v>214</v>
+      </c>
+      <c r="T8" t="s">
         <v>215</v>
-      </c>
-      <c r="J8" t="s">
-        <v>216</v>
-      </c>
-      <c r="K8" t="s">
-        <v>217</v>
-      </c>
-      <c r="L8" t="s">
-        <v>218</v>
-      </c>
-      <c r="M8" t="s">
-        <v>212</v>
-      </c>
-      <c r="N8" t="s">
-        <v>219</v>
-      </c>
-      <c r="O8" t="s">
-        <v>220</v>
-      </c>
-      <c r="P8" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>221</v>
-      </c>
-      <c r="R8" t="s">
-        <v>222</v>
-      </c>
-      <c r="S8" t="s">
-        <v>223</v>
-      </c>
-      <c r="T8" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:20">
@@ -7152,58 +7081,58 @@
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="D9" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="E9" t="s">
+        <v>203</v>
+      </c>
+      <c r="F9" t="s">
+        <v>213</v>
+      </c>
+      <c r="G9" t="s">
+        <v>174</v>
+      </c>
+      <c r="H9" t="s">
+        <v>205</v>
+      </c>
+      <c r="I9" t="s">
+        <v>227</v>
+      </c>
+      <c r="J9" t="s">
+        <v>207</v>
+      </c>
+      <c r="K9" t="s">
+        <v>208</v>
+      </c>
+      <c r="L9" t="s">
+        <v>209</v>
+      </c>
+      <c r="M9" t="s">
+        <v>203</v>
+      </c>
+      <c r="N9" t="s">
+        <v>210</v>
+      </c>
+      <c r="O9" t="s">
+        <v>211</v>
+      </c>
+      <c r="P9" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q9" t="s">
         <v>212</v>
       </c>
-      <c r="F9" t="s">
-        <v>222</v>
-      </c>
-      <c r="G9" t="s">
-        <v>183</v>
-      </c>
-      <c r="H9" t="s">
+      <c r="R9" t="s">
+        <v>213</v>
+      </c>
+      <c r="S9" t="s">
         <v>214</v>
       </c>
-      <c r="I9" t="s">
-        <v>236</v>
-      </c>
-      <c r="J9" t="s">
-        <v>216</v>
-      </c>
-      <c r="K9" t="s">
-        <v>217</v>
-      </c>
-      <c r="L9" t="s">
-        <v>218</v>
-      </c>
-      <c r="M9" t="s">
-        <v>212</v>
-      </c>
-      <c r="N9" t="s">
-        <v>219</v>
-      </c>
-      <c r="O9" t="s">
-        <v>220</v>
-      </c>
-      <c r="P9" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>221</v>
-      </c>
-      <c r="R9" t="s">
-        <v>222</v>
-      </c>
-      <c r="S9" t="s">
-        <v>223</v>
-      </c>
       <c r="T9" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="10" spans="1:20">
@@ -7211,58 +7140,58 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="D10" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="E10" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="F10" t="s">
+        <v>204</v>
+      </c>
+      <c r="G10" t="s">
+        <v>174</v>
+      </c>
+      <c r="H10" t="s">
+        <v>205</v>
+      </c>
+      <c r="I10" t="s">
+        <v>230</v>
+      </c>
+      <c r="J10" t="s">
+        <v>207</v>
+      </c>
+      <c r="K10" t="s">
+        <v>208</v>
+      </c>
+      <c r="L10" t="s">
+        <v>209</v>
+      </c>
+      <c r="M10" t="s">
+        <v>203</v>
+      </c>
+      <c r="N10" t="s">
+        <v>210</v>
+      </c>
+      <c r="O10" t="s">
+        <v>211</v>
+      </c>
+      <c r="P10" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>212</v>
+      </c>
+      <c r="R10" t="s">
         <v>213</v>
       </c>
-      <c r="G10" t="s">
-        <v>183</v>
-      </c>
-      <c r="H10" t="s">
+      <c r="S10" t="s">
         <v>214</v>
       </c>
-      <c r="I10" t="s">
-        <v>239</v>
-      </c>
-      <c r="J10" t="s">
-        <v>216</v>
-      </c>
-      <c r="K10" t="s">
-        <v>217</v>
-      </c>
-      <c r="L10" t="s">
-        <v>218</v>
-      </c>
-      <c r="M10" t="s">
-        <v>212</v>
-      </c>
-      <c r="N10" t="s">
-        <v>219</v>
-      </c>
-      <c r="O10" t="s">
-        <v>220</v>
-      </c>
-      <c r="P10" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>221</v>
-      </c>
-      <c r="R10" t="s">
-        <v>222</v>
-      </c>
-      <c r="S10" t="s">
-        <v>223</v>
-      </c>
       <c r="T10" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="11" spans="1:20">
@@ -7270,58 +7199,58 @@
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="D11" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="E11" t="s">
+        <v>203</v>
+      </c>
+      <c r="F11" t="s">
+        <v>215</v>
+      </c>
+      <c r="G11" t="s">
+        <v>174</v>
+      </c>
+      <c r="H11" t="s">
+        <v>218</v>
+      </c>
+      <c r="I11" t="s">
+        <v>227</v>
+      </c>
+      <c r="J11" t="s">
+        <v>207</v>
+      </c>
+      <c r="K11" t="s">
+        <v>208</v>
+      </c>
+      <c r="L11" t="s">
+        <v>209</v>
+      </c>
+      <c r="M11" t="s">
+        <v>203</v>
+      </c>
+      <c r="N11" t="s">
+        <v>210</v>
+      </c>
+      <c r="O11" t="s">
+        <v>211</v>
+      </c>
+      <c r="P11" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q11" t="s">
         <v>212</v>
       </c>
-      <c r="F11" t="s">
-        <v>224</v>
-      </c>
-      <c r="G11" t="s">
-        <v>183</v>
-      </c>
-      <c r="H11" t="s">
-        <v>227</v>
-      </c>
-      <c r="I11" t="s">
-        <v>236</v>
-      </c>
-      <c r="J11" t="s">
-        <v>216</v>
-      </c>
-      <c r="K11" t="s">
-        <v>217</v>
-      </c>
-      <c r="L11" t="s">
-        <v>218</v>
-      </c>
-      <c r="M11" t="s">
-        <v>212</v>
-      </c>
-      <c r="N11" t="s">
-        <v>219</v>
-      </c>
-      <c r="O11" t="s">
-        <v>220</v>
-      </c>
-      <c r="P11" t="s">
+      <c r="R11" t="s">
         <v>213</v>
       </c>
-      <c r="Q11" t="s">
-        <v>221</v>
-      </c>
-      <c r="R11" t="s">
-        <v>222</v>
-      </c>
       <c r="S11" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T11" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="12" spans="1:20">
@@ -7329,58 +7258,58 @@
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="D12" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="E12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F12" t="s">
+        <v>204</v>
+      </c>
+      <c r="G12" t="s">
+        <v>174</v>
+      </c>
+      <c r="H12" t="s">
+        <v>218</v>
+      </c>
+      <c r="I12" t="s">
+        <v>230</v>
+      </c>
+      <c r="J12" t="s">
+        <v>207</v>
+      </c>
+      <c r="K12" t="s">
+        <v>208</v>
+      </c>
+      <c r="L12" t="s">
+        <v>209</v>
+      </c>
+      <c r="M12" t="s">
+        <v>203</v>
+      </c>
+      <c r="N12" t="s">
+        <v>210</v>
+      </c>
+      <c r="O12" t="s">
+        <v>211</v>
+      </c>
+      <c r="P12" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q12" t="s">
         <v>212</v>
       </c>
-      <c r="F12" t="s">
+      <c r="R12" t="s">
         <v>213</v>
       </c>
-      <c r="G12" t="s">
-        <v>183</v>
-      </c>
-      <c r="H12" t="s">
-        <v>227</v>
-      </c>
-      <c r="I12" t="s">
-        <v>239</v>
-      </c>
-      <c r="J12" t="s">
-        <v>216</v>
-      </c>
-      <c r="K12" t="s">
-        <v>217</v>
-      </c>
-      <c r="L12" t="s">
-        <v>218</v>
-      </c>
-      <c r="M12" t="s">
-        <v>212</v>
-      </c>
-      <c r="N12" t="s">
-        <v>219</v>
-      </c>
-      <c r="O12" t="s">
-        <v>220</v>
-      </c>
-      <c r="P12" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>221</v>
-      </c>
-      <c r="R12" t="s">
-        <v>222</v>
-      </c>
       <c r="S12" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T12" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="13" spans="1:20">
@@ -7388,58 +7317,58 @@
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="D13" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="E13" t="s">
+        <v>203</v>
+      </c>
+      <c r="F13" t="s">
+        <v>215</v>
+      </c>
+      <c r="G13" t="s">
+        <v>174</v>
+      </c>
+      <c r="H13" t="s">
+        <v>221</v>
+      </c>
+      <c r="I13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J13" t="s">
+        <v>207</v>
+      </c>
+      <c r="K13" t="s">
+        <v>208</v>
+      </c>
+      <c r="L13" t="s">
+        <v>209</v>
+      </c>
+      <c r="M13" t="s">
+        <v>203</v>
+      </c>
+      <c r="N13" t="s">
+        <v>210</v>
+      </c>
+      <c r="O13" t="s">
+        <v>211</v>
+      </c>
+      <c r="P13" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q13" t="s">
         <v>212</v>
       </c>
-      <c r="F13" t="s">
-        <v>224</v>
-      </c>
-      <c r="G13" t="s">
-        <v>183</v>
-      </c>
-      <c r="H13" t="s">
-        <v>230</v>
-      </c>
-      <c r="I13" t="s">
-        <v>236</v>
-      </c>
-      <c r="J13" t="s">
-        <v>216</v>
-      </c>
-      <c r="K13" t="s">
-        <v>217</v>
-      </c>
-      <c r="L13" t="s">
-        <v>218</v>
-      </c>
-      <c r="M13" t="s">
-        <v>212</v>
-      </c>
-      <c r="N13" t="s">
-        <v>219</v>
-      </c>
-      <c r="O13" t="s">
-        <v>220</v>
-      </c>
-      <c r="P13" t="s">
+      <c r="R13" t="s">
         <v>213</v>
       </c>
-      <c r="Q13" t="s">
-        <v>221</v>
-      </c>
-      <c r="R13" t="s">
-        <v>222</v>
-      </c>
       <c r="S13" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T13" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="14" spans="1:20">
@@ -7447,58 +7376,58 @@
         <v>1010</v>
       </c>
       <c r="C14" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="D14" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="E14" t="s">
+        <v>203</v>
+      </c>
+      <c r="F14" t="s">
+        <v>204</v>
+      </c>
+      <c r="G14" t="s">
+        <v>174</v>
+      </c>
+      <c r="H14" t="s">
+        <v>221</v>
+      </c>
+      <c r="I14" t="s">
+        <v>230</v>
+      </c>
+      <c r="J14" t="s">
+        <v>207</v>
+      </c>
+      <c r="K14" t="s">
+        <v>208</v>
+      </c>
+      <c r="L14" t="s">
+        <v>209</v>
+      </c>
+      <c r="M14" t="s">
+        <v>203</v>
+      </c>
+      <c r="N14" t="s">
+        <v>210</v>
+      </c>
+      <c r="O14" t="s">
+        <v>211</v>
+      </c>
+      <c r="P14" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q14" t="s">
         <v>212</v>
       </c>
-      <c r="F14" t="s">
+      <c r="R14" t="s">
         <v>213</v>
       </c>
-      <c r="G14" t="s">
-        <v>183</v>
-      </c>
-      <c r="H14" t="s">
-        <v>230</v>
-      </c>
-      <c r="I14" t="s">
-        <v>239</v>
-      </c>
-      <c r="J14" t="s">
-        <v>216</v>
-      </c>
-      <c r="K14" t="s">
-        <v>217</v>
-      </c>
-      <c r="L14" t="s">
-        <v>218</v>
-      </c>
-      <c r="M14" t="s">
-        <v>212</v>
-      </c>
-      <c r="N14" t="s">
-        <v>219</v>
-      </c>
-      <c r="O14" t="s">
-        <v>220</v>
-      </c>
-      <c r="P14" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>221</v>
-      </c>
-      <c r="R14" t="s">
-        <v>222</v>
-      </c>
       <c r="S14" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T14" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="15" spans="1:20">
@@ -7506,58 +7435,58 @@
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="D15" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="E15" t="s">
+        <v>203</v>
+      </c>
+      <c r="F15" t="s">
+        <v>204</v>
+      </c>
+      <c r="G15" t="s">
+        <v>174</v>
+      </c>
+      <c r="H15" t="s">
+        <v>224</v>
+      </c>
+      <c r="I15" t="s">
+        <v>227</v>
+      </c>
+      <c r="J15" t="s">
+        <v>207</v>
+      </c>
+      <c r="K15" t="s">
+        <v>208</v>
+      </c>
+      <c r="L15" t="s">
+        <v>209</v>
+      </c>
+      <c r="M15" t="s">
+        <v>203</v>
+      </c>
+      <c r="N15" t="s">
+        <v>210</v>
+      </c>
+      <c r="O15" t="s">
+        <v>211</v>
+      </c>
+      <c r="P15" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q15" t="s">
         <v>212</v>
       </c>
-      <c r="F15" t="s">
+      <c r="R15" t="s">
         <v>213</v>
       </c>
-      <c r="G15" t="s">
-        <v>183</v>
-      </c>
-      <c r="H15" t="s">
-        <v>233</v>
-      </c>
-      <c r="I15" t="s">
-        <v>236</v>
-      </c>
-      <c r="J15" t="s">
-        <v>216</v>
-      </c>
-      <c r="K15" t="s">
-        <v>217</v>
-      </c>
-      <c r="L15" t="s">
-        <v>218</v>
-      </c>
-      <c r="M15" t="s">
-        <v>212</v>
-      </c>
-      <c r="N15" t="s">
-        <v>219</v>
-      </c>
-      <c r="O15" t="s">
-        <v>220</v>
-      </c>
-      <c r="P15" t="s">
-        <v>213</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>221</v>
-      </c>
-      <c r="R15" t="s">
-        <v>222</v>
-      </c>
       <c r="S15" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T15" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
     <row r="16" spans="1:20">
@@ -7565,58 +7494,58 @@
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="D16" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="E16" t="s">
+        <v>203</v>
+      </c>
+      <c r="F16" t="s">
+        <v>214</v>
+      </c>
+      <c r="G16" t="s">
+        <v>174</v>
+      </c>
+      <c r="H16" t="s">
+        <v>224</v>
+      </c>
+      <c r="I16" t="s">
+        <v>230</v>
+      </c>
+      <c r="J16" t="s">
+        <v>207</v>
+      </c>
+      <c r="K16" t="s">
+        <v>208</v>
+      </c>
+      <c r="L16" t="s">
+        <v>209</v>
+      </c>
+      <c r="M16" t="s">
+        <v>203</v>
+      </c>
+      <c r="N16" t="s">
+        <v>210</v>
+      </c>
+      <c r="O16" t="s">
+        <v>211</v>
+      </c>
+      <c r="P16" t="s">
+        <v>204</v>
+      </c>
+      <c r="Q16" t="s">
         <v>212</v>
       </c>
-      <c r="F16" t="s">
-        <v>223</v>
-      </c>
-      <c r="G16" t="s">
-        <v>183</v>
-      </c>
-      <c r="H16" t="s">
-        <v>233</v>
-      </c>
-      <c r="I16" t="s">
-        <v>239</v>
-      </c>
-      <c r="J16" t="s">
-        <v>216</v>
-      </c>
-      <c r="K16" t="s">
-        <v>217</v>
-      </c>
-      <c r="L16" t="s">
-        <v>218</v>
-      </c>
-      <c r="M16" t="s">
-        <v>212</v>
-      </c>
-      <c r="N16" t="s">
-        <v>219</v>
-      </c>
-      <c r="O16" t="s">
-        <v>220</v>
-      </c>
-      <c r="P16" t="s">
+      <c r="R16" t="s">
         <v>213</v>
       </c>
-      <c r="Q16" t="s">
-        <v>221</v>
-      </c>
-      <c r="R16" t="s">
-        <v>222</v>
-      </c>
       <c r="S16" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="T16" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
     </row>
   </sheetData>
@@ -7645,16 +7574,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D1" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="E1" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="F1" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7668,7 +7597,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7693,16 +7622,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="E4" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F4" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7716,10 +7645,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="F5" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7727,16 +7656,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="F6" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7750,10 +7679,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F7" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7767,10 +7696,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F8" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7784,10 +7713,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="F9" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7795,16 +7724,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="D10" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="E10" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="F10" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7818,10 +7747,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="F11" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7835,10 +7764,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="F12" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
     </row>
   </sheetData>
@@ -7871,34 +7800,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
+        <v>271</v>
+      </c>
+      <c r="E1" t="s">
+        <v>272</v>
+      </c>
+      <c r="G1" t="s">
+        <v>273</v>
+      </c>
+      <c r="H1" t="s">
+        <v>274</v>
+      </c>
+      <c r="I1" t="s">
+        <v>275</v>
+      </c>
+      <c r="J1" t="s">
+        <v>276</v>
+      </c>
+      <c r="K1" t="s">
+        <v>277</v>
+      </c>
+      <c r="L1" t="s">
+        <v>278</v>
+      </c>
+      <c r="M1" t="s">
+        <v>279</v>
+      </c>
+      <c r="N1" t="s">
         <v>280</v>
-      </c>
-      <c r="E1" t="s">
-        <v>281</v>
-      </c>
-      <c r="G1" t="s">
-        <v>282</v>
-      </c>
-      <c r="H1" t="s">
-        <v>283</v>
-      </c>
-      <c r="I1" t="s">
-        <v>284</v>
-      </c>
-      <c r="J1" t="s">
-        <v>285</v>
-      </c>
-      <c r="K1" t="s">
-        <v>286</v>
-      </c>
-      <c r="L1" t="s">
-        <v>287</v>
-      </c>
-      <c r="M1" t="s">
-        <v>288</v>
-      </c>
-      <c r="N1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7909,10 +7838,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="E2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7924,7 +7853,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7946,13 +7875,13 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7963,40 +7892,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
+        <v>286</v>
+      </c>
+      <c r="D4" t="s">
+        <v>287</v>
+      </c>
+      <c r="E4" t="s">
+        <v>288</v>
+      </c>
+      <c r="F4" t="s">
+        <v>287</v>
+      </c>
+      <c r="G4" t="s">
+        <v>289</v>
+      </c>
+      <c r="H4" t="s">
+        <v>290</v>
+      </c>
+      <c r="I4" t="s">
+        <v>291</v>
+      </c>
+      <c r="J4" t="s">
+        <v>292</v>
+      </c>
+      <c r="K4" t="s">
+        <v>293</v>
+      </c>
+      <c r="L4" t="s">
+        <v>294</v>
+      </c>
+      <c r="M4" t="s">
+        <v>192</v>
+      </c>
+      <c r="N4" t="s">
         <v>295</v>
-      </c>
-      <c r="D4" t="s">
-        <v>296</v>
-      </c>
-      <c r="E4" t="s">
-        <v>297</v>
-      </c>
-      <c r="F4" t="s">
-        <v>296</v>
-      </c>
-      <c r="G4" t="s">
-        <v>298</v>
-      </c>
-      <c r="H4" t="s">
-        <v>299</v>
-      </c>
-      <c r="I4" t="s">
-        <v>300</v>
-      </c>
-      <c r="J4" t="s">
-        <v>301</v>
-      </c>
-      <c r="K4" t="s">
-        <v>302</v>
-      </c>
-      <c r="L4" t="s">
-        <v>303</v>
-      </c>
-      <c r="M4" t="s">
-        <v>201</v>
-      </c>
-      <c r="N4" t="s">
-        <v>304</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -8019,13 +7948,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L5" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M5" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -8039,22 +7968,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H6" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L6" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M6" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -8068,22 +7997,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H7" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L7" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M7" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8097,22 +8026,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H8" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L8" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M8" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8126,22 +8055,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H9" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L9" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M9" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8155,22 +8084,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H10" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L10" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M10" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8184,22 +8113,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H11" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L11" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="M11" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8213,22 +8142,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H12" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="L12" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="M12" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8236,31 +8165,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G13" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="H13" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="L13" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="M13" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="N13" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8268,10 +8197,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>313</v>
+        <v>304</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>314</v>
+        <v>305</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -8280,7 +8209,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8288,10 +8217,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>316</v>
+        <v>307</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>317</v>
+        <v>308</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -8300,7 +8229,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>315</v>
+        <v>306</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8308,10 +8237,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>318</v>
+        <v>309</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>319</v>
+        <v>310</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -8320,7 +8249,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>320</v>
+        <v>311</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -8328,19 +8257,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>321</v>
+        <v>312</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>322</v>
+        <v>313</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F17" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="N17" t="s">
-        <v>325</v>
+        <v>316</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -8348,10 +8277,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>326</v>
+        <v>317</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>327</v>
+        <v>318</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -8360,7 +8289,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>328</v>
+        <v>319</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -8368,10 +8297,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>329</v>
+        <v>320</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>330</v>
+        <v>321</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -8380,7 +8309,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>331</v>
+        <v>322</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -8388,10 +8317,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>332</v>
+        <v>323</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>333</v>
+        <v>324</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -8400,7 +8329,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>334</v>
+        <v>325</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -8408,19 +8337,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
-        <v>335</v>
+        <v>326</v>
       </c>
       <c r="D21" s="5" t="s">
-        <v>336</v>
+        <v>327</v>
       </c>
       <c r="E21" t="s">
-        <v>323</v>
+        <v>314</v>
       </c>
       <c r="F21" t="s">
-        <v>324</v>
+        <v>315</v>
       </c>
       <c r="N21" t="s">
-        <v>337</v>
+        <v>328</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -8428,16 +8357,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>338</v>
+        <v>329</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>339</v>
+        <v>330</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -8445,10 +8374,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>340</v>
+        <v>331</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>341</v>
+        <v>332</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -8462,10 +8391,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>342</v>
+        <v>333</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>343</v>
+        <v>334</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -8479,10 +8408,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>344</v>
+        <v>335</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>345</v>
+        <v>336</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -8496,10 +8425,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>346</v>
+        <v>337</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>347</v>
+        <v>338</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -8513,10 +8442,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>348</v>
+        <v>339</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>349</v>
+        <v>340</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8530,10 +8459,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>350</v>
+        <v>341</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>351</v>
+        <v>342</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8547,10 +8476,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>352</v>
+        <v>343</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>353</v>
+        <v>344</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8559,10 +8488,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="N29" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8570,10 +8499,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>354</v>
+        <v>345</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>355</v>
+        <v>346</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8587,10 +8516,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>356</v>
+        <v>347</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>357</v>
+        <v>348</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8604,10 +8533,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>358</v>
+        <v>349</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>359</v>
+        <v>350</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8616,10 +8545,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>311</v>
+        <v>302</v>
       </c>
       <c r="N32" t="s">
-        <v>312</v>
+        <v>303</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -8627,10 +8556,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>360</v>
+        <v>351</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>361</v>
+        <v>352</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -8639,7 +8568,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>362</v>
+        <v>353</v>
       </c>
     </row>
   </sheetData>
@@ -8675,31 +8604,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>363</v>
+        <v>354</v>
       </c>
       <c r="D1" t="s">
-        <v>364</v>
+        <v>355</v>
       </c>
       <c r="E1" t="s">
-        <v>365</v>
+        <v>356</v>
       </c>
       <c r="F1" t="s">
-        <v>366</v>
+        <v>357</v>
       </c>
       <c r="G1" t="s">
-        <v>367</v>
+        <v>358</v>
       </c>
       <c r="H1" t="s">
+        <v>271</v>
+      </c>
+      <c r="I1" t="s">
+        <v>359</v>
+      </c>
+      <c r="J1" t="s">
+        <v>360</v>
+      </c>
+      <c r="K1" t="s">
         <v>280</v>
-      </c>
-      <c r="I1" t="s">
-        <v>368</v>
-      </c>
-      <c r="J1" t="s">
-        <v>369</v>
-      </c>
-      <c r="K1" t="s">
-        <v>289</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8725,10 +8654,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="I2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8742,34 +8671,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>370</v>
+        <v>361</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>371</v>
+        <v>362</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>372</v>
+        <v>363</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>373</v>
+        <v>364</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>374</v>
+        <v>365</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>375</v>
+        <v>366</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>376</v>
+        <v>367</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>377</v>
+        <v>368</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>378</v>
+        <v>369</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8780,31 +8709,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>379</v>
+        <v>370</v>
       </c>
       <c r="D4" t="s">
-        <v>380</v>
+        <v>371</v>
       </c>
       <c r="E4" t="s">
-        <v>381</v>
+        <v>372</v>
       </c>
       <c r="F4" t="s">
-        <v>382</v>
+        <v>373</v>
       </c>
       <c r="G4" t="s">
-        <v>383</v>
+        <v>374</v>
       </c>
       <c r="H4" t="s">
-        <v>384</v>
+        <v>375</v>
       </c>
       <c r="I4" t="s">
-        <v>385</v>
+        <v>376</v>
       </c>
       <c r="J4" t="s">
-        <v>386</v>
+        <v>377</v>
       </c>
       <c r="K4" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8812,7 +8741,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>387</v>
+        <v>378</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8836,7 +8765,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>388</v>
+        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8844,7 +8773,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>389</v>
+        <v>380</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8868,7 +8797,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8876,7 +8805,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>391</v>
+        <v>382</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8900,7 +8829,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8908,7 +8837,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>392</v>
+        <v>383</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8932,7 +8861,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
     </row>
   </sheetData>
@@ -8963,16 +8892,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="D1" t="s">
-        <v>393</v>
+        <v>384</v>
       </c>
       <c r="E1" t="s">
-        <v>394</v>
+        <v>385</v>
       </c>
       <c r="F1" t="s">
-        <v>395</v>
+        <v>386</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8989,7 +8918,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -9002,10 +8931,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>387</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>397</v>
+        <v>388</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -9016,13 +8945,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>398</v>
+        <v>389</v>
       </c>
       <c r="D4" t="s">
-        <v>399</v>
+        <v>390</v>
       </c>
       <c r="E4" t="s">
-        <v>400</v>
+        <v>391</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -9030,7 +8959,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>401</v>
+        <v>392</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -9039,7 +8968,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>402</v>
+        <v>393</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -9047,7 +8976,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>403</v>
+        <v>394</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -9056,7 +8985,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>404</v>
+        <v>395</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -9064,7 +8993,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>405</v>
+        <v>396</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -9073,7 +9002,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>406</v>
+        <v>397</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9081,7 +9010,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>407</v>
+        <v>398</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -9090,7 +9019,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>408</v>
+        <v>399</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9128,40 +9057,40 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
+        <v>400</v>
+      </c>
+      <c r="C1" t="s">
+        <v>401</v>
+      </c>
+      <c r="D1" t="s">
+        <v>402</v>
+      </c>
+      <c r="E1" t="s">
+        <v>403</v>
+      </c>
+      <c r="F1" t="s">
+        <v>404</v>
+      </c>
+      <c r="G1" t="s">
+        <v>405</v>
+      </c>
+      <c r="H1" t="s">
+        <v>280</v>
+      </c>
+      <c r="I1" t="s">
+        <v>406</v>
+      </c>
+      <c r="J1" t="s">
+        <v>407</v>
+      </c>
+      <c r="K1" t="s">
+        <v>408</v>
+      </c>
+      <c r="L1" t="s">
         <v>409</v>
       </c>
-      <c r="C1" t="s">
+      <c r="M1" t="s">
         <v>410</v>
-      </c>
-      <c r="D1" t="s">
-        <v>411</v>
-      </c>
-      <c r="E1" t="s">
-        <v>412</v>
-      </c>
-      <c r="F1" t="s">
-        <v>413</v>
-      </c>
-      <c r="G1" t="s">
-        <v>414</v>
-      </c>
-      <c r="H1" t="s">
-        <v>289</v>
-      </c>
-      <c r="I1" t="s">
-        <v>415</v>
-      </c>
-      <c r="J1" t="s">
-        <v>416</v>
-      </c>
-      <c r="K1" t="s">
-        <v>417</v>
-      </c>
-      <c r="L1" t="s">
-        <v>418</v>
-      </c>
-      <c r="M1" t="s">
-        <v>419</v>
       </c>
     </row>
     <row r="2" spans="1:13">
@@ -9175,16 +9104,16 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>420</v>
+        <v>411</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
       </c>
       <c r="F2" t="s">
-        <v>421</v>
+        <v>412</v>
       </c>
       <c r="G2" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="H2" t="s">
         <v>109</v>
@@ -9210,40 +9139,40 @@
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
+        <v>413</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>414</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>415</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>416</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>417</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>418</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>419</v>
+      </c>
+      <c r="I3" t="s">
+        <v>420</v>
+      </c>
+      <c r="J3" t="s">
+        <v>421</v>
+      </c>
+      <c r="K3" t="s">
         <v>422</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="L3" t="s">
         <v>423</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="M3" t="s">
         <v>424</v>
-      </c>
-      <c r="E3" s="1" t="s">
-        <v>425</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>426</v>
-      </c>
-      <c r="G3" s="1" t="s">
-        <v>427</v>
-      </c>
-      <c r="H3" s="1" t="s">
-        <v>428</v>
-      </c>
-      <c r="I3" t="s">
-        <v>429</v>
-      </c>
-      <c r="J3" t="s">
-        <v>430</v>
-      </c>
-      <c r="K3" t="s">
-        <v>431</v>
-      </c>
-      <c r="L3" t="s">
-        <v>432</v>
-      </c>
-      <c r="M3" t="s">
-        <v>433</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -9251,54 +9180,54 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C4" t="s">
+        <v>426</v>
+      </c>
+      <c r="D4" t="s">
+        <v>427</v>
+      </c>
+      <c r="E4" t="s">
+        <v>428</v>
+      </c>
+      <c r="F4" t="s">
+        <v>429</v>
+      </c>
+      <c r="G4" t="s">
+        <v>430</v>
+      </c>
+      <c r="H4" t="s">
+        <v>295</v>
+      </c>
+      <c r="I4" t="s">
+        <v>431</v>
+      </c>
+      <c r="J4" t="s">
+        <v>432</v>
+      </c>
+      <c r="K4" t="s">
+        <v>433</v>
+      </c>
+      <c r="L4" t="s">
         <v>434</v>
       </c>
-      <c r="C4" t="s">
+      <c r="M4" t="s">
         <v>435</v>
-      </c>
-      <c r="D4" t="s">
-        <v>436</v>
-      </c>
-      <c r="E4" t="s">
-        <v>437</v>
-      </c>
-      <c r="F4" t="s">
-        <v>438</v>
-      </c>
-      <c r="G4" t="s">
-        <v>439</v>
-      </c>
-      <c r="H4" t="s">
-        <v>304</v>
-      </c>
-      <c r="I4" t="s">
-        <v>440</v>
-      </c>
-      <c r="J4" t="s">
-        <v>441</v>
-      </c>
-      <c r="K4" t="s">
-        <v>442</v>
-      </c>
-      <c r="L4" t="s">
-        <v>443</v>
-      </c>
-      <c r="M4" t="s">
-        <v>444</v>
       </c>
     </row>
     <row r="5" spans="1:13">
       <c r="A5" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>445</v>
+        <v>436</v>
       </c>
       <c r="D5" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E5" t="s">
         <v>0</v>
@@ -9310,36 +9239,36 @@
         <v>0</v>
       </c>
       <c r="H5" t="s">
-        <v>447</v>
+        <v>438</v>
       </c>
       <c r="I5" t="s">
-        <v>448</v>
+        <v>439</v>
       </c>
       <c r="J5" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="K5" t="s">
-        <v>450</v>
+        <v>441</v>
       </c>
       <c r="L5" t="s">
-        <v>451</v>
+        <v>442</v>
       </c>
       <c r="M5" t="s">
-        <v>452</v>
+        <v>443</v>
       </c>
     </row>
     <row r="6" spans="1:13">
       <c r="A6" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>453</v>
+        <v>444</v>
       </c>
       <c r="D6" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E6" t="s">
         <v>9</v>
@@ -9351,36 +9280,36 @@
         <v>0</v>
       </c>
       <c r="H6" t="s">
-        <v>454</v>
+        <v>445</v>
       </c>
       <c r="I6" t="s">
-        <v>455</v>
+        <v>446</v>
       </c>
       <c r="J6" t="s">
-        <v>456</v>
+        <v>447</v>
       </c>
       <c r="K6" t="s">
-        <v>457</v>
+        <v>448</v>
       </c>
       <c r="L6" t="s">
-        <v>458</v>
+        <v>449</v>
       </c>
       <c r="M6" t="s">
-        <v>459</v>
+        <v>450</v>
       </c>
     </row>
     <row r="7" spans="1:13">
       <c r="A7" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
-        <v>460</v>
+        <v>451</v>
       </c>
       <c r="D7" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E7" t="s">
         <v>18</v>
@@ -9392,36 +9321,36 @@
         <v>0</v>
       </c>
       <c r="H7" t="s">
-        <v>461</v>
+        <v>452</v>
       </c>
       <c r="I7" t="s">
-        <v>462</v>
+        <v>453</v>
       </c>
       <c r="J7" t="s">
-        <v>463</v>
+        <v>454</v>
       </c>
       <c r="K7" t="s">
-        <v>464</v>
+        <v>455</v>
       </c>
       <c r="L7" t="s">
-        <v>465</v>
+        <v>456</v>
       </c>
       <c r="M7" t="s">
-        <v>466</v>
+        <v>457</v>
       </c>
     </row>
     <row r="8" spans="1:13">
       <c r="A8" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>467</v>
+        <v>458</v>
       </c>
       <c r="D8" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E8" t="s">
         <v>27</v>
@@ -9433,36 +9362,36 @@
         <v>0</v>
       </c>
       <c r="H8" s="4" t="s">
-        <v>468</v>
+        <v>459</v>
       </c>
       <c r="I8" t="s">
-        <v>469</v>
+        <v>460</v>
       </c>
       <c r="J8" t="s">
-        <v>470</v>
+        <v>461</v>
       </c>
       <c r="K8" t="s">
-        <v>471</v>
+        <v>462</v>
       </c>
       <c r="L8" t="s">
-        <v>472</v>
+        <v>463</v>
       </c>
       <c r="M8" t="s">
-        <v>473</v>
+        <v>464</v>
       </c>
     </row>
     <row r="9" spans="1:13">
       <c r="A9" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>474</v>
+        <v>465</v>
       </c>
       <c r="D9" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E9" t="s">
         <v>36</v>
@@ -9474,36 +9403,36 @@
         <v>0</v>
       </c>
       <c r="H9" t="s">
-        <v>475</v>
+        <v>466</v>
       </c>
       <c r="I9" t="s">
-        <v>476</v>
+        <v>467</v>
       </c>
       <c r="J9" t="s">
-        <v>477</v>
+        <v>468</v>
       </c>
       <c r="K9" t="s">
-        <v>478</v>
+        <v>469</v>
       </c>
       <c r="L9" t="s">
-        <v>479</v>
+        <v>470</v>
       </c>
       <c r="M9" t="s">
-        <v>480</v>
+        <v>471</v>
       </c>
     </row>
     <row r="10" spans="1:13">
       <c r="A10" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>481</v>
+        <v>472</v>
       </c>
       <c r="D10" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E10" t="s">
         <v>45</v>
@@ -9515,36 +9444,36 @@
         <v>0</v>
       </c>
       <c r="H10" t="s">
-        <v>482</v>
+        <v>473</v>
       </c>
       <c r="I10" t="s">
-        <v>483</v>
+        <v>474</v>
       </c>
       <c r="J10" t="s">
-        <v>484</v>
+        <v>475</v>
       </c>
       <c r="K10" t="s">
-        <v>485</v>
+        <v>476</v>
       </c>
       <c r="L10" t="s">
-        <v>486</v>
+        <v>477</v>
       </c>
       <c r="M10" t="s">
-        <v>487</v>
+        <v>478</v>
       </c>
     </row>
     <row r="11" spans="1:13">
       <c r="A11" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>488</v>
+        <v>479</v>
       </c>
       <c r="D11" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E11" t="s">
         <v>54</v>
@@ -9556,36 +9485,36 @@
         <v>0</v>
       </c>
       <c r="H11" t="s">
-        <v>489</v>
+        <v>480</v>
       </c>
       <c r="I11" t="s">
-        <v>490</v>
+        <v>481</v>
       </c>
       <c r="J11" t="s">
-        <v>491</v>
+        <v>482</v>
       </c>
       <c r="K11" t="s">
-        <v>492</v>
+        <v>483</v>
       </c>
       <c r="L11" t="s">
-        <v>493</v>
+        <v>484</v>
       </c>
       <c r="M11" t="s">
-        <v>494</v>
+        <v>485</v>
       </c>
     </row>
     <row r="12" spans="1:13">
       <c r="A12" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>495</v>
+        <v>486</v>
       </c>
       <c r="D12" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E12" t="s">
         <v>61</v>
@@ -9597,36 +9526,36 @@
         <v>0</v>
       </c>
       <c r="H12" t="s">
-        <v>496</v>
+        <v>487</v>
       </c>
       <c r="I12" t="s">
-        <v>497</v>
+        <v>488</v>
       </c>
       <c r="J12" t="s">
-        <v>498</v>
+        <v>489</v>
       </c>
       <c r="K12" t="s">
-        <v>499</v>
+        <v>490</v>
       </c>
       <c r="L12" t="s">
-        <v>500</v>
+        <v>491</v>
       </c>
       <c r="M12" t="s">
-        <v>501</v>
+        <v>492</v>
       </c>
     </row>
     <row r="13" spans="1:13">
       <c r="A13" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>502</v>
+        <v>493</v>
       </c>
       <c r="D13" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E13" t="s">
         <v>68</v>
@@ -9638,36 +9567,36 @@
         <v>0</v>
       </c>
       <c r="H13" t="s">
-        <v>503</v>
+        <v>494</v>
       </c>
       <c r="I13" t="s">
-        <v>504</v>
+        <v>495</v>
       </c>
       <c r="J13" t="s">
-        <v>505</v>
+        <v>496</v>
       </c>
       <c r="K13" t="s">
-        <v>506</v>
+        <v>497</v>
       </c>
       <c r="L13" t="s">
-        <v>507</v>
+        <v>498</v>
       </c>
       <c r="M13" t="s">
-        <v>508</v>
+        <v>499</v>
       </c>
     </row>
     <row r="14" spans="1:13">
       <c r="A14" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>509</v>
+        <v>500</v>
       </c>
       <c r="D14" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E14" t="s">
         <v>73</v>
@@ -9679,36 +9608,36 @@
         <v>1</v>
       </c>
       <c r="H14" t="s">
-        <v>510</v>
+        <v>501</v>
       </c>
       <c r="I14" t="s">
-        <v>511</v>
+        <v>502</v>
       </c>
       <c r="J14" t="s">
-        <v>512</v>
+        <v>503</v>
       </c>
       <c r="K14" t="s">
-        <v>513</v>
+        <v>504</v>
       </c>
       <c r="L14" t="s">
-        <v>514</v>
+        <v>505</v>
       </c>
       <c r="M14" t="s">
-        <v>515</v>
+        <v>506</v>
       </c>
     </row>
     <row r="15" spans="1:13">
       <c r="A15" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>516</v>
+        <v>507</v>
       </c>
       <c r="D15" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E15" t="s">
         <v>78</v>
@@ -9720,39 +9649,39 @@
         <v>1</v>
       </c>
       <c r="H15" t="s">
-        <v>517</v>
+        <v>508</v>
       </c>
       <c r="I15" t="s">
-        <v>518</v>
+        <v>509</v>
       </c>
       <c r="J15" t="s">
-        <v>519</v>
+        <v>510</v>
       </c>
       <c r="K15" t="s">
-        <v>520</v>
+        <v>511</v>
       </c>
       <c r="L15" t="s">
-        <v>521</v>
+        <v>512</v>
       </c>
       <c r="M15" t="s">
-        <v>522</v>
+        <v>513</v>
       </c>
     </row>
     <row r="16" spans="1:13">
       <c r="A16" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>523</v>
+        <v>514</v>
       </c>
       <c r="D16" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E16" t="s">
-        <v>525</v>
+        <v>516</v>
       </c>
       <c r="F16">
         <v>1</v>
@@ -9761,39 +9690,39 @@
         <v>0</v>
       </c>
       <c r="H16" t="s">
-        <v>526</v>
+        <v>517</v>
       </c>
       <c r="I16" t="s">
-        <v>527</v>
+        <v>518</v>
       </c>
       <c r="J16" t="s">
-        <v>528</v>
+        <v>519</v>
       </c>
       <c r="K16" t="s">
-        <v>529</v>
+        <v>520</v>
       </c>
       <c r="L16" t="s">
-        <v>530</v>
+        <v>521</v>
       </c>
       <c r="M16" t="s">
-        <v>531</v>
+        <v>522</v>
       </c>
     </row>
     <row r="17" spans="1:13">
       <c r="A17" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>532</v>
+        <v>523</v>
       </c>
       <c r="D17" t="s">
+        <v>515</v>
+      </c>
+      <c r="E17" t="s">
         <v>524</v>
-      </c>
-      <c r="E17" t="s">
-        <v>533</v>
       </c>
       <c r="F17">
         <v>1</v>
@@ -9802,39 +9731,39 @@
         <v>0</v>
       </c>
       <c r="H17" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="I17" t="s">
-        <v>535</v>
+        <v>526</v>
       </c>
       <c r="J17" t="s">
-        <v>536</v>
+        <v>527</v>
       </c>
       <c r="K17" t="s">
-        <v>537</v>
+        <v>528</v>
       </c>
       <c r="L17" t="s">
-        <v>538</v>
+        <v>529</v>
       </c>
       <c r="M17" t="s">
-        <v>539</v>
+        <v>530</v>
       </c>
     </row>
     <row r="18" spans="1:13">
       <c r="A18" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>540</v>
+        <v>531</v>
       </c>
       <c r="D18" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E18" t="s">
-        <v>541</v>
+        <v>532</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -9843,39 +9772,39 @@
         <v>0</v>
       </c>
       <c r="H18" t="s">
-        <v>542</v>
+        <v>533</v>
       </c>
       <c r="I18" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="J18" t="s">
-        <v>544</v>
+        <v>535</v>
       </c>
       <c r="K18" t="s">
-        <v>545</v>
+        <v>536</v>
       </c>
       <c r="L18" t="s">
-        <v>546</v>
+        <v>537</v>
       </c>
       <c r="M18" t="s">
-        <v>547</v>
+        <v>538</v>
       </c>
     </row>
     <row r="19" spans="1:13">
       <c r="A19" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>548</v>
+        <v>539</v>
       </c>
       <c r="D19" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E19" t="s">
-        <v>549</v>
+        <v>540</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -9884,39 +9813,39 @@
         <v>0</v>
       </c>
       <c r="H19" t="s">
-        <v>550</v>
+        <v>541</v>
       </c>
       <c r="I19" t="s">
-        <v>551</v>
+        <v>542</v>
       </c>
       <c r="J19" t="s">
-        <v>552</v>
+        <v>543</v>
       </c>
       <c r="K19" t="s">
-        <v>553</v>
+        <v>544</v>
       </c>
       <c r="L19" t="s">
-        <v>554</v>
+        <v>545</v>
       </c>
       <c r="M19" t="s">
-        <v>555</v>
+        <v>546</v>
       </c>
     </row>
     <row r="20" spans="1:13">
       <c r="A20" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>556</v>
+        <v>547</v>
       </c>
       <c r="D20" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E20" t="s">
-        <v>557</v>
+        <v>548</v>
       </c>
       <c r="F20">
         <v>1</v>
@@ -9925,39 +9854,39 @@
         <v>0</v>
       </c>
       <c r="H20" t="s">
-        <v>558</v>
+        <v>549</v>
       </c>
       <c r="I20" t="s">
-        <v>559</v>
+        <v>550</v>
       </c>
       <c r="J20" t="s">
-        <v>560</v>
+        <v>551</v>
       </c>
       <c r="K20" t="s">
-        <v>561</v>
+        <v>552</v>
       </c>
       <c r="L20" t="s">
-        <v>562</v>
+        <v>553</v>
       </c>
       <c r="M20" t="s">
-        <v>563</v>
+        <v>554</v>
       </c>
     </row>
     <row r="21" spans="1:13">
       <c r="A21" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>564</v>
+        <v>555</v>
       </c>
       <c r="D21" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E21" t="s">
-        <v>565</v>
+        <v>556</v>
       </c>
       <c r="F21">
         <v>1</v>
@@ -9966,39 +9895,39 @@
         <v>0</v>
       </c>
       <c r="H21" t="s">
-        <v>566</v>
+        <v>557</v>
       </c>
       <c r="I21" t="s">
-        <v>567</v>
+        <v>558</v>
       </c>
       <c r="J21" t="s">
-        <v>568</v>
+        <v>559</v>
       </c>
       <c r="K21" t="s">
-        <v>569</v>
+        <v>560</v>
       </c>
       <c r="L21" t="s">
-        <v>570</v>
+        <v>561</v>
       </c>
       <c r="M21" t="s">
-        <v>571</v>
+        <v>562</v>
       </c>
     </row>
     <row r="22" spans="1:13">
       <c r="A22" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>572</v>
+        <v>563</v>
       </c>
       <c r="D22" t="s">
-        <v>524</v>
+        <v>515</v>
       </c>
       <c r="E22" t="s">
-        <v>573</v>
+        <v>564</v>
       </c>
       <c r="F22">
         <v>1</v>
@@ -10007,39 +9936,39 @@
         <v>0</v>
       </c>
       <c r="H22" t="s">
-        <v>574</v>
+        <v>565</v>
       </c>
       <c r="I22" t="s">
-        <v>575</v>
+        <v>566</v>
       </c>
       <c r="J22" t="s">
-        <v>576</v>
+        <v>567</v>
       </c>
       <c r="K22" t="s">
-        <v>577</v>
+        <v>568</v>
       </c>
       <c r="L22" t="s">
-        <v>578</v>
+        <v>569</v>
       </c>
       <c r="M22" t="s">
-        <v>579</v>
+        <v>570</v>
       </c>
     </row>
     <row r="23" spans="1:13">
       <c r="A23" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>580</v>
+        <v>571</v>
       </c>
       <c r="D23" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E23" t="s">
-        <v>582</v>
+        <v>573</v>
       </c>
       <c r="F23">
         <v>1</v>
@@ -10048,39 +9977,39 @@
         <v>0</v>
       </c>
       <c r="H23" t="s">
-        <v>583</v>
+        <v>574</v>
       </c>
       <c r="I23" t="s">
-        <v>584</v>
+        <v>575</v>
       </c>
       <c r="J23" t="s">
-        <v>585</v>
+        <v>576</v>
       </c>
       <c r="K23" t="s">
-        <v>586</v>
+        <v>577</v>
       </c>
       <c r="L23" t="s">
-        <v>587</v>
+        <v>578</v>
       </c>
       <c r="M23" t="s">
-        <v>588</v>
+        <v>579</v>
       </c>
     </row>
     <row r="24" spans="1:13">
       <c r="A24" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>589</v>
+        <v>580</v>
       </c>
       <c r="D24" t="s">
+        <v>572</v>
+      </c>
+      <c r="E24" t="s">
         <v>581</v>
-      </c>
-      <c r="E24" t="s">
-        <v>590</v>
       </c>
       <c r="F24">
         <v>1</v>
@@ -10089,39 +10018,39 @@
         <v>1</v>
       </c>
       <c r="H24" t="s">
-        <v>591</v>
+        <v>582</v>
       </c>
       <c r="I24" t="s">
-        <v>592</v>
+        <v>583</v>
       </c>
       <c r="J24" t="s">
-        <v>593</v>
+        <v>584</v>
       </c>
       <c r="K24" t="s">
-        <v>594</v>
+        <v>585</v>
       </c>
       <c r="L24" t="s">
-        <v>595</v>
+        <v>586</v>
       </c>
       <c r="M24" t="s">
-        <v>596</v>
+        <v>587</v>
       </c>
     </row>
     <row r="25" spans="1:13">
       <c r="A25" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>597</v>
+        <v>588</v>
       </c>
       <c r="D25" t="s">
-        <v>581</v>
+        <v>572</v>
       </c>
       <c r="E25" t="s">
-        <v>598</v>
+        <v>589</v>
       </c>
       <c r="F25">
         <v>1</v>
@@ -10130,22 +10059,22 @@
         <v>0</v>
       </c>
       <c r="H25" t="s">
-        <v>599</v>
+        <v>590</v>
       </c>
       <c r="I25" t="s">
         <v>52</v>
       </c>
       <c r="J25" t="s">
-        <v>600</v>
+        <v>591</v>
       </c>
       <c r="K25" t="s">
-        <v>601</v>
+        <v>592</v>
       </c>
       <c r="L25" t="s">
-        <v>602</v>
+        <v>593</v>
       </c>
       <c r="M25" t="s">
-        <v>603</v>
+        <v>594</v>
       </c>
     </row>
     <row r="26" spans="1:13">
@@ -10153,10 +10082,10 @@
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="D26" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E26" t="s">
         <v>29</v>
@@ -10168,22 +10097,22 @@
         <v>0</v>
       </c>
       <c r="H26" t="s">
-        <v>606</v>
+        <v>597</v>
       </c>
       <c r="I26" t="s">
-        <v>607</v>
+        <v>598</v>
       </c>
       <c r="J26" t="s">
-        <v>608</v>
+        <v>599</v>
       </c>
       <c r="K26" t="s">
-        <v>609</v>
+        <v>600</v>
       </c>
       <c r="L26" t="s">
-        <v>610</v>
+        <v>601</v>
       </c>
       <c r="M26" t="s">
-        <v>611</v>
+        <v>602</v>
       </c>
     </row>
     <row r="27" spans="1:13">
@@ -10191,13 +10120,13 @@
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>612</v>
+        <v>603</v>
       </c>
       <c r="D27" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E27" t="s">
-        <v>613</v>
+        <v>604</v>
       </c>
       <c r="F27">
         <v>1</v>
@@ -10206,36 +10135,36 @@
         <v>0</v>
       </c>
       <c r="H27" t="s">
-        <v>614</v>
+        <v>605</v>
       </c>
       <c r="I27" t="s">
-        <v>615</v>
+        <v>606</v>
       </c>
       <c r="J27" t="s">
-        <v>616</v>
+        <v>607</v>
       </c>
       <c r="K27" t="s">
-        <v>617</v>
+        <v>608</v>
       </c>
       <c r="L27" t="s">
-        <v>618</v>
+        <v>609</v>
       </c>
       <c r="M27" t="s">
-        <v>619</v>
+        <v>610</v>
       </c>
     </row>
     <row r="28" spans="1:13">
       <c r="A28" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="D28" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E28" t="s">
         <v>20</v>
@@ -10247,36 +10176,36 @@
         <v>0</v>
       </c>
       <c r="H28" t="s">
-        <v>621</v>
+        <v>612</v>
       </c>
       <c r="I28" t="s">
-        <v>622</v>
+        <v>613</v>
       </c>
       <c r="J28" t="s">
-        <v>623</v>
+        <v>614</v>
       </c>
       <c r="K28" t="s">
-        <v>624</v>
+        <v>615</v>
       </c>
       <c r="L28" t="s">
-        <v>625</v>
+        <v>616</v>
       </c>
       <c r="M28" t="s">
-        <v>626</v>
+        <v>617</v>
       </c>
     </row>
     <row r="29" spans="1:13">
       <c r="A29" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>627</v>
+        <v>618</v>
       </c>
       <c r="D29" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E29" t="s">
         <v>11</v>
@@ -10288,36 +10217,36 @@
         <v>0</v>
       </c>
       <c r="H29" t="s">
-        <v>628</v>
+        <v>619</v>
       </c>
       <c r="I29" t="s">
-        <v>629</v>
+        <v>620</v>
       </c>
       <c r="J29" t="s">
-        <v>630</v>
+        <v>621</v>
       </c>
       <c r="K29" t="s">
-        <v>631</v>
+        <v>622</v>
       </c>
       <c r="L29" t="s">
-        <v>632</v>
+        <v>623</v>
       </c>
       <c r="M29" t="s">
-        <v>633</v>
+        <v>624</v>
       </c>
     </row>
     <row r="30" spans="1:13">
       <c r="A30" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>634</v>
+        <v>625</v>
       </c>
       <c r="D30" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E30" t="s">
         <v>2</v>
@@ -10329,39 +10258,39 @@
         <v>0</v>
       </c>
       <c r="H30" t="s">
-        <v>635</v>
+        <v>626</v>
       </c>
       <c r="I30" t="s">
-        <v>636</v>
+        <v>627</v>
       </c>
       <c r="J30" t="s">
-        <v>637</v>
+        <v>628</v>
       </c>
       <c r="K30" t="s">
-        <v>638</v>
+        <v>629</v>
       </c>
       <c r="L30" t="s">
-        <v>639</v>
+        <v>630</v>
       </c>
       <c r="M30" t="s">
-        <v>640</v>
+        <v>631</v>
       </c>
     </row>
     <row r="31" spans="1:13">
       <c r="A31" t="s">
-        <v>390</v>
+        <v>381</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>641</v>
+        <v>632</v>
       </c>
       <c r="D31" t="s">
-        <v>605</v>
+        <v>596</v>
       </c>
       <c r="E31" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="F31">
         <v>1</v>
@@ -10370,22 +10299,22 @@
         <v>0</v>
       </c>
       <c r="H31" t="s">
-        <v>642</v>
+        <v>633</v>
       </c>
       <c r="I31" t="s">
-        <v>643</v>
+        <v>634</v>
       </c>
       <c r="J31" t="s">
-        <v>644</v>
+        <v>635</v>
       </c>
       <c r="K31" t="s">
-        <v>645</v>
+        <v>636</v>
       </c>
       <c r="L31" t="s">
-        <v>646</v>
+        <v>637</v>
       </c>
       <c r="M31" t="s">
-        <v>647</v>
+        <v>638</v>
       </c>
     </row>
     <row r="32" spans="1:13">
@@ -10393,13 +10322,13 @@
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>648</v>
+        <v>639</v>
       </c>
       <c r="D32" t="s">
-        <v>446</v>
+        <v>437</v>
       </c>
       <c r="E32" t="s">
-        <v>649</v>
+        <v>640</v>
       </c>
       <c r="F32">
         <v>1</v>
@@ -10408,22 +10337,22 @@
         <v>0</v>
       </c>
       <c r="H32" t="s">
-        <v>650</v>
+        <v>641</v>
       </c>
       <c r="I32" t="s">
-        <v>651</v>
+        <v>642</v>
       </c>
       <c r="J32" t="s">
-        <v>652</v>
+        <v>643</v>
       </c>
       <c r="K32" t="s">
-        <v>653</v>
+        <v>644</v>
       </c>
       <c r="L32" t="s">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="M32" t="s">
-        <v>655</v>
+        <v>646</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="2"/>
+    <workbookView windowWidth="29868" windowHeight="13451" tabRatio="717" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="枚举示例" sheetId="3" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1546" uniqueCount="899">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="959">
   <si>
     <t>Dog</t>
   </si>
@@ -537,6 +537,9 @@
     <t>未领取奖励的条目和固定条目数量之和不足该值时，以已领取奖励的条目填充占位</t>
   </si>
   <si>
+    <t>Alias</t>
+  </si>
+  <si>
     <t>IconName</t>
   </si>
   <si>
@@ -549,6 +552,9 @@
     <t>DefaultTongue</t>
   </si>
   <si>
+    <t>FixedEyewear</t>
+  </si>
+  <si>
     <t>FolderPath</t>
   </si>
   <si>
@@ -588,10 +594,10 @@
     <t>Eyes_Wink</t>
   </si>
   <si>
-    <t>只影响图标和伪装模式，不影响打牌模式</t>
-  </si>
-  <si>
-    <t>备注名</t>
+    <t>只影响图标和桌宠模式，不影响打牌模式</t>
+  </si>
+  <si>
+    <t>策划粗记名</t>
   </si>
   <si>
     <t>图标名称</t>
@@ -603,6 +609,12 @@
     <t>默认眼神</t>
   </si>
   <si>
+    <t>默认舌头</t>
+  </si>
+  <si>
+    <t>默认眼镜</t>
+  </si>
+  <si>
     <t>资源所在文件夹</t>
   </si>
   <si>
@@ -720,6 +732,9 @@
     <t>Shiba_ThinRed.png</t>
   </si>
   <si>
+    <t>Sunglasses_Blade.png</t>
+  </si>
+  <si>
     <t>Head_Thin.png</t>
   </si>
   <si>
@@ -729,6 +744,9 @@
     <t>Shiba_UnshavenRed.png</t>
   </si>
   <si>
+    <t>Monocle_black.png</t>
+  </si>
+  <si>
     <t>Head_Unshaven.png</t>
   </si>
   <si>
@@ -738,12 +756,18 @@
     <t>Shiba_ThinBlack.png</t>
   </si>
   <si>
+    <t>EyePatch.png</t>
+  </si>
+  <si>
     <t>胡渣黑柴</t>
   </si>
   <si>
     <t>Shiba_UnshavenBlack.png</t>
   </si>
   <si>
+    <t>Monocle_golden.png</t>
+  </si>
+  <si>
     <t>瘦白柴</t>
   </si>
   <si>
@@ -756,6 +780,9 @@
     <t>Shiba_UnshavenCream.png</t>
   </si>
   <si>
+    <t>3DGlasses.png</t>
+  </si>
+  <si>
     <t>瘦芝麻柴</t>
   </si>
   <si>
@@ -768,6 +795,9 @@
     <t>Shiba_UnshavenSesame.png</t>
   </si>
   <si>
+    <t>新狗狗 1013</t>
+  </si>
+  <si>
     <t>Name</t>
   </si>
   <si>
@@ -894,6 +924,9 @@
     <t>有些表情需要临时更换头饰，例如被打晕的时候头上转的星星。但目前版本没有</t>
   </si>
   <si>
+    <t>该功能处于改版器，暂时禁用效果。bool字段保留后续用其他方式表示狗狗沉默。</t>
+  </si>
+  <si>
     <t>左指画面左侧，而非狗自己的左</t>
   </si>
   <si>
@@ -1245,6 +1278,9 @@
     <t>ApiName</t>
   </si>
   <si>
+    <t>IsEnabled</t>
+  </si>
+  <si>
     <t>RuleType</t>
   </si>
   <si>
@@ -1284,6 +1320,10 @@
     <t>平台和存档使用的稳定机器名；发布后不要改名</t>
   </si>
   <si>
+    <t>控制该成就是否参与实际功能。设为 FALSE 时，仅保留 AchievementId 和 ApiName 作为历史墓碑；客户端不再进行条件判定、历史补发、平台读取、解锁或同步，Steam 成就配置转换器也不再导出该行。已停用成就的 AchievementId 和 ApiName 不得复用。
+注意：已经为FALSE的条目禁止改回TRUE，如有必要可新增条目</t>
+  </si>
+  <si>
     <t>FirstExternalItemType=首次非初始获得部位；FirstExternalItemRarity=首次非初始获得指定品质；FirstEvent=首次发生事件；StatisticAtLeast=统计达到数值</t>
   </si>
   <si>
@@ -1320,6 +1360,9 @@
     <t>API 名</t>
   </si>
   <si>
+    <t>是否启用</t>
+  </si>
+  <si>
     <t>解锁规则</t>
   </si>
   <si>
@@ -2016,6 +2059,10 @@
     <t>CSV 数据字典用的中文名称</t>
   </si>
   <si>
+    <t>控制该统计定义是否参与实际功能。设为 FALSE 时，仅保留 StatisticId、StatisticKey 和 PlatformApiName 作为历史墓碑；客户端不再累计、显示、用于成就判定或参与平台同步，Steam统计配置转换器也不再导出。玩家存档中已有的历史统计值可以保留，但运行时忽略。已停用统计的 StatisticId、StatisticKey 和 PlatformApiName 不得复用。
+注意：已经为FALSE的条目禁止改回TRUE，如有必要可新增条目</t>
+  </si>
+  <si>
     <t>数值单位</t>
   </si>
   <si>
@@ -2605,6 +2652,141 @@
   </si>
   <si>
     <t>游戏运行期间，按系统本地时间的自然半小时分段累计键鼠获得的筹码；首尾分段可能不足 30 分钟。</t>
+  </si>
+  <si>
+    <t>PlaytestCohortMember</t>
+  </si>
+  <si>
+    <t>Playtest统计样本玩家</t>
+  </si>
+  <si>
+    <t>Flag</t>
+  </si>
+  <si>
+    <t>STAT_PT1_COHORT_MEMBER</t>
+  </si>
+  <si>
+    <t>Playtest正式环境首次完成统计初始化后置1；仅正常模式记录，Debug和Mock不记录</t>
+  </si>
+  <si>
+    <t>ReturnedAfter24Hours</t>
+  </si>
+  <si>
+    <t>24小时后回访玩家</t>
+  </si>
+  <si>
+    <t>STAT_PT1_RETURNED_AFTER_24H</t>
+  </si>
+  <si>
+    <t>距本版本首次观察时间达到24小时后的下一次独立启动置1；持续运行不算回访；每名玩家只记一次</t>
+  </si>
+  <si>
+    <t>ReturnedAfter72Hours</t>
+  </si>
+  <si>
+    <t>72小时后回访玩家</t>
+  </si>
+  <si>
+    <t>STAT_PT1_RETURNED_AFTER_72H</t>
+  </si>
+  <si>
+    <t>距本版本首次观察时间达到72小时后的下一次独立启动置1；持续运行不算回访；每名玩家只记一次</t>
+  </si>
+  <si>
+    <t>ReturnedAfter168Hours</t>
+  </si>
+  <si>
+    <t>168小时后回访玩家</t>
+  </si>
+  <si>
+    <t>STAT_PT1_RETURNED_AFTER_168H</t>
+  </si>
+  <si>
+    <t>距本版本首次观察时间达到168小时后的下一次独立启动置1；持续运行不算回访；每名玩家只记一次</t>
+  </si>
+  <si>
+    <t>PokerBasicsGuidanceCompleted</t>
+  </si>
+  <si>
+    <t>完成扑克基础引导玩家</t>
+  </si>
+  <si>
+    <t>STAT_PT1_POKER_GUIDANCE_COMPLETED</t>
+  </si>
+  <si>
+    <t>正常扑克游玩成功消除扑克新手标记后置1；每名玩家只记一次；Debug和Mock不记录</t>
+  </si>
+  <si>
+    <t>PokerBasicsGuidanceCompletionSeconds</t>
+  </si>
+  <si>
+    <t>完成扑克基础引导所需秒数</t>
+  </si>
+  <si>
+    <t>STAT_PT1_POKER_GUIDANCE_SECONDS</t>
+  </si>
+  <si>
+    <t>从本版本首次观察到成功消除扑克新手标记的累计正常游戏秒数；仅完成时写入一次</t>
+  </si>
+  <si>
+    <t>PokerBasicsGuidanceCompletionHandsPlayed</t>
+  </si>
+  <si>
+    <t>完成扑克基础引导所需局数</t>
+  </si>
+  <si>
+    <t>STAT_PT1_POKER_GUIDANCE_HANDS</t>
+  </si>
+  <si>
+    <t>从本版本首次观察到成功消除扑克新手标记前完成的扑克局数；仅完成时写入一次</t>
+  </si>
+  <si>
+    <t>NewcomerBox1SteamRewardClaimed</t>
+  </si>
+  <si>
+    <t>新手第1盲盒Steam奖励成功</t>
+  </si>
+  <si>
+    <t>STAT_PT1_NEWCOMER_BOX_1_STEAM_CLAIMED</t>
+  </si>
+  <si>
+    <t>Schedule 1001 的Steam装扮成功入账后置1；Fallback和该Schedule结束后的LateSteam均不记录；每名玩家只记一次</t>
+  </si>
+  <si>
+    <t>NewcomerBox4SteamRewardClaimed</t>
+  </si>
+  <si>
+    <t>新手第4盲盒Steam奖励成功</t>
+  </si>
+  <si>
+    <t>STAT_PT1_NEWCOMER_BOX_4_STEAM_CLAIMED</t>
+  </si>
+  <si>
+    <t>Schedule 1004 的Steam装扮成功入账后置1；Fallback和该Schedule结束后的LateSteam均不记录；每名玩家只记一次</t>
+  </si>
+  <si>
+    <t>FirstLoopBoxSteamRewardClaimed</t>
+  </si>
+  <si>
+    <t>首个循环盲盒Steam奖励成功</t>
+  </si>
+  <si>
+    <t>STAT_PT1_FIRST_LOOP_BOX_STEAM_CLAIMED</t>
+  </si>
+  <si>
+    <t>Schedule 2001 的首次Steam装扮成功入账后置1；Fallback和该Schedule结束后的LateSteam均不记录；每名玩家只记一次</t>
+  </si>
+  <si>
+    <t>AnyLinkTreeRewardClaimed</t>
+  </si>
+  <si>
+    <t>任意LinkTree奖励领取成功</t>
+  </si>
+  <si>
+    <t>STAT_PT1_ANY_LINKTREE_REWARD_CLAIMED</t>
+  </si>
+  <si>
+    <t>任意LinkTree永久回执经Steam确认且奖励成功应用后置1；每名玩家只记一次</t>
   </si>
   <si>
     <t>Key</t>
@@ -3441,7 +3623,14 @@
     <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
     <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
-  <dxfs count="17">
+  <dxfs count="18">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor theme="2" tint="-0.25"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill patternType="solid">
@@ -3635,25 +3824,25 @@
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="6"/>
-      <tableStyleElement type="headerRow" dxfId="5"/>
-      <tableStyleElement type="totalRow" dxfId="4"/>
-      <tableStyleElement type="firstColumn" dxfId="3"/>
-      <tableStyleElement type="lastColumn" dxfId="2"/>
-      <tableStyleElement type="firstRowStripe" dxfId="1"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
+      <tableStyleElement type="wholeTable" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="6"/>
+      <tableStyleElement type="totalRow" dxfId="5"/>
+      <tableStyleElement type="firstColumn" dxfId="4"/>
+      <tableStyleElement type="lastColumn" dxfId="3"/>
+      <tableStyleElement type="firstRowStripe" dxfId="2"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="16"/>
-      <tableStyleElement type="totalRow" dxfId="15"/>
-      <tableStyleElement type="firstRowStripe" dxfId="14"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
-      <tableStyleElement type="pageFieldValues" dxfId="7"/>
+      <tableStyleElement type="headerRow" dxfId="17"/>
+      <tableStyleElement type="totalRow" dxfId="16"/>
+      <tableStyleElement type="firstRowStripe" dxfId="15"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="14"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="13"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="11"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="10"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="9"/>
+      <tableStyleElement type="pageFieldValues" dxfId="8"/>
     </tableStyle>
   </tableStyles>
   <extLst>
@@ -4303,50 +4492,53 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:J62"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="11.5833333333333" customWidth="1"/>
     <col min="3" max="3" width="30.9166666666667" customWidth="1"/>
-    <col min="4" max="4" width="22.8333333333333" customWidth="1"/>
-    <col min="5" max="5" width="14.9166666666667" customWidth="1"/>
-    <col min="6" max="6" width="13.6666666666667" customWidth="1"/>
-    <col min="7" max="7" width="51" customWidth="1"/>
-    <col min="8" max="8" width="20.5833333333333" customWidth="1"/>
-    <col min="9" max="9" width="53.0833333333333" customWidth="1"/>
+    <col min="4" max="5" width="22.8333333333333" customWidth="1"/>
+    <col min="6" max="6" width="14.9166666666667" customWidth="1"/>
+    <col min="7" max="7" width="13.6666666666667" customWidth="1"/>
+    <col min="8" max="8" width="51" customWidth="1"/>
+    <col min="9" max="9" width="20.5833333333333" customWidth="1"/>
+    <col min="10" max="10" width="53.0833333333333" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9">
+    <row r="1" spans="1:10">
       <c r="A1" t="s">
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>647</v>
+        <v>661</v>
       </c>
       <c r="C1" t="s">
-        <v>648</v>
+        <v>662</v>
       </c>
       <c r="D1" t="s">
-        <v>649</v>
+        <v>663</v>
       </c>
       <c r="E1" t="s">
-        <v>650</v>
+        <v>413</v>
       </c>
       <c r="F1" t="s">
-        <v>651</v>
+        <v>664</v>
       </c>
       <c r="G1" t="s">
-        <v>652</v>
+        <v>665</v>
       </c>
       <c r="H1" t="s">
-        <v>653</v>
+        <v>666</v>
       </c>
       <c r="I1" t="s">
-        <v>280</v>
-      </c>
-    </row>
-    <row r="2" spans="1:9">
+        <v>667</v>
+      </c>
+      <c r="J1" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10">
       <c r="A2" t="s">
         <v>106</v>
       </c>
@@ -4360,1437 +4552,1911 @@
         <v>109</v>
       </c>
       <c r="E2" t="s">
-        <v>654</v>
+        <v>292</v>
       </c>
       <c r="F2" t="s">
-        <v>655</v>
+        <v>668</v>
       </c>
       <c r="G2" t="s">
+        <v>669</v>
+      </c>
+      <c r="H2" t="s">
         <v>109</v>
       </c>
-      <c r="H2" t="s">
-        <v>282</v>
-      </c>
       <c r="I2" t="s">
+        <v>292</v>
+      </c>
+      <c r="J2" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="89" customHeight="1" spans="1:9">
+    <row r="3" s="1" customFormat="1" ht="89" customHeight="1" spans="1:10">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>656</v>
+        <v>670</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>657</v>
+        <v>671</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>658</v>
+        <v>672</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>660</v>
+        <v>674</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>661</v>
+        <v>675</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>662</v>
+        <v>676</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9">
+        <v>677</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>678</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10">
       <c r="A4" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>664</v>
+        <v>679</v>
       </c>
       <c r="C4" t="s">
-        <v>665</v>
+        <v>680</v>
       </c>
       <c r="D4" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="E4" t="s">
-        <v>666</v>
+        <v>440</v>
       </c>
       <c r="F4" t="s">
-        <v>667</v>
+        <v>681</v>
       </c>
       <c r="G4" t="s">
-        <v>668</v>
+        <v>682</v>
       </c>
       <c r="H4" t="s">
-        <v>669</v>
+        <v>683</v>
       </c>
       <c r="I4" t="s">
-        <v>295</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9">
+        <v>684</v>
+      </c>
+      <c r="J4" t="s">
+        <v>306</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B5">
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>670</v>
+        <v>685</v>
       </c>
       <c r="D5" t="s">
-        <v>671</v>
-      </c>
-      <c r="E5" t="s">
-        <v>672</v>
+        <v>686</v>
+      </c>
+      <c r="E5" t="b">
+        <v>1</v>
       </c>
       <c r="F5" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="G5" t="s">
-        <v>674</v>
-      </c>
-      <c r="H5" t="b">
-        <v>1</v>
-      </c>
-      <c r="I5" t="s">
-        <v>675</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H5" t="s">
+        <v>689</v>
+      </c>
+      <c r="I5" t="b">
+        <v>0</v>
+      </c>
+      <c r="J5" t="s">
+        <v>690</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B6">
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>676</v>
+        <v>691</v>
       </c>
       <c r="D6" t="s">
-        <v>677</v>
-      </c>
-      <c r="E6" t="s">
-        <v>678</v>
+        <v>692</v>
+      </c>
+      <c r="E6" t="b">
+        <v>1</v>
       </c>
       <c r="F6" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G6" t="s">
-        <v>679</v>
-      </c>
-      <c r="H6" t="b">
-        <v>1</v>
-      </c>
-      <c r="I6" t="s">
-        <v>680</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H6" t="s">
+        <v>694</v>
+      </c>
+      <c r="I6" t="b">
+        <v>0</v>
+      </c>
+      <c r="J6" t="s">
+        <v>695</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B7">
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>681</v>
+        <v>696</v>
       </c>
       <c r="D7" t="s">
-        <v>682</v>
-      </c>
-      <c r="E7" t="s">
-        <v>672</v>
+        <v>697</v>
+      </c>
+      <c r="E7" t="b">
+        <v>1</v>
       </c>
       <c r="F7" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="G7" t="s">
-        <v>683</v>
-      </c>
-      <c r="H7" t="b">
-        <v>1</v>
-      </c>
-      <c r="I7" t="s">
-        <v>684</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H7" t="s">
+        <v>698</v>
+      </c>
+      <c r="I7" t="b">
+        <v>1</v>
+      </c>
+      <c r="J7" t="s">
+        <v>699</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B8">
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>685</v>
+        <v>700</v>
       </c>
       <c r="D8" t="s">
-        <v>686</v>
-      </c>
-      <c r="E8" t="s">
-        <v>672</v>
+        <v>701</v>
+      </c>
+      <c r="E8" t="b">
+        <v>1</v>
       </c>
       <c r="F8" t="s">
-        <v>673</v>
+        <v>687</v>
       </c>
       <c r="G8" t="s">
-        <v>687</v>
-      </c>
-      <c r="H8" t="b">
-        <v>1</v>
-      </c>
-      <c r="I8" t="s">
         <v>688</v>
       </c>
-    </row>
-    <row r="9" spans="1:9">
+      <c r="H8" t="s">
+        <v>702</v>
+      </c>
+      <c r="I8" t="b">
+        <v>0</v>
+      </c>
+      <c r="J8" t="s">
+        <v>703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B9">
         <v>1005</v>
       </c>
       <c r="C9" t="s">
-        <v>689</v>
+        <v>704</v>
       </c>
       <c r="D9" t="s">
-        <v>690</v>
-      </c>
-      <c r="E9" t="s">
-        <v>678</v>
+        <v>705</v>
+      </c>
+      <c r="E9" t="b">
+        <v>1</v>
       </c>
       <c r="F9" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G9" t="s">
-        <v>691</v>
-      </c>
-      <c r="H9" t="b">
-        <v>1</v>
-      </c>
-      <c r="I9" t="s">
-        <v>692</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H9" t="s">
+        <v>706</v>
+      </c>
+      <c r="I9" t="b">
+        <v>0</v>
+      </c>
+      <c r="J9" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B10">
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>693</v>
+        <v>708</v>
       </c>
       <c r="D10" t="s">
-        <v>694</v>
-      </c>
-      <c r="E10" t="s">
-        <v>695</v>
+        <v>709</v>
+      </c>
+      <c r="E10" t="b">
+        <v>1</v>
       </c>
       <c r="F10" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G10" t="s">
-        <v>696</v>
-      </c>
-      <c r="H10" t="b">
-        <v>1</v>
-      </c>
-      <c r="I10" t="s">
-        <v>697</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H10" t="s">
+        <v>711</v>
+      </c>
+      <c r="I10" t="b">
+        <v>0</v>
+      </c>
+      <c r="J10" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B11">
         <v>1007</v>
       </c>
       <c r="C11" t="s">
-        <v>698</v>
+        <v>713</v>
       </c>
       <c r="D11" t="s">
-        <v>699</v>
-      </c>
-      <c r="E11" t="s">
-        <v>678</v>
+        <v>714</v>
+      </c>
+      <c r="E11" t="b">
+        <v>1</v>
       </c>
       <c r="F11" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G11" t="s">
-        <v>700</v>
-      </c>
-      <c r="H11" t="b">
-        <v>1</v>
-      </c>
-      <c r="I11" t="s">
-        <v>701</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H11" t="s">
+        <v>715</v>
+      </c>
+      <c r="I11" t="b">
+        <v>0</v>
+      </c>
+      <c r="J11" t="s">
+        <v>716</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B12">
         <v>1008</v>
       </c>
       <c r="C12" t="s">
-        <v>702</v>
+        <v>717</v>
       </c>
       <c r="D12" t="s">
-        <v>703</v>
-      </c>
-      <c r="E12" t="s">
-        <v>678</v>
+        <v>718</v>
+      </c>
+      <c r="E12" t="b">
+        <v>1</v>
       </c>
       <c r="F12" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G12" t="s">
-        <v>704</v>
-      </c>
-      <c r="H12" t="b">
-        <v>1</v>
-      </c>
-      <c r="I12" t="s">
-        <v>705</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H12" t="s">
+        <v>719</v>
+      </c>
+      <c r="I12" t="b">
+        <v>0</v>
+      </c>
+      <c r="J12" t="s">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B13">
         <v>1009</v>
       </c>
       <c r="C13" t="s">
-        <v>706</v>
+        <v>721</v>
       </c>
       <c r="D13" t="s">
-        <v>707</v>
-      </c>
-      <c r="E13" t="s">
-        <v>678</v>
+        <v>722</v>
+      </c>
+      <c r="E13" t="b">
+        <v>1</v>
       </c>
       <c r="F13" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G13" t="s">
-        <v>708</v>
-      </c>
-      <c r="H13" t="b">
-        <v>1</v>
-      </c>
-      <c r="I13" t="s">
-        <v>709</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H13" t="s">
+        <v>723</v>
+      </c>
+      <c r="I13" t="b">
+        <v>0</v>
+      </c>
+      <c r="J13" t="s">
+        <v>724</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B14">
         <v>1010</v>
       </c>
       <c r="C14" t="s">
+        <v>725</v>
+      </c>
+      <c r="D14" t="s">
+        <v>726</v>
+      </c>
+      <c r="E14" t="b">
+        <v>1</v>
+      </c>
+      <c r="F14" t="s">
         <v>710</v>
       </c>
-      <c r="D14" t="s">
-        <v>711</v>
-      </c>
-      <c r="E14" t="s">
-        <v>695</v>
-      </c>
-      <c r="F14" t="s">
-        <v>673</v>
-      </c>
       <c r="G14" t="s">
-        <v>712</v>
-      </c>
-      <c r="H14" t="b">
-        <v>1</v>
-      </c>
-      <c r="I14" t="s">
-        <v>713</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H14" t="s">
+        <v>727</v>
+      </c>
+      <c r="I14" t="b">
+        <v>0</v>
+      </c>
+      <c r="J14" t="s">
+        <v>728</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B15">
         <v>1011</v>
       </c>
       <c r="C15" t="s">
-        <v>714</v>
+        <v>729</v>
       </c>
       <c r="D15" t="s">
-        <v>715</v>
-      </c>
-      <c r="E15" t="s">
-        <v>695</v>
+        <v>730</v>
+      </c>
+      <c r="E15" t="b">
+        <v>1</v>
       </c>
       <c r="F15" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G15" t="s">
-        <v>716</v>
-      </c>
-      <c r="H15" t="b">
-        <v>1</v>
-      </c>
-      <c r="I15" t="s">
-        <v>717</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H15" t="s">
+        <v>731</v>
+      </c>
+      <c r="I15" t="b">
+        <v>0</v>
+      </c>
+      <c r="J15" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B16">
         <v>1012</v>
       </c>
       <c r="C16" t="s">
-        <v>718</v>
+        <v>733</v>
       </c>
       <c r="D16" t="s">
-        <v>719</v>
-      </c>
-      <c r="E16" t="s">
-        <v>678</v>
+        <v>734</v>
+      </c>
+      <c r="E16" t="b">
+        <v>1</v>
       </c>
       <c r="F16" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G16" t="s">
-        <v>720</v>
-      </c>
-      <c r="H16" t="b">
-        <v>1</v>
-      </c>
-      <c r="I16" t="s">
-        <v>721</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H16" t="s">
+        <v>735</v>
+      </c>
+      <c r="I16" t="b">
+        <v>0</v>
+      </c>
+      <c r="J16" t="s">
+        <v>736</v>
+      </c>
+    </row>
+    <row r="17" spans="1:10">
       <c r="A17" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B17">
         <v>1013</v>
       </c>
       <c r="C17" t="s">
-        <v>722</v>
+        <v>737</v>
       </c>
       <c r="D17" t="s">
-        <v>723</v>
-      </c>
-      <c r="E17" t="s">
-        <v>678</v>
+        <v>738</v>
+      </c>
+      <c r="E17" t="b">
+        <v>1</v>
       </c>
       <c r="F17" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G17" t="s">
-        <v>724</v>
-      </c>
-      <c r="H17" t="b">
-        <v>1</v>
-      </c>
-      <c r="I17" t="s">
-        <v>725</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H17" t="s">
+        <v>739</v>
+      </c>
+      <c r="I17" t="b">
+        <v>0</v>
+      </c>
+      <c r="J17" t="s">
+        <v>740</v>
+      </c>
+    </row>
+    <row r="18" spans="1:10">
       <c r="A18" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B18">
         <v>1014</v>
       </c>
       <c r="C18" t="s">
-        <v>726</v>
+        <v>741</v>
       </c>
       <c r="D18" t="s">
-        <v>727</v>
-      </c>
-      <c r="E18" t="s">
-        <v>678</v>
+        <v>742</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
       </c>
       <c r="F18" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G18" t="s">
-        <v>728</v>
-      </c>
-      <c r="H18" t="b">
-        <v>1</v>
-      </c>
-      <c r="I18" t="s">
-        <v>729</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H18" t="s">
+        <v>743</v>
+      </c>
+      <c r="I18" t="b">
+        <v>0</v>
+      </c>
+      <c r="J18" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="19" spans="1:10">
       <c r="A19" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B19">
         <v>1015</v>
       </c>
       <c r="C19" t="s">
-        <v>516</v>
+        <v>530</v>
       </c>
       <c r="D19" t="s">
-        <v>730</v>
-      </c>
-      <c r="E19" t="s">
-        <v>678</v>
+        <v>745</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
       </c>
       <c r="F19" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G19" t="s">
-        <v>731</v>
-      </c>
-      <c r="H19" t="b">
-        <v>1</v>
-      </c>
-      <c r="I19" t="s">
-        <v>732</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H19" t="s">
+        <v>746</v>
+      </c>
+      <c r="I19" t="b">
+        <v>0</v>
+      </c>
+      <c r="J19" t="s">
+        <v>747</v>
+      </c>
+    </row>
+    <row r="20" spans="1:10">
       <c r="A20" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B20">
         <v>1016</v>
       </c>
       <c r="C20" t="s">
-        <v>524</v>
+        <v>538</v>
       </c>
       <c r="D20" t="s">
-        <v>733</v>
-      </c>
-      <c r="E20" t="s">
-        <v>678</v>
+        <v>748</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
       </c>
       <c r="F20" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G20" t="s">
-        <v>734</v>
-      </c>
-      <c r="H20" t="b">
-        <v>1</v>
-      </c>
-      <c r="I20" t="s">
-        <v>735</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H20" t="s">
+        <v>749</v>
+      </c>
+      <c r="I20" t="b">
+        <v>0</v>
+      </c>
+      <c r="J20" t="s">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="21" spans="1:10">
       <c r="A21" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B21">
         <v>1017</v>
       </c>
       <c r="C21" t="s">
-        <v>532</v>
+        <v>546</v>
       </c>
       <c r="D21" t="s">
-        <v>736</v>
-      </c>
-      <c r="E21" t="s">
-        <v>678</v>
+        <v>751</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
       </c>
       <c r="F21" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G21" t="s">
-        <v>737</v>
-      </c>
-      <c r="H21" t="b">
-        <v>1</v>
-      </c>
-      <c r="I21" t="s">
-        <v>738</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H21" t="s">
+        <v>752</v>
+      </c>
+      <c r="I21" t="b">
+        <v>0</v>
+      </c>
+      <c r="J21" t="s">
+        <v>753</v>
+      </c>
+    </row>
+    <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B22">
         <v>1018</v>
       </c>
       <c r="C22" t="s">
-        <v>540</v>
+        <v>554</v>
       </c>
       <c r="D22" t="s">
-        <v>739</v>
-      </c>
-      <c r="E22" t="s">
-        <v>678</v>
+        <v>754</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
       </c>
       <c r="F22" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G22" t="s">
-        <v>740</v>
-      </c>
-      <c r="H22" t="b">
-        <v>1</v>
-      </c>
-      <c r="I22" t="s">
-        <v>741</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H22" t="s">
+        <v>755</v>
+      </c>
+      <c r="I22" t="b">
+        <v>0</v>
+      </c>
+      <c r="J22" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B23">
         <v>1019</v>
       </c>
       <c r="C23" t="s">
-        <v>548</v>
+        <v>562</v>
       </c>
       <c r="D23" t="s">
-        <v>742</v>
-      </c>
-      <c r="E23" t="s">
-        <v>678</v>
+        <v>757</v>
+      </c>
+      <c r="E23" t="b">
+        <v>1</v>
       </c>
       <c r="F23" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G23" t="s">
-        <v>743</v>
-      </c>
-      <c r="H23" t="b">
-        <v>1</v>
-      </c>
-      <c r="I23" t="s">
-        <v>744</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H23" t="s">
+        <v>758</v>
+      </c>
+      <c r="I23" t="b">
+        <v>0</v>
+      </c>
+      <c r="J23" t="s">
+        <v>759</v>
+      </c>
+    </row>
+    <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B24">
         <v>1020</v>
       </c>
       <c r="C24" t="s">
-        <v>556</v>
+        <v>570</v>
       </c>
       <c r="D24" t="s">
-        <v>745</v>
-      </c>
-      <c r="E24" t="s">
-        <v>678</v>
+        <v>760</v>
+      </c>
+      <c r="E24" t="b">
+        <v>1</v>
       </c>
       <c r="F24" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G24" t="s">
-        <v>746</v>
-      </c>
-      <c r="H24" t="b">
-        <v>1</v>
-      </c>
-      <c r="I24" t="s">
-        <v>747</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H24" t="s">
+        <v>761</v>
+      </c>
+      <c r="I24" t="b">
+        <v>0</v>
+      </c>
+      <c r="J24" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B25">
         <v>1021</v>
       </c>
       <c r="C25" t="s">
-        <v>564</v>
+        <v>578</v>
       </c>
       <c r="D25" t="s">
-        <v>748</v>
-      </c>
-      <c r="E25" t="s">
-        <v>678</v>
+        <v>763</v>
+      </c>
+      <c r="E25" t="b">
+        <v>1</v>
       </c>
       <c r="F25" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G25" t="s">
-        <v>749</v>
-      </c>
-      <c r="H25" t="b">
-        <v>1</v>
-      </c>
-      <c r="I25" t="s">
-        <v>750</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H25" t="s">
+        <v>764</v>
+      </c>
+      <c r="I25" t="b">
+        <v>0</v>
+      </c>
+      <c r="J25" t="s">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B26">
         <v>1022</v>
       </c>
       <c r="C26" t="s">
-        <v>751</v>
+        <v>766</v>
       </c>
       <c r="D26" t="s">
-        <v>752</v>
-      </c>
-      <c r="E26" t="s">
-        <v>678</v>
+        <v>767</v>
+      </c>
+      <c r="E26" t="b">
+        <v>1</v>
       </c>
       <c r="F26" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G26" t="s">
-        <v>753</v>
-      </c>
-      <c r="H26" t="b">
-        <v>1</v>
-      </c>
-      <c r="I26" t="s">
-        <v>754</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H26" t="s">
+        <v>768</v>
+      </c>
+      <c r="I26" t="b">
+        <v>0</v>
+      </c>
+      <c r="J26" t="s">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B27">
         <v>1030</v>
       </c>
       <c r="C27" t="s">
-        <v>755</v>
+        <v>770</v>
       </c>
       <c r="D27" t="s">
-        <v>756</v>
-      </c>
-      <c r="E27" t="s">
-        <v>695</v>
+        <v>771</v>
+      </c>
+      <c r="E27" t="b">
+        <v>1</v>
       </c>
       <c r="F27" t="s">
-        <v>673</v>
+        <v>710</v>
       </c>
       <c r="G27" t="s">
-        <v>757</v>
-      </c>
-      <c r="H27" t="b">
-        <v>1</v>
-      </c>
-      <c r="I27" t="s">
-        <v>758</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H27" t="s">
+        <v>772</v>
+      </c>
+      <c r="I27" t="b">
+        <v>0</v>
+      </c>
+      <c r="J27" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B28">
         <v>1023</v>
       </c>
       <c r="C28" t="s">
-        <v>759</v>
+        <v>774</v>
       </c>
       <c r="D28" t="s">
-        <v>760</v>
-      </c>
-      <c r="E28" t="s">
-        <v>678</v>
+        <v>775</v>
+      </c>
+      <c r="E28" t="b">
+        <v>1</v>
       </c>
       <c r="F28" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G28" t="s">
-        <v>761</v>
-      </c>
-      <c r="H28" t="b">
-        <v>1</v>
-      </c>
-      <c r="I28" t="s">
-        <v>762</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H28" t="s">
+        <v>776</v>
+      </c>
+      <c r="I28" t="b">
+        <v>0</v>
+      </c>
+      <c r="J28" t="s">
+        <v>777</v>
+      </c>
+    </row>
+    <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B29">
         <v>1024</v>
       </c>
       <c r="C29" t="s">
-        <v>763</v>
+        <v>778</v>
       </c>
       <c r="D29" t="s">
-        <v>764</v>
-      </c>
-      <c r="E29" t="s">
-        <v>678</v>
+        <v>779</v>
+      </c>
+      <c r="E29" t="b">
+        <v>1</v>
       </c>
       <c r="F29" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G29" t="s">
-        <v>765</v>
-      </c>
-      <c r="H29" t="b">
-        <v>1</v>
-      </c>
-      <c r="I29" t="s">
-        <v>766</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H29" t="s">
+        <v>780</v>
+      </c>
+      <c r="I29" t="b">
+        <v>0</v>
+      </c>
+      <c r="J29" t="s">
+        <v>781</v>
+      </c>
+    </row>
+    <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B30">
         <v>1025</v>
       </c>
       <c r="C30" t="s">
-        <v>767</v>
+        <v>782</v>
       </c>
       <c r="D30" t="s">
-        <v>768</v>
-      </c>
-      <c r="E30" t="s">
-        <v>678</v>
+        <v>783</v>
+      </c>
+      <c r="E30" t="b">
+        <v>1</v>
       </c>
       <c r="F30" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G30" t="s">
-        <v>769</v>
-      </c>
-      <c r="H30" t="b">
-        <v>1</v>
-      </c>
-      <c r="I30" t="s">
-        <v>770</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H30" t="s">
+        <v>784</v>
+      </c>
+      <c r="I30" t="b">
+        <v>0</v>
+      </c>
+      <c r="J30" t="s">
+        <v>785</v>
+      </c>
+    </row>
+    <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B31">
         <v>1026</v>
       </c>
       <c r="C31" t="s">
-        <v>771</v>
+        <v>786</v>
       </c>
       <c r="D31" t="s">
-        <v>772</v>
-      </c>
-      <c r="E31" t="s">
-        <v>678</v>
+        <v>787</v>
+      </c>
+      <c r="E31" t="b">
+        <v>1</v>
       </c>
       <c r="F31" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G31" t="s">
-        <v>773</v>
-      </c>
-      <c r="H31" t="b">
-        <v>1</v>
-      </c>
-      <c r="I31" t="s">
-        <v>774</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H31" t="s">
+        <v>788</v>
+      </c>
+      <c r="I31" t="b">
+        <v>0</v>
+      </c>
+      <c r="J31" t="s">
+        <v>789</v>
+      </c>
+    </row>
+    <row r="32" spans="1:10">
       <c r="A32" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B32">
         <v>1031</v>
       </c>
       <c r="C32" t="s">
-        <v>775</v>
+        <v>790</v>
       </c>
       <c r="D32" t="s">
-        <v>776</v>
-      </c>
-      <c r="E32" t="s">
-        <v>678</v>
+        <v>791</v>
+      </c>
+      <c r="E32" t="b">
+        <v>1</v>
       </c>
       <c r="F32" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G32" t="s">
-        <v>777</v>
-      </c>
-      <c r="H32" t="b">
-        <v>1</v>
-      </c>
-      <c r="I32" t="s">
-        <v>778</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H32" t="s">
+        <v>792</v>
+      </c>
+      <c r="I32" t="b">
+        <v>0</v>
+      </c>
+      <c r="J32" t="s">
+        <v>793</v>
+      </c>
+    </row>
+    <row r="33" spans="1:10">
       <c r="A33" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B33">
         <v>1032</v>
       </c>
       <c r="C33" t="s">
-        <v>779</v>
+        <v>794</v>
       </c>
       <c r="D33" t="s">
-        <v>780</v>
-      </c>
-      <c r="E33" t="s">
-        <v>678</v>
+        <v>795</v>
+      </c>
+      <c r="E33" t="b">
+        <v>1</v>
       </c>
       <c r="F33" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G33" t="s">
-        <v>781</v>
-      </c>
-      <c r="H33" t="b">
-        <v>1</v>
-      </c>
-      <c r="I33" t="s">
-        <v>782</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H33" t="s">
+        <v>796</v>
+      </c>
+      <c r="I33" t="b">
+        <v>0</v>
+      </c>
+      <c r="J33" t="s">
+        <v>797</v>
+      </c>
+    </row>
+    <row r="34" spans="1:10">
       <c r="A34" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B34">
         <v>1033</v>
       </c>
       <c r="C34" t="s">
-        <v>783</v>
+        <v>798</v>
       </c>
       <c r="D34" t="s">
-        <v>784</v>
-      </c>
-      <c r="E34" t="s">
-        <v>678</v>
+        <v>799</v>
+      </c>
+      <c r="E34" t="b">
+        <v>1</v>
       </c>
       <c r="F34" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G34" t="s">
-        <v>785</v>
-      </c>
-      <c r="H34" t="b">
-        <v>1</v>
-      </c>
-      <c r="I34" t="s">
-        <v>786</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H34" t="s">
+        <v>800</v>
+      </c>
+      <c r="I34" t="b">
+        <v>0</v>
+      </c>
+      <c r="J34" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="35" spans="1:10">
       <c r="A35" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B35">
         <v>1034</v>
       </c>
       <c r="C35" t="s">
-        <v>787</v>
+        <v>802</v>
       </c>
       <c r="D35" t="s">
-        <v>788</v>
-      </c>
-      <c r="E35" t="s">
-        <v>678</v>
+        <v>803</v>
+      </c>
+      <c r="E35" t="b">
+        <v>1</v>
       </c>
       <c r="F35" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G35" t="s">
-        <v>789</v>
-      </c>
-      <c r="H35" t="b">
-        <v>1</v>
-      </c>
-      <c r="I35" t="s">
-        <v>790</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H35" t="s">
+        <v>804</v>
+      </c>
+      <c r="I35" t="b">
+        <v>0</v>
+      </c>
+      <c r="J35" t="s">
+        <v>805</v>
+      </c>
+    </row>
+    <row r="36" spans="1:10">
       <c r="A36" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B36">
         <v>1035</v>
       </c>
       <c r="C36" t="s">
-        <v>791</v>
+        <v>806</v>
       </c>
       <c r="D36" t="s">
-        <v>792</v>
-      </c>
-      <c r="E36" t="s">
-        <v>678</v>
+        <v>807</v>
+      </c>
+      <c r="E36" t="b">
+        <v>1</v>
       </c>
       <c r="F36" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G36" t="s">
-        <v>793</v>
-      </c>
-      <c r="H36" t="b">
-        <v>1</v>
-      </c>
-      <c r="I36" t="s">
-        <v>794</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H36" t="s">
+        <v>808</v>
+      </c>
+      <c r="I36" t="b">
+        <v>0</v>
+      </c>
+      <c r="J36" t="s">
+        <v>809</v>
+      </c>
+    </row>
+    <row r="37" spans="1:10">
       <c r="A37" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B37">
         <v>1036</v>
       </c>
       <c r="C37" t="s">
-        <v>795</v>
+        <v>810</v>
       </c>
       <c r="D37" t="s">
-        <v>796</v>
-      </c>
-      <c r="E37" t="s">
-        <v>678</v>
+        <v>811</v>
+      </c>
+      <c r="E37" t="b">
+        <v>1</v>
       </c>
       <c r="F37" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G37" t="s">
-        <v>797</v>
-      </c>
-      <c r="H37" t="b">
-        <v>1</v>
-      </c>
-      <c r="I37" t="s">
-        <v>798</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H37" t="s">
+        <v>812</v>
+      </c>
+      <c r="I37" t="b">
+        <v>0</v>
+      </c>
+      <c r="J37" t="s">
+        <v>813</v>
+      </c>
+    </row>
+    <row r="38" spans="1:10">
       <c r="A38" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B38">
         <v>1037</v>
       </c>
       <c r="C38" t="s">
-        <v>799</v>
+        <v>814</v>
       </c>
       <c r="D38" t="s">
-        <v>800</v>
-      </c>
-      <c r="E38" t="s">
-        <v>678</v>
+        <v>815</v>
+      </c>
+      <c r="E38" t="b">
+        <v>1</v>
       </c>
       <c r="F38" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G38" t="s">
-        <v>801</v>
-      </c>
-      <c r="H38" t="b">
-        <v>1</v>
-      </c>
-      <c r="I38" t="s">
-        <v>802</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H38" t="s">
+        <v>816</v>
+      </c>
+      <c r="I38" t="b">
+        <v>0</v>
+      </c>
+      <c r="J38" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="39" spans="1:10">
       <c r="A39" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B39">
         <v>1038</v>
       </c>
       <c r="C39" t="s">
-        <v>803</v>
+        <v>818</v>
       </c>
       <c r="D39" t="s">
-        <v>804</v>
-      </c>
-      <c r="E39" t="s">
-        <v>678</v>
+        <v>819</v>
+      </c>
+      <c r="E39" t="b">
+        <v>1</v>
       </c>
       <c r="F39" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G39" t="s">
-        <v>805</v>
-      </c>
-      <c r="H39" t="b">
-        <v>1</v>
-      </c>
-      <c r="I39" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H39" t="s">
+        <v>820</v>
+      </c>
+      <c r="I39" t="b">
+        <v>0</v>
+      </c>
+      <c r="J39" t="s">
+        <v>821</v>
+      </c>
+    </row>
+    <row r="40" spans="1:10">
       <c r="A40" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B40">
         <v>1039</v>
       </c>
       <c r="C40" t="s">
-        <v>807</v>
+        <v>822</v>
       </c>
       <c r="D40" t="s">
-        <v>808</v>
-      </c>
-      <c r="E40" t="s">
-        <v>678</v>
+        <v>823</v>
+      </c>
+      <c r="E40" t="b">
+        <v>1</v>
       </c>
       <c r="F40" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G40" t="s">
-        <v>809</v>
-      </c>
-      <c r="H40" t="b">
-        <v>1</v>
-      </c>
-      <c r="I40" t="s">
-        <v>810</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H40" t="s">
+        <v>824</v>
+      </c>
+      <c r="I40" t="b">
+        <v>0</v>
+      </c>
+      <c r="J40" t="s">
+        <v>825</v>
+      </c>
+    </row>
+    <row r="41" spans="1:10">
       <c r="A41" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B41">
         <v>1040</v>
       </c>
       <c r="C41" t="s">
-        <v>811</v>
+        <v>826</v>
       </c>
       <c r="D41" t="s">
-        <v>812</v>
-      </c>
-      <c r="E41" t="s">
-        <v>678</v>
+        <v>827</v>
+      </c>
+      <c r="E41" t="b">
+        <v>0</v>
       </c>
       <c r="F41" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G41" t="s">
-        <v>813</v>
-      </c>
-      <c r="H41" t="b">
-        <v>1</v>
-      </c>
-      <c r="I41" t="s">
-        <v>814</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H41" t="s">
+        <v>828</v>
+      </c>
+      <c r="I41" t="b">
+        <v>0</v>
+      </c>
+      <c r="J41" t="s">
+        <v>829</v>
+      </c>
+    </row>
+    <row r="42" spans="1:10">
       <c r="A42" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B42">
         <v>1041</v>
       </c>
       <c r="C42" t="s">
-        <v>815</v>
+        <v>830</v>
       </c>
       <c r="D42" t="s">
-        <v>816</v>
-      </c>
-      <c r="E42" t="s">
-        <v>678</v>
+        <v>831</v>
+      </c>
+      <c r="E42" t="b">
+        <v>1</v>
       </c>
       <c r="F42" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G42" t="s">
-        <v>817</v>
-      </c>
-      <c r="H42" t="b">
-        <v>1</v>
-      </c>
-      <c r="I42" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H42" t="s">
+        <v>832</v>
+      </c>
+      <c r="I42" t="b">
+        <v>0</v>
+      </c>
+      <c r="J42" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="43" spans="1:10">
       <c r="A43" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B43">
         <v>1042</v>
       </c>
       <c r="C43" t="s">
-        <v>819</v>
+        <v>834</v>
       </c>
       <c r="D43" t="s">
-        <v>820</v>
-      </c>
-      <c r="E43" t="s">
-        <v>678</v>
+        <v>835</v>
+      </c>
+      <c r="E43" t="b">
+        <v>1</v>
       </c>
       <c r="F43" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G43" t="s">
-        <v>821</v>
-      </c>
-      <c r="H43" t="b">
-        <v>1</v>
-      </c>
-      <c r="I43" t="s">
-        <v>822</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H43" t="s">
+        <v>836</v>
+      </c>
+      <c r="I43" t="b">
+        <v>0</v>
+      </c>
+      <c r="J43" t="s">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="44" spans="1:10">
       <c r="A44" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B44">
         <v>1043</v>
       </c>
       <c r="C44" t="s">
-        <v>823</v>
+        <v>838</v>
       </c>
       <c r="D44" t="s">
-        <v>824</v>
-      </c>
-      <c r="E44" t="s">
-        <v>678</v>
+        <v>839</v>
+      </c>
+      <c r="E44" t="b">
+        <v>1</v>
       </c>
       <c r="F44" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G44" t="s">
-        <v>825</v>
-      </c>
-      <c r="H44" t="b">
-        <v>1</v>
-      </c>
-      <c r="I44" t="s">
-        <v>826</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H44" t="s">
+        <v>840</v>
+      </c>
+      <c r="I44" t="b">
+        <v>0</v>
+      </c>
+      <c r="J44" t="s">
+        <v>841</v>
+      </c>
+    </row>
+    <row r="45" spans="1:10">
       <c r="A45" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B45">
         <v>1044</v>
       </c>
       <c r="C45" t="s">
-        <v>827</v>
+        <v>842</v>
       </c>
       <c r="D45" t="s">
-        <v>828</v>
-      </c>
-      <c r="E45" t="s">
-        <v>678</v>
+        <v>843</v>
+      </c>
+      <c r="E45" t="b">
+        <v>1</v>
       </c>
       <c r="F45" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G45" t="s">
-        <v>829</v>
-      </c>
-      <c r="H45" t="b">
-        <v>1</v>
-      </c>
-      <c r="I45" t="s">
-        <v>830</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H45" t="s">
+        <v>844</v>
+      </c>
+      <c r="I45" t="b">
+        <v>0</v>
+      </c>
+      <c r="J45" t="s">
+        <v>845</v>
+      </c>
+    </row>
+    <row r="46" spans="1:10">
       <c r="A46" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B46">
         <v>1045</v>
       </c>
       <c r="C46" t="s">
-        <v>831</v>
+        <v>846</v>
       </c>
       <c r="D46" t="s">
-        <v>832</v>
-      </c>
-      <c r="E46" t="s">
-        <v>678</v>
+        <v>847</v>
+      </c>
+      <c r="E46" t="b">
+        <v>1</v>
       </c>
       <c r="F46" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G46" t="s">
-        <v>833</v>
-      </c>
-      <c r="H46" t="b">
-        <v>1</v>
-      </c>
-      <c r="I46" t="s">
-        <v>834</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H46" t="s">
+        <v>848</v>
+      </c>
+      <c r="I46" t="b">
+        <v>0</v>
+      </c>
+      <c r="J46" t="s">
+        <v>849</v>
+      </c>
+    </row>
+    <row r="47" spans="1:10">
       <c r="A47" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B47">
         <v>1046</v>
       </c>
       <c r="C47" t="s">
-        <v>835</v>
+        <v>850</v>
       </c>
       <c r="D47" t="s">
-        <v>836</v>
-      </c>
-      <c r="E47" t="s">
-        <v>678</v>
+        <v>851</v>
+      </c>
+      <c r="E47" t="b">
+        <v>1</v>
       </c>
       <c r="F47" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G47" t="s">
-        <v>837</v>
-      </c>
-      <c r="H47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I47" t="s">
-        <v>838</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H47" t="s">
+        <v>852</v>
+      </c>
+      <c r="I47" t="b">
+        <v>0</v>
+      </c>
+      <c r="J47" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="48" spans="1:10">
       <c r="A48" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B48">
         <v>1047</v>
       </c>
       <c r="C48" t="s">
-        <v>839</v>
+        <v>854</v>
       </c>
       <c r="D48" t="s">
-        <v>840</v>
-      </c>
-      <c r="E48" t="s">
-        <v>678</v>
+        <v>855</v>
+      </c>
+      <c r="E48" t="b">
+        <v>1</v>
       </c>
       <c r="F48" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G48" t="s">
-        <v>841</v>
-      </c>
-      <c r="H48" t="b">
-        <v>1</v>
-      </c>
-      <c r="I48" t="s">
-        <v>842</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H48" t="s">
+        <v>856</v>
+      </c>
+      <c r="I48" t="b">
+        <v>0</v>
+      </c>
+      <c r="J48" t="s">
+        <v>857</v>
+      </c>
+    </row>
+    <row r="49" spans="1:10">
       <c r="A49" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B49">
         <v>1048</v>
       </c>
       <c r="C49" t="s">
-        <v>843</v>
+        <v>858</v>
       </c>
       <c r="D49" t="s">
-        <v>844</v>
-      </c>
-      <c r="E49" t="s">
-        <v>678</v>
+        <v>859</v>
+      </c>
+      <c r="E49" t="b">
+        <v>1</v>
       </c>
       <c r="F49" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G49" t="s">
-        <v>845</v>
-      </c>
-      <c r="H49" t="b">
-        <v>1</v>
-      </c>
-      <c r="I49" t="s">
-        <v>846</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H49" t="s">
+        <v>860</v>
+      </c>
+      <c r="I49" t="b">
+        <v>0</v>
+      </c>
+      <c r="J49" t="s">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="50" spans="1:10">
       <c r="B50">
         <v>1049</v>
       </c>
       <c r="C50" t="s">
-        <v>847</v>
+        <v>862</v>
       </c>
       <c r="D50" t="s">
-        <v>848</v>
-      </c>
-      <c r="E50" t="s">
-        <v>678</v>
+        <v>863</v>
+      </c>
+      <c r="E50" t="b">
+        <v>1</v>
       </c>
       <c r="F50" t="s">
-        <v>673</v>
+        <v>693</v>
       </c>
       <c r="G50" t="s">
-        <v>849</v>
-      </c>
-      <c r="H50" t="b">
-        <v>1</v>
-      </c>
-      <c r="I50" t="s">
-        <v>850</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9">
+        <v>688</v>
+      </c>
+      <c r="H50" t="s">
+        <v>864</v>
+      </c>
+      <c r="I50" t="b">
+        <v>0</v>
+      </c>
+      <c r="J50" t="s">
+        <v>865</v>
+      </c>
+    </row>
+    <row r="51" spans="1:10">
       <c r="B51">
         <v>1050</v>
       </c>
       <c r="C51" t="s">
-        <v>851</v>
+        <v>866</v>
       </c>
       <c r="D51" t="s">
-        <v>852</v>
-      </c>
-      <c r="E51" t="s">
-        <v>695</v>
+        <v>867</v>
+      </c>
+      <c r="E51" t="b">
+        <v>1</v>
       </c>
       <c r="F51" t="s">
-        <v>853</v>
+        <v>710</v>
       </c>
       <c r="G51" t="s">
-        <v>854</v>
-      </c>
-      <c r="H51" t="b">
-        <v>1</v>
-      </c>
-      <c r="I51" t="s">
-        <v>855</v>
+        <v>868</v>
+      </c>
+      <c r="H51" t="s">
+        <v>869</v>
+      </c>
+      <c r="I51" t="b">
+        <v>0</v>
+      </c>
+      <c r="J51" t="s">
+        <v>870</v>
+      </c>
+    </row>
+    <row r="52" spans="1:10">
+      <c r="B52">
+        <v>1051</v>
+      </c>
+      <c r="C52" t="s">
+        <v>871</v>
+      </c>
+      <c r="D52" t="s">
+        <v>872</v>
+      </c>
+      <c r="E52" t="b">
+        <v>1</v>
+      </c>
+      <c r="F52" t="s">
+        <v>873</v>
+      </c>
+      <c r="G52" t="s">
+        <v>873</v>
+      </c>
+      <c r="H52" t="s">
+        <v>874</v>
+      </c>
+      <c r="I52" t="b">
+        <v>1</v>
+      </c>
+      <c r="J52" t="s">
+        <v>875</v>
+      </c>
+    </row>
+    <row r="53" spans="1:10">
+      <c r="B53">
+        <v>1052</v>
+      </c>
+      <c r="C53" t="s">
+        <v>876</v>
+      </c>
+      <c r="D53" t="s">
+        <v>877</v>
+      </c>
+      <c r="E53" t="b">
+        <v>1</v>
+      </c>
+      <c r="F53" t="s">
+        <v>873</v>
+      </c>
+      <c r="G53" t="s">
+        <v>873</v>
+      </c>
+      <c r="H53" t="s">
+        <v>878</v>
+      </c>
+      <c r="I53" t="b">
+        <v>1</v>
+      </c>
+      <c r="J53" t="s">
+        <v>879</v>
+      </c>
+    </row>
+    <row r="54" spans="1:10">
+      <c r="B54">
+        <v>1053</v>
+      </c>
+      <c r="C54" t="s">
+        <v>880</v>
+      </c>
+      <c r="D54" t="s">
+        <v>881</v>
+      </c>
+      <c r="E54" t="b">
+        <v>1</v>
+      </c>
+      <c r="F54" t="s">
+        <v>873</v>
+      </c>
+      <c r="G54" t="s">
+        <v>873</v>
+      </c>
+      <c r="H54" t="s">
+        <v>882</v>
+      </c>
+      <c r="I54" t="b">
+        <v>1</v>
+      </c>
+      <c r="J54" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="55" spans="1:10">
+      <c r="B55">
+        <v>1054</v>
+      </c>
+      <c r="C55" t="s">
+        <v>884</v>
+      </c>
+      <c r="D55" t="s">
+        <v>885</v>
+      </c>
+      <c r="E55" t="b">
+        <v>1</v>
+      </c>
+      <c r="F55" t="s">
+        <v>873</v>
+      </c>
+      <c r="G55" t="s">
+        <v>873</v>
+      </c>
+      <c r="H55" t="s">
+        <v>886</v>
+      </c>
+      <c r="I55" t="b">
+        <v>1</v>
+      </c>
+      <c r="J55" t="s">
+        <v>887</v>
+      </c>
+    </row>
+    <row r="56" spans="1:10">
+      <c r="B56">
+        <v>1055</v>
+      </c>
+      <c r="C56" t="s">
+        <v>888</v>
+      </c>
+      <c r="D56" t="s">
+        <v>889</v>
+      </c>
+      <c r="E56" t="b">
+        <v>1</v>
+      </c>
+      <c r="F56" t="s">
+        <v>873</v>
+      </c>
+      <c r="G56" t="s">
+        <v>873</v>
+      </c>
+      <c r="H56" t="s">
+        <v>890</v>
+      </c>
+      <c r="I56" t="b">
+        <v>1</v>
+      </c>
+      <c r="J56" t="s">
+        <v>891</v>
+      </c>
+    </row>
+    <row r="57" spans="1:10">
+      <c r="B57">
+        <v>1056</v>
+      </c>
+      <c r="C57" t="s">
+        <v>892</v>
+      </c>
+      <c r="D57" t="s">
+        <v>893</v>
+      </c>
+      <c r="E57" t="b">
+        <v>1</v>
+      </c>
+      <c r="F57" t="s">
+        <v>687</v>
+      </c>
+      <c r="G57" t="s">
+        <v>688</v>
+      </c>
+      <c r="H57" t="s">
+        <v>894</v>
+      </c>
+      <c r="I57" t="b">
+        <v>1</v>
+      </c>
+      <c r="J57" t="s">
+        <v>895</v>
+      </c>
+    </row>
+    <row r="58" spans="1:10">
+      <c r="B58">
+        <v>1057</v>
+      </c>
+      <c r="C58" t="s">
+        <v>896</v>
+      </c>
+      <c r="D58" t="s">
+        <v>897</v>
+      </c>
+      <c r="E58" t="b">
+        <v>1</v>
+      </c>
+      <c r="F58" t="s">
+        <v>693</v>
+      </c>
+      <c r="G58" t="s">
+        <v>688</v>
+      </c>
+      <c r="H58" t="s">
+        <v>898</v>
+      </c>
+      <c r="I58" t="b">
+        <v>1</v>
+      </c>
+      <c r="J58" t="s">
+        <v>899</v>
+      </c>
+    </row>
+    <row r="59" spans="1:10">
+      <c r="B59">
+        <v>1058</v>
+      </c>
+      <c r="C59" t="s">
+        <v>900</v>
+      </c>
+      <c r="D59" t="s">
+        <v>901</v>
+      </c>
+      <c r="E59" t="b">
+        <v>1</v>
+      </c>
+      <c r="F59" t="s">
+        <v>873</v>
+      </c>
+      <c r="G59" t="s">
+        <v>873</v>
+      </c>
+      <c r="H59" t="s">
+        <v>902</v>
+      </c>
+      <c r="I59" t="b">
+        <v>1</v>
+      </c>
+      <c r="J59" t="s">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="60" spans="1:10">
+      <c r="B60">
+        <v>1059</v>
+      </c>
+      <c r="C60" t="s">
+        <v>904</v>
+      </c>
+      <c r="D60" t="s">
+        <v>905</v>
+      </c>
+      <c r="E60" t="b">
+        <v>1</v>
+      </c>
+      <c r="F60" t="s">
+        <v>873</v>
+      </c>
+      <c r="G60" t="s">
+        <v>873</v>
+      </c>
+      <c r="H60" t="s">
+        <v>906</v>
+      </c>
+      <c r="I60" t="b">
+        <v>1</v>
+      </c>
+      <c r="J60" t="s">
+        <v>907</v>
+      </c>
+    </row>
+    <row r="61" spans="1:10">
+      <c r="B61">
+        <v>1060</v>
+      </c>
+      <c r="C61" t="s">
+        <v>908</v>
+      </c>
+      <c r="D61" t="s">
+        <v>909</v>
+      </c>
+      <c r="E61" t="b">
+        <v>1</v>
+      </c>
+      <c r="F61" t="s">
+        <v>873</v>
+      </c>
+      <c r="G61" t="s">
+        <v>873</v>
+      </c>
+      <c r="H61" t="s">
+        <v>910</v>
+      </c>
+      <c r="I61" t="b">
+        <v>1</v>
+      </c>
+      <c r="J61" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="62" spans="1:10">
+      <c r="B62">
+        <v>1061</v>
+      </c>
+      <c r="C62" t="s">
+        <v>912</v>
+      </c>
+      <c r="D62" t="s">
+        <v>913</v>
+      </c>
+      <c r="E62" t="b">
+        <v>1</v>
+      </c>
+      <c r="F62" t="s">
+        <v>873</v>
+      </c>
+      <c r="G62" t="s">
+        <v>873</v>
+      </c>
+      <c r="H62" t="s">
+        <v>914</v>
+      </c>
+      <c r="I62" t="b">
+        <v>1</v>
+      </c>
+      <c r="J62" t="s">
+        <v>915</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="E$1:E$1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",E1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
@@ -5817,25 +6483,25 @@
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>856</v>
+        <v>916</v>
       </c>
       <c r="C1" t="s">
-        <v>857</v>
+        <v>917</v>
       </c>
       <c r="D1" t="s">
-        <v>858</v>
+        <v>918</v>
       </c>
       <c r="E1" t="s">
-        <v>859</v>
+        <v>919</v>
       </c>
       <c r="F1" t="s">
-        <v>860</v>
+        <v>920</v>
       </c>
       <c r="G1" t="s">
-        <v>861</v>
+        <v>921</v>
       </c>
       <c r="H1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
     </row>
     <row r="2" spans="1:9">
@@ -5849,7 +6515,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="E2" t="s">
         <v>158</v>
@@ -5869,28 +6535,28 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>862</v>
+        <v>922</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>863</v>
+        <v>923</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>864</v>
+        <v>924</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>865</v>
+        <v>925</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>866</v>
+        <v>926</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>867</v>
+        <v>927</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>868</v>
+        <v>928</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>869</v>
+        <v>929</v>
       </c>
     </row>
     <row r="4" spans="1:9">
@@ -5898,39 +6564,39 @@
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>870</v>
+        <v>930</v>
       </c>
       <c r="C4" t="s">
-        <v>863</v>
+        <v>923</v>
       </c>
       <c r="D4" t="s">
-        <v>871</v>
+        <v>931</v>
       </c>
       <c r="E4" t="s">
-        <v>872</v>
+        <v>932</v>
       </c>
       <c r="F4" t="s">
-        <v>873</v>
+        <v>933</v>
       </c>
       <c r="G4" t="s">
-        <v>874</v>
+        <v>934</v>
       </c>
       <c r="H4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="I4" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:9">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B5" t="s">
-        <v>875</v>
+        <v>935</v>
       </c>
       <c r="C5" t="s">
-        <v>876</v>
+        <v>936</v>
       </c>
       <c r="D5" t="b">
         <v>1</v>
@@ -5948,18 +6614,18 @@
         <v>200</v>
       </c>
       <c r="I5" t="s">
-        <v>877</v>
+        <v>937</v>
       </c>
     </row>
     <row r="6" spans="1:9">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B6" t="s">
-        <v>878</v>
+        <v>938</v>
       </c>
       <c r="C6" t="s">
-        <v>879</v>
+        <v>939</v>
       </c>
       <c r="D6" t="b">
         <v>1</v>
@@ -5977,18 +6643,18 @@
         <v>100</v>
       </c>
       <c r="I6" t="s">
-        <v>880</v>
+        <v>940</v>
       </c>
     </row>
     <row r="7" spans="1:9">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B7" t="s">
-        <v>881</v>
+        <v>941</v>
       </c>
       <c r="C7" t="s">
-        <v>882</v>
+        <v>942</v>
       </c>
       <c r="D7" t="b">
         <v>1</v>
@@ -6006,18 +6672,18 @@
         <v>300</v>
       </c>
       <c r="I7" t="s">
-        <v>883</v>
+        <v>943</v>
       </c>
     </row>
     <row r="8" spans="1:9">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B8" t="s">
-        <v>884</v>
+        <v>944</v>
       </c>
       <c r="C8" t="s">
-        <v>885</v>
+        <v>945</v>
       </c>
       <c r="D8" t="b">
         <v>1</v>
@@ -6035,18 +6701,18 @@
         <v>100</v>
       </c>
       <c r="I8" t="s">
-        <v>886</v>
+        <v>946</v>
       </c>
     </row>
     <row r="9" spans="1:9">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B9" t="s">
-        <v>887</v>
+        <v>947</v>
       </c>
       <c r="C9" t="s">
-        <v>888</v>
+        <v>948</v>
       </c>
       <c r="D9" t="b">
         <v>1</v>
@@ -6064,18 +6730,18 @@
         <v>100</v>
       </c>
       <c r="I9" t="s">
-        <v>889</v>
+        <v>949</v>
       </c>
     </row>
     <row r="10" spans="1:9">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B10" t="s">
-        <v>890</v>
+        <v>950</v>
       </c>
       <c r="C10" t="s">
-        <v>891</v>
+        <v>951</v>
       </c>
       <c r="D10" t="b">
         <v>1</v>
@@ -6093,18 +6759,18 @@
         <v>100</v>
       </c>
       <c r="I10" t="s">
-        <v>892</v>
+        <v>952</v>
       </c>
     </row>
     <row r="11" spans="1:9">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B11" t="s">
-        <v>893</v>
+        <v>953</v>
       </c>
       <c r="C11" t="s">
-        <v>894</v>
+        <v>954</v>
       </c>
       <c r="D11" t="b">
         <v>1</v>
@@ -6122,18 +6788,18 @@
         <v>100</v>
       </c>
       <c r="I11" t="s">
-        <v>895</v>
+        <v>955</v>
       </c>
     </row>
     <row r="12" spans="1:9">
       <c r="A12" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B12" t="s">
-        <v>896</v>
+        <v>956</v>
       </c>
       <c r="C12" t="s">
-        <v>897</v>
+        <v>957</v>
       </c>
       <c r="D12" t="b">
         <v>1</v>
@@ -6151,7 +6817,7 @@
         <v>100</v>
       </c>
       <c r="I12" t="s">
-        <v>898</v>
+        <v>958</v>
       </c>
     </row>
   </sheetData>
@@ -6591,8 +7257,6 @@
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="2"/>
-      <c r="B6"/>
-      <c r="C6"/>
       <c r="D6" s="2"/>
       <c r="E6" s="2"/>
     </row>
@@ -6623,95 +7287,102 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:T16"/>
+  <dimension ref="A1:V30"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.25" customWidth="1"/>
     <col min="3" max="3" width="9.58333333333333" customWidth="1"/>
-    <col min="4" max="7" width="21.9166666666667" customWidth="1"/>
-    <col min="8" max="8" width="15.5" customWidth="1"/>
-    <col min="9" max="9" width="16.5833333333333" customWidth="1"/>
-    <col min="10" max="10" width="18.5" customWidth="1"/>
-    <col min="11" max="12" width="20.8333333333333" customWidth="1"/>
-    <col min="13" max="13" width="14.5" customWidth="1"/>
-    <col min="14" max="14" width="13.4166666666667" customWidth="1"/>
-    <col min="15" max="15" width="14.3333333333333" customWidth="1"/>
-    <col min="16" max="16" width="13" customWidth="1"/>
-    <col min="17" max="17" width="14.8333333333333" customWidth="1"/>
-    <col min="18" max="18" width="14" customWidth="1"/>
-    <col min="19" max="19" width="15.4166666666667" customWidth="1"/>
-    <col min="20" max="20" width="13.4166666666667" customWidth="1"/>
+    <col min="4" max="8" width="21.9166666666667" customWidth="1"/>
+    <col min="9" max="9" width="15.5" customWidth="1"/>
+    <col min="10" max="10" width="16.5833333333333" customWidth="1"/>
+    <col min="11" max="11" width="18.5" customWidth="1"/>
+    <col min="12" max="13" width="20.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="14.5" customWidth="1"/>
+    <col min="15" max="15" width="13.4166666666667" customWidth="1"/>
+    <col min="16" max="16" width="14.3333333333333" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="14.8333333333333" customWidth="1"/>
+    <col min="19" max="19" width="14" customWidth="1"/>
+    <col min="20" max="20" width="15.4166666666667" customWidth="1"/>
+    <col min="21" max="21" width="13.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20">
+    <row r="1" spans="1:22">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C1" s="2"/>
+      <c r="C1" s="2" t="s">
+        <v>166</v>
+      </c>
       <c r="D1" s="2" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="I1" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="J1" t="s">
         <v>172</v>
       </c>
+      <c r="J1" s="2" t="s">
+        <v>173</v>
+      </c>
       <c r="K1" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="L1" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="M1" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="N1" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O1" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="P1" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="Q1" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="R1" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="S1" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="T1" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="2" spans="1:20">
+        <v>183</v>
+      </c>
+      <c r="U1" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="2" spans="1:22">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
       <c r="B2" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="C2" s="2"/>
+      <c r="C2" s="2" t="s">
+        <v>109</v>
+      </c>
       <c r="D2" s="2" t="s">
         <v>109</v>
       </c>
@@ -6763,8 +7434,11 @@
       <c r="T2" s="2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" ht="34.8" spans="1:20">
+      <c r="U2" s="2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="34.8" spans="1:22">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
@@ -6772,16 +7446,17 @@
       <c r="C3" s="3"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="F3" s="3" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
       <c r="I3" s="3"/>
-    </row>
-    <row r="4" spans="1:20">
+      <c r="J3" s="3"/>
+    </row>
+    <row r="4" spans="1:22">
       <c r="A4" s="3" t="s">
         <v>110</v>
       </c>
@@ -6789,764 +7464,1159 @@
         <v>99</v>
       </c>
       <c r="C4" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="D4" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="E4" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="F4" t="s">
-        <v>187</v>
+        <v>189</v>
+      </c>
+      <c r="G4" t="s">
+        <v>190</v>
       </c>
       <c r="H4" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="I4" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="J4" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="K4" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="L4" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="M4" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="N4" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="O4" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="P4" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="Q4" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="R4" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="S4" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="T4" t="s">
-        <v>200</v>
-      </c>
-    </row>
-    <row r="5" spans="1:20">
-      <c r="B5">
+        <v>203</v>
+      </c>
+      <c r="U4" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:22">
+      <c r="B5" s="2">
         <v>1001</v>
       </c>
-      <c r="C5" t="s">
-        <v>201</v>
-      </c>
-      <c r="D5" t="s">
-        <v>202</v>
-      </c>
-      <c r="E5" t="s">
-        <v>203</v>
-      </c>
-      <c r="F5" t="s">
-        <v>204</v>
-      </c>
-      <c r="G5" t="s">
-        <v>174</v>
-      </c>
-      <c r="H5" t="s">
+      <c r="C5" s="2" t="s">
         <v>205</v>
       </c>
-      <c r="I5" t="s">
+      <c r="D5" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="J5" t="s">
+      <c r="E5" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="K5" t="s">
+      <c r="F5" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="L5" t="s">
+      <c r="G5" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H5" s="2"/>
+      <c r="I5" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="M5" t="s">
-        <v>203</v>
-      </c>
-      <c r="N5" t="s">
+      <c r="J5" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="O5" t="s">
+      <c r="K5" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="P5" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q5" t="s">
+      <c r="L5" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="R5" t="s">
+      <c r="M5" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="S5" t="s">
+      <c r="N5" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O5" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="T5" t="s">
+      <c r="P5" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="6" spans="1:20">
-      <c r="B6">
+      <c r="Q5" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R5" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S5" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T5" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U5" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V5" s="2"/>
+    </row>
+    <row r="6" spans="1:22">
+      <c r="B6" s="2">
         <v>1002</v>
       </c>
-      <c r="C6" t="s">
+      <c r="C6" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H6" s="2"/>
+      <c r="I6" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M6" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N6" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O6" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P6" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q6" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R6" s="2" t="s">
         <v>216</v>
       </c>
-      <c r="D6" t="s">
+      <c r="S6" s="2" t="s">
         <v>217</v>
       </c>
-      <c r="E6" t="s">
-        <v>203</v>
-      </c>
-      <c r="F6" t="s">
+      <c r="T6" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U6" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V6" s="2"/>
+    </row>
+    <row r="7" spans="1:22">
+      <c r="B7" s="2">
+        <v>1003</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>223</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H7" s="2"/>
+      <c r="I7" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L7" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="G6" t="s">
-        <v>174</v>
-      </c>
-      <c r="H6" t="s">
+      <c r="M7" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N7" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P7" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q7" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R7" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S7" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T7" s="2" t="s">
         <v>218</v>
       </c>
-      <c r="I6" t="s">
+      <c r="U7" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V7" s="2"/>
+    </row>
+    <row r="8" spans="1:22">
+      <c r="B8" s="2">
+        <v>1004</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>226</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>227</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G8" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H8" s="2"/>
+      <c r="I8" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M8" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N8" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O8" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P8" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q8" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R8" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S8" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T8" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U8" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V8" s="2"/>
+    </row>
+    <row r="9" spans="1:22">
+      <c r="B9" s="2">
+        <v>1005</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>229</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>230</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="G9" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M9" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N9" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O9" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P9" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q9" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R9" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S9" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T9" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U9" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V9" s="2"/>
+    </row>
+    <row r="10" spans="1:22">
+      <c r="B10" s="2">
+        <v>1006</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>233</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>234</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G10" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>235</v>
+      </c>
+      <c r="I10" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K10" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M10" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N10" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O10" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P10" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q10" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R10" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S10" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T10" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U10" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V10" s="2"/>
+    </row>
+    <row r="11" spans="1:22">
+      <c r="B11" s="2">
+        <v>1007</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>237</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>238</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G11" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I11" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K11" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M11" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N11" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O11" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P11" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q11" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R11" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S11" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T11" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U11" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V11" s="2"/>
+    </row>
+    <row r="12" spans="1:22">
+      <c r="B12" s="2">
+        <v>1008</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F12" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G12" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="I12" s="2" t="s">
+        <v>222</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K12" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M12" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N12" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O12" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P12" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q12" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R12" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S12" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T12" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U12" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V12" s="2"/>
+    </row>
+    <row r="13" spans="1:22">
+      <c r="B13" s="2">
+        <v>1009</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="G13" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>231</v>
+      </c>
+      <c r="I13" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K13" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M13" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N13" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O13" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P13" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q13" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R13" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S13" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T13" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U13" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V13" s="2"/>
+    </row>
+    <row r="14" spans="1:22">
+      <c r="B14" s="2">
+        <v>1010</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G14" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H14" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I14" s="2" t="s">
+        <v>225</v>
+      </c>
+      <c r="J14" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K14" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M14" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N14" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O14" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P14" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q14" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R14" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S14" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T14" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U14" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V14" s="2"/>
+    </row>
+    <row r="15" spans="1:22">
+      <c r="B15" s="2">
+        <v>1011</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>248</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>249</v>
+      </c>
+      <c r="E15" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G15" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H15" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>232</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M15" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N15" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O15" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q15" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R15" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S15" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T15" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U15" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V15" s="2"/>
+    </row>
+    <row r="16" spans="1:22">
+      <c r="B16" s="2">
+        <v>1012</v>
+      </c>
+      <c r="C16" s="2" t="s">
+        <v>250</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>251</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="F16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="G16" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H16" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I16" s="2" t="s">
+        <v>228</v>
+      </c>
+      <c r="J16" s="2" t="s">
+        <v>236</v>
+      </c>
+      <c r="K16" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="M16" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="N16" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O16" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="P16" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="Q16" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S16" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T16" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U16" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="V16" s="2"/>
+    </row>
+    <row r="17" spans="2:22">
+      <c r="B17" s="2">
+        <v>1013</v>
+      </c>
+      <c r="C17" s="2" t="s">
+        <v>252</v>
+      </c>
+      <c r="D17" s="2" t="s">
         <v>206</v>
       </c>
-      <c r="J6" t="s">
+      <c r="E17" s="2" t="s">
         <v>207</v>
       </c>
-      <c r="K6" t="s">
+      <c r="F17" s="2" t="s">
         <v>208</v>
       </c>
-      <c r="L6" t="s">
+      <c r="G17" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="H17" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="I17" s="2" t="s">
         <v>209</v>
       </c>
-      <c r="M6" t="s">
-        <v>203</v>
-      </c>
-      <c r="N6" t="s">
+      <c r="J17" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="O6" t="s">
+      <c r="K17" s="2" t="s">
         <v>211</v>
       </c>
-      <c r="P6" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q6" t="s">
+      <c r="L17" s="2" t="s">
         <v>212</v>
       </c>
-      <c r="R6" t="s">
+      <c r="M17" s="2" t="s">
         <v>213</v>
       </c>
-      <c r="S6" t="s">
+      <c r="N17" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="O17" s="2" t="s">
         <v>214</v>
       </c>
-      <c r="T6" t="s">
+      <c r="P17" s="2" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="7" spans="1:20">
-      <c r="B7">
-        <v>1003</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="Q17" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="R17" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="S17" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="T17" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="U17" s="2" t="s">
         <v>219</v>
       </c>
-      <c r="D7" t="s">
-        <v>220</v>
-      </c>
-      <c r="E7" t="s">
-        <v>203</v>
-      </c>
-      <c r="F7" t="s">
-        <v>213</v>
-      </c>
-      <c r="G7" t="s">
-        <v>174</v>
-      </c>
-      <c r="H7" t="s">
-        <v>221</v>
-      </c>
-      <c r="I7" t="s">
-        <v>206</v>
-      </c>
-      <c r="J7" t="s">
-        <v>207</v>
-      </c>
-      <c r="K7" t="s">
-        <v>208</v>
-      </c>
-      <c r="L7" t="s">
-        <v>209</v>
-      </c>
-      <c r="M7" t="s">
-        <v>203</v>
-      </c>
-      <c r="N7" t="s">
-        <v>210</v>
-      </c>
-      <c r="O7" t="s">
-        <v>211</v>
-      </c>
-      <c r="P7" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q7" t="s">
-        <v>212</v>
-      </c>
-      <c r="R7" t="s">
-        <v>213</v>
-      </c>
-      <c r="S7" t="s">
-        <v>214</v>
-      </c>
-      <c r="T7" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="8" spans="1:20">
-      <c r="B8">
-        <v>1004</v>
-      </c>
-      <c r="C8" t="s">
-        <v>222</v>
-      </c>
-      <c r="D8" t="s">
-        <v>223</v>
-      </c>
-      <c r="E8" t="s">
-        <v>210</v>
-      </c>
-      <c r="F8" t="s">
-        <v>211</v>
-      </c>
-      <c r="G8" t="s">
-        <v>174</v>
-      </c>
-      <c r="H8" t="s">
-        <v>224</v>
-      </c>
-      <c r="I8" t="s">
-        <v>206</v>
-      </c>
-      <c r="J8" t="s">
-        <v>207</v>
-      </c>
-      <c r="K8" t="s">
-        <v>208</v>
-      </c>
-      <c r="L8" t="s">
-        <v>209</v>
-      </c>
-      <c r="M8" t="s">
-        <v>203</v>
-      </c>
-      <c r="N8" t="s">
-        <v>210</v>
-      </c>
-      <c r="O8" t="s">
-        <v>211</v>
-      </c>
-      <c r="P8" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q8" t="s">
-        <v>212</v>
-      </c>
-      <c r="R8" t="s">
-        <v>213</v>
-      </c>
-      <c r="S8" t="s">
-        <v>214</v>
-      </c>
-      <c r="T8" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="9" spans="1:20">
-      <c r="B9">
-        <v>1005</v>
-      </c>
-      <c r="C9" t="s">
-        <v>225</v>
-      </c>
-      <c r="D9" t="s">
-        <v>226</v>
-      </c>
-      <c r="E9" t="s">
-        <v>203</v>
-      </c>
-      <c r="F9" t="s">
-        <v>213</v>
-      </c>
-      <c r="G9" t="s">
-        <v>174</v>
-      </c>
-      <c r="H9" t="s">
-        <v>205</v>
-      </c>
-      <c r="I9" t="s">
-        <v>227</v>
-      </c>
-      <c r="J9" t="s">
-        <v>207</v>
-      </c>
-      <c r="K9" t="s">
-        <v>208</v>
-      </c>
-      <c r="L9" t="s">
-        <v>209</v>
-      </c>
-      <c r="M9" t="s">
-        <v>203</v>
-      </c>
-      <c r="N9" t="s">
-        <v>210</v>
-      </c>
-      <c r="O9" t="s">
-        <v>211</v>
-      </c>
-      <c r="P9" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q9" t="s">
-        <v>212</v>
-      </c>
-      <c r="R9" t="s">
-        <v>213</v>
-      </c>
-      <c r="S9" t="s">
-        <v>214</v>
-      </c>
-      <c r="T9" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="10" spans="1:20">
-      <c r="B10">
-        <v>1006</v>
-      </c>
-      <c r="C10" t="s">
-        <v>228</v>
-      </c>
-      <c r="D10" t="s">
-        <v>229</v>
-      </c>
-      <c r="E10" t="s">
-        <v>210</v>
-      </c>
-      <c r="F10" t="s">
-        <v>204</v>
-      </c>
-      <c r="G10" t="s">
-        <v>174</v>
-      </c>
-      <c r="H10" t="s">
-        <v>205</v>
-      </c>
-      <c r="I10" t="s">
-        <v>230</v>
-      </c>
-      <c r="J10" t="s">
-        <v>207</v>
-      </c>
-      <c r="K10" t="s">
-        <v>208</v>
-      </c>
-      <c r="L10" t="s">
-        <v>209</v>
-      </c>
-      <c r="M10" t="s">
-        <v>203</v>
-      </c>
-      <c r="N10" t="s">
-        <v>210</v>
-      </c>
-      <c r="O10" t="s">
-        <v>211</v>
-      </c>
-      <c r="P10" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q10" t="s">
-        <v>212</v>
-      </c>
-      <c r="R10" t="s">
-        <v>213</v>
-      </c>
-      <c r="S10" t="s">
-        <v>214</v>
-      </c>
-      <c r="T10" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="11" spans="1:20">
-      <c r="B11">
-        <v>1007</v>
-      </c>
-      <c r="C11" t="s">
-        <v>231</v>
-      </c>
-      <c r="D11" t="s">
-        <v>232</v>
-      </c>
-      <c r="E11" t="s">
-        <v>203</v>
-      </c>
-      <c r="F11" t="s">
-        <v>215</v>
-      </c>
-      <c r="G11" t="s">
-        <v>174</v>
-      </c>
-      <c r="H11" t="s">
-        <v>218</v>
-      </c>
-      <c r="I11" t="s">
-        <v>227</v>
-      </c>
-      <c r="J11" t="s">
-        <v>207</v>
-      </c>
-      <c r="K11" t="s">
-        <v>208</v>
-      </c>
-      <c r="L11" t="s">
-        <v>209</v>
-      </c>
-      <c r="M11" t="s">
-        <v>203</v>
-      </c>
-      <c r="N11" t="s">
-        <v>210</v>
-      </c>
-      <c r="O11" t="s">
-        <v>211</v>
-      </c>
-      <c r="P11" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q11" t="s">
-        <v>212</v>
-      </c>
-      <c r="R11" t="s">
-        <v>213</v>
-      </c>
-      <c r="S11" t="s">
-        <v>214</v>
-      </c>
-      <c r="T11" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="12" spans="1:20">
-      <c r="B12">
-        <v>1008</v>
-      </c>
-      <c r="C12" t="s">
-        <v>233</v>
-      </c>
-      <c r="D12" t="s">
-        <v>234</v>
-      </c>
-      <c r="E12" t="s">
-        <v>203</v>
-      </c>
-      <c r="F12" t="s">
-        <v>204</v>
-      </c>
-      <c r="G12" t="s">
-        <v>174</v>
-      </c>
-      <c r="H12" t="s">
-        <v>218</v>
-      </c>
-      <c r="I12" t="s">
-        <v>230</v>
-      </c>
-      <c r="J12" t="s">
-        <v>207</v>
-      </c>
-      <c r="K12" t="s">
-        <v>208</v>
-      </c>
-      <c r="L12" t="s">
-        <v>209</v>
-      </c>
-      <c r="M12" t="s">
-        <v>203</v>
-      </c>
-      <c r="N12" t="s">
-        <v>210</v>
-      </c>
-      <c r="O12" t="s">
-        <v>211</v>
-      </c>
-      <c r="P12" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q12" t="s">
-        <v>212</v>
-      </c>
-      <c r="R12" t="s">
-        <v>213</v>
-      </c>
-      <c r="S12" t="s">
-        <v>214</v>
-      </c>
-      <c r="T12" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="13" spans="1:20">
-      <c r="B13">
-        <v>1009</v>
-      </c>
-      <c r="C13" t="s">
-        <v>235</v>
-      </c>
-      <c r="D13" t="s">
-        <v>236</v>
-      </c>
-      <c r="E13" t="s">
-        <v>203</v>
-      </c>
-      <c r="F13" t="s">
-        <v>215</v>
-      </c>
-      <c r="G13" t="s">
-        <v>174</v>
-      </c>
-      <c r="H13" t="s">
-        <v>221</v>
-      </c>
-      <c r="I13" t="s">
-        <v>227</v>
-      </c>
-      <c r="J13" t="s">
-        <v>207</v>
-      </c>
-      <c r="K13" t="s">
-        <v>208</v>
-      </c>
-      <c r="L13" t="s">
-        <v>209</v>
-      </c>
-      <c r="M13" t="s">
-        <v>203</v>
-      </c>
-      <c r="N13" t="s">
-        <v>210</v>
-      </c>
-      <c r="O13" t="s">
-        <v>211</v>
-      </c>
-      <c r="P13" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>212</v>
-      </c>
-      <c r="R13" t="s">
-        <v>213</v>
-      </c>
-      <c r="S13" t="s">
-        <v>214</v>
-      </c>
-      <c r="T13" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="14" spans="1:20">
-      <c r="B14">
-        <v>1010</v>
-      </c>
-      <c r="C14" t="s">
-        <v>237</v>
-      </c>
-      <c r="D14" t="s">
-        <v>238</v>
-      </c>
-      <c r="E14" t="s">
-        <v>203</v>
-      </c>
-      <c r="F14" t="s">
-        <v>204</v>
-      </c>
-      <c r="G14" t="s">
-        <v>174</v>
-      </c>
-      <c r="H14" t="s">
-        <v>221</v>
-      </c>
-      <c r="I14" t="s">
-        <v>230</v>
-      </c>
-      <c r="J14" t="s">
-        <v>207</v>
-      </c>
-      <c r="K14" t="s">
-        <v>208</v>
-      </c>
-      <c r="L14" t="s">
-        <v>209</v>
-      </c>
-      <c r="M14" t="s">
-        <v>203</v>
-      </c>
-      <c r="N14" t="s">
-        <v>210</v>
-      </c>
-      <c r="O14" t="s">
-        <v>211</v>
-      </c>
-      <c r="P14" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q14" t="s">
-        <v>212</v>
-      </c>
-      <c r="R14" t="s">
-        <v>213</v>
-      </c>
-      <c r="S14" t="s">
-        <v>214</v>
-      </c>
-      <c r="T14" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="15" spans="1:20">
-      <c r="B15">
-        <v>1011</v>
-      </c>
-      <c r="C15" t="s">
-        <v>239</v>
-      </c>
-      <c r="D15" t="s">
-        <v>240</v>
-      </c>
-      <c r="E15" t="s">
-        <v>203</v>
-      </c>
-      <c r="F15" t="s">
-        <v>204</v>
-      </c>
-      <c r="G15" t="s">
-        <v>174</v>
-      </c>
-      <c r="H15" t="s">
-        <v>224</v>
-      </c>
-      <c r="I15" t="s">
-        <v>227</v>
-      </c>
-      <c r="J15" t="s">
-        <v>207</v>
-      </c>
-      <c r="K15" t="s">
-        <v>208</v>
-      </c>
-      <c r="L15" t="s">
-        <v>209</v>
-      </c>
-      <c r="M15" t="s">
-        <v>203</v>
-      </c>
-      <c r="N15" t="s">
-        <v>210</v>
-      </c>
-      <c r="O15" t="s">
-        <v>211</v>
-      </c>
-      <c r="P15" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>212</v>
-      </c>
-      <c r="R15" t="s">
-        <v>213</v>
-      </c>
-      <c r="S15" t="s">
-        <v>214</v>
-      </c>
-      <c r="T15" t="s">
-        <v>215</v>
-      </c>
-    </row>
-    <row r="16" spans="1:20">
-      <c r="B16">
-        <v>1012</v>
-      </c>
-      <c r="C16" t="s">
-        <v>241</v>
-      </c>
-      <c r="D16" t="s">
-        <v>242</v>
-      </c>
-      <c r="E16" t="s">
-        <v>203</v>
-      </c>
-      <c r="F16" t="s">
-        <v>214</v>
-      </c>
-      <c r="G16" t="s">
-        <v>174</v>
-      </c>
-      <c r="H16" t="s">
-        <v>224</v>
-      </c>
-      <c r="I16" t="s">
-        <v>230</v>
-      </c>
-      <c r="J16" t="s">
-        <v>207</v>
-      </c>
-      <c r="K16" t="s">
-        <v>208</v>
-      </c>
-      <c r="L16" t="s">
-        <v>209</v>
-      </c>
-      <c r="M16" t="s">
-        <v>203</v>
-      </c>
-      <c r="N16" t="s">
-        <v>210</v>
-      </c>
-      <c r="O16" t="s">
-        <v>211</v>
-      </c>
-      <c r="P16" t="s">
-        <v>204</v>
-      </c>
-      <c r="Q16" t="s">
-        <v>212</v>
-      </c>
-      <c r="R16" t="s">
-        <v>213</v>
-      </c>
-      <c r="S16" t="s">
-        <v>214</v>
-      </c>
-      <c r="T16" t="s">
-        <v>215</v>
-      </c>
+      <c r="V17" s="2"/>
+    </row>
+    <row r="18" spans="2:22">
+      <c r="B18" s="2"/>
+      <c r="C18" s="2"/>
+      <c r="D18" s="2"/>
+      <c r="E18" s="2"/>
+      <c r="F18" s="2"/>
+      <c r="G18" s="2"/>
+      <c r="H18" s="2"/>
+      <c r="I18" s="2"/>
+      <c r="J18" s="2"/>
+      <c r="K18" s="2"/>
+      <c r="L18" s="2"/>
+      <c r="M18" s="2"/>
+      <c r="N18" s="2"/>
+      <c r="O18" s="2"/>
+      <c r="P18" s="2"/>
+      <c r="Q18" s="2"/>
+      <c r="R18" s="2"/>
+      <c r="S18" s="2"/>
+      <c r="T18" s="2"/>
+      <c r="U18" s="2"/>
+    </row>
+    <row r="19" spans="2:22">
+      <c r="B19" s="2"/>
+      <c r="C19" s="2"/>
+      <c r="D19" s="2"/>
+      <c r="E19" s="2"/>
+      <c r="F19" s="2"/>
+      <c r="G19" s="2"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="2"/>
+      <c r="J19" s="2"/>
+      <c r="K19" s="2"/>
+      <c r="L19" s="2"/>
+      <c r="M19" s="2"/>
+      <c r="N19" s="2"/>
+      <c r="O19" s="2"/>
+      <c r="P19" s="2"/>
+      <c r="Q19" s="2"/>
+      <c r="R19" s="2"/>
+      <c r="S19" s="2"/>
+      <c r="T19" s="2"/>
+      <c r="U19" s="2"/>
+    </row>
+    <row r="20" spans="2:22">
+      <c r="B20" s="2"/>
+      <c r="C20" s="2"/>
+      <c r="D20" s="2"/>
+      <c r="E20" s="2"/>
+      <c r="F20" s="2"/>
+      <c r="G20" s="2"/>
+      <c r="H20" s="2"/>
+      <c r="I20" s="2"/>
+      <c r="J20" s="2"/>
+      <c r="K20" s="2"/>
+      <c r="L20" s="2"/>
+      <c r="M20" s="2"/>
+      <c r="N20" s="2"/>
+      <c r="O20" s="2"/>
+      <c r="P20" s="2"/>
+      <c r="Q20" s="2"/>
+      <c r="R20" s="2"/>
+      <c r="S20" s="2"/>
+      <c r="T20" s="2"/>
+      <c r="U20" s="2"/>
+    </row>
+    <row r="21" spans="2:22">
+      <c r="B21" s="2"/>
+      <c r="C21" s="2"/>
+      <c r="D21" s="2"/>
+      <c r="E21" s="2"/>
+      <c r="F21" s="2"/>
+      <c r="G21" s="2"/>
+      <c r="H21" s="2"/>
+      <c r="I21" s="2"/>
+      <c r="J21" s="2"/>
+      <c r="K21" s="2"/>
+      <c r="L21" s="2"/>
+      <c r="M21" s="2"/>
+      <c r="N21" s="2"/>
+      <c r="O21" s="2"/>
+      <c r="P21" s="2"/>
+      <c r="Q21" s="2"/>
+      <c r="R21" s="2"/>
+      <c r="S21" s="2"/>
+      <c r="T21" s="2"/>
+      <c r="U21" s="2"/>
+    </row>
+    <row r="22" spans="2:22">
+      <c r="B22" s="2"/>
+      <c r="C22" s="2"/>
+      <c r="D22" s="2"/>
+      <c r="E22" s="2"/>
+      <c r="F22" s="2"/>
+      <c r="G22" s="2"/>
+      <c r="H22" s="2"/>
+      <c r="I22" s="2"/>
+      <c r="J22" s="2"/>
+      <c r="K22" s="2"/>
+      <c r="L22" s="2"/>
+      <c r="M22" s="2"/>
+      <c r="N22" s="2"/>
+      <c r="O22" s="2"/>
+      <c r="P22" s="2"/>
+      <c r="Q22" s="2"/>
+      <c r="R22" s="2"/>
+      <c r="S22" s="2"/>
+      <c r="T22" s="2"/>
+      <c r="U22" s="2"/>
+    </row>
+    <row r="23" spans="2:22">
+      <c r="B23" s="2"/>
+      <c r="C23" s="2"/>
+      <c r="D23" s="2"/>
+      <c r="E23" s="2"/>
+      <c r="F23" s="2"/>
+      <c r="G23" s="2"/>
+      <c r="H23" s="2"/>
+      <c r="I23" s="2"/>
+      <c r="J23" s="2"/>
+      <c r="K23" s="2"/>
+      <c r="L23" s="2"/>
+      <c r="M23" s="2"/>
+      <c r="N23" s="2"/>
+      <c r="O23" s="2"/>
+      <c r="P23" s="2"/>
+      <c r="Q23" s="2"/>
+      <c r="R23" s="2"/>
+      <c r="S23" s="2"/>
+      <c r="T23" s="2"/>
+      <c r="U23" s="2"/>
+    </row>
+    <row r="24" spans="2:22">
+      <c r="B24" s="2"/>
+      <c r="C24" s="2"/>
+      <c r="D24" s="2"/>
+      <c r="E24" s="2"/>
+      <c r="F24" s="2"/>
+      <c r="G24" s="2"/>
+      <c r="H24" s="2"/>
+      <c r="I24" s="2"/>
+      <c r="J24" s="2"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="2"/>
+      <c r="M24" s="2"/>
+      <c r="N24" s="2"/>
+      <c r="O24" s="2"/>
+      <c r="P24" s="2"/>
+      <c r="Q24" s="2"/>
+      <c r="R24" s="2"/>
+      <c r="S24" s="2"/>
+      <c r="T24" s="2"/>
+      <c r="U24" s="2"/>
+    </row>
+    <row r="25" spans="2:22">
+      <c r="B25" s="2"/>
+      <c r="C25" s="2"/>
+      <c r="D25" s="2"/>
+      <c r="E25" s="2"/>
+      <c r="F25" s="2"/>
+      <c r="G25" s="2"/>
+      <c r="H25" s="2"/>
+      <c r="I25" s="2"/>
+      <c r="J25" s="2"/>
+      <c r="K25" s="2"/>
+      <c r="L25" s="2"/>
+      <c r="M25" s="2"/>
+      <c r="N25" s="2"/>
+      <c r="O25" s="2"/>
+      <c r="P25" s="2"/>
+      <c r="Q25" s="2"/>
+      <c r="R25" s="2"/>
+      <c r="S25" s="2"/>
+      <c r="T25" s="2"/>
+      <c r="U25" s="2"/>
+    </row>
+    <row r="26" spans="2:22">
+      <c r="B26" s="2"/>
+      <c r="C26" s="2"/>
+      <c r="D26" s="2"/>
+      <c r="E26" s="2"/>
+      <c r="F26" s="2"/>
+      <c r="G26" s="2"/>
+      <c r="H26" s="2"/>
+      <c r="I26" s="2"/>
+      <c r="J26" s="2"/>
+      <c r="K26" s="2"/>
+      <c r="L26" s="2"/>
+      <c r="M26" s="2"/>
+      <c r="N26" s="2"/>
+      <c r="O26" s="2"/>
+      <c r="P26" s="2"/>
+      <c r="Q26" s="2"/>
+      <c r="R26" s="2"/>
+      <c r="S26" s="2"/>
+      <c r="T26" s="2"/>
+      <c r="U26" s="2"/>
+    </row>
+    <row r="27" spans="2:22">
+      <c r="B27" s="2"/>
+      <c r="C27" s="2"/>
+      <c r="D27" s="2"/>
+      <c r="E27" s="2"/>
+      <c r="F27" s="2"/>
+      <c r="G27" s="2"/>
+      <c r="H27" s="2"/>
+      <c r="I27" s="2"/>
+      <c r="J27" s="2"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="2"/>
+      <c r="M27" s="2"/>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
+      <c r="P27" s="2"/>
+      <c r="Q27" s="2"/>
+      <c r="R27" s="2"/>
+      <c r="S27" s="2"/>
+      <c r="T27" s="2"/>
+      <c r="U27" s="2"/>
+    </row>
+    <row r="28" spans="2:22">
+      <c r="B28" s="2"/>
+      <c r="C28" s="2"/>
+      <c r="D28" s="2"/>
+      <c r="E28" s="2"/>
+      <c r="F28" s="2"/>
+      <c r="G28" s="2"/>
+      <c r="H28" s="2"/>
+      <c r="I28" s="2"/>
+      <c r="J28" s="2"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="2"/>
+      <c r="M28" s="2"/>
+      <c r="N28" s="2"/>
+      <c r="O28" s="2"/>
+      <c r="P28" s="2"/>
+      <c r="Q28" s="2"/>
+      <c r="R28" s="2"/>
+      <c r="S28" s="2"/>
+      <c r="T28" s="2"/>
+      <c r="U28" s="2"/>
+    </row>
+    <row r="29" spans="2:22">
+      <c r="B29" s="2"/>
+      <c r="C29" s="2"/>
+      <c r="D29" s="2"/>
+      <c r="E29" s="2"/>
+      <c r="F29" s="2"/>
+      <c r="G29" s="2"/>
+      <c r="H29" s="2"/>
+      <c r="I29" s="2"/>
+      <c r="J29" s="2"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="2"/>
+      <c r="M29" s="2"/>
+      <c r="N29" s="2"/>
+      <c r="O29" s="2"/>
+      <c r="P29" s="2"/>
+      <c r="Q29" s="2"/>
+      <c r="R29" s="2"/>
+      <c r="S29" s="2"/>
+      <c r="T29" s="2"/>
+      <c r="U29" s="2"/>
+    </row>
+    <row r="30" spans="2:22">
+      <c r="B30" s="2"/>
+      <c r="C30" s="2"/>
+      <c r="D30" s="2"/>
+      <c r="E30" s="2"/>
+      <c r="F30" s="2"/>
+      <c r="G30" s="2"/>
+      <c r="H30" s="2"/>
+      <c r="I30" s="2"/>
+      <c r="J30" s="2"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="2"/>
+      <c r="M30" s="2"/>
+      <c r="N30" s="2"/>
+      <c r="O30" s="2"/>
+      <c r="P30" s="2"/>
+      <c r="Q30" s="2"/>
+      <c r="R30" s="2"/>
+      <c r="S30" s="2"/>
+      <c r="T30" s="2"/>
+      <c r="U30" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -7574,16 +8644,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>244</v>
+        <v>254</v>
       </c>
       <c r="E1" t="s">
-        <v>245</v>
+        <v>255</v>
       </c>
       <c r="F1" t="s">
-        <v>246</v>
+        <v>256</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -7597,7 +8667,7 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>247</v>
+        <v>257</v>
       </c>
       <c r="E2" t="s">
         <v>109</v>
@@ -7622,16 +8692,16 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>248</v>
+        <v>258</v>
       </c>
       <c r="D4" t="s">
-        <v>249</v>
+        <v>259</v>
       </c>
       <c r="E4" t="s">
-        <v>250</v>
+        <v>260</v>
       </c>
       <c r="F4" t="s">
-        <v>251</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -7645,10 +8715,10 @@
         <v>30</v>
       </c>
       <c r="E5" t="s">
-        <v>252</v>
+        <v>262</v>
       </c>
       <c r="F5" t="s">
-        <v>253</v>
+        <v>263</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -7656,16 +8726,16 @@
         <v>1002</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>254</v>
+        <v>264</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>30</v>
       </c>
       <c r="E6" t="s">
-        <v>255</v>
+        <v>265</v>
       </c>
       <c r="F6" t="s">
-        <v>256</v>
+        <v>266</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -7679,10 +8749,10 @@
         <v>21</v>
       </c>
       <c r="E7" t="s">
-        <v>257</v>
+        <v>267</v>
       </c>
       <c r="F7" t="s">
-        <v>258</v>
+        <v>268</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -7696,10 +8766,10 @@
         <v>12</v>
       </c>
       <c r="E8" t="s">
-        <v>259</v>
+        <v>269</v>
       </c>
       <c r="F8" t="s">
-        <v>260</v>
+        <v>270</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -7713,10 +8783,10 @@
         <v>3</v>
       </c>
       <c r="E9" t="s">
-        <v>261</v>
+        <v>271</v>
       </c>
       <c r="F9" t="s">
-        <v>262</v>
+        <v>272</v>
       </c>
     </row>
     <row r="10" spans="1:6">
@@ -7724,16 +8794,16 @@
         <v>1006</v>
       </c>
       <c r="C10" t="s">
-        <v>263</v>
+        <v>273</v>
       </c>
       <c r="D10" t="s">
-        <v>264</v>
+        <v>274</v>
       </c>
       <c r="E10" t="s">
-        <v>265</v>
+        <v>275</v>
       </c>
       <c r="F10" t="s">
-        <v>266</v>
+        <v>276</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -7747,10 +8817,10 @@
         <v>39</v>
       </c>
       <c r="E11" t="s">
-        <v>267</v>
+        <v>277</v>
       </c>
       <c r="F11" t="s">
-        <v>268</v>
+        <v>278</v>
       </c>
     </row>
     <row r="12" spans="1:6">
@@ -7764,10 +8834,10 @@
         <v>48</v>
       </c>
       <c r="E12" t="s">
-        <v>269</v>
+        <v>279</v>
       </c>
       <c r="F12" t="s">
-        <v>270</v>
+        <v>280</v>
       </c>
     </row>
   </sheetData>
@@ -7800,34 +8870,34 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="E1" t="s">
-        <v>272</v>
+        <v>282</v>
       </c>
       <c r="G1" t="s">
-        <v>273</v>
+        <v>283</v>
       </c>
       <c r="H1" t="s">
-        <v>274</v>
+        <v>284</v>
       </c>
       <c r="I1" t="s">
-        <v>275</v>
+        <v>285</v>
       </c>
       <c r="J1" t="s">
-        <v>276</v>
+        <v>286</v>
       </c>
       <c r="K1" t="s">
-        <v>277</v>
+        <v>287</v>
       </c>
       <c r="L1" t="s">
-        <v>278</v>
+        <v>288</v>
       </c>
       <c r="M1" t="s">
-        <v>279</v>
+        <v>289</v>
       </c>
       <c r="N1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:14">
@@ -7838,10 +8908,10 @@
         <v>107</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="E2" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -7853,7 +8923,7 @@
         <v>109</v>
       </c>
       <c r="J2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="K2" t="s">
         <v>109</v>
@@ -7875,13 +8945,16 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="E3" s="1" t="s">
-        <v>283</v>
+        <v>293</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>284</v>
+        <v>294</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>295</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>285</v>
+        <v>296</v>
       </c>
     </row>
     <row r="4" spans="1:14">
@@ -7892,40 +8965,40 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>286</v>
+        <v>297</v>
       </c>
       <c r="D4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="E4" t="s">
-        <v>288</v>
+        <v>299</v>
       </c>
       <c r="F4" t="s">
-        <v>287</v>
+        <v>298</v>
       </c>
       <c r="G4" t="s">
-        <v>289</v>
+        <v>300</v>
       </c>
       <c r="H4" t="s">
-        <v>290</v>
+        <v>301</v>
       </c>
       <c r="I4" t="s">
-        <v>291</v>
+        <v>302</v>
       </c>
       <c r="J4" t="s">
-        <v>292</v>
+        <v>303</v>
       </c>
       <c r="K4" t="s">
-        <v>293</v>
+        <v>304</v>
       </c>
       <c r="L4" t="s">
-        <v>294</v>
+        <v>305</v>
       </c>
       <c r="M4" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="N4" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:14">
@@ -7948,13 +9021,13 @@
         <v>0</v>
       </c>
       <c r="K5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L5" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M5" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="6" spans="1:14">
@@ -7968,22 +9041,22 @@
         <v>17</v>
       </c>
       <c r="G6" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H6" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J6" t="b">
         <v>0</v>
       </c>
       <c r="K6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L6" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M6" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="7" spans="1:14">
@@ -7997,22 +9070,22 @@
         <v>26</v>
       </c>
       <c r="G7" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H7" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J7" t="b">
         <v>0</v>
       </c>
       <c r="K7" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L7" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M7" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="8" spans="1:14">
@@ -8026,22 +9099,22 @@
         <v>35</v>
       </c>
       <c r="G8" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H8" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="J8" t="b">
         <v>0</v>
       </c>
       <c r="K8" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L8" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M8" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="9" spans="1:14">
@@ -8055,22 +9128,22 @@
         <v>44</v>
       </c>
       <c r="G9" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="J9" t="b">
         <v>0</v>
       </c>
       <c r="K9" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L9" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M9" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="10" spans="1:14">
@@ -8084,22 +9157,22 @@
         <v>53</v>
       </c>
       <c r="G10" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H10" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="J10" t="b">
         <v>0</v>
       </c>
       <c r="K10" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L10" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M10" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="11" spans="1:14">
@@ -8113,22 +9186,22 @@
         <v>60</v>
       </c>
       <c r="G11" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H11" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="J11" t="b">
         <v>1</v>
       </c>
       <c r="K11" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L11" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="M11" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="12" spans="1:14">
@@ -8142,22 +9215,22 @@
         <v>67</v>
       </c>
       <c r="G12" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="H12" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="J12" t="b">
         <v>1</v>
       </c>
       <c r="K12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="L12" t="s">
-        <v>298</v>
+        <v>309</v>
       </c>
       <c r="M12" t="s">
-        <v>297</v>
+        <v>308</v>
       </c>
     </row>
     <row r="13" spans="1:14">
@@ -8165,31 +9238,31 @@
         <v>1009</v>
       </c>
       <c r="C13" s="5" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="D13" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
       <c r="G13" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="H13" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="J13" t="b">
         <v>0</v>
       </c>
       <c r="K13" t="s">
-        <v>296</v>
+        <v>307</v>
       </c>
       <c r="L13" t="s">
-        <v>301</v>
+        <v>312</v>
       </c>
       <c r="M13" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="N13" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="14" spans="1:14">
@@ -8197,10 +9270,10 @@
         <v>2001</v>
       </c>
       <c r="C14" s="5" t="s">
-        <v>304</v>
+        <v>315</v>
       </c>
       <c r="D14" s="5" t="s">
-        <v>305</v>
+        <v>316</v>
       </c>
       <c r="E14" s="5" t="s">
         <v>7</v>
@@ -8209,7 +9282,7 @@
         <v>8</v>
       </c>
       <c r="N14" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="15" spans="1:14">
@@ -8217,10 +9290,10 @@
         <v>2002</v>
       </c>
       <c r="C15" s="5" t="s">
-        <v>307</v>
+        <v>318</v>
       </c>
       <c r="D15" s="5" t="s">
-        <v>308</v>
+        <v>319</v>
       </c>
       <c r="E15" s="5" t="s">
         <v>7</v>
@@ -8229,7 +9302,7 @@
         <v>8</v>
       </c>
       <c r="N15" t="s">
-        <v>306</v>
+        <v>317</v>
       </c>
     </row>
     <row r="16" spans="1:14">
@@ -8237,10 +9310,10 @@
         <v>2003</v>
       </c>
       <c r="C16" s="5" t="s">
-        <v>309</v>
+        <v>320</v>
       </c>
       <c r="D16" s="5" t="s">
-        <v>310</v>
+        <v>321</v>
       </c>
       <c r="E16" s="5" t="s">
         <v>16</v>
@@ -8249,7 +9322,7 @@
         <v>17</v>
       </c>
       <c r="N16" t="s">
-        <v>311</v>
+        <v>322</v>
       </c>
     </row>
     <row r="17" spans="2:14">
@@ -8257,19 +9330,19 @@
         <v>2004</v>
       </c>
       <c r="C17" s="5" t="s">
-        <v>312</v>
+        <v>323</v>
       </c>
       <c r="D17" s="5" t="s">
-        <v>313</v>
+        <v>324</v>
       </c>
       <c r="E17" s="5" t="s">
-        <v>314</v>
+        <v>325</v>
       </c>
       <c r="F17" t="s">
-        <v>315</v>
+        <v>326</v>
       </c>
       <c r="N17" t="s">
-        <v>316</v>
+        <v>327</v>
       </c>
     </row>
     <row r="18" spans="2:14">
@@ -8277,10 +9350,10 @@
         <v>2005</v>
       </c>
       <c r="C18" s="5" t="s">
-        <v>317</v>
+        <v>328</v>
       </c>
       <c r="D18" s="5" t="s">
-        <v>318</v>
+        <v>329</v>
       </c>
       <c r="E18" s="5" t="s">
         <v>59</v>
@@ -8289,7 +9362,7 @@
         <v>60</v>
       </c>
       <c r="N18" t="s">
-        <v>319</v>
+        <v>330</v>
       </c>
     </row>
     <row r="19" spans="2:14">
@@ -8297,10 +9370,10 @@
         <v>2006</v>
       </c>
       <c r="C19" s="5" t="s">
-        <v>320</v>
+        <v>331</v>
       </c>
       <c r="D19" s="5" t="s">
-        <v>321</v>
+        <v>332</v>
       </c>
       <c r="E19" s="5" t="s">
         <v>66</v>
@@ -8309,7 +9382,7 @@
         <v>67</v>
       </c>
       <c r="N19" t="s">
-        <v>322</v>
+        <v>333</v>
       </c>
     </row>
     <row r="20" spans="2:14">
@@ -8317,10 +9390,10 @@
         <v>2007</v>
       </c>
       <c r="C20" s="5" t="s">
-        <v>323</v>
+        <v>334</v>
       </c>
       <c r="D20" s="5" t="s">
-        <v>324</v>
+        <v>335</v>
       </c>
       <c r="E20" s="5" t="s">
         <v>16</v>
@@ -8329,7 +9402,7 @@
         <v>17</v>
       </c>
       <c r="N20" t="s">
-        <v>325</v>
+        <v>336</v>
       </c>
     </row>
     <row r="21" spans="2:14">
@@ -8337,19 +9410,19 @@
         <v>2008</v>
       </c>
       <c r="C21" s="5" t="s">
+        <v>337</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>338</v>
+      </c>
+      <c r="E21" t="s">
+        <v>325</v>
+      </c>
+      <c r="F21" t="s">
         <v>326</v>
       </c>
-      <c r="D21" s="5" t="s">
-        <v>327</v>
-      </c>
-      <c r="E21" t="s">
-        <v>314</v>
-      </c>
-      <c r="F21" t="s">
-        <v>315</v>
-      </c>
       <c r="N21" t="s">
-        <v>328</v>
+        <v>339</v>
       </c>
     </row>
     <row r="22" spans="2:14">
@@ -8357,16 +9430,16 @@
         <v>2009</v>
       </c>
       <c r="C22" s="5" t="s">
-        <v>329</v>
+        <v>340</v>
       </c>
       <c r="D22" s="5" t="s">
-        <v>330</v>
+        <v>341</v>
       </c>
       <c r="E22" s="5" t="s">
-        <v>299</v>
+        <v>310</v>
       </c>
       <c r="F22" s="5" t="s">
-        <v>300</v>
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="2:14">
@@ -8374,10 +9447,10 @@
         <v>3001</v>
       </c>
       <c r="C23" s="5" t="s">
-        <v>331</v>
+        <v>342</v>
       </c>
       <c r="D23" s="5" t="s">
-        <v>332</v>
+        <v>343</v>
       </c>
       <c r="E23" s="5" t="s">
         <v>25</v>
@@ -8391,10 +9464,10 @@
         <v>3002</v>
       </c>
       <c r="C24" s="5" t="s">
-        <v>333</v>
+        <v>344</v>
       </c>
       <c r="D24" s="5" t="s">
-        <v>334</v>
+        <v>345</v>
       </c>
       <c r="E24" s="5" t="s">
         <v>25</v>
@@ -8408,10 +9481,10 @@
         <v>3003</v>
       </c>
       <c r="C25" s="5" t="s">
-        <v>335</v>
+        <v>346</v>
       </c>
       <c r="D25" s="5" t="s">
-        <v>336</v>
+        <v>347</v>
       </c>
       <c r="E25" s="5" t="s">
         <v>34</v>
@@ -8425,10 +9498,10 @@
         <v>3004</v>
       </c>
       <c r="C26" s="5" t="s">
-        <v>337</v>
+        <v>348</v>
       </c>
       <c r="D26" s="5" t="s">
-        <v>338</v>
+        <v>349</v>
       </c>
       <c r="E26" s="5" t="s">
         <v>34</v>
@@ -8442,10 +9515,10 @@
         <v>3005</v>
       </c>
       <c r="C27" s="5" t="s">
-        <v>339</v>
+        <v>350</v>
       </c>
       <c r="D27" s="5" t="s">
-        <v>340</v>
+        <v>351</v>
       </c>
       <c r="E27" s="5" t="s">
         <v>43</v>
@@ -8459,10 +9532,10 @@
         <v>3006</v>
       </c>
       <c r="C28" s="5" t="s">
-        <v>341</v>
+        <v>352</v>
       </c>
       <c r="D28" s="5" t="s">
-        <v>342</v>
+        <v>353</v>
       </c>
       <c r="E28" s="5" t="s">
         <v>43</v>
@@ -8476,10 +9549,10 @@
         <v>3007</v>
       </c>
       <c r="C29" s="5" t="s">
-        <v>343</v>
+        <v>354</v>
       </c>
       <c r="D29" s="5" t="s">
-        <v>344</v>
+        <v>355</v>
       </c>
       <c r="E29" s="5" t="s">
         <v>43</v>
@@ -8488,10 +9561,10 @@
         <v>44</v>
       </c>
       <c r="M29" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="N29" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="30" spans="2:14">
@@ -8499,10 +9572,10 @@
         <v>3008</v>
       </c>
       <c r="C30" s="5" t="s">
-        <v>345</v>
+        <v>356</v>
       </c>
       <c r="D30" s="5" t="s">
-        <v>346</v>
+        <v>357</v>
       </c>
       <c r="E30" s="5" t="s">
         <v>52</v>
@@ -8516,10 +9589,10 @@
         <v>3009</v>
       </c>
       <c r="C31" s="5" t="s">
-        <v>347</v>
+        <v>358</v>
       </c>
       <c r="D31" s="5" t="s">
-        <v>348</v>
+        <v>359</v>
       </c>
       <c r="E31" s="5" t="s">
         <v>52</v>
@@ -8533,10 +9606,10 @@
         <v>3010</v>
       </c>
       <c r="C32" s="5" t="s">
-        <v>349</v>
+        <v>360</v>
       </c>
       <c r="D32" s="5" t="s">
-        <v>350</v>
+        <v>361</v>
       </c>
       <c r="E32" s="5" t="s">
         <v>52</v>
@@ -8545,10 +9618,10 @@
         <v>53</v>
       </c>
       <c r="M32" t="s">
-        <v>302</v>
+        <v>313</v>
       </c>
       <c r="N32" t="s">
-        <v>303</v>
+        <v>314</v>
       </c>
     </row>
     <row r="33" customFormat="1" spans="2:14">
@@ -8556,10 +9629,10 @@
         <v>4001</v>
       </c>
       <c r="C33" s="5" t="s">
-        <v>351</v>
+        <v>362</v>
       </c>
       <c r="D33" s="5" t="s">
-        <v>352</v>
+        <v>363</v>
       </c>
       <c r="E33" s="5" t="s">
         <v>66</v>
@@ -8568,7 +9641,7 @@
         <v>67</v>
       </c>
       <c r="N33" t="s">
-        <v>353</v>
+        <v>364</v>
       </c>
     </row>
   </sheetData>
@@ -8604,31 +9677,31 @@
         <v>99</v>
       </c>
       <c r="C1" t="s">
-        <v>354</v>
+        <v>365</v>
       </c>
       <c r="D1" t="s">
-        <v>355</v>
+        <v>366</v>
       </c>
       <c r="E1" t="s">
-        <v>356</v>
+        <v>367</v>
       </c>
       <c r="F1" t="s">
-        <v>357</v>
+        <v>368</v>
       </c>
       <c r="G1" t="s">
-        <v>358</v>
+        <v>369</v>
       </c>
       <c r="H1" t="s">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="I1" t="s">
-        <v>359</v>
+        <v>370</v>
       </c>
       <c r="J1" t="s">
-        <v>360</v>
+        <v>371</v>
       </c>
       <c r="K1" t="s">
-        <v>280</v>
+        <v>290</v>
       </c>
     </row>
     <row r="2" spans="1:11">
@@ -8654,10 +9727,10 @@
         <v>158</v>
       </c>
       <c r="H2" t="s">
-        <v>281</v>
+        <v>291</v>
       </c>
       <c r="I2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="J2" t="s">
         <v>107</v>
@@ -8671,34 +9744,34 @@
         <v>110</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>361</v>
+        <v>372</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>362</v>
+        <v>373</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>363</v>
+        <v>374</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>364</v>
+        <v>375</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>365</v>
+        <v>376</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>366</v>
+        <v>377</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>367</v>
+        <v>378</v>
       </c>
       <c r="I3" s="1" t="s">
-        <v>368</v>
+        <v>379</v>
       </c>
       <c r="J3" s="1" t="s">
-        <v>369</v>
+        <v>380</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="4" spans="1:11">
@@ -8709,31 +9782,31 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>370</v>
+        <v>381</v>
       </c>
       <c r="D4" t="s">
-        <v>371</v>
+        <v>382</v>
       </c>
       <c r="E4" t="s">
-        <v>372</v>
+        <v>383</v>
       </c>
       <c r="F4" t="s">
-        <v>373</v>
+        <v>384</v>
       </c>
       <c r="G4" t="s">
-        <v>374</v>
+        <v>385</v>
       </c>
       <c r="H4" t="s">
-        <v>375</v>
+        <v>386</v>
       </c>
       <c r="I4" t="s">
-        <v>376</v>
+        <v>387</v>
       </c>
       <c r="J4" t="s">
-        <v>377</v>
+        <v>388</v>
       </c>
       <c r="K4" t="s">
-        <v>295</v>
+        <v>306</v>
       </c>
     </row>
     <row r="5" spans="1:11">
@@ -8741,7 +9814,7 @@
         <v>1</v>
       </c>
       <c r="C5" t="s">
-        <v>378</v>
+        <v>389</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8765,7 +9838,7 @@
         <v>1</v>
       </c>
       <c r="K5" t="s">
-        <v>379</v>
+        <v>390</v>
       </c>
     </row>
     <row r="6" spans="1:11">
@@ -8773,7 +9846,7 @@
         <v>2</v>
       </c>
       <c r="C6" t="s">
-        <v>380</v>
+        <v>391</v>
       </c>
       <c r="D6">
         <v>1</v>
@@ -8797,7 +9870,7 @@
         <v>2</v>
       </c>
       <c r="K6" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -8805,7 +9878,7 @@
         <v>3</v>
       </c>
       <c r="C7" t="s">
-        <v>382</v>
+        <v>393</v>
       </c>
       <c r="D7">
         <v>81</v>
@@ -8829,7 +9902,7 @@
         <v>3</v>
       </c>
       <c r="K7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -8837,7 +9910,7 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>383</v>
+        <v>394</v>
       </c>
       <c r="D8">
         <v>301</v>
@@ -8861,7 +9934,7 @@
         <v>4</v>
       </c>
       <c r="K8" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
     </row>
   </sheetData>
@@ -8892,16 +9965,16 @@
         <v>99</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="D1" t="s">
-        <v>384</v>
+        <v>395</v>
       </c>
       <c r="E1" t="s">
-        <v>385</v>
+        <v>396</v>
       </c>
       <c r="F1" t="s">
-        <v>386</v>
+        <v>397</v>
       </c>
     </row>
     <row r="2" spans="1:6">
@@ -8918,7 +9991,7 @@
         <v>158</v>
       </c>
       <c r="E2" t="s">
-        <v>282</v>
+        <v>292</v>
       </c>
       <c r="F2" t="s">
         <v>109</v>
@@ -8931,10 +10004,10 @@
       <c r="B3" s="3"/>
       <c r="C3" s="3"/>
       <c r="D3" s="1" t="s">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>388</v>
+        <v>399</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -8945,13 +10018,13 @@
         <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>389</v>
+        <v>400</v>
       </c>
       <c r="D4" t="s">
-        <v>390</v>
+        <v>401</v>
       </c>
       <c r="E4" t="s">
-        <v>391</v>
+        <v>402</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -8959,7 +10032,7 @@
         <v>1001</v>
       </c>
       <c r="C5" t="s">
-        <v>392</v>
+        <v>403</v>
       </c>
       <c r="D5">
         <v>0</v>
@@ -8968,7 +10041,7 @@
         <v>1</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>393</v>
+        <v>404</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -8976,7 +10049,7 @@
         <v>1002</v>
       </c>
       <c r="C6" t="s">
-        <v>394</v>
+        <v>405</v>
       </c>
       <c r="D6">
         <v>0</v>
@@ -8985,7 +10058,7 @@
         <v>1</v>
       </c>
       <c r="F6" s="5" t="s">
-        <v>395</v>
+        <v>406</v>
       </c>
     </row>
     <row r="7" spans="1:6">
@@ -8993,7 +10066,7 @@
         <v>1003</v>
       </c>
       <c r="C7" t="s">
-        <v>396</v>
+        <v>407</v>
       </c>
       <c r="D7">
         <v>0</v>
@@ -9002,7 +10075,7 @@
         <v>1</v>
       </c>
       <c r="F7" s="5" t="s">
-        <v>397</v>
+        <v>408</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -9010,7 +10083,7 @@
         <v>1004</v>
       </c>
       <c r="C8" t="s">
-        <v>398</v>
+        <v>409</v>
       </c>
       <c r="D8">
         <v>0</v>
@@ -9019,7 +10092,7 @@
         <v>1</v>
       </c>
       <c r="F8" s="5" t="s">
-        <v>399</v>
+        <v>410</v>
       </c>
     </row>
     <row r="9" spans="1:6">
@@ -9034,66 +10107,69 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:M32"/>
+  <dimension ref="A1:N32"/>
   <sheetFormatPr defaultColWidth="8.66666666666667" defaultRowHeight="17.4"/>
   <cols>
     <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
     <col min="2" max="2" width="13.4166666666667" customWidth="1"/>
-    <col min="3" max="3" width="28.6666666666667" customWidth="1"/>
-    <col min="4" max="4" width="19.0833333333333" customWidth="1"/>
-    <col min="5" max="5" width="29.4166666666667" customWidth="1"/>
-    <col min="6" max="6" width="22.25" customWidth="1"/>
-    <col min="7" max="7" width="25" customWidth="1"/>
-    <col min="8" max="8" width="42.5" customWidth="1"/>
-    <col min="9" max="9" width="33.9166666666667" customWidth="1"/>
-    <col min="10" max="10" width="59.9166666666667" customWidth="1"/>
-    <col min="11" max="11" width="33.9166666666667" customWidth="1"/>
-    <col min="12" max="12" width="38.8333333333333" customWidth="1"/>
-    <col min="13" max="13" width="85.4166666666667" customWidth="1"/>
+    <col min="3" max="4" width="28.6666666666667" customWidth="1"/>
+    <col min="5" max="5" width="19.0833333333333" customWidth="1"/>
+    <col min="6" max="6" width="29.4166666666667" customWidth="1"/>
+    <col min="7" max="7" width="22.25" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="42.5" customWidth="1"/>
+    <col min="10" max="10" width="33.9166666666667" customWidth="1"/>
+    <col min="11" max="11" width="59.9166666666667" customWidth="1"/>
+    <col min="12" max="12" width="33.9166666666667" customWidth="1"/>
+    <col min="13" max="13" width="38.8333333333333" customWidth="1"/>
+    <col min="14" max="14" width="85.4166666666667" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13">
+    <row r="1" spans="1:14">
       <c r="A1" s="2" t="s">
         <v>98</v>
       </c>
       <c r="B1" t="s">
-        <v>400</v>
+        <v>411</v>
       </c>
       <c r="C1" t="s">
-        <v>401</v>
+        <v>412</v>
       </c>
       <c r="D1" t="s">
-        <v>402</v>
+        <v>413</v>
       </c>
       <c r="E1" t="s">
-        <v>403</v>
+        <v>414</v>
       </c>
       <c r="F1" t="s">
-        <v>404</v>
+        <v>415</v>
       </c>
       <c r="G1" t="s">
-        <v>405</v>
+        <v>416</v>
       </c>
       <c r="H1" t="s">
-        <v>280</v>
+        <v>417</v>
       </c>
       <c r="I1" t="s">
-        <v>406</v>
+        <v>290</v>
       </c>
       <c r="J1" t="s">
-        <v>407</v>
+        <v>418</v>
       </c>
       <c r="K1" t="s">
-        <v>408</v>
+        <v>419</v>
       </c>
       <c r="L1" t="s">
-        <v>409</v>
+        <v>420</v>
       </c>
       <c r="M1" t="s">
-        <v>410</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13">
+        <v>421</v>
+      </c>
+      <c r="N1" t="s">
+        <v>422</v>
+      </c>
+    </row>
+    <row r="2" spans="1:14">
       <c r="A2" s="2" t="s">
         <v>106</v>
       </c>
@@ -9104,19 +10180,19 @@
         <v>109</v>
       </c>
       <c r="D2" t="s">
-        <v>411</v>
+        <v>292</v>
       </c>
       <c r="E2" t="s">
+        <v>423</v>
+      </c>
+      <c r="F2" t="s">
         <v>109</v>
       </c>
-      <c r="F2" t="s">
-        <v>412</v>
-      </c>
       <c r="G2" t="s">
-        <v>282</v>
+        <v>424</v>
       </c>
       <c r="H2" t="s">
-        <v>109</v>
+        <v>292</v>
       </c>
       <c r="I2" t="s">
         <v>109</v>
@@ -9133,1229 +10209,1327 @@
       <c r="M2" t="s">
         <v>109</v>
       </c>
-    </row>
-    <row r="3" ht="150" customHeight="1" spans="1:13">
+      <c r="N2" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="3" ht="150" customHeight="1" spans="1:14">
       <c r="A3" s="3" t="s">
         <v>110</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>413</v>
+        <v>425</v>
       </c>
       <c r="C3" s="1" t="s">
-        <v>414</v>
+        <v>426</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>415</v>
+        <v>427</v>
       </c>
       <c r="E3" s="1" t="s">
-        <v>416</v>
+        <v>428</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>417</v>
+        <v>429</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>418</v>
+        <v>430</v>
       </c>
       <c r="H3" s="1" t="s">
-        <v>419</v>
-      </c>
-      <c r="I3" t="s">
-        <v>420</v>
+        <v>431</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>432</v>
       </c>
       <c r="J3" t="s">
-        <v>421</v>
+        <v>433</v>
       </c>
       <c r="K3" t="s">
-        <v>422</v>
+        <v>434</v>
       </c>
       <c r="L3" t="s">
-        <v>423</v>
+        <v>435</v>
       </c>
       <c r="M3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="4" spans="1:13">
+        <v>436</v>
+      </c>
+      <c r="N3" t="s">
+        <v>437</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14">
       <c r="A4" t="s">
         <v>110</v>
       </c>
       <c r="B4" t="s">
-        <v>425</v>
+        <v>438</v>
       </c>
       <c r="C4" t="s">
-        <v>426</v>
+        <v>439</v>
       </c>
       <c r="D4" t="s">
-        <v>427</v>
+        <v>440</v>
       </c>
       <c r="E4" t="s">
-        <v>428</v>
+        <v>441</v>
       </c>
       <c r="F4" t="s">
-        <v>429</v>
+        <v>442</v>
       </c>
       <c r="G4" t="s">
-        <v>430</v>
+        <v>443</v>
       </c>
       <c r="H4" t="s">
-        <v>295</v>
+        <v>444</v>
       </c>
       <c r="I4" t="s">
-        <v>431</v>
+        <v>306</v>
       </c>
       <c r="J4" t="s">
-        <v>432</v>
+        <v>445</v>
       </c>
       <c r="K4" t="s">
-        <v>433</v>
+        <v>446</v>
       </c>
       <c r="L4" t="s">
-        <v>434</v>
+        <v>447</v>
       </c>
       <c r="M4" t="s">
-        <v>435</v>
-      </c>
-    </row>
-    <row r="5" spans="1:13">
+        <v>448</v>
+      </c>
+      <c r="N4" t="s">
+        <v>449</v>
+      </c>
+    </row>
+    <row r="5" spans="1:14">
       <c r="A5" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B5">
         <v>1000</v>
       </c>
       <c r="C5" t="s">
-        <v>436</v>
-      </c>
-      <c r="D5" t="s">
-        <v>437</v>
+        <v>450</v>
+      </c>
+      <c r="D5" t="b">
+        <v>1</v>
       </c>
       <c r="E5" t="s">
+        <v>451</v>
+      </c>
+      <c r="F5" t="s">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>1</v>
-      </c>
-      <c r="G5" t="b">
+      <c r="G5">
+        <v>1</v>
+      </c>
+      <c r="H5" t="b">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>438</v>
-      </c>
       <c r="I5" t="s">
-        <v>439</v>
+        <v>452</v>
       </c>
       <c r="J5" t="s">
-        <v>440</v>
+        <v>453</v>
       </c>
       <c r="K5" t="s">
-        <v>441</v>
+        <v>454</v>
       </c>
       <c r="L5" t="s">
-        <v>442</v>
+        <v>455</v>
       </c>
       <c r="M5" t="s">
-        <v>443</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13">
+        <v>456</v>
+      </c>
+      <c r="N5" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="6" spans="1:14">
       <c r="A6" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B6">
         <v>1001</v>
       </c>
       <c r="C6" t="s">
-        <v>444</v>
-      </c>
-      <c r="D6" t="s">
-        <v>437</v>
+        <v>458</v>
+      </c>
+      <c r="D6" t="b">
+        <v>1</v>
       </c>
       <c r="E6" t="s">
+        <v>451</v>
+      </c>
+      <c r="F6" t="s">
         <v>9</v>
       </c>
-      <c r="F6">
-        <v>1</v>
-      </c>
-      <c r="G6" t="b">
+      <c r="G6">
+        <v>1</v>
+      </c>
+      <c r="H6" t="b">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>445</v>
-      </c>
       <c r="I6" t="s">
-        <v>446</v>
+        <v>459</v>
       </c>
       <c r="J6" t="s">
-        <v>447</v>
+        <v>460</v>
       </c>
       <c r="K6" t="s">
-        <v>448</v>
+        <v>461</v>
       </c>
       <c r="L6" t="s">
-        <v>449</v>
+        <v>462</v>
       </c>
       <c r="M6" t="s">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13">
+        <v>463</v>
+      </c>
+      <c r="N6" t="s">
+        <v>464</v>
+      </c>
+    </row>
+    <row r="7" spans="1:14">
       <c r="A7" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B7">
         <v>1002</v>
       </c>
       <c r="C7" t="s">
+        <v>465</v>
+      </c>
+      <c r="D7" t="b">
+        <v>0</v>
+      </c>
+      <c r="E7" t="s">
         <v>451</v>
       </c>
-      <c r="D7" t="s">
-        <v>437</v>
-      </c>
-      <c r="E7" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="F7">
-        <v>1</v>
-      </c>
-      <c r="G7" t="b">
+      <c r="G7">
+        <v>1</v>
+      </c>
+      <c r="H7" t="b">
         <v>0</v>
       </c>
-      <c r="H7" t="s">
-        <v>452</v>
-      </c>
       <c r="I7" t="s">
-        <v>453</v>
+        <v>466</v>
       </c>
       <c r="J7" t="s">
-        <v>454</v>
+        <v>467</v>
       </c>
       <c r="K7" t="s">
-        <v>455</v>
+        <v>468</v>
       </c>
       <c r="L7" t="s">
-        <v>456</v>
+        <v>469</v>
       </c>
       <c r="M7" t="s">
-        <v>457</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13">
+        <v>470</v>
+      </c>
+      <c r="N7" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="8" spans="1:14">
       <c r="A8" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B8">
         <v>1003</v>
       </c>
       <c r="C8" t="s">
-        <v>458</v>
-      </c>
-      <c r="D8" t="s">
-        <v>437</v>
+        <v>472</v>
+      </c>
+      <c r="D8" t="b">
+        <v>1</v>
       </c>
       <c r="E8" t="s">
+        <v>451</v>
+      </c>
+      <c r="F8" t="s">
         <v>27</v>
       </c>
-      <c r="F8">
-        <v>1</v>
-      </c>
-      <c r="G8" t="b">
+      <c r="G8">
+        <v>1</v>
+      </c>
+      <c r="H8" t="b">
         <v>0</v>
       </c>
-      <c r="H8" s="4" t="s">
-        <v>459</v>
-      </c>
-      <c r="I8" t="s">
-        <v>460</v>
+      <c r="I8" s="4" t="s">
+        <v>473</v>
       </c>
       <c r="J8" t="s">
-        <v>461</v>
+        <v>474</v>
       </c>
       <c r="K8" t="s">
-        <v>462</v>
+        <v>475</v>
       </c>
       <c r="L8" t="s">
-        <v>463</v>
+        <v>476</v>
       </c>
       <c r="M8" t="s">
-        <v>464</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13">
+        <v>477</v>
+      </c>
+      <c r="N8" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="9" spans="1:14">
       <c r="A9" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B9">
         <v>1004</v>
       </c>
       <c r="C9" t="s">
-        <v>465</v>
-      </c>
-      <c r="D9" t="s">
-        <v>437</v>
+        <v>479</v>
+      </c>
+      <c r="D9" t="b">
+        <v>1</v>
       </c>
       <c r="E9" t="s">
+        <v>451</v>
+      </c>
+      <c r="F9" t="s">
         <v>36</v>
       </c>
-      <c r="F9">
-        <v>1</v>
-      </c>
-      <c r="G9" t="b">
+      <c r="G9">
+        <v>1</v>
+      </c>
+      <c r="H9" t="b">
         <v>0</v>
       </c>
-      <c r="H9" t="s">
-        <v>466</v>
-      </c>
       <c r="I9" t="s">
-        <v>467</v>
+        <v>480</v>
       </c>
       <c r="J9" t="s">
-        <v>468</v>
+        <v>481</v>
       </c>
       <c r="K9" t="s">
-        <v>469</v>
+        <v>482</v>
       </c>
       <c r="L9" t="s">
-        <v>470</v>
+        <v>483</v>
       </c>
       <c r="M9" t="s">
-        <v>471</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13">
+        <v>484</v>
+      </c>
+      <c r="N9" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="10" spans="1:14">
       <c r="A10" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B10">
         <v>1005</v>
       </c>
       <c r="C10" t="s">
-        <v>472</v>
-      </c>
-      <c r="D10" t="s">
-        <v>437</v>
+        <v>486</v>
+      </c>
+      <c r="D10" t="b">
+        <v>1</v>
       </c>
       <c r="E10" t="s">
+        <v>451</v>
+      </c>
+      <c r="F10" t="s">
         <v>45</v>
       </c>
-      <c r="F10">
-        <v>1</v>
-      </c>
-      <c r="G10" t="b">
+      <c r="G10">
+        <v>1</v>
+      </c>
+      <c r="H10" t="b">
         <v>0</v>
       </c>
-      <c r="H10" t="s">
-        <v>473</v>
-      </c>
       <c r="I10" t="s">
-        <v>474</v>
+        <v>487</v>
       </c>
       <c r="J10" t="s">
-        <v>475</v>
+        <v>488</v>
       </c>
       <c r="K10" t="s">
-        <v>476</v>
+        <v>489</v>
       </c>
       <c r="L10" t="s">
-        <v>477</v>
+        <v>490</v>
       </c>
       <c r="M10" t="s">
-        <v>478</v>
-      </c>
-    </row>
-    <row r="11" spans="1:13">
+        <v>491</v>
+      </c>
+      <c r="N10" t="s">
+        <v>492</v>
+      </c>
+    </row>
+    <row r="11" spans="1:14">
       <c r="A11" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B11">
         <v>1006</v>
       </c>
       <c r="C11" t="s">
-        <v>479</v>
-      </c>
-      <c r="D11" t="s">
-        <v>437</v>
+        <v>493</v>
+      </c>
+      <c r="D11" t="b">
+        <v>1</v>
       </c>
       <c r="E11" t="s">
+        <v>451</v>
+      </c>
+      <c r="F11" t="s">
         <v>54</v>
       </c>
-      <c r="F11">
-        <v>1</v>
-      </c>
-      <c r="G11" t="b">
+      <c r="G11">
+        <v>1</v>
+      </c>
+      <c r="H11" t="b">
         <v>0</v>
       </c>
-      <c r="H11" t="s">
-        <v>480</v>
-      </c>
       <c r="I11" t="s">
-        <v>481</v>
+        <v>494</v>
       </c>
       <c r="J11" t="s">
-        <v>482</v>
+        <v>495</v>
       </c>
       <c r="K11" t="s">
-        <v>483</v>
+        <v>496</v>
       </c>
       <c r="L11" t="s">
-        <v>484</v>
+        <v>497</v>
       </c>
       <c r="M11" t="s">
-        <v>485</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13">
+        <v>498</v>
+      </c>
+      <c r="N11" t="s">
+        <v>499</v>
+      </c>
+    </row>
+    <row r="12" spans="1:14">
       <c r="A12" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B12">
         <v>1007</v>
       </c>
       <c r="C12" t="s">
-        <v>486</v>
-      </c>
-      <c r="D12" t="s">
-        <v>437</v>
+        <v>500</v>
+      </c>
+      <c r="D12" t="b">
+        <v>1</v>
       </c>
       <c r="E12" t="s">
+        <v>451</v>
+      </c>
+      <c r="F12" t="s">
         <v>61</v>
       </c>
-      <c r="F12">
-        <v>1</v>
-      </c>
-      <c r="G12" t="b">
+      <c r="G12">
+        <v>1</v>
+      </c>
+      <c r="H12" t="b">
         <v>0</v>
       </c>
-      <c r="H12" t="s">
-        <v>487</v>
-      </c>
       <c r="I12" t="s">
-        <v>488</v>
+        <v>501</v>
       </c>
       <c r="J12" t="s">
-        <v>489</v>
+        <v>502</v>
       </c>
       <c r="K12" t="s">
-        <v>490</v>
+        <v>503</v>
       </c>
       <c r="L12" t="s">
-        <v>491</v>
+        <v>504</v>
       </c>
       <c r="M12" t="s">
-        <v>492</v>
-      </c>
-    </row>
-    <row r="13" spans="1:13">
+        <v>505</v>
+      </c>
+      <c r="N12" t="s">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="13" spans="1:14">
       <c r="A13" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B13">
         <v>1008</v>
       </c>
       <c r="C13" t="s">
-        <v>493</v>
-      </c>
-      <c r="D13" t="s">
-        <v>437</v>
+        <v>507</v>
+      </c>
+      <c r="D13" t="b">
+        <v>1</v>
       </c>
       <c r="E13" t="s">
+        <v>451</v>
+      </c>
+      <c r="F13" t="s">
         <v>68</v>
       </c>
-      <c r="F13">
-        <v>1</v>
-      </c>
-      <c r="G13" t="b">
+      <c r="G13">
+        <v>1</v>
+      </c>
+      <c r="H13" t="b">
         <v>0</v>
       </c>
-      <c r="H13" t="s">
-        <v>494</v>
-      </c>
       <c r="I13" t="s">
-        <v>495</v>
+        <v>508</v>
       </c>
       <c r="J13" t="s">
-        <v>496</v>
+        <v>509</v>
       </c>
       <c r="K13" t="s">
-        <v>497</v>
+        <v>510</v>
       </c>
       <c r="L13" t="s">
-        <v>498</v>
+        <v>511</v>
       </c>
       <c r="M13" t="s">
-        <v>499</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13">
+        <v>512</v>
+      </c>
+      <c r="N13" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="14" spans="1:14">
       <c r="A14" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B14">
         <v>1009</v>
       </c>
       <c r="C14" t="s">
-        <v>500</v>
-      </c>
-      <c r="D14" t="s">
-        <v>437</v>
+        <v>514</v>
+      </c>
+      <c r="D14" t="b">
+        <v>1</v>
       </c>
       <c r="E14" t="s">
+        <v>451</v>
+      </c>
+      <c r="F14" t="s">
         <v>73</v>
       </c>
-      <c r="F14">
-        <v>1</v>
-      </c>
-      <c r="G14" t="b">
-        <v>1</v>
-      </c>
-      <c r="H14" t="s">
-        <v>501</v>
+      <c r="G14">
+        <v>1</v>
+      </c>
+      <c r="H14" t="b">
+        <v>1</v>
       </c>
       <c r="I14" t="s">
-        <v>502</v>
+        <v>515</v>
       </c>
       <c r="J14" t="s">
-        <v>503</v>
+        <v>516</v>
       </c>
       <c r="K14" t="s">
-        <v>504</v>
+        <v>517</v>
       </c>
       <c r="L14" t="s">
-        <v>505</v>
+        <v>518</v>
       </c>
       <c r="M14" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13">
+        <v>519</v>
+      </c>
+      <c r="N14" t="s">
+        <v>520</v>
+      </c>
+    </row>
+    <row r="15" spans="1:14">
       <c r="A15" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B15">
         <v>1010</v>
       </c>
       <c r="C15" t="s">
-        <v>507</v>
-      </c>
-      <c r="D15" t="s">
-        <v>437</v>
+        <v>521</v>
+      </c>
+      <c r="D15" t="b">
+        <v>1</v>
       </c>
       <c r="E15" t="s">
+        <v>451</v>
+      </c>
+      <c r="F15" t="s">
         <v>78</v>
       </c>
-      <c r="F15">
-        <v>1</v>
-      </c>
-      <c r="G15" t="b">
-        <v>1</v>
-      </c>
-      <c r="H15" t="s">
-        <v>508</v>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="H15" t="b">
+        <v>1</v>
       </c>
       <c r="I15" t="s">
-        <v>509</v>
+        <v>522</v>
       </c>
       <c r="J15" t="s">
-        <v>510</v>
+        <v>523</v>
       </c>
       <c r="K15" t="s">
-        <v>511</v>
+        <v>524</v>
       </c>
       <c r="L15" t="s">
-        <v>512</v>
+        <v>525</v>
       </c>
       <c r="M15" t="s">
-        <v>513</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13">
+        <v>526</v>
+      </c>
+      <c r="N15" t="s">
+        <v>527</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14">
       <c r="A16" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B16">
         <v>1101</v>
       </c>
       <c r="C16" t="s">
-        <v>514</v>
-      </c>
-      <c r="D16" t="s">
-        <v>515</v>
+        <v>528</v>
+      </c>
+      <c r="D16" t="b">
+        <v>1</v>
       </c>
       <c r="E16" t="s">
-        <v>516</v>
-      </c>
-      <c r="F16">
-        <v>1</v>
-      </c>
-      <c r="G16" t="b">
+        <v>529</v>
+      </c>
+      <c r="F16" t="s">
+        <v>530</v>
+      </c>
+      <c r="G16">
+        <v>1</v>
+      </c>
+      <c r="H16" t="b">
         <v>0</v>
       </c>
-      <c r="H16" t="s">
-        <v>517</v>
-      </c>
       <c r="I16" t="s">
-        <v>518</v>
+        <v>531</v>
       </c>
       <c r="J16" t="s">
-        <v>519</v>
+        <v>532</v>
       </c>
       <c r="K16" t="s">
-        <v>520</v>
+        <v>533</v>
       </c>
       <c r="L16" t="s">
-        <v>521</v>
+        <v>534</v>
       </c>
       <c r="M16" t="s">
-        <v>522</v>
-      </c>
-    </row>
-    <row r="17" spans="1:13">
+        <v>535</v>
+      </c>
+      <c r="N16" t="s">
+        <v>536</v>
+      </c>
+    </row>
+    <row r="17" spans="1:14">
       <c r="A17" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B17">
         <v>1102</v>
       </c>
       <c r="C17" t="s">
-        <v>523</v>
-      </c>
-      <c r="D17" t="s">
-        <v>515</v>
+        <v>537</v>
+      </c>
+      <c r="D17" t="b">
+        <v>1</v>
       </c>
       <c r="E17" t="s">
-        <v>524</v>
-      </c>
-      <c r="F17">
-        <v>1</v>
-      </c>
-      <c r="G17" t="b">
+        <v>529</v>
+      </c>
+      <c r="F17" t="s">
+        <v>538</v>
+      </c>
+      <c r="G17">
+        <v>1</v>
+      </c>
+      <c r="H17" t="b">
         <v>0</v>
       </c>
-      <c r="H17" t="s">
-        <v>525</v>
-      </c>
       <c r="I17" t="s">
-        <v>526</v>
+        <v>539</v>
       </c>
       <c r="J17" t="s">
-        <v>527</v>
+        <v>540</v>
       </c>
       <c r="K17" t="s">
-        <v>528</v>
+        <v>541</v>
       </c>
       <c r="L17" t="s">
-        <v>529</v>
+        <v>542</v>
       </c>
       <c r="M17" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="18" spans="1:13">
+        <v>543</v>
+      </c>
+      <c r="N17" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="18" spans="1:14">
       <c r="A18" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B18">
         <v>1103</v>
       </c>
       <c r="C18" t="s">
-        <v>531</v>
-      </c>
-      <c r="D18" t="s">
-        <v>515</v>
+        <v>545</v>
+      </c>
+      <c r="D18" t="b">
+        <v>1</v>
       </c>
       <c r="E18" t="s">
-        <v>532</v>
-      </c>
-      <c r="F18">
-        <v>1</v>
-      </c>
-      <c r="G18" t="b">
+        <v>529</v>
+      </c>
+      <c r="F18" t="s">
+        <v>546</v>
+      </c>
+      <c r="G18">
+        <v>1</v>
+      </c>
+      <c r="H18" t="b">
         <v>0</v>
       </c>
-      <c r="H18" t="s">
-        <v>533</v>
-      </c>
       <c r="I18" t="s">
-        <v>534</v>
+        <v>547</v>
       </c>
       <c r="J18" t="s">
-        <v>535</v>
+        <v>548</v>
       </c>
       <c r="K18" t="s">
-        <v>536</v>
+        <v>549</v>
       </c>
       <c r="L18" t="s">
-        <v>537</v>
+        <v>550</v>
       </c>
       <c r="M18" t="s">
-        <v>538</v>
-      </c>
-    </row>
-    <row r="19" spans="1:13">
+        <v>551</v>
+      </c>
+      <c r="N18" t="s">
+        <v>552</v>
+      </c>
+    </row>
+    <row r="19" spans="1:14">
       <c r="A19" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B19">
         <v>1104</v>
       </c>
       <c r="C19" t="s">
-        <v>539</v>
-      </c>
-      <c r="D19" t="s">
-        <v>515</v>
+        <v>553</v>
+      </c>
+      <c r="D19" t="b">
+        <v>1</v>
       </c>
       <c r="E19" t="s">
-        <v>540</v>
-      </c>
-      <c r="F19">
-        <v>1</v>
-      </c>
-      <c r="G19" t="b">
+        <v>529</v>
+      </c>
+      <c r="F19" t="s">
+        <v>554</v>
+      </c>
+      <c r="G19">
+        <v>1</v>
+      </c>
+      <c r="H19" t="b">
         <v>0</v>
       </c>
-      <c r="H19" t="s">
-        <v>541</v>
-      </c>
       <c r="I19" t="s">
-        <v>542</v>
+        <v>555</v>
       </c>
       <c r="J19" t="s">
-        <v>543</v>
+        <v>556</v>
       </c>
       <c r="K19" t="s">
-        <v>544</v>
+        <v>557</v>
       </c>
       <c r="L19" t="s">
-        <v>545</v>
+        <v>558</v>
       </c>
       <c r="M19" t="s">
-        <v>546</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13">
+        <v>559</v>
+      </c>
+      <c r="N19" t="s">
+        <v>560</v>
+      </c>
+    </row>
+    <row r="20" spans="1:14">
       <c r="A20" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B20">
         <v>1105</v>
       </c>
       <c r="C20" t="s">
-        <v>547</v>
-      </c>
-      <c r="D20" t="s">
-        <v>515</v>
+        <v>561</v>
+      </c>
+      <c r="D20" t="b">
+        <v>1</v>
       </c>
       <c r="E20" t="s">
-        <v>548</v>
-      </c>
-      <c r="F20">
-        <v>1</v>
-      </c>
-      <c r="G20" t="b">
+        <v>529</v>
+      </c>
+      <c r="F20" t="s">
+        <v>562</v>
+      </c>
+      <c r="G20">
+        <v>1</v>
+      </c>
+      <c r="H20" t="b">
         <v>0</v>
       </c>
-      <c r="H20" t="s">
-        <v>549</v>
-      </c>
       <c r="I20" t="s">
-        <v>550</v>
+        <v>563</v>
       </c>
       <c r="J20" t="s">
-        <v>551</v>
+        <v>564</v>
       </c>
       <c r="K20" t="s">
-        <v>552</v>
+        <v>565</v>
       </c>
       <c r="L20" t="s">
-        <v>553</v>
+        <v>566</v>
       </c>
       <c r="M20" t="s">
-        <v>554</v>
-      </c>
-    </row>
-    <row r="21" spans="1:13">
+        <v>567</v>
+      </c>
+      <c r="N20" t="s">
+        <v>568</v>
+      </c>
+    </row>
+    <row r="21" spans="1:14">
       <c r="A21" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B21">
         <v>1106</v>
       </c>
       <c r="C21" t="s">
-        <v>555</v>
-      </c>
-      <c r="D21" t="s">
-        <v>515</v>
+        <v>569</v>
+      </c>
+      <c r="D21" t="b">
+        <v>1</v>
       </c>
       <c r="E21" t="s">
-        <v>556</v>
-      </c>
-      <c r="F21">
-        <v>1</v>
-      </c>
-      <c r="G21" t="b">
+        <v>529</v>
+      </c>
+      <c r="F21" t="s">
+        <v>570</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="H21" t="b">
         <v>0</v>
       </c>
-      <c r="H21" t="s">
-        <v>557</v>
-      </c>
       <c r="I21" t="s">
-        <v>558</v>
+        <v>571</v>
       </c>
       <c r="J21" t="s">
-        <v>559</v>
+        <v>572</v>
       </c>
       <c r="K21" t="s">
-        <v>560</v>
+        <v>573</v>
       </c>
       <c r="L21" t="s">
-        <v>561</v>
+        <v>574</v>
       </c>
       <c r="M21" t="s">
-        <v>562</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13">
+        <v>575</v>
+      </c>
+      <c r="N21" t="s">
+        <v>576</v>
+      </c>
+    </row>
+    <row r="22" spans="1:14">
       <c r="A22" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B22">
         <v>1107</v>
       </c>
       <c r="C22" t="s">
-        <v>563</v>
-      </c>
-      <c r="D22" t="s">
-        <v>515</v>
+        <v>577</v>
+      </c>
+      <c r="D22" t="b">
+        <v>1</v>
       </c>
       <c r="E22" t="s">
-        <v>564</v>
-      </c>
-      <c r="F22">
-        <v>1</v>
-      </c>
-      <c r="G22" t="b">
+        <v>529</v>
+      </c>
+      <c r="F22" t="s">
+        <v>578</v>
+      </c>
+      <c r="G22">
+        <v>1</v>
+      </c>
+      <c r="H22" t="b">
         <v>0</v>
       </c>
-      <c r="H22" t="s">
-        <v>565</v>
-      </c>
       <c r="I22" t="s">
-        <v>566</v>
+        <v>579</v>
       </c>
       <c r="J22" t="s">
-        <v>567</v>
+        <v>580</v>
       </c>
       <c r="K22" t="s">
-        <v>568</v>
+        <v>581</v>
       </c>
       <c r="L22" t="s">
-        <v>569</v>
+        <v>582</v>
       </c>
       <c r="M22" t="s">
-        <v>570</v>
-      </c>
-    </row>
-    <row r="23" spans="1:13">
+        <v>583</v>
+      </c>
+      <c r="N22" t="s">
+        <v>584</v>
+      </c>
+    </row>
+    <row r="23" spans="1:14">
       <c r="A23" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B23">
         <v>1201</v>
       </c>
       <c r="C23" t="s">
-        <v>571</v>
-      </c>
-      <c r="D23" t="s">
-        <v>572</v>
+        <v>585</v>
+      </c>
+      <c r="D23" t="b">
+        <v>1</v>
       </c>
       <c r="E23" t="s">
-        <v>573</v>
-      </c>
-      <c r="F23">
-        <v>1</v>
-      </c>
-      <c r="G23" t="b">
+        <v>586</v>
+      </c>
+      <c r="F23" t="s">
+        <v>587</v>
+      </c>
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23" t="b">
         <v>0</v>
       </c>
-      <c r="H23" t="s">
-        <v>574</v>
-      </c>
       <c r="I23" t="s">
-        <v>575</v>
+        <v>588</v>
       </c>
       <c r="J23" t="s">
-        <v>576</v>
+        <v>589</v>
       </c>
       <c r="K23" t="s">
-        <v>577</v>
+        <v>590</v>
       </c>
       <c r="L23" t="s">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="M23" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13">
+        <v>592</v>
+      </c>
+      <c r="N23" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="24" spans="1:14">
       <c r="A24" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B24">
         <v>1202</v>
       </c>
       <c r="C24" t="s">
-        <v>580</v>
-      </c>
-      <c r="D24" t="s">
-        <v>572</v>
+        <v>594</v>
+      </c>
+      <c r="D24" t="b">
+        <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>581</v>
-      </c>
-      <c r="F24">
-        <v>1</v>
-      </c>
-      <c r="G24" t="b">
-        <v>1</v>
-      </c>
-      <c r="H24" t="s">
-        <v>582</v>
+        <v>586</v>
+      </c>
+      <c r="F24" t="s">
+        <v>595</v>
+      </c>
+      <c r="G24">
+        <v>1</v>
+      </c>
+      <c r="H24" t="b">
+        <v>1</v>
       </c>
       <c r="I24" t="s">
-        <v>583</v>
+        <v>596</v>
       </c>
       <c r="J24" t="s">
-        <v>584</v>
+        <v>597</v>
       </c>
       <c r="K24" t="s">
-        <v>585</v>
+        <v>598</v>
       </c>
       <c r="L24" t="s">
-        <v>586</v>
+        <v>599</v>
       </c>
       <c r="M24" t="s">
-        <v>587</v>
-      </c>
-    </row>
-    <row r="25" spans="1:13">
+        <v>600</v>
+      </c>
+      <c r="N24" t="s">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="25" spans="1:14">
       <c r="A25" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B25">
         <v>1203</v>
       </c>
       <c r="C25" t="s">
-        <v>588</v>
-      </c>
-      <c r="D25" t="s">
-        <v>572</v>
+        <v>602</v>
+      </c>
+      <c r="D25" t="b">
+        <v>1</v>
       </c>
       <c r="E25" t="s">
-        <v>589</v>
-      </c>
-      <c r="F25">
-        <v>1</v>
-      </c>
-      <c r="G25" t="b">
+        <v>586</v>
+      </c>
+      <c r="F25" t="s">
+        <v>603</v>
+      </c>
+      <c r="G25">
+        <v>1</v>
+      </c>
+      <c r="H25" t="b">
         <v>0</v>
       </c>
-      <c r="H25" t="s">
-        <v>590</v>
-      </c>
       <c r="I25" t="s">
+        <v>604</v>
+      </c>
+      <c r="J25" t="s">
         <v>52</v>
       </c>
-      <c r="J25" t="s">
-        <v>591</v>
-      </c>
       <c r="K25" t="s">
-        <v>592</v>
+        <v>605</v>
       </c>
       <c r="L25" t="s">
-        <v>593</v>
+        <v>606</v>
       </c>
       <c r="M25" t="s">
-        <v>594</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13">
+        <v>607</v>
+      </c>
+      <c r="N25" t="s">
+        <v>608</v>
+      </c>
+    </row>
+    <row r="26" spans="1:14">
       <c r="B26">
         <v>1301</v>
       </c>
       <c r="C26" t="s">
-        <v>595</v>
-      </c>
-      <c r="D26" t="s">
-        <v>596</v>
+        <v>609</v>
+      </c>
+      <c r="D26" t="b">
+        <v>1</v>
       </c>
       <c r="E26" t="s">
+        <v>610</v>
+      </c>
+      <c r="F26" t="s">
         <v>29</v>
       </c>
-      <c r="F26">
-        <v>1</v>
-      </c>
-      <c r="G26" t="b">
+      <c r="G26">
+        <v>1</v>
+      </c>
+      <c r="H26" t="b">
         <v>0</v>
       </c>
-      <c r="H26" t="s">
-        <v>597</v>
-      </c>
       <c r="I26" t="s">
-        <v>598</v>
+        <v>611</v>
       </c>
       <c r="J26" t="s">
-        <v>599</v>
+        <v>612</v>
       </c>
       <c r="K26" t="s">
-        <v>600</v>
+        <v>613</v>
       </c>
       <c r="L26" t="s">
-        <v>601</v>
+        <v>614</v>
       </c>
       <c r="M26" t="s">
-        <v>602</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13">
+        <v>615</v>
+      </c>
+      <c r="N26" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="27" spans="1:14">
       <c r="B27">
         <v>1302</v>
       </c>
       <c r="C27" t="s">
-        <v>603</v>
-      </c>
-      <c r="D27" t="s">
-        <v>596</v>
+        <v>617</v>
+      </c>
+      <c r="D27" t="b">
+        <v>1</v>
       </c>
       <c r="E27" t="s">
-        <v>604</v>
-      </c>
-      <c r="F27">
-        <v>1</v>
-      </c>
-      <c r="G27" t="b">
+        <v>610</v>
+      </c>
+      <c r="F27" t="s">
+        <v>618</v>
+      </c>
+      <c r="G27">
+        <v>1</v>
+      </c>
+      <c r="H27" t="b">
         <v>0</v>
       </c>
-      <c r="H27" t="s">
-        <v>605</v>
-      </c>
       <c r="I27" t="s">
-        <v>606</v>
+        <v>619</v>
       </c>
       <c r="J27" t="s">
-        <v>607</v>
+        <v>620</v>
       </c>
       <c r="K27" t="s">
-        <v>608</v>
+        <v>621</v>
       </c>
       <c r="L27" t="s">
-        <v>609</v>
+        <v>622</v>
       </c>
       <c r="M27" t="s">
-        <v>610</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13">
+        <v>623</v>
+      </c>
+      <c r="N27" t="s">
+        <v>624</v>
+      </c>
+    </row>
+    <row r="28" spans="1:14">
       <c r="A28" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B28">
         <v>1303</v>
       </c>
       <c r="C28" t="s">
-        <v>611</v>
-      </c>
-      <c r="D28" t="s">
-        <v>596</v>
+        <v>625</v>
+      </c>
+      <c r="D28" t="b">
+        <v>1</v>
       </c>
       <c r="E28" t="s">
+        <v>610</v>
+      </c>
+      <c r="F28" t="s">
         <v>20</v>
       </c>
-      <c r="F28">
-        <v>1</v>
-      </c>
-      <c r="G28" t="b">
+      <c r="G28">
+        <v>1</v>
+      </c>
+      <c r="H28" t="b">
         <v>0</v>
       </c>
-      <c r="H28" t="s">
-        <v>612</v>
-      </c>
       <c r="I28" t="s">
-        <v>613</v>
+        <v>626</v>
       </c>
       <c r="J28" t="s">
-        <v>614</v>
+        <v>627</v>
       </c>
       <c r="K28" t="s">
-        <v>615</v>
+        <v>628</v>
       </c>
       <c r="L28" t="s">
-        <v>616</v>
+        <v>629</v>
       </c>
       <c r="M28" t="s">
-        <v>617</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13">
+        <v>630</v>
+      </c>
+      <c r="N28" t="s">
+        <v>631</v>
+      </c>
+    </row>
+    <row r="29" spans="1:14">
       <c r="A29" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B29">
         <v>1304</v>
       </c>
       <c r="C29" t="s">
-        <v>618</v>
-      </c>
-      <c r="D29" t="s">
-        <v>596</v>
+        <v>632</v>
+      </c>
+      <c r="D29" t="b">
+        <v>1</v>
       </c>
       <c r="E29" t="s">
+        <v>610</v>
+      </c>
+      <c r="F29" t="s">
         <v>11</v>
       </c>
-      <c r="F29">
-        <v>1</v>
-      </c>
-      <c r="G29" t="b">
+      <c r="G29">
+        <v>1</v>
+      </c>
+      <c r="H29" t="b">
         <v>0</v>
       </c>
-      <c r="H29" t="s">
-        <v>619</v>
-      </c>
       <c r="I29" t="s">
-        <v>620</v>
+        <v>633</v>
       </c>
       <c r="J29" t="s">
-        <v>621</v>
+        <v>634</v>
       </c>
       <c r="K29" t="s">
-        <v>622</v>
+        <v>635</v>
       </c>
       <c r="L29" t="s">
-        <v>623</v>
+        <v>636</v>
       </c>
       <c r="M29" t="s">
-        <v>624</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13">
+        <v>637</v>
+      </c>
+      <c r="N29" t="s">
+        <v>638</v>
+      </c>
+    </row>
+    <row r="30" spans="1:14">
       <c r="A30" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B30">
         <v>1305</v>
       </c>
       <c r="C30" t="s">
-        <v>625</v>
-      </c>
-      <c r="D30" t="s">
-        <v>596</v>
+        <v>639</v>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
       </c>
       <c r="E30" t="s">
+        <v>610</v>
+      </c>
+      <c r="F30" t="s">
         <v>2</v>
       </c>
-      <c r="F30">
-        <v>1</v>
-      </c>
-      <c r="G30" t="b">
+      <c r="G30">
+        <v>1</v>
+      </c>
+      <c r="H30" t="b">
         <v>0</v>
       </c>
-      <c r="H30" t="s">
-        <v>626</v>
-      </c>
       <c r="I30" t="s">
-        <v>627</v>
+        <v>640</v>
       </c>
       <c r="J30" t="s">
-        <v>628</v>
+        <v>641</v>
       </c>
       <c r="K30" t="s">
-        <v>629</v>
+        <v>642</v>
       </c>
       <c r="L30" t="s">
-        <v>630</v>
+        <v>643</v>
       </c>
       <c r="M30" t="s">
-        <v>631</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13">
+        <v>644</v>
+      </c>
+      <c r="N30" t="s">
+        <v>645</v>
+      </c>
+    </row>
+    <row r="31" spans="1:14">
       <c r="A31" t="s">
-        <v>381</v>
+        <v>392</v>
       </c>
       <c r="B31">
         <v>1306</v>
       </c>
       <c r="C31" t="s">
-        <v>632</v>
-      </c>
-      <c r="D31" t="s">
-        <v>596</v>
+        <v>646</v>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
       </c>
       <c r="E31" t="s">
-        <v>263</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
-      </c>
-      <c r="G31" t="b">
+        <v>610</v>
+      </c>
+      <c r="F31" t="s">
+        <v>273</v>
+      </c>
+      <c r="G31">
+        <v>1</v>
+      </c>
+      <c r="H31" t="b">
         <v>0</v>
       </c>
-      <c r="H31" t="s">
-        <v>633</v>
-      </c>
       <c r="I31" t="s">
-        <v>634</v>
+        <v>647</v>
       </c>
       <c r="J31" t="s">
-        <v>635</v>
+        <v>648</v>
       </c>
       <c r="K31" t="s">
-        <v>636</v>
+        <v>649</v>
       </c>
       <c r="L31" t="s">
-        <v>637</v>
+        <v>650</v>
       </c>
       <c r="M31" t="s">
-        <v>638</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13">
+        <v>651</v>
+      </c>
+      <c r="N31" t="s">
+        <v>652</v>
+      </c>
+    </row>
+    <row r="32" spans="1:14">
       <c r="B32">
         <v>1011</v>
       </c>
       <c r="C32" t="s">
-        <v>639</v>
-      </c>
-      <c r="D32" t="s">
-        <v>437</v>
+        <v>653</v>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
       </c>
       <c r="E32" t="s">
-        <v>640</v>
-      </c>
-      <c r="F32">
-        <v>1</v>
-      </c>
-      <c r="G32" t="b">
+        <v>451</v>
+      </c>
+      <c r="F32" t="s">
+        <v>654</v>
+      </c>
+      <c r="G32">
+        <v>1</v>
+      </c>
+      <c r="H32" t="b">
         <v>0</v>
       </c>
-      <c r="H32" t="s">
-        <v>641</v>
-      </c>
       <c r="I32" t="s">
-        <v>642</v>
+        <v>655</v>
       </c>
       <c r="J32" t="s">
-        <v>643</v>
+        <v>656</v>
       </c>
       <c r="K32" t="s">
-        <v>644</v>
+        <v>657</v>
       </c>
       <c r="L32" t="s">
-        <v>645</v>
+        <v>658</v>
       </c>
       <c r="M32" t="s">
-        <v>646</v>
+        <v>659</v>
+      </c>
+      <c r="N32" t="s">
+        <v>660</v>
       </c>
     </row>
   </sheetData>
+  <conditionalFormatting sqref="D$1:D$1048576">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="between" text="FALSE">
+      <formula>NOT(ISERROR(SEARCH("FALSE",D1)))</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1654" uniqueCount="959">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="967">
   <si>
     <t>Dog</t>
   </si>
@@ -2916,12 +2916,36 @@
   </si>
   <si>
     <t>存在可领取奖励筹码时使用</t>
+  </si>
+  <si>
+    <t>ChipLedgerCredits</t>
+  </si>
+  <si>
+    <t>累计筹码入账</t>
+  </si>
+  <si>
+    <t>STAT_CHIP_LEDGER_CREDITS</t>
+  </si>
+  <si>
+    <t>用于跨设备恢复当前筹码余额的只增账本；包含初始筹码、正常游戏入账及退款补偿；首次启用时以当前本地余额作为迁移入账基线；Debug和Mock不记录</t>
+  </si>
+  <si>
+    <t>ChipLedgerDebits</t>
+  </si>
+  <si>
+    <t>累计筹码支出</t>
+  </si>
+  <si>
+    <t>STAT_CHIP_LEDGER_DEBITS</t>
+  </si>
+  <si>
+    <t>用于跨设备恢复当前筹码余额的只增账本；记录正常游戏中的全部筹码支出；Debug和Mock不记录；当前余额取累计入账减累计支出且不低于0</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="4">
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
@@ -2930,166 +2954,166 @@
   </numFmts>
   <fonts count="22">
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF1C1E21"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <color rgb="FF1C1E21"/>
+      <sz val="12"/>
     </font>
     <font>
-      <b/>
-      <sz val="12"/>
-      <color theme="1"/>
       <name val="微软雅黑"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="12"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF0000FF"/>
+      <sz val="11"/>
+      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF800080"/>
+      <sz val="11"/>
+      <u/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFF0000"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="18"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <i val="1"/>
+      <color rgb="FF7F7F7F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="15"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="13"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
       <name val="宋体"/>
       <charset val="134"/>
+      <b val="1"/>
+      <color theme="3"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF3F3F76"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FF3F3F3F"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FFFA7D00"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <b val="1"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF006100"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C0006"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color rgb="FF9C6500"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="0"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="0"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="0"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3398,148 +3422,148 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="false" applyFont="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="false" applyFill="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="4" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="6" applyNumberFormat="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="7" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="8" applyNumberFormat="false" applyFill="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3547,29 +3571,29 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="true" applyFill="true" applyAlignment="true">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment horizontal="center" vertical="center" wrapText="true"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="true" applyAlignment="true">
+      <alignment vertical="center" wrapText="true"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -3822,8 +3846,8 @@
       </border>
     </dxf>
   </dxfs>
-  <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
-    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
+  <tableStyles count="2" defaultPivotStyle="PivotStylePreset2_Accent1" defaultTableStyle="TableStylePreset3_Accent1">
+    <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7">
       <tableStyleElement type="wholeTable" dxfId="7"/>
       <tableStyleElement type="headerRow" dxfId="6"/>
       <tableStyleElement type="totalRow" dxfId="5"/>
@@ -3832,7 +3856,7 @@
       <tableStyleElement type="firstRowStripe" dxfId="2"/>
       <tableStyleElement type="firstColumnStripe" dxfId="1"/>
     </tableStyle>
-    <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
+    <tableStyle name="PivotStylePreset2_Accent1" pivot="0" count="10">
       <tableStyleElement type="headerRow" dxfId="17"/>
       <tableStyleElement type="totalRow" dxfId="16"/>
       <tableStyleElement type="firstRowStripe" dxfId="15"/>
@@ -3854,7 +3878,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="WPS">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WPS">
   <a:themeElements>
     <a:clrScheme name="WPS">
       <a:dk1>
@@ -4097,6 +4121,7 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
@@ -4492,18 +4517,18 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J62"/>
+  <dimension ref="A1:J64"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
-    <col min="1" max="1" width="6.91666666666667" customWidth="1"/>
-    <col min="2" max="2" width="11.5833333333333" customWidth="1"/>
-    <col min="3" max="3" width="30.9166666666667" customWidth="1"/>
-    <col min="4" max="5" width="22.8333333333333" customWidth="1"/>
-    <col min="6" max="6" width="14.9166666666667" customWidth="1"/>
-    <col min="7" max="7" width="13.6666666666667" customWidth="1"/>
-    <col min="8" max="8" width="51" customWidth="1"/>
-    <col min="9" max="9" width="20.5833333333333" customWidth="1"/>
-    <col min="10" max="10" width="53.0833333333333" customWidth="1"/>
+    <col customWidth="true" max="1" min="1" width="6.91666666666667"/>
+    <col customWidth="true" max="2" min="2" width="11.5833333333333"/>
+    <col customWidth="true" max="3" min="3" width="30.9166666666667"/>
+    <col customWidth="true" max="5" min="4" width="22.8333333333333"/>
+    <col customWidth="true" max="6" min="6" width="14.9166666666667"/>
+    <col customWidth="true" max="7" min="7" width="13.6666666666667"/>
+    <col customWidth="true" max="8" min="8" width="51"/>
+    <col customWidth="true" max="9" min="9" width="20.5833333333333"/>
+    <col customWidth="true" max="10" min="10" width="53.0833333333333"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -4570,7 +4595,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="3" s="1" customFormat="1" ht="89" customHeight="1" spans="1:10">
+    <row r="3" spans="1:10" s="1" customFormat="true" ht="89" customHeight="true">
       <c r="A3" s="1" t="s">
         <v>110</v>
       </c>
@@ -4820,7 +4845,7 @@
         <v>711</v>
       </c>
       <c r="I10" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10" t="s">
         <v>712</v>
@@ -6449,6 +6474,70 @@
       </c>
       <c r="J62" t="s">
         <v>915</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="s">
+        <v>392</v>
+      </c>
+      <c r="B63">
+        <v>1062</v>
+      </c>
+      <c r="C63" t="s">
+        <v>959</v>
+      </c>
+      <c r="D63" t="s">
+        <v>960</v>
+      </c>
+      <c r="E63" t="b">
+        <v>1</v>
+      </c>
+      <c r="F63" t="s">
+        <v>710</v>
+      </c>
+      <c r="G63" t="s">
+        <v>688</v>
+      </c>
+      <c r="H63" t="s">
+        <v>961</v>
+      </c>
+      <c r="I63" t="b">
+        <v>1</v>
+      </c>
+      <c r="J63" t="s">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="s">
+        <v>392</v>
+      </c>
+      <c r="B64">
+        <v>1063</v>
+      </c>
+      <c r="C64" t="s">
+        <v>963</v>
+      </c>
+      <c r="D64" t="s">
+        <v>964</v>
+      </c>
+      <c r="E64" t="b">
+        <v>1</v>
+      </c>
+      <c r="F64" t="s">
+        <v>710</v>
+      </c>
+      <c r="G64" t="s">
+        <v>688</v>
+      </c>
+      <c r="H64" t="s">
+        <v>965</v>
+      </c>
+      <c r="I64" t="b">
+        <v>1</v>
+      </c>
+      <c r="J64" t="s">
+        <v>966</v>
       </c>
     </row>
   </sheetData>

--- a/luban-excels/bak/xlsx/Main.xlsx
+++ b/luban-excels/bak/xlsx/Main.xlsx
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="967" uniqueCount="967">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="971" uniqueCount="971">
   <si>
     <t>Dog</t>
   </si>
@@ -2940,6 +2940,18 @@
   </si>
   <si>
     <t>用于跨设备恢复当前筹码余额的只增账本；记录正常游戏中的全部筹码支出；Debug和Mock不记录；当前余额取累计入账减累计支出且不低于0</t>
+  </si>
+  <si>
+    <t>InitialRewardSequenceProgress</t>
+  </si>
+  <si>
+    <t>首轮奖励序列进度</t>
+  </si>
+  <si>
+    <t>STAT_INITIAL_REWARD_SEQUENCE_PROGRESS</t>
+  </si>
+  <si>
+    <t>记录玩家已正式完成的首轮奖励序列最高 ProgressCheckpoint；Steam奖励、Fallback和本地奖励只要正式领取并推进当前Schedule均记录；LateSteam不推进；用于跨设备恢复首轮奖励序列进度；Debug和Mock不记录</t>
   </si>
 </sst>
 </file>
@@ -4517,7 +4529,7 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:J64"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr defaultColWidth="7.5" defaultRowHeight="17.4"/>
   <cols>
     <col customWidth="true" max="1" min="1" width="6.91666666666667"/>
@@ -6538,6 +6550,35 @@
       </c>
       <c r="J64" t="s">
         <v>966</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="B65">
+        <v>1064</v>
+      </c>
+      <c r="C65" t="s">
+        <v>967</v>
+      </c>
+      <c r="D65" t="s">
+        <v>968</v>
+      </c>
+      <c r="E65" t="b">
+        <v>1</v>
+      </c>
+      <c r="F65" t="s">
+        <v>693</v>
+      </c>
+      <c r="G65" t="s">
+        <v>868</v>
+      </c>
+      <c r="H65" t="s">
+        <v>969</v>
+      </c>
+      <c r="I65" t="b">
+        <v>1</v>
+      </c>
+      <c r="J65" t="s">
+        <v>970</v>
       </c>
     </row>
   </sheetData>
